--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1870,7 +1870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3566,268 +3566,659 @@
     <row r="107">
       <c r="A107" s="67" t="inlineStr">
         <is>
-          <t>Achiziție MF + amortizare</t>
+          <t>Leasing financiar auto (limitări TVA/amortizare)</t>
         </is>
       </c>
       <c r="B107" s="67" t="inlineStr">
         <is>
-          <t>Achiziție mijloc fix intern + amortizare liniară</t>
+          <t>Leasing financiar auto: avans, intrare, rate, corecții TVA 50%, amortizare plafonată</t>
         </is>
       </c>
       <c r="C107" s="67" t="inlineStr">
         <is>
-          <t>Titlu prea generic: concura cu fluxul de achiziție intracomunitară / import de mijloc fix, care tratează alt regim. Precizarea „intern” le separă.</t>
+          <t>MOD_LEASING_FIN a devenit modul intern, cu foile Declarații/Reguli/Jurnale/NotaExport în acest workbook. Metadatele vechi trimiteau la un fișier separat și la un status „EXEMPLU EXTERN” care nu mai sunt adevărate.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="67" t="inlineStr">
         <is>
-          <t>F-26 - Achiziție mijloc fix + amortizare</t>
+          <t>Template_leasing_financiar_auto.xlsx</t>
         </is>
       </c>
       <c r="B108" s="67" t="inlineStr">
         <is>
-          <t>F-204 — Achiziție mijloc fix intern + amortizare liniară</t>
+          <t>Declarații_LEASING_FIN, Reguli_, Jurnale_, NotaExport_</t>
         </is>
       </c>
       <c r="C108" s="67" t="inlineStr">
         <is>
-          <t>Idem, pe titlul blocului de monografie.</t>
+          <t>MOD_LEASING_FIN a devenit modul intern, cu foile Declarații/Reguli/Jurnale/NotaExport în acest workbook. Metadatele vechi trimiteau la un fișier separat și la un status „EXEMPLU EXTERN” care nu mai sunt adevărate.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="67" t="inlineStr">
         <is>
-          <t>Fluxuri: 38/38 detaliate. Matrice Tier A: acoperire completă.</t>
+          <t>Pe contract + lună — fișier separat</t>
         </is>
       </c>
       <c r="B109" s="67" t="inlineStr">
         <is>
-          <t>Fluxuri: 60/60 detaliate. Matrice Tier A: acoperire completă.</t>
+          <t>Pe contract + lunar</t>
         </is>
       </c>
       <c r="C109" s="67" t="inlineStr">
         <is>
-          <t>Numărătoare depășită: sunt 60 de fluxuri după trainingurile 2 și 3 și după cele două contopiri. Textul original e păstrat în foaia Istoric.</t>
+          <t>MOD_LEASING_FIN a devenit modul intern, cu foile Declarații/Reguli/Jurnale/NotaExport în acest workbook. Metadatele vechi trimiteau la un fișier separat și la un status „EXEMPLU EXTERN” care nu mai sunt adevărate.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="67" t="inlineStr">
         <is>
-          <t>~38 fluxuri × pași, tabelar cu note complete + coloană Declarativ</t>
+          <t>Pe contract + lună</t>
         </is>
       </c>
       <c r="B110" s="67" t="inlineStr">
         <is>
-          <t>60 fluxuri × pași, tabelar cu note complete + coloană Declarativ</t>
+          <t>Pe contract + lunar</t>
         </is>
       </c>
       <c r="C110" s="67" t="inlineStr">
         <is>
-          <t>Idem — descrierea structurii workbook-ului anunța 38 de fluxuri.</t>
+          <t>MOD_LEASING_FIN a devenit modul intern, cu foile Declarații/Reguli/Jurnale/NotaExport în acest workbook. Metadatele vechi trimiteau la un fișier separat și la un status „EXEMPLU EXTERN” care nu mai sunt adevărate.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="67" t="inlineStr">
         <is>
-          <t>245+ rânduri, cu 3 coloane noi: Analitice recomandate · Factor · Flux (pas)</t>
+          <t>F-26 + F-28 + reeval</t>
         </is>
       </c>
       <c r="B111" s="67" t="inlineStr">
         <is>
-          <t>270+ rânduri, cu 3 coloane noi: Analitice recomandate · Factor · Flux (pas)</t>
+          <t>F-50</t>
         </is>
       </c>
       <c r="C111" s="67" t="inlineStr">
         <is>
-          <t>Planul are acum 270+ rânduri, după adăugarea conturilor care lipseau (1011, 1012, 1171, 1174, 2812, 6583 ș.a.).</t>
+          <t>MOD_LEASING_FIN a devenit modul intern, cu foile Declarații/Reguli/Jurnale/NotaExport în acest workbook. Metadatele vechi trimiteau la un fișier separat și la un status „EXEMPLU EXTERN” care nu mai sunt adevărate.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="67" t="inlineStr">
         <is>
-          <t>Ilustrativ (sume descriptive)</t>
+          <t>Contract, Scadențar, Regim vehicul, Curs BNR — vezi Template_leasing_financiar_auto</t>
         </is>
       </c>
       <c r="B112" s="67" t="inlineStr">
         <is>
-          <t>F-50 plafon 1.500 lei/lună; F-51 reluare 7812</t>
+          <t>Valoare contract, avans, rată, dobândă, comision, CASCO, regim vehicul, durată</t>
         </is>
       </c>
       <c r="C112" s="67" t="inlineStr">
         <is>
-          <t>Marcajul PARȚIAL de la 681/781 era corect când sumele erau descriptive. Acum 681 și 781 au cifre reale în F-50 (plafonul de 1.500 lei/lună) și F-51 (reluarea prin 7812), deci nota nu mai descrie realitatea.</t>
+          <t>MOD_LEASING_FIN a devenit modul intern, cu foile Declarații/Reguli/Jurnale/NotaExport în acest workbook. Metadatele vechi trimiteau la un fișier separat și la un status „EXEMPLU EXTERN” care nu mai sunt adevărate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="67" t="inlineStr">
+        <is>
+          <t>MIXT/EXCLUSIV/EXCEPTAT; Capitalizare vs Cheltuială TVA neded.</t>
+        </is>
+      </c>
+      <c r="B113" s="67" t="inlineStr">
+        <is>
+          <t>MIXT 50% / EXCLUSIV 100% / EXCEPTAT; capitalizare vs. cheltuială pentru TVA nededusă</t>
+        </is>
+      </c>
+      <c r="C113" s="67" t="inlineStr">
+        <is>
+          <t>MOD_LEASING_FIN a devenit modul intern, cu foile Declarații/Reguli/Jurnale/NotaExport în acest workbook. Metadatele vechi trimiteau la un fișier separat și la un status „EXEMPLU EXTERN” care nu mai sunt adevărate.</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="36" t="inlineStr">
-        <is>
-          <t>6. Titluri și note de secțiune, scoase la reordonare</t>
+      <c r="A114" s="67" t="inlineStr">
+        <is>
+          <t>B1–B7 pe momente — EXEMPLU EXTERN complet</t>
+        </is>
+      </c>
+      <c r="B114" s="67" t="inlineStr">
+        <is>
+          <t>B1 Avans; B2 TVA avans; B3 Intrare + 167; B4 Stingere avans; B5 Factura lunară; B6 Corecție TVA 50%; B7 Limitare 50% cheltuieli; B8 Amortizare</t>
+        </is>
+      </c>
+      <c r="C114" s="67" t="inlineStr">
+        <is>
+          <t>MOD_LEASING_FIN a devenit modul intern, cu foile Declarații/Reguli/Jurnale/NotaExport în acest workbook. Metadatele vechi trimiteau la un fișier separat și la un status „EXEMPLU EXTERN” care nu mai sunt adevărate.</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="62" t="inlineStr">
-        <is>
-          <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
+      <c r="A115" s="67" t="inlineStr">
+        <is>
+          <t>Salarii complete (exemplu extern cifrat)</t>
+        </is>
+      </c>
+      <c r="B115" s="67" t="inlineStr">
+        <is>
+          <t>B1 Plata avansului; B2 Costurile lunii; B3 Plăți (net, taxe, CAM)</t>
+        </is>
+      </c>
+      <c r="C115" s="67" t="inlineStr">
+        <is>
+          <t>Modulul a devenit intern, cu foile Declarații/Reguli/(Registru)/Jurnale/NotaExport în acest workbook. Cifrele lui sunt verificate contra fișierului extern, care rămâne în surse/module-externe/ doar ca referință.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="67" t="inlineStr">
         <is>
-          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
+          <t>Salarii AS Kids - 31.07.2026.xlsx</t>
+        </is>
+      </c>
+      <c r="B116" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_SALARII, Reguli_SALARII, Jurnale_SALARII, NotaExport_SALARII</t>
+        </is>
+      </c>
+      <c r="C116" s="67" t="inlineStr">
+        <is>
+          <t>Modulul a devenit intern, cu foile Declarații/Reguli/(Registru)/Jurnale/NotaExport în acest workbook. Cifrele lui sunt verificate contra fișierului extern, care rămâne în surse/module-externe/ doar ca referință.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="67" t="inlineStr">
         <is>
-          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
+          <t>Brut, Tichete, Avans, Angajat, Luna — vezi fișierul Salarii AS Kids</t>
+        </is>
+      </c>
+      <c r="B117" s="67" t="inlineStr">
+        <is>
+          <t>Brut, tichete, avans, pe angajat; cotele CAS/CASS/impozit/CAM</t>
+        </is>
+      </c>
+      <c r="C117" s="67" t="inlineStr">
+        <is>
+          <t>Modulul a devenit intern, cu foile Declarații/Reguli/(Registru)/Jurnale/NotaExport în acest workbook. Cifrele lui sunt verificate contra fișierului extern, care rămâne în surse/module-externe/ doar ca referință.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="67" t="inlineStr">
         <is>
-          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
+          <t>B1 Costuri; B2 Plăți net+taxe; B3 Tichete — EXEMPLU EXTERN complet</t>
+        </is>
+      </c>
+      <c r="B118" s="67" t="inlineStr">
+        <is>
+          <t>B1 Plata avansului; B2 Costurile lunii; B3 Plăți (net, taxe, CAM)</t>
+        </is>
+      </c>
+      <c r="C118" s="67" t="inlineStr">
+        <is>
+          <t>Modulul a devenit intern, cu foile Declarații/Reguli/(Registru)/Jurnale/NotaExport în acest workbook. Cifrele lui sunt verificate contra fișierului extern, care rămâne în surse/module-externe/ doar ca referință.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="67" t="inlineStr">
         <is>
-          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+          <t>Lunar — fișier separat</t>
+        </is>
+      </c>
+      <c r="B119" s="67" t="inlineStr">
+        <is>
+          <t>Lunar, pe registru de angajați</t>
+        </is>
+      </c>
+      <c r="C119" s="67" t="inlineStr">
+        <is>
+          <t>Modulul a devenit intern, cu foile Declarații/Reguli/(Registru)/Jurnale/NotaExport în acest workbook. Cifrele lui sunt verificate contra fișierului extern, care rămâne în surse/module-externe/ doar ca referință.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="67" t="inlineStr">
         <is>
-          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+          <t>Lunar + plăți</t>
+        </is>
+      </c>
+      <c r="B120" s="67" t="inlineStr">
+        <is>
+          <t>Lunar, pe registru de angajați</t>
+        </is>
+      </c>
+      <c r="C120" s="67" t="inlineStr">
+        <is>
+          <t>Modulul a devenit intern, cu foile Declarații/Reguli/(Registru)/Jurnale/NotaExport în acest workbook. Cifrele lui sunt verificate contra fișierului extern, care rămâne în surse/module-externe/ doar ca referință.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="67" t="inlineStr">
         <is>
+          <t>Deconturi cheltuieli + avansuri</t>
+        </is>
+      </c>
+      <c r="B121" s="67" t="inlineStr">
+        <is>
+          <t>B1 Avans; B2 Cheltuieli + TVA; B3 Regularizare avans; B4 Plată / restituire</t>
+        </is>
+      </c>
+      <c r="C121" s="67" t="inlineStr">
+        <is>
+          <t>Modulul a devenit intern, cu foile Declarații/Reguli/(Registru)/Jurnale/NotaExport în acest workbook. Cifrele lui sunt verificate contra fișierului extern, care rămâne în surse/module-externe/ doar ca referință.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="67" t="inlineStr">
+        <is>
+          <t>Deconturi AS Kids - ….xlsx</t>
+        </is>
+      </c>
+      <c r="B122" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_DECONT, Reguli_DECONT, Registru_DECONT, Jurnale_DECONT, NotaExport_DECONT</t>
+        </is>
+      </c>
+      <c r="C122" s="67" t="inlineStr">
+        <is>
+          <t>Modulul a devenit intern, cu foile Declarații/Reguli/(Registru)/Jurnale/NotaExport în acest workbook. Cifrele lui sunt verificate contra fișierului extern, care rămâne în surse/module-externe/ doar ca referință.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="67" t="inlineStr">
+        <is>
+          <t>Linii decont, Titular, Avans, Cotă TVA — vezi Deconturi AS Kids</t>
+        </is>
+      </c>
+      <c r="B123" s="67" t="inlineStr">
+        <is>
+          <t>Linii de decont (furnizor, sumă, natură, tip document, CUI), avans, cote</t>
+        </is>
+      </c>
+      <c r="C123" s="67" t="inlineStr">
+        <is>
+          <t>Modulul a devenit intern, cu foile Declarații/Reguli/(Registru)/Jurnale/NotaExport în acest workbook. Cifrele lui sunt verificate contra fișierului extern, care rămâne în surse/module-externe/ doar ca referință.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="67" t="inlineStr">
+        <is>
+          <t>B1 Avans; B2 Cheltuieli; B3 Regularizare; B4 Plată — EXEMPLU EXTERN complet</t>
+        </is>
+      </c>
+      <c r="B124" s="67" t="inlineStr">
+        <is>
+          <t>B1 Avans; B2 Cheltuieli + TVA; B3 Regularizare avans; B4 Plată / restituire</t>
+        </is>
+      </c>
+      <c r="C124" s="67" t="inlineStr">
+        <is>
+          <t>Modulul a devenit intern, cu foile Declarații/Reguli/(Registru)/Jurnale/NotaExport în acest workbook. Cifrele lui sunt verificate contra fișierului extern, care rămâne în surse/module-externe/ doar ca referință.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="67" t="inlineStr">
+        <is>
+          <t>La deconturi — fișier separat</t>
+        </is>
+      </c>
+      <c r="B125" s="67" t="inlineStr">
+        <is>
+          <t>Pe decont</t>
+        </is>
+      </c>
+      <c r="C125" s="67" t="inlineStr">
+        <is>
+          <t>Modulul a devenit intern, cu foile Declarații/Reguli/(Registru)/Jurnale/NotaExport în acest workbook. Cifrele lui sunt verificate contra fișierului extern, care rămâne în surse/module-externe/ doar ca referință.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="67" t="inlineStr">
+        <is>
+          <t>F-35 + deplasări</t>
+        </is>
+      </c>
+      <c r="B126" s="67" t="inlineStr">
+        <is>
+          <t>F-35</t>
+        </is>
+      </c>
+      <c r="C126" s="67" t="inlineStr">
+        <is>
+          <t>Modulul a devenit intern, cu foile Declarații/Reguli/(Registru)/Jurnale/NotaExport în acest workbook. Cifrele lui sunt verificate contra fișierului extern, care rămâne în surse/module-externe/ doar ca referință.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="67" t="inlineStr">
+        <is>
+          <t>Platitor TVA, % ded. vehicule</t>
+        </is>
+      </c>
+      <c r="B127" s="67" t="inlineStr">
+        <is>
+          <t>Plătitor de TVA; % deducere vehicule; matricea document × CUI</t>
+        </is>
+      </c>
+      <c r="C127" s="67" t="inlineStr">
+        <is>
+          <t>Modulul a devenit intern, cu foile Declarații/Reguli/(Registru)/Jurnale/NotaExport în acest workbook. Cifrele lui sunt verificate contra fișierului extern, care rămâne în surse/module-externe/ doar ca referință.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="67" t="inlineStr">
+        <is>
+          <t>F-32 ilustrativ; modul extern Salarii e cifrat</t>
+        </is>
+      </c>
+      <c r="B128" s="67" t="inlineStr">
+        <is>
+          <t>Lanțul complet în MOD_SALARII, cu cifre verificate contra statului real din 31.07.2026; F-52/F-58 acoperă ipostaza de cost capitalizat</t>
+        </is>
+      </c>
+      <c r="C128" s="67" t="inlineStr">
+        <is>
+          <t>Marcajul PARȚIAL era corect cât timp salariile existau doar ca exemplu extern cifrat. MOD_SALARII acoperă acum lanțul complet (brut → CAS/CASS/impozit → net → CAM → tichete → plăți), cu cifre verificate contra statului real din 31.07.2026. Limitările rămase sunt declarate în Reguli_SALARII, tabelul C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="67" t="inlineStr">
+        <is>
+          <t>Idem F-32 / modul extern</t>
+        </is>
+      </c>
+      <c r="B129" s="67" t="inlineStr">
+        <is>
+          <t>MOD_SALARII acoperă 641 salarii, 642 tichete și 646 CAM; limitările rămase sunt declarate în Reguli_SALARII, tabelul C</t>
+        </is>
+      </c>
+      <c r="C129" s="67" t="inlineStr">
+        <is>
+          <t>Marcajul PARȚIAL era corect cât timp salariile existau doar ca exemplu extern cifrat. MOD_SALARII acoperă acum lanțul complet (brut → CAS/CASS/impozit → net → CAM → tichete → plăți), cu cifre verificate contra statului real din 31.07.2026. Limitările rămase sunt declarate în Reguli_SALARII, tabelul C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="67" t="inlineStr">
+        <is>
+          <t>Achiziție MF + amortizare</t>
+        </is>
+      </c>
+      <c r="B130" s="67" t="inlineStr">
+        <is>
+          <t>Achiziție mijloc fix intern + amortizare liniară</t>
+        </is>
+      </c>
+      <c r="C130" s="67" t="inlineStr">
+        <is>
+          <t>Titlu prea generic: concura cu fluxul de achiziție intracomunitară / import de mijloc fix, care tratează alt regim. Precizarea „intern” le separă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="67" t="inlineStr">
+        <is>
+          <t>F-26 - Achiziție mijloc fix + amortizare</t>
+        </is>
+      </c>
+      <c r="B131" s="67" t="inlineStr">
+        <is>
+          <t>F-204 — Achiziție mijloc fix intern + amortizare liniară</t>
+        </is>
+      </c>
+      <c r="C131" s="67" t="inlineStr">
+        <is>
+          <t>Idem, pe titlul blocului de monografie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="67" t="inlineStr">
+        <is>
+          <t>Fluxuri: 38/38 detaliate. Matrice Tier A: acoperire completă.</t>
+        </is>
+      </c>
+      <c r="B132" s="67" t="inlineStr">
+        <is>
+          <t>Fluxuri: 60/60 detaliate. Matrice Tier A: acoperire completă.</t>
+        </is>
+      </c>
+      <c r="C132" s="67" t="inlineStr">
+        <is>
+          <t>Numărătoare depășită: sunt 60 de fluxuri după trainingurile 2 și 3 și după cele două contopiri. Textul original e păstrat în foaia Istoric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="67" t="inlineStr">
+        <is>
+          <t>~38 fluxuri × pași, tabelar cu note complete + coloană Declarativ</t>
+        </is>
+      </c>
+      <c r="B133" s="67" t="inlineStr">
+        <is>
+          <t>60 fluxuri × pași, tabelar cu note complete + coloană Declarativ</t>
+        </is>
+      </c>
+      <c r="C133" s="67" t="inlineStr">
+        <is>
+          <t>Idem — descrierea structurii workbook-ului anunța 38 de fluxuri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="67" t="inlineStr">
+        <is>
+          <t>245+ rânduri, cu 3 coloane noi: Analitice recomandate · Factor · Flux (pas)</t>
+        </is>
+      </c>
+      <c r="B134" s="67" t="inlineStr">
+        <is>
+          <t>270+ rânduri, cu 3 coloane noi: Analitice recomandate · Factor · Flux (pas)</t>
+        </is>
+      </c>
+      <c r="C134" s="67" t="inlineStr">
+        <is>
+          <t>Planul are acum 270+ rânduri, după adăugarea conturilor care lipseau (1011, 1012, 1171, 1174, 2812, 6583 ș.a.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="67" t="inlineStr">
+        <is>
+          <t>Ilustrativ (sume descriptive)</t>
+        </is>
+      </c>
+      <c r="B135" s="67" t="inlineStr">
+        <is>
+          <t>F-50 plafon 1.500 lei/lună; F-51 reluare 7812</t>
+        </is>
+      </c>
+      <c r="C135" s="67" t="inlineStr">
+        <is>
+          <t>Marcajul PARȚIAL de la 681/781 era corect când sumele erau descriptive. Acum 681 și 781 au cifre reale în F-50 (plafonul de 1.500 lei/lună) și F-51 (reluarea prin 7812), deci nota nu mai descrie realitatea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="36" t="inlineStr">
+        <is>
+          <t>6. Titluri și note de secțiune, scoase la reordonare</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="62" t="inlineStr">
+        <is>
+          <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="67" t="inlineStr">
+        <is>
+          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="67" t="inlineStr">
+        <is>
+          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="67" t="inlineStr">
+        <is>
+          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="67" t="inlineStr">
+        <is>
+          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="67" t="inlineStr">
+        <is>
+          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="67" t="inlineStr">
+        <is>
           <t>Nu sunt liniare. Fiecare pornește dintr-o stare „murdară" sau produce intersecție între două roluri. Acolo apar erorile de cabinet. Valoarea didactică &gt; încă 10 fluxuri liniare.</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="36" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="36" t="inlineStr">
         <is>
           <t>7. Narativul de etape, mutat din Legendă</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="62" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="62" t="inlineStr">
         <is>
           <t>Descria ordinea livrărilor, nu conținutul contabil. Mutat aici verbatim ca Legenda să descrie sistemul, nu istoria lui.</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="4" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>6. LISTA FLUXURILOR (~38, în 3 tranșe) — cele bold sunt „didactice”</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+    <row r="149" ht="40" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
         <is>
           <t>Tranșa 1 — stocuri și producție (F-01…F-12)</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="12" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="12" t="inlineStr">
         <is>
           <t>aprovizionare intern · prin 32x (tranzit) · intracomunitar cu taxare inversă · obiecte de inventar cu 8035 cap-coadă · producție termopan multi-stadiu (601→331→711→345→vânzare) · deșeuri 346 · servicii în curs 332/712 · diferențe de preț 308 · ajustare depreciere stoc · piese de schimb 3024→371 · stocuri la terți · ambalaje + taxa AFM</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
+    <row r="151" ht="40" customHeight="1">
+      <c r="A151" s="5" t="inlineStr">
         <is>
           <t>Tranșa 2 — TVA, comerț, import (F-13…F-25)</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="12" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="12" t="inlineStr">
         <is>
           <t>vânzare en-gros · gestiune amănunt completă cu verificarea ambelor corelații · import prin comisionar (446, taxe vamale + transport în cost) · import cu plată directă în vamă · TVA la încasare pe achiziție și pe vânzare · taxare inversă internă · livrare intracomunitară scutită · export · închiderea lunară de TVA · înregistrări fără document (50% auto, lipsă la inventar) · 408/418 · reduceri 609/709</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" s="5" t="inlineStr">
+    <row r="153" ht="40" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
         <is>
           <t>Tranșa 3 — imobilizări, personal, închidere (F-26…F-38)</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="12" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="12" t="inlineStr">
         <is>
           <t>achiziție MF + amortizare · imobilizări în curs · producție în regie proprie (722) · subvenție 475 eliberată pe măsura amortizării · avansuri 471/472 · cedare MF · salarii complet · viramente interne 581 · sumă neidentificată → 473 · avansuri de trezorerie · închiderea exercițiului (121/129/117 + 691/697/4417) · angajamente extrabilanțiere · decontări 481/482</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
         <is>
           <t>PROGRES IMPLEMENTARE</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="39" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="39" t="inlineStr">
         <is>
           <t>ETAPA 0: Arhitectură + skeleton complet (Legendă, Plan, Doar rol, Analitice Tier A, Catalog 38 fluxuri, Matrice).</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="39" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="39" t="inlineStr">
         <is>
           <t>ETAPA 1: 12 fluxuri detaliate.</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="26" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="26" t="inlineStr">
         <is>
           <t>ETAPA 2: Tranșa 1 completă + F-07 + F-28 → 22 fluxuri.</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="48" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="48" t="inlineStr">
         <is>
           <t>ETAPA 3 (FINAL): Tranșa 2 + Tranșa 3 complete. Total 38/38 fluxuri cu pași detaliați. Matrice verde. Workbook gata pentru utilizare cabinet + învățare.</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="26" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="26" t="inlineStr">
         <is>
           <t>Livrat 14.08.2026 — OMFP 1802/2014 actualizat + OMF 981/2024 + cote TVA 21%/11% + SAGA ca reper.</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="65" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="65" t="inlineStr">
         <is>
           <t>ETAPA 4 — EXTINDERE LA TRAININGURILE 2 ȘI 3</t>
         </is>
@@ -3835,31 +4226,31 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A135:G135"/>
+    <mergeCell ref="A159:G159"/>
+    <mergeCell ref="A137:F137"/>
+    <mergeCell ref="A150:G150"/>
     <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A131:G131"/>
-    <mergeCell ref="A125:G125"/>
+    <mergeCell ref="A156:G156"/>
     <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A134:G134"/>
+    <mergeCell ref="A161:G161"/>
+    <mergeCell ref="A152:G152"/>
+    <mergeCell ref="A155:G155"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A127:G127"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A148:G148"/>
+    <mergeCell ref="A157:G157"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A138:G138"/>
+    <mergeCell ref="A147:F147"/>
     <mergeCell ref="A81:F81"/>
-    <mergeCell ref="A115:F115"/>
-    <mergeCell ref="A132:G132"/>
     <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A114:F114"/>
-    <mergeCell ref="A137:G137"/>
-    <mergeCell ref="A133:G133"/>
-    <mergeCell ref="A123:F123"/>
-    <mergeCell ref="A136:G136"/>
+    <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A158:G158"/>
+    <mergeCell ref="A154:G154"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A129:G129"/>
+    <mergeCell ref="A146:F146"/>
     <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A160:G160"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3871,7 +4262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4172,22 +4563,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>Salarii complete (exemplu extern cifrat)</t>
+          <t>B1 Plata avansului; B2 Costurile lunii; B3 Plăți (net, taxe, CAM)</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>EXEMPLU EXTERN</t>
+          <t>IMPLEMENTAT</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>Salarii AS Kids - 31.07.2026.xlsx</t>
+          <t>Declarații_SALARII, Reguli_SALARII, Jurnale_SALARII, NotaExport_SALARII</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>Lunar — fișier separat</t>
+          <t>Lunar, pe registru de angajați</t>
         </is>
       </c>
     </row>
@@ -4204,22 +4595,22 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>Deconturi cheltuieli + avansuri</t>
+          <t>B1 Avans; B2 Cheltuieli + TVA; B3 Regularizare avans; B4 Plată / restituire</t>
         </is>
       </c>
       <c r="D14" s="28" t="inlineStr">
         <is>
-          <t>EXEMPLU EXTERN</t>
+          <t>IMPLEMENTAT</t>
         </is>
       </c>
       <c r="E14" s="28" t="inlineStr">
         <is>
-          <t>Deconturi AS Kids - ….xlsx</t>
+          <t>Declarații_DECONT, Reguli_DECONT, Jurnale_DECONT, NotaExport_DECONT</t>
         </is>
       </c>
       <c r="F14" s="28" t="inlineStr">
         <is>
-          <t>La deconturi — fișier separat</t>
+          <t>Pe decont</t>
         </is>
       </c>
     </row>
@@ -4231,27 +4622,27 @@
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
-          <t>F-204+</t>
+          <t>F-108</t>
         </is>
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>Leasing financiar auto (limitări TVA/amortizare)</t>
+          <t>B1 Avans; B2 TVA avans; B3 Intrare + 167; B4 Stingere avans; B5 Factura lunară; B6 Corecție TVA 50%; B7 Limitare 50% cheltuieli; B8 Amortizare</t>
         </is>
       </c>
       <c r="D15" s="28" t="inlineStr">
         <is>
-          <t>EXEMPLU EXTERN</t>
+          <t>IMPLEMENTAT</t>
         </is>
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>Template_leasing_financiar_auto.xlsx</t>
+          <t>Declarații_LEASING_FIN, Reguli_LEASING_FIN, Jurnale_LEASING_FIN, NotaExport_LEASING_FIN</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>Pe contract + lună — fișier separat</t>
+          <t>Pe contract + lunar</t>
         </is>
       </c>
     </row>
@@ -4346,17 +4737,17 @@
     <row r="28">
       <c r="A28" s="67" t="inlineStr">
         <is>
-          <t>MOD_LEASING_FIN</t>
+          <t>MOD_IMOBILIZARI</t>
         </is>
       </c>
       <c r="B28" s="67" t="inlineStr">
         <is>
-          <t>F-108</t>
+          <t>F-203, F-205, F-207, F-214</t>
         </is>
       </c>
       <c r="C28" s="67" t="inlineStr">
         <is>
-          <t>Leasing financiar auto: avans, intrare, rate, corecții TVA 50%, amortizare plafonată</t>
+          <t>B1 Intrare; B2 TVA pe regim; B3 Costuri capitalizate; B4 Amortizare lunară</t>
         </is>
       </c>
       <c r="D28" s="67" t="inlineStr">
@@ -4366,29 +4757,29 @@
       </c>
       <c r="E28" s="67" t="inlineStr">
         <is>
-          <t>Declarații_LEASING_FIN, Reguli_, Jurnale_, NotaExport_</t>
+          <t>Declarații_IMOBILIZARI, Reguli_IMOBILIZARI, Jurnale_IMOBILIZARI, NotaExport_IMOBILIZARI</t>
         </is>
       </c>
       <c r="F28" s="67" t="inlineStr">
         <is>
-          <t>Pe contract + lunar (nu mai e exemplu extern)</t>
+          <t>Pe mijloc fix + lunar</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67" t="inlineStr">
         <is>
-          <t>MOD_IMOBILIZARI</t>
+          <t>MOD_IESIRE_MF</t>
         </is>
       </c>
       <c r="B29" s="67" t="inlineStr">
         <is>
-          <t>F-203, F-205, F-207, F-214</t>
+          <t>F-211, F-212</t>
         </is>
       </c>
       <c r="C29" s="67" t="inlineStr">
         <is>
-          <t>Intrare mijloc fix pe grupe, regim TVA, plan de amortizare, oglinda 21x↔28x</t>
+          <t>B1 Descărcare amortizare; B2 Valoare rămasă; B3 Vânzare; B4 Piese recuperate</t>
         </is>
       </c>
       <c r="D29" s="67" t="inlineStr">
@@ -4398,29 +4789,29 @@
       </c>
       <c r="E29" s="67" t="inlineStr">
         <is>
-          <t>Declarații_IMOBILIZARI, Reguli_, Jurnale_, NotaExport_</t>
+          <t>Declarații_IESIRE_MF, Reguli_IESIRE_MF, Jurnale_IESIRE_MF, NotaExport_IESIRE_MF</t>
         </is>
       </c>
       <c r="F29" s="67" t="inlineStr">
         <is>
-          <t>La fiecare achiziție de imobilizare + control lunar</t>
+          <t>Pe eveniment de ieșire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67" t="inlineStr">
         <is>
-          <t>MOD_IESIRE_MF</t>
+          <t>MOD_CAPITALURI</t>
         </is>
       </c>
       <c r="B30" s="67" t="inlineStr">
         <is>
-          <t>F-211, F-212</t>
+          <t>F-103, F-105</t>
         </is>
       </c>
       <c r="C30" s="67" t="inlineStr">
         <is>
-          <t>Vânzare / casare: descărcare 28x, valoare rămasă, test de deductibilitate, piese recuperate</t>
+          <t>B1 Rezervă legală; B2 Închidere 121; B3 Dividende; B4 Corecție 1174</t>
         </is>
       </c>
       <c r="D30" s="67" t="inlineStr">
@@ -4430,49 +4821,17 @@
       </c>
       <c r="E30" s="67" t="inlineStr">
         <is>
-          <t>Declarații_IESIRE_MF, Reguli_, Jurnale_, NotaExport_</t>
+          <t>Declarații_CAPITALURI, Reguli_CAPITALURI, Jurnale_CAPITALURI, NotaExport_CAPITALURI</t>
         </is>
       </c>
       <c r="F30" s="67" t="inlineStr">
         <is>
-          <t>La fiecare ieșire de mijloc fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="67" t="inlineStr">
-        <is>
-          <t>MOD_CAPITALURI</t>
-        </is>
-      </c>
-      <c r="B31" s="67" t="inlineStr">
-        <is>
-          <t>F-103, F-105</t>
-        </is>
-      </c>
-      <c r="C31" s="67" t="inlineStr">
-        <is>
-          <t>Rezervă legală cu dublu plafon, repartizare 129, report 1171 pe an, corecții 1174</t>
-        </is>
-      </c>
-      <c r="D31" s="67" t="inlineStr">
-        <is>
-          <t>IMPLEMENTAT</t>
-        </is>
-      </c>
-      <c r="E31" s="67" t="inlineStr">
-        <is>
-          <t>Declarații_CAPITALURI, Reguli_, Jurnale_, NotaExport_</t>
-        </is>
-      </c>
-      <c r="F31" s="67" t="inlineStr">
-        <is>
-          <t>La 31.12 și în ianuarie, după închiderea exercițiului</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="33" t="inlineStr">
+          <t>Anual (31.12 + ianuarie)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>MOD_CAPITALURI nu dublează MOD_INCHIDERE_EX: acela închide clasele 6 și 7 pe 121, acesta repartizează rezultatul obținut (129/1061/1171).</t>
         </is>
@@ -4482,9 +4841,9 @@
   <mergeCells count="10">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A26:F26"/>
@@ -43775,17 +44134,17 @@
       </c>
       <c r="D42" s="22" t="inlineStr">
         <is>
-          <t>F-413</t>
+          <t>F-413, F-201, F-208</t>
         </is>
       </c>
       <c r="E42" s="22" t="inlineStr">
         <is>
-          <t>F-413 ilustrativ; modul extern Salarii e cifrat</t>
+          <t>Lanțul complet în MOD_SALARII, cu cifre verificate contra statului real din 31.07.2026; F-201/F-208 acoperă ipostaza de cost capitalizat</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t>PARȚIAL</t>
+          <t>NU</t>
         </is>
       </c>
     </row>
@@ -44255,17 +44614,17 @@
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
-          <t>F-413</t>
+          <t>F-413, F-201, F-208</t>
         </is>
       </c>
       <c r="E57" s="22" t="inlineStr">
         <is>
-          <t>Idem F-413 / modul extern</t>
+          <t>MOD_SALARII acoperă 641 salarii, 642 tichete și 646 CAM; limitările rămase sunt declarate în Reguli_SALARII, tabelul C</t>
         </is>
       </c>
       <c r="F57" s="22" t="inlineStr">
         <is>
-          <t>PARȚIAL</t>
+          <t>NU</t>
         </is>
       </c>
     </row>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1905,7 +1905,7 @@
     <row r="5">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>Numerotarea veche era secvențială, în ordinea livrărilor. Cea nouă codifică clasa contului principal, deci un flux adăugat peste un an primește următorul număr liber din clasa lui și stă fizic la locul lui. Tabelul rămâne aici permanent, ca referințele vechi să se poată rezolva.</t>
+          <t>Numerotarea veche era secvențială, în ordinea livrărilor. Cea nouă codifică clasa contului principal, deci un flux adăugat peste un an primește următorul număr liber din clasa lui și stă fizic la locul lui. Tabelul rămâne aici permanent, ca referințele vechi să se poată rezolva. Ultima coloană păstrează statusul dinainte de curățare: „(Etapa N)” era istoric de livrare, nu stare a fluxului, deci a ieșit din foaia de lucru.</t>
         </is>
       </c>
     </row>
@@ -1930,6 +1930,11 @@
           <t>Denumire</t>
         </is>
       </c>
+      <c r="E6" s="66" t="inlineStr">
+        <is>
+          <t>Status original (înainte de curățare)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="67" t="inlineStr">
@@ -1950,6 +1955,11 @@
           <t>Constituire / majorare capital social</t>
         </is>
       </c>
+      <c r="E7" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="67" t="inlineStr">
@@ -1970,6 +1980,11 @@
           <t>Rezerve din reevaluare: 105 → 1175</t>
         </is>
       </c>
+      <c r="E8" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="67" t="inlineStr">
@@ -1990,6 +2005,11 @@
           <t>Repartizarea rezultatului: 121 → 129/1061 → 1171</t>
         </is>
       </c>
+      <c r="E9" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="67" t="inlineStr">
@@ -2010,6 +2030,11 @@
           <t>Închiderea exercițiului (121/129/117 + 691/697/4417)</t>
         </is>
       </c>
+      <c r="E10" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 1)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="67" t="inlineStr">
@@ -2030,6 +2055,11 @@
           <t>Corecția erorilor din exerciții anterioare (1174)</t>
         </is>
       </c>
+      <c r="E11" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="67" t="inlineStr">
@@ -2050,6 +2080,11 @@
           <t>Provizioane pentru litigii (151x)</t>
         </is>
       </c>
+      <c r="E12" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="67" t="inlineStr">
@@ -2070,6 +2105,11 @@
           <t>Credit bancar în valută (162x)</t>
         </is>
       </c>
+      <c r="E13" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="67" t="inlineStr">
@@ -2090,6 +2130,11 @@
           <t>Leasing financiar autoturism cu deductibilitate 50%</t>
         </is>
       </c>
+      <c r="E14" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="67" t="inlineStr">
@@ -2110,6 +2155,11 @@
           <t>Imobilizări necorporale (20x)</t>
         </is>
       </c>
+      <c r="E15" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="67" t="inlineStr">
@@ -2130,6 +2180,11 @@
           <t>Terenuri și amenajări de terenuri (211)</t>
         </is>
       </c>
+      <c r="E16" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="67" t="inlineStr">
@@ -2150,6 +2205,11 @@
           <t>Construcții (212)</t>
         </is>
       </c>
+      <c r="E17" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="67" t="inlineStr">
@@ -2170,6 +2230,11 @@
           <t>Achiziție mijloc fix intern + amortizare liniară</t>
         </is>
       </c>
+      <c r="E18" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 3)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="67" t="inlineStr">
@@ -2190,6 +2255,11 @@
           <t>Instalații tehnice și mijloace de transport (213)</t>
         </is>
       </c>
+      <c r="E19" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="67" t="inlineStr">
@@ -2210,6 +2280,11 @@
           <t>Investiții imobiliare (215) și defalcarea teren / construcție</t>
         </is>
       </c>
+      <c r="E20" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="67" t="inlineStr">
@@ -2230,6 +2305,11 @@
           <t>Imobilizări facturate dar nesosite (223 / 224)</t>
         </is>
       </c>
+      <c r="E21" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="67" t="inlineStr">
@@ -2250,6 +2330,11 @@
           <t>Imobilizări în curs de execuție (231)</t>
         </is>
       </c>
+      <c r="E22" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="67" t="inlineStr">
@@ -2270,6 +2355,11 @@
           <t>Producție de imobilizări în regie proprie (722)</t>
         </is>
       </c>
+      <c r="E23" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 2) | CORECTAT 14.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="67" t="inlineStr">
@@ -2290,6 +2380,11 @@
           <t>Subvenție 475 eliberată pe măsura amortizării</t>
         </is>
       </c>
+      <c r="E24" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 1)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="67" t="inlineStr">
@@ -2310,6 +2405,11 @@
           <t>Vânzarea unui mijloc fix și testul valorii rămase</t>
         </is>
       </c>
+      <c r="E25" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="67" t="inlineStr">
@@ -2330,6 +2430,11 @@
           <t>Casarea unui mijloc fix și piesele recuperate</t>
         </is>
       </c>
+      <c r="E26" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="67" t="inlineStr">
@@ -2350,6 +2455,11 @@
           <t>Imobilizări financiare (26x)</t>
         </is>
       </c>
+      <c r="E27" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="67" t="inlineStr">
@@ -2370,6 +2480,11 @@
           <t>Controlul lunar analitic ↔ sintetic la imobilizări</t>
         </is>
       </c>
+      <c r="E28" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 4)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="67" t="inlineStr">
@@ -2390,6 +2505,11 @@
           <t>Aprovizionare internă (fără tranzit)</t>
         </is>
       </c>
+      <c r="E29" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 2)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="67" t="inlineStr">
@@ -2410,6 +2530,11 @@
           <t>Aprovizionare prin 32x (tranzit)</t>
         </is>
       </c>
+      <c r="E30" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 1)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="67" t="inlineStr">
@@ -2430,6 +2555,11 @@
           <t>Aprovizionare intracomunitară cu taxare inversă</t>
         </is>
       </c>
+      <c r="E31" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 2)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="67" t="inlineStr">
@@ -2450,6 +2580,11 @@
           <t>Intersecție 32x ↔ 408 (marfă parțială)</t>
         </is>
       </c>
+      <c r="E32" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="67" t="inlineStr">
@@ -2470,6 +2605,11 @@
           <t>Obiecte de inventar cu 8035 cap-coadă</t>
         </is>
       </c>
+      <c r="E33" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="67" t="inlineStr">
@@ -2490,6 +2630,11 @@
           <t>Diferențe de preț 308 / 348</t>
         </is>
       </c>
+      <c r="E34" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="67" t="inlineStr">
@@ -2510,6 +2655,11 @@
           <t>Ajustare pentru deprecierea stocurilor</t>
         </is>
       </c>
+      <c r="E35" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="67" t="inlineStr">
@@ -2530,6 +2680,11 @@
           <t>Piese de schimb 3024 → 371</t>
         </is>
       </c>
+      <c r="E36" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="67" t="inlineStr">
@@ -2550,6 +2705,11 @@
           <t>Stocuri aflate la terți</t>
         </is>
       </c>
+      <c r="E37" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="67" t="inlineStr">
@@ -2570,6 +2730,11 @@
           <t>Ambalaje + taxa AFM</t>
         </is>
       </c>
+      <c r="E38" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="67" t="inlineStr">
@@ -2590,6 +2755,11 @@
           <t>Producție termopan multi-stadiu (331 → 711 → 345)</t>
         </is>
       </c>
+      <c r="E39" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 1) | CORECTAT 14.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="67" t="inlineStr">
@@ -2610,6 +2780,11 @@
           <t>Servicii în curs 332 / 712</t>
         </is>
       </c>
+      <c r="E40" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 2) | CORECTAT 14.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="67" t="inlineStr">
@@ -2630,6 +2805,11 @@
           <t>Deșeuri 346</t>
         </is>
       </c>
+      <c r="E41" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 2) | CORECTAT 14.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="67" t="inlineStr">
@@ -2650,6 +2830,11 @@
           <t>Sold 331 la 31.12 → inventar → reluare ianuarie</t>
         </is>
       </c>
+      <c r="E42" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="67" t="inlineStr">
@@ -2670,6 +2855,11 @@
           <t>Vânzare en-gros</t>
         </is>
       </c>
+      <c r="E43" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="67" t="inlineStr">
@@ -2690,6 +2880,11 @@
           <t>Gestiune amănunt completă</t>
         </is>
       </c>
+      <c r="E44" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="67" t="inlineStr">
@@ -2710,6 +2905,11 @@
           <t>Vânzare parțială amănunt</t>
         </is>
       </c>
+      <c r="E45" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="67" t="inlineStr">
@@ -2730,6 +2930,11 @@
           <t>Retur din gestiune amănunt</t>
         </is>
       </c>
+      <c r="E46" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="67" t="inlineStr">
@@ -2750,6 +2955,11 @@
           <t>Import prin comisionar (446.VAMA)</t>
         </is>
       </c>
+      <c r="E47" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 1) | CORECTAT 14.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="67" t="inlineStr">
@@ -2770,6 +2980,11 @@
           <t>Import cu plată directă în vamă</t>
         </is>
       </c>
+      <c r="E48" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 3) | CORECTAT 14.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="67" t="inlineStr">
@@ -2790,6 +3005,11 @@
           <t>TVA la încasare (4428.INC)</t>
         </is>
       </c>
+      <c r="E49" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 1)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="67" t="inlineStr">
@@ -2810,6 +3030,11 @@
           <t>Taxare inversă internă</t>
         </is>
       </c>
+      <c r="E50" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 3)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="67" t="inlineStr">
@@ -2830,6 +3055,11 @@
           <t>Livrare intracomunitară scutită</t>
         </is>
       </c>
+      <c r="E51" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 3)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="67" t="inlineStr">
@@ -2850,6 +3080,11 @@
           <t>Export</t>
         </is>
       </c>
+      <c r="E52" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 3)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="67" t="inlineStr">
@@ -2870,6 +3105,11 @@
           <t>Închiderea lunară de TVA</t>
         </is>
       </c>
+      <c r="E53" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="67" t="inlineStr">
@@ -2890,6 +3130,11 @@
           <t>Înregistrări fără document (50% auto, lipsă la inventar)</t>
         </is>
       </c>
+      <c r="E54" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 3) | CORECTAT 14.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="67" t="inlineStr">
@@ -2910,6 +3155,11 @@
           <t>Corecție după D300 depusă</t>
         </is>
       </c>
+      <c r="E55" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="67" t="inlineStr">
@@ -2930,6 +3180,11 @@
           <t>408 / 418 (facturi nesosite / de întocmit)</t>
         </is>
       </c>
+      <c r="E56" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 1)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="67" t="inlineStr">
@@ -2950,6 +3205,11 @@
           <t>Reduceri comerciale 609 / 709</t>
         </is>
       </c>
+      <c r="E57" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 3) | CORECTAT 14.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="67" t="inlineStr">
@@ -2970,6 +3230,11 @@
           <t>Avansuri clienți / furnizori (419 / 409)</t>
         </is>
       </c>
+      <c r="E58" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 3) | CLARIFICAT 14.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="67" t="inlineStr">
@@ -2990,6 +3255,11 @@
           <t>Sumă neidentificată din extras → 473</t>
         </is>
       </c>
+      <c r="E59" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 1)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="67" t="inlineStr">
@@ -3010,6 +3280,11 @@
           <t>Avansuri 471 / 472 (regularizare temporală)</t>
         </is>
       </c>
+      <c r="E60" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 3)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="67" t="inlineStr">
@@ -3030,6 +3305,11 @@
           <t>Salarii</t>
         </is>
       </c>
+      <c r="E61" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 3)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="67" t="inlineStr">
@@ -3050,6 +3330,11 @@
           <t>Decontări 481 / 482 (unitate ↔ subunități)</t>
         </is>
       </c>
+      <c r="E62" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 3)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="67" t="inlineStr">
@@ -3070,6 +3355,11 @@
           <t>Viramente interne 581</t>
         </is>
       </c>
+      <c r="E63" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 1)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="67" t="inlineStr">
@@ -3090,6 +3380,11 @@
           <t>Avansuri de trezorerie (542)</t>
         </is>
       </c>
+      <c r="E64" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 3)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="67" t="inlineStr">
@@ -3110,6 +3405,11 @@
           <t>Angajamente extrabilanțiere</t>
         </is>
       </c>
+      <c r="E65" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat (Etapa 3)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="67" t="inlineStr">
@@ -3128,6 +3428,11 @@
       <c r="D66" s="67" t="inlineStr">
         <is>
           <t>Inventariere 8035 (scriptic vs. faptic)</t>
+        </is>
+      </c>
+      <c r="E66" s="67" t="inlineStr">
+        <is>
+          <t>Detaliat</t>
         </is>
       </c>
     </row>
@@ -22318,7 +22623,7 @@
       </c>
       <c r="G11" s="69" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H11" s="69" t="inlineStr">
@@ -22358,7 +22663,7 @@
       </c>
       <c r="G12" s="69" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H12" s="69" t="inlineStr">
@@ -22398,7 +22703,7 @@
       </c>
       <c r="G13" s="70" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H13" s="70" t="inlineStr">
@@ -22438,7 +22743,7 @@
       </c>
       <c r="G14" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 1)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H14" s="29" t="inlineStr">
@@ -22478,7 +22783,7 @@
       </c>
       <c r="G15" s="70" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H15" s="70" t="inlineStr">
@@ -22518,7 +22823,7 @@
       </c>
       <c r="G16" s="69" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H16" s="69" t="inlineStr">
@@ -22558,7 +22863,7 @@
       </c>
       <c r="G17" s="70" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H17" s="70" t="inlineStr">
@@ -22598,7 +22903,7 @@
       </c>
       <c r="G18" s="70" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H18" s="70" t="inlineStr">
@@ -22645,7 +22950,7 @@
       </c>
       <c r="G20" s="70" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H20" s="70" t="inlineStr">
@@ -22685,7 +22990,7 @@
       </c>
       <c r="G21" s="69" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H21" s="69" t="inlineStr">
@@ -22725,7 +23030,7 @@
       </c>
       <c r="G22" s="70" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H22" s="70" t="inlineStr">
@@ -22765,7 +23070,7 @@
       </c>
       <c r="G23" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 3)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
@@ -22805,7 +23110,7 @@
       </c>
       <c r="G24" s="69" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H24" s="69" t="inlineStr">
@@ -22845,7 +23150,7 @@
       </c>
       <c r="G25" s="69" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H25" s="69" t="inlineStr">
@@ -22885,7 +23190,7 @@
       </c>
       <c r="G26" s="69" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H26" s="69" t="inlineStr">
@@ -22925,7 +23230,7 @@
       </c>
       <c r="G27" s="70" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H27" s="70" t="inlineStr">
@@ -22965,7 +23270,7 @@
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 2) | CORECTAT 14.08.2026</t>
+          <t>Detaliat | CORECTAT 14.08.2026</t>
         </is>
       </c>
       <c r="H28" s="29" t="inlineStr">
@@ -23005,7 +23310,7 @@
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 1)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H29" s="29" t="inlineStr">
@@ -23045,7 +23350,7 @@
       </c>
       <c r="G30" s="70" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H30" s="70" t="inlineStr">
@@ -23085,7 +23390,7 @@
       </c>
       <c r="G31" s="69" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H31" s="69" t="inlineStr">
@@ -23125,7 +23430,7 @@
       </c>
       <c r="G32" s="69" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H32" s="69" t="inlineStr">
@@ -23165,7 +23470,7 @@
       </c>
       <c r="G33" s="70" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 4)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H33" s="70" t="inlineStr">
@@ -23212,7 +23517,7 @@
       </c>
       <c r="G35" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 2)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H35" s="28" t="inlineStr">
@@ -23252,7 +23557,7 @@
       </c>
       <c r="G36" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 1)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H36" s="29" t="inlineStr">
@@ -23292,7 +23597,7 @@
       </c>
       <c r="G37" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 2)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H37" s="28" t="inlineStr">
@@ -23612,7 +23917,7 @@
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 1) | CORECTAT 14.08.2026</t>
+          <t>Detaliat | CORECTAT 14.08.2026</t>
         </is>
       </c>
       <c r="H45" s="29" t="inlineStr">
@@ -23652,7 +23957,7 @@
       </c>
       <c r="G46" s="23" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 2) | CORECTAT 14.08.2026</t>
+          <t>Detaliat | CORECTAT 14.08.2026</t>
         </is>
       </c>
       <c r="H46" s="23" t="inlineStr">
@@ -23697,7 +24002,7 @@
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 2) | CORECTAT 14.08.2026</t>
+          <t>Detaliat | CORECTAT 14.08.2026</t>
         </is>
       </c>
       <c r="H47" s="28" t="inlineStr">
@@ -23937,7 +24242,7 @@
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 1) | CORECTAT 14.08.2026</t>
+          <t>Detaliat | CORECTAT 14.08.2026</t>
         </is>
       </c>
       <c r="H53" s="29" t="inlineStr">
@@ -23977,7 +24282,7 @@
       </c>
       <c r="G54" s="23" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 3) | CORECTAT 14.08.2026</t>
+          <t>Detaliat | CORECTAT 14.08.2026</t>
         </is>
       </c>
       <c r="H54" s="30" t="inlineStr">
@@ -24024,7 +24329,7 @@
       </c>
       <c r="G56" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 1)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H56" s="29" t="inlineStr">
@@ -24064,7 +24369,7 @@
       </c>
       <c r="G57" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 3)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H57" s="30" t="inlineStr">
@@ -24104,7 +24409,7 @@
       </c>
       <c r="G58" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 3)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H58" s="30" t="inlineStr">
@@ -24144,7 +24449,7 @@
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 3)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H59" s="30" t="inlineStr">
@@ -24224,7 +24529,7 @@
       </c>
       <c r="G61" s="23" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 3) | CORECTAT 14.08.2026</t>
+          <t>Detaliat | CORECTAT 14.08.2026</t>
         </is>
       </c>
       <c r="H61" s="30" t="inlineStr">
@@ -24304,7 +24609,7 @@
       </c>
       <c r="G63" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 1)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H63" s="29" t="inlineStr">
@@ -24344,7 +24649,7 @@
       </c>
       <c r="G64" s="23" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 3) | CORECTAT 14.08.2026</t>
+          <t>Detaliat | CORECTAT 14.08.2026</t>
         </is>
       </c>
       <c r="H64" s="30" t="inlineStr">
@@ -24384,7 +24689,7 @@
       </c>
       <c r="G65" s="23" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 3) | CLARIFICAT 14.08.2026</t>
+          <t>Detaliat | CLARIFICAT 14.08.2026</t>
         </is>
       </c>
       <c r="H65" s="30" t="inlineStr">
@@ -24424,7 +24729,7 @@
       </c>
       <c r="G66" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 1)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H66" s="29" t="inlineStr">
@@ -24464,7 +24769,7 @@
       </c>
       <c r="G67" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 3)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H67" s="23" t="inlineStr">
@@ -24504,7 +24809,7 @@
       </c>
       <c r="G68" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 3)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H68" s="23" t="inlineStr">
@@ -24544,7 +24849,7 @@
       </c>
       <c r="G69" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 3)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H69" s="23" t="inlineStr">
@@ -24591,7 +24896,7 @@
       </c>
       <c r="G71" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 1)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H71" s="29" t="inlineStr">
@@ -24631,7 +24936,7 @@
       </c>
       <c r="G72" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 3)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H72" s="23" t="inlineStr">
@@ -24678,7 +24983,7 @@
       </c>
       <c r="G74" s="29" t="inlineStr">
         <is>
-          <t>Detaliat (Etapa 3)</t>
+          <t>Detaliat</t>
         </is>
       </c>
       <c r="H74" s="23" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -4567,7 +4567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5042,17 +5042,17 @@
     <row r="28">
       <c r="A28" s="67" t="inlineStr">
         <is>
-          <t>MOD_IMOBILIZARI</t>
+          <t>MOD_CAPITALURI</t>
         </is>
       </c>
       <c r="B28" s="67" t="inlineStr">
         <is>
-          <t>F-203, F-205, F-207, F-214</t>
+          <t>F-103, F-105</t>
         </is>
       </c>
       <c r="C28" s="67" t="inlineStr">
         <is>
-          <t>B1 Intrare; B2 TVA pe regim; B3 Costuri capitalizate; B4 Amortizare lunară</t>
+          <t>B1 Rezervă legală; B2 Închidere 121; B3 Dividende; B4 Corecție 1174</t>
         </is>
       </c>
       <c r="D28" s="67" t="inlineStr">
@@ -5062,29 +5062,29 @@
       </c>
       <c r="E28" s="67" t="inlineStr">
         <is>
-          <t>Declarații_IMOBILIZARI, Reguli_IMOBILIZARI, Jurnale_IMOBILIZARI, NotaExport_IMOBILIZARI</t>
+          <t>Declarații_CAPITALURI, Reguli_CAPITALURI, Jurnale_CAPITALURI, NotaExport_CAPITALURI</t>
         </is>
       </c>
       <c r="F28" s="67" t="inlineStr">
         <is>
-          <t>Pe mijloc fix + lunar</t>
+          <t>Anual (31.12 + ianuarie)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67" t="inlineStr">
         <is>
-          <t>MOD_IESIRE_MF</t>
+          <t>MOD_CREDIT_VALUTA</t>
         </is>
       </c>
       <c r="B29" s="67" t="inlineStr">
         <is>
-          <t>F-211, F-212</t>
+          <t>F-107</t>
         </is>
       </c>
       <c r="C29" s="67" t="inlineStr">
         <is>
-          <t>B1 Descărcare amortizare; B2 Valoare rămasă; B3 Vânzare; B4 Piese recuperate</t>
+          <t>B1 Rata + diferența la plată; B2 Dobânda; B3 Comisioane; B4 Reevaluarea soldului</t>
         </is>
       </c>
       <c r="D29" s="67" t="inlineStr">
@@ -5094,29 +5094,29 @@
       </c>
       <c r="E29" s="67" t="inlineStr">
         <is>
-          <t>Declarații_IESIRE_MF, Reguli_IESIRE_MF, Jurnale_IESIRE_MF, NotaExport_IESIRE_MF</t>
+          <t>Declarații_CREDIT_VALUTA, Reguli_CREDIT_VALUTA, Jurnale_CREDIT_VALUTA, NotaExport_CREDIT_VALUTA</t>
         </is>
       </c>
       <c r="F29" s="67" t="inlineStr">
         <is>
-          <t>Pe eveniment de ieșire</t>
+          <t>Lunar, pe contract</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67" t="inlineStr">
         <is>
-          <t>MOD_CAPITALURI</t>
+          <t>MOD_PROVIZION</t>
         </is>
       </c>
       <c r="B30" s="67" t="inlineStr">
         <is>
-          <t>F-103, F-105</t>
+          <t>F-106</t>
         </is>
       </c>
       <c r="C30" s="67" t="inlineStr">
         <is>
-          <t>B1 Rezervă legală; B2 Închidere 121; B3 Dividende; B4 Corecție 1174</t>
+          <t>B1 Constituire; B2 Factura efectivă (independentă); B3 Reluare</t>
         </is>
       </c>
       <c r="D30" s="67" t="inlineStr">
@@ -5126,17 +5126,113 @@
       </c>
       <c r="E30" s="67" t="inlineStr">
         <is>
-          <t>Declarații_CAPITALURI, Reguli_CAPITALURI, Jurnale_CAPITALURI, NotaExport_CAPITALURI</t>
+          <t>Declarații_PROVIZION, Reguli_PROVIZION, Jurnale_PROVIZION, NotaExport_PROVIZION</t>
         </is>
       </c>
       <c r="F30" s="67" t="inlineStr">
         <is>
-          <t>Anual (31.12 + ianuarie)</t>
+          <t>Pe eveniment + la fiecare dată a bilanțului</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="67" t="inlineStr">
+        <is>
+          <t>MOD_IMOBILIZARI</t>
+        </is>
+      </c>
+      <c r="B31" s="67" t="inlineStr">
+        <is>
+          <t>F-203, F-205, F-207, F-214</t>
+        </is>
+      </c>
+      <c r="C31" s="67" t="inlineStr">
+        <is>
+          <t>B1 Intrare; B2 TVA pe regim; B3 Costuri capitalizate; B4 Amortizare lunară</t>
+        </is>
+      </c>
+      <c r="D31" s="67" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+      <c r="E31" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_IMOBILIZARI, Reguli_IMOBILIZARI, Jurnale_IMOBILIZARI, NotaExport_IMOBILIZARI</t>
+        </is>
+      </c>
+      <c r="F31" s="67" t="inlineStr">
+        <is>
+          <t>Pe mijloc fix + lunar</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="33" t="inlineStr">
+      <c r="A32" s="67" t="inlineStr">
+        <is>
+          <t>MOD_SUBVENTIE</t>
+        </is>
+      </c>
+      <c r="B32" s="67" t="inlineStr">
+        <is>
+          <t>F-210</t>
+        </is>
+      </c>
+      <c r="C32" s="67" t="inlineStr">
+        <is>
+          <t>B1 Încasarea subvenției; B2 Achiziția activului; B3 Amortizare + eliberare</t>
+        </is>
+      </c>
+      <c r="D32" s="67" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+      <c r="E32" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_SUBVENTIE, Reguli_SUBVENTIE, Jurnale_SUBVENTIE, NotaExport_SUBVENTIE</t>
+        </is>
+      </c>
+      <c r="F32" s="67" t="inlineStr">
+        <is>
+          <t>Lunar, pe activ subvenționat</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="67" t="inlineStr">
+        <is>
+          <t>MOD_IESIRE_MF</t>
+        </is>
+      </c>
+      <c r="B33" s="67" t="inlineStr">
+        <is>
+          <t>F-211, F-212</t>
+        </is>
+      </c>
+      <c r="C33" s="67" t="inlineStr">
+        <is>
+          <t>B1 Descărcare amortizare; B2 Valoare rămasă; B3 Vânzare; B4 Piese recuperate</t>
+        </is>
+      </c>
+      <c r="D33" s="67" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+      <c r="E33" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_IESIRE_MF, Reguli_IESIRE_MF, Jurnale_IESIRE_MF, NotaExport_IESIRE_MF</t>
+        </is>
+      </c>
+      <c r="F33" s="67" t="inlineStr">
+        <is>
+          <t>Pe eveniment de ieșire</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t>MOD_CAPITALURI nu dublează MOD_INCHIDERE_EX: acela închide clasele 6 și 7 pe 121, acesta repartizează rezultatul obținut (129/1061/1171).</t>
         </is>
@@ -5148,9 +5244,9 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A20:F20"/>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Legendă" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Index module" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Plan de conturi" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Doar rol în flux" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Analitice (Tier A)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Arbore analitice" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Fluxuri" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Corelații de control" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Matrice acoperire" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Istoric" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legendă" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index module" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan de conturi" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doar rol în flux" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analitice (Tier A)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arbore analitice" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fluxuri" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corelații de control" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrice acoperire" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istoric" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan de conturi'!$A$1:$J$314</definedName>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -16,7 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fluxuri" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corelații de control" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrice acoperire" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istoric" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Întrebări deschise" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istoric" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan de conturi'!$A$1:$J$314</definedName>
@@ -429,13 +430,13 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -831,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1595,152 +1596,212 @@
     <row r="73">
       <c r="A73" s="61" t="inlineStr">
         <is>
+          <t>Index module</t>
+        </is>
+      </c>
+      <c r="B73" s="61" t="inlineStr">
+        <is>
+          <t>Legătura cu Module_Declarative_Fluxuri.xlsx: ce modul acoperă ce flux, cu ce foi și când se rulează</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="61" t="inlineStr">
+        <is>
+          <t>Arbore analitice</t>
+        </is>
+      </c>
+      <c r="B74" s="61" t="inlineStr">
+        <is>
+          <t>Arborele de decizie pentru analitice (3 întrebări) + contra-regula: când analiticul e o greșeală</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="61" t="inlineStr">
+        <is>
+          <t>Corelații de control</t>
+        </is>
+      </c>
+      <c r="B75" s="61" t="inlineStr">
+        <is>
+          <t>Formulă · unde se verifică · ce o rupe LEGITIM vs. SUSPECT · fluxul și modulul legat</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="61" t="inlineStr">
+        <is>
+          <t>Întrebări deschise</t>
+        </is>
+      </c>
+      <c r="B76" s="61" t="inlineStr">
+        <is>
+          <t>Ce e încă provizoriu în workbook: întrebările la care sistemul așteaptă răspuns. Fluxurile atinse poartă ❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="61" t="inlineStr">
+        <is>
+          <t>Istoric</t>
+        </is>
+      </c>
+      <c r="B77" s="61" t="inlineStr">
+        <is>
+          <t>Echivalența de numerotare veche → nouă, contopirile, defectele reparate, textul mutat la deduplicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="62" t="inlineStr">
+        <is>
           <t>6. HARTA FLUXURILOR — pe clase de conturi</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="62" t="inlineStr">
-        <is>
-          <t>Ordinea fluxurilor urmează planul de conturi, nu ordinea în care au fost adăugate. Un flux nou primește următorul număr liber din clasa lui și stă fizic la locul lui. Echivalența cu numerotarea veche e în foaia Istoric.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="63" t="inlineStr">
-        <is>
-          <t>F-1xx — capitaluri, provizioane, împrumuturi: capital social · rezerve din reevaluare · repartizarea rezultatului · închiderea exercițiului · corecții 1174 · provizioane · credite în valută · leasing financiar</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="63" t="inlineStr">
-        <is>
-          <t>F-2xx — imobilizări: necorporale · terenuri · construcții · instalații și transport · investiții imobiliare · facturate nesosite · în curs de execuție · regie proprie · subvenții · ieșiri (vânzare, casare) · financiare · control analitic ↔ sintetic</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="63" t="inlineStr">
-        <is>
-          <t>F-3xx — stocuri și producție: aprovizionare (internă, tranzit, intracomunitară) · obiecte de inventar · diferențe de preț · ajustări · producție în curs · deșeuri · mărfuri en-gros și amănunt · import</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="63" t="inlineStr">
-        <is>
-          <t>F-4xx — terți, TVA, decontări: TVA la încasare · taxare inversă · scutiri și export · închiderea lunară de TVA · înregistrări fără document · 408/418 · reduceri · avansuri · 473 · salarii · decontări interne</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="63" t="inlineStr">
-        <is>
-          <t>F-5xx — trezorerie: viramente interne · avansuri de trezorerie</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="63" t="inlineStr">
         <is>
+          <t>Ordinea fluxurilor urmează planul de conturi, nu ordinea în care au fost adăugate. Un flux nou primește următorul număr liber din clasa lui și stă fizic la locul lui. Echivalența cu numerotarea veche e în foaia Istoric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="61" t="inlineStr">
+        <is>
+          <t>F-1xx — capitaluri, provizioane, împrumuturi: capital social · rezerve din reevaluare · repartizarea rezultatului · închiderea exercițiului · corecții 1174 · provizioane · credite în valută · leasing financiar</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="61" t="inlineStr">
+        <is>
+          <t>F-2xx — imobilizări: necorporale · terenuri · construcții · instalații și transport · investiții imobiliare · facturate nesosite · în curs de execuție · regie proprie · subvenții · ieșiri (vânzare, casare) · financiare · control analitic ↔ sintetic</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="61" t="inlineStr">
+        <is>
+          <t>F-3xx — stocuri și producție: aprovizionare (internă, tranzit, intracomunitară) · obiecte de inventar · diferențe de preț · ajustări · producție în curs · deșeuri · mărfuri en-gros și amănunt · import</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="61" t="inlineStr">
+        <is>
+          <t>F-4xx — terți, TVA, decontări: TVA la încasare · taxare inversă · scutiri și export · închiderea lunară de TVA · înregistrări fără document · 408/418 · reduceri · avansuri · 473 · salarii · decontări interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="61" t="inlineStr">
+        <is>
+          <t>F-5xx — trezorerie: viramente interne · avansuri de trezorerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="61" t="inlineStr">
+        <is>
           <t>F-8xx — conturi în afara bilanțului: angajamente · inventarierea obiectelor de inventar</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>7. FORMATUL UNUI RÂND DE FLUX</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>Flux ID | Pas | Document | Explicație | Cont D | Cont C | Sumă | Rol revelat | Declarativ</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>Ultima coloană (Declarativ) leagă pasul de declarația în care ajunge (D300, D394, D406/SAF-T, D100 etc.) — util în cabinet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>8. PORȚI DE CALITATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="45" customHeight="1">
-      <c r="A87" s="12" t="inlineStr">
-        <is>
-          <t>ΣD = ΣC pe fiecare pas · fiecare flux se închide într-o stare terminală declarată · fiecare cont din antetul fluxului apare într-o notă reală · fiecare analitic are un factor · fiecare cont cu rol în flux are un pas care îi demonstrează rolul · corelațiile se verifică pe cifrele fluxului, nu declarativ · Tier C rămâne marcat „acoperire minimă”.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>9. CONFIRMARE COTE TVA (verificare Etapa 1, 14.08.2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="45" customHeight="1">
-      <c r="A90" s="14" t="inlineStr">
-        <is>
-          <t>Cota standard: 21% (în vigoare din 01.08.2025, Legea 141/2025). Cota redusă unică: 11% (alimente, medicamente, cazare, restaurante, cărți etc.). Cotă tranzitorie 9% doar pentru locuințe eligibile până la 30.09.2026 (Legea 161/2026). Export / livrări IC: 0%. Toate fluxurile Tranșa 2 folosesc 21%/11%.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
+          <t>8. PORȚI DE CALITATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="45" customHeight="1">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>ΣD = ΣC pe fiecare pas · fiecare flux se închide într-o stare terminală declarată · fiecare cont din antetul fluxului apare într-o notă reală · fiecare analitic are un factor · fiecare cont cu rol în flux are un pas care îi demonstrează rolul · corelațiile se verifică pe cifrele fluxului, nu declarativ · Tier C rămâne marcat „acoperire minimă”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>9. CONFIRMARE COTE TVA (verificare Etapa 1, 14.08.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="45" customHeight="1">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>Cota standard: 21% (în vigoare din 01.08.2025, Legea 141/2025). Cota redusă unică: 11% (alimente, medicamente, cazare, restaurante, cărți etc.). Cotă tranzitorie 9% doar pentru locuințe eligibile până la 30.09.2026 (Legea 161/2026). Export / livrări IC: 0%. Toate fluxurile Tranșa 2 folosesc 21%/11%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
           <t>10. NOTĂ DE RIGUROZITATE (din original + actualizare)</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>1. Taxonomia 'pe rol' este o grilă FUNCȚIONALĂ (pt. control și înțelegere), nu clasificarea oficială. OMFP 1802 clasifică după funcția contabilă (A / P / bifuncțional A/P) — vezi col. 'Fct'.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>2. 'Bifuncțional' (A/P) e o PROPRIETATE (poate avea sold pe D și pe C), nu un rol. De aceea 4428 apare o dată, cu două roluri: rectificativ (amănunt) ȘI intermediar (la încasare).</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>3. Corelații sfinte: 707-607 = rulaj D 378 ; sold 371 * c/(100+c) = sold 4428 ; 4426=jurnal cumpărări, 4427=jurnal vânzări (fără sold, se închid lunar în 4423/4424).</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>4. Analiticele se judecă după dacă se declară efectiv (D394, D300, D406/SAF-T). Fluxurile pot fi narative, cu pași de verificare la final.</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="49" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="49" t="inlineStr">
         <is>
           <t>VERIFICARE ONLINE 14.08.2026 — CONTRA-VERIFICARE COMPLETITUDINE &amp; ACTUALITATE</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="75" customHeight="1">
-      <c r="A100" s="50" t="inlineStr">
+    <row r="106" ht="75" customHeight="1">
+      <c r="A106" s="50" t="inlineStr">
         <is>
           <t>Surse verificate: OMF 981/2024 (conturi noi 4417, 6351, 697 — prezente și marcate), OMF 6670/2024 (denumiri extinse 694 și 794 — actualizate în fișier), accountantsgroup.ro Plan 2026, PwC/Accace alerts, mfinante.gov.ro.
 Cote TVA 21%/11% confirmate (Legea 141/2025 + actualizări 2026).
@@ -1750,114 +1811,146 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="48" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="48" t="inlineStr">
         <is>
           <t>Concluzie: informația din fișier este corectă, actualizată la zi (14.08.2026) și completă în raport cu scopul „cabinet + învățare” + SAGA. Corecțiile minore (694/794/6351) au fost aplicate acum.</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="63" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="61" t="inlineStr">
         <is>
           <t>Sursă: notițele revizuite din 07.08.2026 (capitaluri) și 12.08.2026 (imobilizări). Adăugate 18 fluxuri (F-101…F-213), 10 corelații (C-13…C-22) și 21 de conturi Tier A din clasele 1 și 2. Total fluxuri: 62.</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="63" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="61" t="inlineStr">
         <is>
           <t>Fluxuri didactice noi: F-103 (121 = 129, nu invers), F-105 (1174 ocolește 121), F-107 (cele două momente de curs), F-108 (leasing 50% — trei limitări pe baze diferite), F-201 (721, nu 711), F-203 (cod 27 în D394), F-208 (722, nu 711), F-211 (valoare rămasă vs. venit), F-214 (control analitic ↔ sintetic — singurul flux de procedură, fără note contabile).</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="64" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="64" t="inlineStr">
         <is>
           <t>Corecție aplicată pe planul de conturi: contul 235 avea denumirea contului 233. Conform OMFP 1802/2014: 231 corporale în curs, 233 necorporale în curs, 235 investiții imobiliare în curs. Contul 233 a fost adăugat.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="63" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="61" t="inlineStr">
         <is>
           <t>Erori din notițele brute NEreintroduse (corectate deja în documentele revizuite): 7815 nu există (corect 6811 = 2805/2808); taxele vamale se capitalizează, nu pe 635; softul intern prin 721; salariile din 231 prin 722; 2114 este 214; CASCO nedeductibil pe 613.NED, nu 615; typo-urile 1067 (=167) și 4424 (=4426) la leasing.</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="62" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="63" t="inlineStr">
         <is>
           <t>Reproductibilitate: workbook-ul se generează cu `make build` din surse/ + date/. Porțile de calitate se verifică cu `make verifica`.</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="65" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="65" t="inlineStr">
+        <is>
+          <t>LIVRABILE CONEXE — sistemul nu se termină la acest fișier</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="61" t="inlineStr">
+        <is>
+          <t>Module_Declarative_Fluxuri.xlsx — 16 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="61" t="inlineStr">
+        <is>
+          <t>intrebari-formator.md / .html — cele 21 de întrebări rămase deschise, grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="61" t="inlineStr">
+        <is>
+          <t>notite-training-2/3/4 .md și .docx — cele trei documente revizuite, armonizate: aceeași legendă de marcaje, aceleași anexe, aceeași ordine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="65" t="inlineStr">
         <is>
           <t>VERIFICARE LEGISLATIVĂ — completări ulterioare datei de 14.08.2026</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="63" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="61" t="inlineStr">
         <is>
           <t>Afirmațiile adăugate odată cu trainingurile 2 și 3 nu intră sub verificarea din 14.08.2026 de mai sus și au propria dată: L. 239/2025 (capital social minim și blocajul de activ net), OUG 8/2026 (pragul mijloacelor fixe la 5.000 lei), L. 141/2025 (cotele 21% / 11%). Reconfirmă orice prag sau cotă înainte de aplicare la un caz concret.</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="62" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="63" t="inlineStr">
         <is>
           <t>Reproductibilitate: `make build` regenerează ambele workbook-uri din surse/ + date/; `make verifica` rulează porțile, inclusiv poarta de conservare care demonstrează că nimic din originalul training 4 nu s-a pierdut.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="48">
+    <mergeCell ref="A116:G116"/>
     <mergeCell ref="A106:G106"/>
+    <mergeCell ref="A122:G122"/>
     <mergeCell ref="A109:G109"/>
     <mergeCell ref="A62:G62"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A96:G96"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A112:G112"/>
+    <mergeCell ref="A121:G121"/>
+    <mergeCell ref="A115:G115"/>
+    <mergeCell ref="A117:G117"/>
     <mergeCell ref="A93:G93"/>
     <mergeCell ref="A111:G111"/>
     <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A102:G102"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A83:G83"/>
     <mergeCell ref="A92:G92"/>
     <mergeCell ref="A64:G64"/>
     <mergeCell ref="A82:G82"/>
     <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A98:G98"/>
     <mergeCell ref="A49:G49"/>
     <mergeCell ref="A107:G107"/>
-    <mergeCell ref="A103:G103"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A61:G61"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A94:G94"/>
+    <mergeCell ref="A88:G88"/>
     <mergeCell ref="A110:G110"/>
     <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A78:G78"/>
     <mergeCell ref="A90:G90"/>
     <mergeCell ref="A99:G99"/>
-    <mergeCell ref="A75:G75"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="A84:G84"/>
-    <mergeCell ref="A89:G89"/>
-    <mergeCell ref="A74:G74"/>
     <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A118:G118"/>
     <mergeCell ref="A56:G56"/>
+    <mergeCell ref="A120:G120"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A105:G105"/>
     <mergeCell ref="A95:G95"/>
     <mergeCell ref="A101:G101"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A104:G104"/>
-    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A113:G113"/>
+    <mergeCell ref="A85:G85"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1865,6 +1958,915 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>ÎNTREBĂRI DESCHISE — ce e încă provizoriu în acest workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="63" t="inlineStr">
+        <is>
+          <t>Restul foilor prezintă regulile ca tranșate. Cele de mai jos nu sunt: notițele erau ambigue sau practica diferă, iar coloana „Ce am presupus” spune ce am ales ca să pot merge mai departe. Un răspuns diferit schimbă exact ce scrie acolo. Fluxurile și corelațiile atinse poartă marcajul ❓.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t>Cele trei care blochează cel mai mult</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="64" t="inlineStr">
+        <is>
+          <t>❓  Ne puteți da procedura scrisă de reconciliere, pentru cazul în care analiticul din balanța contabilă nu corespunde cu registrul mijloacelor fixe?  —  Blochează singurul flux de procedură din sistem (F-214) și corelația C-15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="64" t="inlineStr">
+        <is>
+          <t>❓  TVA nedeductibilă de pe rata de capital la leasingul financiar: se capitalizează în valoarea mijlocului fix (2133) sau se trece pe cheltuială (635 / 6588)?  —  Schimbă valoarea de intrare a mijlocului fix, deci amortizarea și impozitul pe profit pe toată durata contractului.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="64" t="inlineStr">
+        <is>
+          <t>❓  Care este baza legală exactă pentru a trata ca nedeductibilă diferența dintre valoarea rămasă și prețul de vânzare, față de art. 28 alin. (17)?  —  E testul central al MOD_IESIRE_MF; azi semnalează un risc fără să poată cita articolul pe care se sprijină.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="66" t="inlineStr">
+        <is>
+          <t>Nr.</t>
+        </is>
+      </c>
+      <c r="B9" s="66" t="inlineStr">
+        <is>
+          <t>Temă</t>
+        </is>
+      </c>
+      <c r="C9" s="66" t="inlineStr">
+        <is>
+          <t>Întrebare</t>
+        </is>
+      </c>
+      <c r="D9" s="66" t="inlineStr">
+        <is>
+          <t>Atinge</t>
+        </is>
+      </c>
+      <c r="E9" s="66" t="inlineStr">
+        <is>
+          <t>Ce depinde de răspuns</t>
+        </is>
+      </c>
+      <c r="F9" s="66" t="inlineStr">
+        <is>
+          <t>Ce am presupus</t>
+        </is>
+      </c>
+      <c r="G9" s="66" t="inlineStr">
+        <is>
+          <t>Sursa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="61" t="inlineStr">
+        <is>
+          <t>Î-01</t>
+        </is>
+      </c>
+      <c r="B10" s="61" t="inlineStr">
+        <is>
+          <t>Repartizarea rezultatului și rezultatul reportat</t>
+        </is>
+      </c>
+      <c r="C10" s="61" t="inlineStr">
+        <is>
+          <t>Care este temeiul legal al termenului de 3 ani pentru a decide ce se face cu soldul rămas în 1171?</t>
+        </is>
+      </c>
+      <c r="D10" s="61" t="inlineStr">
+        <is>
+          <t>F-103
+MOD_CAPITALURI
+C-21</t>
+        </is>
+      </c>
+      <c r="E10" s="61" t="inlineStr">
+        <is>
+          <t>F-103 (repartizarea rezultatului) și MOD_CAPITALURI. Dacă termenul există, modulul ar trebui să semnaleze soldurile 1171 mai vechi de 3 ani; dacă nu, semnalarea ar fi un fals pozitiv la fiecare client cu profit nerepartizat.</t>
+        </is>
+      </c>
+      <c r="F10" s="61" t="inlineStr">
+        <is>
+          <t>Nu l-am implementat. MOD_CAPITALURI raportează soldul 1171 pe an, prin C-21, fără să-l judece după vechime.</t>
+        </is>
+      </c>
+      <c r="G10" s="61" t="inlineStr">
+        <is>
+          <t>training 07.08.2026, întrebarea 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="61" t="inlineStr">
+        <is>
+          <t>Î-02</t>
+        </is>
+      </c>
+      <c r="B11" s="61" t="inlineStr">
+        <is>
+          <t>Repartizarea rezultatului și rezultatul reportat</t>
+        </is>
+      </c>
+      <c r="C11" s="61" t="inlineStr">
+        <is>
+          <t>În exemplul cu rezerva legală, profitul era 250 sau 2.500 lei?</t>
+        </is>
+      </c>
+      <c r="D11" s="61" t="inlineStr">
+        <is>
+          <t>F-103
+MOD_CAPITALURI</t>
+        </is>
+      </c>
+      <c r="E11" s="61" t="inlineStr">
+        <is>
+          <t>F-103 și MOD_CAPITALURI folosesc exemplul ca test. Am nevoie să știu dacă a fost o scăpare de notare sau dacă mi-a scăpat mie o regulă de calcul.</t>
+        </is>
+      </c>
+      <c r="F11" s="61" t="inlineStr">
+        <is>
+          <t>Am folosit 2.500 lei, singura variantă în care 5% dau 125. Dacă profitul chiar era 250, atunci procentul aplicat nu era 5% și trebuie relămurit.</t>
+        </is>
+      </c>
+      <c r="G11" s="61" t="inlineStr">
+        <is>
+          <t>training 07.08.2026, întrebarea 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="61" t="inlineStr">
+        <is>
+          <t>Î-03</t>
+        </is>
+      </c>
+      <c r="B12" s="61" t="inlineStr">
+        <is>
+          <t>Repartizarea rezultatului și rezultatul reportat</t>
+        </is>
+      </c>
+      <c r="C12" s="61" t="inlineStr">
+        <is>
+          <t>Pierderile nedeductibile fiscal se urmăresc pe analitic al lui 1171 sau pe alt cont?</t>
+        </is>
+      </c>
+      <c r="D12" s="61" t="inlineStr">
+        <is>
+          <t>C-21</t>
+        </is>
+      </c>
+      <c r="E12" s="61" t="inlineStr">
+        <is>
+          <t>C-21 cere ca 1171 să aibă analitic pe an, cu sensul debitor/creditor explicit. Dacă pierderea nedeductibilă are cont propriu, corelația trebuie extinsă, iar recuperarea în 5 ani (70% din profitul impozabil) se urmărește altfel.</t>
+        </is>
+      </c>
+      <c r="F12" s="61" t="inlineStr">
+        <is>
+          <t>Am lăsat 1171 cu analitic pe an, fără separare a pierderii nedeductibile.</t>
+        </is>
+      </c>
+      <c r="G12" s="61" t="inlineStr">
+        <is>
+          <t>training 07.08.2026, întrebarea 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="61" t="inlineStr">
+        <is>
+          <t>Î-04</t>
+        </is>
+      </c>
+      <c r="B13" s="61" t="inlineStr">
+        <is>
+          <t>Repartizarea rezultatului și rezultatul reportat</t>
+        </is>
+      </c>
+      <c r="C13" s="61" t="inlineStr">
+        <is>
+          <t>Care este actul normativ care a permanentizat termenul de 25 iunie pentru D101?</t>
+        </is>
+      </c>
+      <c r="D13" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="61" t="inlineStr">
+        <is>
+          <t>Checklistul de închidere din documentele revizuite și calendarul din foaia Legendă. Un termen greșit aici se propagă la toți clienții.</t>
+        </is>
+      </c>
+      <c r="F13" s="61" t="inlineStr">
+        <is>
+          <t>Am scris 25 iunie, marcat ca „de reconfirmat”.</t>
+        </is>
+      </c>
+      <c r="G13" s="61" t="inlineStr">
+        <is>
+          <t>training 07.08.2026, întrebarea 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="61" t="inlineStr">
+        <is>
+          <t>Î-05</t>
+        </is>
+      </c>
+      <c r="B14" s="61" t="inlineStr">
+        <is>
+          <t>Corectarea erorilor din exerciții anterioare</t>
+        </is>
+      </c>
+      <c r="C14" s="61" t="inlineStr">
+        <is>
+          <t>Cum se tratează o factură a exercițiului anterior, descoperită neînregistrată în anul curent — și când se folosește 1174 în loc de 628 cu semn schimbat?</t>
+        </is>
+      </c>
+      <c r="D14" s="61" t="inlineStr">
+        <is>
+          <t>F-105
+MOD_CAPITALURI
+C-18</t>
+        </is>
+      </c>
+      <c r="E14" s="61" t="inlineStr">
+        <is>
+          <t>F-105 (corecția erorilor prin 1174) și MOD_CAPITALURI. Pragul de semnificație din politicile contabile decide între cele două căi, dar nu știu ce prag folosește cabinetul.</t>
+        </is>
+      </c>
+      <c r="F14" s="61" t="inlineStr">
+        <is>
+          <t>Am construit arborele de decizie pe pragul de semnificație, cu 1174 pentru erorile semnificative din exerciții închise și corecția pe cheltuiala curentă sub prag. C-18 cere ca 1174 să ajungă la zero la 31.12.</t>
+        </is>
+      </c>
+      <c r="G14" s="61" t="inlineStr">
+        <is>
+          <t>training 07.08.2026, întrebarea 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="61" t="inlineStr">
+        <is>
+          <t>Î-06</t>
+        </is>
+      </c>
+      <c r="B15" s="61" t="inlineStr">
+        <is>
+          <t>Capital social și activ net</t>
+        </is>
+      </c>
+      <c r="C15" s="61" t="inlineStr">
+        <is>
+          <t>Cum se documentează reîntregirea activului net cerută de Legea 239/2025 — prin conversia creanței asociatului în capital sau prin aport nou?</t>
+        </is>
+      </c>
+      <c r="D15" s="61" t="inlineStr">
+        <is>
+          <t>C-20
+MOD_CAPITALURI</t>
+        </is>
+      </c>
+      <c r="E15" s="61" t="inlineStr">
+        <is>
+          <t>C-20 (testul de activ net) și MOD_CAPITALURI, care azi doar semnalează blocajul. Ca să propună o cale de rezolvare, are nevoie de varianta preferată a cabinetului.</t>
+        </is>
+      </c>
+      <c r="F15" s="61" t="inlineStr">
+        <is>
+          <t>Modulul semnalează blocajul și se oprește acolo — nu propune nicio soluție.</t>
+        </is>
+      </c>
+      <c r="G15" s="61" t="inlineStr">
+        <is>
+          <t>training 07.08.2026, întrebarea 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="61" t="inlineStr">
+        <is>
+          <t>Î-07</t>
+        </is>
+      </c>
+      <c r="B16" s="61" t="inlineStr">
+        <is>
+          <t>Capital social și activ net</t>
+        </is>
+      </c>
+      <c r="C16" s="61" t="inlineStr">
+        <is>
+          <t>Verificăm sistematic pragul de capital social minim (500 / 5.000 lei) pe tot portofoliul de clienți, sau doar la firmele noi?</t>
+        </is>
+      </c>
+      <c r="D16" s="61" t="inlineStr">
+        <is>
+          <t>F-101</t>
+        </is>
+      </c>
+      <c r="E16" s="61" t="inlineStr">
+        <is>
+          <t>F-101 (constituirea capitalului) și checklistul de deschidere de dosar. Dacă verificarea e sistematică, intră în checklistul lunar, nu în cel de deschidere.</t>
+        </is>
+      </c>
+      <c r="F16" s="61" t="inlineStr">
+        <is>
+          <t>Am pus-o în checklistul de deschidere a dosarului.</t>
+        </is>
+      </c>
+      <c r="G16" s="61" t="inlineStr">
+        <is>
+          <t>training 07.08.2026, întrebarea 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="61" t="inlineStr">
+        <is>
+          <t>Î-08</t>
+        </is>
+      </c>
+      <c r="B17" s="61" t="inlineStr">
+        <is>
+          <t>Leasing și vehicule</t>
+        </is>
+      </c>
+      <c r="C17" s="61" t="inlineStr">
+        <is>
+          <t>TVA nedeductibilă de pe rata de capital la leasingul financiar: se capitalizează în valoarea mijlocului fix (2133) sau se trece pe cheltuială (635 / 6588)?</t>
+        </is>
+      </c>
+      <c r="D17" s="61" t="inlineStr">
+        <is>
+          <t>F-108
+MOD_LEASING_FIN</t>
+        </is>
+      </c>
+      <c r="E17" s="61" t="inlineStr">
+        <is>
+          <t>F-108 și MOD_LEASING_FIN. E singura variabilă a modulului care schimbă valoarea de intrare a mijlocului fix, deci și amortizarea, deci și impozitul pe profit pe toată durata contractului.</t>
+        </is>
+      </c>
+      <c r="F17" s="61" t="inlineStr">
+        <is>
+          <t>Am făcut din ea o OPȚIUNE DE CONFIGURARE în modul (CAPITALIZEAZA / CHELTUIALA), cu implicit „capitalizează”, coerent cu tratamentul avansului. Nu am tranșat-o ca regulă.</t>
+        </is>
+      </c>
+      <c r="G17" s="61" t="inlineStr">
+        <is>
+          <t>training 07.08.2026, întrebarea 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="61" t="inlineStr">
+        <is>
+          <t>Î-09</t>
+        </is>
+      </c>
+      <c r="B18" s="61" t="inlineStr">
+        <is>
+          <t>Imobilizări — prag și amortizare</t>
+        </is>
+      </c>
+      <c r="C18" s="61" t="inlineStr">
+        <is>
+          <t>Recomandați alinierea pragului contabil de recunoaștere la cel fiscal (5.000 lei), sau menținerea unui prag intern mai mic pentru control de gestiune?</t>
+        </is>
+      </c>
+      <c r="D18" s="61" t="inlineStr">
+        <is>
+          <t>MOD_IMOBILIZARI</t>
+        </is>
+      </c>
+      <c r="E18" s="61" t="inlineStr">
+        <is>
+          <t>MOD_IMOBILIZARI face un test de prag la intrare. Dacă cele două praguri diferă, apar diferențe temporare de urmărit în registrul de evidență fiscală — un lucru pe care modulul nu îl tratează azi.</t>
+        </is>
+      </c>
+      <c r="F18" s="61" t="inlineStr">
+        <is>
+          <t>Am folosit un singur prag, cel fiscal, și am semnalat în notițe că divergența produce diferențe temporare.</t>
+        </is>
+      </c>
+      <c r="G18" s="61" t="inlineStr">
+        <is>
+          <t>training 12.08.2026, întrebarea 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="61" t="inlineStr">
+        <is>
+          <t>Î-10</t>
+        </is>
+      </c>
+      <c r="B19" s="61" t="inlineStr">
+        <is>
+          <t>Imobilizări — prag și amortizare</t>
+        </is>
+      </c>
+      <c r="C19" s="61" t="inlineStr">
+        <is>
+          <t>Excepția de la cumulul cu profitul reinvestit (art. 22 alin. 9) acoperă doar amortizarea accelerată, sau și pe cea superaccelerată de 65%?</t>
+        </is>
+      </c>
+      <c r="D19" s="61" t="inlineStr">
+        <is>
+          <t>F-204
+MOD_IMOBILIZARI</t>
+        </is>
+      </c>
+      <c r="E19" s="61" t="inlineStr">
+        <is>
+          <t>F-204 și MOD_IMOBILIZARI, la alegerea metodei de amortizare. Dacă excepția nu acoperă superaccelerata, calculul comparativ are altă concluzie.</t>
+        </is>
+      </c>
+      <c r="F19" s="61" t="inlineStr">
+        <is>
+          <t>Nu am implementat comparația. Modulul propune metoda, fără să optimizeze fiscal.</t>
+        </is>
+      </c>
+      <c r="G19" s="61" t="inlineStr">
+        <is>
+          <t>training 12.08.2026, întrebarea 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="61" t="inlineStr">
+        <is>
+          <t>Î-11</t>
+        </is>
+      </c>
+      <c r="B20" s="61" t="inlineStr">
+        <is>
+          <t>Imobilizări — ieșiri din gestiune</t>
+        </is>
+      </c>
+      <c r="C20" s="61" t="inlineStr">
+        <is>
+          <t>Care este baza legală exactă pentru a trata ca nedeductibilă diferența dintre valoarea rămasă și prețul de vânzare, față de art. 28 alin. (17)?</t>
+        </is>
+      </c>
+      <c r="D20" s="61" t="inlineStr">
+        <is>
+          <t>F-211
+MOD_IESIRE_MF</t>
+        </is>
+      </c>
+      <c r="E20" s="61" t="inlineStr">
+        <is>
+          <t>F-211 și MOD_IESIRE_MF. E testul central al modulului: azi calculează diferența și cere documentul justificativ, dar nu poate cita articolul pe care se sprijină.</t>
+        </is>
+      </c>
+      <c r="F20" s="61" t="inlineStr">
+        <is>
+          <t>Modulul semnalează riscul și cere documentarea prețului, invocând art. 11 (reîncadrare) și art. 25 alin. (1) (scopul activității economice) — nu art. 28.</t>
+        </is>
+      </c>
+      <c r="G20" s="61" t="inlineStr">
+        <is>
+          <t>training 12.08.2026, întrebarea 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="61" t="inlineStr">
+        <is>
+          <t>Î-12</t>
+        </is>
+      </c>
+      <c r="B21" s="61" t="inlineStr">
+        <is>
+          <t>Imobilizări — ieșiri din gestiune</t>
+        </is>
+      </c>
+      <c r="C21" s="61" t="inlineStr">
+        <is>
+          <t>La o casare din care nu rezultă nici deșeuri, nici piese reutilizabile, cum se justifică deductibilitatea valorii rămase neamortizate?</t>
+        </is>
+      </c>
+      <c r="D21" s="61" t="inlineStr">
+        <is>
+          <t>F-212
+MOD_IESIRE_MF</t>
+        </is>
+      </c>
+      <c r="E21" s="61" t="inlineStr">
+        <is>
+          <t>F-212 (casarea) și MOD_IESIRE_MF, unde valoarea pieselor recuperate poate fi zero. Fără răspuns, modulul nu poate spune dacă procesul-verbal de scoatere din funcțiune e suficient singur.</t>
+        </is>
+      </c>
+      <c r="F21" s="61" t="inlineStr">
+        <is>
+          <t>Modulul acceptă valoarea zero a recuperărilor și lasă deductibilitatea nejudecată, cu procesul-verbal ca singur document.</t>
+        </is>
+      </c>
+      <c r="G21" s="61" t="inlineStr">
+        <is>
+          <t>training 12.08.2026, întrebarea 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="61" t="inlineStr">
+        <is>
+          <t>Î-13</t>
+        </is>
+      </c>
+      <c r="B22" s="61" t="inlineStr">
+        <is>
+          <t>Imobilizări — control și raportare</t>
+        </is>
+      </c>
+      <c r="C22" s="61" t="inlineStr">
+        <is>
+          <t>În secțiunea Active din D406 (SAF-T) se raportează și 231 (investiții neterminate), și 261 (imobilizări financiare)?</t>
+        </is>
+      </c>
+      <c r="D22" s="61" t="inlineStr">
+        <is>
+          <t>F-208
+F-213</t>
+        </is>
+      </c>
+      <c r="E22" s="61" t="inlineStr">
+        <is>
+          <t>Coloana Declarativ a fluxurilor F-208 (imobilizări în curs) și F-213 (imobilizări financiare). Azi nu marchez D406 pe ele, ca să nu afirm ceva greșit.</t>
+        </is>
+      </c>
+      <c r="F22" s="61" t="inlineStr">
+        <is>
+          <t>Le-am lăsat nemarcate în coloana Declarativ.</t>
+        </is>
+      </c>
+      <c r="G22" s="61" t="inlineStr">
+        <is>
+          <t>training 12.08.2026, întrebarea 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="61" t="inlineStr">
+        <is>
+          <t>Î-14</t>
+        </is>
+      </c>
+      <c r="B23" s="61" t="inlineStr">
+        <is>
+          <t>Imobilizări — control și raportare</t>
+        </is>
+      </c>
+      <c r="C23" s="61" t="inlineStr">
+        <is>
+          <t>Ne puteți da procedura scrisă de reconciliere, pentru cazul în care analiticul din balanța contabilă nu corespunde cu registrul mijloacelor fixe?</t>
+        </is>
+      </c>
+      <c r="D23" s="61" t="inlineStr">
+        <is>
+          <t>F-214
+C-15</t>
+        </is>
+      </c>
+      <c r="E23" s="61" t="inlineStr">
+        <is>
+          <t>F-214 este singurul flux de PROCEDURĂ din tot sistemul — nu produce note contabile, descrie un control lunar. Azi se oprește la „dacă soldurile nu corespund”, fără pașii de rezolvare. C-15 depinde de aceeași procedură.</t>
+        </is>
+      </c>
+      <c r="F23" s="61" t="inlineStr">
+        <is>
+          <t>Am scris pașii de identificare (listing, comparare pe perechi 21x↔28x, fișă de cont), dar NU și pașii de corecție — aceia sunt procedura promisă.</t>
+        </is>
+      </c>
+      <c r="G23" s="61" t="inlineStr">
+        <is>
+          <t>training 12.08.2026, întrebarea 6 — PUNCTUL CEL MAI IMPORTANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="61" t="inlineStr">
+        <is>
+          <t>Î-15</t>
+        </is>
+      </c>
+      <c r="B24" s="61" t="inlineStr">
+        <is>
+          <t>Stocuri și producție</t>
+        </is>
+      </c>
+      <c r="C24" s="61" t="inlineStr">
+        <is>
+          <t>Care sunt celelalte metode de calculație a costurilor acceptate de OMFP 1802/2014, și în ce situații se alege fiecare?</t>
+        </is>
+      </c>
+      <c r="D24" s="61" t="inlineStr">
+        <is>
+          <t>F-311</t>
+        </is>
+      </c>
+      <c r="E24" s="61" t="inlineStr">
+        <is>
+          <t>F-311 (producția multi-stadiu) ține gestiunea lui 331 analitic pe comandă. Pe faze, structura analitică e alta, deci și fluxul.</t>
+        </is>
+      </c>
+      <c r="F24" s="61" t="inlineStr">
+        <is>
+          <t>Am implementat doar metoda pe comenzi.</t>
+        </is>
+      </c>
+      <c r="G24" s="61" t="inlineStr">
+        <is>
+          <t>training 14.08.2026, întrebarea 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="61" t="inlineStr">
+        <is>
+          <t>Î-16</t>
+        </is>
+      </c>
+      <c r="B25" s="61" t="inlineStr">
+        <is>
+          <t>TVA — import, vamă, taxare inversă</t>
+        </is>
+      </c>
+      <c r="C25" s="61" t="inlineStr">
+        <is>
+          <t>La decontarea cu comisionarul vamal folosiți 446 sau 462? Care e standardul cabinetului și de ce?</t>
+        </is>
+      </c>
+      <c r="D25" s="61" t="inlineStr">
+        <is>
+          <t>F-319</t>
+        </is>
+      </c>
+      <c r="E25" s="61" t="inlineStr">
+        <is>
+          <t>F-319 (import prin comisionar) și analiticul 446.VAMA din foaia Analitice. Contul ales determină unde apare soldul în bilanț: datorie la buget vs. datorie către un terț.</t>
+        </is>
+      </c>
+      <c r="F25" s="61" t="inlineStr">
+        <is>
+          <t>Am păstrat 446.VAMA, ca în notițe, și am notat 461/462 ca alternativă.</t>
+        </is>
+      </c>
+      <c r="G25" s="61" t="inlineStr">
+        <is>
+          <t>training 14.08.2026, întrebarea 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="61" t="inlineStr">
+        <is>
+          <t>Î-17</t>
+        </is>
+      </c>
+      <c r="B26" s="61" t="inlineStr">
+        <is>
+          <t>TVA — import, vamă, taxare inversă</t>
+        </is>
+      </c>
+      <c r="C26" s="61" t="inlineStr">
+        <is>
+          <t>Verificăm sistematic dacă clienții importatori îndeplinesc condițiile pentru certificatul de amânare de la plata TVA în vamă?</t>
+        </is>
+      </c>
+      <c r="D26" s="61" t="inlineStr">
+        <is>
+          <t>F-320</t>
+        </is>
+      </c>
+      <c r="E26" s="61" t="inlineStr">
+        <is>
+          <t>F-320 (import cu plată directă) capătă o a treia variantă dacă certificatul există. Ar trebui să intre în checklistul de deschidere a dosarului.</t>
+        </is>
+      </c>
+      <c r="F26" s="61" t="inlineStr">
+        <is>
+          <t>L-am adăugat ca variantă în documentul revizuit, dar nu în checklist.</t>
+        </is>
+      </c>
+      <c r="G26" s="61" t="inlineStr">
+        <is>
+          <t>training 14.08.2026, întrebarea 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="61" t="inlineStr">
+        <is>
+          <t>Î-18</t>
+        </is>
+      </c>
+      <c r="B27" s="61" t="inlineStr">
+        <is>
+          <t>TVA — import, vamă, taxare inversă</t>
+        </is>
+      </c>
+      <c r="C27" s="61" t="inlineStr">
+        <is>
+          <t>Derogarea UE pentru taxarea inversă la cereale și electronice avea termen 31.12.2026 — a fost prelungită?</t>
+        </is>
+      </c>
+      <c r="D27" s="61" t="inlineStr">
+        <is>
+          <t>F-402</t>
+        </is>
+      </c>
+      <c r="E27" s="61" t="inlineStr">
+        <is>
+          <t>F-402 (taxare inversă internă) și lista de categorii din documentul revizuit. Aplicarea taxării inverse după expirare înseamnă factură greșit întocmită.</t>
+        </is>
+      </c>
+      <c r="F27" s="61" t="inlineStr">
+        <is>
+          <t>Am marcat termenul în document cu avertisment de reverificare.</t>
+        </is>
+      </c>
+      <c r="G27" s="61" t="inlineStr">
+        <is>
+          <t>training 14.08.2026, întrebarea 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="61" t="inlineStr">
+        <is>
+          <t>Î-19</t>
+        </is>
+      </c>
+      <c r="B28" s="61" t="inlineStr">
+        <is>
+          <t>TVA — ajustări fără document</t>
+        </is>
+      </c>
+      <c r="C28" s="61" t="inlineStr">
+        <is>
+          <t>La lipsa la inventar, practica implicită a cabinetului este colectarea de TVA sau ajustarea dreptului de deducere? Ce set de documente se cere clientului?</t>
+        </is>
+      </c>
+      <c r="D28" s="61" t="inlineStr">
+        <is>
+          <t>F-406
+C-03
+C-04</t>
+        </is>
+      </c>
+      <c r="E28" s="61" t="inlineStr">
+        <is>
+          <t>F-406 (înregistrări fără document) și corelațiile C-03 / C-04, unde ajustările care nu vin din facturi trebuie să apară în jurnale cu semnul corect. Cele două tratamente ating conturi diferite, deci și jurnale diferite.</t>
+        </is>
+      </c>
+      <c r="F28" s="61" t="inlineStr">
+        <is>
+          <t>Am descris toate patru situațiile, fără să declar una ca implicită.</t>
+        </is>
+      </c>
+      <c r="G28" s="61" t="inlineStr">
+        <is>
+          <t>training 14.08.2026, întrebarea 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="61" t="inlineStr">
+        <is>
+          <t>Î-20</t>
+        </is>
+      </c>
+      <c r="B29" s="61" t="inlineStr">
+        <is>
+          <t>Obligații de mediu</t>
+        </is>
+      </c>
+      <c r="C29" s="61" t="inlineStr">
+        <is>
+          <t>Care este termenul curent de depunere a declarației la Fondul pentru Mediu — lunar sau trimestrial?</t>
+        </is>
+      </c>
+      <c r="D29" s="61" t="inlineStr">
+        <is>
+          <t>F-310</t>
+        </is>
+      </c>
+      <c r="E29" s="61" t="inlineStr">
+        <is>
+          <t>F-310 (ambalaje și taxa AFM) și checklistul lunar. Un termen greșit produce penalități direct.</t>
+        </is>
+      </c>
+      <c r="F29" s="61" t="inlineStr">
+        <is>
+          <t>Am lăsat termenul nespecificat, cu trimitere la sursa oficială.</t>
+        </is>
+      </c>
+      <c r="G29" s="61" t="inlineStr">
+        <is>
+          <t>training 14.08.2026, întrebarea 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="61" t="inlineStr">
+        <is>
+          <t>Î-21</t>
+        </is>
+      </c>
+      <c r="B30" s="61" t="inlineStr">
+        <is>
+          <t>Material lipsă din notițe</t>
+        </is>
+      </c>
+      <c r="C30" s="61" t="inlineStr">
+        <is>
+          <t>Ce fișier și ce sarcină erau în spatele notițelor „Fișierul atașat arată corelații importante între conturi” și „task”?</t>
+        </is>
+      </c>
+      <c r="D30" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="61" t="inlineStr">
+        <is>
+          <t>Fișierul cu corelații ar putea conține exact materialul din foaia „Corelații de control”, care azi are 22 de corelații construite de mine. Dacă există o listă a formatorului, merită confruntată cu a mea.</t>
+        </is>
+      </c>
+      <c r="F30" s="61" t="inlineStr">
+        <is>
+          <t>Am construit corelațiile din notițe și din practică, fără fișierul original.</t>
+        </is>
+      </c>
+      <c r="G30" s="61" t="inlineStr">
+        <is>
+          <t>training 14.08.2026, întrebarea 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="63" t="inlineStr">
+        <is>
+          <t>21 de întrebări, 12 teme. Aceeași sursă cu dist/intrebari-formator.md și cu pagina publicată — nu pot diverge.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1889,7 +2891,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="62" t="inlineStr">
+      <c r="A2" s="63" t="inlineStr">
         <is>
           <t>Foaia de lucru descrie sistemul așa cum este ACUM, ordonat contabil. Aici stă cronologia: ce s-a renumerotat, ce s-a contopit, ce s-a eliminat ca duplicat și ce narativ de etapă a fost mutat din Legendă. Nimic din originalul training 4 nu s-a pierdut — s-a mutat.</t>
         </is>
@@ -1903,7 +2905,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="62" t="inlineStr">
+      <c r="A5" s="63" t="inlineStr">
         <is>
           <t>Numerotarea veche era secvențială, în ordinea livrărilor. Cea nouă codifică clasa contului principal, deci un flux adăugat peste un an primește următorul număr liber din clasa lui și stă fizic la locul lui. Tabelul rămâne aici permanent, ca referințele vechi să se poată rezolva. Ultima coloană păstrează statusul dinainte de curățare: „(Etapa N)” era istoric de livrare, nu stare a fluxului, deci a ieșit din foaia de lucru.</t>
         </is>
@@ -3444,7 +4446,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="62" t="inlineStr">
+      <c r="A69" s="63" t="inlineStr">
         <is>
           <t>Fluxul absorbit nu a fost șters: pașii și cifrele lui au devenit o variantă etichetată în interiorul fluxului gazdă.</t>
         </is>
@@ -3629,7 +4631,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="62" t="inlineStr">
+      <c r="A81" s="63" t="inlineStr">
         <is>
           <t>Păstrat cuvânt cu cuvânt, ca poarta de conservare să treacă fără excepții și ca formularea să rămână consultabilă.</t>
         </is>
@@ -4369,7 +5371,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="62" t="inlineStr">
+      <c r="A138" s="63" t="inlineStr">
         <is>
           <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
         </is>
@@ -4425,7 +5427,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="62" t="inlineStr">
+      <c r="A147" s="63" t="inlineStr">
         <is>
           <t>Descria ordinea livrărilor, nu conținutul contabil. Mutat aici verbatim ca Legenda să descrie sistemul, nu istoria lui.</t>
         </is>
@@ -20167,7 +21169,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="62" t="inlineStr">
+      <c r="A2" s="63" t="inlineStr">
         <is>
           <t>Ordonat pe simbol de cont, ca planul de conturi. Rândurile duplicate apărute la extinderi succesive au fost contopite, fără pierdere de text.</t>
         </is>
@@ -22619,7 +23621,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="62" t="inlineStr">
+      <c r="A4" s="63" t="inlineStr">
         <is>
           <t>Observație păstrată din gruparea veche, valabilă în continuare: fluxurile didactice grele „nu sunt liniare. Fiecare pornește dintr-o stare «murdară» sau produce intersecție între două roluri. Acolo apar erorile de cabinet.” Ele nu mai stau grupate la final, ci fiecare la clasa lui de conturi.</t>
         </is>
@@ -22633,7 +23635,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="62" t="inlineStr">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>Catalogul se generează din monografiile reale, deci nu poate să rămână în urma lor. ★ = flux didactic, cu pas revelator identificat.</t>
         </is>
@@ -22724,7 +23726,7 @@
       </c>
       <c r="H11" s="69" t="inlineStr">
         <is>
-          <t>Prag minim: 500 lei firme noi / 5.000 lei la CA netă &gt; 400.000 lei (L. 239/2025)</t>
+          <t>Prag minim: 500 lei firme noi / 5.000 lei la CA netă &gt; 400.000 lei (L. 239/2025) | ❓ Î-07</t>
         </is>
       </c>
     </row>
@@ -22804,7 +23806,7 @@
       </c>
       <c r="H13" s="70" t="inlineStr">
         <is>
-          <t>Pas revelator: 121 = 129 (NU 129 = 1171). D101</t>
+          <t>Pas revelator: 121 = 129 (NU 129 = 1171). D101 | modul: MOD_CAPITALURI | ❓ Î-01, Î-02</t>
         </is>
       </c>
     </row>
@@ -22844,7 +23846,7 @@
       </c>
       <c r="H14" s="29" t="inlineStr">
         <is>
-          <t>Pas revelator: 121 colectează cls.6+7. D101, D100</t>
+          <t>Pas revelator: 121 colectează cls.6+7. D101, D100 | modul: MOD_INCHIDERE_EX</t>
         </is>
       </c>
     </row>
@@ -22884,7 +23886,7 @@
       </c>
       <c r="H15" s="70" t="inlineStr">
         <is>
-          <t>Pas revelator: cheltuiala nu atinge niciodată 121. D101 rectificativ</t>
+          <t>Pas revelator: cheltuiala nu atinge niciodată 121. D101 rectificativ | modul: MOD_CAPITALURI | ❓ Î-05</t>
         </is>
       </c>
     </row>
@@ -22924,7 +23926,7 @@
       </c>
       <c r="H16" s="69" t="inlineStr">
         <is>
-          <t>Nedeductibil fiscal — nu e optimizare, e imagine fidelă</t>
+          <t>Nedeductibil fiscal — nu e optimizare, e imagine fidelă | modul: MOD_PROVIZION</t>
         </is>
       </c>
     </row>
@@ -22964,7 +23966,7 @@
       </c>
       <c r="H17" s="70" t="inlineStr">
         <is>
-          <t>Pas revelator: reevaluarea LUNARĂ a soldului, nu doar diferența la plată</t>
+          <t>Pas revelator: reevaluarea LUNARĂ a soldului, nu doar diferența la plată | modul: MOD_CREDIT_VALUTA</t>
         </is>
       </c>
     </row>
@@ -23004,7 +24006,7 @@
       </c>
       <c r="H18" s="70" t="inlineStr">
         <is>
-          <t>Pas revelator: 167 este 1-la-1 cu contractul. D300, D101</t>
+          <t>Pas revelator: 167 este 1-la-1 cu contractul. D300, D101 | modul: MOD_LEASING_FIN | ❓ Î-08</t>
         </is>
       </c>
     </row>
@@ -23131,7 +24133,7 @@
       </c>
       <c r="H22" s="70" t="inlineStr">
         <is>
-          <t>Pas revelator: codul 27 în D394 pentru taxare inversă la clădiri</t>
+          <t>Pas revelator: codul 27 în D394 pentru taxare inversă la clădiri | modul: MOD_IMOBILIZARI</t>
         </is>
       </c>
     </row>
@@ -23171,7 +24173,7 @@
       </c>
       <c r="H23" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>modul: MOD_LEASING_FIN | ❓ Î-10</t>
         </is>
       </c>
     </row>
@@ -23211,7 +24213,7 @@
       </c>
       <c r="H24" s="69" t="inlineStr">
         <is>
-          <t>Taxele vamale și transportul se CAPITALIZEAZĂ. D390, D300</t>
+          <t>Taxele vamale și transportul se CAPITALIZEAZĂ. D390, D300 | modul: MOD_IMOBILIZARI</t>
         </is>
       </c>
     </row>
@@ -23291,7 +24293,7 @@
       </c>
       <c r="H26" s="69" t="inlineStr">
         <is>
-          <t>Oglinda lui F-302, pe imobilizări în loc de stocuri</t>
+          <t>Oglinda lui F-302, pe imobilizări în loc de stocuri | modul: MOD_IMOBILIZARI</t>
         </is>
       </c>
     </row>
@@ -23331,7 +24333,7 @@
       </c>
       <c r="H27" s="70" t="inlineStr">
         <is>
-          <t>Pas revelator: 722, nu 711 — și nu 628 pentru prestațiile terților</t>
+          <t>Pas revelator: 722, nu 711 — și nu 628 pentru prestațiile terților | ❓ Î-13</t>
         </is>
       </c>
     </row>
@@ -23371,7 +24373,7 @@
       </c>
       <c r="H28" s="29" t="inlineStr">
         <is>
-          <t>Pas revelator: 722 neutralizează cheltuiala capitalizată</t>
+          <t>Pas revelator: 722 neutralizează cheltuiala capitalizată | modul: MOD_NEUTRALIZARE</t>
         </is>
       </c>
     </row>
@@ -23411,7 +24413,7 @@
       </c>
       <c r="H29" s="29" t="inlineStr">
         <is>
-          <t>Pas revelator: eliberare sistematică 475 → venit</t>
+          <t>Pas revelator: eliberare sistematică 475 → venit | modul: MOD_SUBVENTIE</t>
         </is>
       </c>
     </row>
@@ -23451,7 +24453,7 @@
       </c>
       <c r="H30" s="70" t="inlineStr">
         <is>
-          <t>Pas revelator: 6583 deductibil în limita venitului. D101</t>
+          <t>Pas revelator: 6583 deductibil în limita venitului. D101 | modul: MOD_IESIRE_MF | ❓ Î-11</t>
         </is>
       </c>
     </row>
@@ -23491,7 +24493,7 @@
       </c>
       <c r="H31" s="69" t="inlineStr">
         <is>
-          <t>Piesele recuperate intră pe stoc, nu direct pe venit la vânzare</t>
+          <t>Piesele recuperate intră pe stoc, nu direct pe venit la vânzare | modul: MOD_IESIRE_MF | ❓ Î-12</t>
         </is>
       </c>
     </row>
@@ -23531,7 +24533,7 @@
       </c>
       <c r="H32" s="69" t="inlineStr">
         <is>
-          <t>Analitic pe partener/contract, obligatoriu</t>
+          <t>Analitic pe partener/contract, obligatoriu | ❓ Î-13</t>
         </is>
       </c>
     </row>
@@ -23571,7 +24573,7 @@
       </c>
       <c r="H33" s="70" t="inlineStr">
         <is>
-          <t>Flux de CONTROL: pașii sunt verificări, nu înregistrări</t>
+          <t>Flux de CONTROL: pașii sunt verificări, nu înregistrări | modul: MOD_IMOBILIZARI | ❓ Î-14</t>
         </is>
       </c>
     </row>
@@ -23658,7 +24660,7 @@
       </c>
       <c r="H36" s="29" t="inlineStr">
         <is>
-          <t>D300; pas revelator: stingere 30x=32x</t>
+          <t>D300; pas revelator: stingere 30x=32x | modul: MOD_APROV_TRANZIT</t>
         </is>
       </c>
     </row>
@@ -23738,7 +24740,7 @@
       </c>
       <c r="H38" s="28" t="inlineStr">
         <is>
-          <t>Intermediar 408 (pas revelator: coexistă cu 327)</t>
+          <t>Intermediar 408 (pas revelator: coexistă cu 327) | modul: MOD_APROV_TRANZIT / MOD_INTERMEDIAR</t>
         </is>
       </c>
     </row>
@@ -23978,7 +24980,7 @@
       </c>
       <c r="H44" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❓ Î-20</t>
         </is>
       </c>
     </row>
@@ -24018,7 +25020,7 @@
       </c>
       <c r="H45" s="29" t="inlineStr">
         <is>
-          <t>Pas revelator: 711 ține 121 la zero până la livrare</t>
+          <t>Pas revelator: 711 ține 121 la zero până la livrare | modul: MOD_NEUTRALIZARE | ❓ Î-15</t>
         </is>
       </c>
     </row>
@@ -24058,7 +25060,7 @@
       </c>
       <c r="H46" s="23" t="inlineStr">
         <is>
-          <t>Pas revelator: 712 neutralizează pentru servicii în curs</t>
+          <t>Pas revelator: 712 neutralizează pentru servicii în curs | modul: MOD_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="I46" s="23" t="inlineStr">
@@ -24143,7 +25145,7 @@
       </c>
       <c r="H48" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>modul: MOD_INCHIDERE_EX</t>
         </is>
       </c>
     </row>
@@ -24223,7 +25225,7 @@
       </c>
       <c r="H50" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>modul: MOD_VANZ_AMANUNT</t>
         </is>
       </c>
     </row>
@@ -24263,7 +25265,7 @@
       </c>
       <c r="H51" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>modul: MOD_VANZ_AMANUNT</t>
         </is>
       </c>
     </row>
@@ -24303,7 +25305,7 @@
       </c>
       <c r="H52" s="28" t="inlineStr">
         <is>
-          <t>Rectificativ invers (pas revelator)</t>
+          <t>Rectificativ invers (pas revelator) | modul: MOD_VANZ_AMANUNT</t>
         </is>
       </c>
     </row>
@@ -24343,7 +25345,7 @@
       </c>
       <c r="H53" s="29" t="inlineStr">
         <is>
-          <t>Pas revelator: 446.VAMA se stinge. D300, D394</t>
+          <t>Pas revelator: 446.VAMA se stinge. D300, D394 | ❓ Î-16</t>
         </is>
       </c>
     </row>
@@ -24383,7 +25385,7 @@
       </c>
       <c r="H54" s="30" t="inlineStr">
         <is>
-          <t>D300</t>
+          <t>D300 | ❓ Î-17</t>
         </is>
       </c>
     </row>
@@ -24430,7 +25432,7 @@
       </c>
       <c r="H56" s="29" t="inlineStr">
         <is>
-          <t>Pas revelator: 4428.INC la încasare/plată. D300</t>
+          <t>Pas revelator: 4428.INC la încasare/plată. D300 | modul: MOD_TVA_INCASARE</t>
         </is>
       </c>
     </row>
@@ -24470,7 +25472,7 @@
       </c>
       <c r="H57" s="30" t="inlineStr">
         <is>
-          <t>D300</t>
+          <t>D300 | ❓ Î-18</t>
         </is>
       </c>
     </row>
@@ -24590,7 +25592,7 @@
       </c>
       <c r="H60" s="29" t="inlineStr">
         <is>
-          <t>Pas revelator: 4426/4427 fără sold după închidere. D300</t>
+          <t>Pas revelator: 4426/4427 fără sold după închidere. D300 | modul: MOD_INCHIDERE_TVA</t>
         </is>
       </c>
     </row>
@@ -24630,7 +25632,7 @@
       </c>
       <c r="H61" s="30" t="inlineStr">
         <is>
-          <t>D300 (ajustare), D100</t>
+          <t>D300 (ajustare), D100 | ❓ Î-19</t>
         </is>
       </c>
     </row>
@@ -24710,7 +25712,7 @@
       </c>
       <c r="H63" s="29" t="inlineStr">
         <is>
-          <t>Pas revelator: stingere la document. D300 (când se facturează)</t>
+          <t>Pas revelator: stingere la document. D300 (când se facturează) | modul: MOD_INTERMEDIAR</t>
         </is>
       </c>
     </row>
@@ -24830,7 +25832,7 @@
       </c>
       <c r="H66" s="29" t="inlineStr">
         <is>
-          <t>Pas revelator: sold 473 la 31.12 = suspect. Clarificare obligatorie.</t>
+          <t>Pas revelator: sold 473 la 31.12 = suspect. Clarificare obligatorie. | modul: MOD_INTERMEDIAR</t>
         </is>
       </c>
     </row>
@@ -24910,7 +25912,7 @@
       </c>
       <c r="H68" s="23" t="inlineStr">
         <is>
-          <t>D112, D100</t>
+          <t>D112, D100 | modul: MOD_SALARII</t>
         </is>
       </c>
     </row>
@@ -25037,7 +26039,7 @@
       </c>
       <c r="H72" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>modul: MOD_DECONT</t>
         </is>
       </c>
     </row>
@@ -30184,7 +31186,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="62" t="inlineStr">
+      <c r="A244" s="63" t="inlineStr">
         <is>
           <t>De ce e variantă și nu flux separat: F-208 era conținut practic de F-208: aceeași secvență 231 → 21x, doar fără pasul de capitalizare a salariilor.</t>
         </is>
@@ -31375,7 +32377,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="62" t="inlineStr">
+      <c r="A290" s="63" t="inlineStr">
         <is>
           <t>De ce e variantă și nu flux separat: F-211 și F-211 tratau același subiect (vânzarea unui mijloc fix) cu cifre diferite; F-211 adaugă testul fiscal care lipsea.</t>
         </is>
@@ -42394,7 +43396,7 @@
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>F-316, F-318, F-409</t>
+          <t>F-316, F-318, F-409 | Module_Declarative_Fluxuri.xlsx → MOD_VANZ_AMANUNT</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -42436,7 +43438,7 @@
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>F-401, F-402, F-405 | Module_Declarative_Fluxuri.xlsx → MOD_TVA_INCASARE</t>
+          <t>F-401, F-402, F-405 | Module_Declarative_Fluxuri.xlsx → MOD_TVA_INCASARE | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_TVA | ❓ Î-19</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -42479,7 +43481,7 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>F-316, F-401, F-403, F-404, F-410</t>
+          <t>F-316, F-401, F-403, F-404, F-410 | Module_Declarative_Fluxuri.xlsx → MOD_VANZ_AMANUNT / MOD_TVA_INCASARE | ❓ Î-19</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -42563,7 +43565,7 @@
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>F-104, F-314, F-311, F-312, F-209 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_EX</t>
+          <t>F-104, F-314, F-311, F-312, F-209 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_EX | Module_Declarative_Fluxuri.xlsx → MOD_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -42604,7 +43606,7 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>F-204, F-211, F-210</t>
+          <t>F-204, F-211, F-210 | Module_Declarative_Fluxuri.xlsx → MOD_LEASING_FIN / MOD_IESIRE_MF / MOD_SUBVENTIE</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -42686,7 +43688,7 @@
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>F-302, F-304 | Module_Declarative_Fluxuri.xlsx → MOD_APROV_TRANZIT</t>
+          <t>F-302, F-304 | Module_Declarative_Fluxuri.xlsx → MOD_APROV_TRANZIT | Module_Declarative_Fluxuri.xlsx → MOD_INTERMEDIAR</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -42727,7 +43729,7 @@
       </c>
       <c r="F14" s="28" t="inlineStr">
         <is>
-          <t>F-408, F-304 | Module_Declarative_Fluxuri.xlsx → MOD_INTERMEDIAR</t>
+          <t>F-408, F-304 | Module_Declarative_Fluxuri.xlsx → MOD_INTERMEDIAR | Module_Declarative_Fluxuri.xlsx → MOD_APROV_TRANZIT</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -42910,29 +43912,29 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="63" t="inlineStr">
+      <c r="A31" s="61" t="inlineStr">
         <is>
           <t>C-13</t>
         </is>
       </c>
-      <c r="B31" s="63" t="inlineStr">
+      <c r="B31" s="61" t="inlineStr">
         <is>
           <t>sold 28x ≤ sold 21x
 (pe fiecare mijloc fix, nu pe total)</t>
         </is>
       </c>
-      <c r="C31" s="63" t="inlineStr">
+      <c r="C31" s="61" t="inlineStr">
         <is>
           <t>Balanță analitică 21x vs. 28x, pe mijloc</t>
         </is>
       </c>
-      <c r="D31" s="63" t="inlineStr">
+      <c r="D31" s="61" t="inlineStr">
         <is>
           <t>Nimic — amortizarea cumulată nu poate depăși valoarea de intrare.
 Bun integral amortizat: sold 28x = sold 21x (egalitate, nu depășire).</t>
         </is>
       </c>
-      <c r="E31" s="63" t="inlineStr">
+      <c r="E31" s="61" t="inlineStr">
         <is>
           <t>Amortizare calculată peste durata normală
 Mijloc ieșit din gestiune fără descărcarea lui 28x
@@ -42940,328 +43942,328 @@
 Cont setat greșit în planul societății (bifuncțional sau pe sens invers)</t>
         </is>
       </c>
-      <c r="F31" s="63" t="inlineStr">
-        <is>
-          <t>F-211, F-212, F-214</t>
-        </is>
-      </c>
-      <c r="G31" s="63" t="inlineStr">
+      <c r="F31" s="61" t="inlineStr">
+        <is>
+          <t>F-211, F-212, F-214 | Module_Declarative_Fluxuri.xlsx → MOD_IESIRE_MF / MOD_IMOBILIZARI</t>
+        </is>
+      </c>
+      <c r="G31" s="61" t="inlineStr">
         <is>
           <t>Înaltă — valoare netă și rezultat denaturate</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="63" t="inlineStr">
+      <c r="A32" s="61" t="inlineStr">
         <is>
           <t>C-14</t>
         </is>
       </c>
-      <c r="B32" s="63" t="inlineStr">
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t>oglinda cont activ ↔ cont amortizare:
 205↔2805 · 208↔2808 · 2112↔2811
 212↔2812 · 213x↔2813 · 214↔2814 · 215↔2815</t>
         </is>
       </c>
-      <c r="C32" s="63" t="inlineStr">
+      <c r="C32" s="61" t="inlineStr">
         <is>
           <t>Nota de amortizare din PRIMA lună + balanța analitică</t>
         </is>
       </c>
-      <c r="D32" s="63" t="inlineStr">
+      <c r="D32" s="61" t="inlineStr">
         <is>
           <t>2813 deservește mai multe conturi (2131, 2132, 2133, 2134) —
 e normal ca soldul lui să acopere mai multe analitice de 213.
 2111 Terenuri nu are pereche: nu se amortizează.</t>
         </is>
       </c>
-      <c r="E32" s="63" t="inlineStr">
+      <c r="E32" s="61" t="inlineStr">
         <is>
           <t>Amortizare postată pe alt cont decât perechea
 Softul nu face automat corespondența și nimeni nu a verificat
 Analitic de 213 fără corespondent în 2813</t>
         </is>
       </c>
-      <c r="F32" s="63" t="inlineStr">
-        <is>
-          <t>F-202, F-203, F-214</t>
-        </is>
-      </c>
-      <c r="G32" s="63" t="inlineStr">
+      <c r="F32" s="61" t="inlineStr">
+        <is>
+          <t>F-202, F-203, F-214 | Module_Declarative_Fluxuri.xlsx → MOD_IMOBILIZARI</t>
+        </is>
+      </c>
+      <c r="G32" s="61" t="inlineStr">
         <is>
           <t>Medie — se propagă lunar dacă nu e prinsă în prima lună</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="63" t="inlineStr">
+      <c r="A33" s="61" t="inlineStr">
         <is>
           <t>C-15</t>
         </is>
       </c>
-      <c r="B33" s="63" t="inlineStr">
+      <c r="B33" s="61" t="inlineStr">
         <is>
           <t>analitic 21x din balanța contabilă =
 registrul mijloacelor fixe / modulul de imobilizări
 (LUNAR)</t>
         </is>
       </c>
-      <c r="C33" s="63" t="inlineStr">
+      <c r="C33" s="61" t="inlineStr">
         <is>
           <t>Listing modul imobilizări vs. balanță analitică</t>
         </is>
       </c>
-      <c r="D33" s="63" t="inlineStr">
+      <c r="D33" s="61" t="inlineStr">
         <is>
           <t>Intrare la sfârșit de lună, încă neintrodusă în modul (se reglează în luna următoare, cu notă)
 Mijloc în 223/224, facturat dar nerecepționat (nu e încă în modul)</t>
         </is>
       </c>
-      <c r="E33" s="63" t="inlineStr">
+      <c r="E33" s="61" t="inlineStr">
         <is>
           <t>Mijloc fix neintrodus în modulul de imobilizări → amortizare neînregistrată →
 impozit pe profit plătit în plus
 Ieșire operată în modul dar nu în contabilitate (sau invers)</t>
         </is>
       </c>
-      <c r="F33" s="63" t="inlineStr">
-        <is>
-          <t>F-207, F-214</t>
-        </is>
-      </c>
-      <c r="G33" s="63" t="inlineStr">
+      <c r="F33" s="61" t="inlineStr">
+        <is>
+          <t>F-207, F-214 | Module_Declarative_Fluxuri.xlsx → MOD_IMOBILIZARI | ❓ Î-14</t>
+        </is>
+      </c>
+      <c r="G33" s="61" t="inlineStr">
         <is>
           <t>Înaltă — impozit pe profit supraevaluat</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="63" t="inlineStr">
+      <c r="A34" s="61" t="inlineStr">
         <is>
           <t>C-16</t>
         </is>
       </c>
-      <c r="B34" s="63" t="inlineStr">
+      <c r="B34" s="61" t="inlineStr">
         <is>
           <t>Σ rulaj clasa 7 − Σ rulaj clasa 6 = sold 121
 (înainte de închidere)
 sold 121 = 0 după închidere</t>
         </is>
       </c>
-      <c r="C34" s="63" t="inlineStr">
+      <c r="C34" s="61" t="inlineStr">
         <is>
           <t>Balanță + nota de închidere a exercițiului</t>
         </is>
       </c>
-      <c r="D34" s="63" t="inlineStr">
+      <c r="D34" s="61" t="inlineStr">
         <is>
           <t>Repartizarea pe 129 făcută la 31.12, înainte de închiderea lui 121
 711/712/722 cu sold creditor înainte de închidere = variația stocului / producția capitalizată, normal</t>
         </is>
       </c>
-      <c r="E34" s="63" t="inlineStr">
+      <c r="E34" s="61" t="inlineStr">
         <is>
           <t>121 din anul precedent NEÎNCHIS — cauza #1 când corelația nu ține
 Cont de cheltuială sau venit rămas neînchis după notă
 331 închis greșit pe 121</t>
         </is>
       </c>
-      <c r="F34" s="63" t="inlineStr">
-        <is>
-          <t>F-104, F-314, F-103</t>
-        </is>
-      </c>
-      <c r="G34" s="63" t="inlineStr">
+      <c r="F34" s="61" t="inlineStr">
+        <is>
+          <t>F-104, F-314, F-103 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_EX / MOD_CAPITALURI</t>
+        </is>
+      </c>
+      <c r="G34" s="61" t="inlineStr">
         <is>
           <t>Critică — bilanț, D101 și baza de dividende</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="63" t="inlineStr">
+      <c r="A35" s="61" t="inlineStr">
         <is>
           <t>C-17</t>
         </is>
       </c>
-      <c r="B35" s="63" t="inlineStr">
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>sold 1061 ≤ 20% × capital social subscris ȘI VĂRSAT
 rulaj anual 1061 ≤ 5% × (sold 121 + rulaj 691)</t>
         </is>
       </c>
-      <c r="C35" s="63" t="inlineStr">
+      <c r="C35" s="61" t="inlineStr">
         <is>
           <t>Balanță 1061 vs. 1012 + nota de repartizare</t>
         </is>
       </c>
-      <c r="D35" s="63" t="inlineStr">
+      <c r="D35" s="61" t="inlineStr">
         <is>
           <t>Plafonul de 20% atins → nu se mai constituie rezervă (rulaj 0, sold la plafon)
 Majorare de capital social în cursul anului → plafonul crește</t>
         </is>
       </c>
-      <c r="E35" s="63" t="inlineStr">
+      <c r="E35" s="61" t="inlineStr">
         <is>
           <t>Plafonul calculat pe capital SUBSCRIS, ignorând partea nevărsată din 1011
 Rezerva constituită peste 5% din profitul contabil brut → partea în plus nedeductibilă
 Rezerva constituită pe profit net, nu pe profit brut</t>
         </is>
       </c>
-      <c r="F35" s="63" t="inlineStr">
-        <is>
-          <t>F-101, F-103</t>
-        </is>
-      </c>
-      <c r="G35" s="63" t="inlineStr">
+      <c r="F35" s="61" t="inlineStr">
+        <is>
+          <t>F-101, F-103 | Module_Declarative_Fluxuri.xlsx → MOD_CAPITALURI</t>
+        </is>
+      </c>
+      <c r="G35" s="61" t="inlineStr">
         <is>
           <t>Medie — deductibilitate și conformare L. 31/1990</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="63" t="inlineStr">
+      <c r="A36" s="61" t="inlineStr">
         <is>
           <t>C-18</t>
         </is>
       </c>
-      <c r="B36" s="63" t="inlineStr">
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t>sold 1174 = 0 la 31.12</t>
         </is>
       </c>
-      <c r="C36" s="63" t="inlineStr">
+      <c r="C36" s="61" t="inlineStr">
         <is>
           <t>Balanță 1174 la închidere</t>
         </is>
       </c>
-      <c r="D36" s="63" t="inlineStr">
+      <c r="D36" s="61" t="inlineStr">
         <is>
           <t>Corecție înregistrată în decembrie, transferată în 1171 după hotărârea AGA din anul următor
 (cu notă explicativă la dosarul de închidere)</t>
         </is>
       </c>
-      <c r="E36" s="63" t="inlineStr">
+      <c r="E36" s="61" t="inlineStr">
         <is>
           <t>1174 lăsat cu sold pe termen lung — cont TRANZITORIU, nu de sold
 Corecție făcută pe 1174 fără D101 rectificativ depus
 Corecție trecută prin 628 în loc de 1174 (denaturează rezultatul curent)</t>
         </is>
       </c>
-      <c r="F36" s="63" t="inlineStr">
-        <is>
-          <t>F-105</t>
-        </is>
-      </c>
-      <c r="G36" s="63" t="inlineStr">
+      <c r="F36" s="61" t="inlineStr">
+        <is>
+          <t>F-105 | Module_Declarative_Fluxuri.xlsx → MOD_CAPITALURI | ❓ Î-05</t>
+        </is>
+      </c>
+      <c r="G36" s="61" t="inlineStr">
         <is>
           <t>Înaltă — D101 și trasabilitatea corecției</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="63" t="inlineStr">
+      <c r="A37" s="61" t="inlineStr">
         <is>
           <t>C-19</t>
         </is>
       </c>
-      <c r="B37" s="63" t="inlineStr">
+      <c r="B37" s="61" t="inlineStr">
         <is>
           <t>sold 167 pe contract = sold din scadențar
 (în valuta contractului)</t>
         </is>
       </c>
-      <c r="C37" s="63" t="inlineStr">
+      <c r="C37" s="61" t="inlineStr">
         <is>
           <t>Balanță analitică 167 vs. scadențarul de la firma de leasing</t>
         </is>
       </c>
-      <c r="D37" s="63" t="inlineStr">
+      <c r="D37" s="61" t="inlineStr">
         <is>
           <t>Factură de rată emisă la un curs diferit de cel din scadențar (se explică prin diferența de curs)
 Rate restante sau reeșalonare comunicată de finanțator</t>
         </is>
       </c>
-      <c r="E37" s="63" t="inlineStr">
+      <c r="E37" s="61" t="inlineStr">
         <is>
           <t>167 fără analitic pe contract → nu poți ști la ce rată te raportezi la reevaluare
 Mai multe contracte amestecate pe același analitic
 Avansul (4093) neînchis în 167</t>
         </is>
       </c>
-      <c r="F37" s="63" t="inlineStr">
-        <is>
-          <t>F-108</t>
-        </is>
-      </c>
-      <c r="G37" s="63" t="inlineStr">
+      <c r="F37" s="61" t="inlineStr">
+        <is>
+          <t>F-108 | Module_Declarative_Fluxuri.xlsx → MOD_LEASING_FIN</t>
+        </is>
+      </c>
+      <c r="G37" s="61" t="inlineStr">
         <is>
           <t>Înaltă — reevaluare la curs greșit, valoare de intrare greșită</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="63" t="inlineStr">
+      <c r="A38" s="61" t="inlineStr">
         <is>
           <t>C-20</t>
         </is>
       </c>
-      <c r="B38" s="63" t="inlineStr">
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>capitaluri proprii (activ net) ≥ ½ × capital social subscris</t>
         </is>
       </c>
-      <c r="C38" s="63" t="inlineStr">
+      <c r="C38" s="61" t="inlineStr">
         <is>
           <t>Bilanț — nu balanță de cont</t>
         </is>
       </c>
-      <c r="D38" s="63" t="inlineStr">
+      <c r="D38" s="61" t="inlineStr">
         <is>
           <t>Pierdere din primul an de activitate, în curs de reconstituire în termenul legal
 (până la încheierea exercițiului financiar ULTERIOR celui în care s-a constatat)</t>
         </is>
       </c>
-      <c r="E38" s="63" t="inlineStr">
+      <c r="E38" s="61" t="inlineStr">
         <is>
           <t>Activ net sub ½ și totuși s-au distribuit dividende (inclusiv interimare)
 S-au restituit împrumuturi de la asociați / afiliați
 Corecție 1174 → 1171 care duce rezultatul reportat pe debitor, după distribuire</t>
         </is>
       </c>
-      <c r="F38" s="63" t="inlineStr">
-        <is>
-          <t>F-103, F-105</t>
-        </is>
-      </c>
-      <c r="G38" s="63" t="inlineStr">
+      <c r="F38" s="61" t="inlineStr">
+        <is>
+          <t>F-103, F-105 | Module_Declarative_Fluxuri.xlsx → MOD_CAPITALURI | ❓ Î-06</t>
+        </is>
+      </c>
+      <c r="G38" s="61" t="inlineStr">
         <is>
           <t>Critică — L. 239/2025: amenzi 10.000–300.000 lei, răspundere solidară, risc de dizolvare judiciară</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="63" t="inlineStr">
+      <c r="A39" s="61" t="inlineStr">
         <is>
           <t>C-21</t>
         </is>
       </c>
-      <c r="B39" s="63" t="inlineStr">
+      <c r="B39" s="61" t="inlineStr">
         <is>
           <t>1171 cu analitic PE AN, cu sens Debitor/Creditor explicit</t>
         </is>
       </c>
-      <c r="C39" s="63" t="inlineStr">
+      <c r="C39" s="61" t="inlineStr">
         <is>
           <t>Balanță analitică 1171 vs. rândurile de pierdere din D101</t>
         </is>
       </c>
-      <c r="D39" s="63" t="inlineStr">
+      <c r="D39" s="61" t="inlineStr">
         <is>
           <t>Analitic pe an cu solduri mixte (unii ani profit, alții pierdere) — e chiar scopul</t>
         </is>
       </c>
-      <c r="E39" s="63" t="inlineStr">
+      <c r="E39" s="61" t="inlineStr">
         <is>
           <t>1171 agregat, fără analitic pe an → nu poți urmări recuperarea pierderii
 (70% din profitul impozabil, în 5 ani consecutivi, pentru pierderi din 2024 încolo)
@@ -43269,41 +44271,41 @@
 plafonul de dividende distribuibile e SUPRAEVALUAT</t>
         </is>
       </c>
-      <c r="F39" s="63" t="inlineStr">
-        <is>
-          <t>F-103, F-105</t>
-        </is>
-      </c>
-      <c r="G39" s="63" t="inlineStr">
+      <c r="F39" s="61" t="inlineStr">
+        <is>
+          <t>F-103, F-105 | Module_Declarative_Fluxuri.xlsx → MOD_CAPITALURI | ❓ Î-01, Î-03</t>
+        </is>
+      </c>
+      <c r="G39" s="61" t="inlineStr">
         <is>
           <t>Înaltă — impozit pe profit și plafon de dividende</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="63" t="inlineStr">
+      <c r="A40" s="61" t="inlineStr">
         <is>
           <t>C-22</t>
         </is>
       </c>
-      <c r="B40" s="63" t="inlineStr">
+      <c r="B40" s="61" t="inlineStr">
         <is>
           <t>sold 231/233 = lista obiectivelor în curs
 (pe analitic de obiectiv)</t>
         </is>
       </c>
-      <c r="C40" s="63" t="inlineStr">
+      <c r="C40" s="61" t="inlineStr">
         <is>
           <t>Balanță 231/233 + situațiile de lucrări + PV de punere în funcțiune</t>
         </is>
       </c>
-      <c r="D40" s="63" t="inlineStr">
+      <c r="D40" s="61" t="inlineStr">
         <is>
           <t>Obiectiv real în execuție la 31.12, care continuă în anul următor
 Recepție în ianuarie pentru lucrări din decembrie</t>
         </is>
       </c>
-      <c r="E40" s="63" t="inlineStr">
+      <c r="E40" s="61" t="inlineStr">
         <is>
           <t>Obiectiv pus în funcțiune fără PV → rămâne în 231 și nu se amortizează
 Sold 231 mare, fără listă pe obiectiv (administratorul întreabă ce e acolo)
@@ -43311,12 +44313,12 @@
 Salarii capitalizate prin 711 în loc de 722 (sau deloc)</t>
         </is>
       </c>
-      <c r="F40" s="63" t="inlineStr">
+      <c r="F40" s="61" t="inlineStr">
         <is>
           <t>F-201, F-208</t>
         </is>
       </c>
-      <c r="G40" s="63" t="inlineStr">
+      <c r="G40" s="61" t="inlineStr">
         <is>
           <t>Înaltă — amortizare neînregistrată, bilanț denaturat</t>
         </is>
@@ -43455,7 +44457,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="62" t="inlineStr">
+      <c r="A8" s="63" t="inlineStr">
         <is>
           <t>Ordonat pe simbol de cont. PARȚIAL rămâne doar unde acoperirea chiar este parțială — vezi GOLURI_ACCEPTATE în date/plan.py.</t>
         </is>
@@ -43484,7 +44486,7 @@
       </c>
       <c r="E9" s="67" t="inlineStr">
         <is>
-          <t>F-101 pas 3: nevărsat → vărsat</t>
+          <t>F-101 pas 3: nevărsat → vărsat | modul: MOD_CAPITALURI</t>
         </is>
       </c>
       <c r="F9" s="67" t="inlineStr">
@@ -43516,7 +44518,7 @@
       </c>
       <c r="E10" s="67" t="inlineStr">
         <is>
-          <t>F-103 pași 2–3 (121 = 129)</t>
+          <t>F-103 pași 2–3 (121 = 129) | modul: MOD_CAPITALURI</t>
         </is>
       </c>
       <c r="F10" s="67" t="inlineStr">
@@ -43548,7 +44550,7 @@
       </c>
       <c r="E11" s="29" t="inlineStr">
         <is>
-          <t>F-104</t>
+          <t>F-104 | modul: MOD_INCHIDERE_EX</t>
         </is>
       </c>
       <c r="F11" s="29" t="inlineStr">
@@ -43580,7 +44582,7 @@
       </c>
       <c r="E12" s="67" t="inlineStr">
         <is>
-          <t>F-103 pas 4; analitic pe an (C-21)</t>
+          <t>F-103 pas 4; analitic pe an (C-21) | modul: MOD_CAPITALURI</t>
         </is>
       </c>
       <c r="F12" s="67" t="inlineStr">
@@ -43612,7 +44614,7 @@
       </c>
       <c r="E13" s="67" t="inlineStr">
         <is>
-          <t>F-105 pas 2: ocolește 121</t>
+          <t>F-105 pas 2: ocolește 121 | modul: MOD_CAPITALURI</t>
         </is>
       </c>
       <c r="F13" s="67" t="inlineStr">
@@ -43676,7 +44678,7 @@
       </c>
       <c r="E15" s="29" t="inlineStr">
         <is>
-          <t>F-104; F-314 711 se închide pe 121</t>
+          <t>F-104; F-314 711 se închide pe 121 | modul: MOD_INCHIDERE_EX</t>
         </is>
       </c>
       <c r="F15" s="29" t="inlineStr">
@@ -43708,7 +44710,7 @@
       </c>
       <c r="E16" s="67" t="inlineStr">
         <is>
-          <t>F-106 pas 3: reluarea e independentă de factură</t>
+          <t>F-106 pas 3: reluarea e independentă de factură | modul: MOD_PROVIZION</t>
         </is>
       </c>
       <c r="F16" s="67" t="inlineStr">
@@ -43740,7 +44742,7 @@
       </c>
       <c r="E17" s="67" t="inlineStr">
         <is>
-          <t>F-107 pas 4: reevaluarea lunară</t>
+          <t>F-107 pas 4: reevaluarea lunară | modul: MOD_CREDIT_VALUTA</t>
         </is>
       </c>
       <c r="F17" s="67" t="inlineStr">
@@ -43772,7 +44774,7 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>F-108 pas 9: 167 = scadențar, 1:1 cu contractul</t>
+          <t>F-108 pas 9: 167 = scadențar, 1:1 cu contractul | modul: MOD_LEASING_FIN</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -43868,7 +44870,7 @@
       </c>
       <c r="E21" s="67" t="inlineStr">
         <is>
-          <t>F-203 pas 3: taxare inversă + cod 27 în D394</t>
+          <t>F-203 pas 3: taxare inversă + cod 27 în D394 | modul: MOD_IMOBILIZARI / MOD_IESIRE_MF</t>
         </is>
       </c>
       <c r="F21" s="67" t="inlineStr">
@@ -43900,7 +44902,7 @@
       </c>
       <c r="E22" s="67" t="inlineStr">
         <is>
-          <t>F-205 pas 4: taxa vamală în cost</t>
+          <t>F-205 pas 4: taxa vamală în cost | modul: MOD_IMOBILIZARI / MOD_IESIRE_MF</t>
         </is>
       </c>
       <c r="F22" s="67" t="inlineStr">
@@ -43932,7 +44934,7 @@
       </c>
       <c r="E23" s="67" t="inlineStr">
         <is>
-          <t>F-206 pas 3: defalcare teren/construcție</t>
+          <t>F-206 pas 3: defalcare teren/construcție | modul: MOD_IMOBILIZARI</t>
         </is>
       </c>
       <c r="F23" s="67" t="inlineStr">
@@ -43964,7 +44966,7 @@
       </c>
       <c r="E24" s="67" t="inlineStr">
         <is>
-          <t>F-207 pas 2: stingere la recepție</t>
+          <t>F-207 pas 2: stingere la recepție | modul: MOD_IMOBILIZARI</t>
         </is>
       </c>
       <c r="F24" s="67" t="inlineStr">
@@ -44060,7 +45062,7 @@
       </c>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>F-214 oglinda 21x↔28x; F-211/F-212 descărcare la ieșire</t>
+          <t>F-214 oglinda 21x↔28x; F-211/F-212 descărcare la ieșire | modul: MOD_LEASING_FIN / MOD_IESIRE_MF / MOD_IMOBILIZARI</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -44220,7 +45222,7 @@
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>F-302 stingere; F-304 coexistă cu 408</t>
+          <t>F-302 stingere; F-304 coexistă cu 408 | modul: MOD_APROV_TRANZIT / MOD_INTERMEDIAR</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
@@ -44252,7 +45254,7 @@
       </c>
       <c r="E33" s="29" t="inlineStr">
         <is>
-          <t>F-311/F-312; F-314 graniță 31.12 + inventar</t>
+          <t>F-311/F-312; F-314 graniță 31.12 + inventar | modul: MOD_NEUTRALIZARE / MOD_INCHIDERE_EX</t>
         </is>
       </c>
       <c r="F33" s="29" t="inlineStr">
@@ -44284,7 +45286,7 @@
       </c>
       <c r="E34" s="29" t="inlineStr">
         <is>
-          <t>F-316/F-317 corelații; F-304 intersecție; F-318 retur</t>
+          <t>F-316/F-317 corelații; F-304 intersecție; F-318 retur | modul: MOD_VANZ_AMANUNT / MOD_APROV_TRANZIT / MOD_INTERMEDIAR</t>
         </is>
       </c>
       <c r="F34" s="29" t="inlineStr">
@@ -44316,7 +45318,7 @@
       </c>
       <c r="E35" s="29" t="inlineStr">
         <is>
-          <t>F-316/F-317; F-318 storno proporțional</t>
+          <t>F-316/F-317; F-318 storno proporțional | modul: MOD_VANZ_AMANUNT</t>
         </is>
       </c>
       <c r="F35" s="29" t="inlineStr">
@@ -44348,7 +45350,7 @@
       </c>
       <c r="E36" s="29" t="inlineStr">
         <is>
-          <t>F-304 același furnizor 32x+408</t>
+          <t>F-304 același furnizor 32x+408 | modul: MOD_APROV_TRANZIT / MOD_INTERMEDIAR</t>
         </is>
       </c>
       <c r="F36" s="29" t="inlineStr">
@@ -44380,7 +45382,7 @@
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>F-408; F-304 intersecție cu 32x</t>
+          <t>F-408; F-304 intersecție cu 32x | modul: MOD_INTERMEDIAR / MOD_APROV_TRANZIT</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
@@ -44444,7 +45446,7 @@
       </c>
       <c r="E39" s="67" t="inlineStr">
         <is>
-          <t>F-108 pas 4: stingerea avansului în 167</t>
+          <t>F-108 pas 4: stingerea avansului în 167 | modul: MOD_LEASING_FIN</t>
         </is>
       </c>
       <c r="F39" s="67" t="inlineStr">
@@ -44476,7 +45478,7 @@
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>modul: MOD_VANZ_AMANUNT</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr">
@@ -44508,7 +45510,7 @@
       </c>
       <c r="E41" s="29" t="inlineStr">
         <is>
-          <t>F-408</t>
+          <t>F-408 | modul: MOD_INTERMEDIAR</t>
         </is>
       </c>
       <c r="F41" s="29" t="inlineStr">
@@ -44572,7 +45574,7 @@
       </c>
       <c r="E43" s="29" t="inlineStr">
         <is>
-          <t>F-104</t>
+          <t>F-104 | modul: MOD_INCHIDERE_EX</t>
         </is>
       </c>
       <c r="F43" s="29" t="inlineStr">
@@ -44604,7 +45606,7 @@
       </c>
       <c r="E44" s="29" t="inlineStr">
         <is>
-          <t>F-405</t>
+          <t>F-405 | modul: MOD_INCHIDERE_TVA</t>
         </is>
       </c>
       <c r="F44" s="29" t="inlineStr">
@@ -44636,7 +45638,7 @@
       </c>
       <c r="E45" s="29" t="inlineStr">
         <is>
-          <t>F-405 închidere sold 0; F-407 corecție post-D300</t>
+          <t>F-405 închidere sold 0; F-407 corecție post-D300 | modul: MOD_INCHIDERE_TVA</t>
         </is>
       </c>
       <c r="F45" s="29" t="inlineStr">
@@ -44668,7 +45670,7 @@
       </c>
       <c r="E46" s="29" t="inlineStr">
         <is>
-          <t>F-405; F-406 credit la lipsă; F-318 storno retur</t>
+          <t>F-405; F-406 credit la lipsă; F-318 storno retur | modul: MOD_INCHIDERE_TVA / MOD_VANZ_AMANUNT</t>
         </is>
       </c>
       <c r="F46" s="29" t="inlineStr">
@@ -44700,7 +45702,7 @@
       </c>
       <c r="E47" s="29" t="inlineStr">
         <is>
-          <t>F-316/F-317 corelație; F-401 INC; F-318 retur proporțional</t>
+          <t>F-316/F-317 corelație; F-401 INC; F-318 retur proporțional | modul: MOD_VANZ_AMANUNT / MOD_TVA_INCASARE</t>
         </is>
       </c>
       <c r="F47" s="29" t="inlineStr">
@@ -44860,7 +45862,7 @@
       </c>
       <c r="E52" s="29" t="inlineStr">
         <is>
-          <t>F-411 sold 31.12 = red flag</t>
+          <t>F-411 sold 31.12 = red flag | modul: MOD_INTERMEDIAR</t>
         </is>
       </c>
       <c r="F52" s="29" t="inlineStr">
@@ -44892,7 +45894,7 @@
       </c>
       <c r="E53" s="29" t="inlineStr">
         <is>
-          <t>F-210 eliberare pe amortizare</t>
+          <t>F-210 eliberare pe amortizare | modul: MOD_SUBVENTIE</t>
         </is>
       </c>
       <c r="F53" s="29" t="inlineStr">
@@ -44988,7 +45990,7 @@
       </c>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>F-209 capitalizare; F-317 parțial</t>
+          <t>F-209 capitalizare; F-317 parțial | modul: MOD_NEUTRALIZARE / MOD_VANZ_AMANUNT</t>
         </is>
       </c>
       <c r="F56" s="29" t="inlineStr">
@@ -45052,7 +46054,7 @@
       </c>
       <c r="E58" s="67" t="inlineStr">
         <is>
-          <t>F-211 pas 5: deductibil în limita venitului</t>
+          <t>F-211 pas 5: deductibil în limita venitului | modul: MOD_IESIRE_MF</t>
         </is>
       </c>
       <c r="F58" s="67" t="inlineStr">
@@ -45084,7 +46086,7 @@
       </c>
       <c r="E59" s="67" t="inlineStr">
         <is>
-          <t>F-107 pași 1 și 4: cele două momente</t>
+          <t>F-107 pași 1 și 4: cele două momente | modul: MOD_CREDIT_VALUTA / MOD_LEASING_FIN</t>
         </is>
       </c>
       <c r="F59" s="67" t="inlineStr">
@@ -45116,7 +46118,7 @@
       </c>
       <c r="E60" s="22" t="inlineStr">
         <is>
-          <t>F-108 plafon 1.500 lei/lună; F-106 reluare 7812</t>
+          <t>F-108 plafon 1.500 lei/lună; F-106 reluare 7812 | modul: MOD_LEASING_FIN / MOD_SUBVENTIE / MOD_IMOBILIZARI / MOD_PROVIZION</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
@@ -45148,7 +46150,7 @@
       </c>
       <c r="E61" s="29" t="inlineStr">
         <is>
-          <t>F-318 storno retur</t>
+          <t>F-318 storno retur | modul: MOD_NEUTRALIZARE / MOD_VANZ_AMANUNT</t>
         </is>
       </c>
       <c r="F61" s="29" t="inlineStr">
@@ -45180,7 +46182,7 @@
       </c>
       <c r="E62" s="29" t="inlineStr">
         <is>
-          <t>F-314: sold creditor 711 ÎNAINTE de închidere = normal (variație stoc); 0 după închidere</t>
+          <t>F-314: sold creditor 711 ÎNAINTE de închidere = normal (variație stoc); 0 după închidere | modul: MOD_NEUTRALIZARE / MOD_INCHIDERE_EX</t>
         </is>
       </c>
       <c r="F62" s="29" t="inlineStr">
@@ -45212,7 +46214,7 @@
       </c>
       <c r="E63" s="29" t="inlineStr">
         <is>
-          <t>F-209 231=722 (corectat) | F-208 pas 3 (era acoperit doar prin F-209)</t>
+          <t>F-209 231=722 (corectat) | F-208 pas 3 (era acoperit doar prin F-209) | modul: MOD_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="F63" s="29" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -15,9 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arbore analitice" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fluxuri" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corelații de control" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrice acoperire" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Întrebări deschise" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istoric" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Închideri periodice" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrice acoperire" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Întrebări deschise" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istoric" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan de conturi'!$A$1:$J$314</definedName>
@@ -194,7 +195,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -291,6 +292,12 @@
         <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -318,7 +325,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -466,6 +473,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -832,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1644,164 +1657,176 @@
     <row r="77">
       <c r="A77" s="61" t="inlineStr">
         <is>
+          <t>Închideri periodice</t>
+        </is>
+      </c>
+      <c r="B77" s="61" t="inlineStr">
+        <is>
+          <t>Disciplina de închidere: ce cont, la ce cadență, cu ce stare terminală declarată în flux. Rândurile fără flux sunt goluri cunoscute, marcate ca atare</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="61" t="inlineStr">
+        <is>
           <t>Istoric</t>
         </is>
       </c>
-      <c r="B77" s="61" t="inlineStr">
+      <c r="B78" s="61" t="inlineStr">
         <is>
           <t>Echivalența de numerotare veche → nouă, contopirile, defectele reparate, textul mutat la deduplicare</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="62" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="62" t="inlineStr">
         <is>
           <t>6. HARTA FLUXURILOR — pe clase de conturi</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="63" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="63" t="inlineStr">
         <is>
           <t>Ordinea fluxurilor urmează planul de conturi, nu ordinea în care au fost adăugate. Un flux nou primește următorul număr liber din clasa lui și stă fizic la locul lui. Echivalența cu numerotarea veche e în foaia Istoric.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="61" t="inlineStr">
-        <is>
-          <t>F-1xx — capitaluri, provizioane, împrumuturi: capital social · rezerve din reevaluare · repartizarea rezultatului · închiderea exercițiului · corecții 1174 · provizioane · credite în valută · leasing financiar</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="61" t="inlineStr">
         <is>
-          <t>F-2xx — imobilizări: necorporale · terenuri · construcții · instalații și transport · investiții imobiliare · facturate nesosite · în curs de execuție · regie proprie · subvenții · ieșiri (vânzare, casare) · financiare · control analitic ↔ sintetic</t>
+          <t>F-1xx — capitaluri, provizioane, împrumuturi: capital social · rezerve din reevaluare · repartizarea rezultatului · închiderea exercițiului · corecții 1174 · provizioane · credite în valută · leasing financiar</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="61" t="inlineStr">
         <is>
-          <t>F-3xx — stocuri și producție: aprovizionare (internă, tranzit, intracomunitară) · obiecte de inventar · diferențe de preț · ajustări · producție în curs · deșeuri · mărfuri en-gros și amănunt · import</t>
+          <t>F-2xx — imobilizări: necorporale · terenuri · construcții · instalații și transport · investiții imobiliare · facturate nesosite · în curs de execuție · regie proprie · subvenții · ieșiri (vânzare, casare) · financiare · control analitic ↔ sintetic</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="61" t="inlineStr">
         <is>
-          <t>F-4xx — terți, TVA, decontări: TVA la încasare · taxare inversă · scutiri și export · închiderea lunară de TVA · înregistrări fără document · 408/418 · reduceri · avansuri · 473 · salarii · decontări interne</t>
+          <t>F-3xx — stocuri și producție: aprovizionare (internă, tranzit, intracomunitară) · obiecte de inventar · diferențe de preț · ajustări · producție în curs · deșeuri · mărfuri en-gros și amănunt · import</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="61" t="inlineStr">
         <is>
-          <t>F-5xx — trezorerie: viramente interne · avansuri de trezorerie</t>
+          <t>F-4xx — terți, TVA, decontări: TVA la încasare · taxare inversă · scutiri și export · închiderea lunară de TVA · înregistrări fără document · 408/418 · reduceri · avansuri · 473 · salarii · decontări interne</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="61" t="inlineStr">
         <is>
+          <t>F-5xx — trezorerie: viramente interne · avansuri de trezorerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="61" t="inlineStr">
+        <is>
           <t>F-8xx — conturi în afara bilanțului: angajamente · inventarierea obiectelor de inventar</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>7. FORMATUL UNUI RÂND DE FLUX</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>Flux ID | Pas | Document | Explicație | Cont D | Cont C | Sumă | Rol revelat | Declarativ</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>Ultima coloană (Declarativ) leagă pasul de declarația în care ajunge (D300, D394, D406/SAF-T, D100 etc.) — util în cabinet.</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>8. PORȚI DE CALITATE</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="45" customHeight="1">
-      <c r="A93" s="12" t="inlineStr">
+    <row r="94" ht="45" customHeight="1">
+      <c r="A94" s="12" t="inlineStr">
         <is>
           <t>ΣD = ΣC pe fiecare pas · fiecare flux se închide într-o stare terminală declarată · fiecare cont din antetul fluxului apare într-o notă reală · fiecare analitic are un factor · fiecare cont cu rol în flux are un pas care îi demonstrează rolul · corelațiile se verifică pe cifrele fluxului, nu declarativ · Tier C rămâne marcat „acoperire minimă”.</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>9. CONFIRMARE COTE TVA (verificare Etapa 1, 14.08.2026)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="45" customHeight="1">
-      <c r="A96" s="14" t="inlineStr">
+    <row r="97" ht="45" customHeight="1">
+      <c r="A97" s="14" t="inlineStr">
         <is>
           <t>Cota standard: 21% (în vigoare din 01.08.2025, Legea 141/2025). Cota redusă unică: 11% (alimente, medicamente, cazare, restaurante, cărți etc.). Cotă tranzitorie 9% doar pentru locuințe eligibile până la 30.09.2026 (Legea 161/2026). Export / livrări IC: 0%. Toate fluxurile Tranșa 2 folosesc 21%/11%.</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>10. NOTĂ DE RIGUROZITATE (din original + actualizare)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>1. Taxonomia 'pe rol' este o grilă FUNCȚIONALĂ (pt. control și înțelegere), nu clasificarea oficială. OMFP 1802 clasifică după funcția contabilă (A / P / bifuncțional A/P) — vezi col. 'Fct'.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2. 'Bifuncțional' (A/P) e o PROPRIETATE (poate avea sold pe D și pe C), nu un rol. De aceea 4428 apare o dată, cu două roluri: rectificativ (amănunt) ȘI intermediar (la încasare).</t>
+          <t>1. Taxonomia 'pe rol' este o grilă FUNCȚIONALĂ (pt. control și înțelegere), nu clasificarea oficială. OMFP 1802 clasifică după funcția contabilă (A / P / bifuncțional A/P) — vezi col. 'Fct'.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3. Corelații sfinte: 707-607 = rulaj D 378 ; sold 371 * c/(100+c) = sold 4428 ; 4426=jurnal cumpărări, 4427=jurnal vânzări (fără sold, se închid lunar în 4423/4424).</t>
+          <t>2. 'Bifuncțional' (A/P) e o PROPRIETATE (poate avea sold pe D și pe C), nu un rol. De aceea 4428 apare o dată, cu două roluri: rectificativ (amănunt) ȘI intermediar (la încasare).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>3. Corelații sfinte: 707-607 = rulaj D 378 ; sold 371 * c/(100+c) = sold 4428 ; 4426=jurnal cumpărări, 4427=jurnal vânzări (fără sold, se închid lunar în 4423/4424).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>4. Analiticele se judecă după dacă se declară efectiv (D394, D300, D406/SAF-T). Fluxurile pot fi narative, cu pași de verificare la final.</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="49" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="49" t="inlineStr">
         <is>
           <t>VERIFICARE ONLINE 14.08.2026 — CONTRA-VERIFICARE COMPLETITUDINE &amp; ACTUALITATE</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="75" customHeight="1">
-      <c r="A106" s="50" t="inlineStr">
+    <row r="107" ht="75" customHeight="1">
+      <c r="A107" s="50" t="inlineStr">
         <is>
           <t>Surse verificate: OMF 981/2024 (conturi noi 4417, 6351, 697 — prezente și marcate), OMF 6670/2024 (denumiri extinse 694 și 794 — actualizate în fișier), accountantsgroup.ro Plan 2026, PwC/Accace alerts, mfinante.gov.ro.
 Cote TVA 21%/11% confirmate (Legea 141/2025 + actualizări 2026).
@@ -1811,92 +1836,92 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="48" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="48" t="inlineStr">
         <is>
           <t>Concluzie: informația din fișier este corectă, actualizată la zi (14.08.2026) și completă în raport cu scopul „cabinet + învățare” + SAGA. Corecțiile minore (694/794/6351) au fost aplicate acum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="61" t="inlineStr">
-        <is>
-          <t>Sursă: notițele revizuite din 07.08.2026 (capitaluri) și 12.08.2026 (imobilizări). Adăugate 18 fluxuri (F-101…F-213), 10 corelații (C-13…C-22) și 21 de conturi Tier A din clasele 1 și 2. Total fluxuri: 62.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="61" t="inlineStr">
         <is>
+          <t>Sursă: notițele revizuite din 07.08.2026 (capitaluri) și 12.08.2026 (imobilizări). Adăugate 18 fluxuri (F-101…F-213), 10 corelații (C-13…C-22) și 21 de conturi Tier A din clasele 1 și 2. Total fluxuri: 62.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="61" t="inlineStr">
+        <is>
           <t>Fluxuri didactice noi: F-103 (121 = 129, nu invers), F-105 (1174 ocolește 121), F-107 (cele două momente de curs), F-108 (leasing 50% — trei limitări pe baze diferite), F-201 (721, nu 711), F-203 (cod 27 în D394), F-208 (722, nu 711), F-211 (valoare rămasă vs. venit), F-214 (control analitic ↔ sintetic — singurul flux de procedură, fără note contabile).</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="64" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="64" t="inlineStr">
         <is>
           <t>Corecție aplicată pe planul de conturi: contul 235 avea denumirea contului 233. Conform OMFP 1802/2014: 231 corporale în curs, 233 necorporale în curs, 235 investiții imobiliare în curs. Contul 233 a fost adăugat.</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="61" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="61" t="inlineStr">
         <is>
           <t>Erori din notițele brute NEreintroduse (corectate deja în documentele revizuite): 7815 nu există (corect 6811 = 2805/2808); taxele vamale se capitalizează, nu pe 635; softul intern prin 721; salariile din 231 prin 722; 2114 este 214; CASCO nedeductibil pe 613.NED, nu 615; typo-urile 1067 (=167) și 4424 (=4426) la leasing.</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="63" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="63" t="inlineStr">
         <is>
           <t>Reproductibilitate: workbook-ul se generează cu `make build` din surse/ + date/. Porțile de calitate se verifică cu `make verifica`.</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="65" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="65" t="inlineStr">
         <is>
           <t>LIVRABILE CONEXE — sistemul nu se termină la acest fișier</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="61" t="inlineStr">
-        <is>
-          <t>Module_Declarative_Fluxuri.xlsx — 16 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="61" t="inlineStr">
         <is>
-          <t>intrebari-formator.md / .html — cele 21 de întrebări rămase deschise, grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
+          <t>Module_Declarative_Fluxuri.xlsx — 16 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="61" t="inlineStr">
         <is>
+          <t>intrebari-formator.md / .html — cele 21 de întrebări rămase deschise, grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="61" t="inlineStr">
+        <is>
           <t>notite-training-2/3/4 .md și .docx — cele trei documente revizuite, armonizate: aceeași legendă de marcaje, aceleași anexe, aceeași ordine.</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="65" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="65" t="inlineStr">
         <is>
           <t>VERIFICARE LEGISLATIVĂ — completări ulterioare datei de 14.08.2026</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="61" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="61" t="inlineStr">
         <is>
           <t>Afirmațiile adăugate odată cu trainingurile 2 și 3 nu intră sub verificarea din 14.08.2026 de mai sus și au propria dată: L. 239/2025 (capital social minim și blocajul de activ net), OUG 8/2026 (pragul mijloacelor fixe la 5.000 lei), L. 141/2025 (cotele 21% / 11%). Reconfirmă orice prag sau cotă înainte de aplicare la un caz concret.</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="63" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="63" t="inlineStr">
         <is>
           <t>Reproductibilitate: `make build` regenerează ambele workbook-uri din surse/ + date/; `make verifica` rulează porțile, inclusiv poarta de conservare care demonstrează că nimic din originalul training 4 nu s-a pierdut.</t>
         </is>
@@ -1905,47 +1930,47 @@
   </sheetData>
   <mergeCells count="48">
     <mergeCell ref="A116:G116"/>
+    <mergeCell ref="A97:G97"/>
     <mergeCell ref="A106:G106"/>
     <mergeCell ref="A122:G122"/>
-    <mergeCell ref="A109:G109"/>
+    <mergeCell ref="A91:G91"/>
     <mergeCell ref="A62:G62"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A96:G96"/>
     <mergeCell ref="A81:G81"/>
     <mergeCell ref="A112:G112"/>
     <mergeCell ref="A121:G121"/>
-    <mergeCell ref="A115:G115"/>
     <mergeCell ref="A117:G117"/>
     <mergeCell ref="A93:G93"/>
     <mergeCell ref="A111:G111"/>
     <mergeCell ref="A58:G58"/>
     <mergeCell ref="A102:G102"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A114:G114"/>
     <mergeCell ref="A83:G83"/>
-    <mergeCell ref="A92:G92"/>
     <mergeCell ref="A64:G64"/>
     <mergeCell ref="A82:G82"/>
     <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A98:G98"/>
     <mergeCell ref="A49:G49"/>
     <mergeCell ref="A107:G107"/>
+    <mergeCell ref="A103:G103"/>
     <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A123:G123"/>
     <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A119:G119"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A88:G88"/>
+    <mergeCell ref="A94:G94"/>
     <mergeCell ref="A110:G110"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A90:G90"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A108:G108"/>
     <mergeCell ref="A99:G99"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="A84:G84"/>
+    <mergeCell ref="A89:G89"/>
     <mergeCell ref="A80:G80"/>
     <mergeCell ref="A118:G118"/>
     <mergeCell ref="A56:G56"/>
-    <mergeCell ref="A120:G120"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A105:G105"/>
-    <mergeCell ref="A95:G95"/>
     <mergeCell ref="A101:G101"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A86:G86"/>
@@ -1958,6 +1983,1934 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>MATRICE ACOPERIRE — Cont → Flux(uri) → Pas revelator (actualizată 14.08.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>Gol = lipsă flux sau pas revelator. PARȚIAL = ilustrativ (sume descriptive) sau acoperit în modul extern. Tier C = acoperire minimă intenționată.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="59" t="inlineStr">
+        <is>
+          <t>Simbol</t>
+        </is>
+      </c>
+      <c r="B3" s="59" t="inlineStr">
+        <is>
+          <t>Denumire scurtă</t>
+        </is>
+      </c>
+      <c r="C3" s="59" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="D3" s="59" t="inlineStr">
+        <is>
+          <t>Flux(uri)</t>
+        </is>
+      </c>
+      <c r="E3" s="59" t="inlineStr">
+        <is>
+          <t>Pas revelator / note</t>
+        </is>
+      </c>
+      <c r="F3" s="59" t="inlineStr">
+        <is>
+          <t>Gol?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>LEGENDĂ: NU = acoperit cu flux detaliat + pas revelator (inclusiv intersecție/inversare). PARȚIAL = ilustrativ sau doar în modul extern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>Intersecții reflectate: F-304 (32x↔408), F-318 (retur amănunt), F-314 (331@31.12), F-407 (post-D300), F-317 (vânzare parțială), F-802 (inventariere 8035). Corelații C-01…C-12 și Arbore analitice = foi separate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="66" t="inlineStr">
+        <is>
+          <t>Simbol</t>
+        </is>
+      </c>
+      <c r="B6" s="66" t="inlineStr">
+        <is>
+          <t>Denumire scurtă</t>
+        </is>
+      </c>
+      <c r="C6" s="66" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="D6" s="66" t="inlineStr">
+        <is>
+          <t>Flux(uri)</t>
+        </is>
+      </c>
+      <c r="E6" s="66" t="inlineStr">
+        <is>
+          <t>Pas revelator / note</t>
+        </is>
+      </c>
+      <c r="F6" s="66" t="inlineStr">
+        <is>
+          <t>Gol?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>Marcajele PARȚIAL de la 28x, 681/781 și 167 din etapele anterioare au trecut pe NU prin fluxurile F-108, F-211, F-212 și F-214.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="63" t="inlineStr">
+        <is>
+          <t>Ordonat pe simbol de cont. PARȚIAL rămâne doar unde acoperirea chiar este parțială — vezi GOLURI_ACCEPTATE în date/plan.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="67" t="inlineStr">
+        <is>
+          <t>101 / 1012</t>
+        </is>
+      </c>
+      <c r="B9" s="67" t="inlineStr">
+        <is>
+          <t>Capital social</t>
+        </is>
+      </c>
+      <c r="C9" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D9" s="67" t="inlineStr">
+        <is>
+          <t>F-101, F-103</t>
+        </is>
+      </c>
+      <c r="E9" s="67" t="inlineStr">
+        <is>
+          <t>F-101 pas 3: nevărsat → vărsat | modul: MOD_CAPITALURI</t>
+        </is>
+      </c>
+      <c r="F9" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="67" t="inlineStr">
+        <is>
+          <t>1061 / 129</t>
+        </is>
+      </c>
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>Rezervă legală / repartizare</t>
+        </is>
+      </c>
+      <c r="C10" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D10" s="67" t="inlineStr">
+        <is>
+          <t>F-103</t>
+        </is>
+      </c>
+      <c r="E10" s="67" t="inlineStr">
+        <is>
+          <t>F-103 pași 2–3 (121 = 129) | modul: MOD_CAPITALURI</t>
+        </is>
+      </c>
+      <c r="F10" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>Rezultat reportat</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>F-104</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>F-104 | modul: MOD_INCHIDERE_EX</t>
+        </is>
+      </c>
+      <c r="F11" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="67" t="inlineStr">
+        <is>
+          <t>117 (1171)</t>
+        </is>
+      </c>
+      <c r="B12" s="67" t="inlineStr">
+        <is>
+          <t>Rezultat reportat</t>
+        </is>
+      </c>
+      <c r="C12" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D12" s="67" t="inlineStr">
+        <is>
+          <t>F-103, F-105</t>
+        </is>
+      </c>
+      <c r="E12" s="67" t="inlineStr">
+        <is>
+          <t>F-103 pas 4; analitic pe an (C-21) | modul: MOD_CAPITALURI</t>
+        </is>
+      </c>
+      <c r="F12" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="67" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="B13" s="67" t="inlineStr">
+        <is>
+          <t>Corecții erori exerciții anterioare</t>
+        </is>
+      </c>
+      <c r="C13" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D13" s="67" t="inlineStr">
+        <is>
+          <t>F-105</t>
+        </is>
+      </c>
+      <c r="E13" s="67" t="inlineStr">
+        <is>
+          <t>F-105 pas 2: ocolește 121 | modul: MOD_CAPITALURI</t>
+        </is>
+      </c>
+      <c r="F13" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="67" t="inlineStr">
+        <is>
+          <t>1175 / 105</t>
+        </is>
+      </c>
+      <c r="B14" s="67" t="inlineStr">
+        <is>
+          <t>Surplus din reevaluare</t>
+        </is>
+      </c>
+      <c r="C14" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D14" s="67" t="inlineStr">
+        <is>
+          <t>F-102</t>
+        </is>
+      </c>
+      <c r="E14" s="67" t="inlineStr">
+        <is>
+          <t>F-102 pas 3: realizare pe măsura amortizării</t>
+        </is>
+      </c>
+      <c r="F14" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>121/129</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Rezultat + repartizare</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>F-104, F-314</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>F-104; F-314 711 se închide pe 121 | modul: MOD_INCHIDERE_EX</t>
+        </is>
+      </c>
+      <c r="F15" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>151x</t>
+        </is>
+      </c>
+      <c r="B16" s="67" t="inlineStr">
+        <is>
+          <t>Provizioane</t>
+        </is>
+      </c>
+      <c r="C16" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D16" s="67" t="inlineStr">
+        <is>
+          <t>F-106</t>
+        </is>
+      </c>
+      <c r="E16" s="67" t="inlineStr">
+        <is>
+          <t>F-106 pas 3: reluarea e independentă de factură | modul: MOD_PROVIZION</t>
+        </is>
+      </c>
+      <c r="F16" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="67" t="inlineStr">
+        <is>
+          <t>162x / 1682</t>
+        </is>
+      </c>
+      <c r="B17" s="67" t="inlineStr">
+        <is>
+          <t>Credite bancare în valută</t>
+        </is>
+      </c>
+      <c r="C17" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D17" s="67" t="inlineStr">
+        <is>
+          <t>F-107</t>
+        </is>
+      </c>
+      <c r="E17" s="67" t="inlineStr">
+        <is>
+          <t>F-107 pas 4: reevaluarea lunară | modul: MOD_CREDIT_VALUTA</t>
+        </is>
+      </c>
+      <c r="F17" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Datorii leasing</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>F-108</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>F-108 pas 9: 167 = scadențar, 1:1 cu contractul | modul: MOD_LEASING_FIN</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>205 / 208 / 233</t>
+        </is>
+      </c>
+      <c r="B19" s="67" t="inlineStr">
+        <is>
+          <t>Imobilizări necorporale</t>
+        </is>
+      </c>
+      <c r="C19" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D19" s="67" t="inlineStr">
+        <is>
+          <t>F-201</t>
+        </is>
+      </c>
+      <c r="E19" s="67" t="inlineStr">
+        <is>
+          <t>F-201 pas 5: capitalizare prin 721</t>
+        </is>
+      </c>
+      <c r="F19" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="67" t="inlineStr">
+        <is>
+          <t>211 (2111/2112)</t>
+        </is>
+      </c>
+      <c r="B20" s="67" t="inlineStr">
+        <is>
+          <t>Terenuri și amenajări</t>
+        </is>
+      </c>
+      <c r="C20" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" s="67" t="inlineStr">
+        <is>
+          <t>F-202</t>
+        </is>
+      </c>
+      <c r="E20" s="67" t="inlineStr">
+        <is>
+          <t>F-202 pas 3: se amortizează doar amenajarea</t>
+        </is>
+      </c>
+      <c r="F20" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B21" s="67" t="inlineStr">
+        <is>
+          <t>Construcții</t>
+        </is>
+      </c>
+      <c r="C21" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D21" s="67" t="inlineStr">
+        <is>
+          <t>F-203, F-208, F-211</t>
+        </is>
+      </c>
+      <c r="E21" s="67" t="inlineStr">
+        <is>
+          <t>F-203 pas 3: taxare inversă + cod 27 în D394 | modul: MOD_IMOBILIZARI / MOD_IESIRE_MF</t>
+        </is>
+      </c>
+      <c r="F21" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="67" t="inlineStr">
+        <is>
+          <t>213x</t>
+        </is>
+      </c>
+      <c r="B22" s="67" t="inlineStr">
+        <is>
+          <t>Instalații și mijloace de transport</t>
+        </is>
+      </c>
+      <c r="C22" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D22" s="67" t="inlineStr">
+        <is>
+          <t>F-205, F-207, F-212</t>
+        </is>
+      </c>
+      <c r="E22" s="67" t="inlineStr">
+        <is>
+          <t>F-205 pas 4: taxa vamală în cost | modul: MOD_IMOBILIZARI / MOD_IESIRE_MF</t>
+        </is>
+      </c>
+      <c r="F22" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="67" t="inlineStr">
+        <is>
+          <t>214 / 215</t>
+        </is>
+      </c>
+      <c r="B23" s="67" t="inlineStr">
+        <is>
+          <t>Birotică / Investiții imobiliare</t>
+        </is>
+      </c>
+      <c r="C23" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D23" s="67" t="inlineStr">
+        <is>
+          <t>F-206, F-207</t>
+        </is>
+      </c>
+      <c r="E23" s="67" t="inlineStr">
+        <is>
+          <t>F-206 pas 3: defalcare teren/construcție | modul: MOD_IMOBILIZARI</t>
+        </is>
+      </c>
+      <c r="F23" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="67" t="inlineStr">
+        <is>
+          <t>223 / 224</t>
+        </is>
+      </c>
+      <c r="B24" s="67" t="inlineStr">
+        <is>
+          <t>Imobilizări în curs de aprovizionare</t>
+        </is>
+      </c>
+      <c r="C24" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D24" s="67" t="inlineStr">
+        <is>
+          <t>F-207</t>
+        </is>
+      </c>
+      <c r="E24" s="67" t="inlineStr">
+        <is>
+          <t>F-207 pas 2: stingere la recepție | modul: MOD_IMOBILIZARI</t>
+        </is>
+      </c>
+      <c r="F24" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="67" t="inlineStr">
+        <is>
+          <t>231 / 233</t>
+        </is>
+      </c>
+      <c r="B25" s="67" t="inlineStr">
+        <is>
+          <t>Imobilizări în curs de execuție</t>
+        </is>
+      </c>
+      <c r="C25" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D25" s="67" t="inlineStr">
+        <is>
+          <t>F-208, F-201</t>
+        </is>
+      </c>
+      <c r="E25" s="67" t="inlineStr">
+        <is>
+          <t>F-208 pas 3: capitalizare prin 722</t>
+        </is>
+      </c>
+      <c r="F25" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="67" t="inlineStr">
+        <is>
+          <t>26x</t>
+        </is>
+      </c>
+      <c r="B26" s="67" t="inlineStr">
+        <is>
+          <t>Imobilizări financiare</t>
+        </is>
+      </c>
+      <c r="C26" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D26" s="67" t="inlineStr">
+        <is>
+          <t>F-213</t>
+        </is>
+      </c>
+      <c r="E26" s="67" t="inlineStr">
+        <is>
+          <t>F-213 pas 3: analiticul face garanția identificabilă</t>
+        </is>
+      </c>
+      <c r="F26" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>28x</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Amortizări</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>F-204, F-211, F-211, F-212, F-214</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>F-214 oglinda 21x↔28x; F-211/F-212 descărcare la ieșire | modul: MOD_LEASING_FIN / MOD_IESIRE_MF / MOD_IMOBILIZARI</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>29x/39x/49x</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="inlineStr">
+        <is>
+          <t>Ajustări depreciere</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="inlineStr">
+        <is>
+          <t>F-307</t>
+        </is>
+      </c>
+      <c r="E28" s="29" t="inlineStr">
+        <is>
+          <t>F-307</t>
+        </is>
+      </c>
+      <c r="F28" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>Piese schimb</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="inlineStr">
+        <is>
+          <t>F-308</t>
+        </is>
+      </c>
+      <c r="E29" s="29" t="inlineStr">
+        <is>
+          <t>F-308</t>
+        </is>
+      </c>
+      <c r="F29" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>Obiecte inventar</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="inlineStr">
+        <is>
+          <t>F-305, F-802</t>
+        </is>
+      </c>
+      <c r="E30" s="29" t="inlineStr">
+        <is>
+          <t>F-305 deschidere 8035; F-802 inventariere</t>
+        </is>
+      </c>
+      <c r="F30" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>308/348/388</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>Dif. preț stocuri</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D31" s="29" t="inlineStr">
+        <is>
+          <t>F-306</t>
+        </is>
+      </c>
+      <c r="E31" s="29" t="inlineStr">
+        <is>
+          <t>F-306</t>
+        </is>
+      </c>
+      <c r="F31" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>32x</t>
+        </is>
+      </c>
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>Stocuri în curs aprov.</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D32" s="29" t="inlineStr">
+        <is>
+          <t>F-302, F-304</t>
+        </is>
+      </c>
+      <c r="E32" s="29" t="inlineStr">
+        <is>
+          <t>F-302 stingere; F-304 coexistă cu 408 | modul: MOD_APROV_TRANZIT / MOD_INTERMEDIAR</t>
+        </is>
+      </c>
+      <c r="F32" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>331/332</t>
+        </is>
+      </c>
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>Producție/servicii în curs</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D33" s="29" t="inlineStr">
+        <is>
+          <t>F-311, F-312, F-314</t>
+        </is>
+      </c>
+      <c r="E33" s="29" t="inlineStr">
+        <is>
+          <t>F-311/F-312; F-314 graniță 31.12 + inventar | modul: MOD_NEUTRALIZARE / MOD_INCHIDERE_EX</t>
+        </is>
+      </c>
+      <c r="F33" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="B34" s="29" t="inlineStr">
+        <is>
+          <t>Mărfuri</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D34" s="29" t="inlineStr">
+        <is>
+          <t>F-316, F-302, F-304, F-318, F-317</t>
+        </is>
+      </c>
+      <c r="E34" s="29" t="inlineStr">
+        <is>
+          <t>F-316/F-317 corelații; F-304 intersecție; F-318 retur | modul: MOD_VANZ_AMANUNT / MOD_APROV_TRANZIT / MOD_INTERMEDIAR</t>
+        </is>
+      </c>
+      <c r="F34" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="inlineStr">
+        <is>
+          <t>Dif. preț mărfuri</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D35" s="29" t="inlineStr">
+        <is>
+          <t>F-316, F-318, F-317</t>
+        </is>
+      </c>
+      <c r="E35" s="29" t="inlineStr">
+        <is>
+          <t>F-316/F-317; F-318 storno proporțional | modul: MOD_VANZ_AMANUNT</t>
+        </is>
+      </c>
+      <c r="F35" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B36" s="29" t="inlineStr">
+        <is>
+          <t>Furnizori</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D36" s="29" t="inlineStr">
+        <is>
+          <t>F-301, F-302, F-319, F-304</t>
+        </is>
+      </c>
+      <c r="E36" s="29" t="inlineStr">
+        <is>
+          <t>F-304 același furnizor 32x+408 | modul: MOD_APROV_TRANZIT / MOD_INTERMEDIAR</t>
+        </is>
+      </c>
+      <c r="F36" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>Facturi nesosite</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D37" s="29" t="inlineStr">
+        <is>
+          <t>F-408, F-304</t>
+        </is>
+      </c>
+      <c r="E37" s="29" t="inlineStr">
+        <is>
+          <t>F-408; F-304 intersecție cu 32x | modul: MOD_INTERMEDIAR / MOD_APROV_TRANZIT</t>
+        </is>
+      </c>
+      <c r="F37" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="29" t="inlineStr">
+        <is>
+          <t>409/419</t>
+        </is>
+      </c>
+      <c r="B38" s="29" t="inlineStr">
+        <is>
+          <t>Avansuri furnizori/clienți</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D38" s="29" t="inlineStr">
+        <is>
+          <t>F-410</t>
+        </is>
+      </c>
+      <c r="E38" s="29" t="inlineStr">
+        <is>
+          <t>F-410 clarificat sume</t>
+        </is>
+      </c>
+      <c r="F38" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="67" t="inlineStr">
+        <is>
+          <t>4093</t>
+        </is>
+      </c>
+      <c r="B39" s="67" t="inlineStr">
+        <is>
+          <t>Avansuri pentru imobilizări</t>
+        </is>
+      </c>
+      <c r="C39" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D39" s="67" t="inlineStr">
+        <is>
+          <t>F-108, F-410</t>
+        </is>
+      </c>
+      <c r="E39" s="67" t="inlineStr">
+        <is>
+          <t>F-108 pas 4: stingerea avansului în 167 | modul: MOD_LEASING_FIN</t>
+        </is>
+      </c>
+      <c r="F39" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>Clienți</t>
+        </is>
+      </c>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D40" s="29" t="inlineStr">
+        <is>
+          <t>F-315, F-316, F-318</t>
+        </is>
+      </c>
+      <c r="E40" s="29" t="inlineStr">
+        <is>
+          <t>modul: MOD_VANZ_AMANUNT</t>
+        </is>
+      </c>
+      <c r="F40" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="B41" s="29" t="inlineStr">
+        <is>
+          <t>Facturi de întocmit</t>
+        </is>
+      </c>
+      <c r="C41" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D41" s="29" t="inlineStr">
+        <is>
+          <t>F-408</t>
+        </is>
+      </c>
+      <c r="E41" s="29" t="inlineStr">
+        <is>
+          <t>F-408 | modul: MOD_INTERMEDIAR</t>
+        </is>
+      </c>
+      <c r="F41" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>421/431/444/436</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Salarii + contribuții</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>F-413, F-201, F-208</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>Lanțul complet în MOD_SALARII, cu cifre verificate contra statului real din 31.07.2026; F-201/F-208 acoperă ipostaza de cost capitalizat</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>441/4417</t>
+        </is>
+      </c>
+      <c r="B43" s="29" t="inlineStr">
+        <is>
+          <t>Impozit profit / IMCA</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="inlineStr">
+        <is>
+          <t>F-104</t>
+        </is>
+      </c>
+      <c r="E43" s="29" t="inlineStr">
+        <is>
+          <t>F-104 | modul: MOD_INCHIDERE_EX</t>
+        </is>
+      </c>
+      <c r="F43" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>4423/4424</t>
+        </is>
+      </c>
+      <c r="B44" s="29" t="inlineStr">
+        <is>
+          <t>TVA plată/recuperat</t>
+        </is>
+      </c>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D44" s="29" t="inlineStr">
+        <is>
+          <t>F-405</t>
+        </is>
+      </c>
+      <c r="E44" s="29" t="inlineStr">
+        <is>
+          <t>F-405 | modul: MOD_INCHIDERE_TVA</t>
+        </is>
+      </c>
+      <c r="F44" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+      <c r="B45" s="29" t="inlineStr">
+        <is>
+          <t>TVA deductibilă</t>
+        </is>
+      </c>
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D45" s="29" t="inlineStr">
+        <is>
+          <t>F-405, F-319, F-407</t>
+        </is>
+      </c>
+      <c r="E45" s="29" t="inlineStr">
+        <is>
+          <t>F-405 închidere sold 0; F-407 corecție post-D300 | modul: MOD_INCHIDERE_TVA</t>
+        </is>
+      </c>
+      <c r="F45" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>4427</t>
+        </is>
+      </c>
+      <c r="B46" s="29" t="inlineStr">
+        <is>
+          <t>TVA colectată</t>
+        </is>
+      </c>
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D46" s="29" t="inlineStr">
+        <is>
+          <t>F-405, F-406, F-318</t>
+        </is>
+      </c>
+      <c r="E46" s="29" t="inlineStr">
+        <is>
+          <t>F-405; F-406 credit la lipsă; F-318 storno retur | modul: MOD_INCHIDERE_TVA / MOD_VANZ_AMANUNT</t>
+        </is>
+      </c>
+      <c r="F46" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>4428</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="inlineStr">
+        <is>
+          <t>TVA neexigibilă</t>
+        </is>
+      </c>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D47" s="29" t="inlineStr">
+        <is>
+          <t>F-316, F-401, F-318, F-317</t>
+        </is>
+      </c>
+      <c r="E47" s="29" t="inlineStr">
+        <is>
+          <t>F-316/F-317 corelație; F-401 INC; F-318 retur proporțional | modul: MOD_VANZ_AMANUNT / MOD_TVA_INCASARE</t>
+        </is>
+      </c>
+      <c r="F47" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="B48" s="29" t="inlineStr">
+        <is>
+          <t>Alte impozite (VAMA)</t>
+        </is>
+      </c>
+      <c r="C48" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D48" s="29" t="inlineStr">
+        <is>
+          <t>F-319</t>
+        </is>
+      </c>
+      <c r="E48" s="29" t="inlineStr">
+        <is>
+          <t>F-319 stingere 446.VAMA</t>
+        </is>
+      </c>
+      <c r="F48" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="B49" s="29" t="inlineStr">
+        <is>
+          <t>Fonduri speciale</t>
+        </is>
+      </c>
+      <c r="C49" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D49" s="29" t="inlineStr">
+        <is>
+          <t>F-310</t>
+        </is>
+      </c>
+      <c r="E49" s="29" t="inlineStr">
+        <is>
+          <t>F-310</t>
+        </is>
+      </c>
+      <c r="F49" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="67" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="B50" s="67" t="inlineStr">
+        <is>
+          <t>Decontări cu asociații</t>
+        </is>
+      </c>
+      <c r="C50" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D50" s="67" t="inlineStr">
+        <is>
+          <t>F-101</t>
+        </is>
+      </c>
+      <c r="E50" s="67" t="inlineStr">
+        <is>
+          <t>F-101 stingere la vărsare</t>
+        </is>
+      </c>
+      <c r="F50" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>471/472</t>
+        </is>
+      </c>
+      <c r="B51" s="29" t="inlineStr">
+        <is>
+          <t>Avansuri temporale</t>
+        </is>
+      </c>
+      <c r="C51" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D51" s="29" t="inlineStr">
+        <is>
+          <t>F-412</t>
+        </is>
+      </c>
+      <c r="E51" s="29" t="inlineStr">
+        <is>
+          <t>F-412</t>
+        </is>
+      </c>
+      <c r="F51" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="B52" s="29" t="inlineStr">
+        <is>
+          <t>Operațiuni clarificare</t>
+        </is>
+      </c>
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D52" s="29" t="inlineStr">
+        <is>
+          <t>F-411</t>
+        </is>
+      </c>
+      <c r="E52" s="29" t="inlineStr">
+        <is>
+          <t>F-411 sold 31.12 = red flag | modul: MOD_INTERMEDIAR</t>
+        </is>
+      </c>
+      <c r="F52" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="29" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="B53" s="29" t="inlineStr">
+        <is>
+          <t>Subvenții investiții</t>
+        </is>
+      </c>
+      <c r="C53" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D53" s="29" t="inlineStr">
+        <is>
+          <t>F-210</t>
+        </is>
+      </c>
+      <c r="E53" s="29" t="inlineStr">
+        <is>
+          <t>F-210 eliberare pe amortizare | modul: MOD_SUBVENTIE</t>
+        </is>
+      </c>
+      <c r="F53" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="29" t="inlineStr">
+        <is>
+          <t>481/482</t>
+        </is>
+      </c>
+      <c r="B54" s="29" t="inlineStr">
+        <is>
+          <t>Decontări interne</t>
+        </is>
+      </c>
+      <c r="C54" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D54" s="29" t="inlineStr">
+        <is>
+          <t>F-414</t>
+        </is>
+      </c>
+      <c r="E54" s="29" t="inlineStr">
+        <is>
+          <t>F-414 eliminare la centralizare</t>
+        </is>
+      </c>
+      <c r="F54" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="29" t="inlineStr">
+        <is>
+          <t>511/512/581</t>
+        </is>
+      </c>
+      <c r="B55" s="29" t="inlineStr">
+        <is>
+          <t>Trezorerie + viramente</t>
+        </is>
+      </c>
+      <c r="C55" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D55" s="29" t="inlineStr">
+        <is>
+          <t>F-501</t>
+        </is>
+      </c>
+      <c r="E55" s="29" t="inlineStr">
+        <is>
+          <t>F-501 581</t>
+        </is>
+      </c>
+      <c r="F55" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="29" t="inlineStr">
+        <is>
+          <t>601/602/603/607</t>
+        </is>
+      </c>
+      <c r="B56" s="29" t="inlineStr">
+        <is>
+          <t>Cheltuieli stocuri</t>
+        </is>
+      </c>
+      <c r="C56" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D56" s="29" t="inlineStr">
+        <is>
+          <t>F-305, F-311, F-316, F-209, F-317</t>
+        </is>
+      </c>
+      <c r="E56" s="29" t="inlineStr">
+        <is>
+          <t>F-209 capitalizare; F-317 parțial | modul: MOD_NEUTRALIZARE / MOD_VANZ_AMANUNT</t>
+        </is>
+      </c>
+      <c r="F56" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>641/642/646</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>Cheltuieli personal</t>
+        </is>
+      </c>
+      <c r="C57" s="22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D57" s="22" t="inlineStr">
+        <is>
+          <t>F-413, F-201, F-208</t>
+        </is>
+      </c>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>MOD_SALARII acoperă 641 salarii, 642 tichete și 646 CAM; limitările rămase sunt declarate în Reguli_SALARII, tabelul C</t>
+        </is>
+      </c>
+      <c r="F57" s="22" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="67" t="inlineStr">
+        <is>
+          <t>6583 / 7583</t>
+        </is>
+      </c>
+      <c r="B58" s="67" t="inlineStr">
+        <is>
+          <t>Cedarea activelor</t>
+        </is>
+      </c>
+      <c r="C58" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D58" s="67" t="inlineStr">
+        <is>
+          <t>F-211, F-212</t>
+        </is>
+      </c>
+      <c r="E58" s="67" t="inlineStr">
+        <is>
+          <t>F-211 pas 5: deductibil în limita venitului | modul: MOD_IESIRE_MF</t>
+        </is>
+      </c>
+      <c r="F58" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="67" t="inlineStr">
+        <is>
+          <t>665 / 765</t>
+        </is>
+      </c>
+      <c r="B59" s="67" t="inlineStr">
+        <is>
+          <t>Diferențe de curs</t>
+        </is>
+      </c>
+      <c r="C59" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D59" s="67" t="inlineStr">
+        <is>
+          <t>F-107, F-108</t>
+        </is>
+      </c>
+      <c r="E59" s="67" t="inlineStr">
+        <is>
+          <t>F-107 pași 1 și 4: cele două momente | modul: MOD_CREDIT_VALUTA / MOD_LEASING_FIN</t>
+        </is>
+      </c>
+      <c r="F59" s="67" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>681/781</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>Amortiz./ajustări P&amp;L</t>
+        </is>
+      </c>
+      <c r="C60" s="22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D60" s="22" t="inlineStr">
+        <is>
+          <t>F-204, F-210, F-108, F-201, F-202, F-203, F-106</t>
+        </is>
+      </c>
+      <c r="E60" s="22" t="inlineStr">
+        <is>
+          <t>F-108 plafon 1.500 lei/lună; F-106 reluare 7812 | modul: MOD_LEASING_FIN / MOD_SUBVENTIE / MOD_IMOBILIZARI / MOD_PROVIZION</t>
+        </is>
+      </c>
+      <c r="F60" s="22" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="29" t="inlineStr">
+        <is>
+          <t>707/701/704</t>
+        </is>
+      </c>
+      <c r="B61" s="29" t="inlineStr">
+        <is>
+          <t>Venituri CA</t>
+        </is>
+      </c>
+      <c r="C61" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D61" s="29" t="inlineStr">
+        <is>
+          <t>F-311, F-312, F-316, F-318, F-317</t>
+        </is>
+      </c>
+      <c r="E61" s="29" t="inlineStr">
+        <is>
+          <t>F-318 storno retur | modul: MOD_NEUTRALIZARE / MOD_VANZ_AMANUNT</t>
+        </is>
+      </c>
+      <c r="F61" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="29" t="inlineStr">
+        <is>
+          <t>711/712</t>
+        </is>
+      </c>
+      <c r="B62" s="29" t="inlineStr">
+        <is>
+          <t>Neutralizare producție</t>
+        </is>
+      </c>
+      <c r="C62" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D62" s="29" t="inlineStr">
+        <is>
+          <t>F-311, F-312, F-314</t>
+        </is>
+      </c>
+      <c r="E62" s="29" t="inlineStr">
+        <is>
+          <t>F-314: sold creditor 711 ÎNAINTE de închidere = normal (variație stoc); 0 după închidere | modul: MOD_NEUTRALIZARE / MOD_INCHIDERE_EX</t>
+        </is>
+      </c>
+      <c r="F62" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>721/722 | 721 / 722</t>
+        </is>
+      </c>
+      <c r="B63" s="29" t="inlineStr">
+        <is>
+          <t>Producție imobilizări | Producția de imobilizări</t>
+        </is>
+      </c>
+      <c r="C63" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D63" s="29" t="inlineStr">
+        <is>
+          <t>F-209 | F-201, F-208, F-209</t>
+        </is>
+      </c>
+      <c r="E63" s="29" t="inlineStr">
+        <is>
+          <t>F-209 231=722 (corectat) | F-208 pas 3 (era acoperit doar prin F-209) | modul: MOD_NEUTRALIZARE</t>
+        </is>
+      </c>
+      <c r="F63" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="29" t="inlineStr">
+        <is>
+          <t>8035</t>
+        </is>
+      </c>
+      <c r="B64" s="29" t="inlineStr">
+        <is>
+          <t>Obiecte inventar extrab.</t>
+        </is>
+      </c>
+      <c r="C64" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D64" s="29" t="inlineStr">
+        <is>
+          <t>F-305, F-802</t>
+        </is>
+      </c>
+      <c r="E64" s="29" t="inlineStr">
+        <is>
+          <t>F-305 deschidere; F-802 inventariere scriptic↔faptic</t>
+        </is>
+      </c>
+      <c r="F64" s="29" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2866,7 +4819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -44346,1923 +46299,603 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>MATRICE ACOPERIRE — Cont → Flux(uri) → Pas revelator (actualizată 14.08.2026)</t>
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>CONTURI DE URMĂRIT PERIODIC — disciplina de închidere</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="inlineStr">
-        <is>
-          <t>Gol = lipsă flux sau pas revelator. PARȚIAL = ilustrativ (sume descriptive) sau acoperit în modul extern. Tier C = acoperire minimă intenționată.</t>
+      <c r="A2" s="63" t="inlineStr">
+        <is>
+          <t>Răspuns la întrebarea din notițe: care sunt conturile care trebuie urmărite cel puțin trimestrial, dacă nu lunar.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="59" t="inlineStr">
-        <is>
-          <t>Simbol</t>
-        </is>
-      </c>
-      <c r="B3" s="59" t="inlineStr">
-        <is>
-          <t>Denumire scurtă</t>
-        </is>
-      </c>
-      <c r="C3" s="59" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="D3" s="59" t="inlineStr">
-        <is>
-          <t>Flux(uri)</t>
-        </is>
-      </c>
-      <c r="E3" s="59" t="inlineStr">
-        <is>
-          <t>Pas revelator / note</t>
-        </is>
-      </c>
-      <c r="F3" s="59" t="inlineStr">
-        <is>
-          <t>Gol?</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="33" t="inlineStr">
-        <is>
-          <t>LEGENDĂ: NU = acoperit cu flux detaliat + pas revelator (inclusiv intersecție/inversare). PARȚIAL = ilustrativ sau doar în modul extern.</t>
+      <c r="A3" s="63" t="inlineStr">
+        <is>
+          <t>Coloana „Stare terminală declarată” nu e scrisă aici: e citită din pașii de verificare ai fluxurilor. Dacă se schimbă o monografie, se schimbă și rândul de mai jos. Un rând fără flux e un gol cunoscut — checklistul cere ceva ce sistemul nu demonstrează încă, iar coloana din dreapta spune ce lipsește.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
-        <is>
-          <t>Intersecții reflectate: F-304 (32x↔408), F-318 (retur amănunt), F-314 (331@31.12), F-407 (post-D300), F-317 (vânzare parțială), F-802 (inventariere 8035). Corelații C-01…C-12 și Arbore analitice = foi separate.</t>
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Lunar — obligatoriu</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="66" t="inlineStr">
-        <is>
-          <t>Simbol</t>
-        </is>
-      </c>
-      <c r="B6" s="66" t="inlineStr">
-        <is>
-          <t>Denumire scurtă</t>
-        </is>
-      </c>
-      <c r="C6" s="66" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="D6" s="66" t="inlineStr">
-        <is>
-          <t>Flux(uri)</t>
-        </is>
-      </c>
-      <c r="E6" s="66" t="inlineStr">
-        <is>
-          <t>Pas revelator / note</t>
-        </is>
-      </c>
-      <c r="F6" s="66" t="inlineStr">
-        <is>
-          <t>Gol?</t>
+      <c r="A6" s="74" t="inlineStr">
+        <is>
+          <t>Cont</t>
+        </is>
+      </c>
+      <c r="B6" s="74" t="inlineStr">
+        <is>
+          <t>Cadență</t>
+        </is>
+      </c>
+      <c r="C6" s="74" t="inlineStr">
+        <is>
+          <t>De ce se urmărește</t>
+        </is>
+      </c>
+      <c r="D6" s="74" t="inlineStr">
+        <is>
+          <t>Flux</t>
+        </is>
+      </c>
+      <c r="E6" s="74" t="inlineStr">
+        <is>
+          <t>Stare terminală declarată</t>
+        </is>
+      </c>
+      <c r="F6" s="74" t="inlineStr">
+        <is>
+          <t>Gol cunoscut</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
-        <is>
-          <t>Marcajele PARȚIAL de la 28x, 681/781 și 167 din etapele anterioare au trecut pe NU prin fluxurile F-108, F-211, F-212 și F-214.</t>
+      <c r="A7" s="61" t="inlineStr">
+        <is>
+          <t>4426 / 4427 / 4423 / 4424</t>
+        </is>
+      </c>
+      <c r="B7" s="61" t="inlineStr">
+        <is>
+          <t>Lunar — obligatoriu</t>
+        </is>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>închiderea TVA; orice sold rămas e o eroare</t>
+        </is>
+      </c>
+      <c r="D7" s="61" t="inlineStr">
+        <is>
+          <t>F-303 · F-405</t>
+        </is>
+      </c>
+      <c r="E7" s="61" t="inlineStr">
+        <is>
+          <t>Sold 4426/4427 se închid la final de lună ca de obicei · Sold 4426 = 0; sold 4427 = 0; sold 4423 = 5.250</t>
+        </is>
+      </c>
+      <c r="F7" s="61" t="inlineStr">
+        <is>
+          <t>4424: F-405 declară starea lui 4426/4427, nu și pe a lui 4424 (TVA de recuperat).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="63" t="inlineStr">
-        <is>
-          <t>Ordonat pe simbol de cont. PARȚIAL rămâne doar unde acoperirea chiar este parțială — vezi GOLURI_ACCEPTATE în date/plan.py.</t>
+      <c r="A8" s="75" t="inlineStr">
+        <is>
+          <t>4428</t>
+        </is>
+      </c>
+      <c r="B8" s="75" t="inlineStr">
+        <is>
+          <t>Lunar — obligatoriu</t>
+        </is>
+      </c>
+      <c r="C8" s="75" t="inlineStr">
+        <is>
+          <t>bifuncțional; trebuie să se golească pe operațiunile facturate</t>
+        </is>
+      </c>
+      <c r="D8" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="75" t="inlineStr">
+        <is>
+          <t>4428: Se golește în F-408, F-316 și F-401, dar niciunul nu declară asta ca stare terminală pe 4428 — se vede doar pe conturile din jur.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="67" t="inlineStr">
-        <is>
-          <t>101 / 1012</t>
-        </is>
-      </c>
-      <c r="B9" s="67" t="inlineStr">
-        <is>
-          <t>Capital social</t>
-        </is>
-      </c>
-      <c r="C9" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D9" s="67" t="inlineStr">
-        <is>
-          <t>F-101, F-103</t>
-        </is>
-      </c>
-      <c r="E9" s="67" t="inlineStr">
-        <is>
-          <t>F-101 pas 3: nevărsat → vărsat | modul: MOD_CAPITALURI</t>
-        </is>
-      </c>
-      <c r="F9" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
+      <c r="A9" s="61" t="inlineStr">
+        <is>
+          <t>408 / 418</t>
+        </is>
+      </c>
+      <c r="B9" s="61" t="inlineStr">
+        <is>
+          <t>Lunar — obligatoriu</t>
+        </is>
+      </c>
+      <c r="C9" s="61" t="inlineStr">
+        <is>
+          <t>bifuncționale; risc de dublare a gestiunii</t>
+        </is>
+      </c>
+      <c r="D9" s="61" t="inlineStr">
+        <is>
+          <t>F-408</t>
+        </is>
+      </c>
+      <c r="E9" s="61" t="inlineStr">
+        <is>
+          <t>Sold 408/418 = 0 după document</t>
+        </is>
+      </c>
+      <c r="F9" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="67" t="inlineStr">
-        <is>
-          <t>1061 / 129</t>
-        </is>
-      </c>
-      <c r="B10" s="67" t="inlineStr">
-        <is>
-          <t>Rezervă legală / repartizare</t>
-        </is>
-      </c>
-      <c r="C10" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D10" s="67" t="inlineStr">
-        <is>
-          <t>F-103</t>
-        </is>
-      </c>
-      <c r="E10" s="67" t="inlineStr">
-        <is>
-          <t>F-103 pași 2–3 (121 = 129) | modul: MOD_CAPITALURI</t>
-        </is>
-      </c>
-      <c r="F10" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>Rezultat reportat</t>
-        </is>
-      </c>
-      <c r="C11" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D11" s="29" t="inlineStr">
-        <is>
-          <t>F-104</t>
-        </is>
-      </c>
-      <c r="E11" s="29" t="inlineStr">
-        <is>
-          <t>F-104 | modul: MOD_INCHIDERE_EX</t>
-        </is>
-      </c>
-      <c r="F11" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
+      <c r="A10" s="61" t="inlineStr">
+        <is>
+          <t>471 / 472</t>
+        </is>
+      </c>
+      <c r="B10" s="61" t="inlineStr">
+        <is>
+          <t>Lunar — obligatoriu</t>
+        </is>
+      </c>
+      <c r="C10" s="61" t="inlineStr">
+        <is>
+          <t>reluarea eșalonată trebuie făcută lună de lună</t>
+        </is>
+      </c>
+      <c r="D10" s="61" t="inlineStr">
+        <is>
+          <t>F-412</t>
+        </is>
+      </c>
+      <c r="E10" s="61" t="inlineStr">
+        <is>
+          <t>Sold 471/472 scade sistematic</t>
+        </is>
+      </c>
+      <c r="F10" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="61" t="inlineStr">
+        <is>
+          <t>473 Decontări din operațiuni în curs de clarificare</t>
+        </is>
+      </c>
+      <c r="B11" s="61" t="inlineStr">
+        <is>
+          <t>Lunar — obligatoriu</t>
+        </is>
+      </c>
+      <c r="C11" s="61" t="inlineStr">
+        <is>
+          <t>trebuie să ajungă la sold zero; altfel ascunde erori</t>
+        </is>
+      </c>
+      <c r="D11" s="61" t="inlineStr">
+        <is>
+          <t>F-411</t>
+        </is>
+      </c>
+      <c r="E11" s="61" t="inlineStr">
+        <is>
+          <t>Sold 473 la 31.12 = suspect (audit / control)</t>
+        </is>
+      </c>
+      <c r="F11" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="67" t="inlineStr">
-        <is>
-          <t>117 (1171)</t>
-        </is>
-      </c>
-      <c r="B12" s="67" t="inlineStr">
-        <is>
-          <t>Rezultat reportat</t>
-        </is>
-      </c>
-      <c r="C12" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D12" s="67" t="inlineStr">
-        <is>
-          <t>F-103, F-105</t>
-        </is>
-      </c>
-      <c r="E12" s="67" t="inlineStr">
-        <is>
-          <t>F-103 pas 4; analitic pe an (C-21) | modul: MOD_CAPITALURI</t>
-        </is>
-      </c>
-      <c r="F12" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
+      <c r="A12" s="61" t="inlineStr">
+        <is>
+          <t>581 Viramente interne</t>
+        </is>
+      </c>
+      <c r="B12" s="61" t="inlineStr">
+        <is>
+          <t>Lunar — obligatoriu</t>
+        </is>
+      </c>
+      <c r="C12" s="61" t="inlineStr">
+        <is>
+          <t>trebuie să aibă sold zero; sold ≠ 0 = transfer neînchis</t>
+        </is>
+      </c>
+      <c r="D12" s="61" t="inlineStr">
+        <is>
+          <t>F-501</t>
+        </is>
+      </c>
+      <c r="E12" s="61" t="inlineStr">
+        <is>
+          <t>Sold 581 = 0</t>
+        </is>
+      </c>
+      <c r="F12" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="67" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="B13" s="67" t="inlineStr">
-        <is>
-          <t>Corecții erori exerciții anterioare</t>
-        </is>
-      </c>
-      <c r="C13" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D13" s="67" t="inlineStr">
-        <is>
-          <t>F-105</t>
-        </is>
-      </c>
-      <c r="E13" s="67" t="inlineStr">
-        <is>
-          <t>F-105 pas 2: ocolește 121 | modul: MOD_CAPITALURI</t>
-        </is>
-      </c>
-      <c r="F13" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
+      <c r="A13" s="75" t="inlineStr">
+        <is>
+          <t>5311 / 5121</t>
+        </is>
+      </c>
+      <c r="B13" s="75" t="inlineStr">
+        <is>
+          <t>Lunar — obligatoriu</t>
+        </is>
+      </c>
+      <c r="C13" s="75" t="inlineStr">
+        <is>
+          <t>reconciliere cu extrasul și cu registrul de casă</t>
+        </is>
+      </c>
+      <c r="D13" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="75" t="inlineStr">
+        <is>
+          <t>5311: Reconcilierea cu registrul de casă nu e flux: nu produce articol contabil. 5121: Reconcilierea cu extrasul nu e flux.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="67" t="inlineStr">
-        <is>
-          <t>1175 / 105</t>
-        </is>
-      </c>
-      <c r="B14" s="67" t="inlineStr">
-        <is>
-          <t>Surplus din reevaluare</t>
-        </is>
-      </c>
-      <c r="C14" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D14" s="67" t="inlineStr">
-        <is>
-          <t>F-102</t>
-        </is>
-      </c>
-      <c r="E14" s="67" t="inlineStr">
-        <is>
-          <t>F-102 pas 3: realizare pe măsura amortizării</t>
-        </is>
-      </c>
-      <c r="F14" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="29" t="inlineStr">
-        <is>
-          <t>121/129</t>
-        </is>
-      </c>
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>Rezultat + repartizare</t>
-        </is>
-      </c>
-      <c r="C15" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D15" s="29" t="inlineStr">
-        <is>
-          <t>F-104, F-314</t>
-        </is>
-      </c>
-      <c r="E15" s="29" t="inlineStr">
-        <is>
-          <t>F-104; F-314 711 se închide pe 121 | modul: MOD_INCHIDERE_EX</t>
-        </is>
-      </c>
-      <c r="F15" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
+      <c r="A14" s="61" t="inlineStr">
+        <is>
+          <t>542 Avansuri de trezorerie</t>
+        </is>
+      </c>
+      <c r="B14" s="61" t="inlineStr">
+        <is>
+          <t>Lunar — obligatoriu</t>
+        </is>
+      </c>
+      <c r="C14" s="61" t="inlineStr">
+        <is>
+          <t>deconturi nejustificate</t>
+        </is>
+      </c>
+      <c r="D14" s="61" t="inlineStr">
+        <is>
+          <t>F-502</t>
+        </is>
+      </c>
+      <c r="E14" s="61" t="inlineStr">
+        <is>
+          <t>Sold 542 = 0 după decont</t>
+        </is>
+      </c>
+      <c r="F14" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="67" t="inlineStr">
-        <is>
-          <t>151x</t>
-        </is>
-      </c>
-      <c r="B16" s="67" t="inlineStr">
-        <is>
-          <t>Provizioane</t>
-        </is>
-      </c>
-      <c r="C16" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D16" s="67" t="inlineStr">
-        <is>
-          <t>F-106</t>
-        </is>
-      </c>
-      <c r="E16" s="67" t="inlineStr">
-        <is>
-          <t>F-106 pas 3: reluarea e independentă de factură | modul: MOD_PROVIZION</t>
-        </is>
-      </c>
-      <c r="F16" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="67" t="inlineStr">
-        <is>
-          <t>162x / 1682</t>
-        </is>
-      </c>
-      <c r="B17" s="67" t="inlineStr">
-        <is>
-          <t>Credite bancare în valută</t>
-        </is>
-      </c>
-      <c r="C17" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D17" s="67" t="inlineStr">
+      <c r="A17" s="74" t="inlineStr">
+        <is>
+          <t>Cont</t>
+        </is>
+      </c>
+      <c r="B17" s="74" t="inlineStr">
+        <is>
+          <t>Cadență</t>
+        </is>
+      </c>
+      <c r="C17" s="74" t="inlineStr">
+        <is>
+          <t>De ce se urmărește</t>
+        </is>
+      </c>
+      <c r="D17" s="74" t="inlineStr">
+        <is>
+          <t>Flux</t>
+        </is>
+      </c>
+      <c r="E17" s="74" t="inlineStr">
+        <is>
+          <t>Stare terminală declarată</t>
+        </is>
+      </c>
+      <c r="F17" s="74" t="inlineStr">
+        <is>
+          <t>Gol cunoscut</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="75" t="inlineStr">
+        <is>
+          <t>4091 – 4094</t>
+        </is>
+      </c>
+      <c r="B18" s="75" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C18" s="75" t="inlineStr">
+        <is>
+          <t>avansuri care nu s-au stornat la factura finală</t>
+        </is>
+      </c>
+      <c r="D18" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="75" t="inlineStr">
+        <is>
+          <t>4091: F-410 declară starea lui 409 la nivel sintetic, nu pe analiticele de destinație 4091–4094. 4094: Idem 4093.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="61" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="B19" s="61" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C19" s="61" t="inlineStr">
+        <is>
+          <t>avansuri de la clienți rămase deschise</t>
+        </is>
+      </c>
+      <c r="D19" s="61" t="inlineStr">
+        <is>
+          <t>F-410</t>
+        </is>
+      </c>
+      <c r="E19" s="61" t="inlineStr">
+        <is>
+          <t>Sold 419=0, sold 409=0 după livrare/recepție</t>
+        </is>
+      </c>
+      <c r="F19" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="75" t="inlineStr">
+        <is>
+          <t>401 / 411</t>
+        </is>
+      </c>
+      <c r="B20" s="75" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C20" s="75" t="inlineStr">
+        <is>
+          <t>balanță analitică; solduri cu semn contrar = eroare</t>
+        </is>
+      </c>
+      <c r="D20" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="75" t="inlineStr">
+        <is>
+          <t>401: Nu există flux care să declare „401 fără sold debitor”. Regula e o corelație de sold contrar naturii, nu o stare terminală de flux. 411: Idem 401 — vezi C-23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="75" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="B21" s="75" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C21" s="75" t="inlineStr">
+        <is>
+          <t>sume datorate asociaților, cu restricții legale</t>
+        </is>
+      </c>
+      <c r="D21" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="75" t="inlineStr">
+        <is>
+          <t>455: Nu există flux pe 455. Restricțiile de numerar sunt rămase deschise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="75" t="inlineStr">
+        <is>
+          <t>461 / 462</t>
+        </is>
+      </c>
+      <c r="B22" s="75" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C22" s="75" t="inlineStr">
+        <is>
+          <t>debitori/creditori diverși, se împotmolesc ușor</t>
+        </is>
+      </c>
+      <c r="D22" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="75" t="inlineStr">
+        <is>
+          <t>461: Nu există flux pe debitori/creditori diverși. 462: Idem 461.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="61" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="B23" s="61" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C23" s="61" t="inlineStr">
+        <is>
+          <t>imobilizări în curs care trebuiau puse în funcțiune</t>
+        </is>
+      </c>
+      <c r="D23" s="61" t="inlineStr">
+        <is>
+          <t>F-208</t>
+        </is>
+      </c>
+      <c r="E23" s="61" t="inlineStr">
+        <is>
+          <t>Sold 231 = 0 după PV · Sold 231 = 0 după recepție</t>
+        </is>
+      </c>
+      <c r="F23" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="61" t="inlineStr">
+        <is>
+          <t>1621 / 5187</t>
+        </is>
+      </c>
+      <c r="B24" s="61" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C24" s="61" t="inlineStr">
+        <is>
+          <t>credite și dobânzi de calculat</t>
+        </is>
+      </c>
+      <c r="D24" s="61" t="inlineStr">
         <is>
           <t>F-107</t>
         </is>
       </c>
-      <c r="E17" s="67" t="inlineStr">
-        <is>
-          <t>F-107 pas 4: reevaluarea lunară | modul: MOD_CREDIT_VALUTA</t>
-        </is>
-      </c>
-      <c r="F17" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>Datorii leasing</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>F-108</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>F-108 pas 9: 167 = scadențar, 1:1 cu contractul | modul: MOD_LEASING_FIN</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="67" t="inlineStr">
-        <is>
-          <t>205 / 208 / 233</t>
-        </is>
-      </c>
-      <c r="B19" s="67" t="inlineStr">
-        <is>
-          <t>Imobilizări necorporale</t>
-        </is>
-      </c>
-      <c r="C19" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D19" s="67" t="inlineStr">
-        <is>
-          <t>F-201</t>
-        </is>
-      </c>
-      <c r="E19" s="67" t="inlineStr">
-        <is>
-          <t>F-201 pas 5: capitalizare prin 721</t>
-        </is>
-      </c>
-      <c r="F19" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="67" t="inlineStr">
-        <is>
-          <t>211 (2111/2112)</t>
-        </is>
-      </c>
-      <c r="B20" s="67" t="inlineStr">
-        <is>
-          <t>Terenuri și amenajări</t>
-        </is>
-      </c>
-      <c r="C20" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D20" s="67" t="inlineStr">
-        <is>
-          <t>F-202</t>
-        </is>
-      </c>
-      <c r="E20" s="67" t="inlineStr">
-        <is>
-          <t>F-202 pas 3: se amortizează doar amenajarea</t>
-        </is>
-      </c>
-      <c r="F20" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="67" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="B21" s="67" t="inlineStr">
-        <is>
-          <t>Construcții</t>
-        </is>
-      </c>
-      <c r="C21" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D21" s="67" t="inlineStr">
-        <is>
-          <t>F-203, F-208, F-211</t>
-        </is>
-      </c>
-      <c r="E21" s="67" t="inlineStr">
-        <is>
-          <t>F-203 pas 3: taxare inversă + cod 27 în D394 | modul: MOD_IMOBILIZARI / MOD_IESIRE_MF</t>
-        </is>
-      </c>
-      <c r="F21" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="67" t="inlineStr">
-        <is>
-          <t>213x</t>
-        </is>
-      </c>
-      <c r="B22" s="67" t="inlineStr">
-        <is>
-          <t>Instalații și mijloace de transport</t>
-        </is>
-      </c>
-      <c r="C22" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D22" s="67" t="inlineStr">
-        <is>
-          <t>F-205, F-207, F-212</t>
-        </is>
-      </c>
-      <c r="E22" s="67" t="inlineStr">
-        <is>
-          <t>F-205 pas 4: taxa vamală în cost | modul: MOD_IMOBILIZARI / MOD_IESIRE_MF</t>
-        </is>
-      </c>
-      <c r="F22" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="67" t="inlineStr">
-        <is>
-          <t>214 / 215</t>
-        </is>
-      </c>
-      <c r="B23" s="67" t="inlineStr">
-        <is>
-          <t>Birotică / Investiții imobiliare</t>
-        </is>
-      </c>
-      <c r="C23" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D23" s="67" t="inlineStr">
-        <is>
-          <t>F-206, F-207</t>
-        </is>
-      </c>
-      <c r="E23" s="67" t="inlineStr">
-        <is>
-          <t>F-206 pas 3: defalcare teren/construcție | modul: MOD_IMOBILIZARI</t>
-        </is>
-      </c>
-      <c r="F23" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="67" t="inlineStr">
-        <is>
-          <t>223 / 224</t>
-        </is>
-      </c>
-      <c r="B24" s="67" t="inlineStr">
-        <is>
-          <t>Imobilizări în curs de aprovizionare</t>
-        </is>
-      </c>
-      <c r="C24" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D24" s="67" t="inlineStr">
-        <is>
-          <t>F-207</t>
-        </is>
-      </c>
-      <c r="E24" s="67" t="inlineStr">
-        <is>
-          <t>F-207 pas 2: stingere la recepție | modul: MOD_IMOBILIZARI</t>
-        </is>
-      </c>
-      <c r="F24" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="67" t="inlineStr">
-        <is>
-          <t>231 / 233</t>
-        </is>
-      </c>
-      <c r="B25" s="67" t="inlineStr">
-        <is>
-          <t>Imobilizări în curs de execuție</t>
-        </is>
-      </c>
-      <c r="C25" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D25" s="67" t="inlineStr">
-        <is>
-          <t>F-208, F-201</t>
-        </is>
-      </c>
-      <c r="E25" s="67" t="inlineStr">
-        <is>
-          <t>F-208 pas 3: capitalizare prin 722</t>
-        </is>
-      </c>
-      <c r="F25" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="67" t="inlineStr">
-        <is>
-          <t>26x</t>
-        </is>
-      </c>
-      <c r="B26" s="67" t="inlineStr">
-        <is>
-          <t>Imobilizări financiare</t>
-        </is>
-      </c>
-      <c r="C26" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D26" s="67" t="inlineStr">
-        <is>
-          <t>F-213</t>
-        </is>
-      </c>
-      <c r="E26" s="67" t="inlineStr">
-        <is>
-          <t>F-213 pas 3: analiticul face garanția identificabilă</t>
-        </is>
-      </c>
-      <c r="F26" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>28x</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>Amortizări</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>F-204, F-211, F-211, F-212, F-214</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
-        <is>
-          <t>F-214 oglinda 21x↔28x; F-211/F-212 descărcare la ieșire | modul: MOD_LEASING_FIN / MOD_IESIRE_MF / MOD_IMOBILIZARI</t>
-        </is>
-      </c>
-      <c r="F27" s="22" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="29" t="inlineStr">
-        <is>
-          <t>29x/39x/49x</t>
-        </is>
-      </c>
-      <c r="B28" s="29" t="inlineStr">
-        <is>
-          <t>Ajustări depreciere</t>
-        </is>
-      </c>
-      <c r="C28" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D28" s="29" t="inlineStr">
-        <is>
-          <t>F-307</t>
-        </is>
-      </c>
-      <c r="E28" s="29" t="inlineStr">
-        <is>
-          <t>F-307</t>
-        </is>
-      </c>
-      <c r="F28" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="29" t="inlineStr">
-        <is>
-          <t>3024</t>
-        </is>
-      </c>
-      <c r="B29" s="29" t="inlineStr">
-        <is>
-          <t>Piese schimb</t>
-        </is>
-      </c>
-      <c r="C29" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D29" s="29" t="inlineStr">
-        <is>
-          <t>F-308</t>
-        </is>
-      </c>
-      <c r="E29" s="29" t="inlineStr">
-        <is>
-          <t>F-308</t>
-        </is>
-      </c>
-      <c r="F29" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="29" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="B30" s="29" t="inlineStr">
-        <is>
-          <t>Obiecte inventar</t>
-        </is>
-      </c>
-      <c r="C30" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D30" s="29" t="inlineStr">
-        <is>
-          <t>F-305, F-802</t>
-        </is>
-      </c>
-      <c r="E30" s="29" t="inlineStr">
-        <is>
-          <t>F-305 deschidere 8035; F-802 inventariere</t>
-        </is>
-      </c>
-      <c r="F30" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="29" t="inlineStr">
-        <is>
-          <t>308/348/388</t>
-        </is>
-      </c>
-      <c r="B31" s="29" t="inlineStr">
-        <is>
-          <t>Dif. preț stocuri</t>
-        </is>
-      </c>
-      <c r="C31" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D31" s="29" t="inlineStr">
-        <is>
-          <t>F-306</t>
-        </is>
-      </c>
-      <c r="E31" s="29" t="inlineStr">
-        <is>
-          <t>F-306</t>
-        </is>
-      </c>
-      <c r="F31" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="29" t="inlineStr">
-        <is>
-          <t>32x</t>
-        </is>
-      </c>
-      <c r="B32" s="29" t="inlineStr">
-        <is>
-          <t>Stocuri în curs aprov.</t>
-        </is>
-      </c>
-      <c r="C32" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D32" s="29" t="inlineStr">
-        <is>
-          <t>F-302, F-304</t>
-        </is>
-      </c>
-      <c r="E32" s="29" t="inlineStr">
-        <is>
-          <t>F-302 stingere; F-304 coexistă cu 408 | modul: MOD_APROV_TRANZIT / MOD_INTERMEDIAR</t>
-        </is>
-      </c>
-      <c r="F32" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="29" t="inlineStr">
-        <is>
-          <t>331/332</t>
-        </is>
-      </c>
-      <c r="B33" s="29" t="inlineStr">
-        <is>
-          <t>Producție/servicii în curs</t>
-        </is>
-      </c>
-      <c r="C33" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D33" s="29" t="inlineStr">
-        <is>
-          <t>F-311, F-312, F-314</t>
-        </is>
-      </c>
-      <c r="E33" s="29" t="inlineStr">
-        <is>
-          <t>F-311/F-312; F-314 graniță 31.12 + inventar | modul: MOD_NEUTRALIZARE / MOD_INCHIDERE_EX</t>
-        </is>
-      </c>
-      <c r="F33" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="29" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="B34" s="29" t="inlineStr">
-        <is>
-          <t>Mărfuri</t>
-        </is>
-      </c>
-      <c r="C34" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D34" s="29" t="inlineStr">
-        <is>
-          <t>F-316, F-302, F-304, F-318, F-317</t>
-        </is>
-      </c>
-      <c r="E34" s="29" t="inlineStr">
-        <is>
-          <t>F-316/F-317 corelații; F-304 intersecție; F-318 retur | modul: MOD_VANZ_AMANUNT / MOD_APROV_TRANZIT / MOD_INTERMEDIAR</t>
-        </is>
-      </c>
-      <c r="F34" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="29" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="B35" s="29" t="inlineStr">
-        <is>
-          <t>Dif. preț mărfuri</t>
-        </is>
-      </c>
-      <c r="C35" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D35" s="29" t="inlineStr">
-        <is>
-          <t>F-316, F-318, F-317</t>
-        </is>
-      </c>
-      <c r="E35" s="29" t="inlineStr">
-        <is>
-          <t>F-316/F-317; F-318 storno proporțional | modul: MOD_VANZ_AMANUNT</t>
-        </is>
-      </c>
-      <c r="F35" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="29" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="B36" s="29" t="inlineStr">
-        <is>
-          <t>Furnizori</t>
-        </is>
-      </c>
-      <c r="C36" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D36" s="29" t="inlineStr">
-        <is>
-          <t>F-301, F-302, F-319, F-304</t>
-        </is>
-      </c>
-      <c r="E36" s="29" t="inlineStr">
-        <is>
-          <t>F-304 același furnizor 32x+408 | modul: MOD_APROV_TRANZIT / MOD_INTERMEDIAR</t>
-        </is>
-      </c>
-      <c r="F36" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="29" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="B37" s="29" t="inlineStr">
-        <is>
-          <t>Facturi nesosite</t>
-        </is>
-      </c>
-      <c r="C37" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D37" s="29" t="inlineStr">
-        <is>
-          <t>F-408, F-304</t>
-        </is>
-      </c>
-      <c r="E37" s="29" t="inlineStr">
-        <is>
-          <t>F-408; F-304 intersecție cu 32x | modul: MOD_INTERMEDIAR / MOD_APROV_TRANZIT</t>
-        </is>
-      </c>
-      <c r="F37" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="29" t="inlineStr">
-        <is>
-          <t>409/419</t>
-        </is>
-      </c>
-      <c r="B38" s="29" t="inlineStr">
-        <is>
-          <t>Avansuri furnizori/clienți</t>
-        </is>
-      </c>
-      <c r="C38" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D38" s="29" t="inlineStr">
-        <is>
-          <t>F-410</t>
-        </is>
-      </c>
-      <c r="E38" s="29" t="inlineStr">
-        <is>
-          <t>F-410 clarificat sume</t>
-        </is>
-      </c>
-      <c r="F38" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="67" t="inlineStr">
-        <is>
-          <t>4093</t>
-        </is>
-      </c>
-      <c r="B39" s="67" t="inlineStr">
-        <is>
-          <t>Avansuri pentru imobilizări</t>
-        </is>
-      </c>
-      <c r="C39" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D39" s="67" t="inlineStr">
-        <is>
-          <t>F-108, F-410</t>
-        </is>
-      </c>
-      <c r="E39" s="67" t="inlineStr">
-        <is>
-          <t>F-108 pas 4: stingerea avansului în 167 | modul: MOD_LEASING_FIN</t>
-        </is>
-      </c>
-      <c r="F39" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="29" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="B40" s="29" t="inlineStr">
-        <is>
-          <t>Clienți</t>
-        </is>
-      </c>
-      <c r="C40" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D40" s="29" t="inlineStr">
-        <is>
-          <t>F-315, F-316, F-318</t>
-        </is>
-      </c>
-      <c r="E40" s="29" t="inlineStr">
-        <is>
-          <t>modul: MOD_VANZ_AMANUNT</t>
-        </is>
-      </c>
-      <c r="F40" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="29" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="B41" s="29" t="inlineStr">
-        <is>
-          <t>Facturi de întocmit</t>
-        </is>
-      </c>
-      <c r="C41" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D41" s="29" t="inlineStr">
-        <is>
-          <t>F-408</t>
-        </is>
-      </c>
-      <c r="E41" s="29" t="inlineStr">
-        <is>
-          <t>F-408 | modul: MOD_INTERMEDIAR</t>
-        </is>
-      </c>
-      <c r="F41" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="22" t="inlineStr">
-        <is>
-          <t>421/431/444/436</t>
-        </is>
-      </c>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>Salarii + contribuții</t>
-        </is>
-      </c>
-      <c r="C42" s="22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D42" s="22" t="inlineStr">
-        <is>
-          <t>F-413, F-201, F-208</t>
-        </is>
-      </c>
-      <c r="E42" s="22" t="inlineStr">
-        <is>
-          <t>Lanțul complet în MOD_SALARII, cu cifre verificate contra statului real din 31.07.2026; F-201/F-208 acoperă ipostaza de cost capitalizat</t>
-        </is>
-      </c>
-      <c r="F42" s="22" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="29" t="inlineStr">
-        <is>
-          <t>441/4417</t>
-        </is>
-      </c>
-      <c r="B43" s="29" t="inlineStr">
-        <is>
-          <t>Impozit profit / IMCA</t>
-        </is>
-      </c>
-      <c r="C43" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D43" s="29" t="inlineStr">
-        <is>
-          <t>F-104</t>
-        </is>
-      </c>
-      <c r="E43" s="29" t="inlineStr">
-        <is>
-          <t>F-104 | modul: MOD_INCHIDERE_EX</t>
-        </is>
-      </c>
-      <c r="F43" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="29" t="inlineStr">
-        <is>
-          <t>4423/4424</t>
-        </is>
-      </c>
-      <c r="B44" s="29" t="inlineStr">
-        <is>
-          <t>TVA plată/recuperat</t>
-        </is>
-      </c>
-      <c r="C44" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D44" s="29" t="inlineStr">
-        <is>
-          <t>F-405</t>
-        </is>
-      </c>
-      <c r="E44" s="29" t="inlineStr">
-        <is>
-          <t>F-405 | modul: MOD_INCHIDERE_TVA</t>
-        </is>
-      </c>
-      <c r="F44" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="29" t="inlineStr">
-        <is>
-          <t>4426</t>
-        </is>
-      </c>
-      <c r="B45" s="29" t="inlineStr">
-        <is>
-          <t>TVA deductibilă</t>
-        </is>
-      </c>
-      <c r="C45" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D45" s="29" t="inlineStr">
-        <is>
-          <t>F-405, F-319, F-407</t>
-        </is>
-      </c>
-      <c r="E45" s="29" t="inlineStr">
-        <is>
-          <t>F-405 închidere sold 0; F-407 corecție post-D300 | modul: MOD_INCHIDERE_TVA</t>
-        </is>
-      </c>
-      <c r="F45" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="29" t="inlineStr">
-        <is>
-          <t>4427</t>
-        </is>
-      </c>
-      <c r="B46" s="29" t="inlineStr">
-        <is>
-          <t>TVA colectată</t>
-        </is>
-      </c>
-      <c r="C46" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D46" s="29" t="inlineStr">
-        <is>
-          <t>F-405, F-406, F-318</t>
-        </is>
-      </c>
-      <c r="E46" s="29" t="inlineStr">
-        <is>
-          <t>F-405; F-406 credit la lipsă; F-318 storno retur | modul: MOD_INCHIDERE_TVA / MOD_VANZ_AMANUNT</t>
-        </is>
-      </c>
-      <c r="F46" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="29" t="inlineStr">
-        <is>
-          <t>4428</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="inlineStr">
-        <is>
-          <t>TVA neexigibilă</t>
-        </is>
-      </c>
-      <c r="C47" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D47" s="29" t="inlineStr">
-        <is>
-          <t>F-316, F-401, F-318, F-317</t>
-        </is>
-      </c>
-      <c r="E47" s="29" t="inlineStr">
-        <is>
-          <t>F-316/F-317 corelație; F-401 INC; F-318 retur proporțional | modul: MOD_VANZ_AMANUNT / MOD_TVA_INCASARE</t>
-        </is>
-      </c>
-      <c r="F47" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="29" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="B48" s="29" t="inlineStr">
-        <is>
-          <t>Alte impozite (VAMA)</t>
-        </is>
-      </c>
-      <c r="C48" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D48" s="29" t="inlineStr">
-        <is>
-          <t>F-319</t>
-        </is>
-      </c>
-      <c r="E48" s="29" t="inlineStr">
-        <is>
-          <t>F-319 stingere 446.VAMA</t>
-        </is>
-      </c>
-      <c r="F48" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="29" t="inlineStr">
-        <is>
-          <t>447</t>
-        </is>
-      </c>
-      <c r="B49" s="29" t="inlineStr">
-        <is>
-          <t>Fonduri speciale</t>
-        </is>
-      </c>
-      <c r="C49" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D49" s="29" t="inlineStr">
-        <is>
-          <t>F-310</t>
-        </is>
-      </c>
-      <c r="E49" s="29" t="inlineStr">
-        <is>
-          <t>F-310</t>
-        </is>
-      </c>
-      <c r="F49" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="67" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="B50" s="67" t="inlineStr">
-        <is>
-          <t>Decontări cu asociații</t>
-        </is>
-      </c>
-      <c r="C50" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D50" s="67" t="inlineStr">
-        <is>
-          <t>F-101</t>
-        </is>
-      </c>
-      <c r="E50" s="67" t="inlineStr">
-        <is>
-          <t>F-101 stingere la vărsare</t>
-        </is>
-      </c>
-      <c r="F50" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="29" t="inlineStr">
-        <is>
-          <t>471/472</t>
-        </is>
-      </c>
-      <c r="B51" s="29" t="inlineStr">
-        <is>
-          <t>Avansuri temporale</t>
-        </is>
-      </c>
-      <c r="C51" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D51" s="29" t="inlineStr">
-        <is>
-          <t>F-412</t>
-        </is>
-      </c>
-      <c r="E51" s="29" t="inlineStr">
-        <is>
-          <t>F-412</t>
-        </is>
-      </c>
-      <c r="F51" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="29" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="B52" s="29" t="inlineStr">
-        <is>
-          <t>Operațiuni clarificare</t>
-        </is>
-      </c>
-      <c r="C52" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D52" s="29" t="inlineStr">
-        <is>
-          <t>F-411</t>
-        </is>
-      </c>
-      <c r="E52" s="29" t="inlineStr">
-        <is>
-          <t>F-411 sold 31.12 = red flag | modul: MOD_INTERMEDIAR</t>
-        </is>
-      </c>
-      <c r="F52" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="29" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="B53" s="29" t="inlineStr">
-        <is>
-          <t>Subvenții investiții</t>
-        </is>
-      </c>
-      <c r="C53" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D53" s="29" t="inlineStr">
-        <is>
-          <t>F-210</t>
-        </is>
-      </c>
-      <c r="E53" s="29" t="inlineStr">
-        <is>
-          <t>F-210 eliberare pe amortizare | modul: MOD_SUBVENTIE</t>
-        </is>
-      </c>
-      <c r="F53" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="29" t="inlineStr">
-        <is>
-          <t>481/482</t>
-        </is>
-      </c>
-      <c r="B54" s="29" t="inlineStr">
-        <is>
-          <t>Decontări interne</t>
-        </is>
-      </c>
-      <c r="C54" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D54" s="29" t="inlineStr">
-        <is>
-          <t>F-414</t>
-        </is>
-      </c>
-      <c r="E54" s="29" t="inlineStr">
-        <is>
-          <t>F-414 eliminare la centralizare</t>
-        </is>
-      </c>
-      <c r="F54" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="29" t="inlineStr">
-        <is>
-          <t>511/512/581</t>
-        </is>
-      </c>
-      <c r="B55" s="29" t="inlineStr">
-        <is>
-          <t>Trezorerie + viramente</t>
-        </is>
-      </c>
-      <c r="C55" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D55" s="29" t="inlineStr">
-        <is>
-          <t>F-501</t>
-        </is>
-      </c>
-      <c r="E55" s="29" t="inlineStr">
-        <is>
-          <t>F-501 581</t>
-        </is>
-      </c>
-      <c r="F55" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="29" t="inlineStr">
-        <is>
-          <t>601/602/603/607</t>
-        </is>
-      </c>
-      <c r="B56" s="29" t="inlineStr">
-        <is>
-          <t>Cheltuieli stocuri</t>
-        </is>
-      </c>
-      <c r="C56" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D56" s="29" t="inlineStr">
-        <is>
-          <t>F-305, F-311, F-316, F-209, F-317</t>
-        </is>
-      </c>
-      <c r="E56" s="29" t="inlineStr">
-        <is>
-          <t>F-209 capitalizare; F-317 parțial | modul: MOD_NEUTRALIZARE / MOD_VANZ_AMANUNT</t>
-        </is>
-      </c>
-      <c r="F56" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="22" t="inlineStr">
-        <is>
-          <t>641/642/646</t>
-        </is>
-      </c>
-      <c r="B57" s="22" t="inlineStr">
-        <is>
-          <t>Cheltuieli personal</t>
-        </is>
-      </c>
-      <c r="C57" s="22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D57" s="22" t="inlineStr">
-        <is>
-          <t>F-413, F-201, F-208</t>
-        </is>
-      </c>
-      <c r="E57" s="22" t="inlineStr">
-        <is>
-          <t>MOD_SALARII acoperă 641 salarii, 642 tichete și 646 CAM; limitările rămase sunt declarate în Reguli_SALARII, tabelul C</t>
-        </is>
-      </c>
-      <c r="F57" s="22" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="67" t="inlineStr">
-        <is>
-          <t>6583 / 7583</t>
-        </is>
-      </c>
-      <c r="B58" s="67" t="inlineStr">
-        <is>
-          <t>Cedarea activelor</t>
-        </is>
-      </c>
-      <c r="C58" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D58" s="67" t="inlineStr">
-        <is>
-          <t>F-211, F-212</t>
-        </is>
-      </c>
-      <c r="E58" s="67" t="inlineStr">
-        <is>
-          <t>F-211 pas 5: deductibil în limita venitului | modul: MOD_IESIRE_MF</t>
-        </is>
-      </c>
-      <c r="F58" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="67" t="inlineStr">
-        <is>
-          <t>665 / 765</t>
-        </is>
-      </c>
-      <c r="B59" s="67" t="inlineStr">
-        <is>
-          <t>Diferențe de curs</t>
-        </is>
-      </c>
-      <c r="C59" s="67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D59" s="67" t="inlineStr">
-        <is>
-          <t>F-107, F-108</t>
-        </is>
-      </c>
-      <c r="E59" s="67" t="inlineStr">
-        <is>
-          <t>F-107 pași 1 și 4: cele două momente | modul: MOD_CREDIT_VALUTA / MOD_LEASING_FIN</t>
-        </is>
-      </c>
-      <c r="F59" s="67" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="22" t="inlineStr">
-        <is>
-          <t>681/781</t>
-        </is>
-      </c>
-      <c r="B60" s="22" t="inlineStr">
-        <is>
-          <t>Amortiz./ajustări P&amp;L</t>
-        </is>
-      </c>
-      <c r="C60" s="22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D60" s="22" t="inlineStr">
-        <is>
-          <t>F-204, F-210, F-108, F-201, F-202, F-203, F-106</t>
-        </is>
-      </c>
-      <c r="E60" s="22" t="inlineStr">
-        <is>
-          <t>F-108 plafon 1.500 lei/lună; F-106 reluare 7812 | modul: MOD_LEASING_FIN / MOD_SUBVENTIE / MOD_IMOBILIZARI / MOD_PROVIZION</t>
-        </is>
-      </c>
-      <c r="F60" s="22" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="29" t="inlineStr">
-        <is>
-          <t>707/701/704</t>
-        </is>
-      </c>
-      <c r="B61" s="29" t="inlineStr">
-        <is>
-          <t>Venituri CA</t>
-        </is>
-      </c>
-      <c r="C61" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D61" s="29" t="inlineStr">
-        <is>
-          <t>F-311, F-312, F-316, F-318, F-317</t>
-        </is>
-      </c>
-      <c r="E61" s="29" t="inlineStr">
-        <is>
-          <t>F-318 storno retur | modul: MOD_NEUTRALIZARE / MOD_VANZ_AMANUNT</t>
-        </is>
-      </c>
-      <c r="F61" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="29" t="inlineStr">
-        <is>
-          <t>711/712</t>
-        </is>
-      </c>
-      <c r="B62" s="29" t="inlineStr">
-        <is>
-          <t>Neutralizare producție</t>
-        </is>
-      </c>
-      <c r="C62" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D62" s="29" t="inlineStr">
-        <is>
-          <t>F-311, F-312, F-314</t>
-        </is>
-      </c>
-      <c r="E62" s="29" t="inlineStr">
-        <is>
-          <t>F-314: sold creditor 711 ÎNAINTE de închidere = normal (variație stoc); 0 după închidere | modul: MOD_NEUTRALIZARE / MOD_INCHIDERE_EX</t>
-        </is>
-      </c>
-      <c r="F62" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="29" t="inlineStr">
-        <is>
-          <t>721/722 | 721 / 722</t>
-        </is>
-      </c>
-      <c r="B63" s="29" t="inlineStr">
-        <is>
-          <t>Producție imobilizări | Producția de imobilizări</t>
-        </is>
-      </c>
-      <c r="C63" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D63" s="29" t="inlineStr">
-        <is>
-          <t>F-209 | F-201, F-208, F-209</t>
-        </is>
-      </c>
-      <c r="E63" s="29" t="inlineStr">
-        <is>
-          <t>F-209 231=722 (corectat) | F-208 pas 3 (era acoperit doar prin F-209) | modul: MOD_NEUTRALIZARE</t>
-        </is>
-      </c>
-      <c r="F63" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="29" t="inlineStr">
-        <is>
-          <t>8035</t>
-        </is>
-      </c>
-      <c r="B64" s="29" t="inlineStr">
-        <is>
-          <t>Obiecte inventar extrab.</t>
-        </is>
-      </c>
-      <c r="C64" s="29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D64" s="29" t="inlineStr">
-        <is>
-          <t>F-305, F-802</t>
-        </is>
-      </c>
-      <c r="E64" s="29" t="inlineStr">
-        <is>
-          <t>F-305 deschidere; F-802 inventariere scriptic↔faptic</t>
-        </is>
-      </c>
-      <c r="F64" s="29" t="inlineStr">
-        <is>
-          <t>NU</t>
+      <c r="E24" s="61" t="inlineStr">
+        <is>
+          <t>Sold 1621 = 74.550 + 600 = 75.150 lei = 15.000 EUR × 5,0100</t>
+        </is>
+      </c>
+      <c r="F24" s="61" t="inlineStr">
+        <is>
+          <t>5187: F-107 declară starea lui 1621, nu și dobânda de calculat pe 5187.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -3916,7 +3916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4798,22 +4798,210 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="61" t="inlineStr">
+        <is>
+          <t>Î-22</t>
+        </is>
+      </c>
+      <c r="B31" s="61" t="inlineStr">
+        <is>
+          <t>Plafoane de numerar și contul 455</t>
+        </is>
+      </c>
+      <c r="C31" s="61" t="inlineStr">
+        <is>
+          <t>Care sunt valorile exacte ale plafoanelor din Legea 70/2015 în forma modificată prin Legea 296/2023, la data operațiunii?</t>
+        </is>
+      </c>
+      <c r="D31" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="61" t="inlineStr">
+        <is>
+          <t>Documentul „Control, documente și numerar”, secțiunea de plafoane. Un plafon greșit produce amendă direct, iar fragmentarea e interzisă expres — deci nici împărțirea pe tranșe nu e o ieșire.</t>
+        </is>
+      </c>
+      <c r="F31" s="61" t="inlineStr">
+        <is>
+          <t>Am păstrat cifrele din notițe, cu mențiunea explicită că trebuie confirmate în textul în vigoare la data operațiunii.</t>
+        </is>
+      </c>
+      <c r="G31" s="61" t="inlineStr">
+        <is>
+          <t>training 19.08.2026, punctul 1</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
-      <c r="A32" s="63" t="inlineStr">
-        <is>
-          <t>21 de întrebări, 12 teme. Aceeași sursă cu dist/intrebari-formator.md și cu pagina publicată — nu pot diverge.</t>
+      <c r="A32" s="61" t="inlineStr">
+        <is>
+          <t>Î-23</t>
+        </is>
+      </c>
+      <c r="B32" s="61" t="inlineStr">
+        <is>
+          <t>Plafoane de numerar și contul 455</t>
+        </is>
+      </c>
+      <c r="C32" s="61" t="inlineStr">
+        <is>
+          <t>Care sunt exact operațiunile în numerar interzise pe contul 455 și care e temeiul legal?</t>
+        </is>
+      </c>
+      <c r="D32" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="61" t="inlineStr">
+        <is>
+          <t>Foaia „Închideri periodice”, unde 455 e urmărit trimestrial fără flux în spate. Fără regula exactă, rândul rămâne gol declarat — nu se poate scrie o monografie pentru o restricție pe care n-o cunosc.</t>
+        </is>
+      </c>
+      <c r="F32" s="61" t="inlineStr">
+        <is>
+          <t>Am lăsat 455 fără flux, cu golul marcat ca atare în foaie.</t>
+        </is>
+      </c>
+      <c r="G32" s="61" t="inlineStr">
+        <is>
+          <t>training 19.08.2026, punctul 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="61" t="inlineStr">
+        <is>
+          <t>Î-24</t>
+        </is>
+      </c>
+      <c r="B33" s="61" t="inlineStr">
+        <is>
+          <t>Comportamentul softului la încasarea în plus</t>
+        </is>
+      </c>
+      <c r="C33" s="61" t="inlineStr">
+        <is>
+          <t>Programul de contabilitate extrage automat TVA-ul din diferența trecută pe 419 la o încasare mai mare decât factura, sau trebuie forțat manual?</t>
+        </is>
+      </c>
+      <c r="D33" s="61" t="inlineStr">
+        <is>
+          <t>F-415
+C-23</t>
+        </is>
+      </c>
+      <c r="E33" s="61" t="inlineStr">
+        <is>
+          <t>F-415 (încasare peste factură) și C-23. Notițele cer explicit contraverificarea lui 4427 după simulare — deci nici formatorul nu presupune că softul o face.</t>
+        </is>
+      </c>
+      <c r="F33" s="61" t="inlineStr">
+        <is>
+          <t>Am scris fluxul cu extragerea explicită a TVA-ului, ca pas separat, tocmai ca să nu depindă de comportamentul softului.</t>
+        </is>
+      </c>
+      <c r="G33" s="61" t="inlineStr">
+        <is>
+          <t>training 19.08.2026, punctul 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="61" t="inlineStr">
+        <is>
+          <t>Î-25</t>
+        </is>
+      </c>
+      <c r="B34" s="61" t="inlineStr">
+        <is>
+          <t>Convenții de analitic rămase de fixat</t>
+        </is>
+      </c>
+      <c r="C34" s="61" t="inlineStr">
+        <is>
+          <t>Care e structura analitică exactă pe 4428 — pe situație și pe cotă?</t>
+        </is>
+      </c>
+      <c r="D34" s="61" t="inlineStr">
+        <is>
+          <t>F-316
+F-408</t>
+        </is>
+      </c>
+      <c r="E34" s="61" t="inlineStr">
+        <is>
+          <t>F-316, F-408 și analiticul Tier A al lui 4428. Workbook-ul folosește azi 4428.AM (amănunt) și 4428.INC (la încasare); pentru avizul de intrare nu există convenție scrisă.</t>
+        </is>
+      </c>
+      <c r="F34" s="61" t="inlineStr">
+        <is>
+          <t>Am folosit convenția existentă din training 4 și am lăsat avizul de intrare fără analitic propriu — vizibil ca gol în foaia „Închideri periodice”.</t>
+        </is>
+      </c>
+      <c r="G34" s="61" t="inlineStr">
+        <is>
+          <t>training 19.08.2026, punctul 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="61" t="inlineStr">
+        <is>
+          <t>Î-26</t>
+        </is>
+      </c>
+      <c r="B35" s="61" t="inlineStr">
+        <is>
+          <t>Convenții de analitic rămase de fixat</t>
+        </is>
+      </c>
+      <c r="C35" s="61" t="inlineStr">
+        <is>
+          <t>Facturile nesosite pentru imobilizări se țin pe 408 cu analitic sau direct pe 404 cu analitic?</t>
+        </is>
+      </c>
+      <c r="D35" s="61" t="inlineStr">
+        <is>
+          <t>F-408
+F-207</t>
+        </is>
+      </c>
+      <c r="E35" s="61" t="inlineStr">
+        <is>
+          <t>F-408 și F-207. Alegerea decide dacă furnizorii de exploatare se amestecă sau nu cu cei de imobilizări în balanța analitică — adică dacă 401/404 mai pot fi verificate separat.</t>
+        </is>
+      </c>
+      <c r="F35" s="61" t="inlineStr">
+        <is>
+          <t>Am păstrat 408 cu analitic, ca în exemplul din notițe, semnalând alternativa în observația contului.</t>
+        </is>
+      </c>
+      <c r="G35" s="61" t="inlineStr">
+        <is>
+          <t>training 19.08.2026, punctul 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="63" t="inlineStr">
+        <is>
+          <t>26 de întrebări, 15 teme. Aceeași sursă cu dist/intrebari-formator.md și cu pagina publicată — nu pot diverge.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8216,7 +8404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J319"/>
+  <dimension ref="A1:J326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12187,7 +12375,7 @@
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t>Adaosul comercial (amanunt). Corelatie: 707-607 = rulaj D 378.</t>
+          <t>Adaosul comercial (amanunt). Corelatie: 707-607 = rulaj D 378. — Diferențe de preț la mărfuri (adaos). Rectificativ al lui 371 la preț cu amănuntul, alături de 4428.</t>
         </is>
       </c>
       <c r="G100" s="22" t="inlineStr">
@@ -13195,7 +13383,7 @@
       </c>
       <c r="F125" s="20" t="inlineStr">
         <is>
-          <t>Avansuri incasate de la clienti.</t>
+          <t>Avansuri incasate de la clienti. — Clienți-creditori (avansuri încasate). TVA se colectează la încasarea avansului, iar la factura finală avansul se stornează — nu e venit, deci nu poate merge pe 472.</t>
         </is>
       </c>
       <c r="G125" s="20" t="inlineStr"/>
@@ -15287,7 +15475,7 @@
       </c>
       <c r="F178" s="22" t="inlineStr">
         <is>
-          <t>Contra-creanta.</t>
+          <t>Contra-creanta. — Ajustări pentru deprecierea creanțelor-clienți. Spre deosebire de ajustările de stoc, acestea SUNT deductibile condiționat, în limitele art. 26. Nu se confundă cele două regimuri.</t>
         </is>
       </c>
       <c r="G178" s="22" t="inlineStr"/>
@@ -20282,7 +20470,7 @@
     <row r="317">
       <c r="A317" s="36" t="inlineStr">
         <is>
-          <t>CONTURI ADĂUGATE ÎN ETAPA 4 (lipseau din planul inițial)</t>
+          <t>CONTURI ADĂUGATE — lipseau din planul inițial (inclusiv tabel recapitulativ de conturi, sursa 19.08.2026)</t>
         </is>
       </c>
     </row>
@@ -20387,6 +20575,370 @@
       <c r="J319" s="67" t="inlineStr">
         <is>
           <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="67" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="B320" s="67" t="inlineStr">
+        <is>
+          <t>Amortizarea instalațiilor și mijloacelor de transport</t>
+        </is>
+      </c>
+      <c r="C320" s="67" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D320" s="67" t="inlineStr">
+        <is>
+          <t>Rol in flux</t>
+        </is>
+      </c>
+      <c r="E320" s="67" t="inlineStr">
+        <is>
+          <t>Rectificativ / contra</t>
+        </is>
+      </c>
+      <c r="F320" s="67" t="inlineStr">
+        <is>
+          <t>Rectificativ pasiv al lui 213. La ieșire se debitează cu amortizarea cumulată, iar valoarea rămasă trece prin 6583.</t>
+        </is>
+      </c>
+      <c r="G320" s="67" t="inlineStr">
+        <is>
+          <t>2813 pe grupa de mijloc fix</t>
+        </is>
+      </c>
+      <c r="H320" s="67" t="inlineStr">
+        <is>
+          <t>C B</t>
+        </is>
+      </c>
+      <c r="I320" s="67" t="inlineStr">
+        <is>
+          <t>F-211, F-212</t>
+        </is>
+      </c>
+      <c r="J320" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="67" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="B321" s="67" t="inlineStr">
+        <is>
+          <t>Conturi la bănci în lei</t>
+        </is>
+      </c>
+      <c r="C321" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D321" s="67" t="inlineStr">
+        <is>
+          <t>Patrimonial (real)</t>
+        </is>
+      </c>
+      <c r="E321" s="67" t="inlineStr">
+        <is>
+          <t>Trezorerie</t>
+        </is>
+      </c>
+      <c r="F321" s="67" t="inlineStr">
+        <is>
+          <t>Contul de bancă, indiferent de instrument (ordin de plată, internet banking, mandat). Nu se confundă cu 5311 (casa) sau 5111 (cecuri de încasat, cont de ÎNCASĂRI).</t>
+        </is>
+      </c>
+      <c r="G321" s="67" t="inlineStr">
+        <is>
+          <t>5121 pe bancă și pe valută</t>
+        </is>
+      </c>
+      <c r="H321" s="67" t="inlineStr">
+        <is>
+          <t>V O</t>
+        </is>
+      </c>
+      <c r="I321" s="67" t="inlineStr">
+        <is>
+          <t>F-405, F-410</t>
+        </is>
+      </c>
+      <c r="J321" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="67" t="inlineStr">
+        <is>
+          <t>6583</t>
+        </is>
+      </c>
+      <c r="B322" s="67" t="inlineStr">
+        <is>
+          <t>Cheltuieli privind activele cedate</t>
+        </is>
+      </c>
+      <c r="C322" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D322" s="67" t="inlineStr">
+        <is>
+          <t>Patrimonial (real)</t>
+        </is>
+      </c>
+      <c r="E322" s="67" t="inlineStr">
+        <is>
+          <t>Cheltuiala</t>
+        </is>
+      </c>
+      <c r="F322" s="67" t="inlineStr">
+        <is>
+          <t>Valoarea rămasă neamortizată la ieșirea unui activ. Perechea lui 7583 — facturarea singură nu scoate activul din evidență.</t>
+        </is>
+      </c>
+      <c r="G322" s="67" t="inlineStr">
+        <is>
+          <t>6583 pe activ cedat</t>
+        </is>
+      </c>
+      <c r="H322" s="67" t="inlineStr">
+        <is>
+          <t>F C</t>
+        </is>
+      </c>
+      <c r="I322" s="67" t="inlineStr">
+        <is>
+          <t>F-211, F-212</t>
+        </is>
+      </c>
+      <c r="J322" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="67" t="inlineStr">
+        <is>
+          <t>7583</t>
+        </is>
+      </c>
+      <c r="B323" s="67" t="inlineStr">
+        <is>
+          <t>Venituri din vânzarea activelor și alte operațiuni de capital</t>
+        </is>
+      </c>
+      <c r="C323" s="67" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D323" s="67" t="inlineStr">
+        <is>
+          <t>Patrimonial (real)</t>
+        </is>
+      </c>
+      <c r="E323" s="67" t="inlineStr">
+        <is>
+          <t>Venit</t>
+        </is>
+      </c>
+      <c r="F323" s="67" t="inlineStr">
+        <is>
+          <t>Prețul de vânzare al activului. Se compară cu 6583: diferența e rezultatul cedării.</t>
+        </is>
+      </c>
+      <c r="G323" s="67" t="inlineStr">
+        <is>
+          <t>7583 pe activ cedat</t>
+        </is>
+      </c>
+      <c r="H323" s="67" t="inlineStr">
+        <is>
+          <t>F C</t>
+        </is>
+      </c>
+      <c r="I323" s="67" t="inlineStr">
+        <is>
+          <t>F-211, F-212</t>
+        </is>
+      </c>
+      <c r="J323" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="67" t="inlineStr">
+        <is>
+          <t>6814</t>
+        </is>
+      </c>
+      <c r="B324" s="67" t="inlineStr">
+        <is>
+          <t>Cheltuieli de exploatare privind ajustările pentru deprecierea activelor circulante</t>
+        </is>
+      </c>
+      <c r="C324" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D324" s="67" t="inlineStr">
+        <is>
+          <t>Patrimonial (real)</t>
+        </is>
+      </c>
+      <c r="E324" s="67" t="inlineStr">
+        <is>
+          <t>Cheltuiala</t>
+        </is>
+      </c>
+      <c r="F324" s="67" t="inlineStr">
+        <is>
+          <t>Constituirea ajustării de stoc. NEDEDUCTIBILĂ fiscal — art. 26 Cod fiscal enumeră limitativ, iar deprecierea stocurilor nu e acolo. Funcționează în oglindă cu 7814.</t>
+        </is>
+      </c>
+      <c r="G324" s="67" t="inlineStr">
+        <is>
+          <t>6814 pe natura stocului ajustat</t>
+        </is>
+      </c>
+      <c r="H324" s="67" t="inlineStr">
+        <is>
+          <t>F N</t>
+        </is>
+      </c>
+      <c r="I324" s="67" t="inlineStr">
+        <is>
+          <t>F-307</t>
+        </is>
+      </c>
+      <c r="J324" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="67" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="B325" s="67" t="inlineStr">
+        <is>
+          <t>Venituri din ajustări pentru deprecierea activelor circulante</t>
+        </is>
+      </c>
+      <c r="C325" s="67" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D325" s="67" t="inlineStr">
+        <is>
+          <t>Patrimonial (real)</t>
+        </is>
+      </c>
+      <c r="E325" s="67" t="inlineStr">
+        <is>
+          <t>Venit</t>
+        </is>
+      </c>
+      <c r="F325" s="67" t="inlineStr">
+        <is>
+          <t>Reluarea ajustării la valorificarea bunului — obligatorie prin lege. NEIMPOZABILĂ (art. 23 lit. d), ca să neutralizeze cheltuiala nedeductibilă din 6814.</t>
+        </is>
+      </c>
+      <c r="G325" s="67" t="inlineStr">
+        <is>
+          <t>7814 pe natura stocului ajustat</t>
+        </is>
+      </c>
+      <c r="H325" s="67" t="inlineStr">
+        <is>
+          <t>F N</t>
+        </is>
+      </c>
+      <c r="I325" s="67" t="inlineStr">
+        <is>
+          <t>F-307</t>
+        </is>
+      </c>
+      <c r="J325" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="67" t="inlineStr">
+        <is>
+          <t>4091</t>
+        </is>
+      </c>
+      <c r="B326" s="67" t="inlineStr">
+        <is>
+          <t>Furnizori-debitori (avansuri plătite)</t>
+        </is>
+      </c>
+      <c r="C326" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D326" s="67" t="inlineStr">
+        <is>
+          <t>Patrimonial (real)</t>
+        </is>
+      </c>
+      <c r="E326" s="67" t="inlineStr">
+        <is>
+          <t>Creanta</t>
+        </is>
+      </c>
+      <c r="F326" s="67" t="inlineStr">
+        <is>
+          <t>Avansurile se analitizează pe DESTINAȚIE: 4091 stocuri, 4092 servicii, 4093 imobilizări corporale, 4094 imobilizări necorporale. 4093/4094 au furnizor 404, nu 401. Stornarea la factura finală se face și pe 4091, și pe 401, ca efectul net să fie zero.</t>
+        </is>
+      </c>
+      <c r="G326" s="67" t="inlineStr">
+        <is>
+          <t>4091 – 4094 pe destinație</t>
+        </is>
+      </c>
+      <c r="H326" s="67" t="inlineStr">
+        <is>
+          <t>C O</t>
+        </is>
+      </c>
+      <c r="I326" s="67" t="inlineStr">
+        <is>
+          <t>F-410</t>
+        </is>
+      </c>
+      <c r="J326" s="67" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -26246,7 +26798,7 @@
       </c>
       <c r="H26" s="69" t="inlineStr">
         <is>
-          <t>Oglinda lui F-302, pe imobilizări în loc de stocuri | modul: MOD_IMOBILIZARI</t>
+          <t>Oglinda lui F-302, pe imobilizări în loc de stocuri | modul: MOD_IMOBILIZARI | ❓ Î-26</t>
         </is>
       </c>
     </row>
@@ -27178,7 +27730,7 @@
       </c>
       <c r="H50" s="28" t="inlineStr">
         <is>
-          <t>modul: MOD_VANZ_AMANUNT</t>
+          <t>modul: MOD_VANZ_AMANUNT | ❓ Î-25</t>
         </is>
       </c>
     </row>
@@ -27665,7 +28217,7 @@
       </c>
       <c r="H63" s="29" t="inlineStr">
         <is>
-          <t>Pas revelator: stingere la document. D300 (când se facturează) | modul: MOD_INTERMEDIAR</t>
+          <t>Pas revelator: stingere la document. D300 (când se facturează) | modul: MOD_INTERMEDIAR | ❓ Î-25, Î-26</t>
         </is>
       </c>
     </row>
@@ -46299,7 +46851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -46626,145 +47178,145 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="61" t="inlineStr">
+        <is>
+          <t>327 Mărfuri în curs de aprovizionare</t>
+        </is>
+      </c>
+      <c r="B15" s="61" t="inlineStr">
+        <is>
+          <t>Lunar — obligatoriu</t>
+        </is>
+      </c>
+      <c r="C15" s="61" t="inlineStr">
+        <is>
+          <t>tranzit; sold ≠ 0 înseamnă marfă plătită și neintrată în gestiune (F-302)</t>
+        </is>
+      </c>
+      <c r="D15" s="61" t="inlineStr">
+        <is>
+          <t>F-302 · F-304</t>
+        </is>
+      </c>
+      <c r="E15" s="61" t="inlineStr">
+        <is>
+          <t>Sold 327 = 0 · Sold 327=0, 408=0, 371=10.000, 401=12.100</t>
+        </is>
+      </c>
+      <c r="F15" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>Cel puțin trimestrial</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="74" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="74" t="inlineStr">
         <is>
           <t>Cont</t>
         </is>
       </c>
-      <c r="B17" s="74" t="inlineStr">
+      <c r="B18" s="74" t="inlineStr">
         <is>
           <t>Cadență</t>
         </is>
       </c>
-      <c r="C17" s="74" t="inlineStr">
+      <c r="C18" s="74" t="inlineStr">
         <is>
           <t>De ce se urmărește</t>
         </is>
       </c>
-      <c r="D17" s="74" t="inlineStr">
+      <c r="D18" s="74" t="inlineStr">
         <is>
           <t>Flux</t>
         </is>
       </c>
-      <c r="E17" s="74" t="inlineStr">
+      <c r="E18" s="74" t="inlineStr">
         <is>
           <t>Stare terminală declarată</t>
         </is>
       </c>
-      <c r="F17" s="74" t="inlineStr">
+      <c r="F18" s="74" t="inlineStr">
         <is>
           <t>Gol cunoscut</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="75" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="75" t="inlineStr">
         <is>
           <t>4091 – 4094</t>
         </is>
       </c>
-      <c r="B18" s="75" t="inlineStr">
+      <c r="B19" s="75" t="inlineStr">
         <is>
           <t>Cel puțin trimestrial</t>
         </is>
       </c>
-      <c r="C18" s="75" t="inlineStr">
+      <c r="C19" s="75" t="inlineStr">
         <is>
           <t>avansuri care nu s-au stornat la factura finală</t>
         </is>
       </c>
-      <c r="D18" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="D19" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="75" t="inlineStr">
         <is>
           <t>4091: F-410 declară starea lui 409 la nivel sintetic, nu pe analiticele de destinație 4091–4094. 4094: Idem 4093.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="61" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="61" t="inlineStr">
         <is>
           <t>419</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>Cel puțin trimestrial</t>
         </is>
       </c>
-      <c r="C19" s="61" t="inlineStr">
+      <c r="C20" s="61" t="inlineStr">
         <is>
           <t>avansuri de la clienți rămase deschise</t>
         </is>
       </c>
-      <c r="D19" s="61" t="inlineStr">
+      <c r="D20" s="61" t="inlineStr">
         <is>
           <t>F-410</t>
         </is>
       </c>
-      <c r="E19" s="61" t="inlineStr">
+      <c r="E20" s="61" t="inlineStr">
         <is>
           <t>Sold 419=0, sold 409=0 după livrare/recepție</t>
         </is>
       </c>
-      <c r="F19" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="75" t="inlineStr">
-        <is>
-          <t>401 / 411</t>
-        </is>
-      </c>
-      <c r="B20" s="75" t="inlineStr">
-        <is>
-          <t>Cel puțin trimestrial</t>
-        </is>
-      </c>
-      <c r="C20" s="75" t="inlineStr">
-        <is>
-          <t>balanță analitică; solduri cu semn contrar = eroare</t>
-        </is>
-      </c>
-      <c r="D20" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="75" t="inlineStr">
-        <is>
-          <t>401: Nu există flux care să declare „401 fără sold debitor”. Regula e o corelație de sold contrar naturii, nu o stare terminală de flux. 411: Idem 401 — vezi C-23.</t>
+      <c r="F20" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="75" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>401 / 411</t>
         </is>
       </c>
       <c r="B21" s="75" t="inlineStr">
@@ -46774,7 +47326,7 @@
       </c>
       <c r="C21" s="75" t="inlineStr">
         <is>
-          <t>sume datorate asociaților, cu restricții legale</t>
+          <t>balanță analitică; solduri cu semn contrar = eroare</t>
         </is>
       </c>
       <c r="D21" s="75" t="inlineStr">
@@ -46789,112 +47341,176 @@
       </c>
       <c r="F21" s="75" t="inlineStr">
         <is>
-          <t>455: Nu există flux pe 455. Restricțiile de numerar sunt rămase deschise.</t>
+          <t>401: Nu există flux care să declare „401 fără sold debitor”. Regula e o corelație de sold contrar naturii, nu o stare terminală de flux. 411: Idem 401 — vezi C-23.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="75" t="inlineStr">
         <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="B22" s="75" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C22" s="75" t="inlineStr">
+        <is>
+          <t>sume datorate asociaților, cu restricții legale</t>
+        </is>
+      </c>
+      <c r="D22" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="75" t="inlineStr">
+        <is>
+          <t>455: Nu există flux pe 455. Restricțiile de numerar sunt rămase deschise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="75" t="inlineStr">
+        <is>
           <t>461 / 462</t>
         </is>
       </c>
-      <c r="B22" s="75" t="inlineStr">
+      <c r="B23" s="75" t="inlineStr">
         <is>
           <t>Cel puțin trimestrial</t>
         </is>
       </c>
-      <c r="C22" s="75" t="inlineStr">
+      <c r="C23" s="75" t="inlineStr">
         <is>
           <t>debitori/creditori diverși, se împotmolesc ușor</t>
         </is>
       </c>
-      <c r="D22" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="75" t="inlineStr">
+      <c r="D23" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="75" t="inlineStr">
         <is>
           <t>461: Nu există flux pe debitori/creditori diverși. 462: Idem 461.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="61" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="B23" s="61" t="inlineStr">
-        <is>
-          <t>Cel puțin trimestrial</t>
-        </is>
-      </c>
-      <c r="C23" s="61" t="inlineStr">
-        <is>
-          <t>imobilizări în curs care trebuiau puse în funcțiune</t>
-        </is>
-      </c>
-      <c r="D23" s="61" t="inlineStr">
-        <is>
-          <t>F-208</t>
-        </is>
-      </c>
-      <c r="E23" s="61" t="inlineStr">
-        <is>
-          <t>Sold 231 = 0 după PV · Sold 231 = 0 după recepție</t>
-        </is>
-      </c>
-      <c r="F23" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="61" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="B24" s="61" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C24" s="61" t="inlineStr">
+        <is>
+          <t>imobilizări în curs care trebuiau puse în funcțiune</t>
+        </is>
+      </c>
+      <c r="D24" s="61" t="inlineStr">
+        <is>
+          <t>F-208</t>
+        </is>
+      </c>
+      <c r="E24" s="61" t="inlineStr">
+        <is>
+          <t>Sold 231 = 0 după PV · Sold 231 = 0 după recepție</t>
+        </is>
+      </c>
+      <c r="F24" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="61" t="inlineStr">
+        <is>
           <t>1621 / 5187</t>
         </is>
       </c>
-      <c r="B24" s="61" t="inlineStr">
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>Cel puțin trimestrial</t>
         </is>
       </c>
-      <c r="C24" s="61" t="inlineStr">
+      <c r="C25" s="61" t="inlineStr">
         <is>
           <t>credite și dobânzi de calculat</t>
         </is>
       </c>
-      <c r="D24" s="61" t="inlineStr">
+      <c r="D25" s="61" t="inlineStr">
         <is>
           <t>F-107</t>
         </is>
       </c>
-      <c r="E24" s="61" t="inlineStr">
+      <c r="E25" s="61" t="inlineStr">
         <is>
           <t>Sold 1621 = 74.550 + 600 = 75.150 lei = 15.000 EUR × 5,0100</t>
         </is>
       </c>
-      <c r="F24" s="61" t="inlineStr">
+      <c r="F25" s="61" t="inlineStr">
         <is>
           <t>5187: F-107 declară starea lui 1621, nu și dobânda de calculat pe 5187.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="61" t="inlineStr">
+        <is>
+          <t>223 Instalații tehnice și mijloace de transport în curs de aprovizionare</t>
+        </is>
+      </c>
+      <c r="B26" s="61" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C26" s="61" t="inlineStr">
+        <is>
+          <t>tranzit pe imobilizări; sold ≠ 0 înseamnă recepție neînregistrată (F-207)</t>
+        </is>
+      </c>
+      <c r="D26" s="61" t="inlineStr">
+        <is>
+          <t>F-207</t>
+        </is>
+      </c>
+      <c r="E26" s="61" t="inlineStr">
+        <is>
+          <t>Sold 223 = 0 pe documentele cu recepție în perioadă</t>
+        </is>
+      </c>
+      <c r="F26" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="A3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -27037,7 +27037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I712"/>
+  <dimension ref="A1:I714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -29459,7 +29459,7 @@
       </c>
       <c r="C71" s="70" t="inlineStr">
         <is>
-          <t>Concediu medical (împărțire angajator / FNUASS)</t>
+          <t>Concediu medical (împărțire angajator / FNUASS + rețineri)</t>
         </is>
       </c>
       <c r="D71" s="70" t="inlineStr">
@@ -29474,7 +29474,7 @@
       </c>
       <c r="F71" s="70" t="inlineStr">
         <is>
-          <t>6458, 4382, 423, 5121</t>
+          <t>6458, 4382, 423, 4315, 4316, 444, 646, 436, 5121</t>
         </is>
       </c>
       <c r="G71" s="70" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="H71" s="70" t="inlineStr">
         <is>
-          <t>Zilele suportate de angajator depind de codul de boală; baza e media ultimelor 6 luni, nu ultimul salariu. ❓ Reținerile din indemnizație — de confirmat cu formatorul.</t>
+          <t>Prima zi de concediu medical pentru boală obișnuită NU se plătește, februarie 2026 – decembrie 2027; regula nu se aplică urgențelor, accidentelor de muncă, sarcinii și carantinei. Baza: media veniturilor brute din ultimele 6 luni, plafonată la 12 salarii minime brute.</t>
         </is>
       </c>
     </row>
@@ -29524,7 +29524,7 @@
       </c>
       <c r="H72" s="70" t="inlineStr">
         <is>
-          <t>Limita e o treime din NET pentru datorii obișnuite. ❓ Limita pentru obligații de întreținere — de confirmat.</t>
+          <t>Art. 729 Cod procedură civilă: 1/2 pentru obligații de întreținere sau alocații pentru copii · 1/3 pentru alte datorii · la mai multe popriri, maximum 1/2 în total. Sub salariul minim net se urmărește doar partea care depășește jumătate din el.</t>
         </is>
       </c>
     </row>
@@ -46169,7 +46169,7 @@
     <row r="624">
       <c r="A624" s="36" t="inlineStr">
         <is>
-          <t>F-416 — Concediu medical (împărțire angajator / FNUASS) ★</t>
+          <t>F-416 — Concediu medical (împărțire angajator / FNUASS + rețineri) ★</t>
         </is>
       </c>
     </row>
@@ -46236,7 +46236,7 @@
       </c>
       <c r="D626" s="72" t="inlineStr">
         <is>
-          <t>Indemnizație totală 1.000 lei. Primele zile le suportă angajatorul — aici 250 lei — restul vine de la casa de sănătate (FNUASS).</t>
+          <t>Indemnizație brută 1.000 lei. Primele zile le suportă angajatorul — aici 250 lei — restul vine de la FNUASS. Numărul de zile suportate de angajator depinde de codul de indemnizație.</t>
         </is>
       </c>
       <c r="E626" s="72" t="inlineStr">
@@ -46278,12 +46278,12 @@
       </c>
       <c r="C627" s="72" t="inlineStr">
         <is>
-          <t>Extras de cont — plata indemnizației</t>
+          <t>Stat de plată — reținerile din indemnizație</t>
         </is>
       </c>
       <c r="D627" s="72" t="inlineStr">
         <is>
-          <t>Salariatul primește indemnizația, indiferent cine o suportă în final.</t>
+          <t>Din indemnizația brută se rețin CAS 25% = 250 și, ÎNCEPÂND CU VENITURILE LUNII AUGUST 2026, CASS 10% = 100 (Legea 170/2026 — până atunci CASS nu se datora). Impozitul de 10% se aplică pe ce rămâne: 10% × 650 = 65.</t>
         </is>
       </c>
       <c r="E627" s="72" t="inlineStr">
@@ -46293,17 +46293,21 @@
       </c>
       <c r="F627" s="72" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>4315
+4316
+444</t>
         </is>
       </c>
       <c r="G627" s="72" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>250
+100
+65</t>
         </is>
       </c>
       <c r="H627" s="72" t="inlineStr">
         <is>
-          <t>Stingerea datoriei față de salariat</t>
+          <t>Contribuții și impozit reținute din indemnizație</t>
         </is>
       </c>
       <c r="I627" s="72" t="inlineStr">
@@ -46323,32 +46327,32 @@
       </c>
       <c r="C628" s="73" t="inlineStr">
         <is>
-          <t>Extras de cont — decontarea cu FNUASS</t>
+          <t>Nota de contribuții — partea angajatorului</t>
         </is>
       </c>
       <c r="D628" s="73" t="inlineStr">
         <is>
-          <t>Casa de sănătate rambursează partea ei. ROLUL LUI 4382 se vede aici: e o creanță, nu o cheltuială. Firma a avansat banii casei, nu i-a cheltuit — de aceea partea de 750 nu apare niciodată pe cheltuieli.</t>
+          <t>ROLUL ÎMPĂRȚIRII se vede aici. CAM se calculează DOAR pe partea suportată de angajator: 2,25% × 250 = 5,63. Pe cele 750 de lei care vin din FNUASS nu se datorează CAM — nu sunt cheltuiala firmei, sunt bani avansați în numele casei.</t>
         </is>
       </c>
       <c r="E628" s="73" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F628" s="73" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>436</t>
         </is>
       </c>
       <c r="G628" s="73" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="H628" s="73" t="inlineStr">
         <is>
-          <t>Încasarea creanței sociale</t>
+          <t>CAM doar pe partea proprie, nu pe indemnizația din fond</t>
         </is>
       </c>
       <c r="I628" s="73" t="inlineStr">
@@ -46368,188 +46372,188 @@
       </c>
       <c r="C629" s="72" t="inlineStr">
         <is>
+          <t>Extras de cont — plata către salariat</t>
+        </is>
+      </c>
+      <c r="D629" s="72" t="inlineStr">
+        <is>
+          <t>Netul: 1.000 − 250 − 100 − 65 = 585 lei.</t>
+        </is>
+      </c>
+      <c r="E629" s="72" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="F629" s="72" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="G629" s="72" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="H629" s="72" t="inlineStr">
+        <is>
+          <t>Stingerea datoriei față de salariat</t>
+        </is>
+      </c>
+      <c r="I629" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="72" t="inlineStr">
+        <is>
+          <t>F-416</t>
+        </is>
+      </c>
+      <c r="B630" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="C630" s="72" t="inlineStr">
+        <is>
+          <t>Extras de cont — decontarea cu FNUASS</t>
+        </is>
+      </c>
+      <c r="D630" s="72" t="inlineStr">
+        <is>
+          <t>Casa rambursează partea ei. 4382 e o CREANȚĂ: firma a avansat banii casei, nu i-a cheltuit — de aceea cele 750 nu apar niciodată pe cheltuieli, oricât ar trece prin datoria față de salariat.</t>
+        </is>
+      </c>
+      <c r="E630" s="72" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="F630" s="72" t="inlineStr">
+        <is>
+          <t>4382</t>
+        </is>
+      </c>
+      <c r="G630" s="72" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="H630" s="72" t="inlineStr">
+        <is>
+          <t>Încasarea creanței sociale</t>
+        </is>
+      </c>
+      <c r="I630" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="72" t="inlineStr">
+        <is>
+          <t>F-416</t>
+        </is>
+      </c>
+      <c r="B631" s="72" t="n">
+        <v>6</v>
+      </c>
+      <c r="C631" s="72" t="inlineStr">
+        <is>
           <t>Verificare</t>
         </is>
       </c>
-      <c r="D629" s="72" t="inlineStr">
-        <is>
-          <t>Sold 423 = 0 și sold 4382 = 0 pe indemnizația decontată. Pe rezultat au rămas doar cele 250 suportate efectiv. Un sold 4382 care nu se stinge înseamnă indemnizații nerecuperate de la casă — bani ai firmei blocați, adesea din dosare incomplete.</t>
-        </is>
-      </c>
-      <c r="E629" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F629" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G629" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H629" s="72" t="inlineStr">
-        <is>
-          <t>Stare terminală: 423 și 4382 fără sold; pe cheltuieli doar partea angajatorului</t>
-        </is>
-      </c>
-      <c r="I629" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" s="33" t="inlineStr">
-        <is>
-          <t>Principiul: Indemnizația de concediu medical trece integral prin datoria față de salariat, dar numai o parte din ea e cheltuiala firmei. Restul e o creanță față de FNUASS: bani avansați, nu bani cheltuiți. Cine trece toată indemnizația pe cheltuieli își subestimează rezultatul și pierde din vedere ce are de recuperat.</t>
+      <c r="D631" s="72" t="inlineStr">
+        <is>
+          <t>Sold 423 = 0 și sold 4382 = 0 pe indemnizația decontată. Pe rezultat au rămas 250 (cheltuiala proprie) + 5,63 (CAM aferent ei). Un sold 4382 care nu se stinge înseamnă indemnizații nerecuperate de la casă — bani ai firmei blocați, adesea din dosare incomplete.</t>
+        </is>
+      </c>
+      <c r="E631" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F631" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G631" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H631" s="72" t="inlineStr">
+        <is>
+          <t>Stare terminală: 423 și 4382 fără sold; pe cheltuieli doar partea angajatorului și CAM-ul aferent ei</t>
+        </is>
+      </c>
+      <c r="I631" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="632">
-      <c r="A632" s="36" t="inlineStr">
+      <c r="A632" s="33" t="inlineStr">
+        <is>
+          <t>Principiul: Indemnizația trece integral prin datoria față de salariat, dar numai o parte din ea e cheltuiala firmei — iar linia de demarcație decide și baza CAM. Reținerile se fac pe TOATĂ indemnizația, indiferent cine o suportă; CAM-ul, doar pe partea proprie. Cine trece toată indemnizația pe cheltuieli își subestimează rezultatul și plătește CAM pe banii altcuiva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="36" t="inlineStr">
         <is>
           <t>F-417 — Poprire pe salariu (rețineri datorate terților) ★</t>
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" s="71" t="inlineStr">
+    <row r="635">
+      <c r="A635" s="71" t="inlineStr">
         <is>
           <t>Flux ID</t>
         </is>
       </c>
-      <c r="B633" s="71" t="inlineStr">
+      <c r="B635" s="71" t="inlineStr">
         <is>
           <t>Pas</t>
         </is>
       </c>
-      <c r="C633" s="71" t="inlineStr">
+      <c r="C635" s="71" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="D633" s="71" t="inlineStr">
+      <c r="D635" s="71" t="inlineStr">
         <is>
           <t>Explicație</t>
         </is>
       </c>
-      <c r="E633" s="71" t="inlineStr">
+      <c r="E635" s="71" t="inlineStr">
         <is>
           <t>Cont D</t>
         </is>
       </c>
-      <c r="F633" s="71" t="inlineStr">
+      <c r="F635" s="71" t="inlineStr">
         <is>
           <t>Cont C</t>
         </is>
       </c>
-      <c r="G633" s="71" t="inlineStr">
+      <c r="G635" s="71" t="inlineStr">
         <is>
           <t>Sumă (lei)</t>
         </is>
       </c>
-      <c r="H633" s="71" t="inlineStr">
+      <c r="H635" s="71" t="inlineStr">
         <is>
           <t>Rol revelat</t>
         </is>
       </c>
-      <c r="I633" s="71" t="inlineStr">
+      <c r="I635" s="71" t="inlineStr">
         <is>
           <t>Declarativ</t>
-        </is>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" s="72" t="inlineStr">
-        <is>
-          <t>F-417</t>
-        </is>
-      </c>
-      <c r="B634" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="C634" s="72" t="inlineStr">
-        <is>
-          <t>Adresă de înființare a popririi + stat de plată</t>
-        </is>
-      </c>
-      <c r="D634" s="72" t="inlineStr">
-        <is>
-          <t>Din netul de 29.250 se reține treimea legală: 9.749,03 lei. Se calculează din NET, nu din brut — banii merg la executor, nu la stat, deci după ce statul și-a luat partea.</t>
-        </is>
-      </c>
-      <c r="E634" s="72" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
-      <c r="F634" s="72" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
-      <c r="G634" s="72" t="inlineStr">
-        <is>
-          <t>9.749,03</t>
-        </is>
-      </c>
-      <c r="H634" s="72" t="inlineStr">
-        <is>
-          <t>Datoria față de salariat scade, apare o datorie față de terț</t>
-        </is>
-      </c>
-      <c r="I634" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" s="73" t="inlineStr">
-        <is>
-          <t>F-417</t>
-        </is>
-      </c>
-      <c r="B635" s="73" t="n">
-        <v>2</v>
-      </c>
-      <c r="C635" s="73" t="inlineStr">
-        <is>
-          <t>Extras de cont — plata către executor</t>
-        </is>
-      </c>
-      <c r="D635" s="73" t="inlineStr">
-        <is>
-          <t>ROLUL LUI 427 se vede aici: firma nu a câștigat și nu a cheltuit nimic. A fost doar conductă între salariat și creditorul lui. Contul intră și iese cu aceeași sumă, iar pe rezultat nu apare nimic.</t>
-        </is>
-      </c>
-      <c r="E635" s="73" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
-      <c r="F635" s="73" t="inlineStr">
-        <is>
-          <t>5121</t>
-        </is>
-      </c>
-      <c r="G635" s="73" t="inlineStr">
-        <is>
-          <t>9.749,03</t>
-        </is>
-      </c>
-      <c r="H635" s="73" t="inlineStr">
-        <is>
-          <t>Stingerea datoriei față de terț</t>
-        </is>
-      </c>
-      <c r="I635" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -46560,192 +46564,192 @@
         </is>
       </c>
       <c r="B636" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C636" s="72" t="inlineStr">
+        <is>
+          <t>Adresă de înființare a popririi + stat de plată</t>
+        </is>
+      </c>
+      <c r="D636" s="72" t="inlineStr">
+        <is>
+          <t>Datorie obișnuită, deci limita e o treime: 33,33% din 29.250 = 9.749,03 lei. Se calculează din NET, nu din brut — banii merg la executor, nu la stat, deci după ce statul și-a luat partea. La obligații de întreținere limita ar fi fost 1/2, iar la mai multe popriri pe aceeași sumă tot 1/2 e maximul, indiferent de natura creanțelor.</t>
+        </is>
+      </c>
+      <c r="E636" s="72" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="F636" s="72" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="G636" s="72" t="inlineStr">
+        <is>
+          <t>9.749,03</t>
+        </is>
+      </c>
+      <c r="H636" s="72" t="inlineStr">
+        <is>
+          <t>Datoria față de salariat scade, apare o datorie față de terț</t>
+        </is>
+      </c>
+      <c r="I636" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="73" t="inlineStr">
+        <is>
+          <t>F-417</t>
+        </is>
+      </c>
+      <c r="B637" s="73" t="n">
+        <v>2</v>
+      </c>
+      <c r="C637" s="73" t="inlineStr">
+        <is>
+          <t>Extras de cont — plata către executor</t>
+        </is>
+      </c>
+      <c r="D637" s="73" t="inlineStr">
+        <is>
+          <t>ROLUL LUI 427 se vede aici: firma nu a câștigat și nu a cheltuit nimic. A fost doar conductă între salariat și creditorul lui. Contul intră și iese cu aceeași sumă, iar pe rezultat nu apare nimic.</t>
+        </is>
+      </c>
+      <c r="E637" s="73" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="F637" s="73" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="G637" s="73" t="inlineStr">
+        <is>
+          <t>9.749,03</t>
+        </is>
+      </c>
+      <c r="H637" s="73" t="inlineStr">
+        <is>
+          <t>Stingerea datoriei față de terț</t>
+        </is>
+      </c>
+      <c r="I637" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="72" t="inlineStr">
+        <is>
+          <t>F-417</t>
+        </is>
+      </c>
+      <c r="B638" s="72" t="n">
         <v>3</v>
       </c>
-      <c r="C636" s="72" t="inlineStr">
+      <c r="C638" s="72" t="inlineStr">
         <is>
           <t>Verificare</t>
         </is>
       </c>
-      <c r="D636" s="72" t="inlineStr">
-        <is>
-          <t>Sold 427 = 0 după virare. Un sold creditor care persistă înseamnă bani opriți din salariul cuiva și nevirați — firma nu are ce explica: trebuia fie să îi vireze, fie să nu îi rețină.</t>
-        </is>
-      </c>
-      <c r="E636" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F636" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G636" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H636" s="72" t="inlineStr">
+      <c r="D638" s="72" t="inlineStr">
+        <is>
+          <t>Sold 427 = 0 după virare. Un sold creditor care persistă înseamnă bani opriți din salariul cuiva și nevirați — firma nu are ce explica: trebuia fie să îi vireze, fie să nu îi rețină. Verificare în amonte: dacă venitul salariatului e sub salariul minim NET, se poate urmări doar partea care depășește jumătate din el — reținerea peste acest prag îl păgubește pe salariat, nu pe debitor.</t>
+        </is>
+      </c>
+      <c r="E638" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F638" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G638" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H638" s="72" t="inlineStr">
         <is>
           <t>Stare terminală: sold 427 = 0; rulaj creditor = sold creditor pe luna curentă</t>
         </is>
       </c>
-      <c r="I636" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" s="33" t="inlineStr">
+      <c r="I638" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="33" t="inlineStr">
         <is>
           <t>Principiul: 427 e cont de tranzit, nu de rezultat. Banii care trec prin el nu sunt ai firmei în niciun moment — sunt ai salariatului, opriți în beneficiul creditorului lui. De aceea soldul lui e singurul din grupa 42x care, rămas neachitat, trece din problemă contabilă în problemă penală.</t>
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" s="36" t="inlineStr">
+    <row r="641">
+      <c r="A641" s="36" t="inlineStr">
         <is>
           <t>F-418 — Drepturi de personal neridicate (421 → 426)</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" s="71" t="inlineStr">
+    <row r="642">
+      <c r="A642" s="71" t="inlineStr">
         <is>
           <t>Flux ID</t>
         </is>
       </c>
-      <c r="B640" s="71" t="inlineStr">
+      <c r="B642" s="71" t="inlineStr">
         <is>
           <t>Pas</t>
         </is>
       </c>
-      <c r="C640" s="71" t="inlineStr">
+      <c r="C642" s="71" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="D640" s="71" t="inlineStr">
+      <c r="D642" s="71" t="inlineStr">
         <is>
           <t>Explicație</t>
         </is>
       </c>
-      <c r="E640" s="71" t="inlineStr">
+      <c r="E642" s="71" t="inlineStr">
         <is>
           <t>Cont D</t>
         </is>
       </c>
-      <c r="F640" s="71" t="inlineStr">
+      <c r="F642" s="71" t="inlineStr">
         <is>
           <t>Cont C</t>
         </is>
       </c>
-      <c r="G640" s="71" t="inlineStr">
+      <c r="G642" s="71" t="inlineStr">
         <is>
           <t>Sumă (lei)</t>
         </is>
       </c>
-      <c r="H640" s="71" t="inlineStr">
+      <c r="H642" s="71" t="inlineStr">
         <is>
           <t>Rol revelat</t>
         </is>
       </c>
-      <c r="I640" s="71" t="inlineStr">
+      <c r="I642" s="71" t="inlineStr">
         <is>
           <t>Declarativ</t>
-        </is>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" s="72" t="inlineStr">
-        <is>
-          <t>F-418</t>
-        </is>
-      </c>
-      <c r="B641" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="C641" s="72" t="inlineStr">
-        <is>
-          <t>Stat de plată + registru de casă</t>
-        </is>
-      </c>
-      <c r="D641" s="72" t="inlineStr">
-        <is>
-          <t>Doi salariați nu și-au ridicat salariile: 3.400 lei. Datoria rămâne integral, doar că nu mai e „salariu de plătit luna asta”.</t>
-        </is>
-      </c>
-      <c r="E641" s="72" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
-      <c r="F641" s="72" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="G641" s="72" t="inlineStr">
-        <is>
-          <t>3.400</t>
-        </is>
-      </c>
-      <c r="H641" s="72" t="inlineStr">
-        <is>
-          <t>Reclasificare în interiorul pasivului</t>
-        </is>
-      </c>
-      <c r="I641" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" s="72" t="inlineStr">
-        <is>
-          <t>F-418</t>
-        </is>
-      </c>
-      <c r="B642" s="72" t="n">
-        <v>2</v>
-      </c>
-      <c r="C642" s="72" t="inlineStr">
-        <is>
-          <t>Dispoziție de plată — ridicarea ulterioară</t>
-        </is>
-      </c>
-      <c r="D642" s="72" t="inlineStr">
-        <is>
-          <t>Salariatul se prezintă și își ia banii.</t>
-        </is>
-      </c>
-      <c r="E642" s="72" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="F642" s="72" t="inlineStr">
-        <is>
-          <t>5311</t>
-        </is>
-      </c>
-      <c r="G642" s="72" t="inlineStr">
-        <is>
-          <t>3.400</t>
-        </is>
-      </c>
-      <c r="H642" s="72" t="inlineStr">
-        <is>
-          <t>Stingerea datoriei</t>
-        </is>
-      </c>
-      <c r="I642" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -46756,192 +46760,192 @@
         </is>
       </c>
       <c r="B643" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C643" s="72" t="inlineStr">
+        <is>
+          <t>Stat de plată + registru de casă</t>
+        </is>
+      </c>
+      <c r="D643" s="72" t="inlineStr">
+        <is>
+          <t>Doi salariați nu și-au ridicat salariile: 3.400 lei. Datoria rămâne integral, doar că nu mai e „salariu de plătit luna asta”.</t>
+        </is>
+      </c>
+      <c r="E643" s="72" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="F643" s="72" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="G643" s="72" t="inlineStr">
+        <is>
+          <t>3.400</t>
+        </is>
+      </c>
+      <c r="H643" s="72" t="inlineStr">
+        <is>
+          <t>Reclasificare în interiorul pasivului</t>
+        </is>
+      </c>
+      <c r="I643" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="72" t="inlineStr">
+        <is>
+          <t>F-418</t>
+        </is>
+      </c>
+      <c r="B644" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C644" s="72" t="inlineStr">
+        <is>
+          <t>Dispoziție de plată — ridicarea ulterioară</t>
+        </is>
+      </c>
+      <c r="D644" s="72" t="inlineStr">
+        <is>
+          <t>Salariatul se prezintă și își ia banii.</t>
+        </is>
+      </c>
+      <c r="E644" s="72" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="F644" s="72" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="G644" s="72" t="inlineStr">
+        <is>
+          <t>3.400</t>
+        </is>
+      </c>
+      <c r="H644" s="72" t="inlineStr">
+        <is>
+          <t>Stingerea datoriei</t>
+        </is>
+      </c>
+      <c r="I644" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="72" t="inlineStr">
+        <is>
+          <t>F-418</t>
+        </is>
+      </c>
+      <c r="B645" s="72" t="n">
         <v>3</v>
       </c>
-      <c r="C643" s="72" t="inlineStr">
+      <c r="C645" s="72" t="inlineStr">
         <is>
           <t>Verificare</t>
         </is>
       </c>
-      <c r="D643" s="72" t="inlineStr">
+      <c r="D645" s="72" t="inlineStr">
         <is>
           <t>După reclasificare, sold 421 = restul de plată de pe statul curent, iar sold 426 = exact sumele nerevendicate. Fără pasul 1, corelația se rupe și pare că firma are restanțe de salarii — când de fapt are bani nerevendicați.</t>
         </is>
       </c>
-      <c r="E643" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F643" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G643" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H643" s="72" t="inlineStr">
+      <c r="E645" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F645" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G645" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H645" s="72" t="inlineStr">
         <is>
           <t>Stare terminală: sold 421 reconciliat cu statul; sold 426 = doar sumele nerevendicate, urmărite până la ridicare</t>
         </is>
       </c>
-      <c r="I643" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" s="33" t="inlineStr">
+      <c r="I645" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="33" t="inlineStr">
         <is>
           <t>Principiul: Un salariu neridicat nu e o economie și nu e o restanță. E aceeași datorie, mutată pe un cont care spune de ce nu s-a plătit — iar mutarea e ce face corelația cu statul de plată să funcționeze din nou.</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" s="36" t="inlineStr">
+    <row r="648">
+      <c r="A648" s="36" t="inlineStr">
         <is>
           <t>F-419 — Creanță față de un fost salariat (4282)</t>
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" s="71" t="inlineStr">
+    <row r="649">
+      <c r="A649" s="71" t="inlineStr">
         <is>
           <t>Flux ID</t>
         </is>
       </c>
-      <c r="B647" s="71" t="inlineStr">
+      <c r="B649" s="71" t="inlineStr">
         <is>
           <t>Pas</t>
         </is>
       </c>
-      <c r="C647" s="71" t="inlineStr">
+      <c r="C649" s="71" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="D647" s="71" t="inlineStr">
+      <c r="D649" s="71" t="inlineStr">
         <is>
           <t>Explicație</t>
         </is>
       </c>
-      <c r="E647" s="71" t="inlineStr">
+      <c r="E649" s="71" t="inlineStr">
         <is>
           <t>Cont D</t>
         </is>
       </c>
-      <c r="F647" s="71" t="inlineStr">
+      <c r="F649" s="71" t="inlineStr">
         <is>
           <t>Cont C</t>
         </is>
       </c>
-      <c r="G647" s="71" t="inlineStr">
+      <c r="G649" s="71" t="inlineStr">
         <is>
           <t>Sumă (lei)</t>
         </is>
       </c>
-      <c r="H647" s="71" t="inlineStr">
+      <c r="H649" s="71" t="inlineStr">
         <is>
           <t>Rol revelat</t>
         </is>
       </c>
-      <c r="I647" s="71" t="inlineStr">
+      <c r="I649" s="71" t="inlineStr">
         <is>
           <t>Declarativ</t>
-        </is>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" s="72" t="inlineStr">
-        <is>
-          <t>F-419</t>
-        </is>
-      </c>
-      <c r="B648" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="C648" s="72" t="inlineStr">
-        <is>
-          <t>Notă de lichidare + proces-verbal de predare-primire</t>
-        </is>
-      </c>
-      <c r="D648" s="72" t="inlineStr">
-        <is>
-          <t>Salariatul pleacă fără să predea un echipament de protecție de 400 lei. Firma are de primit, deci are o creanță.</t>
-        </is>
-      </c>
-      <c r="E648" s="72" t="inlineStr">
-        <is>
-          <t>4282</t>
-        </is>
-      </c>
-      <c r="F648" s="72" t="inlineStr">
-        <is>
-          <t>7588</t>
-        </is>
-      </c>
-      <c r="G648" s="72" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="H648" s="72" t="inlineStr">
-        <is>
-          <t>Creanță față de fostul salariat + Venit din despăgubiri</t>
-        </is>
-      </c>
-      <c r="I648" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" s="72" t="inlineStr">
-        <is>
-          <t>F-419</t>
-        </is>
-      </c>
-      <c r="B649" s="72" t="n">
-        <v>2</v>
-      </c>
-      <c r="C649" s="72" t="inlineStr">
-        <is>
-          <t>Chitanță / extras de cont</t>
-        </is>
-      </c>
-      <c r="D649" s="72" t="inlineStr">
-        <is>
-          <t>Încasarea. Crește un activ (casa) și scade alt activ (creanța) — nu e nevoie de niciun cont de pasiv, pentru că firma nu datorează nimic.</t>
-        </is>
-      </c>
-      <c r="E649" s="72" t="inlineStr">
-        <is>
-          <t>5311</t>
-        </is>
-      </c>
-      <c r="F649" s="72" t="inlineStr">
-        <is>
-          <t>4282</t>
-        </is>
-      </c>
-      <c r="G649" s="72" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="H649" s="72" t="inlineStr">
-        <is>
-          <t>Stingerea creanței</t>
-        </is>
-      </c>
-      <c r="I649" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -46952,192 +46956,192 @@
         </is>
       </c>
       <c r="B650" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C650" s="72" t="inlineStr">
+        <is>
+          <t>Notă de lichidare + proces-verbal de predare-primire</t>
+        </is>
+      </c>
+      <c r="D650" s="72" t="inlineStr">
+        <is>
+          <t>Salariatul pleacă fără să predea un echipament de protecție de 400 lei. Firma are de primit, deci are o creanță.</t>
+        </is>
+      </c>
+      <c r="E650" s="72" t="inlineStr">
+        <is>
+          <t>4282</t>
+        </is>
+      </c>
+      <c r="F650" s="72" t="inlineStr">
+        <is>
+          <t>7588</t>
+        </is>
+      </c>
+      <c r="G650" s="72" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H650" s="72" t="inlineStr">
+        <is>
+          <t>Creanță față de fostul salariat + Venit din despăgubiri</t>
+        </is>
+      </c>
+      <c r="I650" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="72" t="inlineStr">
+        <is>
+          <t>F-419</t>
+        </is>
+      </c>
+      <c r="B651" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C651" s="72" t="inlineStr">
+        <is>
+          <t>Chitanță / extras de cont</t>
+        </is>
+      </c>
+      <c r="D651" s="72" t="inlineStr">
+        <is>
+          <t>Încasarea. Crește un activ (casa) și scade alt activ (creanța) — nu e nevoie de niciun cont de pasiv, pentru că firma nu datorează nimic.</t>
+        </is>
+      </c>
+      <c r="E651" s="72" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="F651" s="72" t="inlineStr">
+        <is>
+          <t>4282</t>
+        </is>
+      </c>
+      <c r="G651" s="72" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H651" s="72" t="inlineStr">
+        <is>
+          <t>Stingerea creanței</t>
+        </is>
+      </c>
+      <c r="I651" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="72" t="inlineStr">
+        <is>
+          <t>F-419</t>
+        </is>
+      </c>
+      <c r="B652" s="72" t="n">
         <v>3</v>
       </c>
-      <c r="C650" s="72" t="inlineStr">
+      <c r="C652" s="72" t="inlineStr">
         <is>
           <t>Verificare</t>
         </is>
       </c>
-      <c r="D650" s="72" t="inlineStr">
+      <c r="D652" s="72" t="inlineStr">
         <is>
           <t>Sold 4282 = 0 după încasare. Un sold CREDITOR pe 4282 e contrar naturii contului și înseamnă ori încasare dublă, ori înregistrare inițială pe partea greșită (C-23).</t>
         </is>
       </c>
-      <c r="E650" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F650" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G650" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H650" s="72" t="inlineStr">
+      <c r="E652" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F652" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G652" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H652" s="72" t="inlineStr">
         <is>
           <t>Stare terminală: sold 4282 = 0, niciodată creditor</t>
         </is>
       </c>
-      <c r="I650" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" s="33" t="inlineStr">
+      <c r="I652" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="33" t="inlineStr">
         <is>
           <t>Principiul: Ce ai de primit e activ, ce ai de dat e pasiv — iar întrebarea se pune despre operațiunea economică, nu despre conturi. La încasare nu îți trebuie „opusul băncii”: crește un activ și scade altul, iar totalul bilanțului nu se mișcă.</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" s="36" t="inlineStr">
+    <row r="655">
+      <c r="A655" s="36" t="inlineStr">
         <is>
           <t>F-420 — Impozitul pe venitul microîntreprinderii (698 → 4418)</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" s="71" t="inlineStr">
+    <row r="656">
+      <c r="A656" s="71" t="inlineStr">
         <is>
           <t>Flux ID</t>
         </is>
       </c>
-      <c r="B654" s="71" t="inlineStr">
+      <c r="B656" s="71" t="inlineStr">
         <is>
           <t>Pas</t>
         </is>
       </c>
-      <c r="C654" s="71" t="inlineStr">
+      <c r="C656" s="71" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="D654" s="71" t="inlineStr">
+      <c r="D656" s="71" t="inlineStr">
         <is>
           <t>Explicație</t>
         </is>
       </c>
-      <c r="E654" s="71" t="inlineStr">
+      <c r="E656" s="71" t="inlineStr">
         <is>
           <t>Cont D</t>
         </is>
       </c>
-      <c r="F654" s="71" t="inlineStr">
+      <c r="F656" s="71" t="inlineStr">
         <is>
           <t>Cont C</t>
         </is>
       </c>
-      <c r="G654" s="71" t="inlineStr">
+      <c r="G656" s="71" t="inlineStr">
         <is>
           <t>Sumă (lei)</t>
         </is>
       </c>
-      <c r="H654" s="71" t="inlineStr">
+      <c r="H656" s="71" t="inlineStr">
         <is>
           <t>Rol revelat</t>
         </is>
       </c>
-      <c r="I654" s="71" t="inlineStr">
+      <c r="I656" s="71" t="inlineStr">
         <is>
           <t>Declarativ</t>
-        </is>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" s="72" t="inlineStr">
-        <is>
-          <t>F-420</t>
-        </is>
-      </c>
-      <c r="B655" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="C655" s="72" t="inlineStr">
-        <is>
-          <t>Calcul trimestrial pe veniturile totale</t>
-        </is>
-      </c>
-      <c r="D655" s="72" t="inlineStr">
-        <is>
-          <t>Venituri trimestriale 240.000 lei, cotă 1%: impozit 2.400 lei. Baza e VENITUL, nu profitul — de aceea contul e 698, nu 691.</t>
-        </is>
-      </c>
-      <c r="E655" s="72" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="F655" s="72" t="inlineStr">
-        <is>
-          <t>4418</t>
-        </is>
-      </c>
-      <c r="G655" s="72" t="inlineStr">
-        <is>
-          <t>2.400</t>
-        </is>
-      </c>
-      <c r="H655" s="72" t="inlineStr">
-        <is>
-          <t>Cheltuială cu impozitul pe venit + Datorie</t>
-        </is>
-      </c>
-      <c r="I655" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" s="72" t="inlineStr">
-        <is>
-          <t>F-420</t>
-        </is>
-      </c>
-      <c r="B656" s="72" t="n">
-        <v>2</v>
-      </c>
-      <c r="C656" s="72" t="inlineStr">
-        <is>
-          <t>Extras de cont — plata la termen (D100 trimestrial)</t>
-        </is>
-      </c>
-      <c r="D656" s="72" t="inlineStr">
-        <is>
-          <t>Plata până la data de 25 a lunii următoare trimestrului.</t>
-        </is>
-      </c>
-      <c r="E656" s="72" t="inlineStr">
-        <is>
-          <t>4418</t>
-        </is>
-      </c>
-      <c r="F656" s="72" t="inlineStr">
-        <is>
-          <t>5121</t>
-        </is>
-      </c>
-      <c r="G656" s="72" t="inlineStr">
-        <is>
-          <t>2.400</t>
-        </is>
-      </c>
-      <c r="H656" s="72" t="inlineStr">
-        <is>
-          <t>Stingerea datoriei fiscale</t>
-        </is>
-      </c>
-      <c r="I656" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -47148,235 +47152,235 @@
         </is>
       </c>
       <c r="B657" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C657" s="72" t="inlineStr">
+        <is>
+          <t>Calcul trimestrial pe veniturile totale</t>
+        </is>
+      </c>
+      <c r="D657" s="72" t="inlineStr">
+        <is>
+          <t>Venituri trimestriale 240.000 lei, cotă 1%: impozit 2.400 lei. Baza e VENITUL, nu profitul — de aceea contul e 698, nu 691.</t>
+        </is>
+      </c>
+      <c r="E657" s="72" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="F657" s="72" t="inlineStr">
+        <is>
+          <t>4418</t>
+        </is>
+      </c>
+      <c r="G657" s="72" t="inlineStr">
+        <is>
+          <t>2.400</t>
+        </is>
+      </c>
+      <c r="H657" s="72" t="inlineStr">
+        <is>
+          <t>Cheltuială cu impozitul pe venit + Datorie</t>
+        </is>
+      </c>
+      <c r="I657" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="72" t="inlineStr">
+        <is>
+          <t>F-420</t>
+        </is>
+      </c>
+      <c r="B658" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C658" s="72" t="inlineStr">
+        <is>
+          <t>Extras de cont — plata la termen (D100 trimestrial)</t>
+        </is>
+      </c>
+      <c r="D658" s="72" t="inlineStr">
+        <is>
+          <t>Plata până la data de 25 a lunii următoare trimestrului.</t>
+        </is>
+      </c>
+      <c r="E658" s="72" t="inlineStr">
+        <is>
+          <t>4418</t>
+        </is>
+      </c>
+      <c r="F658" s="72" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="G658" s="72" t="inlineStr">
+        <is>
+          <t>2.400</t>
+        </is>
+      </c>
+      <c r="H658" s="72" t="inlineStr">
+        <is>
+          <t>Stingerea datoriei fiscale</t>
+        </is>
+      </c>
+      <c r="I658" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="72" t="inlineStr">
+        <is>
+          <t>F-420</t>
+        </is>
+      </c>
+      <c r="B659" s="72" t="n">
         <v>3</v>
       </c>
-      <c r="C657" s="72" t="inlineStr">
+      <c r="C659" s="72" t="inlineStr">
         <is>
           <t>Verificare</t>
         </is>
       </c>
-      <c r="D657" s="72" t="inlineStr">
+      <c r="D659" s="72" t="inlineStr">
         <is>
           <t>Sold 4418 creditor = impozitul trimestrului curent, nedatorat încă. Un sold DEBITOR înseamnă că s-a plătit mai mult decât se datorează — de investigat, nu de reportat.</t>
         </is>
       </c>
-      <c r="E657" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F657" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G657" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H657" s="72" t="inlineStr">
+      <c r="E659" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F659" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G659" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H659" s="72" t="inlineStr">
         <is>
           <t>Stare terminală: sold 4418 creditor, egal cu obligația trimestrului curent</t>
         </is>
       </c>
-      <c r="I657" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" s="33" t="inlineStr">
+      <c r="I659" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="33" t="inlineStr">
         <is>
           <t>Principiul: Microul e impozit pe VENIT, nu pe profit — de aceea nu poate sta pe un analitic al lui 691. La depășirea pragului, societatea trece la impozit pe profit din TRIMESTRUL depășirii, nu din următorul: clientul care se apropie de prag trebuie anunțat înainte, nu după.</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" s="36" t="inlineStr">
+    <row r="662">
+      <c r="A662" s="36" t="inlineStr">
         <is>
           <t>F-421 — Decizie de impunere ANAF pe TVA (analitic în afara decontului) ★</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" s="71" t="inlineStr">
+    <row r="663">
+      <c r="A663" s="71" t="inlineStr">
         <is>
           <t>Flux ID</t>
         </is>
       </c>
-      <c r="B661" s="71" t="inlineStr">
+      <c r="B663" s="71" t="inlineStr">
         <is>
           <t>Pas</t>
         </is>
       </c>
-      <c r="C661" s="71" t="inlineStr">
+      <c r="C663" s="71" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="D661" s="71" t="inlineStr">
+      <c r="D663" s="71" t="inlineStr">
         <is>
           <t>Explicație</t>
         </is>
       </c>
-      <c r="E661" s="71" t="inlineStr">
+      <c r="E663" s="71" t="inlineStr">
         <is>
           <t>Cont D</t>
         </is>
       </c>
-      <c r="F661" s="71" t="inlineStr">
+      <c r="F663" s="71" t="inlineStr">
         <is>
           <t>Cont C</t>
         </is>
       </c>
-      <c r="G661" s="71" t="inlineStr">
+      <c r="G663" s="71" t="inlineStr">
         <is>
           <t>Sumă (lei)</t>
         </is>
       </c>
-      <c r="H661" s="71" t="inlineStr">
+      <c r="H663" s="71" t="inlineStr">
         <is>
           <t>Rol revelat</t>
         </is>
       </c>
-      <c r="I661" s="71" t="inlineStr">
+      <c r="I663" s="71" t="inlineStr">
         <is>
           <t>Declarativ</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" s="72" t="inlineStr">
+    <row r="664">
+      <c r="A664" s="72" t="inlineStr">
         <is>
           <t>F-421</t>
         </is>
       </c>
-      <c r="B662" s="72" t="n">
+      <c r="B664" s="72" t="n">
         <v>1</v>
       </c>
-      <c r="C662" s="72" t="inlineStr">
+      <c r="C664" s="72" t="inlineStr">
         <is>
           <t>Decizie de impunere după inspecție fiscală</t>
         </is>
       </c>
-      <c r="D662" s="72" t="inlineStr">
+      <c r="D664" s="72" t="inlineStr">
         <is>
           <t>ANAF stabilește TVA suplimentar de plată 18.000 lei. Suma e o datorie reală, dar nu provine din operațiunile lunii.</t>
         </is>
       </c>
-      <c r="E662" s="72" t="inlineStr">
+      <c r="E664" s="72" t="inlineStr">
         <is>
           <t>635</t>
         </is>
       </c>
-      <c r="F662" s="72" t="inlineStr">
+      <c r="F664" s="72" t="inlineStr">
         <is>
           <t>4423.ANAF</t>
         </is>
       </c>
-      <c r="G662" s="72" t="inlineStr">
+      <c r="G664" s="72" t="inlineStr">
         <is>
           <t>18.000</t>
         </is>
       </c>
-      <c r="H662" s="72" t="inlineStr">
+      <c r="H664" s="72" t="inlineStr">
         <is>
           <t>Cheltuială cu alte impozite + Datorie fiscală pe analitic distinct</t>
         </is>
       </c>
-      <c r="I662" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" s="72" t="inlineStr">
-        <is>
-          <t>F-421</t>
-        </is>
-      </c>
-      <c r="B663" s="72" t="n">
-        <v>2</v>
-      </c>
-      <c r="C663" s="72" t="inlineStr">
-        <is>
-          <t>Extras de cont — plata deciziei</t>
-        </is>
-      </c>
-      <c r="D663" s="72" t="inlineStr">
-        <is>
-          <t>Se plătește ca orice datorie fiscală.</t>
-        </is>
-      </c>
-      <c r="E663" s="72" t="inlineStr">
-        <is>
-          <t>4423.ANAF</t>
-        </is>
-      </c>
-      <c r="F663" s="72" t="inlineStr">
-        <is>
-          <t>5121</t>
-        </is>
-      </c>
-      <c r="G663" s="72" t="inlineStr">
-        <is>
-          <t>18.000</t>
-        </is>
-      </c>
-      <c r="H663" s="72" t="inlineStr">
-        <is>
-          <t>Stingerea datoriei</t>
-        </is>
-      </c>
-      <c r="I663" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" s="73" t="inlineStr">
-        <is>
-          <t>F-421</t>
-        </is>
-      </c>
-      <c r="B664" s="73" t="n">
-        <v>3</v>
-      </c>
-      <c r="C664" s="73" t="inlineStr">
-        <is>
-          <t>Închiderea lunară de TVA</t>
-        </is>
-      </c>
-      <c r="D664" s="73" t="inlineStr">
-        <is>
-          <t>ROLUL ANALITICULUI se vede aici: închiderea lunii lucrează pe 4423 curent și NU atinge 4423.ANAF. Fără analitic, suma din decizie ar intra în soldul care se compară cu decontul, iar decontul ar părea greșit cu exact 18.000 — o eroare care se face singură.</t>
-        </is>
-      </c>
-      <c r="E664" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F664" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G664" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H664" s="73" t="inlineStr">
-        <is>
-          <t>Analiticul ține decizia în afara circuitului declarativ</t>
-        </is>
-      </c>
-      <c r="I664" s="73" t="inlineStr">
+      <c r="I664" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -47389,131 +47393,221 @@
         </is>
       </c>
       <c r="B665" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C665" s="72" t="inlineStr">
+        <is>
+          <t>Extras de cont — plata deciziei</t>
+        </is>
+      </c>
+      <c r="D665" s="72" t="inlineStr">
+        <is>
+          <t>Se plătește ca orice datorie fiscală.</t>
+        </is>
+      </c>
+      <c r="E665" s="72" t="inlineStr">
+        <is>
+          <t>4423.ANAF</t>
+        </is>
+      </c>
+      <c r="F665" s="72" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="G665" s="72" t="inlineStr">
+        <is>
+          <t>18.000</t>
+        </is>
+      </c>
+      <c r="H665" s="72" t="inlineStr">
+        <is>
+          <t>Stingerea datoriei</t>
+        </is>
+      </c>
+      <c r="I665" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="73" t="inlineStr">
+        <is>
+          <t>F-421</t>
+        </is>
+      </c>
+      <c r="B666" s="73" t="n">
+        <v>3</v>
+      </c>
+      <c r="C666" s="73" t="inlineStr">
+        <is>
+          <t>Închiderea lunară de TVA</t>
+        </is>
+      </c>
+      <c r="D666" s="73" t="inlineStr">
+        <is>
+          <t>ROLUL ANALITICULUI se vede aici: închiderea lunii lucrează pe 4423 curent și NU atinge 4423.ANAF. Fără analitic, suma din decizie ar intra în soldul care se compară cu decontul, iar decontul ar părea greșit cu exact 18.000 — o eroare care se face singură.</t>
+        </is>
+      </c>
+      <c r="E666" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F666" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G666" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H666" s="73" t="inlineStr">
+        <is>
+          <t>Analiticul ține decizia în afara circuitului declarativ</t>
+        </is>
+      </c>
+      <c r="I666" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="72" t="inlineStr">
+        <is>
+          <t>F-421</t>
+        </is>
+      </c>
+      <c r="B667" s="72" t="n">
         <v>4</v>
       </c>
-      <c r="C665" s="72" t="inlineStr">
+      <c r="C667" s="72" t="inlineStr">
         <is>
           <t>Verificare</t>
         </is>
       </c>
-      <c r="D665" s="72" t="inlineStr">
+      <c r="D667" s="72" t="inlineStr">
         <is>
           <t>Sold 4423.ANAF = 0 după plată, iar soldul 4423 curent se potrivește cu decontul lunii. Cele două nu se însumează niciodată în decont.</t>
         </is>
       </c>
-      <c r="E665" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F665" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G665" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H665" s="72" t="inlineStr">
+      <c r="E667" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F667" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G667" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H667" s="72" t="inlineStr">
         <is>
           <t>Stare terminală: 4423.ANAF stins; corelația decont ↔ balanță rămâne valabilă pe analiticul curent</t>
         </is>
       </c>
-      <c r="I665" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" s="33" t="inlineStr">
+      <c r="I667" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="33" t="inlineStr">
         <is>
           <t>Principiul: Un analitic nu e o preferință de organizare când separă două lucruri care se supun unor reguli diferite. TVA-ul din decizia de impunere e datorie, dar nu e TVA declarativ — iar dacă stau pe același cont, corelația sfântă dintre decont și balanță se rupe fără ca nimeni să vadă de ce.</t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" s="36" t="inlineStr">
+    <row r="670">
+      <c r="A670" s="36" t="inlineStr">
         <is>
           <t>F-422 — Închiderea lunară a obligațiilor salariale (rulaj = sold) ★</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" s="71" t="inlineStr">
+    <row r="671">
+      <c r="A671" s="71" t="inlineStr">
         <is>
           <t>Flux ID</t>
         </is>
       </c>
-      <c r="B669" s="71" t="inlineStr">
+      <c r="B671" s="71" t="inlineStr">
         <is>
           <t>Pas</t>
         </is>
       </c>
-      <c r="C669" s="71" t="inlineStr">
+      <c r="C671" s="71" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="D669" s="71" t="inlineStr">
+      <c r="D671" s="71" t="inlineStr">
         <is>
           <t>Explicație</t>
         </is>
       </c>
-      <c r="E669" s="71" t="inlineStr">
+      <c r="E671" s="71" t="inlineStr">
         <is>
           <t>Cont D</t>
         </is>
       </c>
-      <c r="F669" s="71" t="inlineStr">
+      <c r="F671" s="71" t="inlineStr">
         <is>
           <t>Cont C</t>
         </is>
       </c>
-      <c r="G669" s="71" t="inlineStr">
+      <c r="G671" s="71" t="inlineStr">
         <is>
           <t>Sumă (lei)</t>
         </is>
       </c>
-      <c r="H669" s="71" t="inlineStr">
+      <c r="H671" s="71" t="inlineStr">
         <is>
           <t>Rol revelat</t>
         </is>
       </c>
-      <c r="I669" s="71" t="inlineStr">
+      <c r="I671" s="71" t="inlineStr">
         <is>
           <t>Declarativ</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" s="72" t="inlineStr">
+    <row r="672">
+      <c r="A672" s="72" t="inlineStr">
         <is>
           <t>F-422</t>
         </is>
       </c>
-      <c r="B670" s="72" t="n">
+      <c r="B672" s="72" t="n">
         <v>1</v>
       </c>
-      <c r="C670" s="72" t="inlineStr">
+      <c r="C672" s="72" t="inlineStr">
         <is>
           <t>Nota de salarii a lunii curente (iulie)</t>
         </is>
       </c>
-      <c r="D670" s="72" t="inlineStr">
+      <c r="D672" s="72" t="inlineStr">
         <is>
           <t>Obligațiile lunii se creează pe credit: CAS 12.500, CASS 5.000, impozit 3.250, CAM 1.125. Total datorat pentru iulie: 21.875.</t>
         </is>
       </c>
-      <c r="E670" s="72" t="inlineStr">
+      <c r="E672" s="72" t="inlineStr">
         <is>
           <t>421
 646</t>
         </is>
       </c>
-      <c r="F670" s="72" t="inlineStr">
+      <c r="F672" s="72" t="inlineStr">
         <is>
           <t>4315
 4316
@@ -47521,43 +47615,43 @@
 436</t>
         </is>
       </c>
-      <c r="G670" s="72" t="inlineStr">
+      <c r="G672" s="72" t="inlineStr">
         <is>
           <t>20.750
 1.125</t>
         </is>
       </c>
-      <c r="H670" s="72" t="inlineStr">
+      <c r="H672" s="72" t="inlineStr">
         <is>
           <t>Constituirea obligațiilor lunii</t>
         </is>
       </c>
-      <c r="I670" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" s="72" t="inlineStr">
+      <c r="I672" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="72" t="inlineStr">
         <is>
           <t>F-422</t>
         </is>
       </c>
-      <c r="B671" s="72" t="n">
+      <c r="B673" s="72" t="n">
         <v>2</v>
       </c>
-      <c r="C671" s="72" t="inlineStr">
+      <c r="C673" s="72" t="inlineStr">
         <is>
           <t>Extras de cont — 25 iulie, plata obligațiilor lunii IUNIE</t>
         </is>
       </c>
-      <c r="D671" s="72" t="inlineStr">
+      <c r="D673" s="72" t="inlineStr">
         <is>
           <t>Pe 25 iulie se plătesc obligațiile lunii iunie, nu ale lui iulie. Presupunem că iunie avea aceleași sume.</t>
         </is>
       </c>
-      <c r="E671" s="72" t="inlineStr">
+      <c r="E673" s="72" t="inlineStr">
         <is>
           <t>4315
 4316
@@ -47565,12 +47659,12 @@
 436</t>
         </is>
       </c>
-      <c r="F671" s="72" t="inlineStr">
+      <c r="F673" s="72" t="inlineStr">
         <is>
           <t>5121</t>
         </is>
       </c>
-      <c r="G671" s="72" t="inlineStr">
+      <c r="G673" s="72" t="inlineStr">
         <is>
           <t>12.500
 5.000
@@ -47578,262 +47672,172 @@
 1.125</t>
         </is>
       </c>
-      <c r="H671" s="72" t="inlineStr">
+      <c r="H673" s="72" t="inlineStr">
         <is>
           <t>Stingerea obligațiilor lunii precedente</t>
         </is>
       </c>
-      <c r="I671" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" s="73" t="inlineStr">
+      <c r="I673" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="73" t="inlineStr">
         <is>
           <t>F-422</t>
         </is>
       </c>
-      <c r="B672" s="73" t="n">
+      <c r="B674" s="73" t="n">
         <v>3</v>
       </c>
-      <c r="C672" s="73" t="inlineStr">
+      <c r="C674" s="73" t="inlineStr">
         <is>
           <t>Verificare la 31 iulie — pasul revelator</t>
         </is>
       </c>
-      <c r="D672" s="73" t="inlineStr">
+      <c r="D674" s="73" t="inlineStr">
         <is>
           <t>ROLUL DECALAJULUI se vede aici. Rulajul debitor al lunii e plata lui iunie; rulajul creditor e obligația lui iulie. Ce rămâne pe credit e exact obligația lui iulie — deci sold creditor = rulaj creditor. Dacă soldul e MAI MARE, diferența e o restanță din trecut, iar mărimea ei spune de cât timp.</t>
         </is>
       </c>
-      <c r="E672" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F672" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G672" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H672" s="73" t="inlineStr">
+      <c r="E674" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F674" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G674" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H674" s="73" t="inlineStr">
         <is>
           <t>Rulajul creditor al lunii = soldul creditor la finalul lunii</t>
         </is>
       </c>
-      <c r="I672" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" s="72" t="inlineStr">
+      <c r="I674" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="72" t="inlineStr">
         <is>
           <t>F-422</t>
         </is>
       </c>
-      <c r="B673" s="72" t="n">
+      <c r="B675" s="72" t="n">
         <v>4</v>
       </c>
-      <c r="C673" s="72" t="inlineStr">
+      <c r="C675" s="72" t="inlineStr">
         <is>
           <t>Verificare</t>
         </is>
       </c>
-      <c r="D673" s="72" t="inlineStr">
+      <c r="D675" s="72" t="inlineStr">
         <is>
           <t>Sold 444 = rulaj creditor 444; sold 4315 și sold 4316 = rulajele lor; sold 436 = rulaj creditor 436. Toate patru se confruntă cu fișa pe plătitor din SPV. Egalitatea e testul de bun-platnic (C-25, C-26).</t>
         </is>
       </c>
-      <c r="E673" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F673" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G673" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H673" s="72" t="inlineStr">
+      <c r="E675" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F675" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G675" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H675" s="72" t="inlineStr">
         <is>
           <t>Stare terminală: pe 444, 4315, 4316 și 436, soldul creditor egalează rulajul creditor al lunii</t>
         </is>
       </c>
-      <c r="I673" s="72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" s="33" t="inlineStr">
+      <c r="I675" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="33" t="inlineStr">
         <is>
           <t>Principiul: O datorie constituită lunar și achitată în luna următoare are, la sfârșit de lună, sold creditor egal cu rulajul creditor. Nu e o coincidență de calendar, e o consecință a decalajului de scadență — și de aceea orice depășire e restanță, nu decalaj. Verificarea nu cere niciun document în plus: totul e deja în balanță.</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" s="68" t="inlineStr">
+    <row r="678">
+      <c r="A678" s="68" t="inlineStr">
         <is>
           <t>CLASA 5 — TREZORERIE</t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" s="36" t="inlineStr">
+    <row r="680">
+      <c r="A680" s="36" t="inlineStr">
         <is>
           <t>F-501 — Viramente interne 581 ★ Intermediar (evită dublă numărare)</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" s="17" t="inlineStr">
+    <row r="681">
+      <c r="A681" s="17" t="inlineStr">
         <is>
           <t>Flux ID</t>
         </is>
       </c>
-      <c r="B679" s="17" t="inlineStr">
+      <c r="B681" s="17" t="inlineStr">
         <is>
           <t>Pas</t>
         </is>
       </c>
-      <c r="C679" s="17" t="inlineStr">
+      <c r="C681" s="17" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="D679" s="17" t="inlineStr">
+      <c r="D681" s="17" t="inlineStr">
         <is>
           <t>Explicație</t>
         </is>
       </c>
-      <c r="E679" s="17" t="inlineStr">
+      <c r="E681" s="17" t="inlineStr">
         <is>
           <t>Cont D</t>
         </is>
       </c>
-      <c r="F679" s="17" t="inlineStr">
+      <c r="F681" s="17" t="inlineStr">
         <is>
           <t>Cont C</t>
         </is>
       </c>
-      <c r="G679" s="17" t="inlineStr">
+      <c r="G681" s="17" t="inlineStr">
         <is>
           <t>Sumă (lei)</t>
         </is>
       </c>
-      <c r="H679" s="17" t="inlineStr">
+      <c r="H681" s="17" t="inlineStr">
         <is>
           <t>Rol revelat</t>
         </is>
       </c>
-      <c r="I679" s="17" t="inlineStr">
+      <c r="I681" s="17" t="inlineStr">
         <is>
           <t>Declarativ</t>
-        </is>
-      </c>
-    </row>
-    <row r="680" ht="42" customHeight="1">
-      <c r="A680" s="32" t="inlineStr">
-        <is>
-          <t>F-501</t>
-        </is>
-      </c>
-      <c r="B680" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C680" s="32" t="inlineStr">
-        <is>
-          <t>Dispoziție de plată / ordin transfer</t>
-        </is>
-      </c>
-      <c r="D680" s="32" t="inlineStr">
-        <is>
-          <t>Transfer 10.000 din bancă către casă (sau între conturi). Până la confirmare se folosește 581.</t>
-        </is>
-      </c>
-      <c r="E680" s="32" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="F680" s="32" t="inlineStr">
-        <is>
-          <t>512.1</t>
-        </is>
-      </c>
-      <c r="G680" s="32" t="inlineStr">
-        <is>
-          <t>10.000</t>
-        </is>
-      </c>
-      <c r="H680" s="32" t="inlineStr">
-        <is>
-          <t>Intermediar / clarificare (pas revelator)</t>
-        </is>
-      </c>
-      <c r="I680" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="681" ht="42" customHeight="1">
-      <c r="A681" s="32" t="inlineStr">
-        <is>
-          <t>F-501</t>
-        </is>
-      </c>
-      <c r="B681" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="C681" s="32" t="inlineStr">
-        <is>
-          <t>Chitanță / extras casă</t>
-        </is>
-      </c>
-      <c r="D681" s="32" t="inlineStr">
-        <is>
-          <t>Confirmare intrare în casă</t>
-        </is>
-      </c>
-      <c r="E681" s="32" t="inlineStr">
-        <is>
-          <t>531.1</t>
-        </is>
-      </c>
-      <c r="F681" s="32" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="G681" s="32" t="inlineStr">
-        <is>
-          <t>10.000</t>
-        </is>
-      </c>
-      <c r="H681" s="32" t="inlineStr">
-        <is>
-          <t>Stingere intermediar → Trezorerie reală</t>
-        </is>
-      </c>
-      <c r="I681" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -47844,383 +47848,383 @@
         </is>
       </c>
       <c r="B682" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C682" s="32" t="inlineStr">
+        <is>
+          <t>Dispoziție de plată / ordin transfer</t>
+        </is>
+      </c>
+      <c r="D682" s="32" t="inlineStr">
+        <is>
+          <t>Transfer 10.000 din bancă către casă (sau între conturi). Până la confirmare se folosește 581.</t>
+        </is>
+      </c>
+      <c r="E682" s="32" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="F682" s="32" t="inlineStr">
+        <is>
+          <t>512.1</t>
+        </is>
+      </c>
+      <c r="G682" s="32" t="inlineStr">
+        <is>
+          <t>10.000</t>
+        </is>
+      </c>
+      <c r="H682" s="32" t="inlineStr">
+        <is>
+          <t>Intermediar / clarificare (pas revelator)</t>
+        </is>
+      </c>
+      <c r="I682" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="683" ht="42" customHeight="1">
+      <c r="A683" s="32" t="inlineStr">
+        <is>
+          <t>F-501</t>
+        </is>
+      </c>
+      <c r="B683" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C683" s="32" t="inlineStr">
+        <is>
+          <t>Chitanță / extras casă</t>
+        </is>
+      </c>
+      <c r="D683" s="32" t="inlineStr">
+        <is>
+          <t>Confirmare intrare în casă</t>
+        </is>
+      </c>
+      <c r="E683" s="32" t="inlineStr">
+        <is>
+          <t>531.1</t>
+        </is>
+      </c>
+      <c r="F683" s="32" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="G683" s="32" t="inlineStr">
+        <is>
+          <t>10.000</t>
+        </is>
+      </c>
+      <c r="H683" s="32" t="inlineStr">
+        <is>
+          <t>Stingere intermediar → Trezorerie reală</t>
+        </is>
+      </c>
+      <c r="I683" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="684" ht="42" customHeight="1">
+      <c r="A684" s="32" t="inlineStr">
+        <is>
+          <t>F-501</t>
+        </is>
+      </c>
+      <c r="B684" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="C682" s="32" t="inlineStr">
+      <c r="C684" s="32" t="inlineStr">
         <is>
           <t>Verificare</t>
         </is>
       </c>
-      <c r="D682" s="32" t="inlineStr">
+      <c r="D684" s="32" t="inlineStr">
         <is>
           <t>Sold 581 = 0. Fără 581: dacă se face 531=512 direct înainte de confirmare, riscă dublă numărare sau solduri inconsistente între journal și extras.</t>
         </is>
       </c>
-      <c r="E682" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F682" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G682" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H682" s="32" t="inlineStr">
+      <c r="E684" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F684" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G684" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H684" s="32" t="inlineStr">
         <is>
           <t>Stare terminală: 581 stins</t>
         </is>
       </c>
-      <c r="I682" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" s="36" t="inlineStr">
+      <c r="I684" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="36" t="inlineStr">
         <is>
           <t>F-502 — Avansuri de trezorerie</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" s="17" t="inlineStr">
+    <row r="687">
+      <c r="A687" s="17" t="inlineStr">
         <is>
           <t>Flux ID</t>
         </is>
       </c>
-      <c r="B685" s="17" t="inlineStr">
+      <c r="B687" s="17" t="inlineStr">
         <is>
           <t>Pas</t>
         </is>
       </c>
-      <c r="C685" s="17" t="inlineStr">
+      <c r="C687" s="17" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="D685" s="17" t="inlineStr">
+      <c r="D687" s="17" t="inlineStr">
         <is>
           <t>Explicație</t>
         </is>
       </c>
-      <c r="E685" s="17" t="inlineStr">
+      <c r="E687" s="17" t="inlineStr">
         <is>
           <t>Cont D</t>
         </is>
       </c>
-      <c r="F685" s="17" t="inlineStr">
+      <c r="F687" s="17" t="inlineStr">
         <is>
           <t>Cont C</t>
         </is>
       </c>
-      <c r="G685" s="17" t="inlineStr">
+      <c r="G687" s="17" t="inlineStr">
         <is>
           <t>Sumă (lei)</t>
         </is>
       </c>
-      <c r="H685" s="17" t="inlineStr">
+      <c r="H687" s="17" t="inlineStr">
         <is>
           <t>Rol revelat</t>
         </is>
       </c>
-      <c r="I685" s="17" t="inlineStr">
+      <c r="I687" s="17" t="inlineStr">
         <is>
           <t>Declarativ</t>
         </is>
       </c>
     </row>
-    <row r="686" ht="38" customHeight="1">
-      <c r="A686" s="46" t="inlineStr">
+    <row r="688" ht="38" customHeight="1">
+      <c r="A688" s="46" t="inlineStr">
         <is>
           <t>F-502</t>
         </is>
       </c>
-      <c r="B686" s="46" t="n">
+      <c r="B688" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="C686" s="46" t="inlineStr">
+      <c r="C688" s="46" t="inlineStr">
         <is>
           <t>Dispoziție de plată / ordin</t>
         </is>
       </c>
-      <c r="D686" s="46" t="inlineStr">
+      <c r="D688" s="46" t="inlineStr">
         <is>
           <t>Avans spre decontare angajat 1.500</t>
         </is>
       </c>
-      <c r="E686" s="46" t="inlineStr">
+      <c r="E688" s="46" t="inlineStr">
         <is>
           <t>542</t>
         </is>
       </c>
-      <c r="F686" s="46" t="inlineStr">
+      <c r="F688" s="46" t="inlineStr">
         <is>
           <t>531.1 / 512</t>
         </is>
       </c>
-      <c r="G686" s="46" t="inlineStr">
+      <c r="G688" s="46" t="inlineStr">
         <is>
           <t>1.500</t>
         </is>
       </c>
-      <c r="H686" s="46" t="inlineStr">
+      <c r="H688" s="46" t="inlineStr">
         <is>
           <t>Creanță (până la decont)</t>
         </is>
       </c>
-      <c r="I686" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="687" ht="38" customHeight="1">
-      <c r="A687" s="46" t="inlineStr">
+      <c r="I688" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="689" ht="38" customHeight="1">
+      <c r="A689" s="46" t="inlineStr">
         <is>
           <t>F-502</t>
         </is>
       </c>
-      <c r="B687" s="46" t="n">
+      <c r="B689" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="C687" s="46" t="inlineStr">
+      <c r="C689" s="46" t="inlineStr">
         <is>
           <t>Decont cheltuieli</t>
         </is>
       </c>
-      <c r="D687" s="46" t="inlineStr">
+      <c r="D689" s="46" t="inlineStr">
         <is>
           <t>Justificare cu documente 1.350 + restituire 150</t>
         </is>
       </c>
-      <c r="E687" s="46" t="inlineStr">
+      <c r="E689" s="46" t="inlineStr">
         <is>
           <t>6xx
 531.1</t>
         </is>
       </c>
-      <c r="F687" s="46" t="inlineStr">
+      <c r="F689" s="46" t="inlineStr">
         <is>
           <t>542</t>
         </is>
       </c>
-      <c r="G687" s="46" t="inlineStr">
+      <c r="G689" s="46" t="inlineStr">
         <is>
           <t>1.350
 150</t>
         </is>
       </c>
-      <c r="H687" s="46" t="inlineStr">
+      <c r="H689" s="46" t="inlineStr">
         <is>
           <t>Cheltuială + Stingere creanță</t>
         </is>
       </c>
-      <c r="I687" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="688" ht="38" customHeight="1">
-      <c r="A688" s="46" t="inlineStr">
+      <c r="I689" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="690" ht="38" customHeight="1">
+      <c r="A690" s="46" t="inlineStr">
         <is>
           <t>F-502</t>
         </is>
       </c>
-      <c r="B688" s="46" t="n">
+      <c r="B690" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="C688" s="46" t="inlineStr">
+      <c r="C690" s="46" t="inlineStr">
         <is>
           <t>Verificare</t>
         </is>
       </c>
-      <c r="D688" s="46" t="inlineStr">
+      <c r="D690" s="46" t="inlineStr">
         <is>
           <t>Sold 542 = 0 după decont. Dacă rămâne sold → angajatul are de restituit sau de justificat.</t>
         </is>
       </c>
-      <c r="E688" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F688" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G688" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H688" s="46" t="inlineStr">
+      <c r="E690" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F690" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G690" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H690" s="46" t="inlineStr">
         <is>
           <t>Stare terminală</t>
         </is>
       </c>
-      <c r="I688" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" s="68" t="inlineStr">
+      <c r="I690" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="68" t="inlineStr">
         <is>
           <t>CLASA 8 — CONTURI ÎN AFARA BILANȚULUI</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" s="36" t="inlineStr">
+    <row r="694">
+      <c r="A694" s="36" t="inlineStr">
         <is>
           <t>F-801 — Angajamente extrabilanțiere</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" s="17" t="inlineStr">
+    <row r="695">
+      <c r="A695" s="17" t="inlineStr">
         <is>
           <t>Flux ID</t>
         </is>
       </c>
-      <c r="B693" s="17" t="inlineStr">
+      <c r="B695" s="17" t="inlineStr">
         <is>
           <t>Pas</t>
         </is>
       </c>
-      <c r="C693" s="17" t="inlineStr">
+      <c r="C695" s="17" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="D693" s="17" t="inlineStr">
+      <c r="D695" s="17" t="inlineStr">
         <is>
           <t>Explicație</t>
         </is>
       </c>
-      <c r="E693" s="17" t="inlineStr">
+      <c r="E695" s="17" t="inlineStr">
         <is>
           <t>Cont D</t>
         </is>
       </c>
-      <c r="F693" s="17" t="inlineStr">
+      <c r="F695" s="17" t="inlineStr">
         <is>
           <t>Cont C</t>
         </is>
       </c>
-      <c r="G693" s="17" t="inlineStr">
+      <c r="G695" s="17" t="inlineStr">
         <is>
           <t>Sumă (lei)</t>
         </is>
       </c>
-      <c r="H693" s="17" t="inlineStr">
+      <c r="H695" s="17" t="inlineStr">
         <is>
           <t>Rol revelat</t>
         </is>
       </c>
-      <c r="I693" s="17" t="inlineStr">
+      <c r="I695" s="17" t="inlineStr">
         <is>
           <t>Declarativ</t>
-        </is>
-      </c>
-    </row>
-    <row r="694" ht="38" customHeight="1">
-      <c r="A694" s="46" t="inlineStr">
-        <is>
-          <t>F-801</t>
-        </is>
-      </c>
-      <c r="B694" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C694" s="46" t="inlineStr">
-        <is>
-          <t>Contract garanție / gir</t>
-        </is>
-      </c>
-      <c r="D694" s="46" t="inlineStr">
-        <is>
-          <t>Garanție acordată 100.000</t>
-        </is>
-      </c>
-      <c r="E694" s="46" t="inlineStr">
-        <is>
-          <t>801</t>
-        </is>
-      </c>
-      <c r="F694" s="46" t="inlineStr">
-        <is>
-          <t>— (sau cont de contrapartidă intern)</t>
-        </is>
-      </c>
-      <c r="G694" s="46" t="inlineStr">
-        <is>
-          <t>100.000</t>
-        </is>
-      </c>
-      <c r="H694" s="46" t="inlineStr">
-        <is>
-          <t>Extrabilanțier / memorie</t>
-        </is>
-      </c>
-      <c r="I694" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="695" ht="38" customHeight="1">
-      <c r="A695" s="46" t="inlineStr">
-        <is>
-          <t>F-801</t>
-        </is>
-      </c>
-      <c r="B695" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="C695" s="46" t="inlineStr">
-        <is>
-          <t>Garanție primită</t>
-        </is>
-      </c>
-      <c r="D695" s="46" t="inlineStr">
-        <is>
-          <t>Garanție primită de la client 20.000</t>
-        </is>
-      </c>
-      <c r="E695" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F695" s="46" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="G695" s="46" t="inlineStr">
-        <is>
-          <t>20.000</t>
-        </is>
-      </c>
-      <c r="H695" s="46" t="inlineStr">
-        <is>
-          <t>Extrabilanțier / memorie</t>
-        </is>
-      </c>
-      <c r="I695" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -48231,26 +48235,26 @@
         </is>
       </c>
       <c r="B696" s="46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C696" s="46" t="inlineStr">
         <is>
-          <t>Stingere (expirare / executare)</t>
+          <t>Contract garanție / gir</t>
         </is>
       </c>
       <c r="D696" s="46" t="inlineStr">
         <is>
-          <t>La expirare sau executare se stinge prin credit/debit propriu</t>
+          <t>Garanție acordată 100.000</t>
         </is>
       </c>
       <c r="E696" s="46" t="inlineStr">
         <is>
-          <t>— / 801</t>
+          <t>801</t>
         </is>
       </c>
       <c r="F696" s="46" t="inlineStr">
         <is>
-          <t>801 / —</t>
+          <t>— (sau cont de contrapartidă intern)</t>
         </is>
       </c>
       <c r="G696" s="46" t="inlineStr">
@@ -48260,7 +48264,7 @@
       </c>
       <c r="H696" s="46" t="inlineStr">
         <is>
-          <t>Stingere memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="I696" s="46" t="inlineStr">
@@ -48276,185 +48280,185 @@
         </is>
       </c>
       <c r="B697" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C697" s="46" t="inlineStr">
+        <is>
+          <t>Garanție primită</t>
+        </is>
+      </c>
+      <c r="D697" s="46" t="inlineStr">
+        <is>
+          <t>Garanție primită de la client 20.000</t>
+        </is>
+      </c>
+      <c r="E697" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F697" s="46" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="G697" s="46" t="inlineStr">
+        <is>
+          <t>20.000</t>
+        </is>
+      </c>
+      <c r="H697" s="46" t="inlineStr">
+        <is>
+          <t>Extrabilanțier / memorie</t>
+        </is>
+      </c>
+      <c r="I697" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="698" ht="38" customHeight="1">
+      <c r="A698" s="46" t="inlineStr">
+        <is>
+          <t>F-801</t>
+        </is>
+      </c>
+      <c r="B698" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C698" s="46" t="inlineStr">
+        <is>
+          <t>Stingere (expirare / executare)</t>
+        </is>
+      </c>
+      <c r="D698" s="46" t="inlineStr">
+        <is>
+          <t>La expirare sau executare se stinge prin credit/debit propriu</t>
+        </is>
+      </c>
+      <c r="E698" s="46" t="inlineStr">
+        <is>
+          <t>— / 801</t>
+        </is>
+      </c>
+      <c r="F698" s="46" t="inlineStr">
+        <is>
+          <t>801 / —</t>
+        </is>
+      </c>
+      <c r="G698" s="46" t="inlineStr">
+        <is>
+          <t>100.000</t>
+        </is>
+      </c>
+      <c r="H698" s="46" t="inlineStr">
+        <is>
+          <t>Stingere memorie</t>
+        </is>
+      </c>
+      <c r="I698" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="699" ht="38" customHeight="1">
+      <c r="A699" s="46" t="inlineStr">
+        <is>
+          <t>F-801</t>
+        </is>
+      </c>
+      <c r="B699" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="C697" s="46" t="inlineStr">
+      <c r="C699" s="46" t="inlineStr">
         <is>
           <t>Verificare</t>
         </is>
       </c>
-      <c r="D697" s="46" t="inlineStr">
+      <c r="D699" s="46" t="inlineStr">
         <is>
           <t>Nu afectează bilanțul. 8035 (obiecte inventar) e cazul special deja acoperit în F-305. Soldurile se urmăresc doar în afara bilanțului.</t>
         </is>
       </c>
-      <c r="E697" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F697" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G697" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H697" s="46" t="inlineStr">
+      <c r="E699" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F699" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G699" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H699" s="46" t="inlineStr">
         <is>
           <t>Stare terminală</t>
         </is>
       </c>
-      <c r="I697" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" s="36" t="inlineStr">
+      <c r="I699" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="36" t="inlineStr">
         <is>
           <t>F-802 — Inventariere 8035 (scriptic vs faptic) ★</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" s="57" t="inlineStr">
+    <row r="702">
+      <c r="A702" s="57" t="inlineStr">
         <is>
           <t>Flux ID</t>
         </is>
       </c>
-      <c r="B700" s="57" t="inlineStr">
+      <c r="B702" s="57" t="inlineStr">
         <is>
           <t>Pas</t>
         </is>
       </c>
-      <c r="C700" s="57" t="inlineStr">
+      <c r="C702" s="57" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="D700" s="57" t="inlineStr">
+      <c r="D702" s="57" t="inlineStr">
         <is>
           <t>Explicație</t>
         </is>
       </c>
-      <c r="E700" s="57" t="inlineStr">
+      <c r="E702" s="57" t="inlineStr">
         <is>
           <t>Cont D</t>
         </is>
       </c>
-      <c r="F700" s="57" t="inlineStr">
+      <c r="F702" s="57" t="inlineStr">
         <is>
           <t>Cont C</t>
         </is>
       </c>
-      <c r="G700" s="57" t="inlineStr">
+      <c r="G702" s="57" t="inlineStr">
         <is>
           <t>Sumă (lei)</t>
         </is>
       </c>
-      <c r="H700" s="57" t="inlineStr">
+      <c r="H702" s="57" t="inlineStr">
         <is>
           <t>Rol revelat</t>
         </is>
       </c>
-      <c r="I700" s="57" t="inlineStr">
+      <c r="I702" s="57" t="inlineStr">
         <is>
           <t>Declarativ</t>
-        </is>
-      </c>
-    </row>
-    <row r="701" ht="42" customHeight="1">
-      <c r="A701" s="30" t="inlineStr">
-        <is>
-          <t>F-802</t>
-        </is>
-      </c>
-      <c r="B701" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C701" s="30" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D701" s="30" t="inlineStr">
-        <is>
-          <t>F-305: obiecte 5.000 pe 303, consum 603=303, Dr 8035 5.000.</t>
-        </is>
-      </c>
-      <c r="E701" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F701" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G701" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H701" s="30" t="inlineStr">
-        <is>
-          <t>8035 = baza inventarierii</t>
-        </is>
-      </c>
-      <c r="I701" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="702" ht="42" customHeight="1">
-      <c r="A702" s="30" t="inlineStr">
-        <is>
-          <t>F-802</t>
-        </is>
-      </c>
-      <c r="B702" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="C702" s="30" t="inlineStr">
-        <is>
-          <t>Listă scriptică din 8035</t>
-        </is>
-      </c>
-      <c r="D702" s="30" t="inlineStr">
-        <is>
-          <t>Fișa/softul 8035 = lista obiectelor în folosință. NU lista din 303 (sold 0 după consum).</t>
-        </is>
-      </c>
-      <c r="E702" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F702" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G702" s="30" t="inlineStr">
-        <is>
-          <t>5.000</t>
-        </is>
-      </c>
-      <c r="H702" s="30" t="inlineStr">
-        <is>
-          <t>Pas revelator: 8035 e singura evidență scriptică după consum</t>
-        </is>
-      </c>
-      <c r="I702" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -48465,16 +48469,16 @@
         </is>
       </c>
       <c r="B703" s="30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C703" s="30" t="inlineStr">
         <is>
-          <t>Inventar faptic</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="D703" s="30" t="inlineStr">
         <is>
-          <t>Găsite 4.200. Lipsă 800.</t>
+          <t>F-305: obiecte 5.000 pe 303, consum 603=303, Dr 8035 5.000.</t>
         </is>
       </c>
       <c r="E703" s="30" t="inlineStr">
@@ -48494,7 +48498,7 @@
       </c>
       <c r="H703" s="30" t="inlineStr">
         <is>
-          <t>Faptic vs scriptic</t>
+          <t>8035 = baza inventarierii</t>
         </is>
       </c>
       <c r="I703" s="30" t="inlineStr">
@@ -48510,36 +48514,36 @@
         </is>
       </c>
       <c r="B704" s="30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C704" s="30" t="inlineStr">
         <is>
-          <t>Scoatere lipsă din 8035</t>
+          <t>Listă scriptică din 8035</t>
         </is>
       </c>
       <c r="D704" s="30" t="inlineStr">
         <is>
-          <t>Cr 8035 pe 800. (Opțional 658 dacă se impută.)</t>
+          <t>Fișa/softul 8035 = lista obiectelor în folosință. NU lista din 303 (sold 0 după consum).</t>
         </is>
       </c>
       <c r="E704" s="30" t="inlineStr">
         <is>
-          <t>— (sau 658)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F704" s="30" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G704" s="30" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>5.000</t>
         </is>
       </c>
       <c r="H704" s="30" t="inlineStr">
         <is>
-          <t>Stingere memorie pe lipsă</t>
+          <t>Pas revelator: 8035 e singura evidență scriptică după consum</t>
         </is>
       </c>
       <c r="I704" s="30" t="inlineStr">
@@ -48555,102 +48559,192 @@
         </is>
       </c>
       <c r="B705" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C705" s="30" t="inlineStr">
+        <is>
+          <t>Inventar faptic</t>
+        </is>
+      </c>
+      <c r="D705" s="30" t="inlineStr">
+        <is>
+          <t>Găsite 4.200. Lipsă 800.</t>
+        </is>
+      </c>
+      <c r="E705" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F705" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G705" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H705" s="30" t="inlineStr">
+        <is>
+          <t>Faptic vs scriptic</t>
+        </is>
+      </c>
+      <c r="I705" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="706" ht="42" customHeight="1">
+      <c r="A706" s="30" t="inlineStr">
+        <is>
+          <t>F-802</t>
+        </is>
+      </c>
+      <c r="B706" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C706" s="30" t="inlineStr">
+        <is>
+          <t>Scoatere lipsă din 8035</t>
+        </is>
+      </c>
+      <c r="D706" s="30" t="inlineStr">
+        <is>
+          <t>Cr 8035 pe 800. (Opțional 658 dacă se impută.)</t>
+        </is>
+      </c>
+      <c r="E706" s="30" t="inlineStr">
+        <is>
+          <t>— (sau 658)</t>
+        </is>
+      </c>
+      <c r="F706" s="30" t="inlineStr">
+        <is>
+          <t>8035</t>
+        </is>
+      </c>
+      <c r="G706" s="30" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="H706" s="30" t="inlineStr">
+        <is>
+          <t>Stingere memorie pe lipsă</t>
+        </is>
+      </c>
+      <c r="I706" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="707" ht="42" customHeight="1">
+      <c r="A707" s="30" t="inlineStr">
+        <is>
+          <t>F-802</t>
+        </is>
+      </c>
+      <c r="B707" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="C705" s="30" t="inlineStr">
+      <c r="C707" s="30" t="inlineStr">
         <is>
           <t>Verificare</t>
         </is>
       </c>
-      <c r="D705" s="30" t="inlineStr">
+      <c r="D707" s="30" t="inlineStr">
         <is>
           <t>Sold 8035=4.200=faptic. Fără 8035, inventarierea după consum nu are bază scriptică.</t>
         </is>
       </c>
-      <c r="E705" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F705" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G705" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H705" s="30" t="inlineStr">
+      <c r="E707" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F707" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G707" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H707" s="30" t="inlineStr">
         <is>
           <t>Stare terminală: 8035 = realitatea din teren</t>
         </is>
       </c>
-      <c r="I705" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" s="33" t="inlineStr">
+      <c r="I707" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="33" t="inlineStr">
         <is>
           <t>Principiul: 8035 există pentru inventariere. F-305 îl deschide; F-802 îl folosește. Softul trebuie să listeze 8035 pe obiecte — altfel e decorativ.</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" s="36" t="inlineStr">
+    <row r="711">
+      <c r="A711" s="36" t="inlineStr">
         <is>
           <t>TRANȘA 4 — CAPITALURI ȘI IMOBILIZĂRI (F-101…F-213) — Etapa 4</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" s="33" t="inlineStr">
+    <row r="712">
+      <c r="A712" s="33" t="inlineStr">
         <is>
           <t>Din trainingurile 07.08.2026 (capitaluri, credite, leasing, provizioane) și 12.08.2026 (imobilizări). Cifrele sunt cele din documentele revizuite, nu din notițele brute. ★ = flux didactic, cu pas revelator identificat.</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" s="66" t="inlineStr">
+    <row r="714">
+      <c r="A714" s="66" t="inlineStr">
         <is>
           <t>Flux ID</t>
         </is>
       </c>
-      <c r="B712" s="66" t="inlineStr">
+      <c r="B714" s="66" t="inlineStr">
         <is>
           <t>Tranșă</t>
         </is>
       </c>
-      <c r="C712" s="66" t="inlineStr">
+      <c r="C714" s="66" t="inlineStr">
         <is>
           <t>Denumire flux</t>
         </is>
       </c>
-      <c r="D712" s="66" t="inlineStr">
+      <c r="D714" s="66" t="inlineStr">
         <is>
           <t>Didactic</t>
         </is>
       </c>
-      <c r="E712" s="66" t="inlineStr">
+      <c r="E714" s="66" t="inlineStr">
         <is>
           <t>Rol(uri) revelate</t>
         </is>
       </c>
-      <c r="F712" s="66" t="inlineStr">
+      <c r="F714" s="66" t="inlineStr">
         <is>
           <t>Conturi cheie</t>
         </is>
       </c>
-      <c r="G712" s="66" t="inlineStr">
+      <c r="G714" s="66" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H712" s="66" t="inlineStr">
+      <c r="H714" s="66" t="inlineStr">
         <is>
           <t>Note / Declarativ legat</t>
         </is>
@@ -48666,10 +48760,8 @@
     <mergeCell ref="A283:I283"/>
     <mergeCell ref="A567:I567"/>
     <mergeCell ref="A335:I335"/>
-    <mergeCell ref="A658:I658"/>
     <mergeCell ref="A519:I519"/>
     <mergeCell ref="A575:I575"/>
-    <mergeCell ref="A690:I690"/>
     <mergeCell ref="A236:I236"/>
     <mergeCell ref="A503:I503"/>
     <mergeCell ref="A267:I267"/>
@@ -48679,33 +48771,33 @@
     <mergeCell ref="A309:I309"/>
     <mergeCell ref="A440:I440"/>
     <mergeCell ref="A538:I538"/>
-    <mergeCell ref="A709:I709"/>
     <mergeCell ref="A609:I609"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A637:I637"/>
     <mergeCell ref="A245:I245"/>
+    <mergeCell ref="A711:I711"/>
     <mergeCell ref="A337:I337"/>
     <mergeCell ref="A692:I692"/>
     <mergeCell ref="A403:I403"/>
+    <mergeCell ref="A701:I701"/>
     <mergeCell ref="A142:I142"/>
+    <mergeCell ref="A694:I694"/>
     <mergeCell ref="A532:I532"/>
     <mergeCell ref="A678:I678"/>
-    <mergeCell ref="A674:I674"/>
     <mergeCell ref="A268:I268"/>
     <mergeCell ref="A484:I484"/>
     <mergeCell ref="A624:I624"/>
+    <mergeCell ref="A655:I655"/>
     <mergeCell ref="A493:I493"/>
     <mergeCell ref="A468:I468"/>
     <mergeCell ref="A586:I586"/>
-    <mergeCell ref="A630:I630"/>
     <mergeCell ref="A129:I129"/>
     <mergeCell ref="A298:I298"/>
-    <mergeCell ref="A666:I666"/>
     <mergeCell ref="A194:I194"/>
     <mergeCell ref="A307:I307"/>
     <mergeCell ref="A203:I203"/>
     <mergeCell ref="A116:I116"/>
+    <mergeCell ref="A641:I641"/>
     <mergeCell ref="A131:I131"/>
     <mergeCell ref="A389:I389"/>
     <mergeCell ref="A660:I660"/>
@@ -48733,7 +48825,9 @@
     <mergeCell ref="A271:I271"/>
     <mergeCell ref="A205:I205"/>
     <mergeCell ref="A354:I354"/>
+    <mergeCell ref="A634:I634"/>
     <mergeCell ref="A317:I317"/>
+    <mergeCell ref="A670:I670"/>
     <mergeCell ref="A264:I264"/>
     <mergeCell ref="A273:I273"/>
     <mergeCell ref="A55:I55"/>
@@ -48750,18 +48844,17 @@
     <mergeCell ref="A432:I432"/>
     <mergeCell ref="A525:I525"/>
     <mergeCell ref="A382:I382"/>
+    <mergeCell ref="A680:I680"/>
     <mergeCell ref="A275:I275"/>
     <mergeCell ref="A511:I511"/>
     <mergeCell ref="A132:I132"/>
     <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A644:I644"/>
     <mergeCell ref="A187:I187"/>
     <mergeCell ref="A653:I653"/>
     <mergeCell ref="A221:I221"/>
     <mergeCell ref="A196:I196"/>
     <mergeCell ref="A423:I423"/>
     <mergeCell ref="A174:I174"/>
-    <mergeCell ref="A699:I699"/>
     <mergeCell ref="A223:I223"/>
     <mergeCell ref="A238:I238"/>
     <mergeCell ref="A1:H1"/>
@@ -48769,13 +48862,12 @@
     <mergeCell ref="A213:I213"/>
     <mergeCell ref="A449:I449"/>
     <mergeCell ref="A254:I254"/>
-    <mergeCell ref="A651:I651"/>
     <mergeCell ref="A150:I150"/>
     <mergeCell ref="A315:I315"/>
     <mergeCell ref="A144:I144"/>
     <mergeCell ref="A159:I159"/>
     <mergeCell ref="A513:I513"/>
-    <mergeCell ref="A684:I684"/>
+    <mergeCell ref="A662:I662"/>
     <mergeCell ref="A373:I373"/>
     <mergeCell ref="A134:I134"/>
     <mergeCell ref="A81:I81"/>
@@ -48784,12 +48876,13 @@
     <mergeCell ref="A161:I161"/>
     <mergeCell ref="A541:I541"/>
     <mergeCell ref="A646:I646"/>
+    <mergeCell ref="A686:I686"/>
     <mergeCell ref="A127:I127"/>
     <mergeCell ref="A176:I176"/>
     <mergeCell ref="A114:I114"/>
     <mergeCell ref="A329:I329"/>
     <mergeCell ref="A412:I412"/>
-    <mergeCell ref="A710:I710"/>
+    <mergeCell ref="A648:I648"/>
     <mergeCell ref="A98:I98"/>
     <mergeCell ref="A540:I540"/>
     <mergeCell ref="A396:I396"/>
@@ -48797,6 +48890,7 @@
     <mergeCell ref="A632:I632"/>
     <mergeCell ref="A476:I476"/>
     <mergeCell ref="A88:I88"/>
+    <mergeCell ref="A712:I712"/>
     <mergeCell ref="A346:I346"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -50069,7 +50163,11 @@
       </c>
       <c r="D45" s="61" t="inlineStr">
         <is>
-          <t>Categorii cu cotă redusă sau scutire, dacă societatea are astfel de
+          <t>Luni cu concedii medicale: CAM NU se datorează pe partea suportată
+  din FNUASS (art. 220^5 Cod fiscal), deci rulajul 436 e mai mic decât
+  2,25% din rulajul 421. Diferența trebuie să fie exact 2,25% ×
+  indemnizația din fond
+Categorii cu cotă redusă sau scutire, dacă societatea are astfel de
   salariați — verificat pe D112, nu presupus</t>
         </is>
       </c>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -2114,7 +2114,7 @@
       </c>
       <c r="E7" s="67" t="inlineStr">
         <is>
-          <t>F-422 pas 3: rulajul creditor al lunii = soldul creditor la finalul ei</t>
+          <t>F-422 pas 3: rulajul creditor al lunii = soldul creditor la finalul ei | modul: MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
       <c r="F7" s="67" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="E45" s="22" t="inlineStr">
         <is>
-          <t>Lanțul complet în MOD_SALARII, cu cifre verificate contra statului real din 31.07.2026; F-201/F-208 acoperă ipostaza de cost capitalizat</t>
+          <t>Lanțul complet în MOD_SALARII, cu cifre verificate contra statului real din 31.07.2026; F-201/F-208 acoperă ipostaza de cost capitalizat | modul: MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
       <c r="F45" s="22" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="E67" s="22" t="inlineStr">
         <is>
-          <t>MOD_SALARII acoperă 641 salarii, 642 tichete și 646 CAM; limitările rămase sunt declarate în Reguli_SALARII, tabelul C</t>
+          <t>MOD_SALARII acoperă 641 salarii, 642 tichete și 646 CAM; limitările rămase sunt declarate în Reguli_SALARII, tabelul C | modul: MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
       <c r="F67" s="22" t="inlineStr">
@@ -8553,7 +8553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9217,8 +9217,40 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="33" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="67" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_LUNARA</t>
+        </is>
+      </c>
+      <c r="B34" s="67" t="inlineStr">
+        <is>
+          <t>F-422, F-413</t>
+        </is>
+      </c>
+      <c r="C34" s="67" t="inlineStr">
+        <is>
+          <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
+        </is>
+      </c>
+      <c r="D34" s="67" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+      <c r="E34" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_INCHIDERE_LUNARA, Reguli_INCHIDERE_LUNARA, Jurnale_INCHIDERE_LUNARA, NotaExport_INCHIDERE_LUNARA</t>
+        </is>
+      </c>
+      <c r="F34" s="67" t="inlineStr">
+        <is>
+          <t>Lunar, pe balanța de verificare</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="33" t="inlineStr">
         <is>
           <t>MOD_CAPITALURI nu dublează MOD_INCHIDERE_EX: acela închide clasele 6 și 7 pe 121, acesta repartizează rezultatul obținut (129/1061/1171).</t>
         </is>
@@ -9229,10 +9261,10 @@
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A20:F20"/>
@@ -29364,7 +29396,7 @@
       </c>
       <c r="H68" s="23" t="inlineStr">
         <is>
-          <t>D112, D100 | modul: MOD_SALARII</t>
+          <t>D112, D100 | modul: MOD_SALARII / MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
     </row>
@@ -29724,7 +29756,7 @@
       </c>
       <c r="H77" s="70" t="inlineStr">
         <is>
-          <t>Corelația care deosebește o firmă la zi de una cu restanțe, fără să ceri niciun document în plus: totul e deja în balanță.</t>
+          <t>Corelația care deosebește o firmă la zi de una cu restanțe, fără să ceri niciun document în plus: totul e deja în balanță. | modul: MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
     </row>
@@ -50053,7 +50085,7 @@
       </c>
       <c r="F42" s="61" t="inlineStr">
         <is>
-          <t>F-413, F-416, F-418 | Module_Declarative_Fluxuri.xlsx → MOD_SALARII</t>
+          <t>F-413, F-416, F-418 | Module_Declarative_Fluxuri.xlsx → MOD_SALARII / MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
       <c r="G42" s="61" t="inlineStr">
@@ -50095,7 +50127,7 @@
       </c>
       <c r="F43" s="61" t="inlineStr">
         <is>
-          <t>F-413 | Module_Declarative_Fluxuri.xlsx → MOD_SALARII</t>
+          <t>F-413 | Module_Declarative_Fluxuri.xlsx → MOD_SALARII / MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
       <c r="G43" s="61" t="inlineStr">
@@ -50135,7 +50167,7 @@
       </c>
       <c r="F44" s="61" t="inlineStr">
         <is>
-          <t>F-413 | Module_Declarative_Fluxuri.xlsx → MOD_SALARII</t>
+          <t>F-413 | Module_Declarative_Fluxuri.xlsx → MOD_SALARII / MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
       <c r="G44" s="61" t="inlineStr">
@@ -50180,7 +50212,7 @@
       </c>
       <c r="F45" s="61" t="inlineStr">
         <is>
-          <t>F-413 | Module_Declarative_Fluxuri.xlsx → MOD_SALARII</t>
+          <t>F-413 | Module_Declarative_Fluxuri.xlsx → MOD_SALARII / MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
       <c r="G45" s="61" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1490,7 +1490,7 @@
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>Tier A (~55) — tratate individual, cu analitice justificate rând cu rând</t>
+          <t>Tier A (87, din care 39 cu rând detaliat de analitice) — tratate individual, cu analitice justificate rând cu rând</t>
         </is>
       </c>
     </row>
@@ -1504,14 +1504,14 @@
     <row r="61">
       <c r="A61" s="15" t="inlineStr">
         <is>
-          <t>Tier B (~110) — analitic prin aplicarea unui tipar deja stabilit la Tier A (ex. toate ajustările urmează același model)</t>
+          <t>Tier B (134) — analitic prin aplicarea unui tipar deja stabilit la Tier A (ex. toate ajustările urmează același model)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Tier C (~80) — conturi rar folosite în cabinet (consolidare, fiducie, resurse minerale, clasa 9). Marcate explicit „acoperire minimă”</t>
+          <t>Tier C (36) — conturi rar folosite în cabinet (consolidare, fiducie, resurse minerale, clasa 9). Marcate explicit „acoperire minimă”</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>270+ rânduri, cu 3 coloane noi: Analitice recomandate · Factor · Flux (pas)</t>
+          <t>257 conturi, cu 3 coloane noi: Analitice recomandate · Factor · Flux (pas)</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>81 conturi de serviciu, grupate pe rol</t>
+          <t>80 conturi de serviciu, grupate pe rol</t>
         </is>
       </c>
     </row>
@@ -1888,21 +1888,21 @@
     <row r="117">
       <c r="A117" s="61" t="inlineStr">
         <is>
-          <t>Module_Declarative_Fluxuri.xlsx — 16 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
+          <t>Module_Declarative_Fluxuri.xlsx — 17 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="61" t="inlineStr">
         <is>
-          <t>intrebari-formator.md / .html — cele 21 de întrebări rămase deschise, grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
+          <t>intrebari-formator.md / .html — cele 20 întrebări rămase deschise (din 33: 13 verificate cu temei legal, 9 decizii de cabinet), grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="61" t="inlineStr">
         <is>
-          <t>notite-training-2/3/4 .md și .docx — cele trei documente revizuite, armonizate: aceeași legendă de marcaje, aceleași anexe, aceeași ordine.</t>
+          <t>Cele 5 documente de studiu, în .md, .docx și .html: Capitaluri, credite, leasing și provizioane · Imobilizări · Stocuri, TVA și corelații de balanță · Salarii, contribuții și rețineri · Control, documente și numerar. Titlurile sunt pe subiect contabil, nu pe ziua de training — cauți o regulă pe clasa contului, nu pe data când s-a predat.</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G169"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8333,183 +8333,268 @@
     <row r="143">
       <c r="A143" s="67" t="inlineStr">
         <is>
-          <t>Ilustrativ (sume descriptive)</t>
+          <t>LISTA FLUXURILOR (~38) — structură + status implementare</t>
         </is>
       </c>
       <c r="B143" s="67" t="inlineStr">
         <is>
-          <t>F-50 plafon 1.500 lei/lună; F-51 reluare 7812</t>
+          <t>LISTA FLUXURILOR (68) — structură + status implementare</t>
         </is>
       </c>
       <c r="C143" s="67" t="inlineStr">
         <is>
-          <t>Marcajul PARȚIAL de la 681/781 era corect când sumele erau descriptive. Acum 681 și 781 au cifre reale în F-50 (plafonul de 1.500 lei/lună) și F-51 (reluarea prin 7812), deci nota nu mai descrie realitatea.</t>
+          <t>Titlul catalogului anunța 38 de fluxuri, la trei rânduri deasupra celor 68 pe care le lista. Înlocuirea exista în cod din prima curățare, dar rula numai pe Legendă, niciodată pe foaia Fluxuri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="67" t="inlineStr">
+        <is>
+          <t>81 conturi de serviciu, grupate pe rol</t>
+        </is>
+      </c>
+      <c r="B144" s="67" t="inlineStr">
+        <is>
+          <t>80 conturi de serviciu, grupate pe rol</t>
+        </is>
+      </c>
+      <c r="C144" s="67" t="inlineStr">
+        <is>
+          <t>Foaia „Doar rol în flux” are 80 de conturi. Se numără la build.</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="36" t="inlineStr">
-        <is>
-          <t>6. Titluri și note de secțiune, scoase la reordonare</t>
+      <c r="A145" s="67" t="inlineStr">
+        <is>
+          <t>Tier A (~55) — tratate individual, cu analitice justificate rând cu rând</t>
+        </is>
+      </c>
+      <c r="B145" s="67" t="inlineStr">
+        <is>
+          <t>Tier A (87, din care 39 cu rând detaliat de analitice) — tratate individual, cu analitice justificate rând cu rând</t>
+        </is>
+      </c>
+      <c r="C145" s="67" t="inlineStr">
+        <is>
+          <t>Sunt 87 de conturi clasificate Tier A, din care 39 au rând detaliat în foaia de analitice. Aproximarea „~55” nu era niciuna din cele două.</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="63" t="inlineStr">
-        <is>
-          <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
+      <c r="A146" s="67" t="inlineStr">
+        <is>
+          <t>Tier B (~110) — analitic prin aplicarea unui tipar deja stabilit la Tier A (ex. toate ajustările urmează același model)</t>
+        </is>
+      </c>
+      <c r="B146" s="67" t="inlineStr">
+        <is>
+          <t>Tier B (134) — analitic prin aplicarea unui tipar deja stabilit la Tier A (ex. toate ajustările urmează același model)</t>
+        </is>
+      </c>
+      <c r="C146" s="67" t="inlineStr">
+        <is>
+          <t>Sunt 134.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="67" t="inlineStr">
         <is>
-          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
+          <t>Tier C (~80) — conturi rar folosite în cabinet (consolidare, fiducie, resurse minerale, clasa 9). Marcate explicit „acoperire minimă”</t>
+        </is>
+      </c>
+      <c r="B147" s="67" t="inlineStr">
+        <is>
+          <t>Tier C (36) — conturi rar folosite în cabinet (consolidare, fiducie, resurse minerale, clasa 9). Marcate explicit „acoperire minimă”</t>
+        </is>
+      </c>
+      <c r="C147" s="67" t="inlineStr">
+        <is>
+          <t>Sunt 36. Eroarea nu era de rotunjire, era de peste dublu — și se vedea abia când cele trei tiere s-au numărat: 87 + 134 + 36 = 257, adică fix planul întreg. Aproximările nu însumau nimic.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="67" t="inlineStr">
         <is>
-          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="67" t="inlineStr">
-        <is>
-          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
+          <t>Ilustrativ (sume descriptive)</t>
+        </is>
+      </c>
+      <c r="B148" s="67" t="inlineStr">
+        <is>
+          <t>F-50 plafon 1.500 lei/lună; F-51 reluare 7812</t>
+        </is>
+      </c>
+      <c r="C148" s="67" t="inlineStr">
+        <is>
+          <t>Marcajul PARȚIAL de la 681/781 era corect când sumele erau descriptive. Acum 681 și 781 au cifre reale în F-50 (plafonul de 1.500 lei/lună) și F-51 (reluarea prin 7812), deci nota nu mai descrie realitatea.</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="67" t="inlineStr">
-        <is>
-          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+      <c r="A150" s="36" t="inlineStr">
+        <is>
+          <t>6. Titluri și note de secțiune, scoase la reordonare</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="67" t="inlineStr">
-        <is>
-          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+      <c r="A151" s="63" t="inlineStr">
+        <is>
+          <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="67" t="inlineStr">
         <is>
+          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="67" t="inlineStr">
+        <is>
+          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="67" t="inlineStr">
+        <is>
+          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="67" t="inlineStr">
+        <is>
+          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="67" t="inlineStr">
+        <is>
+          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="67" t="inlineStr">
+        <is>
           <t>Nu sunt liniare. Fiecare pornește dintr-o stare „murdară" sau produce intersecție între două roluri. Acolo apar erorile de cabinet. Valoarea didactică &gt; încă 10 fluxuri liniare.</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="36" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="36" t="inlineStr">
         <is>
           <t>7. Narativul de etape, mutat din Legendă</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="63" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="63" t="inlineStr">
         <is>
           <t>Descria ordinea livrărilor, nu conținutul contabil. Mutat aici verbatim ca Legenda să descrie sistemul, nu istoria lui.</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="4" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
         <is>
           <t>6. LISTA FLUXURILOR (~38, în 3 tranșe) — cele bold sunt „didactice”</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="40" customHeight="1">
-      <c r="A157" s="5" t="inlineStr">
+    <row r="162" ht="40" customHeight="1">
+      <c r="A162" s="5" t="inlineStr">
         <is>
           <t>Tranșa 1 — stocuri și producție (F-01…F-12)</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="12" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="12" t="inlineStr">
         <is>
           <t>aprovizionare intern · prin 32x (tranzit) · intracomunitar cu taxare inversă · obiecte de inventar cu 8035 cap-coadă · producție termopan multi-stadiu (601→331→711→345→vânzare) · deșeuri 346 · servicii în curs 332/712 · diferențe de preț 308 · ajustare depreciere stoc · piese de schimb 3024→371 · stocuri la terți · ambalaje + taxa AFM</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="40" customHeight="1">
-      <c r="A159" s="5" t="inlineStr">
+    <row r="164" ht="40" customHeight="1">
+      <c r="A164" s="5" t="inlineStr">
         <is>
           <t>Tranșa 2 — TVA, comerț, import (F-13…F-25)</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="12" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="12" t="inlineStr">
         <is>
           <t>vânzare en-gros · gestiune amănunt completă cu verificarea ambelor corelații · import prin comisionar (446, taxe vamale + transport în cost) · import cu plată directă în vamă · TVA la încasare pe achiziție și pe vânzare · taxare inversă internă · livrare intracomunitară scutită · export · închiderea lunară de TVA · înregistrări fără document (50% auto, lipsă la inventar) · 408/418 · reduceri 609/709</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="40" customHeight="1">
-      <c r="A161" s="5" t="inlineStr">
+    <row r="166" ht="40" customHeight="1">
+      <c r="A166" s="5" t="inlineStr">
         <is>
           <t>Tranșa 3 — imobilizări, personal, închidere (F-26…F-38)</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="12" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="12" t="inlineStr">
         <is>
           <t>achiziție MF + amortizare · imobilizări în curs · producție în regie proprie (722) · subvenție 475 eliberată pe măsura amortizării · avansuri 471/472 · cedare MF · salarii complet · viramente interne 581 · sumă neidentificată → 473 · avansuri de trezorerie · închiderea exercițiului (121/129/117 + 691/697/4417) · angajamente extrabilanțiere · decontări 481/482</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
         <is>
           <t>PROGRES IMPLEMENTARE</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="39" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="39" t="inlineStr">
         <is>
           <t>ETAPA 0: Arhitectură + skeleton complet (Legendă, Plan, Doar rol, Analitice Tier A, Catalog 38 fluxuri, Matrice).</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="39" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="39" t="inlineStr">
         <is>
           <t>ETAPA 1: 12 fluxuri detaliate.</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="26" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="26" t="inlineStr">
         <is>
           <t>ETAPA 2: Tranșa 1 completă + F-07 + F-28 → 22 fluxuri.</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="48" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="48" t="inlineStr">
         <is>
           <t>ETAPA 3 (FINAL): Tranșa 2 + Tranșa 3 complete. Total 38/38 fluxuri cu pași detaliați. Matrice verde. Workbook gata pentru utilizare cabinet + învățare.</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="26" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="26" t="inlineStr">
         <is>
           <t>Livrat 14.08.2026 — OMFP 1802/2014 actualizat + OMF 981/2024 + cote TVA 21%/11% + SAGA ca reper.</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="65" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="65" t="inlineStr">
         <is>
           <t>ETAPA 4 — EXTINDERE LA TRAININGURILE 2 ȘI 3</t>
         </is>
@@ -8519,29 +8604,29 @@
   <mergeCells count="25">
     <mergeCell ref="A108:F108"/>
     <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A156:G156"/>
-    <mergeCell ref="A145:F145"/>
+    <mergeCell ref="A171:G171"/>
     <mergeCell ref="A165:G165"/>
-    <mergeCell ref="A154:F154"/>
+    <mergeCell ref="A161:G161"/>
+    <mergeCell ref="A170:G170"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A173:G173"/>
     <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A151:F151"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A150:F150"/>
     <mergeCell ref="A167:G167"/>
+    <mergeCell ref="A159:F159"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A166:G166"/>
     <mergeCell ref="A169:G169"/>
-    <mergeCell ref="A162:G162"/>
     <mergeCell ref="A168:G168"/>
-    <mergeCell ref="A155:F155"/>
+    <mergeCell ref="A172:G172"/>
+    <mergeCell ref="A174:G174"/>
     <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A164:G164"/>
     <mergeCell ref="A82:F82"/>
-    <mergeCell ref="A158:G158"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A146:F146"/>
     <mergeCell ref="A163:G163"/>
     <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A160:G160"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27086,7 +27171,7 @@
     <row r="1">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>LISTA FLUXURILOR (~38) — structură + status implementare</t>
+          <t>LISTA FLUXURILOR (68) — structură + status implementare</t>
         </is>
       </c>
     </row>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -3920,7 +3920,7 @@
       </c>
       <c r="E65" s="29" t="inlineStr">
         <is>
-          <t>F-501 581</t>
+          <t>F-501 581 | modul: MOD_INTERMEDIAR</t>
         </is>
       </c>
       <c r="F65" s="29" t="inlineStr">
@@ -5656,7 +5656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8416,185 +8416,250 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="67" t="inlineStr">
-        <is>
-          <t>Ilustrativ (sume descriptive)</t>
-        </is>
-      </c>
-      <c r="B148" s="67" t="inlineStr">
-        <is>
-          <t>F-50 plafon 1.500 lei/lună; F-51 reluare 7812</t>
-        </is>
+      <c r="A148" s="67" t="str">
+        <f>IF(B10=473,"Sold 473 la 31.12 = suspect — clarificare obligatorie","—")</f>
+        <v>—</v>
+      </c>
+      <c r="B148" s="67" t="str">
+        <f>IF(B10="473","Sold 473 la 31.12 = suspect — clarificare obligatorie","—")</f>
+        <v>—</v>
       </c>
       <c r="C148" s="67" t="inlineStr">
         <is>
-          <t>Marcajul PARȚIAL de la 681/781 era corect când sumele erau descriptive. Acum 681 și 781 au cifre reale în F-50 (plafonul de 1.500 lei/lună) și F-51 (reluarea prin 7812), deci nota nu mai descrie realitatea.</t>
+          <t>Defect viu, găsit la portarea lui MOD_INTERMEDIAR. B10 conține TEXTUL „473”, iar Excel nu compară text cu număr: „473”=473 e FALSE, mereu. Cu tipul implicit chiar pe 473, celula afișa „—”. Adică singurul avertisment serios al modulului — soldul de 473 rămas la 31.12, care în notițe e SUSPECT, nu LEGITIM — era cod mort. Acum se compară text cu text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="67">
+        <f>IF(CatalogModule!A14="DA","ACTIV","INACTIV")</f>
+        <v/>
+      </c>
+      <c r="B149" s="67" t="inlineStr">
+        <is>
+          <t>vezi date/module/comun.py:formula_activ</t>
+        </is>
+      </c>
+      <c r="C149" s="67" t="inlineStr">
+        <is>
+          <t>Rândul din catalog era scris în formulă. Mutai un rând și celula citea steagul altui modul, tăcut. Se caută pe codul modulului, prin INDEX/MATCH — vezi `date/module/comun.py:formula_activ`. Intervalul e mărginit ($A$1:$A$200), pentru că motorul de recalcul nu evaluează `INDEX(CatalogModule!A:A, …)` pe coloană întreagă; forma pe coloană întreagă lăsa celula goală în toate cele patru module care o foloseau.</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="36" t="inlineStr">
-        <is>
-          <t>6. Titluri și note de secțiune, scoase la reordonare</t>
+      <c r="A150" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_INTER, Jurnale_INTER, NotaExport_INTER</t>
+        </is>
+      </c>
+      <c r="B150" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_INTERMEDIAR, Reguli_INTERMEDIAR, Jurnale_INTERMEDIAR, NotaExport_INTERMEDIAR</t>
+        </is>
+      </c>
+      <c r="C150" s="67" t="inlineStr">
+        <is>
+          <t>Foile nu se numesc așa. Sunt Declarații_INTERMEDIAR, Reguli_INTERMEDIAR, Jurnale_INTERMEDIAR, NotaExport_INTERMEDIAR — iar `Reguli_` lipsea cu totul din listă, deși modulul o are. O instrucțiune de navigare greșită în foaia al cărei singur rost e navigarea. Se generează acum din cod.</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="63" t="inlineStr">
-        <is>
-          <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
+      <c r="A151" s="67" t="inlineStr">
+        <is>
+          <t>F-23, F-34, F-39</t>
+        </is>
+      </c>
+      <c r="B151" s="67" t="inlineStr">
+        <is>
+          <t>F-23, F-33, F-34</t>
+        </is>
+      </c>
+      <c r="C151" s="67" t="inlineStr">
+        <is>
+          <t>Lista de fluxuri a lui MOD_INTERMEDIAR din `Index module` nu coincidea cu cea din `CatalogModule` („F-23, F-33, F-34”) — două liste scrise de mână despre același modul, divergente. Rămâne una singură, citită din `CATALOG['fluxuri']`. F-39 (F-304, intersecția 32x ↔ 408 la același furnizor) iese: e o stare inițială murdară, pe care tiparul generic deschidere → stingere de aici nu o modelează.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="67" t="inlineStr">
         <is>
-          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="67" t="inlineStr">
-        <is>
-          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
+          <t>Ilustrativ (sume descriptive)</t>
+        </is>
+      </c>
+      <c r="B152" s="67" t="inlineStr">
+        <is>
+          <t>F-50 plafon 1.500 lei/lună; F-51 reluare 7812</t>
+        </is>
+      </c>
+      <c r="C152" s="67" t="inlineStr">
+        <is>
+          <t>Marcajul PARȚIAL de la 681/781 era corect când sumele erau descriptive. Acum 681 și 781 au cifre reale în F-50 (plafonul de 1.500 lei/lună) și F-51 (reluarea prin 7812), deci nota nu mai descrie realitatea.</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="67" t="inlineStr">
-        <is>
-          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
+      <c r="A154" s="36" t="inlineStr">
+        <is>
+          <t>6. Titluri și note de secțiune, scoase la reordonare</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="67" t="inlineStr">
-        <is>
-          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+      <c r="A155" s="63" t="inlineStr">
+        <is>
+          <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="67" t="inlineStr">
         <is>
-          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="67" t="inlineStr">
         <is>
+          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="67" t="inlineStr">
+        <is>
+          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="67" t="inlineStr">
+        <is>
+          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="67" t="inlineStr">
+        <is>
+          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="67" t="inlineStr">
+        <is>
           <t>Nu sunt liniare. Fiecare pornește dintr-o stare „murdară" sau produce intersecție între două roluri. Acolo apar erorile de cabinet. Valoarea didactică &gt; încă 10 fluxuri liniare.</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="36" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="36" t="inlineStr">
         <is>
           <t>7. Narativul de etape, mutat din Legendă</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="63" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="63" t="inlineStr">
         <is>
           <t>Descria ordinea livrărilor, nu conținutul contabil. Mutat aici verbatim ca Legenda să descrie sistemul, nu istoria lui.</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="4" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
         <is>
           <t>6. LISTA FLUXURILOR (~38, în 3 tranșe) — cele bold sunt „didactice”</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="40" customHeight="1">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>Tranșa 1 — stocuri și producție (F-01…F-12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="12" t="inlineStr">
-        <is>
-          <t>aprovizionare intern · prin 32x (tranzit) · intracomunitar cu taxare inversă · obiecte de inventar cu 8035 cap-coadă · producție termopan multi-stadiu (601→331→711→345→vânzare) · deșeuri 346 · servicii în curs 332/712 · diferențe de preț 308 · ajustare depreciere stoc · piese de schimb 3024→371 · stocuri la terți · ambalaje + taxa AFM</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="40" customHeight="1">
-      <c r="A164" s="5" t="inlineStr">
-        <is>
-          <t>Tranșa 2 — TVA, comerț, import (F-13…F-25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="12" t="inlineStr">
-        <is>
-          <t>vânzare en-gros · gestiune amănunt completă cu verificarea ambelor corelații · import prin comisionar (446, taxe vamale + transport în cost) · import cu plată directă în vamă · TVA la încasare pe achiziție și pe vânzare · taxare inversă internă · livrare intracomunitară scutită · export · închiderea lunară de TVA · înregistrări fără document (50% auto, lipsă la inventar) · 408/418 · reduceri 609/709</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>Tranșa 3 — imobilizări, personal, închidere (F-26…F-38)</t>
+          <t>Tranșa 1 — stocuri și producție (F-01…F-12)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="12" t="inlineStr">
         <is>
+          <t>aprovizionare intern · prin 32x (tranzit) · intracomunitar cu taxare inversă · obiecte de inventar cu 8035 cap-coadă · producție termopan multi-stadiu (601→331→711→345→vânzare) · deșeuri 346 · servicii în curs 332/712 · diferențe de preț 308 · ajustare depreciere stoc · piese de schimb 3024→371 · stocuri la terți · ambalaje + taxa AFM</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="40" customHeight="1">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>Tranșa 2 — TVA, comerț, import (F-13…F-25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="12" t="inlineStr">
+        <is>
+          <t>vânzare en-gros · gestiune amănunt completă cu verificarea ambelor corelații · import prin comisionar (446, taxe vamale + transport în cost) · import cu plată directă în vamă · TVA la încasare pe achiziție și pe vânzare · taxare inversă internă · livrare intracomunitară scutită · export · închiderea lunară de TVA · înregistrări fără document (50% auto, lipsă la inventar) · 408/418 · reduceri 609/709</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="40" customHeight="1">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>Tranșa 3 — imobilizări, personal, închidere (F-26…F-38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="12" t="inlineStr">
+        <is>
           <t>achiziție MF + amortizare · imobilizări în curs · producție în regie proprie (722) · subvenție 475 eliberată pe măsura amortizării · avansuri 471/472 · cedare MF · salarii complet · viramente interne 581 · sumă neidentificată → 473 · avansuri de trezorerie · închiderea exercițiului (121/129/117 + 691/697/4417) · angajamente extrabilanțiere · decontări 481/482</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="3" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
         <is>
           <t>PROGRES IMPLEMENTARE</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="39" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="39" t="inlineStr">
         <is>
           <t>ETAPA 0: Arhitectură + skeleton complet (Legendă, Plan, Doar rol, Analitice Tier A, Catalog 38 fluxuri, Matrice).</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="39" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="39" t="inlineStr">
         <is>
           <t>ETAPA 1: 12 fluxuri detaliate.</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="26" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="26" t="inlineStr">
         <is>
           <t>ETAPA 2: Tranșa 1 completă + F-07 + F-28 → 22 fluxuri.</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="48" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="48" t="inlineStr">
         <is>
           <t>ETAPA 3 (FINAL): Tranșa 2 + Tranșa 3 complete. Total 38/38 fluxuri cu pași detaliați. Matrice verde. Workbook gata pentru utilizare cabinet + învățare.</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="26" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="26" t="inlineStr">
         <is>
           <t>Livrat 14.08.2026 — OMFP 1802/2014 actualizat + OMF 981/2024 + cote TVA 21%/11% + SAGA ca reper.</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="65" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="65" t="inlineStr">
         <is>
           <t>ETAPA 4 — EXTINDERE LA TRAININGURILE 2 ȘI 3</t>
         </is>
@@ -8603,30 +8668,30 @@
   </sheetData>
   <mergeCells count="25">
     <mergeCell ref="A108:F108"/>
+    <mergeCell ref="A164:F164"/>
     <mergeCell ref="A89:F89"/>
     <mergeCell ref="A171:G171"/>
     <mergeCell ref="A165:G165"/>
-    <mergeCell ref="A161:G161"/>
-    <mergeCell ref="A170:G170"/>
+    <mergeCell ref="A163:F163"/>
+    <mergeCell ref="A154:F154"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A160:F160"/>
     <mergeCell ref="A173:G173"/>
     <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="A176:G176"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A150:F150"/>
     <mergeCell ref="A167:G167"/>
-    <mergeCell ref="A159:F159"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A178:G178"/>
     <mergeCell ref="A169:G169"/>
-    <mergeCell ref="A168:G168"/>
+    <mergeCell ref="A155:F155"/>
     <mergeCell ref="A172:G172"/>
+    <mergeCell ref="A177:G177"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="A82:F82"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A163:G163"/>
     <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A175:G175"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8774,7 +8839,7 @@
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>F-408, F-411, F-304</t>
+          <t>F-408, F-501, F-411</t>
         </is>
       </c>
       <c r="C8" s="29" t="inlineStr">
@@ -8789,7 +8854,7 @@
       </c>
       <c r="E8" s="29" t="inlineStr">
         <is>
-          <t>Declarații_INTER, Jurnale_INTER, NotaExport_INTER</t>
+          <t>Declarații_INTERMEDIAR, Reguli_INTERMEDIAR, Jurnale_INTERMEDIAR, NotaExport_INTERMEDIAR</t>
         </is>
       </c>
       <c r="F8" s="29" t="inlineStr">
@@ -29888,7 +29953,7 @@
       </c>
       <c r="H79" s="29" t="inlineStr">
         <is>
-          <t>Pas revelator: 581 evită dublă numărare până la confirmare</t>
+          <t>Pas revelator: 581 evită dublă numărare până la confirmare | modul: MOD_INTERMEDIAR</t>
         </is>
       </c>
     </row>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -5656,7 +5656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G178"/>
+  <dimension ref="A1:G183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8481,185 +8481,268 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="67" t="inlineStr">
-        <is>
-          <t>Ilustrativ (sume descriptive)</t>
-        </is>
+      <c r="A152" s="67">
+        <f>IF(CatalogModule!A6="DA","ACTIV — jurnalele se generează","INACTIV — jurnalele rămân goale")</f>
+        <v/>
       </c>
       <c r="B152" s="67" t="inlineStr">
         <is>
-          <t>F-50 plafon 1.500 lei/lună; F-51 reluare 7812</t>
+          <t>vezi date/module/comun.py:formula_activ</t>
         </is>
       </c>
       <c r="C152" s="67" t="inlineStr">
         <is>
-          <t>Marcajul PARȚIAL de la 681/781 era corect când sumele erau descriptive. Acum 681 și 781 au cifre reale în F-50 (plafonul de 1.500 lei/lună) și F-51 (reluarea prin 7812), deci nota nu mai descrie realitatea.</t>
+          <t>Același rând absolut, la MOD_INCHIDERE_TVA. Vezi motivul de la A14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_TVA, Jurnale_TVA, NotaExport_TVA</t>
+        </is>
+      </c>
+      <c r="B153" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_INCHIDERE_TVA, Reguli_INCHIDERE_TVA, Jurnale_INCHIDERE_TVA, NotaExport_INCHIDERE_TVA</t>
+        </is>
+      </c>
+      <c r="C153" s="67" t="inlineStr">
+        <is>
+          <t>Foile se numesc Declarații_INCHIDERE_TVA ș.a.m.d., iar Reguli_ lipsea din listă. Se generează acum din codul modulului.</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="36" t="inlineStr">
-        <is>
-          <t>6. Titluri și note de secțiune, scoase la reordonare</t>
+      <c r="A154" s="67">
+        <f>IF(CatalogModule!A7="DA","ACTIV","INACTIV")</f>
+        <v/>
+      </c>
+      <c r="B154" s="67" t="inlineStr">
+        <is>
+          <t>vezi date/module/comun.py:formula_activ</t>
+        </is>
+      </c>
+      <c r="C154" s="67" t="inlineStr">
+        <is>
+          <t>Același rând absolut, la MOD_APROV_TRANZIT. Vezi motivul de la A14.</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="63" t="inlineStr">
-        <is>
-          <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
+      <c r="A155" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_APROV, Jurnale_APROV, NotaExport_APROV</t>
+        </is>
+      </c>
+      <c r="B155" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_APROV_TRANZIT, Reguli_APROV_TRANZIT, Jurnale_APROV_TRANZIT, NotaExport_APROV_TRANZIT</t>
+        </is>
+      </c>
+      <c r="C155" s="67" t="inlineStr">
+        <is>
+          <t>Foile se numesc Declarații_APROV_TRANZIT ș.a.m.d., iar Reguli_ lipsea din listă. Se generează acum din codul modulului.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="67" t="inlineStr">
         <is>
-          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
+          <t>F-02 (+408 simetric)</t>
+        </is>
+      </c>
+      <c r="B156" s="67" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="C156" s="67" t="inlineStr">
+        <is>
+          <t>A doua divergență Index ↔ Catalog: `Index module` scria „F-302, F-304”, `CatalogModule` scria „F-302 (+408 simetric)” — o paranteză în proză într-un câmp pe care poarta 21 îl citește ca listă de ID-uri. Rămâne F-302 curat; cazul simetric pe 408 e MOD_INTERMEDIAR și scrie asta în Tabelul B al Regulilor, unde se și caută.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="67" t="inlineStr">
         <is>
-          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="67" t="inlineStr">
-        <is>
-          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
+          <t>Ilustrativ (sume descriptive)</t>
+        </is>
+      </c>
+      <c r="B157" s="67" t="inlineStr">
+        <is>
+          <t>F-50 plafon 1.500 lei/lună; F-51 reluare 7812</t>
+        </is>
+      </c>
+      <c r="C157" s="67" t="inlineStr">
+        <is>
+          <t>Marcajul PARȚIAL de la 681/781 era corect când sumele erau descriptive. Acum 681 și 781 au cifre reale în F-50 (plafonul de 1.500 lei/lună) și F-51 (reluarea prin 7812), deci nota nu mai descrie realitatea.</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="67" t="inlineStr">
-        <is>
-          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+      <c r="A159" s="36" t="inlineStr">
+        <is>
+          <t>6. Titluri și note de secțiune, scoase la reordonare</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="67" t="inlineStr">
-        <is>
-          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+      <c r="A160" s="63" t="inlineStr">
+        <is>
+          <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="67" t="inlineStr">
         <is>
+          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="67" t="inlineStr">
+        <is>
+          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="67" t="inlineStr">
+        <is>
+          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="67" t="inlineStr">
+        <is>
+          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="67" t="inlineStr">
+        <is>
+          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="67" t="inlineStr">
+        <is>
           <t>Nu sunt liniare. Fiecare pornește dintr-o stare „murdară" sau produce intersecție între două roluri. Acolo apar erorile de cabinet. Valoarea didactică &gt; încă 10 fluxuri liniare.</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="36" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="36" t="inlineStr">
         <is>
           <t>7. Narativul de etape, mutat din Legendă</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="63" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="63" t="inlineStr">
         <is>
           <t>Descria ordinea livrărilor, nu conținutul contabil. Mutat aici verbatim ca Legenda să descrie sistemul, nu istoria lui.</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="4" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
         <is>
           <t>6. LISTA FLUXURILOR (~38, în 3 tranșe) — cele bold sunt „didactice”</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="40" customHeight="1">
-      <c r="A166" s="5" t="inlineStr">
+    <row r="171" ht="40" customHeight="1">
+      <c r="A171" s="5" t="inlineStr">
         <is>
           <t>Tranșa 1 — stocuri și producție (F-01…F-12)</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="12" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="12" t="inlineStr">
         <is>
           <t>aprovizionare intern · prin 32x (tranzit) · intracomunitar cu taxare inversă · obiecte de inventar cu 8035 cap-coadă · producție termopan multi-stadiu (601→331→711→345→vânzare) · deșeuri 346 · servicii în curs 332/712 · diferențe de preț 308 · ajustare depreciere stoc · piese de schimb 3024→371 · stocuri la terți · ambalaje + taxa AFM</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="40" customHeight="1">
-      <c r="A168" s="5" t="inlineStr">
+    <row r="173" ht="40" customHeight="1">
+      <c r="A173" s="5" t="inlineStr">
         <is>
           <t>Tranșa 2 — TVA, comerț, import (F-13…F-25)</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="12" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="12" t="inlineStr">
         <is>
           <t>vânzare en-gros · gestiune amănunt completă cu verificarea ambelor corelații · import prin comisionar (446, taxe vamale + transport în cost) · import cu plată directă în vamă · TVA la încasare pe achiziție și pe vânzare · taxare inversă internă · livrare intracomunitară scutită · export · închiderea lunară de TVA · înregistrări fără document (50% auto, lipsă la inventar) · 408/418 · reduceri 609/709</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="40" customHeight="1">
-      <c r="A170" s="5" t="inlineStr">
+    <row r="175" ht="40" customHeight="1">
+      <c r="A175" s="5" t="inlineStr">
         <is>
           <t>Tranșa 3 — imobilizări, personal, închidere (F-26…F-38)</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="12" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="12" t="inlineStr">
         <is>
           <t>achiziție MF + amortizare · imobilizări în curs · producție în regie proprie (722) · subvenție 475 eliberată pe măsura amortizării · avansuri 471/472 · cedare MF · salarii complet · viramente interne 581 · sumă neidentificată → 473 · avansuri de trezorerie · închiderea exercițiului (121/129/117 + 691/697/4417) · angajamente extrabilanțiere · decontări 481/482</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="3" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
         <is>
           <t>PROGRES IMPLEMENTARE</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="39" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="39" t="inlineStr">
         <is>
           <t>ETAPA 0: Arhitectură + skeleton complet (Legendă, Plan, Doar rol, Analitice Tier A, Catalog 38 fluxuri, Matrice).</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="39" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="39" t="inlineStr">
         <is>
           <t>ETAPA 1: 12 fluxuri detaliate.</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="26" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="26" t="inlineStr">
         <is>
           <t>ETAPA 2: Tranșa 1 completă + F-07 + F-28 → 22 fluxuri.</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="48" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="48" t="inlineStr">
         <is>
           <t>ETAPA 3 (FINAL): Tranșa 2 + Tranșa 3 complete. Total 38/38 fluxuri cu pași detaliați. Matrice verde. Workbook gata pentru utilizare cabinet + învățare.</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="26" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="26" t="inlineStr">
         <is>
           <t>Livrat 14.08.2026 — OMFP 1802/2014 actualizat + OMF 981/2024 + cote TVA 21%/11% + SAGA ca reper.</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="65" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="65" t="inlineStr">
         <is>
           <t>ETAPA 4 — EXTINDERE LA TRAININGURILE 2 ȘI 3</t>
         </is>
@@ -8667,31 +8750,31 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A181:G181"/>
     <mergeCell ref="A108:F108"/>
-    <mergeCell ref="A164:F164"/>
     <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A171:G171"/>
-    <mergeCell ref="A165:G165"/>
-    <mergeCell ref="A163:F163"/>
-    <mergeCell ref="A154:F154"/>
+    <mergeCell ref="A180:G180"/>
+    <mergeCell ref="A170:G170"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A173:G173"/>
+    <mergeCell ref="A160:F160"/>
     <mergeCell ref="A76:F76"/>
     <mergeCell ref="A176:G176"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A167:G167"/>
+    <mergeCell ref="A159:F159"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A182:G182"/>
     <mergeCell ref="A178:G178"/>
-    <mergeCell ref="A169:G169"/>
-    <mergeCell ref="A155:F155"/>
     <mergeCell ref="A172:G172"/>
+    <mergeCell ref="A183:G183"/>
     <mergeCell ref="A177:G177"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A168:F168"/>
     <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A175:G175"/>
+    <mergeCell ref="A179:G179"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8790,7 +8873,7 @@
       </c>
       <c r="E6" s="29" t="inlineStr">
         <is>
-          <t>Declarații_TVA, Jurnale_TVA, NotaExport_TVA</t>
+          <t>Declarații_INCHIDERE_TVA, Reguli_INCHIDERE_TVA, Jurnale_INCHIDERE_TVA, NotaExport_INCHIDERE_TVA</t>
         </is>
       </c>
       <c r="F6" s="29" t="inlineStr">
@@ -8807,7 +8890,7 @@
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>F-302, F-304</t>
+          <t>F-302</t>
         </is>
       </c>
       <c r="C7" s="29" t="inlineStr">
@@ -8822,7 +8905,7 @@
       </c>
       <c r="E7" s="29" t="inlineStr">
         <is>
-          <t>Declarații_APROV, Jurnale_APROV, NotaExport_APROV</t>
+          <t>Declarații_APROV_TRANZIT, Reguli_APROV_TRANZIT, Jurnale_APROV_TRANZIT, NotaExport_APROV_TRANZIT</t>
         </is>
       </c>
       <c r="F7" s="29" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -5656,7 +5656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G183"/>
+  <dimension ref="A1:G187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8564,185 +8564,252 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="67" t="inlineStr">
-        <is>
-          <t>Ilustrativ (sume descriptive)</t>
-        </is>
+      <c r="A157" s="67">
+        <f>IF(CatalogModule!A13="DA","ACTIV","INACTIV")</f>
+        <v/>
       </c>
       <c r="B157" s="67" t="inlineStr">
         <is>
-          <t>F-50 plafon 1.500 lei/lună; F-51 reluare 7812</t>
+          <t>vezi date/module/comun.py:formula_activ</t>
         </is>
       </c>
       <c r="C157" s="67" t="inlineStr">
         <is>
-          <t>Marcajul PARȚIAL de la 681/781 era corect când sumele erau descriptive. Acum 681 și 781 au cifre reale în F-50 (plafonul de 1.500 lei/lună) și F-51 (reluarea prin 7812), deci nota nu mai descrie realitatea.</t>
+          <t>Același rând absolut, la MOD_INCHIDERE_EX. Vezi motivul de la A14. Cu asta se termină cele patru; nicio foaie de modul nu mai citește catalogul pe rând, deci reordonarea lui devine sigură.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_EX, Jurnale_EX, NotaExport_EX</t>
+        </is>
+      </c>
+      <c r="B158" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_INCHIDERE_EX, Reguli_INCHIDERE_EX, Jurnale_INCHIDERE_EX, NotaExport_INCHIDERE_EX</t>
+        </is>
+      </c>
+      <c r="C158" s="67" t="inlineStr">
+        <is>
+          <t>Foile se numesc Declarații_INCHIDERE_EX ș.a.m.d., iar Reguli_ lipsea din listă. Se generează acum din codul modulului.</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="36" t="inlineStr">
-        <is>
-          <t>6. Titluri și note de secțiune, scoase la reordonare</t>
+      <c r="A159" s="67" t="inlineStr">
+        <is>
+          <t>B1 Închidere 6xx; B2 Închidere 7xx; B3 Impozit; B4 Repartizare 129; B5 Report 117</t>
+        </is>
+      </c>
+      <c r="B159" s="67" t="inlineStr">
+        <is>
+          <t>B1 Închidere 6xx; B2 Închidere 7xx; B3 Impozit; B4 Report 117</t>
+        </is>
+      </c>
+      <c r="C159" s="67" t="inlineStr">
+        <is>
+          <t>Catalogul anunța cinci blocuri; jurnalele au patru. Blocul de repartizare nu există și n-a existat niciodată: câmpul „Repartizare la rezerve / dividende” se scade din rezultatul reportat, dar nicio înregistrare nu mută suma nicăieri. Cu valoarea implicită 0 nu se vede; pusă pe 5.000, nota ar ieși cu 5.000 de lei care dispar. Lista spune acum ce emite modulul. Cine repartizează efectiv are MOD_CAPITALURI, construit pentru asta (rezervă legală, dividende, 1171).</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="63" t="inlineStr">
-        <is>
-          <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
+      <c r="A160" s="67" t="inlineStr">
+        <is>
+          <t>Închidere cls.6/7 pe 121; 711 cu PN</t>
+        </is>
+      </c>
+      <c r="B160" s="67" t="inlineStr">
+        <is>
+          <t>Închidere cls.6/7 pe 121; impozit; report 117</t>
+        </is>
+      </c>
+      <c r="C160" s="67" t="inlineStr">
+        <is>
+          <t>A patra și ultima divergență Index ↔ Catalog. `Index module` dădea MOD_INCHIDERE_EX drept acoperind și F-314 („711 cu PN”), `CatalogModule` dădea doar F-104. Citit din foile reale, catalogul avea dreptate: modulul închide totaluri de clasă 6 și 7 și nu atinge 711 nicăieri. Producția neterminată la granița de exercițiu e MOD_NEUTRALIZARE.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="67" t="inlineStr">
         <is>
-          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="67" t="inlineStr">
-        <is>
-          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
+          <t>Ilustrativ (sume descriptive)</t>
+        </is>
+      </c>
+      <c r="B161" s="67" t="inlineStr">
+        <is>
+          <t>F-50 plafon 1.500 lei/lună; F-51 reluare 7812</t>
+        </is>
+      </c>
+      <c r="C161" s="67" t="inlineStr">
+        <is>
+          <t>Marcajul PARȚIAL de la 681/781 era corect când sumele erau descriptive. Acum 681 și 781 au cifre reale în F-50 (plafonul de 1.500 lei/lună) și F-51 (reluarea prin 7812), deci nota nu mai descrie realitatea.</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="67" t="inlineStr">
-        <is>
-          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
+      <c r="A163" s="36" t="inlineStr">
+        <is>
+          <t>6. Titluri și note de secțiune, scoase la reordonare</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="67" t="inlineStr">
-        <is>
-          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+      <c r="A164" s="63" t="inlineStr">
+        <is>
+          <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="67" t="inlineStr">
         <is>
-          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="67" t="inlineStr">
         <is>
+          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="67" t="inlineStr">
+        <is>
+          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="67" t="inlineStr">
+        <is>
+          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="67" t="inlineStr">
+        <is>
+          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="67" t="inlineStr">
+        <is>
           <t>Nu sunt liniare. Fiecare pornește dintr-o stare „murdară" sau produce intersecție între două roluri. Acolo apar erorile de cabinet. Valoarea didactică &gt; încă 10 fluxuri liniare.</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="36" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="36" t="inlineStr">
         <is>
           <t>7. Narativul de etape, mutat din Legendă</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="63" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="63" t="inlineStr">
         <is>
           <t>Descria ordinea livrărilor, nu conținutul contabil. Mutat aici verbatim ca Legenda să descrie sistemul, nu istoria lui.</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="4" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
         <is>
           <t>6. LISTA FLUXURILOR (~38, în 3 tranșe) — cele bold sunt „didactice”</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="40" customHeight="1">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t>Tranșa 1 — stocuri și producție (F-01…F-12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="12" t="inlineStr">
-        <is>
-          <t>aprovizionare intern · prin 32x (tranzit) · intracomunitar cu taxare inversă · obiecte de inventar cu 8035 cap-coadă · producție termopan multi-stadiu (601→331→711→345→vânzare) · deșeuri 346 · servicii în curs 332/712 · diferențe de preț 308 · ajustare depreciere stoc · piese de schimb 3024→371 · stocuri la terți · ambalaje + taxa AFM</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="40" customHeight="1">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>Tranșa 2 — TVA, comerț, import (F-13…F-25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="12" t="inlineStr">
-        <is>
-          <t>vânzare en-gros · gestiune amănunt completă cu verificarea ambelor corelații · import prin comisionar (446, taxe vamale + transport în cost) · import cu plată directă în vamă · TVA la încasare pe achiziție și pe vânzare · taxare inversă internă · livrare intracomunitară scutită · export · închiderea lunară de TVA · înregistrări fără document (50% auto, lipsă la inventar) · 408/418 · reduceri 609/709</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>Tranșa 3 — imobilizări, personal, închidere (F-26…F-38)</t>
+          <t>Tranșa 1 — stocuri și producție (F-01…F-12)</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
         <is>
+          <t>aprovizionare intern · prin 32x (tranzit) · intracomunitar cu taxare inversă · obiecte de inventar cu 8035 cap-coadă · producție termopan multi-stadiu (601→331→711→345→vânzare) · deșeuri 346 · servicii în curs 332/712 · diferențe de preț 308 · ajustare depreciere stoc · piese de schimb 3024→371 · stocuri la terți · ambalaje + taxa AFM</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="40" customHeight="1">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>Tranșa 2 — TVA, comerț, import (F-13…F-25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="12" t="inlineStr">
+        <is>
+          <t>vânzare en-gros · gestiune amănunt completă cu verificarea ambelor corelații · import prin comisionar (446, taxe vamale + transport în cost) · import cu plată directă în vamă · TVA la încasare pe achiziție și pe vânzare · taxare inversă internă · livrare intracomunitară scutită · export · închiderea lunară de TVA · înregistrări fără document (50% auto, lipsă la inventar) · 408/418 · reduceri 609/709</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="40" customHeight="1">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>Tranșa 3 — imobilizări, personal, închidere (F-26…F-38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="12" t="inlineStr">
+        <is>
           <t>achiziție MF + amortizare · imobilizări în curs · producție în regie proprie (722) · subvenție 475 eliberată pe măsura amortizării · avansuri 471/472 · cedare MF · salarii complet · viramente interne 581 · sumă neidentificată → 473 · avansuri de trezorerie · închiderea exercițiului (121/129/117 + 691/697/4417) · angajamente extrabilanțiere · decontări 481/482</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="3" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t>PROGRES IMPLEMENTARE</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="39" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="39" t="inlineStr">
         <is>
           <t>ETAPA 0: Arhitectură + skeleton complet (Legendă, Plan, Doar rol, Analitice Tier A, Catalog 38 fluxuri, Matrice).</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="39" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="39" t="inlineStr">
         <is>
           <t>ETAPA 1: 12 fluxuri detaliate.</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="26" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="26" t="inlineStr">
         <is>
           <t>ETAPA 2: Tranșa 1 completă + F-07 + F-28 → 22 fluxuri.</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="48" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="48" t="inlineStr">
         <is>
           <t>ETAPA 3 (FINAL): Tranșa 2 + Tranșa 3 complete. Total 38/38 fluxuri cu pași detaliați. Matrice verde. Workbook gata pentru utilizare cabinet + învățare.</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="26" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="26" t="inlineStr">
         <is>
           <t>Livrat 14.08.2026 — OMFP 1802/2014 actualizat + OMF 981/2024 + cote TVA 21%/11% + SAGA ca reper.</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="65" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="65" t="inlineStr">
         <is>
           <t>ETAPA 4 — EXTINDERE LA TRAININGURILE 2 ȘI 3</t>
         </is>
@@ -8750,31 +8817,31 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A172:F172"/>
+    <mergeCell ref="A185:G185"/>
     <mergeCell ref="A181:G181"/>
     <mergeCell ref="A108:F108"/>
+    <mergeCell ref="A164:F164"/>
+    <mergeCell ref="A184:G184"/>
     <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A163:F163"/>
     <mergeCell ref="A180:G180"/>
-    <mergeCell ref="A170:G170"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A160:F160"/>
     <mergeCell ref="A76:F76"/>
     <mergeCell ref="A176:G176"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A186:G186"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A182:G182"/>
     <mergeCell ref="A178:G178"/>
-    <mergeCell ref="A172:G172"/>
+    <mergeCell ref="A173:F173"/>
+    <mergeCell ref="A187:G187"/>
     <mergeCell ref="A183:G183"/>
-    <mergeCell ref="A177:G177"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="A82:F82"/>
-    <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A168:F168"/>
     <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A179:G179"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8954,12 +9021,12 @@
       </c>
       <c r="B9" s="29" t="inlineStr">
         <is>
-          <t>F-104, F-314</t>
+          <t>F-104</t>
         </is>
       </c>
       <c r="C9" s="29" t="inlineStr">
         <is>
-          <t>Închidere cls.6/7 pe 121; 711 cu PN</t>
+          <t>Închidere cls.6/7 pe 121; impozit; report 117</t>
         </is>
       </c>
       <c r="D9" s="29" t="inlineStr">
@@ -8969,7 +9036,7 @@
       </c>
       <c r="E9" s="29" t="inlineStr">
         <is>
-          <t>Declarații_EX, Jurnale_EX, NotaExport_EX</t>
+          <t>Declarații_INCHIDERE_EX, Reguli_INCHIDERE_EX, Jurnale_INCHIDERE_EX, NotaExport_INCHIDERE_EX</t>
         </is>
       </c>
       <c r="F9" s="29" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -5656,7 +5656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G187"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8633,183 +8633,200 @@
     <row r="161">
       <c r="A161" s="67" t="inlineStr">
         <is>
+          <t>Declarații_TVA_INC, Jurnale_TVA_INC, NotaExport_TVA_INC</t>
+        </is>
+      </c>
+      <c r="B161" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_TVA_INC, Reguli_TVA_INC, Jurnale_TVA_INC, NotaExport_TVA_INC</t>
+        </is>
+      </c>
+      <c r="C161" s="67" t="inlineStr">
+        <is>
+          <t>Singurul modul unde `Index module` numea corect foile — dar tot îi lipsea Reguli_, ca la toate celelalte. Se generează acum din cod. Sufixul foilor (TVA_INC, nu TVA_INCASARE) se declară în CATALOG['sufix']: redenumirea foilor ca să se potrivească cu codul ar rupe orice referință existentă, pentru un simplu câștig de simetrie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="67" t="inlineStr">
+        <is>
           <t>Ilustrativ (sume descriptive)</t>
         </is>
       </c>
-      <c r="B161" s="67" t="inlineStr">
+      <c r="B162" s="67" t="inlineStr">
         <is>
           <t>F-50 plafon 1.500 lei/lună; F-51 reluare 7812</t>
         </is>
       </c>
-      <c r="C161" s="67" t="inlineStr">
+      <c r="C162" s="67" t="inlineStr">
         <is>
           <t>Marcajul PARȚIAL de la 681/781 era corect când sumele erau descriptive. Acum 681 și 781 au cifre reale în F-50 (plafonul de 1.500 lei/lună) și F-51 (reluarea prin 7812), deci nota nu mai descrie realitatea.</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="36" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="36" t="inlineStr">
         <is>
           <t>6. Titluri și note de secțiune, scoase la reordonare</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="63" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="63" t="inlineStr">
         <is>
           <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="67" t="inlineStr">
-        <is>
-          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="67" t="inlineStr">
         <is>
-          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
+          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="67" t="inlineStr">
         <is>
-          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
+          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="67" t="inlineStr">
         <is>
-          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="67" t="inlineStr">
         <is>
-          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="67" t="inlineStr">
         <is>
+          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="67" t="inlineStr">
+        <is>
           <t>Nu sunt liniare. Fiecare pornește dintr-o stare „murdară" sau produce intersecție între două roluri. Acolo apar erorile de cabinet. Valoarea didactică &gt; încă 10 fluxuri liniare.</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="36" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="36" t="inlineStr">
         <is>
           <t>7. Narativul de etape, mutat din Legendă</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="63" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="63" t="inlineStr">
         <is>
           <t>Descria ordinea livrărilor, nu conținutul contabil. Mutat aici verbatim ca Legenda să descrie sistemul, nu istoria lui.</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="4" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
         <is>
           <t>6. LISTA FLUXURILOR (~38, în 3 tranșe) — cele bold sunt „didactice”</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="40" customHeight="1">
-      <c r="A175" s="5" t="inlineStr">
+    <row r="176" ht="40" customHeight="1">
+      <c r="A176" s="5" t="inlineStr">
         <is>
           <t>Tranșa 1 — stocuri și producție (F-01…F-12)</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="12" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="12" t="inlineStr">
         <is>
           <t>aprovizionare intern · prin 32x (tranzit) · intracomunitar cu taxare inversă · obiecte de inventar cu 8035 cap-coadă · producție termopan multi-stadiu (601→331→711→345→vânzare) · deșeuri 346 · servicii în curs 332/712 · diferențe de preț 308 · ajustare depreciere stoc · piese de schimb 3024→371 · stocuri la terți · ambalaje + taxa AFM</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="40" customHeight="1">
-      <c r="A177" s="5" t="inlineStr">
+    <row r="178" ht="40" customHeight="1">
+      <c r="A178" s="5" t="inlineStr">
         <is>
           <t>Tranșa 2 — TVA, comerț, import (F-13…F-25)</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="12" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="12" t="inlineStr">
         <is>
           <t>vânzare en-gros · gestiune amănunt completă cu verificarea ambelor corelații · import prin comisionar (446, taxe vamale + transport în cost) · import cu plată directă în vamă · TVA la încasare pe achiziție și pe vânzare · taxare inversă internă · livrare intracomunitară scutită · export · închiderea lunară de TVA · înregistrări fără document (50% auto, lipsă la inventar) · 408/418 · reduceri 609/709</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="40" customHeight="1">
-      <c r="A179" s="5" t="inlineStr">
+    <row r="180" ht="40" customHeight="1">
+      <c r="A180" s="5" t="inlineStr">
         <is>
           <t>Tranșa 3 — imobilizări, personal, închidere (F-26…F-38)</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="12" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="12" t="inlineStr">
         <is>
           <t>achiziție MF + amortizare · imobilizări în curs · producție în regie proprie (722) · subvenție 475 eliberată pe măsura amortizării · avansuri 471/472 · cedare MF · salarii complet · viramente interne 581 · sumă neidentificată → 473 · avansuri de trezorerie · închiderea exercițiului (121/129/117 + 691/697/4417) · angajamente extrabilanțiere · decontări 481/482</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="3" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
         <is>
           <t>PROGRES IMPLEMENTARE</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="39" t="inlineStr">
-        <is>
-          <t>ETAPA 0: Arhitectură + skeleton complet (Legendă, Plan, Doar rol, Analitice Tier A, Catalog 38 fluxuri, Matrice).</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="39" t="inlineStr">
         <is>
+          <t>ETAPA 0: Arhitectură + skeleton complet (Legendă, Plan, Doar rol, Analitice Tier A, Catalog 38 fluxuri, Matrice).</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="39" t="inlineStr">
+        <is>
           <t>ETAPA 1: 12 fluxuri detaliate.</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="26" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="26" t="inlineStr">
         <is>
           <t>ETAPA 2: Tranșa 1 completă + F-07 + F-28 → 22 fluxuri.</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="48" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="48" t="inlineStr">
         <is>
           <t>ETAPA 3 (FINAL): Tranșa 2 + Tranșa 3 complete. Total 38/38 fluxuri cu pași detaliați. Matrice verde. Workbook gata pentru utilizare cabinet + învățare.</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="26" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="26" t="inlineStr">
         <is>
           <t>Livrat 14.08.2026 — OMFP 1802/2014 actualizat + OMF 981/2024 + cote TVA 21%/11% + SAGA ca reper.</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="65" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="65" t="inlineStr">
         <is>
           <t>ETAPA 4 — EXTINDERE LA TRAININGURILE 2 ȘI 3</t>
         </is>
@@ -8817,31 +8834,31 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A172:F172"/>
+    <mergeCell ref="A174:F174"/>
     <mergeCell ref="A185:G185"/>
     <mergeCell ref="A181:G181"/>
+    <mergeCell ref="A188:G188"/>
     <mergeCell ref="A108:F108"/>
     <mergeCell ref="A164:F164"/>
     <mergeCell ref="A184:G184"/>
     <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A163:F163"/>
-    <mergeCell ref="A180:G180"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A176:G176"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A186:G186"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A182:G182"/>
-    <mergeCell ref="A178:G178"/>
+    <mergeCell ref="A165:F165"/>
     <mergeCell ref="A173:F173"/>
     <mergeCell ref="A187:G187"/>
     <mergeCell ref="A183:G183"/>
-    <mergeCell ref="A174:G174"/>
+    <mergeCell ref="A177:G177"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="A82:F82"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A179:G179"/>
+    <mergeCell ref="A175:G175"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9132,7 +9149,7 @@
       </c>
       <c r="E12" s="29" t="inlineStr">
         <is>
-          <t>Declarații_TVA_INC, Jurnale_TVA_INC, NotaExport_TVA_INC</t>
+          <t>Declarații_TVA_INC, Reguli_TVA_INC, Jurnale_TVA_INC, NotaExport_TVA_INC</t>
         </is>
       </c>
       <c r="F12" s="29" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -5656,7 +5656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8650,183 +8650,200 @@
     <row r="162">
       <c r="A162" s="67" t="inlineStr">
         <is>
+          <t>Declarații_NEUT, Jurnale_NEUT, NotaExport_NEUT</t>
+        </is>
+      </c>
+      <c r="B162" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
+        </is>
+      </c>
+      <c r="C162" s="67" t="inlineStr">
+        <is>
+          <t>Foile se numesc Declarații_NEUTRALIZARE ș.a.m.d., iar Reguli_ lipsea din listă. Se generează acum din codul modulului.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="67" t="inlineStr">
+        <is>
           <t>Ilustrativ (sume descriptive)</t>
         </is>
       </c>
-      <c r="B162" s="67" t="inlineStr">
+      <c r="B163" s="67" t="inlineStr">
         <is>
           <t>F-50 plafon 1.500 lei/lună; F-51 reluare 7812</t>
         </is>
       </c>
-      <c r="C162" s="67" t="inlineStr">
+      <c r="C163" s="67" t="inlineStr">
         <is>
           <t>Marcajul PARȚIAL de la 681/781 era corect când sumele erau descriptive. Acum 681 și 781 au cifre reale în F-50 (plafonul de 1.500 lei/lună) și F-51 (reluarea prin 7812), deci nota nu mai descrie realitatea.</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="36" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="36" t="inlineStr">
         <is>
           <t>6. Titluri și note de secțiune, scoase la reordonare</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="63" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="63" t="inlineStr">
         <is>
           <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="67" t="inlineStr">
-        <is>
-          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="67" t="inlineStr">
         <is>
-          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
+          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="67" t="inlineStr">
         <is>
-          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
+          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="67" t="inlineStr">
         <is>
-          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="67" t="inlineStr">
         <is>
-          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="67" t="inlineStr">
         <is>
+          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="67" t="inlineStr">
+        <is>
           <t>Nu sunt liniare. Fiecare pornește dintr-o stare „murdară" sau produce intersecție între două roluri. Acolo apar erorile de cabinet. Valoarea didactică &gt; încă 10 fluxuri liniare.</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="36" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="36" t="inlineStr">
         <is>
           <t>7. Narativul de etape, mutat din Legendă</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="63" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="63" t="inlineStr">
         <is>
           <t>Descria ordinea livrărilor, nu conținutul contabil. Mutat aici verbatim ca Legenda să descrie sistemul, nu istoria lui.</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="4" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
         <is>
           <t>6. LISTA FLUXURILOR (~38, în 3 tranșe) — cele bold sunt „didactice”</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="40" customHeight="1">
-      <c r="A176" s="5" t="inlineStr">
+    <row r="177" ht="40" customHeight="1">
+      <c r="A177" s="5" t="inlineStr">
         <is>
           <t>Tranșa 1 — stocuri și producție (F-01…F-12)</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="12" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="12" t="inlineStr">
         <is>
           <t>aprovizionare intern · prin 32x (tranzit) · intracomunitar cu taxare inversă · obiecte de inventar cu 8035 cap-coadă · producție termopan multi-stadiu (601→331→711→345→vânzare) · deșeuri 346 · servicii în curs 332/712 · diferențe de preț 308 · ajustare depreciere stoc · piese de schimb 3024→371 · stocuri la terți · ambalaje + taxa AFM</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="40" customHeight="1">
-      <c r="A178" s="5" t="inlineStr">
+    <row r="179" ht="40" customHeight="1">
+      <c r="A179" s="5" t="inlineStr">
         <is>
           <t>Tranșa 2 — TVA, comerț, import (F-13…F-25)</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="12" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="12" t="inlineStr">
         <is>
           <t>vânzare en-gros · gestiune amănunt completă cu verificarea ambelor corelații · import prin comisionar (446, taxe vamale + transport în cost) · import cu plată directă în vamă · TVA la încasare pe achiziție și pe vânzare · taxare inversă internă · livrare intracomunitară scutită · export · închiderea lunară de TVA · înregistrări fără document (50% auto, lipsă la inventar) · 408/418 · reduceri 609/709</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="40" customHeight="1">
-      <c r="A180" s="5" t="inlineStr">
+    <row r="181" ht="40" customHeight="1">
+      <c r="A181" s="5" t="inlineStr">
         <is>
           <t>Tranșa 3 — imobilizări, personal, închidere (F-26…F-38)</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="12" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="12" t="inlineStr">
         <is>
           <t>achiziție MF + amortizare · imobilizări în curs · producție în regie proprie (722) · subvenție 475 eliberată pe măsura amortizării · avansuri 471/472 · cedare MF · salarii complet · viramente interne 581 · sumă neidentificată → 473 · avansuri de trezorerie · închiderea exercițiului (121/129/117 + 691/697/4417) · angajamente extrabilanțiere · decontări 481/482</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="3" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
         <is>
           <t>PROGRES IMPLEMENTARE</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="39" t="inlineStr">
-        <is>
-          <t>ETAPA 0: Arhitectură + skeleton complet (Legendă, Plan, Doar rol, Analitice Tier A, Catalog 38 fluxuri, Matrice).</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="39" t="inlineStr">
         <is>
+          <t>ETAPA 0: Arhitectură + skeleton complet (Legendă, Plan, Doar rol, Analitice Tier A, Catalog 38 fluxuri, Matrice).</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="39" t="inlineStr">
+        <is>
           <t>ETAPA 1: 12 fluxuri detaliate.</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="26" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="26" t="inlineStr">
         <is>
           <t>ETAPA 2: Tranșa 1 completă + F-07 + F-28 → 22 fluxuri.</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="48" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="48" t="inlineStr">
         <is>
           <t>ETAPA 3 (FINAL): Tranșa 2 + Tranșa 3 complete. Total 38/38 fluxuri cu pași detaliați. Matrice verde. Workbook gata pentru utilizare cabinet + învățare.</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="26" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="26" t="inlineStr">
         <is>
           <t>Livrat 14.08.2026 — OMFP 1802/2014 actualizat + OMF 981/2024 + cote TVA 21%/11% + SAGA ca reper.</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="65" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="65" t="inlineStr">
         <is>
           <t>ETAPA 4 — EXTINDERE LA TRAININGURILE 2 ȘI 3</t>
         </is>
@@ -8836,29 +8853,29 @@
   <mergeCells count="25">
     <mergeCell ref="A174:F174"/>
     <mergeCell ref="A185:G185"/>
-    <mergeCell ref="A181:G181"/>
     <mergeCell ref="A188:G188"/>
     <mergeCell ref="A108:F108"/>
-    <mergeCell ref="A164:F164"/>
     <mergeCell ref="A184:G184"/>
     <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A180:G180"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A175:F175"/>
     <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A176:G176"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A186:G186"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A182:G182"/>
     <mergeCell ref="A165:F165"/>
-    <mergeCell ref="A173:F173"/>
+    <mergeCell ref="A178:G178"/>
     <mergeCell ref="A187:G187"/>
     <mergeCell ref="A183:G183"/>
-    <mergeCell ref="A177:G177"/>
     <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A166:F166"/>
     <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A189:G189"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A179:G179"/>
-    <mergeCell ref="A175:G175"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9085,7 +9102,7 @@
       </c>
       <c r="E10" s="29" t="inlineStr">
         <is>
-          <t>Declarații_NEUT, Jurnale_NEUT, NotaExport_NEUT</t>
+          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="F10" s="29" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -5656,7 +5656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8667,183 +8667,217 @@
     <row r="163">
       <c r="A163" s="67" t="inlineStr">
         <is>
+          <t>Declarații_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+        </is>
+      </c>
+      <c r="B163" s="67" t="inlineStr">
+        <is>
+          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+        </is>
+      </c>
+      <c r="C163" s="67" t="inlineStr">
+        <is>
+          <t>Ultima coloană „Foile din modul” la care lipsea Reguli_. Se generează acum din cod, ca toate celelalte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="67" t="inlineStr">
+        <is>
+          <t>B1 Aprovizionare PVA; B2 TVA ded.; B3 Descărcare; B4 Venit; B5 Corelații; B6 Închidere TVA</t>
+        </is>
+      </c>
+      <c r="B164" s="67" t="inlineStr">
+        <is>
+          <t>B1 Aprovizionare PVA; B2 TVA ded.; B3 Descărcare; B4 Venit; B5 Închidere TVA</t>
+        </is>
+      </c>
+      <c r="C164" s="67" t="inlineStr">
+        <is>
+          <t>Catalogul anunța șase blocuri și le numea greșit: jurnalul are cinci, iar al cincilea e închiderea de TVA, nu corelațiile. Corelațiile nu sunt un bloc de înregistrări — sunt două verificări pe cifre, în foaia de Declarații, reluate la finalul jurnalului. Lista spune acum ce emite modulul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="67" t="inlineStr">
+        <is>
           <t>Ilustrativ (sume descriptive)</t>
         </is>
       </c>
-      <c r="B163" s="67" t="inlineStr">
+      <c r="B165" s="67" t="inlineStr">
         <is>
           <t>F-50 plafon 1.500 lei/lună; F-51 reluare 7812</t>
         </is>
       </c>
-      <c r="C163" s="67" t="inlineStr">
+      <c r="C165" s="67" t="inlineStr">
         <is>
           <t>Marcajul PARȚIAL de la 681/781 era corect când sumele erau descriptive. Acum 681 și 781 au cifre reale în F-50 (plafonul de 1.500 lei/lună) și F-51 (reluarea prin 7812), deci nota nu mai descrie realitatea.</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="36" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="36" t="inlineStr">
         <is>
           <t>6. Titluri și note de secțiune, scoase la reordonare</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="63" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="63" t="inlineStr">
         <is>
           <t>Descriau gruparea veche — pe tranșe și pe etape de livrare — care nu mai există: fluxurile stau acum la clasa lor de conturi. Textul se păstrează verbatim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="67" t="inlineStr">
-        <is>
-          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="67" t="inlineStr">
-        <is>
-          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="67" t="inlineStr">
         <is>
-          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
+          <t>EXEMPLE COMPLETE DE FLUXURI DIDACTICE (pași detaliați)</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="67" t="inlineStr">
         <is>
-          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+          <t>STATUS FINAL ETAPA 3 — CATALOG COMPLET</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="67" t="inlineStr">
         <is>
-          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+          <t>Toate cele 38 de fluxuri (F-01…F-38) au acum pași detaliați. Tier A acoperit. Porțile de calitate (ΣD=ΣC, stare terminală, pas revelator, Declarativ, factor pe analitic) sunt respectate pe exemplele didactice. Workbook-ul este livrabil pentru cabinet + învățare.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="67" t="inlineStr">
         <is>
+          <t>Eventuale îmbunătățiri ulterioare: cifre de verificare pe un set complet de corelații (371/378/4428 pe un an), template de checklist lunar, sau export tipărit pe fluxuri didactice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="67" t="inlineStr">
+        <is>
+          <t>——— FLUXURI DE INTERSECȚIE, INVERSARE, GRANIȚĂ EXERCIȚIU, CORECȚIE (F-39…F-44) ———</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="67" t="inlineStr">
+        <is>
           <t>Nu sunt liniare. Fiecare pornește dintr-o stare „murdară" sau produce intersecție între două roluri. Acolo apar erorile de cabinet. Valoarea didactică &gt; încă 10 fluxuri liniare.</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="36" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="36" t="inlineStr">
         <is>
           <t>7. Narativul de etape, mutat din Legendă</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="63" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="63" t="inlineStr">
         <is>
           <t>Descria ordinea livrărilor, nu conținutul contabil. Mutat aici verbatim ca Legenda să descrie sistemul, nu istoria lui.</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="4" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
         <is>
           <t>6. LISTA FLUXURILOR (~38, în 3 tranșe) — cele bold sunt „didactice”</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="40" customHeight="1">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>Tranșa 1 — stocuri și producție (F-01…F-12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="12" t="inlineStr">
-        <is>
-          <t>aprovizionare intern · prin 32x (tranzit) · intracomunitar cu taxare inversă · obiecte de inventar cu 8035 cap-coadă · producție termopan multi-stadiu (601→331→711→345→vânzare) · deșeuri 346 · servicii în curs 332/712 · diferențe de preț 308 · ajustare depreciere stoc · piese de schimb 3024→371 · stocuri la terți · ambalaje + taxa AFM</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>Tranșa 2 — TVA, comerț, import (F-13…F-25)</t>
+          <t>Tranșa 1 — stocuri și producție (F-01…F-12)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="12" t="inlineStr">
         <is>
-          <t>vânzare en-gros · gestiune amănunt completă cu verificarea ambelor corelații · import prin comisionar (446, taxe vamale + transport în cost) · import cu plată directă în vamă · TVA la încasare pe achiziție și pe vânzare · taxare inversă internă · livrare intracomunitară scutită · export · închiderea lunară de TVA · înregistrări fără document (50% auto, lipsă la inventar) · 408/418 · reduceri 609/709</t>
+          <t>aprovizionare intern · prin 32x (tranzit) · intracomunitar cu taxare inversă · obiecte de inventar cu 8035 cap-coadă · producție termopan multi-stadiu (601→331→711→345→vânzare) · deșeuri 346 · servicii în curs 332/712 · diferențe de preț 308 · ajustare depreciere stoc · piese de schimb 3024→371 · stocuri la terți · ambalaje + taxa AFM</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>Tranșa 3 — imobilizări, personal, închidere (F-26…F-38)</t>
+          <t>Tranșa 2 — TVA, comerț, import (F-13…F-25)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="12" t="inlineStr">
         <is>
+          <t>vânzare en-gros · gestiune amănunt completă cu verificarea ambelor corelații · import prin comisionar (446, taxe vamale + transport în cost) · import cu plată directă în vamă · TVA la încasare pe achiziție și pe vânzare · taxare inversă internă · livrare intracomunitară scutită · export · închiderea lunară de TVA · înregistrări fără document (50% auto, lipsă la inventar) · 408/418 · reduceri 609/709</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="40" customHeight="1">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>Tranșa 3 — imobilizări, personal, închidere (F-26…F-38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="12" t="inlineStr">
+        <is>
           <t>achiziție MF + amortizare · imobilizări în curs · producție în regie proprie (722) · subvenție 475 eliberată pe măsura amortizării · avansuri 471/472 · cedare MF · salarii complet · viramente interne 581 · sumă neidentificată → 473 · avansuri de trezorerie · închiderea exercițiului (121/129/117 + 691/697/4417) · angajamente extrabilanțiere · decontări 481/482</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="3" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
         <is>
           <t>PROGRES IMPLEMENTARE</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="39" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="39" t="inlineStr">
         <is>
           <t>ETAPA 0: Arhitectură + skeleton complet (Legendă, Plan, Doar rol, Analitice Tier A, Catalog 38 fluxuri, Matrice).</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="39" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="39" t="inlineStr">
         <is>
           <t>ETAPA 1: 12 fluxuri detaliate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="26" t="inlineStr">
-        <is>
-          <t>ETAPA 2: Tranșa 1 completă + F-07 + F-28 → 22 fluxuri.</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="48" t="inlineStr">
-        <is>
-          <t>ETAPA 3 (FINAL): Tranșa 2 + Tranșa 3 complete. Total 38/38 fluxuri cu pași detaliați. Matrice verde. Workbook gata pentru utilizare cabinet + învățare.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="26" t="inlineStr">
         <is>
+          <t>ETAPA 2: Tranșa 1 completă + F-07 + F-28 → 22 fluxuri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="48" t="inlineStr">
+        <is>
+          <t>ETAPA 3 (FINAL): Tranșa 2 + Tranșa 3 complete. Total 38/38 fluxuri cu pași detaliați. Matrice verde. Workbook gata pentru utilizare cabinet + învățare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="26" t="inlineStr">
+        <is>
           <t>Livrat 14.08.2026 — OMFP 1802/2014 actualizat + OMF 981/2024 + cote TVA 21%/11% + SAGA ca reper.</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="65" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="65" t="inlineStr">
         <is>
           <t>ETAPA 4 — EXTINDERE LA TRAININGURILE 2 ȘI 3</t>
         </is>
@@ -8851,30 +8885,30 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A174:F174"/>
     <mergeCell ref="A185:G185"/>
+    <mergeCell ref="A177:F177"/>
     <mergeCell ref="A188:G188"/>
     <mergeCell ref="A108:F108"/>
     <mergeCell ref="A184:G184"/>
     <mergeCell ref="A89:F89"/>
     <mergeCell ref="A180:G180"/>
+    <mergeCell ref="A190:G190"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A175:F175"/>
     <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A176:G176"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A186:G186"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A191:G191"/>
     <mergeCell ref="A182:G182"/>
-    <mergeCell ref="A165:F165"/>
     <mergeCell ref="A178:G178"/>
     <mergeCell ref="A187:G187"/>
-    <mergeCell ref="A183:G183"/>
+    <mergeCell ref="A167:F167"/>
+    <mergeCell ref="A176:F176"/>
     <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A166:F166"/>
     <mergeCell ref="A82:F82"/>
     <mergeCell ref="A189:G189"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A168:F168"/>
     <mergeCell ref="A88:F88"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9134,7 +9168,7 @@
       </c>
       <c r="E11" s="29" t="inlineStr">
         <is>
-          <t>Declarații_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
         </is>
       </c>
       <c r="F11" s="29" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -9264,7 +9264,7 @@
       </c>
       <c r="E14" s="28" t="inlineStr">
         <is>
-          <t>Declarații_DECONT, Reguli_DECONT, Jurnale_DECONT, NotaExport_DECONT</t>
+          <t>Declarații_DECONT, Reguli_DECONT, Registru_DECONT, Jurnale_DECONT, NotaExport_DECONT</t>
         </is>
       </c>
       <c r="F14" s="28" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="E34" s="67" t="inlineStr">
         <is>
-          <t>Declarații_INCHIDERE_LUNARA, Reguli_INCHIDERE_LUNARA, Jurnale_INCHIDERE_LUNARA, NotaExport_INCHIDERE_LUNARA</t>
+          <t>Declarații_INCHIDERE_LUNARA, Reguli_INCHIDERE_LUNARA, Verificări_INCHIDERE_LUNARA, Abateri_INCHIDERE_LUNARA</t>
         </is>
       </c>
       <c r="F34" s="67" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -9650,7 +9650,7 @@
       </c>
       <c r="F1" s="17" t="inlineStr">
         <is>
-          <t>Observatie</t>
+          <t>Observație</t>
         </is>
       </c>
       <c r="G1" s="17" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="B2" s="18" t="inlineStr">
         <is>
-          <t>CONTURI DE CAPITALURI, PROVIZIOANE, IMPRUMUTURI SI DATORII ASIMILATE</t>
+          <t>CONTURI DE CAPITALURI, PROVIZIOANE, ÎMPRUMUTURI ȘI DATORII ASIMILATE</t>
         </is>
       </c>
       <c r="C2" s="18" t="n"/>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="B3" s="19" t="inlineStr">
         <is>
-          <t>Capital si rezerve</t>
+          <t>Capital și rezerve</t>
         </is>
       </c>
       <c r="C3" s="19" t="n"/>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>Capital subscris (nevarsat 1011 / varsat 1012).</t>
+          <t>Capital subscris (nevărsat 1011 / vărsat 1012).</t>
         </is>
       </c>
       <c r="G4" s="20" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>Diferente de curs valutar din conversie</t>
+          <t>Diferențe de curs valutar din conversie</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>Interese care nu controleaza</t>
+          <t>Interese care nu controlează</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>Actiuni proprii</t>
+          <t>Acțiuni proprii</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>Contra-capital: rascumparari proprii, se deduc din capitaluri.</t>
+          <t>Contra-capital: răscumpărări proprii, se deduc din capitaluri.</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>Rezultatul exercitiului financiar</t>
+          <t>Rezultatul exercițiului financiar</t>
         </is>
       </c>
       <c r="C15" s="19" t="n"/>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t>Colecteaza toate cls.6 si 7 la inchidere; nu tine nimic real.</t>
+          <t>Colectează toate cls.6 și 7 la închidere; nu ține nimic real.</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Castiguri/pierderi din instrumente de capitaluri proprii</t>
+          <t>Câștiguri/pierderi din instrumente de capitaluri proprii</t>
         </is>
       </c>
       <c r="C18" s="19" t="n"/>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>Castiguri legate de instrumente de capitaluri proprii</t>
+          <t>Câștiguri legate de instrumente de capitaluri proprii</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Provizion (datorie estimata)</t>
+          <t>Provizion (datorie estimată)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>Obligatie reala, doar estimata (litigii, garantii, restructurare...).</t>
+          <t>Obligație reală, doar estimată (litigii, garanții, restructurare...).</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>Imprumuturi si datorii asimilate</t>
+          <t>Împrumuturi și datorii asimilate</t>
         </is>
       </c>
       <c r="C23" s="19" t="n"/>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Imprumuturi din emisiuni de obligatiuni</t>
+          <t>Împrumuturi din emisiuni de obligațiuni</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Datorii care privesc imobilizarile financiare</t>
+          <t>Datorii care privesc imobilizările financiare</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>Alte imprumuturi si datorii asimilate</t>
+          <t>Alte împrumuturi și datorii asimilate</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Dobanzi aferente imprumuturilor si datoriilor asimilate</t>
+          <t>Dobânzi aferente împrumuturilor și datoriilor asimilate</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>Prime privind rambursarea obligatiunilor si a altor datorii</t>
+          <t>Prime privind rambursarea obligațiunilor și a altor datorii</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="F29" s="22" t="inlineStr">
         <is>
-          <t>Contra-datorie: discount la obligatiuni, se deduce din 161.</t>
+          <t>Contra-datorie: discount la obligațiuni, se deduce din 161.</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>CONTURI DE IMOBILIZARI</t>
+          <t>CONTURI DE IMOBILIZĂRI</t>
         </is>
       </c>
       <c r="C30" s="18" t="n"/>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>Imobilizari necorporale</t>
+          <t>Imobilizări necorporale</t>
         </is>
       </c>
       <c r="C31" s="19" t="n"/>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Concesiuni, brevete, licente, marci, drepturi si active similare</t>
+          <t>Concesiuni, brevete, licențe, mărci, drepturi și active similare</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B35" s="21" t="inlineStr">
         <is>
-          <t>Active necorporale de explorare si evaluare a resurselor minerale</t>
+          <t>Active necorporale de explorare și evaluare a resurselor minerale</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>Alte imobilizari necorporale</t>
+          <t>Alte imobilizări necorporale</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>Imobilizari corporale</t>
+          <t>Imobilizări corporale</t>
         </is>
       </c>
       <c r="C38" s="19" t="n"/>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>Terenuri si amenajari de terenuri</t>
+          <t>Terenuri și amenajări de terenuri</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Constructii</t>
+          <t>Construcții</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Instalatii tehnice, mijloace de transport, animale si plantatii</t>
+          <t>Instalații tehnice, mijloace de transport, animale și plantații</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Mobilier, aparatura birotica, alte active corporale</t>
+          <t>Mobilier, aparatură birotică, alte active corporale</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>Investitii imobiliare</t>
+          <t>Investiții imobiliare</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Active corporale de explorare si evaluare a resurselor minerale</t>
+          <t>Active corporale de explorare și evaluare a resurselor minerale</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>Imobilizari corporale in curs de aprovizionare</t>
+          <t>Imobilizări corporale în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C46" s="19" t="n"/>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>Instalatii tehnice si mijloace de transport in curs de aprovizionare</t>
+          <t>Instalații tehnice și mijloace de transport în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E47" s="22" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="F47" s="22" t="inlineStr">
         <is>
-          <t>Ca 32x, dar pt. imobilizari: bun facturat, nereceptionat.</t>
+          <t>Ca 32x, dar pt. imobilizări: bun facturat, nerecepționat.</t>
         </is>
       </c>
       <c r="G47" s="22" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>Mobilier, aparatura birotica... in curs de aprovizionare</t>
+          <t>Mobilier, aparatură birotică... în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E48" s="22" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t>Se stinge la receptie in 213/214.</t>
+          <t>Se stinge la recepție în 213/214.</t>
         </is>
       </c>
       <c r="G48" s="22" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t>Imobilizari in curs si avansuri pentru imobilizari</t>
+          <t>Imobilizări în curs și avansuri pentru imobilizări</t>
         </is>
       </c>
       <c r="C49" s="19" t="n"/>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Imobilizari corporale in curs de executie</t>
+          <t>Imobilizări corporale în curs de execuție</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="F50" s="20" t="inlineStr">
         <is>
-          <t>Cost real acumulat de constructie in regie/antrepriza.</t>
+          <t>Cost real acumulat de construcție în regie/antrepriză.</t>
         </is>
       </c>
       <c r="G50" s="20" t="inlineStr">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>Investitii imobiliare in curs de executie</t>
+          <t>Investiții imobiliare în curs de execuție</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="B52" s="19" t="inlineStr">
         <is>
-          <t>Imobilizari financiare</t>
+          <t>Imobilizări financiare</t>
         </is>
       </c>
       <c r="C52" s="19" t="n"/>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B53" s="21" t="inlineStr">
         <is>
-          <t>Actiuni detinute la entitatile afiliate</t>
+          <t>Acțiuni deținute la entitățile afiliate</t>
         </is>
       </c>
       <c r="C53" s="21" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="B54" s="21" t="inlineStr">
         <is>
-          <t>Actiuni detinute la entitati asociate</t>
+          <t>Acțiuni deținute la entități asociate</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="B55" s="21" t="inlineStr">
         <is>
-          <t>Actiuni detinute la entitati controlate in comun</t>
+          <t>Acțiuni deținute la entități controlate în comun</t>
         </is>
       </c>
       <c r="C55" s="21" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="B57" s="21" t="inlineStr">
         <is>
-          <t>Creante imobilizate</t>
+          <t>Creanțe imobilizate</t>
         </is>
       </c>
       <c r="C57" s="21" t="inlineStr">
@@ -11849,12 +11849,12 @@
       </c>
       <c r="E57" s="21" t="inlineStr">
         <is>
-          <t>Creanta</t>
+          <t>Creanță</t>
         </is>
       </c>
       <c r="F57" s="21" t="inlineStr">
         <is>
-          <t>Creante pe termen lung (imprumuturi acordate, garantii).</t>
+          <t>Creanțe pe termen lung (împrumuturi acordate, garanții).</t>
         </is>
       </c>
       <c r="G57" s="21" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B58" s="21" t="inlineStr">
         <is>
-          <t>Varsaminte de efectuat pentru imobilizari financiare</t>
+          <t>Vărsăminte de efectuat pentru imobilizări financiare</t>
         </is>
       </c>
       <c r="C58" s="21" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="F58" s="21" t="inlineStr">
         <is>
-          <t>Datorie pt. titluri subscrise si nevarsate.</t>
+          <t>Datorie pt. titluri subscrise și nevărsate.</t>
         </is>
       </c>
       <c r="G58" s="21" t="inlineStr"/>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t>Amortizari privind imobilizarile</t>
+          <t>Amortizări privind imobilizările</t>
         </is>
       </c>
       <c r="C59" s="19" t="n"/>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>Amortizari privind imobilizarile necorporale</t>
+          <t>Amortizări privind imobilizările necorporale</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E60" s="22" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t>Contra-activ: cumuleaza uzura, se scade din valoarea bruta.</t>
+          <t>Contra-activ: cumulează uzura, se scade din valoarea brută.</t>
         </is>
       </c>
       <c r="G60" s="22" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>Amortizari privind imobilizarile corporale</t>
+          <t>Amortizări privind imobilizările corporale</t>
         </is>
       </c>
       <c r="C61" s="22" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E61" s="22" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="B62" s="19" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea imobilizarilor</t>
+          <t>Ajustări pentru deprecierea imobilizărilor</t>
         </is>
       </c>
       <c r="C62" s="19" t="n"/>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea imobilizarilor necorporale</t>
+          <t>Ajustări pentru deprecierea imobilizărilor necorporale</t>
         </is>
       </c>
       <c r="C63" s="22" t="inlineStr">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E63" s="22" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="F63" s="22" t="inlineStr">
         <is>
-          <t>Contra-activ: depreciere reversibila.</t>
+          <t>Contra-activ: depreciere reversibilă.</t>
         </is>
       </c>
       <c r="G63" s="22" t="inlineStr">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea imobilizarilor corporale</t>
+          <t>Ajustări pentru deprecierea imobilizărilor corporale</t>
         </is>
       </c>
       <c r="C64" s="22" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E64" s="22" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea imobilizarilor in curs</t>
+          <t>Ajustări pentru deprecierea imobilizărilor în curs</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E65" s="22" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru pierderea de valoare a imobilizarilor financiare</t>
+          <t>Ajustări pentru pierderea de valoare a imobilizărilor financiare</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E66" s="22" t="inlineStr">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>CONTURI DE STOCURI SI PRODUCTIE IN CURS DE EXECUTIE</t>
+          <t>CONTURI DE STOCURI ȘI PRODUCȚIE ÎN CURS DE EXECUȚIE</t>
         </is>
       </c>
       <c r="C67" s="18" t="n"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>Stocuri de materii prime si materiale</t>
+          <t>Stocuri de materii prime și materiale</t>
         </is>
       </c>
       <c r="C68" s="19" t="n"/>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="F71" s="22" t="inlineStr">
         <is>
-          <t>Dare in consum prin 603; evidenta extrabilantiera pe 8035.</t>
+          <t>Dare în consum prin 603; evidență extrabilanțieră pe 8035.</t>
         </is>
       </c>
       <c r="G71" s="22" t="inlineStr">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="B72" s="22" t="inlineStr">
         <is>
-          <t>Diferente de pret la materii prime si materiale</t>
+          <t>Diferențe de preț la materii prime și materiale</t>
         </is>
       </c>
       <c r="C72" s="22" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E72" s="22" t="inlineStr">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t>Contra-stoc: diferente fata de pretul standard/inregistrare.</t>
+          <t>Contra-stoc: diferențe fata de prețul standard/înregistrare.</t>
         </is>
       </c>
       <c r="G72" s="22" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="B73" s="19" t="inlineStr">
         <is>
-          <t>Stocuri in curs de aprovizionare</t>
+          <t>Stocuri în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C73" s="19" t="n"/>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>Materii prime in curs de aprovizionare</t>
+          <t>Materii prime în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C74" s="22" t="inlineStr">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E74" s="22" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t>Factura in SPV, marfa pe drum. Se stinge 301=321 la receptie.</t>
+          <t>Factura în SPV, marfă pe drum. Se stinge 301=321 la recepție.</t>
         </is>
       </c>
       <c r="G74" s="22" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="B75" s="22" t="inlineStr">
         <is>
-          <t>Materiale consumabile in curs de aprovizionare</t>
+          <t>Materiale consumabile în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C75" s="22" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="D75" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E75" s="22" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>Materiale de natura obiectelor de inventar in curs de aprovizionare</t>
+          <t>Materiale de natura obiectelor de inventar în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C76" s="22" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E76" s="22" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="B77" s="22" t="inlineStr">
         <is>
-          <t>Active biologice de natura stocurilor in curs de aprovizionare</t>
+          <t>Active biologice de natura stocurilor în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C77" s="22" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="D77" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E77" s="22" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>Marfuri in curs de aprovizionare</t>
+          <t>Mărfuri în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C78" s="22" t="inlineStr">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="D78" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E78" s="22" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>Ambalaje in curs de aprovizionare</t>
+          <t>Ambalaje în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="D79" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E79" s="22" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="B80" s="19" t="inlineStr">
         <is>
-          <t>Productie in curs de executie</t>
+          <t>Producție în curs de execuție</t>
         </is>
       </c>
       <c r="C80" s="19" t="n"/>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="B81" s="22" t="inlineStr">
         <is>
-          <t>Produse in curs de executie</t>
+          <t>Produse în curs de execuție</t>
         </is>
       </c>
       <c r="C81" s="22" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="F81" s="22" t="inlineStr">
         <is>
-          <t>Stoc real de productie neterminata; neutralizarea in 121 o face 711.</t>
+          <t>Stoc real de producție neterminată; neutralizarea în 121 o face 711.</t>
         </is>
       </c>
       <c r="G81" s="22" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>Servicii in curs de executie</t>
+          <t>Servicii în curs de execuție</t>
         </is>
       </c>
       <c r="C82" s="22" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="F86" s="20" t="inlineStr">
         <is>
-          <t>Deseuri din productie predate la colectori (346=711).</t>
+          <t>Deșeuri din producție predate la colectori (346=711).</t>
         </is>
       </c>
       <c r="G86" s="20" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>Diferente de pret la produse</t>
+          <t>Diferențe de preț la produse</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E88" s="22" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="B89" s="19" t="inlineStr">
         <is>
-          <t>Stocuri aflate la terti</t>
+          <t>Stocuri aflate la terți</t>
         </is>
       </c>
       <c r="C89" s="19" t="n"/>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Materii si materiale aflate la terti</t>
+          <t>Materii și materiale aflate la terți</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="B91" s="20" t="inlineStr">
         <is>
-          <t>Produse aflate la terti</t>
+          <t>Produse aflate la terți</t>
         </is>
       </c>
       <c r="C91" s="20" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Active circulante aflate la terti</t>
+          <t>Active circulante aflate la terți</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="B93" s="20" t="inlineStr">
         <is>
-          <t>Marfuri aflate la terti</t>
+          <t>Mărfuri aflate la terți</t>
         </is>
       </c>
       <c r="C93" s="20" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Ambalaje aflate la terti</t>
+          <t>Ambalaje aflate la terți</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="B97" s="20" t="inlineStr">
         <is>
-          <t>Diferente de pret la active biologice de natura stocurilor</t>
+          <t>Diferențe de preț la active biologice de natura stocurilor</t>
         </is>
       </c>
       <c r="C97" s="20" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="D97" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="B98" s="19" t="inlineStr">
         <is>
-          <t>Marfuri</t>
+          <t>Mărfuri</t>
         </is>
       </c>
       <c r="C98" s="19" t="n"/>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>Marfuri</t>
+          <t>Mărfuri</t>
         </is>
       </c>
       <c r="C99" s="22" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="F99" s="22" t="inlineStr">
         <is>
-          <t>Gestiuni separate pe cota TVA si pe en-gros/amanunt.</t>
+          <t>Gestiuni separate pe cota TVA și pe en-gros/amănunt.</t>
         </is>
       </c>
       <c r="G99" s="22" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>Diferente de pret la marfuri</t>
+          <t>Diferențe de preț la mărfuri</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E100" s="22" t="inlineStr">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t>Adaosul comercial (amanunt). Corelatie: 707-607 = rulaj D 378. — Diferențe de preț la mărfuri (adaos). Rectificativ al lui 371 la preț cu amănuntul, alături de 4428.</t>
+          <t>Adaosul comercial (amănunt). Corelație: 707-607 = rulaj D 378. — Diferențe de preț la mărfuri (adaos). Rectificativ al lui 371 la preț cu amănuntul, alături de 4428.</t>
         </is>
       </c>
       <c r="G100" s="22" t="inlineStr">
@@ -13678,7 +13678,7 @@
       </c>
       <c r="B103" s="22" t="inlineStr">
         <is>
-          <t>Diferente de pret la ambalaje</t>
+          <t>Diferențe de preț la ambalaje</t>
         </is>
       </c>
       <c r="C103" s="22" t="inlineStr">
@@ -13688,7 +13688,7 @@
       </c>
       <c r="D103" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E103" s="22" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="B104" s="19" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea stocurilor si productiei in curs</t>
+          <t>Ajustări pentru deprecierea stocurilor și producției în curs</t>
         </is>
       </c>
       <c r="C104" s="19" t="n"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="B105" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea materiilor prime</t>
+          <t>Ajustări pentru deprecierea materiilor prime</t>
         </is>
       </c>
       <c r="C105" s="22" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="D105" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E105" s="22" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="B106" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea materialelor</t>
+          <t>Ajustări pentru deprecierea materialelor</t>
         </is>
       </c>
       <c r="C106" s="22" t="inlineStr">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="D106" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E106" s="22" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="B107" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea productiei in curs de executie</t>
+          <t>Ajustări pentru deprecierea producției în curs de execuție</t>
         </is>
       </c>
       <c r="C107" s="22" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="D107" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E107" s="22" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="B108" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea produselor</t>
+          <t>Ajustări pentru deprecierea produselor</t>
         </is>
       </c>
       <c r="C108" s="22" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="D108" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E108" s="22" t="inlineStr">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="B109" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea stocurilor aflate la terti</t>
+          <t>Ajustări pentru deprecierea stocurilor aflate la terți</t>
         </is>
       </c>
       <c r="C109" s="22" t="inlineStr">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="D109" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E109" s="22" t="inlineStr">
@@ -13962,7 +13962,7 @@
       </c>
       <c r="B110" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea activelor biologice de natura stocurilor</t>
+          <t>Ajustări pentru deprecierea activelor biologice de natura stocurilor</t>
         </is>
       </c>
       <c r="C110" s="22" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="D110" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E110" s="22" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="B111" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea marfurilor</t>
+          <t>Ajustări pentru deprecierea mărfurilor</t>
         </is>
       </c>
       <c r="C111" s="22" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="D111" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E111" s="22" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="B112" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea ambalajelor</t>
+          <t>Ajustări pentru deprecierea ambalajelor</t>
         </is>
       </c>
       <c r="C112" s="22" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="D112" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E112" s="22" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B113" s="18" t="inlineStr">
         <is>
-          <t>CONTURI DE TERTI</t>
+          <t>CONTURI DE TERȚI</t>
         </is>
       </c>
       <c r="C113" s="18" t="n"/>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B114" s="19" t="inlineStr">
         <is>
-          <t>Furnizori si conturi asimilate</t>
+          <t>Furnizori și conturi asimilate</t>
         </is>
       </c>
       <c r="C114" s="19" t="n"/>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="B116" s="20" t="inlineStr">
         <is>
-          <t>Efecte de platit</t>
+          <t>Efecte de plătit</t>
         </is>
       </c>
       <c r="C116" s="20" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="B117" s="20" t="inlineStr">
         <is>
-          <t>Furnizori de imobilizari</t>
+          <t>Furnizori de imobilizări</t>
         </is>
       </c>
       <c r="C117" s="20" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>Efecte de platit pentru imobilizari</t>
+          <t>Efecte de plătit pentru imobilizări</t>
         </is>
       </c>
       <c r="C118" s="20" t="inlineStr">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="D119" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E119" s="22" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="F119" s="22" t="inlineStr">
         <is>
-          <t>Marfa a sosit, factura NU. Oglinda lui 327. Se stinge 408=401.</t>
+          <t>Marfă a sosit, factura NU. Oglinda lui 327. Se stinge 408=401.</t>
         </is>
       </c>
       <c r="G119" s="22" t="inlineStr">
@@ -14373,12 +14373,12 @@
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>Creanta</t>
+          <t>Creanță</t>
         </is>
       </c>
       <c r="F120" s="20" t="inlineStr">
         <is>
-          <t>Avansuri platite furnizorilor (creanta reala).</t>
+          <t>Avansuri plătite furnizorilor (creanță reală).</t>
         </is>
       </c>
       <c r="G120" s="20" t="inlineStr">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="B121" s="19" t="inlineStr">
         <is>
-          <t>Clienti si conturi asimilate</t>
+          <t>Clienți și conturi asimilate</t>
         </is>
       </c>
       <c r="C121" s="19" t="n"/>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="B122" s="22" t="inlineStr">
         <is>
-          <t>Clienti</t>
+          <t>Clienți</t>
         </is>
       </c>
       <c r="C122" s="22" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="E122" s="22" t="inlineStr">
         <is>
-          <t>Creanta</t>
+          <t>Creanță</t>
         </is>
       </c>
       <c r="F122" s="22" t="n"/>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>Efecte de primit de la clienti</t>
+          <t>Efecte de primit de la clienți</t>
         </is>
       </c>
       <c r="C123" s="20" t="inlineStr">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="E123" s="20" t="inlineStr">
         <is>
-          <t>Creanta</t>
+          <t>Creanță</t>
         </is>
       </c>
       <c r="F123" s="20" t="n"/>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="B124" s="22" t="inlineStr">
         <is>
-          <t>Clienti - facturi de intocmit</t>
+          <t>Clienți - facturi de întocmit</t>
         </is>
       </c>
       <c r="C124" s="22" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="D124" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E124" s="22" t="inlineStr">
@@ -14534,7 +14534,7 @@
       </c>
       <c r="F124" s="22" t="inlineStr">
         <is>
-          <t>Livrat/prestat, nefacturat inca. Se stinge 418=4111.</t>
+          <t>Livrat/prestat, nefacturat încă. Se stinge 418=4111.</t>
         </is>
       </c>
       <c r="G124" s="22" t="inlineStr">
@@ -14566,7 +14566,7 @@
       </c>
       <c r="B125" s="20" t="inlineStr">
         <is>
-          <t>Clienti - creditori</t>
+          <t>Clienți - creditori</t>
         </is>
       </c>
       <c r="C125" s="20" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="F125" s="20" t="inlineStr">
         <is>
-          <t>Avansuri incasate de la clienti. — Clienți-creditori (avansuri încasate). TVA se colectează la încasarea avansului, iar la factura finală avansul se stornează — nu e venit, deci nu poate merge pe 472.</t>
+          <t>Avansuri incasate de la clienți. — Clienți-creditori (avansuri încasate). TVA se colectează la încasarea avansului, iar la factura finală avansul se stornează — nu e venit, deci nu poate merge pe 472.</t>
         </is>
       </c>
       <c r="G125" s="20" t="inlineStr"/>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="B126" s="19" t="inlineStr">
         <is>
-          <t>Personal si conturi asimilate</t>
+          <t>Personal și conturi asimilate</t>
         </is>
       </c>
       <c r="C126" s="19" t="n"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="B129" s="20" t="inlineStr">
         <is>
-          <t>Prime reprezentand participarea personalului la profit</t>
+          <t>Prime reprezentând participarea personalului la profit</t>
         </is>
       </c>
       <c r="C129" s="20" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>Creanta</t>
+          <t>Creanță</t>
         </is>
       </c>
       <c r="F130" s="20" t="n"/>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="B132" s="20" t="inlineStr">
         <is>
-          <t>Retineri din salarii datorate tertilor</t>
+          <t>Rețineri din salarii datorate terților</t>
         </is>
       </c>
       <c r="C132" s="20" t="inlineStr">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="B133" s="20" t="inlineStr">
         <is>
-          <t>Alte datorii si creante in legatura cu personalul</t>
+          <t>Alte datorii și creanțe în legătură cu personalul</t>
         </is>
       </c>
       <c r="C133" s="20" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="F133" s="20" t="inlineStr">
         <is>
-          <t>Bifunctional.</t>
+          <t>Bifuncțional.</t>
         </is>
       </c>
       <c r="G133" s="20" t="inlineStr"/>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="B134" s="19" t="inlineStr">
         <is>
-          <t>Asigurari sociale, protectia sociala si conturi asimilate</t>
+          <t>Asigurări sociale, protecția socială și conturi asimilate</t>
         </is>
       </c>
       <c r="C134" s="19" t="n"/>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="B135" s="20" t="inlineStr">
         <is>
-          <t>Asigurari sociale</t>
+          <t>Asigurări sociale</t>
         </is>
       </c>
       <c r="C135" s="20" t="inlineStr">
@@ -14938,7 +14938,7 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>Contributia asiguratorie pentru munca</t>
+          <t>Contribuția asigurătorie pentru muncă</t>
         </is>
       </c>
       <c r="C136" s="20" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="B137" s="20" t="inlineStr">
         <is>
-          <t>Ajutor de somaj</t>
+          <t>Ajutor de șomaj</t>
         </is>
       </c>
       <c r="C137" s="20" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="B138" s="20" t="inlineStr">
         <is>
-          <t>Alte datorii si creante sociale</t>
+          <t>Alte datorii și creanțe sociale</t>
         </is>
       </c>
       <c r="C138" s="20" t="inlineStr">
@@ -15030,7 +15030,7 @@
       </c>
       <c r="F138" s="20" t="inlineStr">
         <is>
-          <t>Bifunctional.</t>
+          <t>Bifuncțional.</t>
         </is>
       </c>
       <c r="G138" s="20" t="inlineStr"/>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="B139" s="19" t="inlineStr">
         <is>
-          <t>Bugetul statului, fonduri speciale si conturi asimilate</t>
+          <t>Bugetul statului, fonduri speciale și conturi asimilate</t>
         </is>
       </c>
       <c r="C139" s="19" t="n"/>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="B140" s="22" t="inlineStr">
         <is>
-          <t>Impozitul pe profit si alte impozite</t>
+          <t>Impozitul pe profit și alte impozite</t>
         </is>
       </c>
       <c r="C140" s="22" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="F140" s="22" t="inlineStr">
         <is>
-          <t>4411 impozit profit; bifunctional.</t>
+          <t>4411 impozit profit; bifuncțional.</t>
         </is>
       </c>
       <c r="G140" s="22" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="B142" s="20" t="inlineStr">
         <is>
-          <t>Taxa pe valoarea adaugata</t>
+          <t>Taxa pe valoarea adăugată</t>
         </is>
       </c>
       <c r="C142" s="20" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="B143" s="22" t="inlineStr">
         <is>
-          <t>TVA de plata</t>
+          <t>TVA de plată</t>
         </is>
       </c>
       <c r="C143" s="22" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="F143" s="22" t="inlineStr">
         <is>
-          <t>Sold datorie lunara catre buget.</t>
+          <t>Sold datorie lunară către buget.</t>
         </is>
       </c>
       <c r="G143" s="22" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="E144" s="22" t="inlineStr">
         <is>
-          <t>Creanta</t>
+          <t>Creanță</t>
         </is>
       </c>
       <c r="F144" s="22" t="inlineStr">
         <is>
-          <t>Sold creanta / de rambursat.</t>
+          <t>Sold creanță / de rambursat.</t>
         </is>
       </c>
       <c r="G144" s="22" t="inlineStr">
@@ -15318,7 +15318,7 @@
       </c>
       <c r="B145" s="22" t="inlineStr">
         <is>
-          <t>TVA deductibila</t>
+          <t>TVA deductibilă</t>
         </is>
       </c>
       <c r="C145" s="22" t="inlineStr">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="D145" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E145" s="22" t="inlineStr">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="F145" s="22" t="inlineStr">
         <is>
-          <t>Colecteaza TVA din cumparari in cursul lunii; se inchide in 4423/4424. Fara sold.</t>
+          <t>Colectează TVA din cumpărări în cursul lunii; se închide în 4423/4424. Fără sold.</t>
         </is>
       </c>
       <c r="G145" s="22" t="inlineStr">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="B146" s="22" t="inlineStr">
         <is>
-          <t>TVA colectata</t>
+          <t>TVA colectată</t>
         </is>
       </c>
       <c r="C146" s="22" t="inlineStr">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="D146" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E146" s="22" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="F146" s="22" t="inlineStr">
         <is>
-          <t>Colecteaza TVA din vanzari; se inchide in 4423/4424. Fara sold.</t>
+          <t>Colectează TVA din vânzări; se închide în 4423/4424. Fără sold.</t>
         </is>
       </c>
       <c r="G146" s="22" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="B147" s="22" t="inlineStr">
         <is>
-          <t>TVA neexigibila</t>
+          <t>TVA neexigibilă</t>
         </is>
       </c>
       <c r="C147" s="22" t="inlineStr">
@@ -15432,7 +15432,7 @@
       </c>
       <c r="D147" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E147" s="22" t="inlineStr">
@@ -15442,7 +15442,7 @@
       </c>
       <c r="F147" s="22" t="inlineStr">
         <is>
-          <t>DUAL - amanunt: rectificativ la 371 (sold*c/(100+c)); la incasare: intermediar. Cere analitice separate.</t>
+          <t>DUAL - amănunt: rectificativ la 371 (sold*c/(100+c)); la încasare: intermediar. Cere analitice separate.</t>
         </is>
       </c>
       <c r="G147" s="22" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="B149" s="20" t="inlineStr">
         <is>
-          <t>Subventii</t>
+          <t>Subvenții</t>
         </is>
       </c>
       <c r="C149" s="20" t="inlineStr">
@@ -15525,12 +15525,12 @@
       </c>
       <c r="E149" s="20" t="inlineStr">
         <is>
-          <t>Creanta</t>
+          <t>Creanță</t>
         </is>
       </c>
       <c r="F149" s="20" t="inlineStr">
         <is>
-          <t>Creanta fata de bugetul care acorda subventia.</t>
+          <t>Creanță fata de bugetul care acordă subvenția.</t>
         </is>
       </c>
       <c r="G149" s="20" t="inlineStr"/>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="B150" s="22" t="inlineStr">
         <is>
-          <t>Alte impozite, taxe si varsaminte asimilate</t>
+          <t>Alte impozite, taxe și vărsăminte asimilate</t>
         </is>
       </c>
       <c r="C150" s="22" t="inlineStr">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="F150" s="22" t="inlineStr">
         <is>
-          <t>Sintetic = datorie reala. Un analitic dedicat (TVA vama prin comisionar) = intermediar.</t>
+          <t>Sintetic = datorie reală. Un analitic dedicat (TVA vama prin comisionar) = intermediar.</t>
         </is>
       </c>
       <c r="G150" s="22" t="inlineStr">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="B151" s="22" t="inlineStr">
         <is>
-          <t>Fonduri speciale - taxe si varsaminte asimilate</t>
+          <t>Fonduri speciale - taxe și vărsăminte asimilate</t>
         </is>
       </c>
       <c r="C151" s="22" t="inlineStr">
@@ -15654,7 +15654,7 @@
       </c>
       <c r="B152" s="20" t="inlineStr">
         <is>
-          <t>Alte datorii si creante cu bugetul statului</t>
+          <t>Alte datorii și creanțe cu bugetul statului</t>
         </is>
       </c>
       <c r="C152" s="20" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>Bifunctional.</t>
+          <t>Bifuncțional.</t>
         </is>
       </c>
       <c r="G152" s="20" t="inlineStr"/>
@@ -15694,7 +15694,7 @@
       </c>
       <c r="B153" s="19" t="inlineStr">
         <is>
-          <t>Grup si actionari/asociati</t>
+          <t>Grup și acționari/asociați</t>
         </is>
       </c>
       <c r="C153" s="19" t="n"/>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="B154" s="20" t="inlineStr">
         <is>
-          <t>Decontari intre entitatile afiliate</t>
+          <t>Decontări între entitățile afiliate</t>
         </is>
       </c>
       <c r="C154" s="20" t="inlineStr">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="B155" s="20" t="inlineStr">
         <is>
-          <t>Decontari privind interesele de participare</t>
+          <t>Decontări privind interesele de participare</t>
         </is>
       </c>
       <c r="C155" s="20" t="inlineStr">
@@ -15790,7 +15790,7 @@
       </c>
       <c r="B156" s="20" t="inlineStr">
         <is>
-          <t>Sume datorate actionarilor/asociatilor</t>
+          <t>Sume datorate acționarilor/asociaților</t>
         </is>
       </c>
       <c r="C156" s="20" t="inlineStr">
@@ -15810,7 +15810,7 @@
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>Asociati - conturi curente (creditare firma).</t>
+          <t>Asociați - conturi curente (creditare firma).</t>
         </is>
       </c>
       <c r="G156" s="20" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="B157" s="20" t="inlineStr">
         <is>
-          <t>Decontari cu actionarii/asociatii privind capitalul</t>
+          <t>Decontări cu acționarii/asociații privind capitalul</t>
         </is>
       </c>
       <c r="C157" s="20" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="E157" s="20" t="inlineStr">
         <is>
-          <t>Creanta</t>
+          <t>Creanță</t>
         </is>
       </c>
       <c r="F157" s="20" t="n"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="B158" s="20" t="inlineStr">
         <is>
-          <t>Dividende de plata</t>
+          <t>Dividende de plată</t>
         </is>
       </c>
       <c r="C158" s="20" t="inlineStr">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="B159" s="21" t="inlineStr">
         <is>
-          <t>Decontari din operatiuni in participatie</t>
+          <t>Decontări din operațiuni în participație</t>
         </is>
       </c>
       <c r="C159" s="21" t="inlineStr">
@@ -15962,7 +15962,7 @@
       </c>
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>Debitori si creditori diversi</t>
+          <t>Debitori și creditori diverși</t>
         </is>
       </c>
       <c r="C160" s="19" t="n"/>
@@ -15982,7 +15982,7 @@
       </c>
       <c r="B161" s="20" t="inlineStr">
         <is>
-          <t>Debitori diversi</t>
+          <t>Debitori diverși</t>
         </is>
       </c>
       <c r="C161" s="20" t="inlineStr">
@@ -15997,7 +15997,7 @@
       </c>
       <c r="E161" s="20" t="inlineStr">
         <is>
-          <t>Creanta</t>
+          <t>Creanță</t>
         </is>
       </c>
       <c r="F161" s="20" t="n"/>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="B162" s="20" t="inlineStr">
         <is>
-          <t>Creditori diversi</t>
+          <t>Creditori diverși</t>
         </is>
       </c>
       <c r="C162" s="20" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="B163" s="20" t="inlineStr">
         <is>
-          <t>Creante reprezentand dividende repartizate in cursul exercitiului</t>
+          <t>Creanțe reprezentând dividende repartizate în cursul exercițiului</t>
         </is>
       </c>
       <c r="C163" s="20" t="inlineStr">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="E163" s="20" t="inlineStr">
         <is>
-          <t>Creanta</t>
+          <t>Creanță</t>
         </is>
       </c>
       <c r="F163" s="20" t="n"/>
@@ -16102,7 +16102,7 @@
       </c>
       <c r="B164" s="21" t="inlineStr">
         <is>
-          <t>Datorii/creante aferente activelor primite/predate in gestiune delegata</t>
+          <t>Datorii/creanțe aferente activelor primite/predate în gestiune delegată</t>
         </is>
       </c>
       <c r="C164" s="21" t="inlineStr">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="B165" s="21" t="inlineStr">
         <is>
-          <t>Decontari din operatiuni de fiducie</t>
+          <t>Decontări din operațiuni de fiducie</t>
         </is>
       </c>
       <c r="C165" s="21" t="inlineStr">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="B167" s="19" t="inlineStr">
         <is>
-          <t>Conturi de subventii, regularizare si asimilate</t>
+          <t>Conturi de subvenții, regularizare și asimilate</t>
         </is>
       </c>
       <c r="C167" s="19" t="n"/>
@@ -16230,7 +16230,7 @@
       </c>
       <c r="B168" s="22" t="inlineStr">
         <is>
-          <t>Cheltuieli inregistrate in avans</t>
+          <t>Cheltuieli înregistrate în avans</t>
         </is>
       </c>
       <c r="C168" s="22" t="inlineStr">
@@ -16240,17 +16240,17 @@
       </c>
       <c r="D168" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E168" s="22" t="inlineStr">
         <is>
-          <t>Regularizare temporala</t>
+          <t>Regularizare temporală</t>
         </is>
       </c>
       <c r="F168" s="22" t="inlineStr">
         <is>
-          <t>Se elibereaza sistematic cu trecerea timpului (ex. asigurare 1/12).</t>
+          <t>Se eliberează sistematic cu trecerea timpului (ex. asigurare 1/12).</t>
         </is>
       </c>
       <c r="G168" s="22" t="inlineStr">
@@ -16282,7 +16282,7 @@
       </c>
       <c r="B169" s="22" t="inlineStr">
         <is>
-          <t>Venituri inregistrate in avans</t>
+          <t>Venituri înregistrate în avans</t>
         </is>
       </c>
       <c r="C169" s="22" t="inlineStr">
@@ -16292,17 +16292,17 @@
       </c>
       <c r="D169" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E169" s="22" t="inlineStr">
         <is>
-          <t>Regularizare temporala</t>
+          <t>Regularizare temporală</t>
         </is>
       </c>
       <c r="F169" s="22" t="inlineStr">
         <is>
-          <t>Se elibereaza la venit pe masura trecerii timpului.</t>
+          <t>Se eliberează la venit pe măsura trecerii timpului.</t>
         </is>
       </c>
       <c r="G169" s="22" t="inlineStr">
@@ -16334,7 +16334,7 @@
       </c>
       <c r="B170" s="22" t="inlineStr">
         <is>
-          <t>Decontari din operatiuni in curs de clarificare</t>
+          <t>Decontări din operațiuni în curs de clarificare</t>
         </is>
       </c>
       <c r="C170" s="22" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="D170" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E170" s="22" t="inlineStr">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="F170" s="22" t="inlineStr">
         <is>
-          <t>CANONIC: suma neidentificata din extras; sold la 31.12 = suspect.</t>
+          <t>CANONIC: suma neidentificată din extras; sold la 31.12 = suspect.</t>
         </is>
       </c>
       <c r="G170" s="22" t="inlineStr">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="B171" s="22" t="inlineStr">
         <is>
-          <t>Subventii pentru investitii</t>
+          <t>Subvenții pentru investiții</t>
         </is>
       </c>
       <c r="C171" s="22" t="inlineStr">
@@ -16396,17 +16396,17 @@
       </c>
       <c r="D171" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E171" s="22" t="inlineStr">
         <is>
-          <t>Regularizare temporala</t>
+          <t>Regularizare temporală</t>
         </is>
       </c>
       <c r="F171" s="22" t="inlineStr">
         <is>
-          <t>CORECTIE: cod actual (nu 131 din vechiul 3055). Se trece la venit pe masura amortizarii activului.</t>
+          <t>CORECȚIE: cod actual (nu 131 din vechiul 3055). Se trece la venit pe măsura amortizării activului.</t>
         </is>
       </c>
       <c r="G171" s="22" t="inlineStr">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="B172" s="20" t="inlineStr">
         <is>
-          <t>Venituri in avans aferente activelor primite prin transfer de la clienti</t>
+          <t>Venituri în avans aferente activelor primite prin transfer de la clienți</t>
         </is>
       </c>
       <c r="C172" s="20" t="inlineStr">
@@ -16448,12 +16448,12 @@
       </c>
       <c r="D172" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E172" s="23" t="inlineStr">
         <is>
-          <t>Regularizare temporala</t>
+          <t>Regularizare temporală</t>
         </is>
       </c>
       <c r="F172" s="20" t="n"/>
@@ -16474,7 +16474,7 @@
       </c>
       <c r="B173" s="19" t="inlineStr">
         <is>
-          <t>Decontari in cadrul unitatii</t>
+          <t>Decontări în cadrul unității</t>
         </is>
       </c>
       <c r="C173" s="19" t="n"/>
@@ -16494,7 +16494,7 @@
       </c>
       <c r="B174" s="22" t="inlineStr">
         <is>
-          <t>Decontari intre unitate si subunitati</t>
+          <t>Decontări între unitate și subunități</t>
         </is>
       </c>
       <c r="C174" s="22" t="inlineStr">
@@ -16504,17 +16504,17 @@
       </c>
       <c r="D174" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E174" s="22" t="inlineStr">
         <is>
-          <t>Decontare interna</t>
+          <t>Decontare internă</t>
         </is>
       </c>
       <c r="F174" s="22" t="inlineStr">
         <is>
-          <t>Sold reciproc unitate-subunitate; se elimina.</t>
+          <t>Sold reciproc unitate-subunitate; se elimină.</t>
         </is>
       </c>
       <c r="G174" s="22" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="B175" s="22" t="inlineStr">
         <is>
-          <t>Decontari intre subunitati</t>
+          <t>Decontări între subunități</t>
         </is>
       </c>
       <c r="C175" s="22" t="inlineStr">
@@ -16556,17 +16556,17 @@
       </c>
       <c r="D175" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E175" s="22" t="inlineStr">
         <is>
-          <t>Decontare interna</t>
+          <t>Decontare internă</t>
         </is>
       </c>
       <c r="F175" s="22" t="inlineStr">
         <is>
-          <t>Se elimina la centralizare.</t>
+          <t>Se elimină la centralizare.</t>
         </is>
       </c>
       <c r="G175" s="22" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B176" s="19" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea creantelor</t>
+          <t>Ajustări pentru deprecierea creanțelor</t>
         </is>
       </c>
       <c r="C176" s="19" t="n"/>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="B177" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea creantelor - avansuri acordate furnizorilor</t>
+          <t>Ajustări pentru deprecierea creanțelor - avansuri acordate furnizorilor</t>
         </is>
       </c>
       <c r="C177" s="22" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="D177" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E177" s="22" t="inlineStr">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="F177" s="22" t="inlineStr">
         <is>
-          <t>Contra-creanta.</t>
+          <t>Contra-creanță.</t>
         </is>
       </c>
       <c r="G177" s="22" t="inlineStr"/>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="B178" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea creantelor - clienti</t>
+          <t>Ajustări pentru deprecierea creanțelor - clienți</t>
         </is>
       </c>
       <c r="C178" s="22" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="D178" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E178" s="22" t="inlineStr">
@@ -16678,7 +16678,7 @@
       </c>
       <c r="F178" s="22" t="inlineStr">
         <is>
-          <t>Contra-creanta. — Ajustări pentru deprecierea creanțelor-clienți. Spre deosebire de ajustările de stoc, acestea SUNT deductibile condiționat, în limitele art. 26. Nu se confundă cele două regimuri.</t>
+          <t>Contra-creanță. — Ajustări pentru deprecierea creanțelor-clienți. Spre deosebire de ajustările de stoc, acestea SUNT deductibile condiționat, în limitele art. 26. Nu se confundă cele două regimuri.</t>
         </is>
       </c>
       <c r="G178" s="22" t="inlineStr"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="B179" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea creantelor - grup si actionari/asociati</t>
+          <t>Ajustări pentru deprecierea creanțelor - grup și acționari/asociați</t>
         </is>
       </c>
       <c r="C179" s="22" t="inlineStr">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="D179" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E179" s="22" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="F179" s="22" t="inlineStr">
         <is>
-          <t>Contra-creanta.</t>
+          <t>Contra-creanță.</t>
         </is>
       </c>
       <c r="G179" s="22" t="inlineStr"/>
@@ -16738,7 +16738,7 @@
       </c>
       <c r="B180" s="22" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea creantelor - debitori diversi</t>
+          <t>Ajustări pentru deprecierea creanțelor - debitori diverși</t>
         </is>
       </c>
       <c r="C180" s="22" t="inlineStr">
@@ -16748,7 +16748,7 @@
       </c>
       <c r="D180" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E180" s="22" t="inlineStr">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="F180" s="22" t="inlineStr">
         <is>
-          <t>Contra-creanta.</t>
+          <t>Contra-creanță.</t>
         </is>
       </c>
       <c r="G180" s="22" t="inlineStr"/>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="B182" s="19" t="inlineStr">
         <is>
-          <t>Investitii pe termen scurt</t>
+          <t>Investiții pe termen scurt</t>
         </is>
       </c>
       <c r="C182" s="19" t="n"/>
@@ -16822,7 +16822,7 @@
       </c>
       <c r="B183" s="20" t="inlineStr">
         <is>
-          <t>Actiuni detinute la entitatile afiliate</t>
+          <t>Acțiuni deținute la entitățile afiliate</t>
         </is>
       </c>
       <c r="C183" s="20" t="inlineStr">
@@ -16858,7 +16858,7 @@
       </c>
       <c r="B184" s="20" t="inlineStr">
         <is>
-          <t>Obligatiuni emise si rascumparate</t>
+          <t>Obligațiuni emise și răscumpărate</t>
         </is>
       </c>
       <c r="C184" s="20" t="inlineStr">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="B185" s="20" t="inlineStr">
         <is>
-          <t>Obligatiuni</t>
+          <t>Obligațiuni</t>
         </is>
       </c>
       <c r="C185" s="20" t="inlineStr">
@@ -16930,7 +16930,7 @@
       </c>
       <c r="B186" s="20" t="inlineStr">
         <is>
-          <t>Alte investitii pe termen scurt si creante asimilate</t>
+          <t>Alte investiții pe termen scurt și creanțe asimilate</t>
         </is>
       </c>
       <c r="C186" s="20" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="B187" s="20" t="inlineStr">
         <is>
-          <t>Varsaminte de efectuat pentru investitiile pe termen scurt</t>
+          <t>Vărsăminte de efectuat pentru investițiile pe termen scurt</t>
         </is>
       </c>
       <c r="C187" s="20" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="B188" s="19" t="inlineStr">
         <is>
-          <t>Conturi la banci</t>
+          <t>Conturi la bănci</t>
         </is>
       </c>
       <c r="C188" s="19" t="n"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="B189" s="22" t="inlineStr">
         <is>
-          <t>Valori de incasat</t>
+          <t>Valori de încasat</t>
         </is>
       </c>
       <c r="C189" s="22" t="inlineStr">
@@ -17042,7 +17042,7 @@
       </c>
       <c r="F189" s="22" t="inlineStr">
         <is>
-          <t>Cecuri/efecte remise spre incasare (instrument real detinut).</t>
+          <t>Cecuri/efecte remise spre încasare (instrument real deținut).</t>
         </is>
       </c>
       <c r="G189" s="22" t="inlineStr">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="B190" s="22" t="inlineStr">
         <is>
-          <t>Conturi curente la banci</t>
+          <t>Conturi curente la bănci</t>
         </is>
       </c>
       <c r="C190" s="22" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="F190" s="22" t="inlineStr">
         <is>
-          <t>5121 lei, 5124 valuta. 5125 sume in curs de decontare = intermediar.</t>
+          <t>5121 lei, 5124 valută. 5125 sume în curs de decontare = intermediar.</t>
         </is>
       </c>
       <c r="G190" s="22" t="inlineStr">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="B191" s="20" t="inlineStr">
         <is>
-          <t>Dobanzi</t>
+          <t>Dobânzi</t>
         </is>
       </c>
       <c r="C191" s="20" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="F191" s="20" t="inlineStr">
         <is>
-          <t>5186 de platit / 5187 de incasat.</t>
+          <t>5186 de plătit / 5187 de încasat.</t>
         </is>
       </c>
       <c r="G191" s="20" t="inlineStr"/>
@@ -17242,7 +17242,7 @@
       </c>
       <c r="F194" s="20" t="inlineStr">
         <is>
-          <t>5311 lei, 5314 valuta.</t>
+          <t>5311 lei, 5314 valută.</t>
         </is>
       </c>
       <c r="G194" s="20" t="inlineStr">
@@ -17385,12 +17385,12 @@
       </c>
       <c r="E198" s="20" t="inlineStr">
         <is>
-          <t>Creanta</t>
+          <t>Creanță</t>
         </is>
       </c>
       <c r="F198" s="20" t="inlineStr">
         <is>
-          <t>Sume date angajatilor pt. cheltuieli - creanta pana la decont.</t>
+          <t>Sume date angajaților pt. cheltuieli - creanță până la decont.</t>
         </is>
       </c>
       <c r="G198" s="20" t="inlineStr"/>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="B199" s="19" t="inlineStr">
         <is>
-          <t>Viramente interne si ajustari</t>
+          <t>Viramente interne și ajustări</t>
         </is>
       </c>
       <c r="C199" s="19" t="n"/>
@@ -17440,7 +17440,7 @@
       </c>
       <c r="D200" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E200" s="22" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="F200" s="22" t="inlineStr">
         <is>
-          <t>Transfer banca&lt;-&gt;casa/banca; evita dubla numarare pana la confirmare.</t>
+          <t>Transfer banca&lt;-&gt;casa/banca; evită dublă numărare până la confirmare.</t>
         </is>
       </c>
       <c r="G200" s="22" t="inlineStr">
@@ -17482,7 +17482,7 @@
       </c>
       <c r="B201" s="19" t="inlineStr">
         <is>
-          <t>Ajustari pentru pierderea de valoare a conturilor de trezorerie</t>
+          <t>Ajustări pentru pierderea de valoare a conturilor de trezorerie</t>
         </is>
       </c>
       <c r="C201" s="19" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="B202" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru pierderea de valoare a actiunilor la entitati afiliate</t>
+          <t>Ajustări pentru pierderea de valoare a acțiunilor la entități afiliate</t>
         </is>
       </c>
       <c r="C202" s="20" t="inlineStr">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="D202" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E202" s="23" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="B203" s="20" t="inlineStr">
         <is>
-          <t>Ajustari... obligatiuni emise si rascumparate</t>
+          <t>Ajustări... obligațiuni emise și răscumpărate</t>
         </is>
       </c>
       <c r="C203" s="20" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="D203" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E203" s="23" t="inlineStr">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="B204" s="20" t="inlineStr">
         <is>
-          <t>Ajustari... obligatiuni</t>
+          <t>Ajustări... obligațiuni</t>
         </is>
       </c>
       <c r="C204" s="20" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="D204" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E204" s="23" t="inlineStr">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="B205" s="20" t="inlineStr">
         <is>
-          <t>Ajustari... alte investitii pe termen scurt</t>
+          <t>Ajustări... alte investiții pe termen scurt</t>
         </is>
       </c>
       <c r="C205" s="20" t="inlineStr">
@@ -17632,7 +17632,7 @@
       </c>
       <c r="D205" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E205" s="23" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="E208" s="22" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F208" s="22" t="inlineStr">
@@ -17773,12 +17773,12 @@
       </c>
       <c r="E209" s="22" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F209" s="22" t="inlineStr">
         <is>
-          <t>6021/6024/6028 trec prin 3021/3024/3028, niciodata direct 401.</t>
+          <t>6021/6024/6028 trec prin 3021/3024/3028, niciodată direct 401.</t>
         </is>
       </c>
       <c r="G209" s="22" t="inlineStr">
@@ -17825,7 +17825,7 @@
       </c>
       <c r="E210" s="22" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F210" s="22" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="E211" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F211" s="20" t="n"/>
@@ -17898,7 +17898,7 @@
       </c>
       <c r="B212" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli privind utilitatile</t>
+          <t>Cheltuieli privind utilitățile</t>
         </is>
       </c>
       <c r="C212" s="20" t="inlineStr">
@@ -17913,7 +17913,7 @@
       </c>
       <c r="E212" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F212" s="20" t="n"/>
@@ -17949,7 +17949,7 @@
       </c>
       <c r="E213" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F213" s="20" t="n"/>
@@ -17970,7 +17970,7 @@
       </c>
       <c r="B214" s="22" t="inlineStr">
         <is>
-          <t>Cheltuieli privind marfurile</t>
+          <t>Cheltuieli privind mărfurile</t>
         </is>
       </c>
       <c r="C214" s="22" t="inlineStr">
@@ -17985,12 +17985,12 @@
       </c>
       <c r="E214" s="22" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F214" s="22" t="inlineStr">
         <is>
-          <t>Corelatie: 707-607 = rulaj D 378.</t>
+          <t>Corelație: 707-607 = rulaj D 378.</t>
         </is>
       </c>
       <c r="G214" s="22" t="inlineStr">
@@ -18037,7 +18037,7 @@
       </c>
       <c r="E215" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F215" s="20" t="n"/>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="D216" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E216" s="22" t="inlineStr">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="F216" s="22" t="inlineStr">
         <is>
-          <t>Contra-cheltuiala: reduce costul achizitiilor.</t>
+          <t>Contra-cheltuială: reduce costul achizițiilor.</t>
         </is>
       </c>
       <c r="G216" s="22" t="inlineStr">
@@ -18110,7 +18110,7 @@
       </c>
       <c r="B217" s="19" t="inlineStr">
         <is>
-          <t>Cheltuieli cu serviciile executate de terti</t>
+          <t>Cheltuieli cu serviciile executate de terți</t>
         </is>
       </c>
       <c r="C217" s="19" t="n"/>
@@ -18130,7 +18130,7 @@
       </c>
       <c r="B218" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli cu intretinerea si reparatiile</t>
+          <t>Cheltuieli cu întreținerea și reparațiile</t>
         </is>
       </c>
       <c r="C218" s="20" t="inlineStr">
@@ -18145,7 +18145,7 @@
       </c>
       <c r="E218" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F218" s="20" t="n"/>
@@ -18166,7 +18166,7 @@
       </c>
       <c r="B219" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli cu redeventele, locatiile si chiriile</t>
+          <t>Cheltuieli cu redevențele, locațiile și chiriile</t>
         </is>
       </c>
       <c r="C219" s="20" t="inlineStr">
@@ -18181,7 +18181,7 @@
       </c>
       <c r="E219" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F219" s="20" t="n"/>
@@ -18217,7 +18217,7 @@
       </c>
       <c r="E220" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F220" s="20" t="n"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="B221" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli cu studiile si cercetarile</t>
+          <t>Cheltuieli cu studiile și cercetările</t>
         </is>
       </c>
       <c r="C221" s="20" t="inlineStr">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="E221" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F221" s="20" t="n"/>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="B222" s="19" t="inlineStr">
         <is>
-          <t>Cheltuieli cu alte servicii executate de terti</t>
+          <t>Cheltuieli cu alte servicii executate de terți</t>
         </is>
       </c>
       <c r="C222" s="19" t="n"/>
@@ -18321,7 +18321,7 @@
       </c>
       <c r="E223" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F223" s="20" t="n"/>
@@ -18342,7 +18342,7 @@
       </c>
       <c r="B224" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli privind comisioanele si onorariile</t>
+          <t>Cheltuieli privind comisioanele și onorariile</t>
         </is>
       </c>
       <c r="C224" s="20" t="inlineStr">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="E224" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F224" s="20" t="n"/>
@@ -18378,7 +18378,7 @@
       </c>
       <c r="B225" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli de protocol, reclama si publicitate</t>
+          <t>Cheltuieli de protocol, reclamă și publicitate</t>
         </is>
       </c>
       <c r="C225" s="20" t="inlineStr">
@@ -18393,7 +18393,7 @@
       </c>
       <c r="E225" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F225" s="20" t="n"/>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="B226" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli cu transportul de bunuri si personal</t>
+          <t>Cheltuieli cu transportul de bunuri și personal</t>
         </is>
       </c>
       <c r="C226" s="20" t="inlineStr">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="E226" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F226" s="20" t="n"/>
@@ -18450,7 +18450,7 @@
       </c>
       <c r="B227" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli cu deplasari, detasari si transferari</t>
+          <t>Cheltuieli cu deplasări, detașări și transferări</t>
         </is>
       </c>
       <c r="C227" s="20" t="inlineStr">
@@ -18465,7 +18465,7 @@
       </c>
       <c r="E227" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F227" s="20" t="n"/>
@@ -18486,7 +18486,7 @@
       </c>
       <c r="B228" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli postale si taxe de telecomunicatii</t>
+          <t>Cheltuieli poștale și taxe de telecomunicații</t>
         </is>
       </c>
       <c r="C228" s="20" t="inlineStr">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="E228" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F228" s="20" t="n"/>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="B229" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli cu serviciile bancare si asimilate</t>
+          <t>Cheltuieli cu serviciile bancare și asimilate</t>
         </is>
       </c>
       <c r="C229" s="20" t="inlineStr">
@@ -18537,7 +18537,7 @@
       </c>
       <c r="E229" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F229" s="20" t="n"/>
@@ -18558,7 +18558,7 @@
       </c>
       <c r="B230" s="20" t="inlineStr">
         <is>
-          <t>Alte cheltuieli cu serviciile executate de terti</t>
+          <t>Alte cheltuieli cu serviciile executate de terți</t>
         </is>
       </c>
       <c r="C230" s="20" t="inlineStr">
@@ -18573,7 +18573,7 @@
       </c>
       <c r="E230" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F230" s="20" t="n"/>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="B231" s="19" t="inlineStr">
         <is>
-          <t>Cheltuieli cu alte impozite, taxe si varsaminte asimilate</t>
+          <t>Cheltuieli cu alte impozite, taxe și vărsăminte asimilate</t>
         </is>
       </c>
       <c r="C231" s="19" t="n"/>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="B232" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli cu alte impozite, taxe si varsaminte asimilate</t>
+          <t>Cheltuieli cu alte impozite, taxe și vărsăminte asimilate</t>
         </is>
       </c>
       <c r="C232" s="20" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="E232" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F232" s="20" t="inlineStr">
@@ -18709,7 +18709,7 @@
       </c>
       <c r="E234" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F234" s="20" t="n"/>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="B235" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli cu avantajele in natura si tichetele acordate</t>
+          <t>Cheltuieli cu avantajele în natura și tichetele acordate</t>
         </is>
       </c>
       <c r="C235" s="20" t="inlineStr">
@@ -18745,7 +18745,7 @@
       </c>
       <c r="E235" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F235" s="20" t="n"/>
@@ -18766,7 +18766,7 @@
       </c>
       <c r="B236" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli privind asigurarile si protectia sociala</t>
+          <t>Cheltuieli privind asigurările și protecția socială</t>
         </is>
       </c>
       <c r="C236" s="20" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="E236" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F236" s="20" t="n"/>
@@ -18802,7 +18802,7 @@
       </c>
       <c r="B237" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli privind contributia asiguratorie pentru munca</t>
+          <t>Cheltuieli privind contribuția asigurătorie pentru muncă</t>
         </is>
       </c>
       <c r="C237" s="20" t="inlineStr">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="E237" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F237" s="20" t="n"/>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="B239" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli cu protectia mediului inconjurator</t>
+          <t>Cheltuieli cu protecția mediului înconjurător</t>
         </is>
       </c>
       <c r="C239" s="20" t="inlineStr">
@@ -18873,12 +18873,12 @@
       </c>
       <c r="E239" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F239" s="20" t="inlineStr">
         <is>
-          <t>Ex. taxa de mediu platita catre AFM.</t>
+          <t>Ex. taxa de mediu plătită către AFM.</t>
         </is>
       </c>
       <c r="G239" s="20" t="inlineStr"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="B240" s="20" t="inlineStr">
         <is>
-          <t>Pierderi din creante si debitori diversi</t>
+          <t>Pierderi din creanțe și debitori diverși</t>
         </is>
       </c>
       <c r="C240" s="20" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="E240" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F240" s="20" t="n"/>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="E241" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F241" s="20" t="n"/>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="B243" s="20" t="inlineStr">
         <is>
-          <t>Pierderi din creante legate de participatii</t>
+          <t>Pierderi din creanțe legate de participații</t>
         </is>
       </c>
       <c r="C243" s="20" t="inlineStr">
@@ -19017,7 +19017,7 @@
       </c>
       <c r="E243" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F243" s="20" t="n"/>
@@ -19038,7 +19038,7 @@
       </c>
       <c r="B244" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli privind investitiile financiare cedate</t>
+          <t>Cheltuieli privind investițiile financiare cedate</t>
         </is>
       </c>
       <c r="C244" s="20" t="inlineStr">
@@ -19053,7 +19053,7 @@
       </c>
       <c r="E244" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F244" s="20" t="n"/>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="B245" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli din diferente de curs valutar</t>
+          <t>Cheltuieli din diferențe de curs valutar</t>
         </is>
       </c>
       <c r="C245" s="20" t="inlineStr">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="E245" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F245" s="20" t="n"/>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="B246" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli privind dobanzile</t>
+          <t>Cheltuieli privind dobânzile</t>
         </is>
       </c>
       <c r="C246" s="20" t="inlineStr">
@@ -19137,7 +19137,7 @@
       </c>
       <c r="E246" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F246" s="20" t="n"/>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="E247" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F247" s="20" t="n"/>
@@ -19221,7 +19221,7 @@
       </c>
       <c r="E248" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F248" s="20" t="n"/>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="B249" s="19" t="inlineStr">
         <is>
-          <t>Cheltuieli cu amortizarile, provizioanele si ajustarile</t>
+          <t>Cheltuieli cu amortizările, provizioanele și ajustările</t>
         </is>
       </c>
       <c r="C249" s="19" t="n"/>
@@ -19262,7 +19262,7 @@
       </c>
       <c r="B250" s="22" t="inlineStr">
         <is>
-          <t>Cheltuieli de exploatare cu amortizarile, provizioanele si ajustarile</t>
+          <t>Cheltuieli de exploatare cu amortizările, provizioanele și ajustările</t>
         </is>
       </c>
       <c r="C250" s="22" t="inlineStr">
@@ -19277,17 +19277,17 @@
       </c>
       <c r="E250" s="22" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F250" s="22" t="inlineStr">
         <is>
-          <t>Contrapartida cheltuiala a rectificativelor 28x/29x/39x/49x.</t>
+          <t>Contrapartidă cheltuială a rectificativelor 28x/29x/39x/49x.</t>
         </is>
       </c>
       <c r="G250" s="22" t="inlineStr">
         <is>
-          <t>681 (contrapartida rectificativelor) — 6811 amortizare / 6812 provizioane</t>
+          <t>681 (contrapartidă rectificativelor) — 6811 amortizare / 6812 provizioane</t>
         </is>
       </c>
       <c r="H250" s="22" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="B251" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli financiare cu amortizarile, provizioanele si ajustarile</t>
+          <t>Cheltuieli financiare cu amortizările, provizioanele și ajustările</t>
         </is>
       </c>
       <c r="C251" s="20" t="inlineStr">
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E251" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F251" s="20" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="B252" s="19" t="inlineStr">
         <is>
-          <t>Cheltuieli cu impozitul pe profit si alte impozite</t>
+          <t>Cheltuieli cu impozitul pe profit și alte impozite</t>
         </is>
       </c>
       <c r="C252" s="19" t="n"/>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="E253" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F253" s="20" t="n"/>
@@ -19433,7 +19433,7 @@
       </c>
       <c r="E254" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F254" s="20" t="inlineStr">
@@ -19458,7 +19458,7 @@
       </c>
       <c r="B255" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli cu impozitul specific unor activitati</t>
+          <t>Cheltuieli cu impozitul specific unor activități</t>
         </is>
       </c>
       <c r="C255" s="20" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="E255" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F255" s="20" t="n"/>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="E256" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F256" s="20" t="inlineStr">
@@ -19566,7 +19566,7 @@
       </c>
       <c r="F257" s="20" t="inlineStr">
         <is>
-          <t>Denumire actualizată OMF 6670/2024. Contrapartida lui 694. NOU ca denumire extinsă.</t>
+          <t>Denumire actualizată OMF 6670/2024. Contrapartidă lui 694. NOU ca denumire extinsă.</t>
         </is>
       </c>
       <c r="G257" s="20" t="inlineStr">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="B258" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli cu impozitul pe venit si cu alte impozite</t>
+          <t>Cheltuieli cu impozitul pe venit și cu alte impozite</t>
         </is>
       </c>
       <c r="C258" s="20" t="inlineStr">
@@ -19613,7 +19613,7 @@
       </c>
       <c r="E258" s="20" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F258" s="20" t="n"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="B260" s="19" t="inlineStr">
         <is>
-          <t>Cifra de afaceri neta</t>
+          <t>Cifra de afaceri netă</t>
         </is>
       </c>
       <c r="C260" s="19" t="n"/>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="B261" s="22" t="inlineStr">
         <is>
-          <t>Venituri din vanzarea produselor finite</t>
+          <t>Venituri din vânzarea produselor finite</t>
         </is>
       </c>
       <c r="C261" s="22" t="inlineStr">
@@ -19746,7 +19746,7 @@
       </c>
       <c r="F262" s="22" t="inlineStr">
         <is>
-          <t>Cuplat contabil cu 301/7015 la productie.</t>
+          <t>Cuplat contabil cu 301/7015 la producție.</t>
         </is>
       </c>
       <c r="G262" s="22" t="inlineStr">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="B263" s="22" t="inlineStr">
         <is>
-          <t>Venituri din vanzarea marfurilor</t>
+          <t>Venituri din vânzarea mărfurilor</t>
         </is>
       </c>
       <c r="C263" s="22" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="F263" s="22" t="inlineStr">
         <is>
-          <t>Corelatie: 707-607 = rulaj D 378.</t>
+          <t>Corelație: 707-607 = rulaj D 378.</t>
         </is>
       </c>
       <c r="G263" s="22" t="inlineStr">
@@ -19830,7 +19830,7 @@
       </c>
       <c r="B264" s="20" t="inlineStr">
         <is>
-          <t>Venituri din activitati diverse</t>
+          <t>Venituri din activități diverse</t>
         </is>
       </c>
       <c r="C264" s="20" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="D265" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E265" s="22" t="inlineStr">
@@ -19918,7 +19918,7 @@
       </c>
       <c r="B266" s="19" t="inlineStr">
         <is>
-          <t>Venituri aferente costului productiei in curs de executie</t>
+          <t>Venituri aferente costului producției în curs de execuție</t>
         </is>
       </c>
       <c r="C266" s="19" t="n"/>
@@ -19948,7 +19948,7 @@
       </c>
       <c r="D267" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E267" s="22" t="inlineStr">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="F267" s="22" t="inlineStr">
         <is>
-          <t>Variatia stocurilor: tine 121 la zero cat timp produsul nu e livrat.</t>
+          <t>Variația stocurilor: ține 121 la zero cât timp produsul nu e livrat.</t>
         </is>
       </c>
       <c r="G267" s="22" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="B268" s="22" t="inlineStr">
         <is>
-          <t>Venituri aferente costurilor serviciilor in curs de executie</t>
+          <t>Venituri aferente costurilor serviciilor în curs de execuție</t>
         </is>
       </c>
       <c r="C268" s="22" t="inlineStr">
@@ -20000,7 +20000,7 @@
       </c>
       <c r="D268" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E268" s="22" t="inlineStr">
@@ -20010,7 +20010,7 @@
       </c>
       <c r="F268" s="22" t="inlineStr">
         <is>
-          <t>Neutralizeaza rezultatul pt. servicii in curs.</t>
+          <t>Neutralizează rezultatul pt. servicii în curs.</t>
         </is>
       </c>
       <c r="G268" s="22" t="inlineStr">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="B269" s="19" t="inlineStr">
         <is>
-          <t>Venituri din productia de imobilizari</t>
+          <t>Venituri din producția de imobilizări</t>
         </is>
       </c>
       <c r="C269" s="19" t="n"/>
@@ -20062,7 +20062,7 @@
       </c>
       <c r="B270" s="22" t="inlineStr">
         <is>
-          <t>Venituri din productia de imobilizari necorporale</t>
+          <t>Venituri din producția de imobilizări necorporale</t>
         </is>
       </c>
       <c r="C270" s="22" t="inlineStr">
@@ -20072,7 +20072,7 @@
       </c>
       <c r="D270" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E270" s="22" t="inlineStr">
@@ -20082,7 +20082,7 @@
       </c>
       <c r="F270" s="22" t="inlineStr">
         <is>
-          <t>Productie imobilizata: neutralizeaza cheltuiala capitalizata in cls.2.</t>
+          <t>Producție imobilizată: neutralizează cheltuială capitalizată în cls.2.</t>
         </is>
       </c>
       <c r="G270" s="22" t="inlineStr">
@@ -20114,7 +20114,7 @@
       </c>
       <c r="B271" s="22" t="inlineStr">
         <is>
-          <t>Venituri din productia de imobilizari corporale</t>
+          <t>Venituri din producția de imobilizări corporale</t>
         </is>
       </c>
       <c r="C271" s="22" t="inlineStr">
@@ -20124,7 +20124,7 @@
       </c>
       <c r="D271" s="22" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E271" s="22" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="F271" s="22" t="inlineStr">
         <is>
-          <t>Productie imobilizata.</t>
+          <t>Producție imobilizată.</t>
         </is>
       </c>
       <c r="G271" s="22" t="inlineStr">
@@ -20166,7 +20166,7 @@
       </c>
       <c r="B272" s="20" t="inlineStr">
         <is>
-          <t>Venituri din productia de investitii imobiliare</t>
+          <t>Venituri din producția de investiții imobiliare</t>
         </is>
       </c>
       <c r="C272" s="20" t="inlineStr">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="D272" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E272" s="23" t="inlineStr">
@@ -20186,7 +20186,7 @@
       </c>
       <c r="F272" s="20" t="inlineStr">
         <is>
-          <t>Productie imobilizata.</t>
+          <t>Producție imobilizată.</t>
         </is>
       </c>
       <c r="G272" s="20" t="inlineStr"/>
@@ -20206,7 +20206,7 @@
       </c>
       <c r="B273" s="19" t="inlineStr">
         <is>
-          <t>Venituri din subventii de exploatare</t>
+          <t>Venituri din subvenții de exploatare</t>
         </is>
       </c>
       <c r="C273" s="19" t="n"/>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="B274" s="20" t="inlineStr">
         <is>
-          <t>Venituri din subventii de exploatare</t>
+          <t>Venituri din subvenții de exploatare</t>
         </is>
       </c>
       <c r="C274" s="20" t="inlineStr">
@@ -20282,7 +20282,7 @@
       </c>
       <c r="B276" s="20" t="inlineStr">
         <is>
-          <t>Venituri din reluarea provizioanelor si a ajustarilor</t>
+          <t>Venituri din reluarea provizioanelor și a ajustărilor</t>
         </is>
       </c>
       <c r="C276" s="20" t="inlineStr">
@@ -20390,7 +20390,7 @@
       </c>
       <c r="B279" s="20" t="inlineStr">
         <is>
-          <t>Venituri din imobilizari financiare</t>
+          <t>Venituri din imobilizări financiare</t>
         </is>
       </c>
       <c r="C279" s="20" t="inlineStr">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="B280" s="20" t="inlineStr">
         <is>
-          <t>Venituri din investitii financiare pe termen scurt</t>
+          <t>Venituri din investiții financiare pe termen scurt</t>
         </is>
       </c>
       <c r="C280" s="20" t="inlineStr">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="B281" s="20" t="inlineStr">
         <is>
-          <t>Venituri din diferente de curs valutar</t>
+          <t>Venituri din diferențe de curs valutar</t>
         </is>
       </c>
       <c r="C281" s="20" t="inlineStr">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="B282" s="20" t="inlineStr">
         <is>
-          <t>Venituri din dobanzi</t>
+          <t>Venituri din dobânzi</t>
         </is>
       </c>
       <c r="C282" s="20" t="inlineStr">
@@ -20546,7 +20546,7 @@
       </c>
       <c r="B283" s="20" t="inlineStr">
         <is>
-          <t>Venituri din sconturi obtinute</t>
+          <t>Venituri din sconturi obținute</t>
         </is>
       </c>
       <c r="C283" s="20" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="B285" s="19" t="inlineStr">
         <is>
-          <t>Venituri din provizioane, amortizari si ajustari</t>
+          <t>Venituri din provizioane, amortizări și ajustări</t>
         </is>
       </c>
       <c r="C285" s="19" t="n"/>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="B286" s="22" t="inlineStr">
         <is>
-          <t>Venituri din provizioane si ajustari privind activitatea de exploatare</t>
+          <t>Venituri din provizioane și ajustări privind activitatea de exploatare</t>
         </is>
       </c>
       <c r="C286" s="22" t="inlineStr">
@@ -20658,7 +20658,7 @@
       </c>
       <c r="F286" s="22" t="inlineStr">
         <is>
-          <t>Reluari (reversari) la venit.</t>
+          <t>Reluări (reversări) la venit.</t>
         </is>
       </c>
       <c r="G286" s="22" t="inlineStr">
@@ -20690,7 +20690,7 @@
       </c>
       <c r="B287" s="20" t="inlineStr">
         <is>
-          <t>Venituri financiare din amortizari si ajustari</t>
+          <t>Venituri financiare din amortizări și ajustări</t>
         </is>
       </c>
       <c r="C287" s="20" t="inlineStr">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="B288" s="18" t="inlineStr">
         <is>
-          <t>CONTURI SPECIALE (in afara bilantului)</t>
+          <t>CONTURI SPECIALE (în afara bilanțului)</t>
         </is>
       </c>
       <c r="C288" s="18" t="n"/>
@@ -20750,7 +20750,7 @@
       </c>
       <c r="B289" s="19" t="inlineStr">
         <is>
-          <t>Conturi in afara bilantului</t>
+          <t>Conturi în afara bilanțului</t>
         </is>
       </c>
       <c r="C289" s="19" t="n"/>
@@ -20784,17 +20784,17 @@
       </c>
       <c r="D290" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E290" s="23" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="F290" s="20" t="inlineStr">
         <is>
-          <t>Garantii, giruri date.</t>
+          <t>Garanții, giruri date.</t>
         </is>
       </c>
       <c r="G290" s="20" t="inlineStr"/>
@@ -20824,17 +20824,17 @@
       </c>
       <c r="D291" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E291" s="23" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="F291" s="20" t="inlineStr">
         <is>
-          <t>Garantii primite.</t>
+          <t>Garanții primite.</t>
         </is>
       </c>
       <c r="G291" s="20" t="inlineStr"/>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="B292" s="20" t="inlineStr">
         <is>
-          <t>Alte conturi in afara bilantului</t>
+          <t>Alte conturi în afara bilanțului</t>
         </is>
       </c>
       <c r="C292" s="20" t="inlineStr">
@@ -20864,17 +20864,17 @@
       </c>
       <c r="D292" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E292" s="23" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="F292" s="20" t="inlineStr">
         <is>
-          <t>8035 = obiecte de inventar date in folosinta (memorie dupa 603=303).</t>
+          <t>8035 = obiecte de inventar date în folosință (memorie după 603=303).</t>
         </is>
       </c>
       <c r="G292" s="20" t="inlineStr"/>
@@ -20898,7 +20898,7 @@
       </c>
       <c r="B293" s="20" t="inlineStr">
         <is>
-          <t>Amortizarea aferenta gradului de neutilizare a mijloacelor fixe</t>
+          <t>Amortizarea aferentă gradului de neutilizare a mijloacelor fixe</t>
         </is>
       </c>
       <c r="C293" s="20" t="inlineStr">
@@ -20908,12 +20908,12 @@
       </c>
       <c r="D293" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E293" s="23" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="F293" s="20" t="n"/>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="B294" s="20" t="inlineStr">
         <is>
-          <t>Dobanzi aferente contractelor de leasing si altor contracte</t>
+          <t>Dobânzi aferente contractelor de leasing și altor contracte</t>
         </is>
       </c>
       <c r="C294" s="20" t="inlineStr">
@@ -20944,12 +20944,12 @@
       </c>
       <c r="D294" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E294" s="23" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="F294" s="20" t="n"/>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="B295" s="20" t="inlineStr">
         <is>
-          <t>Certificate de emisii de gaze cu efect de sera</t>
+          <t>Certificate de emisii de gaze cu efect de seră</t>
         </is>
       </c>
       <c r="C295" s="20" t="inlineStr">
@@ -20980,12 +20980,12 @@
       </c>
       <c r="D295" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E295" s="23" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="F295" s="20" t="n"/>
@@ -21016,12 +21016,12 @@
       </c>
       <c r="D296" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E296" s="23" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="F296" s="20" t="n"/>
@@ -21052,12 +21052,12 @@
       </c>
       <c r="D297" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E297" s="23" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="F297" s="20" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="B298" s="20" t="inlineStr">
         <is>
-          <t>Creante preluate prin cesionare</t>
+          <t>Creanțe preluate prin cesionare</t>
         </is>
       </c>
       <c r="C298" s="20" t="inlineStr">
@@ -21088,12 +21088,12 @@
       </c>
       <c r="D298" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E298" s="23" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="F298" s="20" t="n"/>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="B299" s="19" t="inlineStr">
         <is>
-          <t>Bilant</t>
+          <t>Bilanț</t>
         </is>
       </c>
       <c r="C299" s="19" t="n"/>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="B300" s="20" t="inlineStr">
         <is>
-          <t>Bilant de deschidere</t>
+          <t>Bilanț de deschidere</t>
         </is>
       </c>
       <c r="C300" s="20" t="inlineStr">
@@ -21148,17 +21148,17 @@
       </c>
       <c r="D300" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E300" s="23" t="inlineStr">
         <is>
-          <t>Tehnic - inchidere/deschidere</t>
+          <t>Tehnic - închidere/deschidere</t>
         </is>
       </c>
       <c r="F300" s="20" t="inlineStr">
         <is>
-          <t>Cont tehnic de deschidere a exercitiului.</t>
+          <t>Cont tehnic de deschidere a exercițiului.</t>
         </is>
       </c>
       <c r="G300" s="20" t="inlineStr"/>
@@ -21178,7 +21178,7 @@
       </c>
       <c r="B301" s="20" t="inlineStr">
         <is>
-          <t>Bilant de inchidere</t>
+          <t>Bilanț de închidere</t>
         </is>
       </c>
       <c r="C301" s="20" t="inlineStr">
@@ -21188,17 +21188,17 @@
       </c>
       <c r="D301" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E301" s="23" t="inlineStr">
         <is>
-          <t>Tehnic - inchidere/deschidere</t>
+          <t>Tehnic - închidere/deschidere</t>
         </is>
       </c>
       <c r="F301" s="20" t="inlineStr">
         <is>
-          <t>Cont tehnic de inchidere a exercitiului.</t>
+          <t>Cont tehnic de închidere a exercițiului.</t>
         </is>
       </c>
       <c r="G301" s="20" t="inlineStr"/>
@@ -21218,7 +21218,7 @@
       </c>
       <c r="B302" s="18" t="inlineStr">
         <is>
-          <t>CONTURI DE GESTIUNE (OMFP 1826/2003 - optional)</t>
+          <t>CONTURI DE GESTIUNE (OMFP 1826/2003 - opțional)</t>
         </is>
       </c>
       <c r="C302" s="18" t="n"/>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="B303" s="19" t="inlineStr">
         <is>
-          <t>Decontari interne</t>
+          <t>Decontări interne</t>
         </is>
       </c>
       <c r="C303" s="19" t="n"/>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="B304" s="20" t="inlineStr">
         <is>
-          <t>Decontari interne privind cheltuielile</t>
+          <t>Decontări interne privind cheltuielile</t>
         </is>
       </c>
       <c r="C304" s="20" t="inlineStr">
@@ -21276,7 +21276,7 @@
       </c>
       <c r="D304" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E304" s="23" t="inlineStr">
@@ -21286,7 +21286,7 @@
       </c>
       <c r="F304" s="20" t="inlineStr">
         <is>
-          <t>Oglinda interna a cheltuielilor din cls.6.</t>
+          <t>Oglinda internă a cheltuielilor din cls.6.</t>
         </is>
       </c>
       <c r="G304" s="20" t="inlineStr"/>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="B305" s="20" t="inlineStr">
         <is>
-          <t>Decontari interne privind productia obtinuta</t>
+          <t>Decontări interne privind producția obținută</t>
         </is>
       </c>
       <c r="C305" s="20" t="inlineStr">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="D305" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E305" s="23" t="inlineStr">
@@ -21342,7 +21342,7 @@
       </c>
       <c r="B306" s="20" t="inlineStr">
         <is>
-          <t>Decontari interne privind diferentele de pret</t>
+          <t>Decontări interne privind diferențele de preț</t>
         </is>
       </c>
       <c r="C306" s="20" t="inlineStr">
@@ -21352,7 +21352,7 @@
       </c>
       <c r="D306" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E306" s="23" t="inlineStr">
@@ -21378,7 +21378,7 @@
       </c>
       <c r="B307" s="19" t="inlineStr">
         <is>
-          <t>Conturi de calculatie</t>
+          <t>Conturi de calculație</t>
         </is>
       </c>
       <c r="C307" s="19" t="n"/>
@@ -21402,7 +21402,7 @@
       </c>
       <c r="B308" s="20" t="inlineStr">
         <is>
-          <t>Cheltuielile activitatii de baza</t>
+          <t>Cheltuielile activității de bază</t>
         </is>
       </c>
       <c r="C308" s="20" t="inlineStr">
@@ -21412,7 +21412,7 @@
       </c>
       <c r="D308" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E308" s="23" t="inlineStr">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="B309" s="20" t="inlineStr">
         <is>
-          <t>Cheltuielile activitatilor auxiliare</t>
+          <t>Cheltuielile activităților auxiliare</t>
         </is>
       </c>
       <c r="C309" s="20" t="inlineStr">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="D309" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E309" s="23" t="inlineStr">
@@ -21474,7 +21474,7 @@
       </c>
       <c r="B310" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli indirecte de productie</t>
+          <t>Cheltuieli indirecte de producție</t>
         </is>
       </c>
       <c r="C310" s="20" t="inlineStr">
@@ -21484,7 +21484,7 @@
       </c>
       <c r="D310" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E310" s="23" t="inlineStr">
@@ -21510,7 +21510,7 @@
       </c>
       <c r="B311" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli generale de administratie</t>
+          <t>Cheltuieli generale de administrație</t>
         </is>
       </c>
       <c r="C311" s="20" t="inlineStr">
@@ -21520,7 +21520,7 @@
       </c>
       <c r="D311" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E311" s="23" t="inlineStr">
@@ -21556,7 +21556,7 @@
       </c>
       <c r="D312" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E312" s="23" t="inlineStr">
@@ -21582,7 +21582,7 @@
       </c>
       <c r="B313" s="19" t="inlineStr">
         <is>
-          <t>Costul productiei</t>
+          <t>Costul producției</t>
         </is>
       </c>
       <c r="C313" s="19" t="n"/>
@@ -21606,7 +21606,7 @@
       </c>
       <c r="B314" s="20" t="inlineStr">
         <is>
-          <t>Costul productiei obtinute</t>
+          <t>Costul producției obținute</t>
         </is>
       </c>
       <c r="C314" s="20" t="inlineStr">
@@ -21616,7 +21616,7 @@
       </c>
       <c r="D314" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E314" s="23" t="inlineStr">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="B315" s="20" t="inlineStr">
         <is>
-          <t>Costul productiei in curs de executie</t>
+          <t>Costul producției în curs de execuție</t>
         </is>
       </c>
       <c r="C315" s="20" t="inlineStr">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="D315" s="23" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E315" s="23" t="inlineStr">
@@ -21685,7 +21685,7 @@
       </c>
       <c r="B318" s="66" t="inlineStr">
         <is>
-          <t>Imobilizari necorporale in curs de executie</t>
+          <t>Imobilizări necorporale în curs de execuție</t>
         </is>
       </c>
       <c r="C318" s="66" t="inlineStr">
@@ -21737,7 +21737,7 @@
       </c>
       <c r="B319" s="66" t="inlineStr">
         <is>
-          <t>Avansuri acordate pentru imobilizari corporale</t>
+          <t>Avansuri acordate pentru imobilizări corporale</t>
         </is>
       </c>
       <c r="C319" s="66" t="inlineStr">
@@ -21752,7 +21752,7 @@
       </c>
       <c r="E319" s="66" t="inlineStr">
         <is>
-          <t>Creanta</t>
+          <t>Creanță</t>
         </is>
       </c>
       <c r="F319" s="66" t="inlineStr">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="D322" s="66" t="inlineStr">
         <is>
-          <t>Rol in flux</t>
+          <t>Rol în flux</t>
         </is>
       </c>
       <c r="E322" s="66" t="inlineStr">
@@ -22012,7 +22012,7 @@
       </c>
       <c r="E324" s="66" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F324" s="66" t="inlineStr">
@@ -22116,7 +22116,7 @@
       </c>
       <c r="E326" s="66" t="inlineStr">
         <is>
-          <t>Cheltuiala</t>
+          <t>Cheltuială</t>
         </is>
       </c>
       <c r="F326" s="66" t="inlineStr">
@@ -22173,7 +22173,7 @@
       </c>
       <c r="F327" s="66" t="inlineStr">
         <is>
-          <t>Reluarea ajustării la valorificarea bunului — obligatorie prin lege. NEIMPOZABILĂ (art. 23 lit. d), ca să neutralizeze cheltuiala nedeductibilă din 6814.</t>
+          <t>Reluarea ajustării la valorificarea bunului — obligatorie prin lege. NEIMPOZABILĂ (art. 23 lit. d), ca să neutralizeze cheltuială nedeductibilă din 6814.</t>
         </is>
       </c>
       <c r="G327" s="66" t="inlineStr">
@@ -22220,7 +22220,7 @@
       </c>
       <c r="E328" s="66" t="inlineStr">
         <is>
-          <t>Creanta</t>
+          <t>Creanță</t>
         </is>
       </c>
       <c r="F328" s="66" t="inlineStr">
@@ -22298,7 +22298,7 @@
       </c>
       <c r="E1" s="17" t="inlineStr">
         <is>
-          <t>Observatie</t>
+          <t>Observație</t>
         </is>
       </c>
       <c r="F1" s="17" t="inlineStr">
@@ -22327,7 +22327,7 @@
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>Instalatii tehnice si mijloace de transport in curs de aprovizionare</t>
+          <t>Instalații tehnice și mijloace de transport în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C3" s="20" t="inlineStr">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="E3" s="20" t="inlineStr">
         <is>
-          <t>Ca 32x, dar pt. imobilizari: bun facturat, nereceptionat.</t>
+          <t>Ca 32x, dar pt. imobilizări: bun facturat, nerecepționat.</t>
         </is>
       </c>
       <c r="F3" s="20" t="inlineStr">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Mobilier, aparatura birotica... in curs de aprovizionare</t>
+          <t>Mobilier, aparatură birotică... în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
@@ -22374,7 +22374,7 @@
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
-          <t>Se stinge la receptie in 213/214.</t>
+          <t>Se stinge la recepție în 213/214.</t>
         </is>
       </c>
       <c r="F4" s="20" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>Materii prime in curs de aprovizionare</t>
+          <t>Materii prime în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -22406,7 +22406,7 @@
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>Factura in SPV, marfa pe drum. Se stinge 301=321 la receptie.</t>
+          <t>Factura în SPV, marfă pe drum. Se stinge 301=321 la recepție.</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Materiale consumabile in curs de aprovizionare</t>
+          <t>Materiale consumabile în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -22455,7 +22455,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Materiale de natura obiectelor de inventar in curs de aprovizionare</t>
+          <t>Materiale de natura obiectelor de inventar în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -22487,7 +22487,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Active biologice de natura stocurilor in curs de aprovizionare</t>
+          <t>Active biologice de natura stocurilor în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -22515,7 +22515,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>Marfuri in curs de aprovizionare</t>
+          <t>Mărfuri în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -22547,7 +22547,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Ambalaje in curs de aprovizionare</t>
+          <t>Ambalaje în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -22579,7 +22579,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>TVA deductibila</t>
+          <t>TVA deductibilă</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -22594,7 +22594,7 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>Colecteaza TVA din cumparari in cursul lunii; se inchide in 4423/4424. Fara sold.</t>
+          <t>Colectează TVA din cumpărări în cursul lunii; se închide în 4423/4424. Fără sold.</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>TVA colectata</t>
+          <t>TVA colectată</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Colecteaza TVA din vanzari; se inchide in 4423/4424. Fara sold.</t>
+          <t>Colectează TVA din vânzări; se închide în 4423/4424. Fără sold.</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -22670,7 +22670,7 @@
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>Marfa a sosit, factura NU. Oglinda lui 327. Se stinge 408=401.</t>
+          <t>Marfă a sosit, factura NU. Oglinda lui 327. Se stinge 408=401.</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>Clienti - facturi de intocmit</t>
+          <t>Clienți - facturi de întocmit</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -22702,7 +22702,7 @@
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>Livrat/prestat, nefacturat inca. Se stinge 418=4111.</t>
+          <t>Livrat/prestat, nefacturat încă. Se stinge 418=4111.</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -22719,7 +22719,7 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>Decontari din operatiuni in curs de clarificare</t>
+          <t>Decontări din operațiuni în curs de clarificare</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -22734,7 +22734,7 @@
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>CANONIC: suma neidentificata din extras; sold la 31.12 = suspect.</t>
+          <t>CANONIC: suma neidentificată din extras; sold la 31.12 = suspect.</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -22766,7 +22766,7 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>Transfer banca&lt;-&gt;casa/banca; evita dubla numarare pana la confirmare.</t>
+          <t>Transfer banca&lt;-&gt;casa/banca; evită dublă numărare până la confirmare.</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -22795,7 +22795,7 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>Actiuni proprii</t>
+          <t>Acțiuni proprii</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>Contra-capital: rascumparari proprii, se deduc din capitaluri.</t>
+          <t>Contra-capital: răscumpărări proprii, se deduc din capitaluri.</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -22859,7 +22859,7 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>Prime privind rambursarea obligatiunilor si a altor datorii</t>
+          <t>Prime privind rambursarea obligațiunilor și a altor datorii</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>Contra-datorie: discount la obligatiuni, se deduce din 161.</t>
+          <t>Contra-datorie: discount la obligațiuni, se deduce din 161.</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -22891,7 +22891,7 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Amortizari privind imobilizarile necorporale</t>
+          <t>Amortizări privind imobilizările necorporale</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -22906,7 +22906,7 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Contra-activ: cumuleaza uzura, se scade din valoarea bruta.</t>
+          <t>Contra-activ: cumulează uzura, se scade din valoarea brută.</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -22923,7 +22923,7 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>Amortizari privind imobilizarile corporale</t>
+          <t>Amortizări privind imobilizările corporale</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -22955,7 +22955,7 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea imobilizarilor necorporale</t>
+          <t>Ajustări pentru deprecierea imobilizărilor necorporale</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -22970,7 +22970,7 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Contra-activ: depreciere reversibila.</t>
+          <t>Contra-activ: depreciere reversibilă.</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -22987,7 +22987,7 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea imobilizarilor corporale</t>
+          <t>Ajustări pentru deprecierea imobilizărilor corporale</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea imobilizarilor in curs</t>
+          <t>Ajustări pentru deprecierea imobilizărilor în curs</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -23051,7 +23051,7 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru pierderea de valoare a imobilizarilor financiare</t>
+          <t>Ajustări pentru pierderea de valoare a imobilizărilor financiare</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -23083,7 +23083,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Diferente de pret la materii prime si materiale</t>
+          <t>Diferențe de preț la materii prime și materiale</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -23098,7 +23098,7 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Contra-stoc: diferente fata de pretul standard/inregistrare.</t>
+          <t>Contra-stoc: diferențe fata de prețul standard/înregistrare.</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -23115,7 +23115,7 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>Diferente de pret la produse</t>
+          <t>Diferențe de preț la produse</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -23147,7 +23147,7 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Diferente de pret la active biologice de natura stocurilor</t>
+          <t>Diferențe de preț la active biologice de natura stocurilor</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -23179,7 +23179,7 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>Diferente de pret la marfuri</t>
+          <t>Diferențe de preț la mărfuri</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -23194,7 +23194,7 @@
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>Adaosul comercial (amanunt). Corelatie: 707-607 = rulaj D 378.</t>
+          <t>Adaosul comercial (amănunt). Corelație: 707-607 = rulaj D 378.</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Diferente de pret la ambalaje</t>
+          <t>Diferențe de preț la ambalaje</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -23243,7 +23243,7 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea materiilor prime</t>
+          <t>Ajustări pentru deprecierea materiilor prime</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -23275,7 +23275,7 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea materialelor</t>
+          <t>Ajustări pentru deprecierea materialelor</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -23307,7 +23307,7 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea productiei in curs de executie</t>
+          <t>Ajustări pentru deprecierea producției în curs de execuție</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -23339,7 +23339,7 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea produselor</t>
+          <t>Ajustări pentru deprecierea produselor</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -23371,7 +23371,7 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea stocurilor aflate la terti</t>
+          <t>Ajustări pentru deprecierea stocurilor aflate la terți</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea activelor biologice de natura stocurilor</t>
+          <t>Ajustări pentru deprecierea activelor biologice de natura stocurilor</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
@@ -23435,7 +23435,7 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea marfurilor</t>
+          <t>Ajustări pentru deprecierea mărfurilor</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
@@ -23467,7 +23467,7 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea ambalajelor</t>
+          <t>Ajustări pentru deprecierea ambalajelor</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
@@ -23499,7 +23499,7 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea creantelor - avansuri acordate furnizorilor</t>
+          <t>Ajustări pentru deprecierea creanțelor - avansuri acordate furnizorilor</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
@@ -23514,7 +23514,7 @@
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>Contra-creanta.</t>
+          <t>Contra-creanță.</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -23531,7 +23531,7 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea creantelor - clienti</t>
+          <t>Ajustări pentru deprecierea creanțelor - clienți</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Contra-creanta.</t>
+          <t>Contra-creanță.</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
@@ -23563,7 +23563,7 @@
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea creantelor - grup si actionari/asociati</t>
+          <t>Ajustări pentru deprecierea creanțelor - grup și acționari/asociați</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
@@ -23578,7 +23578,7 @@
       </c>
       <c r="E43" s="20" t="inlineStr">
         <is>
-          <t>Contra-creanta.</t>
+          <t>Contra-creanță.</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru deprecierea creantelor - debitori diversi</t>
+          <t>Ajustări pentru deprecierea creanțelor - debitori diverși</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
@@ -23610,7 +23610,7 @@
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Contra-creanta.</t>
+          <t>Contra-creanță.</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
@@ -23627,7 +23627,7 @@
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>Ajustari pentru pierderea de valoare a actiunilor la entitati afiliate</t>
+          <t>Ajustări pentru pierderea de valoare a acțiunilor la entități afiliate</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
@@ -23659,7 +23659,7 @@
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Ajustari... obligatiuni emise si rascumparate</t>
+          <t>Ajustări... obligațiuni emise și răscumpărate</t>
         </is>
       </c>
       <c r="C46" s="20" t="inlineStr">
@@ -23691,7 +23691,7 @@
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>Ajustari... obligatiuni</t>
+          <t>Ajustări... obligațiuni</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
@@ -23723,7 +23723,7 @@
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Ajustari... alte investitii pe termen scurt</t>
+          <t>Ajustări... alte investiții pe termen scurt</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
@@ -23770,7 +23770,7 @@
       </c>
       <c r="E49" s="20" t="inlineStr">
         <is>
-          <t>Contra-cheltuiala: reduce costul achizitiilor.</t>
+          <t>Contra-cheltuială: reduce costul achizițiilor.</t>
         </is>
       </c>
       <c r="F49" s="20" t="inlineStr">
@@ -23831,7 +23831,7 @@
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli inregistrate in avans</t>
+          <t>Cheltuieli înregistrate în avans</t>
         </is>
       </c>
       <c r="C52" s="20" t="inlineStr">
@@ -23841,12 +23841,12 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Regularizare temporala</t>
+          <t>Regularizare temporală</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Se elibereaza sistematic cu trecerea timpului (ex. asigurare 1/12).</t>
+          <t>Se eliberează sistematic cu trecerea timpului (ex. asigurare 1/12).</t>
         </is>
       </c>
       <c r="F52" s="20" t="inlineStr">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>Venituri inregistrate in avans</t>
+          <t>Venituri înregistrate în avans</t>
         </is>
       </c>
       <c r="C53" s="20" t="inlineStr">
@@ -23873,12 +23873,12 @@
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
-          <t>Regularizare temporala</t>
+          <t>Regularizare temporală</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
-          <t>Se elibereaza la venit pe masura trecerii timpului.</t>
+          <t>Se eliberează la venit pe măsura trecerii timpului.</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
@@ -23895,7 +23895,7 @@
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>Subventii pentru investitii</t>
+          <t>Subvenții pentru investiții</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
@@ -23905,12 +23905,12 @@
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Regularizare temporala</t>
+          <t>Regularizare temporală</t>
         </is>
       </c>
       <c r="E54" s="22" t="inlineStr">
         <is>
-          <t>CORECTIE: cod actual (nu 131 din vechiul 3055). Se trece la venit pe masura amortizarii activului.</t>
+          <t>CORECȚIE: cod actual (nu 131 din vechiul 3055). Se trece la venit pe măsura amortizării activului.</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
@@ -23927,7 +23927,7 @@
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>Venituri in avans aferente activelor primite prin transfer de la clienti</t>
+          <t>Venituri în avans aferente activelor primite prin transfer de la clienți</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
@@ -23937,7 +23937,7 @@
       </c>
       <c r="D55" s="20" t="inlineStr">
         <is>
-          <t>Regularizare temporala</t>
+          <t>Regularizare temporală</t>
         </is>
       </c>
       <c r="E55" s="20" t="n"/>
@@ -23982,7 +23982,7 @@
       </c>
       <c r="E57" s="22" t="inlineStr">
         <is>
-          <t>Variatia stocurilor: tine 121 la zero cat timp produsul nu e livrat.</t>
+          <t>Variația stocurilor: ține 121 la zero cât timp produsul nu e livrat.</t>
         </is>
       </c>
       <c r="F57" s="22" t="inlineStr">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Venituri aferente costurilor serviciilor in curs de executie</t>
+          <t>Venituri aferente costurilor serviciilor în curs de execuție</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr">
@@ -24014,7 +24014,7 @@
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Neutralizeaza rezultatul pt. servicii in curs.</t>
+          <t>Neutralizează rezultatul pt. servicii în curs.</t>
         </is>
       </c>
       <c r="F58" s="20" t="inlineStr">
@@ -24031,7 +24031,7 @@
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>Venituri din productia de imobilizari necorporale</t>
+          <t>Venituri din producția de imobilizări necorporale</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
@@ -24046,7 +24046,7 @@
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>Productie imobilizata: neutralizeaza cheltuiala capitalizata in cls.2.</t>
+          <t>Producție imobilizată: neutralizează cheltuială capitalizată în cls.2.</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
@@ -24063,7 +24063,7 @@
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>Venituri din productia de imobilizari corporale</t>
+          <t>Venituri din producția de imobilizări corporale</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
@@ -24078,7 +24078,7 @@
       </c>
       <c r="E60" s="22" t="inlineStr">
         <is>
-          <t>Productie imobilizata.</t>
+          <t>Producție imobilizată.</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>Venituri din productia de investitii imobiliare</t>
+          <t>Venituri din producția de investiții imobiliare</t>
         </is>
       </c>
       <c r="C61" s="20" t="inlineStr">
@@ -24110,7 +24110,7 @@
       </c>
       <c r="E61" s="20" t="inlineStr">
         <is>
-          <t>Productie imobilizata.</t>
+          <t>Producție imobilizată.</t>
         </is>
       </c>
       <c r="F61" s="20" t="inlineStr">
@@ -24154,7 +24154,7 @@
       </c>
       <c r="E63" s="22" t="inlineStr">
         <is>
-          <t>Colecteaza toate cls.6 si 7 la inchidere; nu tine nimic real.</t>
+          <t>Colectează toate cls.6 și 7 la închidere; nu ține nimic real.</t>
         </is>
       </c>
       <c r="F63" s="22" t="inlineStr">
@@ -24215,7 +24215,7 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Decontari intre unitate si subunitati</t>
+          <t>Decontări între unitate și subunități</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
@@ -24225,12 +24225,12 @@
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>Decontare interna</t>
+          <t>Decontare internă</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Sold reciproc unitate-subunitate; se elimina.</t>
+          <t>Sold reciproc unitate-subunitate; se elimină.</t>
         </is>
       </c>
       <c r="F66" s="20" t="inlineStr">
@@ -24247,7 +24247,7 @@
       </c>
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>Decontari intre subunitati</t>
+          <t>Decontări între subunități</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr">
@@ -24257,12 +24257,12 @@
       </c>
       <c r="D67" s="20" t="inlineStr">
         <is>
-          <t>Decontare interna</t>
+          <t>Decontare internă</t>
         </is>
       </c>
       <c r="E67" s="20" t="inlineStr">
         <is>
-          <t>Se elimina la centralizare.</t>
+          <t>Se elimină la centralizare.</t>
         </is>
       </c>
       <c r="F67" s="20" t="inlineStr">
@@ -24291,7 +24291,7 @@
       </c>
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>Decontari interne privind cheltuielile</t>
+          <t>Decontări interne privind cheltuielile</t>
         </is>
       </c>
       <c r="C69" s="20" t="inlineStr">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>Oglinda interna a cheltuielilor din cls.6.</t>
+          <t>Oglinda internă a cheltuielilor din cls.6.</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
@@ -24323,7 +24323,7 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Decontari interne privind productia obtinuta</t>
+          <t>Decontări interne privind producția obținută</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
@@ -24351,7 +24351,7 @@
       </c>
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>Decontari interne privind diferentele de pret</t>
+          <t>Decontări interne privind diferențele de preț</t>
         </is>
       </c>
       <c r="C71" s="20" t="inlineStr">
@@ -24379,7 +24379,7 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Cheltuielile activitatii de baza</t>
+          <t>Cheltuielile activității de bază</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
@@ -24407,7 +24407,7 @@
       </c>
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>Cheltuielile activitatilor auxiliare</t>
+          <t>Cheltuielile activităților auxiliare</t>
         </is>
       </c>
       <c r="C73" s="20" t="inlineStr">
@@ -24435,7 +24435,7 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli indirecte de productie</t>
+          <t>Cheltuieli indirecte de producție</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
@@ -24463,7 +24463,7 @@
       </c>
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>Cheltuieli generale de administratie</t>
+          <t>Cheltuieli generale de administrație</t>
         </is>
       </c>
       <c r="C75" s="20" t="inlineStr">
@@ -24519,7 +24519,7 @@
       </c>
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>Costul productiei obtinute</t>
+          <t>Costul producției obținute</t>
         </is>
       </c>
       <c r="C77" s="20" t="inlineStr">
@@ -24547,7 +24547,7 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Costul productiei in curs de executie</t>
+          <t>Costul producției în curs de execuție</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
@@ -24597,12 +24597,12 @@
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Garantii, giruri date.</t>
+          <t>Garanții, giruri date.</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
@@ -24629,12 +24629,12 @@
       </c>
       <c r="D81" s="20" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
-          <t>Garantii primite.</t>
+          <t>Garanții primite.</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
@@ -24651,7 +24651,7 @@
       </c>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>Alte conturi in afara bilantului</t>
+          <t>Alte conturi în afara bilanțului</t>
         </is>
       </c>
       <c r="C82" s="22" t="inlineStr">
@@ -24661,12 +24661,12 @@
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="E82" s="22" t="inlineStr">
         <is>
-          <t>8035 = obiecte de inventar date in folosinta (memorie dupa 603=303).</t>
+          <t>8035 = obiecte de inventar date în folosință (memorie după 603=303).</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
@@ -24683,7 +24683,7 @@
       </c>
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>Amortizarea aferenta gradului de neutilizare a mijloacelor fixe</t>
+          <t>Amortizarea aferentă gradului de neutilizare a mijloacelor fixe</t>
         </is>
       </c>
       <c r="C83" s="20" t="inlineStr">
@@ -24693,7 +24693,7 @@
       </c>
       <c r="D83" s="20" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="E83" s="20" t="n"/>
@@ -24711,7 +24711,7 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Dobanzi aferente contractelor de leasing si altor contracte</t>
+          <t>Dobânzi aferente contractelor de leasing și altor contracte</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
@@ -24721,7 +24721,7 @@
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="E84" s="20" t="n"/>
@@ -24739,7 +24739,7 @@
       </c>
       <c r="B85" s="20" t="inlineStr">
         <is>
-          <t>Certificate de emisii de gaze cu efect de sera</t>
+          <t>Certificate de emisii de gaze cu efect de seră</t>
         </is>
       </c>
       <c r="C85" s="20" t="inlineStr">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="D85" s="20" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="E85" s="20" t="n"/>
@@ -24777,7 +24777,7 @@
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="E86" s="20" t="n"/>
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D87" s="20" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="E87" s="20" t="n"/>
@@ -24823,7 +24823,7 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>Creante preluate prin cesionare</t>
+          <t>Creanțe preluate prin cesionare</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
@@ -24833,7 +24833,7 @@
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
-          <t>Extrabilantier / memorie</t>
+          <t>Extrabilanțier / memorie</t>
         </is>
       </c>
       <c r="E88" s="20" t="n"/>
@@ -24863,7 +24863,7 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Bilant de deschidere</t>
+          <t>Bilanț de deschidere</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
@@ -24873,12 +24873,12 @@
       </c>
       <c r="D90" s="20" t="inlineStr">
         <is>
-          <t>Tehnic - inchidere/deschidere</t>
+          <t>Tehnic - închidere/deschidere</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Cont tehnic de deschidere a exercitiului.</t>
+          <t>Cont tehnic de deschidere a exercițiului.</t>
         </is>
       </c>
       <c r="F90" s="20" t="inlineStr">
@@ -24895,7 +24895,7 @@
       </c>
       <c r="B91" s="20" t="inlineStr">
         <is>
-          <t>Bilant de inchidere</t>
+          <t>Bilanț de închidere</t>
         </is>
       </c>
       <c r="C91" s="20" t="inlineStr">
@@ -24905,12 +24905,12 @@
       </c>
       <c r="D91" s="20" t="inlineStr">
         <is>
-          <t>Tehnic - inchidere/deschidere</t>
+          <t>Tehnic - închidere/deschidere</t>
         </is>
       </c>
       <c r="E91" s="20" t="inlineStr">
         <is>
-          <t>Cont tehnic de inchidere a exercitiului.</t>
+          <t>Cont tehnic de închidere a exercițiului.</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1881,7 +1881,7 @@
     <row r="116">
       <c r="A116" s="61" t="inlineStr">
         <is>
-          <t>Module_Declarative_Fluxuri.xlsx — 17 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
+          <t>Module_Declarative_Fluxuri.xlsx — 18 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="E43" s="66" t="inlineStr">
         <is>
-          <t>F-416 pas 3: indemnizația trece prin datorie, dar numai o parte e cheltuială</t>
+          <t>F-416 pas 3: indemnizația trece prin datorie, dar numai o parte e cheltuială | modul: MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="F43" s="66" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E44" s="66" t="inlineStr">
         <is>
-          <t>F-418 pas 3: datoria nu dispare, se reclasifică — corelația cu statul revine</t>
+          <t>F-418 pas 3: datoria nu dispare, se reclasifică — corelația cu statul revine | modul: MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="F44" s="66" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="E45" s="66" t="inlineStr">
         <is>
-          <t>F-417 pas 2: firma e conductă — intră și iese cu aceeași sumă</t>
+          <t>F-417 pas 2: firma e conductă — intră și iese cu aceeași sumă | modul: MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="F45" s="66" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="E46" s="66" t="inlineStr">
         <is>
-          <t>F-419 pas 2: la încasare crește un activ și scade altul</t>
+          <t>F-419 pas 2: la încasare crește un activ și scade altul | modul: MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="F46" s="66" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="E47" s="66" t="inlineStr">
         <is>
-          <t>F-416 pas 3: creanță, nu cheltuială — firma a avansat banii casei</t>
+          <t>F-416 pas 3: creanță, nu cheltuială — firma a avansat banii casei | modul: MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="F47" s="66" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="E66" s="66" t="inlineStr">
         <is>
-          <t>F-416 pas 1: partea de indemnizație suportată efectiv de angajator</t>
+          <t>F-416 pas 1: partea de indemnizație suportată efectiv de angajator | modul: MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="F66" s="66" t="inlineStr">
@@ -8921,7 +8921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9244,17 +9244,17 @@
     <row r="13">
       <c r="A13" s="66" t="inlineStr">
         <is>
-          <t>MOD_DECONT</t>
+          <t>MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="B13" s="66" t="inlineStr">
         <is>
-          <t>F-502</t>
+          <t>F-416, F-417, F-418, F-419</t>
         </is>
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>B1 Avans; B2 Cheltuieli + TVA; B3 Regularizare avans; B4 Plată / restituire</t>
+          <t>42x: medicale, popriri, drepturi neridicate, creanțe față de foști salariați</t>
         </is>
       </c>
       <c r="D13" s="66" t="inlineStr">
@@ -9264,29 +9264,29 @@
       </c>
       <c r="E13" s="66" t="inlineStr">
         <is>
-          <t>Declarații_DECONT, Reguli_DECONT, Registru_DECONT, Jurnale_DECONT, NotaExport_DECONT</t>
+          <t>Declarații_SALARII_EVENIMENTE, Reguli_SALARII_EVENIMENTE, Jurnale_SALARII_EVENIMENTE, NotaExport_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="F13" s="66" t="inlineStr">
         <is>
-          <t>Pe decont</t>
+          <t>Pe eveniment, lângă statul lunar</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="66" t="inlineStr">
         <is>
-          <t>MOD_INTERMEDIAR</t>
+          <t>MOD_DECONT</t>
         </is>
       </c>
       <c r="B14" s="66" t="inlineStr">
         <is>
-          <t>F-408, F-501, F-411</t>
+          <t>F-502</t>
         </is>
       </c>
       <c r="C14" s="66" t="inlineStr">
         <is>
-          <t>408/418/473: deschidere + stingere + red flags</t>
+          <t>B1 Avans; B2 Cheltuieli + TVA; B3 Regularizare avans; B4 Plată / restituire</t>
         </is>
       </c>
       <c r="D14" s="66" t="inlineStr">
@@ -9296,29 +9296,29 @@
       </c>
       <c r="E14" s="66" t="inlineStr">
         <is>
-          <t>Declarații_INTERMEDIAR, Reguli_INTERMEDIAR, Jurnale_INTERMEDIAR, NotaExport_INTERMEDIAR</t>
+          <t>Declarații_DECONT, Reguli_DECONT, Registru_DECONT, Jurnale_DECONT, NotaExport_DECONT</t>
         </is>
       </c>
       <c r="F14" s="66" t="inlineStr">
         <is>
-          <t>La facturi nesosite / sume neclare</t>
+          <t>Pe decont</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="66" t="inlineStr">
         <is>
-          <t>MOD_INCHIDERE_TVA</t>
+          <t>MOD_INTERMEDIAR</t>
         </is>
       </c>
       <c r="B15" s="66" t="inlineStr">
         <is>
-          <t>F-405</t>
+          <t>F-408, F-501, F-411</t>
         </is>
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>Închidere 4426/4427 → 4423/4424</t>
+          <t>408/418/473: deschidere + stingere + red flags</t>
         </is>
       </c>
       <c r="D15" s="66" t="inlineStr">
@@ -9328,29 +9328,29 @@
       </c>
       <c r="E15" s="66" t="inlineStr">
         <is>
-          <t>Declarații_INCHIDERE_TVA, Reguli_INCHIDERE_TVA, Jurnale_INCHIDERE_TVA, NotaExport_INCHIDERE_TVA</t>
+          <t>Declarații_INTERMEDIAR, Reguli_INTERMEDIAR, Jurnale_INTERMEDIAR, NotaExport_INTERMEDIAR</t>
         </is>
       </c>
       <c r="F15" s="66" t="inlineStr">
         <is>
-          <t>La fiecare lună, după rulaje TVA</t>
+          <t>La facturi nesosite / sume neclare</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="66" t="inlineStr">
         <is>
-          <t>MOD_APROV_TRANZIT</t>
+          <t>MOD_INCHIDERE_TVA</t>
         </is>
       </c>
       <c r="B16" s="66" t="inlineStr">
         <is>
-          <t>F-302</t>
+          <t>F-405</t>
         </is>
       </c>
       <c r="C16" s="66" t="inlineStr">
         <is>
-          <t>32x: factură înainte de marfă / NIR înainte de factură</t>
+          <t>Închidere 4426/4427 → 4423/4424</t>
         </is>
       </c>
       <c r="D16" s="66" t="inlineStr">
@@ -9360,29 +9360,29 @@
       </c>
       <c r="E16" s="66" t="inlineStr">
         <is>
-          <t>Declarații_APROV_TRANZIT, Reguli_APROV_TRANZIT, Jurnale_APROV_TRANZIT, NotaExport_APROV_TRANZIT</t>
+          <t>Declarații_INCHIDERE_TVA, Reguli_INCHIDERE_TVA, Jurnale_INCHIDERE_TVA, NotaExport_INCHIDERE_TVA</t>
         </is>
       </c>
       <c r="F16" s="66" t="inlineStr">
         <is>
-          <t>La aprovizionări incomplete</t>
+          <t>La fiecare lună, după rulaje TVA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="66" t="inlineStr">
         <is>
-          <t>MOD_INCHIDERE_EX</t>
+          <t>MOD_APROV_TRANZIT</t>
         </is>
       </c>
       <c r="B17" s="66" t="inlineStr">
         <is>
-          <t>F-104</t>
+          <t>F-302</t>
         </is>
       </c>
       <c r="C17" s="66" t="inlineStr">
         <is>
-          <t>Închidere cls.6/7 pe 121; impozit; report 117</t>
+          <t>32x: factură înainte de marfă / NIR înainte de factură</t>
         </is>
       </c>
       <c r="D17" s="66" t="inlineStr">
@@ -9392,29 +9392,29 @@
       </c>
       <c r="E17" s="66" t="inlineStr">
         <is>
-          <t>Declarații_INCHIDERE_EX, Reguli_INCHIDERE_EX, Jurnale_INCHIDERE_EX, NotaExport_INCHIDERE_EX</t>
+          <t>Declarații_APROV_TRANZIT, Reguli_APROV_TRANZIT, Jurnale_APROV_TRANZIT, NotaExport_APROV_TRANZIT</t>
         </is>
       </c>
       <c r="F17" s="66" t="inlineStr">
         <is>
-          <t>La 31.12</t>
+          <t>La aprovizionări incomplete</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="66" t="inlineStr">
         <is>
-          <t>MOD_TVA_INCASARE</t>
+          <t>MOD_INCHIDERE_EX</t>
         </is>
       </c>
       <c r="B18" s="66" t="inlineStr">
         <is>
-          <t>F-401</t>
+          <t>F-104</t>
         </is>
       </c>
       <c r="C18" s="66" t="inlineStr">
         <is>
-          <t>4428.INC: factură → plată/încasare → 4426/4427</t>
+          <t>Închidere cls.6/7 pe 121; impozit; report 117</t>
         </is>
       </c>
       <c r="D18" s="66" t="inlineStr">
@@ -9424,29 +9424,29 @@
       </c>
       <c r="E18" s="66" t="inlineStr">
         <is>
-          <t>Declarații_TVA_INC, Reguli_TVA_INC, Jurnale_TVA_INC, NotaExport_TVA_INC</t>
+          <t>Declarații_INCHIDERE_EX, Reguli_INCHIDERE_EX, Jurnale_INCHIDERE_EX, NotaExport_INCHIDERE_EX</t>
         </is>
       </c>
       <c r="F18" s="66" t="inlineStr">
         <is>
-          <t>Când regimul e TVA la încasare</t>
+          <t>La 31.12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="66" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE</t>
+          <t>MOD_TVA_INCASARE</t>
         </is>
       </c>
       <c r="B19" s="66" t="inlineStr">
         <is>
-          <t>F-311, F-312, F-209</t>
+          <t>F-401</t>
         </is>
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>711/712/722: lanț complet producție / servicii / MF</t>
+          <t>4428.INC: factură → plată/încasare → 4426/4427</t>
         </is>
       </c>
       <c r="D19" s="66" t="inlineStr">
@@ -9456,29 +9456,29 @@
       </c>
       <c r="E19" s="66" t="inlineStr">
         <is>
-          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
+          <t>Declarații_TVA_INC, Reguli_TVA_INC, Jurnale_TVA_INC, NotaExport_TVA_INC</t>
         </is>
       </c>
       <c r="F19" s="66" t="inlineStr">
         <is>
-          <t>La producție / servicii în curs</t>
+          <t>Când regimul e TVA la încasare</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="66" t="inlineStr">
         <is>
-          <t>MOD_VANZ_AMANUNT</t>
+          <t>MOD_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="B20" s="66" t="inlineStr">
         <is>
-          <t>F-316, F-318, F-317</t>
+          <t>F-311, F-312, F-209</t>
         </is>
       </c>
       <c r="C20" s="66" t="inlineStr">
         <is>
-          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
+          <t>711/712/722: lanț complet producție / servicii / MF</t>
         </is>
       </c>
       <c r="D20" s="66" t="inlineStr">
@@ -9488,98 +9488,130 @@
       </c>
       <c r="E20" s="66" t="inlineStr">
         <is>
-          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="F20" s="66" t="inlineStr">
         <is>
-          <t>La operațiuni amănunt + închidere lună amănunt</t>
+          <t>La producție / servicii în curs</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="66" t="inlineStr">
         <is>
+          <t>MOD_VANZ_AMANUNT</t>
+        </is>
+      </c>
+      <c r="B21" s="66" t="inlineStr">
+        <is>
+          <t>F-316, F-318, F-317</t>
+        </is>
+      </c>
+      <c r="C21" s="66" t="inlineStr">
+        <is>
+          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
+        </is>
+      </c>
+      <c r="D21" s="66" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+      <c r="E21" s="66" t="inlineStr">
+        <is>
+          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+        </is>
+      </c>
+      <c r="F21" s="66" t="inlineStr">
+        <is>
+          <t>La operațiuni amănunt + închidere lună amănunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="66" t="inlineStr">
+        <is>
           <t>MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="B21" s="66" t="inlineStr">
+      <c r="B22" s="66" t="inlineStr">
         <is>
           <t>F-422, F-413</t>
         </is>
       </c>
-      <c r="C21" s="66" t="inlineStr">
+      <c r="C22" s="66" t="inlineStr">
         <is>
           <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
         </is>
       </c>
-      <c r="D21" s="66" t="inlineStr">
+      <c r="D22" s="66" t="inlineStr">
         <is>
           <t>IMPLEMENTAT</t>
         </is>
       </c>
-      <c r="E21" s="66" t="inlineStr">
+      <c r="E22" s="66" t="inlineStr">
         <is>
           <t>Declarații_INCHIDERE_LUNARA, Reguli_INCHIDERE_LUNARA, Verificări_INCHIDERE_LUNARA, Abateri_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="F21" s="66" t="inlineStr">
+      <c r="F22" s="66" t="inlineStr">
         <is>
           <t>Lunar, pe balanța de verificare</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="36" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>CUM SE NAVIGHEAZĂ (cele două grafuri, acum sincronizate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="33" t="inlineStr">
-        <is>
-          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="33" t="inlineStr">
         <is>
-          <t>2. Pe corelație: Corelații de control → C-01…C-29 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
+          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="33" t="inlineStr">
         <is>
-          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
+          <t>2. Pe corelație: Corelații de control → C-01…C-29 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="33" t="inlineStr">
         <is>
-          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="33" t="inlineStr">
         <is>
+          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
           <t>5. Pe modul: CatalogModule (în Module_Declarative…) → Activ=DA → completezi Declarații → notele se generează.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="38" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>INVARIANT: orice cont Tier A din Plan de conturi duce (via Flux pas) la toate fluxurile relevante, inclusiv F-304…F-802 pe cazurile grele (371, 378, 4428, 32x, 408, 331, 711, 8035).</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="63" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="63" t="inlineStr">
         <is>
           <t>MOD_CAPITALURI nu dublează MOD_INCHIDERE_EX: acela închide clasele 6 și 7 pe 121, acesta repartizează rezultatul obținut (129/1061/1171).</t>
         </is>
@@ -9587,13 +9619,13 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
@@ -29844,7 +29876,7 @@
       </c>
       <c r="H71" s="69" t="inlineStr">
         <is>
-          <t>Prima zi de concediu medical pentru boală obișnuită NU se plătește, februarie 2026 – decembrie 2027; regula nu se aplică urgențelor, accidentelor de muncă, sarcinii și carantinei. Baza: media veniturilor brute din ultimele 6 luni, plafonată la 12 salarii minime brute.</t>
+          <t>Prima zi de concediu medical pentru boală obișnuită NU se plătește, februarie 2026 – decembrie 2027; regula nu se aplică urgențelor, accidentelor de muncă, sarcinii și carantinei. Baza: media veniturilor brute din ultimele 6 luni, plafonată la 12 salarii minime brute. | modul: MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
     </row>
@@ -29884,7 +29916,7 @@
       </c>
       <c r="H72" s="69" t="inlineStr">
         <is>
-          <t>Art. 729 Cod procedură civilă: 1/2 pentru obligații de întreținere sau alocații pentru copii · 1/3 pentru alte datorii · la mai multe popriri, maximum 1/2 în total. Sub salariul minim net se urmărește doar partea care depășește jumătate din el.</t>
+          <t>Art. 729 Cod procedură civilă: 1/2 pentru obligații de întreținere sau alocații pentru copii · 1/3 pentru alte datorii · la mai multe popriri, maximum 1/2 în total. Sub salariul minim net se urmărește doar partea care depășește jumătate din el. | modul: MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
     </row>
@@ -29924,7 +29956,7 @@
       </c>
       <c r="H73" s="68" t="inlineStr">
         <is>
-          <t>Se identifică prin corelația sold 421 = restul de plată de pe stat. Diferența se caută pe luni, scoțând statele.</t>
+          <t>Se identifică prin corelația sold 421 = restul de plată de pe stat. Diferența se caută pe luni, scoțând statele. | modul: MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
     </row>
@@ -29964,7 +29996,7 @@
       </c>
       <c r="H74" s="68" t="inlineStr">
         <is>
-          <t>⚠️ Notițele foloseau 4428 (TVA neexigibilă). Contul corect e 4282, „Alte creanțe în legătură cu personalul”.</t>
+          <t>⚠️ Notițele foloseau 4428 (TVA neexigibilă). Contul corect e 4282, „Alte creanțe în legătură cu personalul”. | modul: MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
     </row>
@@ -46933,7 +46965,7 @@
       </c>
       <c r="D636" s="71" t="inlineStr">
         <is>
-          <t>Datorie obișnuită, deci limita e o treime: 33,33% din 29.250 = 9.749,03 lei. Se calculează din NET, nu din brut — banii merg la executor, nu la stat, deci după ce statul și-a luat partea. La obligații de întreținere limita ar fi fost 1/2, iar la mai multe popriri pe aceeași sumă tot 1/2 e maximul, indiferent de natura creanțelor.</t>
+          <t>Datorie obișnuită, deci limita e o treime: 29.250 / 3 = 9.750,00 lei. Fracția e o TREIME, nu „33,33%” — aproximarea zecimală dă alt număr, iar limita e un prag legal, nu o estimare. Se calculează din NET, nu din brut — banii merg la executor, nu la stat, deci după ce statul și-a luat partea. La obligații de întreținere limita ar fi fost 1/2, iar la mai multe popriri pe aceeași sumă tot 1/2 e maximul, indiferent de natura creanțelor.</t>
         </is>
       </c>
       <c r="E636" s="71" t="inlineStr">
@@ -46948,7 +46980,7 @@
       </c>
       <c r="G636" s="71" t="inlineStr">
         <is>
-          <t>9.749,03</t>
+          <t>9.750</t>
         </is>
       </c>
       <c r="H636" s="71" t="inlineStr">
@@ -46993,7 +47025,7 @@
       </c>
       <c r="G637" s="72" t="inlineStr">
         <is>
-          <t>9.749,03</t>
+          <t>9.750</t>
         </is>
       </c>
       <c r="H637" s="72" t="inlineStr">
@@ -50413,7 +50445,7 @@
       </c>
       <c r="F42" s="61" t="inlineStr">
         <is>
-          <t>F-413, F-416, F-418 | Module_Declarative_Fluxuri.xlsx → MOD_SALARII / MOD_INCHIDERE_LUNARA</t>
+          <t>F-413, F-416, F-418 | Module_Declarative_Fluxuri.xlsx → MOD_SALARII / MOD_INCHIDERE_LUNARA / MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="G42" s="61" t="inlineStr">
@@ -50581,7 +50613,7 @@
       </c>
       <c r="F46" s="61" t="inlineStr">
         <is>
-          <t>F-417</t>
+          <t>F-417 | Module_Declarative_Fluxuri.xlsx → MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="G46" s="61" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1881,7 +1881,7 @@
     <row r="116">
       <c r="A116" s="61" t="inlineStr">
         <is>
-          <t>Module_Declarative_Fluxuri.xlsx — 18 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
+          <t>Module_Declarative_Fluxuri.xlsx — 19 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9468,17 +9468,17 @@
     <row r="20">
       <c r="A20" s="66" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE</t>
+          <t>MOD_TAXARE_INVERSA</t>
         </is>
       </c>
       <c r="B20" s="66" t="inlineStr">
         <is>
-          <t>F-311, F-312, F-209</t>
+          <t>F-303, F-402</t>
         </is>
       </c>
       <c r="C20" s="66" t="inlineStr">
         <is>
-          <t>711/712/722: lanț complet producție / servicii / MF</t>
+          <t>Autolichidare 4426 = 4427, intracomunitar și intern</t>
         </is>
       </c>
       <c r="D20" s="66" t="inlineStr">
@@ -9488,29 +9488,29 @@
       </c>
       <c r="E20" s="66" t="inlineStr">
         <is>
-          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
+          <t>Declarații_TAXARE_INVERSA, Reguli_TAXARE_INVERSA, Jurnale_TAXARE_INVERSA, NotaExport_TAXARE_INVERSA</t>
         </is>
       </c>
       <c r="F20" s="66" t="inlineStr">
         <is>
-          <t>La producție / servicii în curs</t>
+          <t>La fiecare factură cu taxare inversă</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="66" t="inlineStr">
         <is>
-          <t>MOD_VANZ_AMANUNT</t>
+          <t>MOD_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="B21" s="66" t="inlineStr">
         <is>
-          <t>F-316, F-318, F-317</t>
+          <t>F-311, F-312, F-209</t>
         </is>
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
+          <t>711/712/722: lanț complet producție / servicii / MF</t>
         </is>
       </c>
       <c r="D21" s="66" t="inlineStr">
@@ -9520,98 +9520,130 @@
       </c>
       <c r="E21" s="66" t="inlineStr">
         <is>
-          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="F21" s="66" t="inlineStr">
         <is>
-          <t>La operațiuni amănunt + închidere lună amănunt</t>
+          <t>La producție / servicii în curs</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="66" t="inlineStr">
         <is>
+          <t>MOD_VANZ_AMANUNT</t>
+        </is>
+      </c>
+      <c r="B22" s="66" t="inlineStr">
+        <is>
+          <t>F-316, F-318, F-317</t>
+        </is>
+      </c>
+      <c r="C22" s="66" t="inlineStr">
+        <is>
+          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
+        </is>
+      </c>
+      <c r="D22" s="66" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+      <c r="E22" s="66" t="inlineStr">
+        <is>
+          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+        </is>
+      </c>
+      <c r="F22" s="66" t="inlineStr">
+        <is>
+          <t>La operațiuni amănunt + închidere lună amănunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="66" t="inlineStr">
+        <is>
           <t>MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="B22" s="66" t="inlineStr">
+      <c r="B23" s="66" t="inlineStr">
         <is>
           <t>F-422, F-413</t>
         </is>
       </c>
-      <c r="C22" s="66" t="inlineStr">
+      <c r="C23" s="66" t="inlineStr">
         <is>
           <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
         </is>
       </c>
-      <c r="D22" s="66" t="inlineStr">
+      <c r="D23" s="66" t="inlineStr">
         <is>
           <t>IMPLEMENTAT</t>
         </is>
       </c>
-      <c r="E22" s="66" t="inlineStr">
+      <c r="E23" s="66" t="inlineStr">
         <is>
           <t>Declarații_INCHIDERE_LUNARA, Reguli_INCHIDERE_LUNARA, Verificări_INCHIDERE_LUNARA, Abateri_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="F22" s="66" t="inlineStr">
+      <c r="F23" s="66" t="inlineStr">
         <is>
           <t>Lunar, pe balanța de verificare</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>CUM SE NAVIGHEAZĂ (cele două grafuri, acum sincronizate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="33" t="inlineStr">
-        <is>
-          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="33" t="inlineStr">
         <is>
-          <t>2. Pe corelație: Corelații de control → C-01…C-29 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
+          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="33" t="inlineStr">
         <is>
-          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
+          <t>2. Pe corelație: Corelații de control → C-01…C-29 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="33" t="inlineStr">
         <is>
-          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="33" t="inlineStr">
         <is>
+          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
           <t>5. Pe modul: CatalogModule (în Module_Declarative…) → Activ=DA → completezi Declarații → notele se generează.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="38" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t>INVARIANT: orice cont Tier A din Plan de conturi duce (via Flux pas) la toate fluxurile relevante, inclusiv F-304…F-802 pe cazurile grele (371, 378, 4428, 32x, 408, 331, 711, 8035).</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="63" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="63" t="inlineStr">
         <is>
           <t>MOD_CAPITALURI nu dublează MOD_INCHIDERE_EX: acela închide clasele 6 și 7 pe 121, acesta repartizează rezultatul obținut (129/1061/1171).</t>
         </is>
@@ -9620,14 +9652,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28544,7 +28576,7 @@
       </c>
       <c r="H37" s="28" t="inlineStr">
         <is>
-          <t>D390, D300, D394</t>
+          <t>D390, D300, D394 | modul: MOD_TAXARE_INVERSA</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29348,7 @@
       </c>
       <c r="H57" s="30" t="inlineStr">
         <is>
-          <t>D300 | ❓ Î-18</t>
+          <t>D300 | modul: MOD_TAXARE_INVERSA | ❓ Î-18</t>
         </is>
       </c>
     </row>
@@ -49477,7 +49509,7 @@
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>F-401, F-402, F-405 | Module_Declarative_Fluxuri.xlsx → MOD_TVA_INCASARE | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_TVA | ❓ Î-19</t>
+          <t>F-401, F-402, F-405 | Module_Declarative_Fluxuri.xlsx → MOD_TVA_INCASARE | Module_Declarative_Fluxuri.xlsx → MOD_TAXARE_INVERSA / MOD_INCHIDERE_TVA | ❓ Î-19</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1881,7 +1881,7 @@
     <row r="116">
       <c r="A116" s="61" t="inlineStr">
         <is>
-          <t>Module_Declarative_Fluxuri.xlsx — 19 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
+          <t>Module_Declarative_Fluxuri.xlsx — 20 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="E53" s="29" t="inlineStr">
         <is>
-          <t>F-405; F-406 credit la lipsă; F-318 storno retur | modul: MOD_INCHIDERE_TVA / MOD_VANZ_AMANUNT</t>
+          <t>F-405; F-406 credit la lipsă; F-318 storno retur | modul: MOD_INCHIDERE_TVA / MOD_FARA_DOCUMENT / MOD_VANZ_AMANUNT</t>
         </is>
       </c>
       <c r="F53" s="29" t="inlineStr">
@@ -8921,7 +8921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9500,17 +9500,17 @@
     <row r="21">
       <c r="A21" s="66" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE</t>
+          <t>MOD_FARA_DOCUMENT</t>
         </is>
       </c>
       <c r="B21" s="66" t="inlineStr">
         <is>
-          <t>F-311, F-312, F-209</t>
+          <t>F-406</t>
         </is>
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>711/712/722: lanț complet producție / servicii / MF</t>
+          <t>TVA nedeductibilă în cheltuială; colectare la lipsa nejustificată</t>
         </is>
       </c>
       <c r="D21" s="66" t="inlineStr">
@@ -9520,29 +9520,29 @@
       </c>
       <c r="E21" s="66" t="inlineStr">
         <is>
-          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
+          <t>Declarații_FARA_DOCUMENT, Reguli_FARA_DOCUMENT, Jurnale_FARA_DOCUMENT, NotaExport_FARA_DOCUMENT</t>
         </is>
       </c>
       <c r="F21" s="66" t="inlineStr">
         <is>
-          <t>La producție / servicii în curs</t>
+          <t>Lunar la cheltuielile auto; la fiecare inventar cu minus</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="66" t="inlineStr">
         <is>
-          <t>MOD_VANZ_AMANUNT</t>
+          <t>MOD_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="B22" s="66" t="inlineStr">
         <is>
-          <t>F-316, F-318, F-317</t>
+          <t>F-311, F-312, F-209</t>
         </is>
       </c>
       <c r="C22" s="66" t="inlineStr">
         <is>
-          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
+          <t>711/712/722: lanț complet producție / servicii / MF</t>
         </is>
       </c>
       <c r="D22" s="66" t="inlineStr">
@@ -9552,98 +9552,130 @@
       </c>
       <c r="E22" s="66" t="inlineStr">
         <is>
-          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="F22" s="66" t="inlineStr">
         <is>
-          <t>La operațiuni amănunt + închidere lună amănunt</t>
+          <t>La producție / servicii în curs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="66" t="inlineStr">
         <is>
+          <t>MOD_VANZ_AMANUNT</t>
+        </is>
+      </c>
+      <c r="B23" s="66" t="inlineStr">
+        <is>
+          <t>F-316, F-318, F-317</t>
+        </is>
+      </c>
+      <c r="C23" s="66" t="inlineStr">
+        <is>
+          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
+        </is>
+      </c>
+      <c r="D23" s="66" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+      <c r="E23" s="66" t="inlineStr">
+        <is>
+          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+        </is>
+      </c>
+      <c r="F23" s="66" t="inlineStr">
+        <is>
+          <t>La operațiuni amănunt + închidere lună amănunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="66" t="inlineStr">
+        <is>
           <t>MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="B23" s="66" t="inlineStr">
+      <c r="B24" s="66" t="inlineStr">
         <is>
           <t>F-422, F-413</t>
         </is>
       </c>
-      <c r="C23" s="66" t="inlineStr">
+      <c r="C24" s="66" t="inlineStr">
         <is>
           <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
         </is>
       </c>
-      <c r="D23" s="66" t="inlineStr">
+      <c r="D24" s="66" t="inlineStr">
         <is>
           <t>IMPLEMENTAT</t>
         </is>
       </c>
-      <c r="E23" s="66" t="inlineStr">
+      <c r="E24" s="66" t="inlineStr">
         <is>
           <t>Declarații_INCHIDERE_LUNARA, Reguli_INCHIDERE_LUNARA, Verificări_INCHIDERE_LUNARA, Abateri_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="F23" s="66" t="inlineStr">
+      <c r="F24" s="66" t="inlineStr">
         <is>
           <t>Lunar, pe balanța de verificare</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="36" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>CUM SE NAVIGHEAZĂ (cele două grafuri, acum sincronizate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="33" t="inlineStr">
-        <is>
-          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="33" t="inlineStr">
         <is>
-          <t>2. Pe corelație: Corelații de control → C-01…C-29 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
+          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="33" t="inlineStr">
         <is>
-          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
+          <t>2. Pe corelație: Corelații de control → C-01…C-29 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="33" t="inlineStr">
         <is>
-          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="33" t="inlineStr">
         <is>
+          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
           <t>5. Pe modul: CatalogModule (în Module_Declarative…) → Activ=DA → completezi Declarații → notele se generează.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="38" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="38" t="inlineStr">
         <is>
           <t>INVARIANT: orice cont Tier A din Plan de conturi duce (via Flux pas) la toate fluxurile relevante, inclusiv F-304…F-802 pe cazurile grele (371, 378, 4428, 32x, 408, 331, 711, 8035).</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="63" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="63" t="inlineStr">
         <is>
           <t>MOD_CAPITALURI nu dublează MOD_INCHIDERE_EX: acela închide clasele 6 și 7 pe 121, acesta repartizează rezultatul obținut (129/1061/1171).</t>
         </is>
@@ -9652,12 +9684,12 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
@@ -29508,7 +29540,7 @@
       </c>
       <c r="H61" s="30" t="inlineStr">
         <is>
-          <t>D300 (ajustare), D100 | ❓ Î-19</t>
+          <t>D300 (ajustare), D100 | modul: MOD_FARA_DOCUMENT | ❓ Î-19</t>
         </is>
       </c>
     </row>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1881,7 +1881,7 @@
     <row r="116">
       <c r="A116" s="61" t="inlineStr">
         <is>
-          <t>Module_Declarative_Fluxuri.xlsx — 20 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
+          <t>Module_Declarative_Fluxuri.xlsx — 21 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="E34" s="29" t="inlineStr">
         <is>
-          <t>F-304 același furnizor 32x+408 | modul: MOD_APROV_TRANZIT / MOD_INTERMEDIAR</t>
+          <t>F-304 același furnizor 32x+408 | modul: MOD_APROV_TRANZIT / MOD_IMPORT / MOD_INTERMEDIAR</t>
         </is>
       </c>
       <c r="F34" s="29" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="E52" s="29" t="inlineStr">
         <is>
-          <t>F-405 închidere sold 0; F-407 corecție post-D300 | modul: MOD_INCHIDERE_TVA</t>
+          <t>F-405 închidere sold 0; F-407 corecție post-D300 | modul: MOD_INCHIDERE_TVA / MOD_IMPORT</t>
         </is>
       </c>
       <c r="F52" s="29" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>F-319 stingere 446.VAMA</t>
+          <t>F-319 stingere 446.VAMA | modul: MOD_IMPORT</t>
         </is>
       </c>
       <c r="F56" s="29" t="inlineStr">
@@ -8921,7 +8921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9404,17 +9404,17 @@
     <row r="18">
       <c r="A18" s="66" t="inlineStr">
         <is>
-          <t>MOD_INCHIDERE_EX</t>
+          <t>MOD_IMPORT</t>
         </is>
       </c>
       <c r="B18" s="66" t="inlineStr">
         <is>
-          <t>F-104</t>
+          <t>F-319, F-320</t>
         </is>
       </c>
       <c r="C18" s="66" t="inlineStr">
         <is>
-          <t>Închidere cls.6/7 pe 121; impozit; report 117</t>
+          <t>TVA vamală prin 446.VAMA sau plătită direct; taxele în costul stocului</t>
         </is>
       </c>
       <c r="D18" s="66" t="inlineStr">
@@ -9424,29 +9424,29 @@
       </c>
       <c r="E18" s="66" t="inlineStr">
         <is>
-          <t>Declarații_INCHIDERE_EX, Reguli_INCHIDERE_EX, Jurnale_INCHIDERE_EX, NotaExport_INCHIDERE_EX</t>
+          <t>Declarații_IMPORT, Reguli_IMPORT, Jurnale_IMPORT, NotaExport_IMPORT</t>
         </is>
       </c>
       <c r="F18" s="66" t="inlineStr">
         <is>
-          <t>La 31.12</t>
+          <t>La fiecare DVI</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="66" t="inlineStr">
         <is>
-          <t>MOD_TVA_INCASARE</t>
+          <t>MOD_INCHIDERE_EX</t>
         </is>
       </c>
       <c r="B19" s="66" t="inlineStr">
         <is>
-          <t>F-401</t>
+          <t>F-104</t>
         </is>
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>4428.INC: factură → plată/încasare → 4426/4427</t>
+          <t>Închidere cls.6/7 pe 121; impozit; report 117</t>
         </is>
       </c>
       <c r="D19" s="66" t="inlineStr">
@@ -9456,29 +9456,29 @@
       </c>
       <c r="E19" s="66" t="inlineStr">
         <is>
-          <t>Declarații_TVA_INC, Reguli_TVA_INC, Jurnale_TVA_INC, NotaExport_TVA_INC</t>
+          <t>Declarații_INCHIDERE_EX, Reguli_INCHIDERE_EX, Jurnale_INCHIDERE_EX, NotaExport_INCHIDERE_EX</t>
         </is>
       </c>
       <c r="F19" s="66" t="inlineStr">
         <is>
-          <t>Când regimul e TVA la încasare</t>
+          <t>La 31.12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="66" t="inlineStr">
         <is>
-          <t>MOD_TAXARE_INVERSA</t>
+          <t>MOD_TVA_INCASARE</t>
         </is>
       </c>
       <c r="B20" s="66" t="inlineStr">
         <is>
-          <t>F-303, F-402</t>
+          <t>F-401</t>
         </is>
       </c>
       <c r="C20" s="66" t="inlineStr">
         <is>
-          <t>Autolichidare 4426 = 4427, intracomunitar și intern</t>
+          <t>4428.INC: factură → plată/încasare → 4426/4427</t>
         </is>
       </c>
       <c r="D20" s="66" t="inlineStr">
@@ -9488,29 +9488,29 @@
       </c>
       <c r="E20" s="66" t="inlineStr">
         <is>
-          <t>Declarații_TAXARE_INVERSA, Reguli_TAXARE_INVERSA, Jurnale_TAXARE_INVERSA, NotaExport_TAXARE_INVERSA</t>
+          <t>Declarații_TVA_INC, Reguli_TVA_INC, Jurnale_TVA_INC, NotaExport_TVA_INC</t>
         </is>
       </c>
       <c r="F20" s="66" t="inlineStr">
         <is>
-          <t>La fiecare factură cu taxare inversă</t>
+          <t>Când regimul e TVA la încasare</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="66" t="inlineStr">
         <is>
-          <t>MOD_FARA_DOCUMENT</t>
+          <t>MOD_TAXARE_INVERSA</t>
         </is>
       </c>
       <c r="B21" s="66" t="inlineStr">
         <is>
-          <t>F-406</t>
+          <t>F-303, F-402</t>
         </is>
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>TVA nedeductibilă în cheltuială; colectare la lipsa nejustificată</t>
+          <t>Autolichidare 4426 = 4427, intracomunitar și intern</t>
         </is>
       </c>
       <c r="D21" s="66" t="inlineStr">
@@ -9520,29 +9520,29 @@
       </c>
       <c r="E21" s="66" t="inlineStr">
         <is>
-          <t>Declarații_FARA_DOCUMENT, Reguli_FARA_DOCUMENT, Jurnale_FARA_DOCUMENT, NotaExport_FARA_DOCUMENT</t>
+          <t>Declarații_TAXARE_INVERSA, Reguli_TAXARE_INVERSA, Jurnale_TAXARE_INVERSA, NotaExport_TAXARE_INVERSA</t>
         </is>
       </c>
       <c r="F21" s="66" t="inlineStr">
         <is>
-          <t>Lunar la cheltuielile auto; la fiecare inventar cu minus</t>
+          <t>La fiecare factură cu taxare inversă</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="66" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE</t>
+          <t>MOD_FARA_DOCUMENT</t>
         </is>
       </c>
       <c r="B22" s="66" t="inlineStr">
         <is>
-          <t>F-311, F-312, F-209</t>
+          <t>F-406</t>
         </is>
       </c>
       <c r="C22" s="66" t="inlineStr">
         <is>
-          <t>711/712/722: lanț complet producție / servicii / MF</t>
+          <t>TVA nedeductibilă în cheltuială; colectare la lipsa nejustificată</t>
         </is>
       </c>
       <c r="D22" s="66" t="inlineStr">
@@ -9552,29 +9552,29 @@
       </c>
       <c r="E22" s="66" t="inlineStr">
         <is>
-          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
+          <t>Declarații_FARA_DOCUMENT, Reguli_FARA_DOCUMENT, Jurnale_FARA_DOCUMENT, NotaExport_FARA_DOCUMENT</t>
         </is>
       </c>
       <c r="F22" s="66" t="inlineStr">
         <is>
-          <t>La producție / servicii în curs</t>
+          <t>Lunar la cheltuielile auto; la fiecare inventar cu minus</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="66" t="inlineStr">
         <is>
-          <t>MOD_VANZ_AMANUNT</t>
+          <t>MOD_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="B23" s="66" t="inlineStr">
         <is>
-          <t>F-316, F-318, F-317</t>
+          <t>F-311, F-312, F-209</t>
         </is>
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
+          <t>711/712/722: lanț complet producție / servicii / MF</t>
         </is>
       </c>
       <c r="D23" s="66" t="inlineStr">
@@ -9584,98 +9584,130 @@
       </c>
       <c r="E23" s="66" t="inlineStr">
         <is>
-          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="F23" s="66" t="inlineStr">
         <is>
-          <t>La operațiuni amănunt + închidere lună amănunt</t>
+          <t>La producție / servicii în curs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="66" t="inlineStr">
         <is>
+          <t>MOD_VANZ_AMANUNT</t>
+        </is>
+      </c>
+      <c r="B24" s="66" t="inlineStr">
+        <is>
+          <t>F-316, F-318, F-317</t>
+        </is>
+      </c>
+      <c r="C24" s="66" t="inlineStr">
+        <is>
+          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
+        </is>
+      </c>
+      <c r="D24" s="66" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+      <c r="E24" s="66" t="inlineStr">
+        <is>
+          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+        </is>
+      </c>
+      <c r="F24" s="66" t="inlineStr">
+        <is>
+          <t>La operațiuni amănunt + închidere lună amănunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="66" t="inlineStr">
+        <is>
           <t>MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="B24" s="66" t="inlineStr">
+      <c r="B25" s="66" t="inlineStr">
         <is>
           <t>F-422, F-413</t>
         </is>
       </c>
-      <c r="C24" s="66" t="inlineStr">
+      <c r="C25" s="66" t="inlineStr">
         <is>
           <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
         </is>
       </c>
-      <c r="D24" s="66" t="inlineStr">
+      <c r="D25" s="66" t="inlineStr">
         <is>
           <t>IMPLEMENTAT</t>
         </is>
       </c>
-      <c r="E24" s="66" t="inlineStr">
+      <c r="E25" s="66" t="inlineStr">
         <is>
           <t>Declarații_INCHIDERE_LUNARA, Reguli_INCHIDERE_LUNARA, Verificări_INCHIDERE_LUNARA, Abateri_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="F24" s="66" t="inlineStr">
+      <c r="F25" s="66" t="inlineStr">
         <is>
           <t>Lunar, pe balanța de verificare</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="36" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>CUM SE NAVIGHEAZĂ (cele două grafuri, acum sincronizate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="33" t="inlineStr">
-        <is>
-          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="33" t="inlineStr">
         <is>
-          <t>2. Pe corelație: Corelații de control → C-01…C-29 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
+          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="33" t="inlineStr">
         <is>
-          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
+          <t>2. Pe corelație: Corelații de control → C-01…C-29 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="33" t="inlineStr">
         <is>
-          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="33" t="inlineStr">
         <is>
+          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="inlineStr">
+        <is>
           <t>5. Pe modul: CatalogModule (în Module_Declarative…) → Activ=DA → completezi Declarații → notele se generează.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="38" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="38" t="inlineStr">
         <is>
           <t>INVARIANT: orice cont Tier A din Plan de conturi duce (via Flux pas) la toate fluxurile relevante, inclusiv F-304…F-802 pe cazurile grele (371, 378, 4428, 32x, 408, 331, 711, 8035).</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="63" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="63" t="inlineStr">
         <is>
           <t>MOD_CAPITALURI nu dublează MOD_INCHIDERE_EX: acela închide clasele 6 și 7 pe 121, acesta repartizează rezultatul obținut (129/1061/1171).</t>
         </is>
@@ -9684,12 +9716,12 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
@@ -29253,7 +29285,7 @@
       </c>
       <c r="H53" s="29" t="inlineStr">
         <is>
-          <t>Pas revelator: 446.VAMA se stinge. D300, D394 | ❓ Î-16</t>
+          <t>Pas revelator: 446.VAMA se stinge. D300, D394 | modul: MOD_IMPORT | ❓ Î-16</t>
         </is>
       </c>
     </row>
@@ -29293,7 +29325,7 @@
       </c>
       <c r="H54" s="30" t="inlineStr">
         <is>
-          <t>D300 | ❓ Î-17</t>
+          <t>D300 | modul: MOD_IMPORT | ❓ Î-17</t>
         </is>
       </c>
     </row>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1881,7 +1881,7 @@
     <row r="116">
       <c r="A116" s="61" t="inlineStr">
         <is>
-          <t>Module_Declarative_Fluxuri.xlsx — 21 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
+          <t>Module_Declarative_Fluxuri.xlsx — 22 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="E36" s="29" t="inlineStr">
         <is>
-          <t>F-410 clarificat sume</t>
+          <t>F-410 clarificat sume | modul: MOD_AVANSURI</t>
         </is>
       </c>
       <c r="F36" s="29" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E37" s="66" t="inlineStr">
         <is>
-          <t>F-108 pas 4: stingerea avansului în 167 | modul: MOD_LEASING_FIN</t>
+          <t>F-108 pas 4: stingerea avansului în 167 | modul: MOD_LEASING_FIN / MOD_AVANSURI</t>
         </is>
       </c>
       <c r="F37" s="66" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="E39" s="66" t="inlineStr">
         <is>
-          <t>F-415 pas 2: cont de activ ajuns cu sold creditor = avans neînregistrat</t>
+          <t>F-415 pas 2: cont de activ ajuns cu sold creditor = avans neînregistrat | modul: MOD_AVANSURI</t>
         </is>
       </c>
       <c r="F39" s="66" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E41" s="66" t="inlineStr">
         <is>
-          <t>F-415 pas 3: soldul creditor de pe 4111 se dovedește avans cu TVA</t>
+          <t>F-415 pas 3: soldul creditor de pe 4111 se dovedește avans cu TVA | modul: MOD_AVANSURI</t>
         </is>
       </c>
       <c r="F41" s="66" t="inlineStr">
@@ -8921,7 +8921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9564,17 +9564,17 @@
     <row r="23">
       <c r="A23" s="66" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE</t>
+          <t>MOD_AVANSURI</t>
         </is>
       </c>
       <c r="B23" s="66" t="inlineStr">
         <is>
-          <t>F-311, F-312, F-209</t>
+          <t>F-410, F-415</t>
         </is>
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>711/712/722: lanț complet producție / servicii / MF</t>
+          <t>419/409: avans cu TVA, stingere la factura finală, supraîncasare</t>
         </is>
       </c>
       <c r="D23" s="66" t="inlineStr">
@@ -9584,29 +9584,29 @@
       </c>
       <c r="E23" s="66" t="inlineStr">
         <is>
-          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
+          <t>Declarații_AVANSURI, Reguli_AVANSURI, Jurnale_AVANSURI, NotaExport_AVANSURI</t>
         </is>
       </c>
       <c r="F23" s="66" t="inlineStr">
         <is>
-          <t>La producție / servicii în curs</t>
+          <t>La fiecare avans și la orice sold creditor pe 4111</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="66" t="inlineStr">
         <is>
-          <t>MOD_VANZ_AMANUNT</t>
+          <t>MOD_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="B24" s="66" t="inlineStr">
         <is>
-          <t>F-316, F-318, F-317</t>
+          <t>F-311, F-312, F-209</t>
         </is>
       </c>
       <c r="C24" s="66" t="inlineStr">
         <is>
-          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
+          <t>711/712/722: lanț complet producție / servicii / MF</t>
         </is>
       </c>
       <c r="D24" s="66" t="inlineStr">
@@ -9616,98 +9616,130 @@
       </c>
       <c r="E24" s="66" t="inlineStr">
         <is>
-          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="F24" s="66" t="inlineStr">
         <is>
-          <t>La operațiuni amănunt + închidere lună amănunt</t>
+          <t>La producție / servicii în curs</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="66" t="inlineStr">
         <is>
+          <t>MOD_VANZ_AMANUNT</t>
+        </is>
+      </c>
+      <c r="B25" s="66" t="inlineStr">
+        <is>
+          <t>F-316, F-318, F-317</t>
+        </is>
+      </c>
+      <c r="C25" s="66" t="inlineStr">
+        <is>
+          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
+        </is>
+      </c>
+      <c r="D25" s="66" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+      <c r="E25" s="66" t="inlineStr">
+        <is>
+          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+        </is>
+      </c>
+      <c r="F25" s="66" t="inlineStr">
+        <is>
+          <t>La operațiuni amănunt + închidere lună amănunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="66" t="inlineStr">
+        <is>
           <t>MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="B25" s="66" t="inlineStr">
+      <c r="B26" s="66" t="inlineStr">
         <is>
           <t>F-422, F-413</t>
         </is>
       </c>
-      <c r="C25" s="66" t="inlineStr">
+      <c r="C26" s="66" t="inlineStr">
         <is>
           <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
         </is>
       </c>
-      <c r="D25" s="66" t="inlineStr">
+      <c r="D26" s="66" t="inlineStr">
         <is>
           <t>IMPLEMENTAT</t>
         </is>
       </c>
-      <c r="E25" s="66" t="inlineStr">
+      <c r="E26" s="66" t="inlineStr">
         <is>
           <t>Declarații_INCHIDERE_LUNARA, Reguli_INCHIDERE_LUNARA, Verificări_INCHIDERE_LUNARA, Abateri_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="F25" s="66" t="inlineStr">
+      <c r="F26" s="66" t="inlineStr">
         <is>
           <t>Lunar, pe balanța de verificare</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="36" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>CUM SE NAVIGHEAZĂ (cele două grafuri, acum sincronizate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="33" t="inlineStr">
-        <is>
-          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="33" t="inlineStr">
         <is>
-          <t>2. Pe corelație: Corelații de control → C-01…C-29 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
+          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="33" t="inlineStr">
         <is>
-          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
+          <t>2. Pe corelație: Corelații de control → C-01…C-29 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="33" t="inlineStr">
         <is>
-          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="33" t="inlineStr">
         <is>
+          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
           <t>5. Pe modul: CatalogModule (în Module_Declarative…) → Activ=DA → completezi Declarații → notele se generează.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="38" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="38" t="inlineStr">
         <is>
           <t>INVARIANT: orice cont Tier A din Plan de conturi duce (via Flux pas) la toate fluxurile relevante, inclusiv F-304…F-802 pe cazurile grele (371, 378, 4428, 32x, 408, 331, 711, 8035).</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="63" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="63" t="inlineStr">
         <is>
           <t>MOD_CAPITALURI nu dublează MOD_INCHIDERE_EX: acela închide clasele 6 și 7 pe 121, acesta repartizează rezultatul obținut (129/1061/1171).</t>
         </is>
@@ -9717,11 +9749,11 @@
   <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
@@ -29732,7 +29764,7 @@
       </c>
       <c r="H65" s="30" t="inlineStr">
         <is>
-          <t>D300 (TVA pe avans)</t>
+          <t>D300 (TVA pe avans) | modul: MOD_AVANSURI</t>
         </is>
       </c>
     </row>
@@ -29932,7 +29964,7 @@
       </c>
       <c r="H70" s="69" t="inlineStr">
         <is>
-          <t>Diferența e TVA-inclusivă (§7.2: sumă fără mențiune = cu tot cu TVA). Legiuitorul nu cere corecție când TU plătești în plus, dar o cere când TU încasezi în plus. | ❓ Î-24</t>
+          <t>Diferența e TVA-inclusivă (§7.2: sumă fără mențiune = cu tot cu TVA). Legiuitorul nu cere corecție când TU plătești în plus, dar o cere când TU încasezi în plus. | modul: MOD_AVANSURI | ❓ Î-24</t>
         </is>
       </c>
     </row>
@@ -49616,7 +49648,7 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>F-316, F-401, F-403, F-404, F-410 | Module_Declarative_Fluxuri.xlsx → MOD_VANZ_AMANUNT / MOD_TVA_INCASARE | ❓ Î-19</t>
+          <t>F-316, F-401, F-403, F-404, F-410 | Module_Declarative_Fluxuri.xlsx → MOD_VANZ_AMANUNT / MOD_TVA_INCASARE / MOD_AVANSURI | ❓ Î-19</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -50497,7 +50529,7 @@
       </c>
       <c r="F41" s="61" t="inlineStr">
         <is>
-          <t>F-415, F-410 | ❓ Î-24</t>
+          <t>F-415, F-410 | Module_Declarative_Fluxuri.xlsx → MOD_AVANSURI | ❓ Î-24</t>
         </is>
       </c>
       <c r="G41" s="61" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -9020,17 +9020,17 @@
     <row r="6">
       <c r="A6" s="66" t="inlineStr">
         <is>
-          <t>MOD_CREDIT_VALUTA</t>
+          <t>MOD_INCHIDERE_EX</t>
         </is>
       </c>
       <c r="B6" s="66" t="inlineStr">
         <is>
-          <t>F-107</t>
+          <t>F-104</t>
         </is>
       </c>
       <c r="C6" s="66" t="inlineStr">
         <is>
-          <t>B1 Rata + diferența la plată; B2 Dobânda; B3 Comisioane; B4 Reevaluarea soldului</t>
+          <t>Închidere cls.6/7 pe 121; impozit; report 117</t>
         </is>
       </c>
       <c r="D6" s="66" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="E6" s="66" t="inlineStr">
         <is>
-          <t>Declarații_CREDIT_VALUTA, Reguli_CREDIT_VALUTA, Jurnale_CREDIT_VALUTA, NotaExport_CREDIT_VALUTA</t>
+          <t>Declarații_INCHIDERE_EX, Reguli_INCHIDERE_EX, Jurnale_INCHIDERE_EX, NotaExport_INCHIDERE_EX</t>
         </is>
       </c>
       <c r="F6" s="66" t="inlineStr">
         <is>
-          <t>Lunar, pe contract</t>
+          <t>La 31.12</t>
         </is>
       </c>
     </row>
@@ -9084,17 +9084,17 @@
     <row r="8">
       <c r="A8" s="66" t="inlineStr">
         <is>
-          <t>MOD_LEASING_FIN</t>
+          <t>MOD_CREDIT_VALUTA</t>
         </is>
       </c>
       <c r="B8" s="66" t="inlineStr">
         <is>
-          <t>F-108</t>
+          <t>F-107</t>
         </is>
       </c>
       <c r="C8" s="66" t="inlineStr">
         <is>
-          <t>B1 Avans; B2 TVA avans; B3 Intrare + 167; B4 Stingere avans; B5 Factura lunară; B6 Corecție TVA 50%; B7 Limitare 50% cheltuieli; B8 Amortizare</t>
+          <t>B1 Rata + diferența la plată; B2 Dobânda; B3 Comisioane; B4 Reevaluarea soldului</t>
         </is>
       </c>
       <c r="D8" s="66" t="inlineStr">
@@ -9104,29 +9104,29 @@
       </c>
       <c r="E8" s="66" t="inlineStr">
         <is>
-          <t>Declarații_LEASING_FIN, Reguli_LEASING_FIN, Jurnale_LEASING_FIN, NotaExport_LEASING_FIN</t>
+          <t>Declarații_CREDIT_VALUTA, Reguli_CREDIT_VALUTA, Jurnale_CREDIT_VALUTA, NotaExport_CREDIT_VALUTA</t>
         </is>
       </c>
       <c r="F8" s="66" t="inlineStr">
         <is>
-          <t>Pe contract + lunar</t>
+          <t>Lunar, pe contract</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="66" t="inlineStr">
         <is>
-          <t>MOD_IMOBILIZARI</t>
+          <t>MOD_LEASING_FIN</t>
         </is>
       </c>
       <c r="B9" s="66" t="inlineStr">
         <is>
-          <t>F-203, F-205, F-207, F-214</t>
+          <t>F-108</t>
         </is>
       </c>
       <c r="C9" s="66" t="inlineStr">
         <is>
-          <t>B1 Intrare; B2 TVA pe regim; B3 Costuri capitalizate; B4 Amortizare lunară</t>
+          <t>B1 Avans; B2 TVA avans; B3 Intrare + 167; B4 Stingere avans; B5 Factura lunară; B6 Corecție TVA 50%; B7 Limitare 50% cheltuieli; B8 Amortizare</t>
         </is>
       </c>
       <c r="D9" s="66" t="inlineStr">
@@ -9136,29 +9136,29 @@
       </c>
       <c r="E9" s="66" t="inlineStr">
         <is>
-          <t>Declarații_IMOBILIZARI, Reguli_IMOBILIZARI, Jurnale_IMOBILIZARI, NotaExport_IMOBILIZARI</t>
+          <t>Declarații_LEASING_FIN, Reguli_LEASING_FIN, Jurnale_LEASING_FIN, NotaExport_LEASING_FIN</t>
         </is>
       </c>
       <c r="F9" s="66" t="inlineStr">
         <is>
-          <t>Pe mijloc fix + lunar</t>
+          <t>Pe contract + lunar</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="66" t="inlineStr">
         <is>
-          <t>MOD_SUBVENTIE</t>
+          <t>MOD_IMOBILIZARI</t>
         </is>
       </c>
       <c r="B10" s="66" t="inlineStr">
         <is>
-          <t>F-210</t>
+          <t>F-203, F-205, F-207, F-214</t>
         </is>
       </c>
       <c r="C10" s="66" t="inlineStr">
         <is>
-          <t>B1 Încasarea subvenției; B2 Achiziția activului; B3 Amortizare + eliberare</t>
+          <t>B1 Intrare; B2 TVA pe regim; B3 Costuri capitalizate; B4 Amortizare lunară</t>
         </is>
       </c>
       <c r="D10" s="66" t="inlineStr">
@@ -9168,29 +9168,29 @@
       </c>
       <c r="E10" s="66" t="inlineStr">
         <is>
-          <t>Declarații_SUBVENTIE, Reguli_SUBVENTIE, Jurnale_SUBVENTIE, NotaExport_SUBVENTIE</t>
+          <t>Declarații_IMOBILIZARI, Reguli_IMOBILIZARI, Jurnale_IMOBILIZARI, NotaExport_IMOBILIZARI</t>
         </is>
       </c>
       <c r="F10" s="66" t="inlineStr">
         <is>
-          <t>Lunar, pe activ subvenționat</t>
+          <t>Pe mijloc fix + lunar</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="66" t="inlineStr">
         <is>
-          <t>MOD_IESIRE_MF</t>
+          <t>MOD_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="B11" s="66" t="inlineStr">
         <is>
-          <t>F-211, F-212</t>
+          <t>F-311, F-312, F-209</t>
         </is>
       </c>
       <c r="C11" s="66" t="inlineStr">
         <is>
-          <t>B1 Descărcare amortizare; B2 Valoare rămasă; B3 Vânzare; B4 Piese recuperate</t>
+          <t>711/712/722: lanț complet producție / servicii / MF</t>
         </is>
       </c>
       <c r="D11" s="66" t="inlineStr">
@@ -9200,29 +9200,29 @@
       </c>
       <c r="E11" s="66" t="inlineStr">
         <is>
-          <t>Declarații_IESIRE_MF, Reguli_IESIRE_MF, Jurnale_IESIRE_MF, NotaExport_IESIRE_MF</t>
+          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="F11" s="66" t="inlineStr">
         <is>
-          <t>Pe eveniment de ieșire</t>
+          <t>La producție / servicii în curs</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="66" t="inlineStr">
         <is>
-          <t>MOD_SALARII</t>
+          <t>MOD_SUBVENTIE</t>
         </is>
       </c>
       <c r="B12" s="66" t="inlineStr">
         <is>
-          <t>F-413</t>
+          <t>F-210</t>
         </is>
       </c>
       <c r="C12" s="66" t="inlineStr">
         <is>
-          <t>B1 Plata avansului; B2 Costurile lunii; B3 Plăți (net, taxe, CAM)</t>
+          <t>B1 Încasarea subvenției; B2 Achiziția activului; B3 Amortizare + eliberare</t>
         </is>
       </c>
       <c r="D12" s="66" t="inlineStr">
@@ -9232,29 +9232,29 @@
       </c>
       <c r="E12" s="66" t="inlineStr">
         <is>
-          <t>Declarații_SALARII, Reguli_SALARII, Jurnale_SALARII, NotaExport_SALARII</t>
+          <t>Declarații_SUBVENTIE, Reguli_SUBVENTIE, Jurnale_SUBVENTIE, NotaExport_SUBVENTIE</t>
         </is>
       </c>
       <c r="F12" s="66" t="inlineStr">
         <is>
-          <t>Lunar, pe registru de angajați</t>
+          <t>Lunar, pe activ subvenționat</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="66" t="inlineStr">
         <is>
-          <t>MOD_SALARII_EVENIMENTE</t>
+          <t>MOD_IESIRE_MF</t>
         </is>
       </c>
       <c r="B13" s="66" t="inlineStr">
         <is>
-          <t>F-416, F-417, F-418, F-419</t>
+          <t>F-211, F-212</t>
         </is>
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>42x: medicale, popriri, drepturi neridicate, creanțe față de foști salariați</t>
+          <t>B1 Descărcare amortizare; B2 Valoare rămasă; B3 Vânzare; B4 Piese recuperate</t>
         </is>
       </c>
       <c r="D13" s="66" t="inlineStr">
@@ -9264,29 +9264,29 @@
       </c>
       <c r="E13" s="66" t="inlineStr">
         <is>
-          <t>Declarații_SALARII_EVENIMENTE, Reguli_SALARII_EVENIMENTE, Jurnale_SALARII_EVENIMENTE, NotaExport_SALARII_EVENIMENTE</t>
+          <t>Declarații_IESIRE_MF, Reguli_IESIRE_MF, Jurnale_IESIRE_MF, NotaExport_IESIRE_MF</t>
         </is>
       </c>
       <c r="F13" s="66" t="inlineStr">
         <is>
-          <t>Pe eveniment, lângă statul lunar</t>
+          <t>Pe eveniment de ieșire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="66" t="inlineStr">
         <is>
-          <t>MOD_DECONT</t>
+          <t>MOD_APROV_TRANZIT</t>
         </is>
       </c>
       <c r="B14" s="66" t="inlineStr">
         <is>
-          <t>F-502</t>
+          <t>F-302</t>
         </is>
       </c>
       <c r="C14" s="66" t="inlineStr">
         <is>
-          <t>B1 Avans; B2 Cheltuieli + TVA; B3 Regularizare avans; B4 Plată / restituire</t>
+          <t>32x: factură înainte de marfă / NIR înainte de factură</t>
         </is>
       </c>
       <c r="D14" s="66" t="inlineStr">
@@ -9296,29 +9296,29 @@
       </c>
       <c r="E14" s="66" t="inlineStr">
         <is>
-          <t>Declarații_DECONT, Reguli_DECONT, Registru_DECONT, Jurnale_DECONT, NotaExport_DECONT</t>
+          <t>Declarații_APROV_TRANZIT, Reguli_APROV_TRANZIT, Jurnale_APROV_TRANZIT, NotaExport_APROV_TRANZIT</t>
         </is>
       </c>
       <c r="F14" s="66" t="inlineStr">
         <is>
-          <t>Pe decont</t>
+          <t>La aprovizionări incomplete</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="66" t="inlineStr">
         <is>
-          <t>MOD_INTERMEDIAR</t>
+          <t>MOD_TAXARE_INVERSA</t>
         </is>
       </c>
       <c r="B15" s="66" t="inlineStr">
         <is>
-          <t>F-408, F-501, F-411</t>
+          <t>F-303, F-402</t>
         </is>
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>408/418/473: deschidere + stingere + red flags</t>
+          <t>Autolichidare 4426 = 4427, intracomunitar și intern</t>
         </is>
       </c>
       <c r="D15" s="66" t="inlineStr">
@@ -9328,29 +9328,29 @@
       </c>
       <c r="E15" s="66" t="inlineStr">
         <is>
-          <t>Declarații_INTERMEDIAR, Reguli_INTERMEDIAR, Jurnale_INTERMEDIAR, NotaExport_INTERMEDIAR</t>
+          <t>Declarații_TAXARE_INVERSA, Reguli_TAXARE_INVERSA, Jurnale_TAXARE_INVERSA, NotaExport_TAXARE_INVERSA</t>
         </is>
       </c>
       <c r="F15" s="66" t="inlineStr">
         <is>
-          <t>La facturi nesosite / sume neclare</t>
+          <t>La fiecare factură cu taxare inversă</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="66" t="inlineStr">
         <is>
-          <t>MOD_INCHIDERE_TVA</t>
+          <t>MOD_VANZ_AMANUNT</t>
         </is>
       </c>
       <c r="B16" s="66" t="inlineStr">
         <is>
-          <t>F-405</t>
+          <t>F-316, F-318, F-317</t>
         </is>
       </c>
       <c r="C16" s="66" t="inlineStr">
         <is>
-          <t>Închidere 4426/4427 → 4423/4424</t>
+          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
         </is>
       </c>
       <c r="D16" s="66" t="inlineStr">
@@ -9360,29 +9360,29 @@
       </c>
       <c r="E16" s="66" t="inlineStr">
         <is>
-          <t>Declarații_INCHIDERE_TVA, Reguli_INCHIDERE_TVA, Jurnale_INCHIDERE_TVA, NotaExport_INCHIDERE_TVA</t>
+          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
         </is>
       </c>
       <c r="F16" s="66" t="inlineStr">
         <is>
-          <t>La fiecare lună, după rulaje TVA</t>
+          <t>La operațiuni amănunt + închidere lună amănunt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="66" t="inlineStr">
         <is>
-          <t>MOD_APROV_TRANZIT</t>
+          <t>MOD_IMPORT</t>
         </is>
       </c>
       <c r="B17" s="66" t="inlineStr">
         <is>
-          <t>F-302</t>
+          <t>F-319, F-320</t>
         </is>
       </c>
       <c r="C17" s="66" t="inlineStr">
         <is>
-          <t>32x: factură înainte de marfă / NIR înainte de factură</t>
+          <t>TVA vamală prin 446.VAMA sau plătită direct; taxele în costul stocului</t>
         </is>
       </c>
       <c r="D17" s="66" t="inlineStr">
@@ -9392,29 +9392,29 @@
       </c>
       <c r="E17" s="66" t="inlineStr">
         <is>
-          <t>Declarații_APROV_TRANZIT, Reguli_APROV_TRANZIT, Jurnale_APROV_TRANZIT, NotaExport_APROV_TRANZIT</t>
+          <t>Declarații_IMPORT, Reguli_IMPORT, Jurnale_IMPORT, NotaExport_IMPORT</t>
         </is>
       </c>
       <c r="F17" s="66" t="inlineStr">
         <is>
-          <t>La aprovizionări incomplete</t>
+          <t>La fiecare DVI</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="66" t="inlineStr">
         <is>
-          <t>MOD_IMPORT</t>
+          <t>MOD_TVA_INCASARE</t>
         </is>
       </c>
       <c r="B18" s="66" t="inlineStr">
         <is>
-          <t>F-319, F-320</t>
+          <t>F-401</t>
         </is>
       </c>
       <c r="C18" s="66" t="inlineStr">
         <is>
-          <t>TVA vamală prin 446.VAMA sau plătită direct; taxele în costul stocului</t>
+          <t>4428.INC: factură → plată/încasare → 4426/4427</t>
         </is>
       </c>
       <c r="D18" s="66" t="inlineStr">
@@ -9424,29 +9424,29 @@
       </c>
       <c r="E18" s="66" t="inlineStr">
         <is>
-          <t>Declarații_IMPORT, Reguli_IMPORT, Jurnale_IMPORT, NotaExport_IMPORT</t>
+          <t>Declarații_TVA_INC, Reguli_TVA_INC, Jurnale_TVA_INC, NotaExport_TVA_INC</t>
         </is>
       </c>
       <c r="F18" s="66" t="inlineStr">
         <is>
-          <t>La fiecare DVI</t>
+          <t>Când regimul e TVA la încasare</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="66" t="inlineStr">
         <is>
-          <t>MOD_INCHIDERE_EX</t>
+          <t>MOD_INCHIDERE_TVA</t>
         </is>
       </c>
       <c r="B19" s="66" t="inlineStr">
         <is>
-          <t>F-104</t>
+          <t>F-405</t>
         </is>
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>Închidere cls.6/7 pe 121; impozit; report 117</t>
+          <t>Închidere 4426/4427 → 4423/4424</t>
         </is>
       </c>
       <c r="D19" s="66" t="inlineStr">
@@ -9456,29 +9456,29 @@
       </c>
       <c r="E19" s="66" t="inlineStr">
         <is>
-          <t>Declarații_INCHIDERE_EX, Reguli_INCHIDERE_EX, Jurnale_INCHIDERE_EX, NotaExport_INCHIDERE_EX</t>
+          <t>Declarații_INCHIDERE_TVA, Reguli_INCHIDERE_TVA, Jurnale_INCHIDERE_TVA, NotaExport_INCHIDERE_TVA</t>
         </is>
       </c>
       <c r="F19" s="66" t="inlineStr">
         <is>
-          <t>La 31.12</t>
+          <t>La fiecare lună, după rulaje TVA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="66" t="inlineStr">
         <is>
-          <t>MOD_TVA_INCASARE</t>
+          <t>MOD_FARA_DOCUMENT</t>
         </is>
       </c>
       <c r="B20" s="66" t="inlineStr">
         <is>
-          <t>F-401</t>
+          <t>F-406</t>
         </is>
       </c>
       <c r="C20" s="66" t="inlineStr">
         <is>
-          <t>4428.INC: factură → plată/încasare → 4426/4427</t>
+          <t>TVA nedeductibilă în cheltuială; colectare la lipsa nejustificată</t>
         </is>
       </c>
       <c r="D20" s="66" t="inlineStr">
@@ -9488,29 +9488,29 @@
       </c>
       <c r="E20" s="66" t="inlineStr">
         <is>
-          <t>Declarații_TVA_INC, Reguli_TVA_INC, Jurnale_TVA_INC, NotaExport_TVA_INC</t>
+          <t>Declarații_FARA_DOCUMENT, Reguli_FARA_DOCUMENT, Jurnale_FARA_DOCUMENT, NotaExport_FARA_DOCUMENT</t>
         </is>
       </c>
       <c r="F20" s="66" t="inlineStr">
         <is>
-          <t>Când regimul e TVA la încasare</t>
+          <t>Lunar la cheltuielile auto; la fiecare inventar cu minus</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="66" t="inlineStr">
         <is>
-          <t>MOD_TAXARE_INVERSA</t>
+          <t>MOD_INTERMEDIAR</t>
         </is>
       </c>
       <c r="B21" s="66" t="inlineStr">
         <is>
-          <t>F-303, F-402</t>
+          <t>F-408, F-501, F-411</t>
         </is>
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>Autolichidare 4426 = 4427, intracomunitar și intern</t>
+          <t>408/418/473: deschidere + stingere + red flags</t>
         </is>
       </c>
       <c r="D21" s="66" t="inlineStr">
@@ -9520,29 +9520,29 @@
       </c>
       <c r="E21" s="66" t="inlineStr">
         <is>
-          <t>Declarații_TAXARE_INVERSA, Reguli_TAXARE_INVERSA, Jurnale_TAXARE_INVERSA, NotaExport_TAXARE_INVERSA</t>
+          <t>Declarații_INTERMEDIAR, Reguli_INTERMEDIAR, Jurnale_INTERMEDIAR, NotaExport_INTERMEDIAR</t>
         </is>
       </c>
       <c r="F21" s="66" t="inlineStr">
         <is>
-          <t>La fiecare factură cu taxare inversă</t>
+          <t>La facturi nesosite / sume neclare</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="66" t="inlineStr">
         <is>
-          <t>MOD_FARA_DOCUMENT</t>
+          <t>MOD_AVANSURI</t>
         </is>
       </c>
       <c r="B22" s="66" t="inlineStr">
         <is>
-          <t>F-406</t>
+          <t>F-410, F-415</t>
         </is>
       </c>
       <c r="C22" s="66" t="inlineStr">
         <is>
-          <t>TVA nedeductibilă în cheltuială; colectare la lipsa nejustificată</t>
+          <t>419/409: avans cu TVA, stingere la factura finală, supraîncasare</t>
         </is>
       </c>
       <c r="D22" s="66" t="inlineStr">
@@ -9552,29 +9552,29 @@
       </c>
       <c r="E22" s="66" t="inlineStr">
         <is>
-          <t>Declarații_FARA_DOCUMENT, Reguli_FARA_DOCUMENT, Jurnale_FARA_DOCUMENT, NotaExport_FARA_DOCUMENT</t>
+          <t>Declarații_AVANSURI, Reguli_AVANSURI, Jurnale_AVANSURI, NotaExport_AVANSURI</t>
         </is>
       </c>
       <c r="F22" s="66" t="inlineStr">
         <is>
-          <t>Lunar la cheltuielile auto; la fiecare inventar cu minus</t>
+          <t>La fiecare avans și la orice sold creditor pe 4111</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="66" t="inlineStr">
         <is>
-          <t>MOD_AVANSURI</t>
+          <t>MOD_SALARII</t>
         </is>
       </c>
       <c r="B23" s="66" t="inlineStr">
         <is>
-          <t>F-410, F-415</t>
+          <t>F-413</t>
         </is>
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>419/409: avans cu TVA, stingere la factura finală, supraîncasare</t>
+          <t>B1 Plata avansului; B2 Costurile lunii; B3 Plăți (net, taxe, CAM)</t>
         </is>
       </c>
       <c r="D23" s="66" t="inlineStr">
@@ -9584,29 +9584,29 @@
       </c>
       <c r="E23" s="66" t="inlineStr">
         <is>
-          <t>Declarații_AVANSURI, Reguli_AVANSURI, Jurnale_AVANSURI, NotaExport_AVANSURI</t>
+          <t>Declarații_SALARII, Reguli_SALARII, Jurnale_SALARII, NotaExport_SALARII</t>
         </is>
       </c>
       <c r="F23" s="66" t="inlineStr">
         <is>
-          <t>La fiecare avans și la orice sold creditor pe 4111</t>
+          <t>Lunar, pe registru de angajați</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="66" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE</t>
+          <t>MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="B24" s="66" t="inlineStr">
         <is>
-          <t>F-311, F-312, F-209</t>
+          <t>F-416, F-417, F-418, F-419</t>
         </is>
       </c>
       <c r="C24" s="66" t="inlineStr">
         <is>
-          <t>711/712/722: lanț complet producție / servicii / MF</t>
+          <t>42x: medicale, popriri, drepturi neridicate, creanțe față de foști salariați</t>
         </is>
       </c>
       <c r="D24" s="66" t="inlineStr">
@@ -9616,29 +9616,29 @@
       </c>
       <c r="E24" s="66" t="inlineStr">
         <is>
-          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
+          <t>Declarații_SALARII_EVENIMENTE, Reguli_SALARII_EVENIMENTE, Jurnale_SALARII_EVENIMENTE, NotaExport_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="F24" s="66" t="inlineStr">
         <is>
-          <t>La producție / servicii în curs</t>
+          <t>Pe eveniment, lângă statul lunar</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="66" t="inlineStr">
         <is>
-          <t>MOD_VANZ_AMANUNT</t>
+          <t>MOD_DECONT</t>
         </is>
       </c>
       <c r="B25" s="66" t="inlineStr">
         <is>
-          <t>F-316, F-318, F-317</t>
+          <t>F-502</t>
         </is>
       </c>
       <c r="C25" s="66" t="inlineStr">
         <is>
-          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
+          <t>B1 Avans; B2 Cheltuieli + TVA; B3 Regularizare avans; B4 Plată / restituire</t>
         </is>
       </c>
       <c r="D25" s="66" t="inlineStr">
@@ -9648,12 +9648,12 @@
       </c>
       <c r="E25" s="66" t="inlineStr">
         <is>
-          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+          <t>Declarații_DECONT, Reguli_DECONT, Registru_DECONT, Jurnale_DECONT, NotaExport_DECONT</t>
         </is>
       </c>
       <c r="F25" s="66" t="inlineStr">
         <is>
-          <t>La operațiuni amănunt + închidere lună amănunt</t>
+          <t>Pe decont</t>
         </is>
       </c>
     </row>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1483,7 +1483,7 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>Tier A (102, din care 39 cu rând detaliat de analitice) — tratate individual, cu analitice justificate rând cu rând</t>
+          <t>Tier A (107, din care 39 cu rând detaliat de analitice) — tratate individual, cu analitice justificate rând cu rând</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>274 conturi, cu 3 coloane noi: Analitice recomandate · Factor · Flux (pas)</t>
+          <t>279 conturi, cu 3 coloane noi: Analitice recomandate · Factor · Flux (pas)</t>
         </is>
       </c>
     </row>
@@ -10451,7 +10451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J345"/>
+  <dimension ref="A1:J350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23928,50 +23928,310 @@
     <row r="345">
       <c r="A345" s="66" t="inlineStr">
         <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="B345" s="66" t="inlineStr">
+        <is>
+          <t>Rezultatul reportat provenit din corectarea erorilor contabile</t>
+        </is>
+      </c>
+      <c r="C345" s="66" t="inlineStr">
+        <is>
+          <t>A/P</t>
+        </is>
+      </c>
+      <c r="D345" s="66" t="inlineStr">
+        <is>
+          <t>Patrimonial (real)</t>
+        </is>
+      </c>
+      <c r="E345" s="66" t="inlineStr">
+        <is>
+          <t>Capital propriu</t>
+        </is>
+      </c>
+      <c r="F345" s="66" t="inlineStr">
+        <is>
+          <t>Corecțiile de erori din exerciții anterioare ocolesc 121 și trec pe aici. Poate avea oricare sens, ca 1171 — dar spre deosebire de el, arată cât din capitalurile proprii vine dintr-o CORECȚIE, nu din profit realizat. Se transferă apoi în 1171.</t>
+        </is>
+      </c>
+      <c r="G345" s="66" t="inlineStr">
+        <is>
+          <t>1174 pe an de proveniență a erorii</t>
+        </is>
+      </c>
+      <c r="H345" s="66" t="inlineStr">
+        <is>
+          <t>N F</t>
+        </is>
+      </c>
+      <c r="I345" s="66" t="inlineStr">
+        <is>
+          <t>F-105</t>
+        </is>
+      </c>
+      <c r="J345" s="66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="66" t="inlineStr">
+        <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="B346" s="66" t="inlineStr">
+        <is>
+          <t>Rezultatul reportat reprezentând surplusul realizat din rezerve din reevaluare</t>
+        </is>
+      </c>
+      <c r="C346" s="66" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D346" s="66" t="inlineStr">
+        <is>
+          <t>Patrimonial (real)</t>
+        </is>
+      </c>
+      <c r="E346" s="66" t="inlineStr">
+        <is>
+          <t>Capital propriu</t>
+        </is>
+      </c>
+      <c r="F346" s="66" t="inlineStr">
+        <is>
+          <t>Partea din rezerva de reevaluare devenită realizată pe măsura amortizării activului reevaluat. Sold creditor: e o rezervă realizată, nu un rezultat de repartizat direct.</t>
+        </is>
+      </c>
+      <c r="G346" s="66" t="inlineStr">
+        <is>
+          <t>1175 pe activ reevaluat</t>
+        </is>
+      </c>
+      <c r="H346" s="66" t="inlineStr">
+        <is>
+          <t>C F</t>
+        </is>
+      </c>
+      <c r="I346" s="66" t="inlineStr">
+        <is>
+          <t>F-102</t>
+        </is>
+      </c>
+      <c r="J346" s="66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="66" t="inlineStr">
+        <is>
+          <t>4382</t>
+        </is>
+      </c>
+      <c r="B347" s="66" t="inlineStr">
+        <is>
+          <t>Alte creanțe sociale</t>
+        </is>
+      </c>
+      <c r="C347" s="66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D347" s="66" t="inlineStr">
+        <is>
+          <t>Patrimonial (real)</t>
+        </is>
+      </c>
+      <c r="E347" s="66" t="inlineStr">
+        <is>
+          <t>Creanță</t>
+        </is>
+      </c>
+      <c r="F347" s="66" t="inlineStr">
+        <is>
+          <t>Partea din indemnizația de concediu medical suportată de FNUASS și avansată de firmă. E CREANȚĂ față de casă, nu cheltuială — cheltuială e doar partea angajatorului, pe 6458. Sold creditor = contrar naturii (C-23).</t>
+        </is>
+      </c>
+      <c r="G347" s="66" t="inlineStr">
+        <is>
+          <t>4382 pe lună de recuperare</t>
+        </is>
+      </c>
+      <c r="H347" s="66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I347" s="66" t="inlineStr">
+        <is>
+          <t>F-416</t>
+        </is>
+      </c>
+      <c r="J347" s="66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="66" t="inlineStr">
+        <is>
+          <t>4418</t>
+        </is>
+      </c>
+      <c r="B348" s="66" t="inlineStr">
+        <is>
+          <t>Impozitul pe venit</t>
+        </is>
+      </c>
+      <c r="C348" s="66" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D348" s="66" t="inlineStr">
+        <is>
+          <t>Patrimonial (real)</t>
+        </is>
+      </c>
+      <c r="E348" s="66" t="inlineStr">
+        <is>
+          <t>Datorie</t>
+        </is>
+      </c>
+      <c r="F348" s="66" t="inlineStr">
+        <is>
+          <t>Impozitul microîntreprinderii. E impozit pe VENIT, nu pe profit — de aceea nu poate sta pe un analitic al lui 4411, iar cheltuială corespondentă e 698, nu 691. Sold normal: creditor.</t>
+        </is>
+      </c>
+      <c r="G348" s="66" t="inlineStr">
+        <is>
+          <t>4418 pe trimestru</t>
+        </is>
+      </c>
+      <c r="H348" s="66" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I348" s="66" t="inlineStr">
+        <is>
+          <t>F-420</t>
+        </is>
+      </c>
+      <c r="J348" s="66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="66" t="inlineStr">
+        <is>
+          <t>5124</t>
+        </is>
+      </c>
+      <c r="B349" s="66" t="inlineStr">
+        <is>
+          <t>Conturi la bănci în valută</t>
+        </is>
+      </c>
+      <c r="C349" s="66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D349" s="66" t="inlineStr">
+        <is>
+          <t>Patrimonial (real)</t>
+        </is>
+      </c>
+      <c r="E349" s="66" t="inlineStr">
+        <is>
+          <t>Trezorerie</t>
+        </is>
+      </c>
+      <c r="F349" s="66" t="inlineStr">
+        <is>
+          <t>Contul de valută, ținut pe fiecare monedă. Se reevaluează la curs la fiecare închidere, cu diferențele pe 765/665 — spre deosebire de 5121, care nu are ce reevalua.</t>
+        </is>
+      </c>
+      <c r="G349" s="66" t="inlineStr">
+        <is>
+          <t>5124 pe bancă ȘI pe valută</t>
+        </is>
+      </c>
+      <c r="H349" s="66" t="inlineStr">
+        <is>
+          <t>V O</t>
+        </is>
+      </c>
+      <c r="I349" s="66" t="inlineStr">
+        <is>
+          <t>F-107</t>
+        </is>
+      </c>
+      <c r="J349" s="66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="66" t="inlineStr">
+        <is>
           <t>4482</t>
         </is>
       </c>
-      <c r="B345" s="66" t="inlineStr">
+      <c r="B350" s="66" t="inlineStr">
         <is>
           <t>Alte creanțe privind bugetul statului</t>
         </is>
       </c>
-      <c r="C345" s="66" t="inlineStr">
+      <c r="C350" s="66" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D345" s="66" t="inlineStr">
+      <c r="D350" s="66" t="inlineStr">
         <is>
           <t>Rol în flux</t>
         </is>
       </c>
-      <c r="E345" s="66" t="inlineStr">
+      <c r="E350" s="66" t="inlineStr">
         <is>
           <t>Intermediar / clarificare</t>
         </is>
       </c>
-      <c r="F345" s="66" t="inlineStr">
+      <c r="F350" s="66" t="inlineStr">
         <is>
           <t>Sumele plătite eronat către buget, până la lămurire: cifre inversate pe ordinul de plată, sau plată făcută cu alt CUI de plătitor. Sold în așteptare care se disecă — nu se lasă de la un an la altul.</t>
         </is>
       </c>
-      <c r="G345" s="66" t="inlineStr">
+      <c r="G350" s="66" t="inlineStr">
         <is>
           <t>4482 pe plată în așteptare</t>
         </is>
       </c>
-      <c r="H345" s="66" t="inlineStr">
+      <c r="H350" s="66" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I345" s="66" t="inlineStr">
+      <c r="I350" s="66" t="inlineStr">
         <is>
           <t>F-425</t>
         </is>
       </c>
-      <c r="J345" s="66" t="inlineStr">
+      <c r="J350" s="66" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1483,7 +1483,7 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>Tier A (107, din care 39 cu rând detaliat de analitice) — tratate individual, cu analitice justificate rând cu rând</t>
+          <t>Tier A (107, din care 42 cu rând detaliat de analitice) — tratate individual, cu analitice justificate rând cu rând</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
     <row r="117">
       <c r="A117" s="61" t="inlineStr">
         <is>
-          <t>intrebari-formator.md / .html — cele 20 întrebări rămase deschise (din 33: 13 verificate cu temei legal, 9 decizii de cabinet), grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
+          <t>intrebari-formator.md / .html — cele 23 întrebări rămase deschise (din 36: 13 verificate cu temei legal, 9 decizii de cabinet), grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5825,32 +5825,32 @@
       </c>
       <c r="B39" s="61" t="inlineStr">
         <is>
-          <t>Microîntreprindere — prag și cotă</t>
+          <t>Salarii — praguri și baze de calcul</t>
         </is>
       </c>
       <c r="C39" s="61" t="inlineStr">
         <is>
-          <t>Care sunt pragul de venituri și cota de impozit pentru microîntreprinderi, în vigoare la data operațiunii?</t>
+          <t>Care e plafonul legal al sumei care se poate imputa unui salariat pentru o pagubă produsă, și în ce ritm se poate reține din salariu?</t>
         </is>
       </c>
       <c r="D39" s="61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-426</t>
         </is>
       </c>
       <c r="E39" s="61" t="inlineStr">
         <is>
-          <t>Fluxul de impozit micro (698 = 4418) și avertizarea clientului care se apropie de prag. Trecerea se face din trimestrul depășirii, deci un prag greșit înseamnă o declarație greșită, nu doar o estimare.</t>
+          <t>F-426 pasul 5, unde reținerea din 421 stinge creanța de pe 461. Dacă plafonul e mai mic decât paguba, fluxul are nevoie de un pas de eșalonare, iar creanța rămâne pe 461 mai multe luni.</t>
         </is>
       </c>
       <c r="F39" s="61" t="inlineStr">
         <is>
-          <t>Am folosit 100.000 EUR și 1% ca în notițe, marcate ❓.</t>
+          <t>Am modelat imputația integrală, cu reținere într-o singură lună, pentru că exemplul din notițe e de 1.000 lei — sub orice plafon plauzibil. Pasul poartă ❓. De verificat art. 254 (răspunderea patrimonială) și art. 169 (reținerile din salariu) din Codul muncii.</t>
         </is>
       </c>
       <c r="G39" s="61" t="inlineStr">
         <is>
-          <t>training 21.08.2026, punctul 2</t>
+          <t>training 26.08.2026, punctul 1</t>
         </is>
       </c>
     </row>
@@ -5862,12 +5862,12 @@
       </c>
       <c r="B40" s="61" t="inlineStr">
         <is>
-          <t>Decontul de TVA și fișa de rol</t>
+          <t>Dividende — CASS, declarații și termene</t>
         </is>
       </c>
       <c r="C40" s="61" t="inlineStr">
         <is>
-          <t>Ce rânduri din D300 sunt preluate în fișa de rol: 36 și 37, sau 44 și 45?</t>
+          <t>CASS pe dividende se datorează la dividendele DISTRIBUITE sau la cele efectiv RIDICATE?</t>
         </is>
       </c>
       <c r="D40" s="61" t="inlineStr">
@@ -5877,17 +5877,17 @@
       </c>
       <c r="E40" s="61" t="inlineStr">
         <is>
-          <t>Corelația decont ↔ fișă de rol ↔ balanță. Fără numerele corecte, corelația nu se poate scrie ca formulă, ci doar descrie.</t>
+          <t>Momentul în care se naște obligația de CASS și, prin el, ce arată Declarația Unică față de soldul lui 457. Un 457 cu sold creditor la 31.12 înseamnă dividende distribuite și neridicate: dacă baza CASS e distribuirea, obligația există deja; dacă e ridicarea, nu.</t>
         </is>
       </c>
       <c r="F40" s="61" t="inlineStr">
         <is>
-          <t>Am scris corelația pe SOLD, care nu depinde de numerotarea rândurilor, și am marcat rândurile ca deschise.</t>
+          <t>Am urmat notițele — baza e ridicarea — pentru că le confirmă structura declarației (două rubrici înseamnă două momente). Locul de verificat e art. 170 din Codul fiscal, care descrie ce venituri intră în baza anuală; n-am putut-o confirma pe sursă publică, deci rămâne întrebare, nu răspuns. Contrastul cu impozitul e clar și el e sigur: impozitul de 16% se datorează la DISTRIBUIRE, cu termen 25.01, indiferent de ridicare.</t>
         </is>
       </c>
       <c r="G40" s="61" t="inlineStr">
         <is>
-          <t>training 21.08.2026, punctul 5</t>
+          <t>training 26.08.2026, punctul 2</t>
         </is>
       </c>
     </row>
@@ -5899,32 +5899,34 @@
       </c>
       <c r="B41" s="61" t="inlineStr">
         <is>
-          <t>Decontul de TVA și fișa de rol</t>
+          <t>Acte de control — 4423 sau 4481</t>
         </is>
       </c>
       <c r="C41" s="61" t="inlineStr">
         <is>
-          <t>La declarațiile care admit rectificare, contează ordinea cronologică a înregistrării facturilor la redepunere?</t>
+          <t>Sumele stabilite prin decizie de impunere pe TVA se înregistrează în 4423 cu analitic distinct, sau în 4481?</t>
         </is>
       </c>
       <c r="D41" s="61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-421
+C-29
+C-33</t>
         </is>
       </c>
       <c r="E41" s="61" t="inlineStr">
         <is>
-          <t>Procedura de corecție după depunere, pe toate declarațiile care admit rectificativă. Decontul de TVA nu admite, deci acolo întrebarea nu se pune — dar la celelalte, da.</t>
+          <t>F-421 în întregime, corelațiile C-29 și C-33, și structura analitică a lui 4423. Nu e o nuanță de stil: cele două variante dau solduri diferite pe contul pe care decontul de TVA îl reconciliază.</t>
         </is>
       </c>
       <c r="F41" s="61" t="inlineStr">
         <is>
-          <t>N-am implementat nimic pe presupunerea asta.</t>
+          <t>Am adoptat varianta din 26.08, pentru că e singura care dă un motiv verificabil: un analitic separă EVIDENȚA, dar nu separă SOLDUL, iar decontul se compară pe soldul sintetic al lui 4423. F-421 e rescris pe 4481, cu ❓ pe el. Dacă formatorul confirmă varianta din 21.08, fluxul se întoarce — dar atunci trebuie explicat cum rămâne corelația decont ↔ balanță valabilă, pentru că azi nu văd cum.</t>
         </is>
       </c>
       <c r="G41" s="61" t="inlineStr">
         <is>
-          <t>training 21.08.2026, punctul 6</t>
+          <t>training 26.08.2026, punctul 3</t>
         </is>
       </c>
     </row>
@@ -5936,50 +5938,161 @@
       </c>
       <c r="B42" s="61" t="inlineStr">
         <is>
+          <t>Microîntreprindere — prag și cotă</t>
+        </is>
+      </c>
+      <c r="C42" s="61" t="inlineStr">
+        <is>
+          <t>Care sunt pragul de venituri și cota de impozit pentru microîntreprinderi, în vigoare la data operațiunii?</t>
+        </is>
+      </c>
+      <c r="D42" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="61" t="inlineStr">
+        <is>
+          <t>Fluxul de impozit micro (698 = 4418) și avertizarea clientului care se apropie de prag. Trecerea se face din trimestrul depășirii, deci un prag greșit înseamnă o declarație greșită, nu doar o estimare.</t>
+        </is>
+      </c>
+      <c r="F42" s="61" t="inlineStr">
+        <is>
+          <t>Am folosit 100.000 EUR și 1% ca în notițe, marcate ❓.</t>
+        </is>
+      </c>
+      <c r="G42" s="61" t="inlineStr">
+        <is>
+          <t>training 21.08.2026, punctul 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="61" t="inlineStr">
+        <is>
+          <t>Î-34</t>
+        </is>
+      </c>
+      <c r="B43" s="61" t="inlineStr">
+        <is>
           <t>Decontul de TVA și fișa de rol</t>
         </is>
       </c>
-      <c r="C42" s="61" t="inlineStr">
+      <c r="C43" s="61" t="inlineStr">
+        <is>
+          <t>Ce rânduri din D300 sunt preluate în fișa de rol: 36 și 37, sau 44 și 45?</t>
+        </is>
+      </c>
+      <c r="D43" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="61" t="inlineStr">
+        <is>
+          <t>Corelația decont ↔ fișă de rol ↔ balanță. Fără numerele corecte, corelația nu se poate scrie ca formulă, ci doar descrie.</t>
+        </is>
+      </c>
+      <c r="F43" s="61" t="inlineStr">
+        <is>
+          <t>Am scris corelația pe SOLD, care nu depinde de numerotarea rândurilor, și am marcat rândurile ca deschise.</t>
+        </is>
+      </c>
+      <c r="G43" s="61" t="inlineStr">
+        <is>
+          <t>training 21.08.2026, punctul 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="61" t="inlineStr">
+        <is>
+          <t>Î-35</t>
+        </is>
+      </c>
+      <c r="B44" s="61" t="inlineStr">
+        <is>
+          <t>Decontul de TVA și fișa de rol</t>
+        </is>
+      </c>
+      <c r="C44" s="61" t="inlineStr">
+        <is>
+          <t>La declarațiile care admit rectificare, contează ordinea cronologică a înregistrării facturilor la redepunere?</t>
+        </is>
+      </c>
+      <c r="D44" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="61" t="inlineStr">
+        <is>
+          <t>Procedura de corecție după depunere, pe toate declarațiile care admit rectificativă. Decontul de TVA nu admite, deci acolo întrebarea nu se pune — dar la celelalte, da.</t>
+        </is>
+      </c>
+      <c r="F44" s="61" t="inlineStr">
+        <is>
+          <t>N-am implementat nimic pe presupunerea asta.</t>
+        </is>
+      </c>
+      <c r="G44" s="61" t="inlineStr">
+        <is>
+          <t>training 21.08.2026, punctul 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="61" t="inlineStr">
+        <is>
+          <t>Î-36</t>
+        </is>
+      </c>
+      <c r="B45" s="61" t="inlineStr">
+        <is>
+          <t>Decontul de TVA și fișa de rol</t>
+        </is>
+      </c>
+      <c r="C45" s="61" t="inlineStr">
         <is>
           <t>Care sunt corelațiile complete între D300 și fișa de rol la TVA?</t>
         </is>
       </c>
-      <c r="D42" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="61" t="inlineStr">
+      <c r="D45" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="61" t="inlineStr">
         <is>
           <t>Corelațiile de control pe TVA. Ce avem acum se verifică pe sold; corelația pe rulaj, rând cu rând, are nevoie de structura exactă a fișei de rol.</t>
         </is>
       </c>
-      <c r="F42" s="61" t="inlineStr">
+      <c r="F45" s="61" t="inlineStr">
         <is>
           <t>Am scris corelația pe sold și am lăsat-o pe cea pe rulaj ca gol declarat — n-am fișă de rol de citit.</t>
         </is>
       </c>
-      <c r="G42" s="61" t="inlineStr">
+      <c r="G45" s="61" t="inlineStr">
         <is>
           <t>training 21.08.2026, punctul 7</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="63" t="inlineStr">
-        <is>
-          <t>33 de întrebări, 18 teme. Aceeași sursă cu dist/intrebari-formator.md și cu pagina publicată — nu pot diverge.</t>
+    <row r="47">
+      <c r="A47" s="63" t="inlineStr">
+        <is>
+          <t>36 de întrebări, 20 teme. Aceeași sursă cu dist/intrebari-formator.md și cu pagina publicată — nu pot diverge.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A44:G44"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A47:G47"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10390,7 +10503,7 @@
     <row r="30">
       <c r="A30" s="33" t="inlineStr">
         <is>
-          <t>2. Pe corelație: Corelații de control → C-01…C-29 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
+          <t>2. Pe corelație: Corelații de control → C-01…C-34 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
         </is>
       </c>
     </row>
@@ -26919,7 +27032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27015,757 +27128,757 @@
     <row r="4">
       <c r="A4" s="66" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="B4" s="66" t="inlineStr">
         <is>
-          <t>Rezerve din reevaluare</t>
+          <t>Capital subscris vărsat</t>
         </is>
       </c>
       <c r="C4" s="66" t="inlineStr">
         <is>
-          <t>105 pe fiecare ACTIV și fiecare reevaluare</t>
+          <t>1012 pe fiecare ASOCIAT, cu PROCENTUL în denumirea analiticului</t>
         </is>
       </c>
       <c r="D4" s="66" t="inlineStr">
         <is>
-          <t>C F</t>
+          <t>N C O</t>
         </is>
       </c>
       <c r="E4" s="66" t="inlineStr">
         <is>
-          <t>Nu poți proba impozitarea corelată cu amortizarea, nici ce sumă e distribuibilă</t>
+          <t>Hotărârea AGA nu se poate contraverifica din balanță: cotele rămân doar în actul constitutiv, iar repartizarea de dividende se face pe încredere</t>
         </is>
       </c>
       <c r="F4" s="66" t="inlineStr">
         <is>
-          <t>Surplusul realizat trece în 1175. Nu poate majora capitalul social (art. 210 alin. 3 L. 31/1990).</t>
+          <t>Procentul în denumire nu e cosmetic — el face balanța să răspundă singură la „cine cât deține”. La preluarea unei firme cu 1012 „la grămadă”, cota se ia de la ONRC și se creează analiticele (F-114). C-31.</t>
         </is>
       </c>
       <c r="G4" s="66" t="inlineStr">
         <is>
-          <t>F-102</t>
+          <t>F-114, F-109, F-112</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="66" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B5" s="66" t="inlineStr">
+        <is>
+          <t>Rezerve din reevaluare</t>
+        </is>
+      </c>
+      <c r="C5" s="66" t="inlineStr">
+        <is>
+          <t>105 pe fiecare ACTIV și fiecare reevaluare</t>
+        </is>
+      </c>
+      <c r="D5" s="66" t="inlineStr">
+        <is>
+          <t>C F</t>
+        </is>
+      </c>
+      <c r="E5" s="66" t="inlineStr">
+        <is>
+          <t>Nu poți proba impozitarea corelată cu amortizarea, nici ce sumă e distribuibilă</t>
+        </is>
+      </c>
+      <c r="F5" s="66" t="inlineStr">
+        <is>
+          <t>Surplusul realizat trece în 1175. Nu poate majora capitalul social (art. 210 alin. 3 L. 31/1990).</t>
+        </is>
+      </c>
+      <c r="G5" s="66" t="inlineStr">
+        <is>
+          <t>F-102</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="66" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="B5" s="66" t="inlineStr">
+      <c r="B6" s="66" t="inlineStr">
         <is>
           <t>Rezerve legale</t>
         </is>
       </c>
-      <c r="C5" s="66" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
         <is>
           <t>1061 (sintetic e suficient; plafonul se urmărește față de 1012)</t>
         </is>
       </c>
-      <c r="D5" s="66" t="inlineStr">
+      <c r="D6" s="66" t="inlineStr">
         <is>
           <t>N F</t>
         </is>
       </c>
-      <c r="E5" s="66" t="inlineStr">
+      <c r="E6" s="66" t="inlineStr">
         <is>
           <t>Depășirea plafonului de 20% din capitalul vărsat sau a limitei de 5% din profitul contabil brut → partea în plus e nedeductibilă</t>
         </is>
       </c>
-      <c r="F5" s="66" t="inlineStr">
+      <c r="F6" s="66" t="inlineStr">
         <is>
           <t>Bază fiscală = sold creditor 121 + rulaj 691 (art. 26 alin. 1 lit. a CF).</t>
         </is>
       </c>
-      <c r="G5" s="66" t="inlineStr">
+      <c r="G6" s="66" t="inlineStr">
         <is>
           <t>F-103</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>Rezultatul reportat</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>117.1 profit / 117.2 pierdere (opțional) | 1171 PE AN, cu sens D/C explicit · 1174 corecții · 1175 surplus reevaluare [N]</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>B | N F B</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>Prezentare bilanț greșită pe ani anteriori | Recuperarea pierderii (70% din profitul impozabil, 5 ani) devine neurmăribilă; plafonul de dividende distribuibile iese supraevaluat</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="inlineStr">
-        <is>
-          <t>1174 e TRANZITORIU — nu poate rămâne cu sold la 31.12 (C-18). Pentru pierderea nerecuperabilă fiscal se folosește un analitic de gestiune, nu un sintetic distinct (nu există).</t>
-        </is>
-      </c>
-      <c r="G6" s="22" t="inlineStr">
-        <is>
-          <t>F-104 | F-103, F-105, F-102</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="22" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Rezultatul reportat</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>117.1 profit / 117.2 pierdere (opțional) | 1171 PE AN, cu sens D/C explicit · 1174 corecții · 1175 surplus reevaluare [N]</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>B | N F B</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>Prezentare bilanț greșită pe ani anteriori | Recuperarea pierderii (70% din profitul impozabil, 5 ani) devine neurmăribilă; plafonul de dividende distribuibile iese supraevaluat</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>1174 e TRANZITORIU — nu poate rămâne cu sold la 31.12 (C-18). Pentru pierderea nerecuperabilă fiscal se folosește un analitic de gestiune, nu un sintetic distinct (nu există).</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F-104 | F-103, F-105, F-102</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
           <t>121/129</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Profit/pierdere + repartizare</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>121 / 129</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>Închiderea exercițiului nu colectează corect cls.6+7; repartizare greșită</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>121 colectează; 129 distribuie spre rezerve/117.</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>F-104</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="66" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="B8" s="66" t="inlineStr">
-        <is>
-          <t>Repartizarea profitului</t>
-        </is>
-      </c>
-      <c r="C8" s="66" t="inlineStr">
-        <is>
-          <t>129 (sintetic)</t>
-        </is>
-      </c>
-      <c r="D8" s="66" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E8" s="66" t="inlineStr">
-        <is>
-          <t>Sold 129 rămas după repartizare = închidere omisă; corelația C-16 nu ține</t>
-        </is>
-      </c>
-      <c r="F8" s="66" t="inlineStr">
-        <is>
-          <t>Sold DEBITOR: se închide prin creditare (`121 = 129`), nu invers.</t>
-        </is>
-      </c>
-      <c r="G8" s="66" t="inlineStr">
-        <is>
-          <t>F-103</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="66" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B9" s="66" t="inlineStr">
         <is>
-          <t>Provizioane</t>
+          <t>Repartizarea profitului</t>
         </is>
       </c>
       <c r="C9" s="66" t="inlineStr">
         <is>
-          <t>1511 litigii · 1512 garanții clienți · 1514 restructurare · 1516 impozite · 1518 alte provizioane [N]</t>
+          <t>129 (sintetic)</t>
         </is>
       </c>
       <c r="D9" s="66" t="inlineStr">
         <is>
-          <t>N F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E9" s="66" t="inlineStr">
         <is>
-          <t>Provizionul nu poate fi utilizat pentru altă cheltuială decât cea pentru care a fost constituit — fără analitic pe motiv, regula devine neverificabilă</t>
+          <t>Sold 129 rămas după repartizare = închidere omisă; corelația C-16 nu ține</t>
         </is>
       </c>
       <c r="F9" s="66" t="inlineStr">
         <is>
-          <t>Litigiile sunt NEDEDUCTIBILE (art. 26 CF, listă limitativă); reluarea pe 7812 = venit neimpozabil.</t>
+          <t>Sold DEBITOR: se închide prin creditare (`121 = 129`), nu invers.</t>
         </is>
       </c>
       <c r="G9" s="66" t="inlineStr">
         <is>
-          <t>F-106</t>
+          <t>F-103</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="66" t="inlineStr">
         <is>
-          <t>162x</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B10" s="66" t="inlineStr">
         <is>
-          <t>Credite bancare pe termen lung</t>
+          <t>Provizioane</t>
         </is>
       </c>
       <c r="C10" s="66" t="inlineStr">
         <is>
-          <t>1621…1627 sunt SINTETICE distincte + analitic pe contract și pe VALUTĂ · 1682 dobânzi neajunse la scadență</t>
+          <t>1511 litigii · 1512 garanții clienți · 1514 restructurare · 1516 impozite · 1518 alte provizioane [N]</t>
         </is>
       </c>
       <c r="D10" s="66" t="inlineStr">
         <is>
-          <t>V B</t>
+          <t>N F</t>
         </is>
       </c>
       <c r="E10" s="66" t="inlineStr">
         <is>
-          <t>Reevaluarea lunară se face la curs greșit; porțiunea curentă (≤ 12 luni) nu se poate reclasifica pentru bilanț</t>
+          <t>Provizionul nu poate fi utilizat pentru altă cheltuială decât cea pentru care a fost constituit — fără analitic pe motiv, regula devine neverificabilă</t>
         </is>
       </c>
       <c r="F10" s="66" t="inlineStr">
         <is>
-          <t>Reevaluare LUNARĂ obligatorie (OMFP 1802/2014). Verifică soldul în valută: sold valută × curs BNR = sold lei.</t>
+          <t>Litigiile sunt NEDEDUCTIBILE (art. 26 CF, listă limitativă); reluarea pe 7812 = venit neimpozabil.</t>
         </is>
       </c>
       <c r="G10" s="66" t="inlineStr">
         <is>
-          <t>F-107</t>
+          <t>F-106</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="66" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>162x</t>
         </is>
       </c>
       <c r="B11" s="66" t="inlineStr">
         <is>
-          <t>Alte împrumuturi și datorii asimilate (leasing financiar)</t>
+          <t>Credite bancare pe termen lung</t>
         </is>
       </c>
       <c r="C11" s="66" t="inlineStr">
         <is>
-          <t>167 PE CONTRACT — 1 la 1 cu contractul, indiferent câte bunuri conține — și pe tip de VALUTĂ</t>
+          <t>1621…1627 sunt SINTETICE distincte + analitic pe contract și pe VALUTĂ · 1682 dobânzi neajunse la scadență</t>
         </is>
       </c>
       <c r="D11" s="66" t="inlineStr">
         <is>
-          <t>C V O</t>
+          <t>V B</t>
         </is>
       </c>
       <c r="E11" s="66" t="inlineStr">
         <is>
-          <t>Nu mai știi la ce rată din scadențar te raportezi → reevaluarea soldului se face greșit; corelația C-19 nu se poate verifica</t>
+          <t>Reevaluarea lunară se face la curs greșit; porțiunea curentă (≤ 12 luni) nu se poate reclasifica pentru bilanț</t>
         </is>
       </c>
       <c r="F11" s="66" t="inlineStr">
         <is>
-          <t>Avansul (4093) se închide în 167 la recepție. Impozitul local e datorat de LOCATAR pe toată durata contractului.</t>
+          <t>Reevaluare LUNARĂ obligatorie (OMFP 1802/2014). Verifică soldul în valută: sold valută × curs BNR = sold lei.</t>
         </is>
       </c>
       <c r="G11" s="66" t="inlineStr">
         <is>
-          <t>F-108</t>
+          <t>F-107</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="66" t="inlineStr">
         <is>
-          <t>205 / 208</t>
+          <t>167</t>
         </is>
       </c>
       <c r="B12" s="66" t="inlineStr">
         <is>
-          <t>Concesiuni, brevete, licențe, mărci / Alte imobilizări necorporale</t>
+          <t>Alte împrumuturi și datorii asimilate (leasing financiar)</t>
         </is>
       </c>
       <c r="C12" s="66" t="inlineStr">
         <is>
-          <t>205 pe titlu (marcă, licență) · 208 pe program</t>
+          <t>167 PE CONTRACT — 1 la 1 cu contractul, indiferent câte bunuri conține — și pe tip de VALUTĂ</t>
         </is>
       </c>
       <c r="D12" s="66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>C V O</t>
         </is>
       </c>
       <c r="E12" s="66" t="inlineStr">
         <is>
-          <t>Duratele diferite (mărci 10 ani, softuri uzual 3 ani) nu se pot urmări pe același sintetic</t>
+          <t>Nu mai știi la ce rată din scadențar te raportezi → reevaluarea soldului se face greșit; corelația C-19 nu se poate verifica</t>
         </is>
       </c>
       <c r="F12" s="66" t="inlineStr">
         <is>
-          <t>Amortizare: 6811 = 2805 / 2808. Contul 7815 din notițe NU există.</t>
+          <t>Avansul (4093) se închide în 167 la recepție. Impozitul local e datorat de LOCATAR pe toată durata contractului.</t>
         </is>
       </c>
       <c r="G12" s="66" t="inlineStr">
         <is>
-          <t>F-201</t>
+          <t>F-108</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="66" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>205 / 208</t>
         </is>
       </c>
       <c r="B13" s="66" t="inlineStr">
         <is>
-          <t>Terenuri și amenajări de terenuri</t>
+          <t>Concesiuni, brevete, licențe, mărci / Alte imobilizări necorporale</t>
         </is>
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>2111 terenuri, pe CATEGORIE DE FOLOSINȚĂ (arabil, curți-construcții, în curs de construcții) · 2112 amenajări [N]</t>
+          <t>205 pe titlu (marcă, licență) · 208 pe program</t>
         </is>
       </c>
       <c r="D13" s="66" t="inlineStr">
         <is>
-          <t>N F O</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E13" s="66" t="inlineStr">
         <is>
-          <t>Tratamentul fiscal la vânzare diferă pe categorie; amenajarea (amortizabilă) se confundă cu terenul (neamortizabil)</t>
+          <t>Duratele diferite (mărci 10 ani, softuri uzual 3 ani) nu se pot urmări pe același sintetic</t>
         </is>
       </c>
       <c r="F13" s="66" t="inlineStr">
         <is>
-          <t>2111 nu are cont de amortizare. 2112 se amortizează pe 10 ani, cont pereche 2811.</t>
+          <t>Amortizare: 6811 = 2805 / 2808. Contul 7815 din notițe NU există.</t>
         </is>
       </c>
       <c r="G13" s="66" t="inlineStr">
         <is>
-          <t>F-202</t>
+          <t>F-201</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="66" t="inlineStr">
         <is>
-          <t>212 / 213 / 214 / 215</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B14" s="66" t="inlineStr">
         <is>
-          <t>Construcții / Instalații și mijloace de transport / Mobilier și birotică / Investiții imobiliare</t>
+          <t>Terenuri și amenajări de terenuri</t>
         </is>
       </c>
       <c r="C14" s="66" t="inlineStr">
         <is>
-          <t>analitic PE MIJLOC FIX, cu COD DE CLASIFICARE din catalog și durată</t>
+          <t>2111 terenuri, pe CATEGORIE DE FOLOSINȚĂ (arabil, curți-construcții, în curs de construcții) · 2112 amenajări [N]</t>
         </is>
       </c>
       <c r="D14" s="66" t="inlineStr">
         <is>
-          <t>N C D O</t>
+          <t>N F O</t>
         </is>
       </c>
       <c r="E14" s="66" t="inlineStr">
         <is>
-          <t>Durata de amortizare se calculează greșit; oglinda cu 28x (C-14) și confruntarea cu registrul MF (C-15) devin imposibile; D406/SAF-T incomplet</t>
+          <t>Tratamentul fiscal la vânzare diferă pe categorie; amenajarea (amortizabilă) se confundă cu terenul (neamortizabil)</t>
         </is>
       </c>
       <c r="F14" s="66" t="inlineStr">
         <is>
-          <t>Codul de clasificare se trece în modulul de mijloace fixe — alimentează D406. Clădirile au obligatoriu amortizare liniară.</t>
+          <t>2111 nu are cont de amortizare. 2112 se amortizează pe 10 ani, cont pereche 2811.</t>
         </is>
       </c>
       <c r="G14" s="66" t="inlineStr">
         <is>
-          <t>F-203, F-205, F-206, F-211</t>
+          <t>F-202</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="66" t="inlineStr">
         <is>
-          <t>223 / 224</t>
+          <t>212 / 213 / 214 / 215</t>
         </is>
       </c>
       <c r="B15" s="66" t="inlineStr">
         <is>
-          <t>Imobilizări corporale în curs de aprovizionare</t>
+          <t>Construcții / Instalații și mijloace de transport / Mobilier și birotică / Investiții imobiliare</t>
         </is>
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>223 → 213 · 224 → 214 (tranzit)</t>
+          <t>analitic PE MIJLOC FIX, cu COD DE CLASIFICARE din catalog și durată</t>
         </is>
       </c>
       <c r="D15" s="66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N C D O</t>
         </is>
       </c>
       <c r="E15" s="66" t="inlineStr">
         <is>
-          <t>Bun facturat nerecepționat fie dispare din evidență, fie se amortizează deși nu există fizic</t>
+          <t>Durata de amortizare se calculează greșit; oglinda cu 28x (C-14) și confruntarea cu registrul MF (C-15) devin imposibile; D406/SAF-T incomplet</t>
         </is>
       </c>
       <c r="F15" s="66" t="inlineStr">
         <is>
-          <t>Oglinda lui 32x, pe imobilizări. Se stinge la procesul-verbal de recepție.</t>
+          <t>Codul de clasificare se trece în modulul de mijloace fixe — alimentează D406. Clădirile au obligatoriu amortizare liniară.</t>
         </is>
       </c>
       <c r="G15" s="66" t="inlineStr">
         <is>
-          <t>F-207</t>
+          <t>F-203, F-205, F-206, F-211</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="66" t="inlineStr">
         <is>
-          <t>231 / 233</t>
+          <t>223 / 224</t>
         </is>
       </c>
       <c r="B16" s="66" t="inlineStr">
         <is>
-          <t>Imobilizări corporale / necorporale în curs de execuție</t>
+          <t>Imobilizări corporale în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C16" s="66" t="inlineStr">
         <is>
-          <t>analitic PE OBIECTIV de investiții</t>
+          <t>223 → 213 · 224 → 214 (tranzit)</t>
         </is>
       </c>
       <c r="D16" s="66" t="inlineStr">
         <is>
-          <t>C O B</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E16" s="66" t="inlineStr">
         <is>
-          <t>La 31.12 nu poți spune ce e în sold (C-22); obiectivele finalizate rămân neamortizate</t>
+          <t>Bun facturat nerecepționat fie dispare din evidență, fie se amortizează deși nu există fizic</t>
         </is>
       </c>
       <c r="F16" s="66" t="inlineStr">
         <is>
-          <t>Prestațiile terților merg în 231, NU pe 628. Salariile proprii se capitalizează prin 722 (corporale) / 721 (necorporale). 235 = Investiții imobiliare în curs.</t>
+          <t>Oglinda lui 32x, pe imobilizări. Se stinge la procesul-verbal de recepție.</t>
         </is>
       </c>
       <c r="G16" s="66" t="inlineStr">
         <is>
-          <t>F-201, F-208</t>
+          <t>F-207</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="66" t="inlineStr">
         <is>
+          <t>231 / 233</t>
+        </is>
+      </c>
+      <c r="B17" s="66" t="inlineStr">
+        <is>
+          <t>Imobilizări corporale / necorporale în curs de execuție</t>
+        </is>
+      </c>
+      <c r="C17" s="66" t="inlineStr">
+        <is>
+          <t>analitic PE OBIECTIV de investiții</t>
+        </is>
+      </c>
+      <c r="D17" s="66" t="inlineStr">
+        <is>
+          <t>C O B</t>
+        </is>
+      </c>
+      <c r="E17" s="66" t="inlineStr">
+        <is>
+          <t>La 31.12 nu poți spune ce e în sold (C-22); obiectivele finalizate rămân neamortizate</t>
+        </is>
+      </c>
+      <c r="F17" s="66" t="inlineStr">
+        <is>
+          <t>Prestațiile terților merg în 231, NU pe 628. Salariile proprii se capitalizează prin 722 (corporale) / 721 (necorporale). 235 = Investiții imobiliare în curs.</t>
+        </is>
+      </c>
+      <c r="G17" s="66" t="inlineStr">
+        <is>
+          <t>F-201, F-208</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="66" t="inlineStr">
+        <is>
           <t>26x</t>
         </is>
       </c>
-      <c r="B17" s="66" t="inlineStr">
+      <c r="B18" s="66" t="inlineStr">
         <is>
           <t>Imobilizări financiare</t>
         </is>
       </c>
-      <c r="C17" s="66" t="inlineStr">
+      <c r="C18" s="66" t="inlineStr">
         <is>
           <t>261 pe entitate · 267 pe PARTENER și CONTRACT</t>
         </is>
       </c>
-      <c r="D17" s="66" t="inlineStr">
+      <c r="D18" s="66" t="inlineStr">
         <is>
           <t>O B</t>
         </is>
       </c>
-      <c r="E17" s="66" t="inlineStr">
+      <c r="E18" s="66" t="inlineStr">
         <is>
           <t>Garanțiile recuperabile peste ani devin neidentificabile; ajungi să scoți fișe de cont pe 3–5 ani</t>
         </is>
       </c>
-      <c r="F17" s="66" t="inlineStr">
+      <c r="F18" s="66" t="inlineStr">
         <is>
           <t>Relevant mai ales la preluarea unei firme noi care ține totul pe un singur analitic.</t>
         </is>
       </c>
-      <c r="G17" s="66" t="inlineStr">
+      <c r="G18" s="66" t="inlineStr">
         <is>
           <t>F-213</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>28x</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>Amortizări imobilizări | Amortizări privind imobilizările</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>280.x / 281.x pe tip | analitic PE MIJLOC FIX, în oglindă cu contul de activ</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>C | C N</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>Valoarea netă greșită; amortizare cumulată neclară | C-13 (28x ≤ 21x) și C-14 (oglinda) nu se pot verifica; amortizarea rămâne pe mijloace ieșite</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>Contra-activ. | 2813 deservește mai multe conturi (2131, 2132, 2133, 2134) — atenție la confruntare. Verifică nota de amortizare în PRIMA lună.</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
-        <is>
-          <t>F-204 | F-203, F-211, F-212, F-214</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>29x/39x/49x</t>
+          <t>28x</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>Ajustări pentru depreciere</t>
+          <t>Amortizări imobilizări | Amortizări privind imobilizările</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>29x / 39x / 49x pe tip activ</t>
+          <t>280.x / 281.x pe tip | analitic PE MIJLOC FIX, în oglindă cu contul de activ</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C | C N</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>Depreciere reversibilă nu e evidențiată; valoare netă greșită</t>
+          <t>Valoarea netă greșită; amortizare cumulată neclară | C-13 (28x ≤ 21x) și C-14 (oglinda) nu se pot verifica; amortizarea rămâne pe mijloace ieșite</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
         <is>
-          <t>Contra-activ / contra-creanță.</t>
+          <t>Contra-activ. | 2813 deservește mai multe conturi (2131, 2132, 2133, 2134) — atenție la confruntare. Verifică nota de amortizare în PRIMA lună.</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
         <is>
-          <t>F-307, F-204</t>
+          <t>F-204 | F-203, F-211, F-212, F-214</t>
         </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>29x/39x/49x</t>
         </is>
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>Piese de schimb</t>
+          <t>Ajustări pentru depreciere</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
-          <t>302.4 (sau 3024 dacă e folosit)</t>
+          <t>29x / 39x / 49x pe tip activ</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>Confuzie cu materiale consumabile; tratament greșit la inventar</t>
+          <t>Depreciere reversibilă nu e evidențiată; valoare netă greșită</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t>Poate trece în 371 dacă se revând.</t>
+          <t>Contra-activ / contra-creanță.</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
         <is>
-          <t>F-308</t>
+          <t>F-307, F-204</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>Materiale de natura obiectelor de inventar</t>
+          <t>Piese de schimb</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>303 + 8035 (extrabilanțier)</t>
+          <t>302.4 (sau 3024 dacă e folosit)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>O C</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>După dare în consum (603=303) se pierde evidența; inventar fizic imposibil</t>
+          <t>Confuzie cu materiale consumabile; tratament greșit la inventar</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
         <is>
-          <t>La 603=303 se debitează simultan 8035. La scoatere din folosință se creditează 8035.</t>
+          <t>Poate trece în 371 dacă se revând.</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
         <is>
-          <t>F-305</t>
+          <t>F-308</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>Diferențe de preț materii/materiale</t>
+          <t>Materiale de natura obiectelor de inventar</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>308 (sau pe tip stoc)</t>
+          <t>303 + 8035 (extrabilanțier)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>O C</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>Preț standard vs. real nu se mai urmărește</t>
+          <t>După dare în consum (603=303) se pierde evidența; inventar fizic imposibil</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t>Opțional pe tip (301/302).</t>
+          <t>La 603=303 se debitează simultan 8035. La scoatere din folosință se creditează 8035.</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
         <is>
-          <t>F-306</t>
+          <t>F-305</t>
         </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>321-328</t>
+          <t>308</t>
         </is>
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>Stocuri în curs de aprovizionare</t>
+          <t>Diferențe de preț materii/materiale</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>32x (tranzit)</t>
+          <t>308 (sau pe tip stoc)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>Bun facturat nereceptionat dispare din evidență; stoc subevaluat</t>
+          <t>Preț standard vs. real nu se mai urmărește</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
         <is>
-          <t>Se stinge la recepție: 301=321 etc.</t>
+          <t>Opțional pe tip (301/302).</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
         <is>
-          <t>F-302</t>
+          <t>F-306</t>
         </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>321-328</t>
         </is>
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>Produse în curs de execuție</t>
+          <t>Stocuri în curs de aprovizionare</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>32x (tranzit)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -27775,34 +27888,34 @@
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>Producție neterminată nu e evidențiată; 711 nu poate neutraliza corect</t>
+          <t>Bun facturat nereceptionat dispare din evidență; stoc subevaluat</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t>Legat de 711.</t>
+          <t>Se stinge la recepție: 301=321 etc.</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
         <is>
-          <t>F-311</t>
+          <t>F-302</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>331</t>
         </is>
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>Servicii în curs de execuție</t>
+          <t>Produse în curs de execuție</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>331</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -27812,123 +27925,123 @@
       </c>
       <c r="E25" s="22" t="inlineStr">
         <is>
-          <t>Servicii în curs nu apar; 712 nu neutralizează</t>
+          <t>Producție neterminată nu e evidențiată; 711 nu poate neutraliza corect</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>Legat de 712.</t>
+          <t>Legat de 711.</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
         <is>
-          <t>F-312</t>
+          <t>F-311</t>
         </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>332</t>
         </is>
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>Diferențe de preț produse</t>
+          <t>Servicii în curs de execuție</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>332</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>Idem pentru produse</t>
+          <t>Servicii în curs nu apar; 712 nu neutralizează</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Legat de 712.</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
         <is>
-          <t>F-306</t>
+          <t>F-312</t>
         </is>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>Mărfuri</t>
+          <t>Diferențe de preț produse</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
         <is>
-          <t>371.AM.21 / 371.AM.11 / 371.EG  (sau prin gestiuni SAGA)</t>
+          <t>348</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
         <is>
-          <t>C O</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>Corelația 371 × c/(100+c) = 4428 se rupe; D394 / SAF-T incomplet pe gestiuni</t>
+          <t>Idem pentru produse</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>SAGA: gestiuni separate cu TVA% și analitice 371/378/4428/607/707. Nu e nevoie de analitic pe plan dacă gestiunea e configurată corect.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
         <is>
-          <t>F-316</t>
+          <t>F-306</t>
         </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>371</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>Diferențe de preț la mărfuri (adaos)</t>
+          <t>Mărfuri</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
         <is>
-          <t>378.AM.21 / 378.AM.11 / 378.EG  (prin gestiune)</t>
+          <t>371.AM.21 / 371.AM.11 / 371.EG  (sau prin gestiuni SAGA)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C O</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>Corelația 707−607 = rulaj D 378 se rupe; adaos greșit</t>
+          <t>Corelația 371 × c/(100+c) = 4428 se rupe; D394 / SAF-T incomplet pe gestiuni</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t>Legat de gestiune. Verificare: rulaj D 378 = 707 − 607 pe perioadă.</t>
+          <t>SAGA: gestiuni separate cu TVA% și analitice 371/378/4428/607/707. Nu e nevoie de analitic pe plan dacă gestiunea e configurată corect.</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -27940,17 +28053,17 @@
     <row r="29" ht="45" customHeight="1">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>378</t>
         </is>
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>Diferențe de preț ambalaje</t>
+          <t>Diferențe de preț la mărfuri (adaos)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>378.AM.21 / 378.AM.11 / 378.EG  (prin gestiune)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -27960,288 +28073,288 @@
       </c>
       <c r="E29" s="22" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Corelația 707−607 = rulaj D 378 se rupe; adaos greșit</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Legat de gestiune. Verificare: rulaj D 378 = 707 − 607 pe perioadă.</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
         <is>
-          <t>F-310</t>
+          <t>F-316</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>388</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>Furnizori</t>
+          <t>Diferențe de preț ambalaje</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
         <is>
-          <t>401.RO / 401.UE / 401.EXT</t>
+          <t>388</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>D394 / D390 / SAF-T incomplet pe rezidență; raportare greșită</t>
+          <t>Idem</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t>Atribut pe partener în SAGA + analitic pe cont. Alimentează D394.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
         <is>
-          <t>F-301, F-319</t>
+          <t>F-310</t>
         </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="22" t="inlineStr">
         <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>Furnizori</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>401.RO / 401.UE / 401.EXT</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D394 / D390 / SAF-T incomplet pe rezidență; raportare greșită</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>Atribut pe partener în SAGA + analitic pe cont. Alimentează D394.</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>F-301, F-319</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
           <t>408</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>Furnizori - facturi nesosite</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>408 (intermediar)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>Marfă sosită fără factură nu e evidențiată; stoc vs. datorie inconsistent</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>Oglinda lui 327. Se stinge 408=401 la sosirea facturii.</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>F-408</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="66" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="66" t="inlineStr">
         <is>
           <t>4093</t>
         </is>
       </c>
-      <c r="B32" s="66" t="inlineStr">
+      <c r="B33" s="66" t="inlineStr">
         <is>
           <t>Avansuri acordate pentru imobilizări corporale</t>
         </is>
       </c>
-      <c r="C32" s="66" t="inlineStr">
+      <c r="C33" s="66" t="inlineStr">
         <is>
           <t>4093 pe contract / furnizor</t>
         </is>
       </c>
-      <c r="D32" s="66" t="inlineStr">
+      <c r="D33" s="66" t="inlineStr">
         <is>
           <t>C O</t>
         </is>
       </c>
-      <c r="E32" s="66" t="inlineStr">
+      <c r="E33" s="66" t="inlineStr">
         <is>
           <t>Avansul rămâne nestins după recepție → valoarea de intrare și soldul 167 sunt greșite</t>
         </is>
       </c>
-      <c r="F32" s="66" t="inlineStr">
+      <c r="F33" s="66" t="inlineStr">
         <is>
           <t>Se închide în 167 (leasing) sau în 404 (achiziție directă) la recepție.</t>
         </is>
       </c>
-      <c r="G32" s="66" t="inlineStr">
+      <c r="G33" s="66" t="inlineStr">
         <is>
           <t>F-108</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="B33" s="22" t="inlineStr">
-        <is>
-          <t>Clienți</t>
-        </is>
-      </c>
-      <c r="C33" s="22" t="inlineStr">
-        <is>
-          <t>411.RO / 411.UE / 411.EXT</t>
-        </is>
-      </c>
-      <c r="D33" s="22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E33" s="22" t="inlineStr">
-        <is>
-          <t>D394 incomplet; raportare greșită pe rezidență</t>
-        </is>
-      </c>
-      <c r="F33" s="22" t="inlineStr">
-        <is>
-          <t>Idem, atribut partener + analitic.</t>
-        </is>
-      </c>
-      <c r="G33" s="22" t="inlineStr">
-        <is>
-          <t>F-315, F-316</t>
         </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t>Clienți - facturi de întocmit</t>
+          <t>Clienți</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
         <is>
-          <t>418 (intermediar)</t>
+          <t>411.RO / 411.UE / 411.EXT</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>Livrat/prestat nefacturat nu apare; venit subevaluat</t>
+          <t>D394 incomplet; raportare greșită pe rezidență</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t>Se stinge 418=411 la facturare.</t>
+          <t>Idem, atribut partener + analitic.</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
         <is>
-          <t>F-408</t>
+          <t>F-315, F-316</t>
         </is>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>441/4417</t>
+          <t>418</t>
         </is>
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>Impozit pe profit / IMCA</t>
+          <t>Clienți - facturi de întocmit</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
         <is>
-          <t>441.1 / 4417 [N]</t>
+          <t>418 (intermediar)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
         <is>
-          <t>N F</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
         <is>
-          <t>IMCA nu e evidențiat separat; Declarație 100/101 greșită</t>
+          <t>Livrat/prestat nefacturat nu apare; venit subevaluat</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
         <is>
-          <t>OMF 981/2024. 697 = cheltuiala.</t>
+          <t>Se stinge 418=411 la facturare.</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
         <is>
-          <t>F-104</t>
+          <t>F-408</t>
         </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>441/4417</t>
         </is>
       </c>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>TVA de plată</t>
+          <t>Impozit pe profit / IMCA</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>441.1 / 4417 [N]</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N F</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>Sold greșit → Declarație 300 greșită</t>
+          <t>IMCA nu e evidențiat separat; Declarație 100/101 greșită</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t>Se alimentează din 4426/4427 la închidere lunară.</t>
+          <t>OMF 981/2024. 697 = cheltuiala.</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
         <is>
-          <t>F-405</t>
+          <t>F-104</t>
         </is>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>TVA de recuperat</t>
+          <t>TVA de plată</t>
         </is>
       </c>
       <c r="C37" s="22" t="inlineStr">
@@ -28256,12 +28369,12 @@
       </c>
       <c r="E37" s="22" t="inlineStr">
         <is>
-          <t>Sold greșit → D300 / cerere rambursare</t>
+          <t>Sold greșit → Declarație 300 greșită</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
         <is>
-          <t>Idem.</t>
+          <t>Se alimentează din 4426/4427 la închidere lunară.</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -28273,17 +28386,17 @@
     <row r="38" ht="45" customHeight="1">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>TVA deductibilă</t>
+          <t>TVA de recuperat</t>
         </is>
       </c>
       <c r="C38" s="22" t="inlineStr">
         <is>
-          <t>Fără analitic obligatoriu (jurnal cumpărări, se închide lunar)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
@@ -28293,12 +28406,12 @@
       </c>
       <c r="E38" s="22" t="inlineStr">
         <is>
-          <t>Nu are sold; dacă rămâne sold → eroare de închidere lunară</t>
+          <t>Sold greșit → D300 / cerere rambursare</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t>SAGA auto-administrează în mare parte. Verificare rulaj vs. jurnal cumpărări.</t>
+          <t>Idem.</t>
         </is>
       </c>
       <c r="G38" s="22" t="inlineStr">
@@ -28310,17 +28423,17 @@
     <row r="39" ht="45" customHeight="1">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>TVA colectată</t>
+          <t>TVA deductibilă</t>
         </is>
       </c>
       <c r="C39" s="22" t="inlineStr">
         <is>
-          <t>Fără analitic obligatoriu (jurnal vânzări, se închide lunar)</t>
+          <t>Fără analitic obligatoriu (jurnal cumpărări, se închide lunar)</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -28330,12 +28443,12 @@
       </c>
       <c r="E39" s="22" t="inlineStr">
         <is>
-          <t>Nu are sold; dacă rămâne sold → eroare</t>
+          <t>Nu are sold; dacă rămâne sold → eroare de închidere lunară</t>
         </is>
       </c>
       <c r="F39" s="22" t="inlineStr">
         <is>
-          <t>SAGA auto. Verificare rulaj vs. jurnal vânzări.</t>
+          <t>SAGA auto-administrează în mare parte. Verificare rulaj vs. jurnal cumpărări.</t>
         </is>
       </c>
       <c r="G39" s="22" t="inlineStr">
@@ -28347,276 +28460,276 @@
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>TVA neexigibilă</t>
+          <t>TVA colectată</t>
         </is>
       </c>
       <c r="C40" s="22" t="inlineStr">
         <is>
-          <t>4428.AM (rectificativ amănunt) + 4428.INC (intermediar la încasare) — SEPARATE OBLIGATORIU</t>
+          <t>Fără analitic obligatoriu (jurnal vânzări, se închide lunar)</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
         <is>
-          <t>C F</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E40" s="22" t="inlineStr">
         <is>
-          <t>Corelația sold 371 × c/(100+c) = sold 4428.AM se rupe; confuzie între roluri; erori la TVA la încasare</t>
+          <t>Nu are sold; dacă rămâne sold → eroare</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t>În SAGA: legat de gestiune. Pentru amănunt: gestiune cu cotă. Pentru INC: analitic distinct sau atribut pe factură.</t>
+          <t>SAGA auto. Verificare rulaj vs. jurnal vânzări.</t>
         </is>
       </c>
       <c r="G40" s="22" t="inlineStr">
         <is>
-          <t>F-316, F-401</t>
+          <t>F-405</t>
         </is>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>Alte impozite, taxe...</t>
+          <t>TVA neexigibilă</t>
         </is>
       </c>
       <c r="C41" s="22" t="inlineStr">
         <is>
-          <t>446.VAMA (tranzit TVA prin comisionar) + 446.alte</t>
+          <t>4428.AM (rectificativ amănunt) + 4428.INC (intermediar la încasare) — SEPARATE OBLIGATORIU</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">
         <is>
-          <t>O D</t>
+          <t>C F</t>
         </is>
       </c>
       <c r="E41" s="22" t="inlineStr">
         <is>
-          <t>TVA vamală nu se mai vede separat; erori la import prin comisionar</t>
+          <t>Corelația sold 371 × c/(100+c) = sold 4428.AM se rupe; confuzie între roluri; erori la TVA la încasare</t>
         </is>
       </c>
       <c r="F41" s="22" t="inlineStr">
         <is>
-          <t>Analitic VAMA e intermediar: se stinge la decontare. Alimentează D300.</t>
+          <t>În SAGA: legat de gestiune. Pentru amănunt: gestiune cu cotă. Pentru INC: analitic distinct sau atribut pe factură.</t>
         </is>
       </c>
       <c r="G41" s="22" t="inlineStr">
         <is>
-          <t>F-319</t>
+          <t>F-316, F-401</t>
         </is>
       </c>
     </row>
     <row r="42" ht="45" customHeight="1">
       <c r="A42" s="22" t="inlineStr">
         <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Alte impozite, taxe...</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>446.VAMA (tranzit TVA prin comisionar) + 446.alte</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>O D</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>TVA vamală nu se mai vede separat; erori la import prin comisionar</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>Analitic VAMA e intermediar: se stinge la decontare. Alimentează D300.</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr">
+        <is>
+          <t>F-319</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
           <t>447</t>
         </is>
       </c>
-      <c r="B42" s="22" t="inlineStr">
+      <c r="B43" s="22" t="inlineStr">
         <is>
           <t>Fonduri speciale - taxe</t>
         </is>
       </c>
-      <c r="C42" s="22" t="inlineStr">
+      <c r="C43" s="22" t="inlineStr">
         <is>
           <t>447 (ex. taxa AFM ambalaje)</t>
         </is>
       </c>
-      <c r="D42" s="22" t="inlineStr">
+      <c r="D43" s="22" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="E42" s="22" t="inlineStr">
+      <c r="E43" s="22" t="inlineStr">
         <is>
           <t>Taxa de mediu nu e evidențiată; erori de cheltuială</t>
         </is>
       </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="F43" s="22" t="inlineStr">
         <is>
           <t>Legat de ambalaje + F-310.</t>
         </is>
       </c>
-      <c r="G42" s="22" t="inlineStr">
+      <c r="G43" s="22" t="inlineStr">
         <is>
           <t>F-310</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="66" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="66" t="inlineStr">
+        <is>
+          <t>4551</t>
+        </is>
+      </c>
+      <c r="B44" s="66" t="inlineStr">
+        <is>
+          <t>Acționari/asociați — conturi curente</t>
+        </is>
+      </c>
+      <c r="C44" s="66" t="inlineStr">
+        <is>
+          <t>4551 pe fiecare ASOCIAT, urmărit în AMBELE sensuri</t>
+        </is>
+      </c>
+      <c r="D44" s="66" t="inlineStr">
+        <is>
+          <t>C O</t>
+        </is>
+      </c>
+      <c r="E44" s="66" t="inlineStr">
+        <is>
+          <t>Compensarea între asociați devine invizibilă: soldul total al lui 455 poate arăta curat în timp ce un asociat e pe debit și altul pe credit</t>
+        </is>
+      </c>
+      <c r="F44" s="66" t="inlineStr">
+        <is>
+          <t>Contract pentru fiecare creditare — sau unul pe lună, pe totalul fișei. Nu se compensează între analitice decât prin act notarial. Niciun analitic nu are voie cu sold debitor. C-30.</t>
+        </is>
+      </c>
+      <c r="G44" s="66" t="inlineStr">
+        <is>
+          <t>F-111, F-112, F-113</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="66" t="inlineStr">
         <is>
           <t>456</t>
         </is>
       </c>
-      <c r="B43" s="66" t="inlineStr">
+      <c r="B45" s="66" t="inlineStr">
         <is>
           <t>Decontări cu acționarii/asociații privind capitalul</t>
         </is>
       </c>
-      <c r="C43" s="66" t="inlineStr">
+      <c r="C45" s="66" t="inlineStr">
         <is>
           <t>456 pe fiecare ASOCIAT</t>
         </is>
       </c>
-      <c r="D43" s="66" t="inlineStr">
+      <c r="D45" s="66" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="E43" s="66" t="inlineStr">
+      <c r="E45" s="66" t="inlineStr">
         <is>
           <t>Nu poți justifica cine ce datorează; vărsămintele parțiale devin neurmăribile</t>
         </is>
       </c>
-      <c r="F43" s="66" t="inlineStr">
+      <c r="F45" s="66" t="inlineStr">
         <is>
           <t>Se închide la vărsare. Sold 456 ≠ 0 la 31.12 = capital subscris nevărsat.</t>
         </is>
       </c>
-      <c r="G43" s="66" t="inlineStr">
+      <c r="G45" s="66" t="inlineStr">
         <is>
           <t>F-101</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="45" customHeight="1">
-      <c r="A44" s="22" t="inlineStr">
-        <is>
-          <t>471/472</t>
-        </is>
-      </c>
-      <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>Cheltuieli/Venituri înregistrate în avans</t>
-        </is>
-      </c>
-      <c r="C44" s="22" t="inlineStr">
-        <is>
-          <t>471 / 472</t>
-        </is>
-      </c>
-      <c r="D44" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="22" t="inlineStr">
-        <is>
-          <t>Regularizarea temporală se pierde; rezultat distorsionat pe perioade</t>
-        </is>
-      </c>
-      <c r="F44" s="22" t="inlineStr">
-        <is>
-          <t>Se eliberează sistematic (ex. 1/12 asigurare).</t>
-        </is>
-      </c>
-      <c r="G44" s="22" t="inlineStr">
-        <is>
-          <t>F-412</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="45" customHeight="1">
-      <c r="A45" s="22" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="B45" s="22" t="inlineStr">
-        <is>
-          <t>Decontări din operațiuni în curs de clarificare</t>
-        </is>
-      </c>
-      <c r="C45" s="22" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="D45" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E45" s="22" t="inlineStr">
-        <is>
-          <t>Sume neidentificate din extras rămân „pierdute”; sold 31.12 = red flag audit</t>
-        </is>
-      </c>
-      <c r="F45" s="22" t="inlineStr">
-        <is>
-          <t>CANONIC: sumă neidentificată din extras bancă. Clarificare rapidă obligatorie.</t>
-        </is>
-      </c>
-      <c r="G45" s="22" t="inlineStr">
-        <is>
-          <t>F-411</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="45" customHeight="1">
-      <c r="A46" s="22" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="B46" s="22" t="inlineStr">
-        <is>
-          <t>Subvenții pentru investiții</t>
-        </is>
-      </c>
-      <c r="C46" s="22" t="inlineStr">
-        <is>
-          <t>475.1–475.8 [N] (pe tip subvenție)</t>
-        </is>
-      </c>
-      <c r="D46" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E46" s="22" t="inlineStr">
-        <is>
-          <t>Eliberarea pe măsura amortizării nu e urmărită pe tip; erori de venit</t>
-        </is>
-      </c>
-      <c r="F46" s="22" t="inlineStr">
-        <is>
-          <t>Normat. Se trece la venit pe măsura amortizării activului.</t>
-        </is>
-      </c>
-      <c r="G46" s="22" t="inlineStr">
-        <is>
-          <t>F-210</t>
+    <row r="46">
+      <c r="A46" s="66" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="B46" s="66" t="inlineStr">
+        <is>
+          <t>Dividende de plată</t>
+        </is>
+      </c>
+      <c r="C46" s="66" t="inlineStr">
+        <is>
+          <t>457 pe fiecare ASOCIAT, în oglindă cu analiticele lui 1012</t>
+        </is>
+      </c>
+      <c r="D46" s="66" t="inlineStr">
+        <is>
+          <t>C F O</t>
+        </is>
+      </c>
+      <c r="E46" s="66" t="inlineStr">
+        <is>
+          <t>Nu poți spune cui i s-a plătit și cui nu; impozitul se datorează oricum la 25.01, deci soldul rămas trebuie să fie atribuibil unei persoane</t>
+        </is>
+      </c>
+      <c r="F46" s="66" t="inlineStr">
+        <is>
+          <t>Se stinge doar prin 446 (impozit) sau 5121/5311 (plată). Stins prin 4551 sau 461 = compensare nedocumentată. C-34.</t>
+        </is>
+      </c>
+      <c r="G46" s="66" t="inlineStr">
+        <is>
+          <t>F-109</t>
         </is>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>481/482</t>
+          <t>471/472</t>
         </is>
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>Decontări unitate-subunități</t>
+          <t>Cheltuieli/Venituri înregistrate în avans</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>481 / 482</t>
+          <t>471 / 472</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
@@ -28626,385 +28739,533 @@
       </c>
       <c r="E47" s="22" t="inlineStr">
         <is>
-          <t>La centralizare nu se elimină; dublă numărare</t>
+          <t>Regularizarea temporală se pierde; rezultat distorsionat pe perioade</t>
         </is>
       </c>
       <c r="F47" s="22" t="inlineStr">
         <is>
-          <t>Sold reciproc; se elimină la consolidare/centralizare.</t>
+          <t>Se eliberează sistematic (ex. 1/12 asigurare).</t>
         </is>
       </c>
       <c r="G47" s="22" t="inlineStr">
         <is>
-          <t>F-414</t>
+          <t>F-412</t>
         </is>
       </c>
     </row>
     <row r="48" ht="45" customHeight="1">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>511/512/581</t>
+          <t>473</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>Trezorerie + viramente</t>
+          <t>Decontări din operațiuni în curs de clarificare</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>512.1 lei / 512.4 valută / 512.5 în curs; 581 intermediar</t>
+          <t>473</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>V O</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E48" s="22" t="inlineStr">
         <is>
-          <t>Diferențe de curs greșite; dublă numărare la transfer bancă↔casă</t>
+          <t>Sume neidentificate din extras rămân „pierdute”; sold 31.12 = red flag audit</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t>581 evită dublă numărare până la confirmare. 512.5 = intermediar.</t>
+          <t>CANONIC: sumă neidentificată din extras bancă. Clarificare rapidă obligatorie.</t>
         </is>
       </c>
       <c r="G48" s="22" t="inlineStr">
         <is>
-          <t>F-501</t>
+          <t>F-411</t>
         </is>
       </c>
     </row>
     <row r="49" ht="45" customHeight="1">
       <c r="A49" s="22" t="inlineStr">
         <is>
-          <t>601/602/603/607</t>
+          <t>475</t>
         </is>
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>Cheltuieli stocuri</t>
+          <t>Subvenții pentru investiții</t>
         </is>
       </c>
       <c r="C49" s="22" t="inlineStr">
         <is>
-          <t>601 (prin 301); 602.x prin 302.x; 603=303+8035; 607 corelat 378</t>
+          <t>475.1–475.8 [N] (pe tip subvenție)</t>
         </is>
       </c>
       <c r="D49" s="22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E49" s="22" t="inlineStr">
         <is>
-          <t>Consum direct din 401 (greșit); corelație 707-607 se rupe</t>
+          <t>Eliberarea pe măsura amortizării nu e urmărită pe tip; erori de venit</t>
         </is>
       </c>
       <c r="F49" s="22" t="inlineStr">
         <is>
-          <t>Niciodată 601=401 direct. Verificare corelații pe cifre.</t>
+          <t>Normat. Se trece la venit pe măsura amortizării activului.</t>
         </is>
       </c>
       <c r="G49" s="22" t="inlineStr">
         <is>
-          <t>F-311, F-316</t>
+          <t>F-210</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="66" t="inlineStr">
         <is>
-          <t>6583 / 7583</t>
+          <t>475x</t>
         </is>
       </c>
       <c r="B50" s="66" t="inlineStr">
         <is>
-          <t>Cheltuieli / Venituri din cedarea activelor</t>
+          <t>Subvenții pentru investiții (venit amânat)</t>
         </is>
       </c>
       <c r="C50" s="66" t="inlineStr">
         <is>
-          <t>analitic pe operațiune de cedare</t>
+          <t>4751 / 4752 / 4753 / 4754 / 4758 pe fiecare PROIECT de finanțare</t>
         </is>
       </c>
       <c r="D50" s="66" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C F O</t>
         </is>
       </c>
       <c r="E50" s="66" t="inlineStr">
         <is>
-          <t>Testul de deductibilitate (valoare rămasă vs. venit din vânzare) nu se poate documenta</t>
+          <t>Reluarea la venit nu se mai poate lega de activul care o justifică: cu două proiecte pe același cont, nimeni nu mai știe care s-a epuizat</t>
         </is>
       </c>
       <c r="F50" s="66" t="inlineStr">
         <is>
-          <t>6583 deductibil în limita venitului din vânzare; diferența e nedeductibilă fără documentarea prețului (raport de evaluare / referință de piață / deviz de service).</t>
+          <t>Perechea creanță ↔ venit amânat se ține pe același analitic de proiect: 4452 ↔ 4758. Reluarea urmează amortizarea, în cota de finanțare — o lună cu amortizare din proiect și fără reluare e o eroare (F-215).</t>
         </is>
       </c>
       <c r="G50" s="66" t="inlineStr">
         <is>
-          <t>F-211, F-212</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="66" t="inlineStr">
-        <is>
-          <t>665 / 765</t>
-        </is>
-      </c>
-      <c r="B51" s="66" t="inlineStr">
-        <is>
-          <t>Diferențe de curs valutar</t>
-        </is>
-      </c>
-      <c r="C51" s="66" t="inlineStr">
-        <is>
-          <t>analitic pe tip de element (credite, furnizori, clienți, trezorerie)</t>
-        </is>
-      </c>
-      <c r="D51" s="66" t="inlineStr">
-        <is>
-          <t>V F</t>
-        </is>
-      </c>
-      <c r="E51" s="66" t="inlineStr">
-        <is>
-          <t>Nu poți separa diferențele la plată de cele din reevaluarea lunară; la vehicule, diferențele intră în baza limitării de 50%</t>
-        </is>
-      </c>
-      <c r="F51" s="66" t="inlineStr">
-        <is>
-          <t>Două momente: la plată și la reevaluarea lunară a soldului (ultima zi bancară).</t>
-        </is>
-      </c>
-      <c r="G51" s="66" t="inlineStr">
-        <is>
-          <t>F-107, F-108</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="66" t="inlineStr">
-        <is>
-          <t>666 / 628 / 613</t>
-        </is>
-      </c>
-      <c r="B52" s="66" t="inlineStr">
-        <is>
-          <t>Dobânzi / Comisioane / Prime de asigurare — vehicule</t>
-        </is>
-      </c>
-      <c r="C52" s="66" t="inlineStr">
-        <is>
-          <t>analitic .NED pentru partea nedeductibilă (ex. 666.NED, 628.NED, 613.NED)</t>
-        </is>
-      </c>
-      <c r="D52" s="66" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E52" s="66" t="inlineStr">
-        <is>
-          <t>Limitarea de 50% (art. 25 alin. 3 lit. l CF) nu se poate proba la control; D101 iese greșit</t>
-        </is>
-      </c>
-      <c r="F52" s="66" t="inlineStr">
-        <is>
-          <t>Baza include TVA nedeductibilă deja trecută pe cheltuială. ⚠ Contul nedeductibil pentru CASCO este 613.NED, NU 615 (= pregătirea personalului).</t>
-        </is>
-      </c>
-      <c r="G52" s="66" t="inlineStr">
-        <is>
-          <t>F-108</t>
+          <t>F-215, F-216, F-210</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>481/482</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>Decontări unitate-subunități</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>481 / 482</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>La centralizare nu se elimină; dublă numărare</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>Sold reciproc; se elimină la consolidare/centralizare.</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr">
+        <is>
+          <t>F-414</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="45" customHeight="1">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>511/512/581</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>Trezorerie + viramente</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>512.1 lei / 512.4 valută / 512.5 în curs; 581 intermediar</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>V O</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>Diferențe de curs greșite; dublă numărare la transfer bancă↔casă</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>581 evită dublă numărare până la confirmare. 512.5 = intermediar.</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr">
+        <is>
+          <t>F-501</t>
         </is>
       </c>
     </row>
     <row r="53" ht="45" customHeight="1">
       <c r="A53" s="22" t="inlineStr">
         <is>
-          <t>681/781</t>
+          <t>601/602/603/607</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>Cheltuieli/Venituri cu amortizări, provizioane, ajustări</t>
+          <t>Cheltuieli stocuri</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>681 / 781</t>
+          <t>601 (prin 301); 602.x prin 302.x; 603=303+8035; 607 corelat 378</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E53" s="22" t="inlineStr">
         <is>
-          <t>Contrapartida rectificativelor lipsește; amortizare/ajustare nu trece pe rezultat</t>
+          <t>Consum direct din 401 (greșit); corelație 707-607 se rupe</t>
         </is>
       </c>
       <c r="F53" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Niciodată 601=401 direct. Verificare corelații pe cifre.</t>
         </is>
       </c>
       <c r="G53" s="22" t="inlineStr">
         <is>
-          <t>F-204</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="22" t="inlineStr">
-        <is>
-          <t>707/701/704</t>
-        </is>
-      </c>
-      <c r="B54" s="22" t="inlineStr">
-        <is>
-          <t>Venituri CA</t>
-        </is>
-      </c>
-      <c r="C54" s="22" t="inlineStr">
-        <is>
-          <t>707 corelat; 701; 704</t>
-        </is>
-      </c>
-      <c r="D54" s="22" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E54" s="22" t="inlineStr">
-        <is>
-          <t>Corelație 707-607 = rulaj D 378 se rupe</t>
-        </is>
-      </c>
-      <c r="F54" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="22" t="inlineStr">
-        <is>
-          <t>F-315, F-316, F-311</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
-      <c r="A55" s="22" t="inlineStr">
-        <is>
-          <t>711/712</t>
-        </is>
-      </c>
-      <c r="B55" s="22" t="inlineStr">
-        <is>
-          <t>Venituri aferente costului producției în curs</t>
-        </is>
-      </c>
-      <c r="C55" s="22" t="inlineStr">
-        <is>
-          <t>711 / 712 (neutralizare)</t>
-        </is>
-      </c>
-      <c r="D55" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E55" s="22" t="inlineStr">
-        <is>
-          <t>121 nu e ținut la zero pentru producție/servicii în curs; rezultat distorsionat</t>
-        </is>
-      </c>
-      <c r="F55" s="22" t="inlineStr">
-        <is>
-          <t>Pas revelator: 711 ține 121 la zero cât timp produsul nu e livrat.</t>
-        </is>
-      </c>
-      <c r="G55" s="22" t="inlineStr">
-        <is>
-          <t>F-311, F-312</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="45" customHeight="1">
-      <c r="A56" s="22" t="inlineStr">
-        <is>
-          <t>721/722 | 721 / 722</t>
-        </is>
-      </c>
-      <c r="B56" s="22" t="inlineStr">
-        <is>
-          <t>Venituri din producția de imobilizări</t>
-        </is>
-      </c>
-      <c r="C56" s="22" t="inlineStr">
-        <is>
-          <t>721 / 722 (neutralizare) | 721 necorporale · 722 corporale</t>
-        </is>
-      </c>
-      <c r="D56" s="22" t="inlineStr">
-        <is>
-          <t>C F</t>
-        </is>
-      </c>
-      <c r="E56" s="22" t="inlineStr">
-        <is>
-          <t>Cheltuiala capitalizată în cls.2 nu e neutralizată; rezultat greșit | Costurile capitalizate rămân pe cheltuială → rezultat și impozit pe profit denaturate</t>
-        </is>
-      </c>
-      <c r="F56" s="22" t="inlineStr">
-        <is>
-          <t>Productie imobilizată: neutralizează cheltuiala. | ⚠ NU 711 (variația stocurilor). Softul intern = 233 → 721 → 208; hala în regie proprie = 231 → 722 → 212.</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="inlineStr">
-        <is>
-          <t>F-209 | F-201, F-208, F-209</t>
+          <t>F-311, F-316</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="66" t="inlineStr">
+        <is>
+          <t>6583 / 7583</t>
+        </is>
+      </c>
+      <c r="B54" s="66" t="inlineStr">
+        <is>
+          <t>Cheltuieli / Venituri din cedarea activelor</t>
+        </is>
+      </c>
+      <c r="C54" s="66" t="inlineStr">
+        <is>
+          <t>analitic pe operațiune de cedare</t>
+        </is>
+      </c>
+      <c r="D54" s="66" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E54" s="66" t="inlineStr">
+        <is>
+          <t>Testul de deductibilitate (valoare rămasă vs. venit din vânzare) nu se poate documenta</t>
+        </is>
+      </c>
+      <c r="F54" s="66" t="inlineStr">
+        <is>
+          <t>6583 deductibil în limita venitului din vânzare; diferența e nedeductibilă fără documentarea prețului (raport de evaluare / referință de piață / deviz de service).</t>
+        </is>
+      </c>
+      <c r="G54" s="66" t="inlineStr">
+        <is>
+          <t>F-211, F-212</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="66" t="inlineStr">
+        <is>
+          <t>665 / 765</t>
+        </is>
+      </c>
+      <c r="B55" s="66" t="inlineStr">
+        <is>
+          <t>Diferențe de curs valutar</t>
+        </is>
+      </c>
+      <c r="C55" s="66" t="inlineStr">
+        <is>
+          <t>analitic pe tip de element (credite, furnizori, clienți, trezorerie)</t>
+        </is>
+      </c>
+      <c r="D55" s="66" t="inlineStr">
+        <is>
+          <t>V F</t>
+        </is>
+      </c>
+      <c r="E55" s="66" t="inlineStr">
+        <is>
+          <t>Nu poți separa diferențele la plată de cele din reevaluarea lunară; la vehicule, diferențele intră în baza limitării de 50%</t>
+        </is>
+      </c>
+      <c r="F55" s="66" t="inlineStr">
+        <is>
+          <t>Două momente: la plată și la reevaluarea lunară a soldului (ultima zi bancară).</t>
+        </is>
+      </c>
+      <c r="G55" s="66" t="inlineStr">
+        <is>
+          <t>F-107, F-108</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="66" t="inlineStr">
+        <is>
+          <t>666 / 628 / 613</t>
+        </is>
+      </c>
+      <c r="B56" s="66" t="inlineStr">
+        <is>
+          <t>Dobânzi / Comisioane / Prime de asigurare — vehicule</t>
+        </is>
+      </c>
+      <c r="C56" s="66" t="inlineStr">
+        <is>
+          <t>analitic .NED pentru partea nedeductibilă (ex. 666.NED, 628.NED, 613.NED)</t>
+        </is>
+      </c>
+      <c r="D56" s="66" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E56" s="66" t="inlineStr">
+        <is>
+          <t>Limitarea de 50% (art. 25 alin. 3 lit. l CF) nu se poate proba la control; D101 iese greșit</t>
+        </is>
+      </c>
+      <c r="F56" s="66" t="inlineStr">
+        <is>
+          <t>Baza include TVA nedeductibilă deja trecută pe cheltuială. ⚠ Contul nedeductibil pentru CASCO este 613.NED, NU 615 (= pregătirea personalului).</t>
+        </is>
+      </c>
+      <c r="G56" s="66" t="inlineStr">
+        <is>
+          <t>F-108</t>
         </is>
       </c>
     </row>
     <row r="57" ht="45" customHeight="1">
       <c r="A57" s="22" t="inlineStr">
         <is>
+          <t>681/781</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>Cheltuieli/Venituri cu amortizări, provizioane, ajustări</t>
+        </is>
+      </c>
+      <c r="C57" s="22" t="inlineStr">
+        <is>
+          <t>681 / 781</t>
+        </is>
+      </c>
+      <c r="D57" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>Contrapartida rectificativelor lipsește; amortizare/ajustare nu trece pe rezultat</t>
+        </is>
+      </c>
+      <c r="F57" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr">
+        <is>
+          <t>F-204</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="45" customHeight="1">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>707/701/704</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>Venituri CA</t>
+        </is>
+      </c>
+      <c r="C58" s="22" t="inlineStr">
+        <is>
+          <t>707 corelat; 701; 704</t>
+        </is>
+      </c>
+      <c r="D58" s="22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E58" s="22" t="inlineStr">
+        <is>
+          <t>Corelație 707-607 = rulaj D 378 se rupe</t>
+        </is>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr">
+        <is>
+          <t>F-315, F-316, F-311</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>711/712</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>Venituri aferente costului producției în curs</t>
+        </is>
+      </c>
+      <c r="C59" s="22" t="inlineStr">
+        <is>
+          <t>711 / 712 (neutralizare)</t>
+        </is>
+      </c>
+      <c r="D59" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>121 nu e ținut la zero pentru producție/servicii în curs; rezultat distorsionat</t>
+        </is>
+      </c>
+      <c r="F59" s="22" t="inlineStr">
+        <is>
+          <t>Pas revelator: 711 ține 121 la zero cât timp produsul nu e livrat.</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="inlineStr">
+        <is>
+          <t>F-311, F-312</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>721/722 | 721 / 722</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>Venituri din producția de imobilizări</t>
+        </is>
+      </c>
+      <c r="C60" s="22" t="inlineStr">
+        <is>
+          <t>721 / 722 (neutralizare) | 721 necorporale · 722 corporale</t>
+        </is>
+      </c>
+      <c r="D60" s="22" t="inlineStr">
+        <is>
+          <t>C F</t>
+        </is>
+      </c>
+      <c r="E60" s="22" t="inlineStr">
+        <is>
+          <t>Cheltuiala capitalizată în cls.2 nu e neutralizată; rezultat greșit | Costurile capitalizate rămân pe cheltuială → rezultat și impozit pe profit denaturate</t>
+        </is>
+      </c>
+      <c r="F60" s="22" t="inlineStr">
+        <is>
+          <t>Productie imobilizată: neutralizează cheltuiala. | ⚠ NU 711 (variația stocurilor). Softul intern = 233 → 721 → 208; hala în regie proprie = 231 → 722 → 212.</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr">
+        <is>
+          <t>F-209 | F-201, F-208, F-209</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
           <t>8035</t>
         </is>
       </c>
-      <c r="B57" s="22" t="inlineStr">
+      <c r="B61" s="22" t="inlineStr">
         <is>
           <t>Obiecte de inventar date în folosință (extrabilanțier)</t>
         </is>
       </c>
-      <c r="C57" s="22" t="inlineStr">
+      <c r="C61" s="22" t="inlineStr">
         <is>
           <t>8035</t>
         </is>
       </c>
-      <c r="D57" s="22" t="inlineStr">
+      <c r="D61" s="22" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="E57" s="22" t="inlineStr">
+      <c r="E61" s="22" t="inlineStr">
         <is>
           <t>După 603=303 se pierde evidența obiectelor în folosință; inventar imposibil</t>
         </is>
       </c>
-      <c r="F57" s="22" t="inlineStr">
+      <c r="F61" s="22" t="inlineStr">
         <is>
           <t>Memorie: se debitează la dare în consum, se creditează la scoatere.</t>
         </is>
       </c>
-      <c r="G57" s="22" t="inlineStr">
+      <c r="G61" s="22" t="inlineStr">
         <is>
           <t>F-305</t>
         </is>
@@ -32352,7 +32613,7 @@
       </c>
       <c r="H84" s="69" t="inlineStr">
         <is>
-          <t>Sumele stabilite prin decizie de impunere NU ajung niciodată în decontul de TVA. ❓ Notițele din 21.08 spun „4423 cu analitic distinct”, cele din 26.08 spun 4481 — vezi principiul și întrebarea din listă.</t>
+          <t>Sumele stabilite prin decizie de impunere NU ajung niciodată în decontul de TVA. ❓ Notițele din 21.08 spun „4423 cu analitic distinct”, cele din 26.08 spun 4481 — vezi principiul și întrebarea din listă. | ❓ Î-32</t>
         </is>
       </c>
     </row>
@@ -32552,7 +32813,7 @@
       </c>
       <c r="H89" s="69" t="inlineStr">
         <is>
-          <t>Entități afiliate (peste 25% acționari comuni, contul 451) sunt altceva: acolo se decontează împrumuturi, aici se împart venituri și cheltuieli.</t>
+          <t>Entități afiliate (peste 25% acționari comuni, contul 451) sunt altceva: acolo se decontează împrumuturi, aici se împart venituri și cheltuieli. | ❓ Î-30</t>
         </is>
       </c>
     </row>
@@ -55306,7 +55567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -56668,12 +56929,233 @@
       </c>
       <c r="F47" s="61" t="inlineStr">
         <is>
-          <t>F-405, F-407, F-421 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_TVA</t>
+          <t>F-405, F-407, F-421 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_TVA | ❓ Î-32</t>
         </is>
       </c>
       <c r="G47" s="61" t="inlineStr">
         <is>
           <t>Înaltă — decontul nu are variantă rectificativă; corecția se face doar pe regularizări</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="61" t="inlineStr">
+        <is>
+          <t>C-30</t>
+        </is>
+      </c>
+      <c r="B48" s="61" t="inlineStr">
+        <is>
+          <t>sold 4551 NICIODATĂ debitor
+(pe fiecare analitic de asociat, nu pe total)</t>
+        </is>
+      </c>
+      <c r="C48" s="61" t="inlineStr">
+        <is>
+          <t>Balanța analitică a lui 455, la orice moment</t>
+        </is>
+      </c>
+      <c r="D48" s="61" t="inlineStr">
+        <is>
+          <t>Nimic. 4551 e cont de pasiv: sold debitor nu are variantă legitimă.
+Sold ZERO e starea normală de final, nu o abatere.</t>
+        </is>
+      </c>
+      <c r="E48" s="61" t="inlineStr">
+        <is>
+          <t>Asociatul a ridicat mai mult decât a pus — creditare inexistentă
+Înregistrare pe sensul greșit
+Compensare între doi asociați, fără act notarial: soldul total
+  pare curat, analiticele nu
+Ridicări puse pe 461 după ce 4551 a ajuns la zero (vezi C-33)</t>
+        </is>
+      </c>
+      <c r="F48" s="61" t="inlineStr">
+        <is>
+          <t>F-111, F-112, F-113</t>
+        </is>
+      </c>
+      <c r="G48" s="61" t="inlineStr">
+        <is>
+          <t>Înaltă — la control apare drept bani scoși fără temei, cu efect și asupra persoanei, nu doar a firmei</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="61" t="inlineStr">
+        <is>
+          <t>C-31</t>
+        </is>
+      </c>
+      <c r="B49" s="61" t="inlineStr">
+        <is>
+          <t>Σ analitice 1012 = sold 1012
+ȘI Σ procentelor din denumiri = 100%</t>
+        </is>
+      </c>
+      <c r="C49" s="61" t="inlineStr">
+        <is>
+          <t>Balanța analitică + certificatul constatator ONRC</t>
+        </is>
+      </c>
+      <c r="D49" s="61" t="inlineStr">
+        <is>
+          <t>Firmă nouă preluată cu 1012 „la grămadă”, înainte de spargerea pe
+  analitice — dar atunci corelația e o SARCINĂ, nu o excepție (F-114)
+Majorare de capital în curs, cu mențiunea nedepusă încă la ONRC:
+  partea nouă stă pe 1011, nu pe 1012</t>
+        </is>
+      </c>
+      <c r="E49" s="61" t="inlineStr">
+        <is>
+          <t>Fuziune sau cedare de părți sociale operată în acte și nu în analitice
+Hotărâre AGA care repartizează pe procente inexistente în balanță
+Analitice cu procente care nu însumează 100% — cineva a fost uitat</t>
+        </is>
+      </c>
+      <c r="F49" s="61" t="inlineStr">
+        <is>
+          <t>F-114, F-109, F-112</t>
+        </is>
+      </c>
+      <c r="G49" s="61" t="inlineStr">
+        <is>
+          <t>Înaltă — cazurile ajunse la comisia de disciplină la ANAF au pornit exact de aici</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="61" t="inlineStr">
+        <is>
+          <t>C-32</t>
+        </is>
+      </c>
+      <c r="B50" s="61" t="inlineStr">
+        <is>
+          <t>sold debitor 463 ≤ sold creditor 121
+(la orice moment, nu doar la 31.12)</t>
+        </is>
+      </c>
+      <c r="C50" s="61" t="inlineStr">
+        <is>
+          <t>Balanța la data bilanțului interimar și la 31.12</t>
+        </is>
+      </c>
+      <c r="D50" s="61" t="inlineStr">
+        <is>
+          <t>Egalitate: s-a repartizat exact profitul realizat — plafonul atins,
+  nu depășit
+Sold 463 = 0 după regularizarea de la 31.12 și trecerea prin 1171</t>
+        </is>
+      </c>
+      <c r="E50" s="61" t="inlineStr">
+        <is>
+          <t>Dividende interimare peste profitul realizat: la 31.12 se stornează,
+  se depune D710, iar asociatul trebuie să aducă banii înapoi
+Repartizare făcută pe disponibilul din bancă, nu pe soldul lui 121
+Lipsa bilanțului interimar sau a inventarierii — condiții legale,
+  nu formalități</t>
+        </is>
+      </c>
+      <c r="F50" s="61" t="inlineStr">
+        <is>
+          <t>F-110</t>
+        </is>
+      </c>
+      <c r="G50" s="61" t="inlineStr">
+        <is>
+          <t>Înaltă — corecția e un proces lung, cu bani de restituit și rectificativă printr-un formular separat (D710), pentru că decontul nu are variantă rectificativă</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="61" t="inlineStr">
+        <is>
+          <t>C-33</t>
+        </is>
+      </c>
+      <c r="B51" s="61" t="inlineStr">
+        <is>
+          <t>4481 și 4482 se sting până la finalul exercițiului
+(sold reportat = 0)</t>
+        </is>
+      </c>
+      <c r="C51" s="61" t="inlineStr">
+        <is>
+          <t>Balanța la 31.12, pe fiecare analitic de decizie sau de plată</t>
+        </is>
+      </c>
+      <c r="D51" s="61" t="inlineStr">
+        <is>
+          <t>Decizie de impunere contestată, cu suspendarea executării — soldul
+  rămâne, dar are dosar
+Plată eronată descoperită în decembrie, returnată în ianuarie</t>
+        </is>
+      </c>
+      <c r="E51" s="61" t="inlineStr">
+        <is>
+          <t>Sold purtat de la un an la altul: decizia n-a fost achitată sau
+  nimeni n-a mai urmărit-o
+4482 folosit ca depozit pentru diferențe pe care nu le-a disecat
+  nimeni — devine coș, ca 461
+Sume din decizii trecute prin 4423: soldul lui 4481 pare curat,
+  dar decontul de TVA e cel stricat (vezi C-29)</t>
+        </is>
+      </c>
+      <c r="F51" s="61" t="inlineStr">
+        <is>
+          <t>F-421, F-424 | ❓ Î-32</t>
+        </is>
+      </c>
+      <c r="G51" s="61" t="inlineStr">
+        <is>
+          <t>Medie — conturile există tocmai ca să protejeze corelațiile pe care ANAF le contraverifică; nefolosite corect, le strică</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="61" t="inlineStr">
+        <is>
+          <t>C-34</t>
+        </is>
+      </c>
+      <c r="B52" s="61" t="inlineStr">
+        <is>
+          <t>Σ analitice 457 = dividendele din hotărârea AGA
+ȘI 457 se stinge doar prin 446 sau 5121</t>
+        </is>
+      </c>
+      <c r="C52" s="61" t="inlineStr">
+        <is>
+          <t>Hotărârea AGA + balanța analitică a lui 457 + fișa contului 446</t>
+        </is>
+      </c>
+      <c r="D52" s="61" t="inlineStr">
+        <is>
+          <t>Dividende repartizate și neridicate: 457 rămâne cu sold creditor,
+  chiar dacă impozitul e deja plătit (termenul e 25.01, indiferent
+  de ridicare)
+Renunțare la dividend, documentată prin hotărâre</t>
+        </is>
+      </c>
+      <c r="E52" s="61" t="inlineStr">
+        <is>
+          <t>Sold 457 fără hotărâre AGA în spate — cea mai frecventă cauză de
+  ajungere la comisia de disciplină
+457 stins prin 4551 sau 461: dividendul nu se compensează cu
+  creditarea decât documentat
+D205 care nu se potrivește cu D100 și cu fișa lui 446 — se caută
+  o plată făcută fără declarație</t>
+        </is>
+      </c>
+      <c r="F52" s="61" t="inlineStr">
+        <is>
+          <t>F-109</t>
+        </is>
+      </c>
+      <c r="G52" s="61" t="inlineStr">
+        <is>
+          <t>Înaltă — impozitul se datorează la data DISTRIBUIRII, nu a plății</t>
         </is>
       </c>
     </row>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1881,7 +1881,7 @@
     <row r="116">
       <c r="A116" s="61" t="inlineStr">
         <is>
-          <t>Module_Declarative_Fluxuri.xlsx — 22 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
+          <t>Module_Declarative_Fluxuri.xlsx — 23 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="E12" s="66" t="inlineStr">
         <is>
-          <t>F-109 pas 1: cu sold debitor pe 1171 nu se distribuie dividende</t>
+          <t>F-109 pas 1: cu sold debitor pe 1171 nu se distribuie dividende | modul: MOD_DIVIDENDE</t>
         </is>
       </c>
       <c r="F12" s="66" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="E64" s="66" t="inlineStr">
         <is>
-          <t>F-109 pas 2: repartizarea urmează cotele din 1012, nu invers</t>
+          <t>F-109 pas 2: repartizarea urmează cotele din 1012, nu invers | modul: MOD_DIVIDENDE</t>
         </is>
       </c>
       <c r="F64" s="66" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="E67" s="66" t="inlineStr">
         <is>
-          <t>F-110 pas 2: plafonul e soldul lui 121, nu disponibilul din bancă</t>
+          <t>F-110 pas 2: plafonul e soldul lui 121, nu disponibilul din bancă | modul: MOD_DIVIDENDE</t>
         </is>
       </c>
       <c r="F67" s="66" t="inlineStr">
@@ -9718,7 +9718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9945,17 +9945,17 @@
     <row r="10">
       <c r="A10" s="66" t="inlineStr">
         <is>
-          <t>MOD_IMOBILIZARI</t>
+          <t>MOD_DIVIDENDE</t>
         </is>
       </c>
       <c r="B10" s="66" t="inlineStr">
         <is>
-          <t>F-203, F-205, F-207, F-214</t>
+          <t>F-109, F-110</t>
         </is>
       </c>
       <c r="C10" s="66" t="inlineStr">
         <is>
-          <t>B1 Intrare; B2 TVA pe regim; B3 Costuri capitalizate; B4 Amortizare lunară</t>
+          <t>Repartizarea rezultatului către asociați, cu impozit și regularizare</t>
         </is>
       </c>
       <c r="D10" s="66" t="inlineStr">
@@ -9965,29 +9965,29 @@
       </c>
       <c r="E10" s="66" t="inlineStr">
         <is>
-          <t>Declarații_IMOBILIZARI, Reguli_IMOBILIZARI, Jurnale_IMOBILIZARI, NotaExport_IMOBILIZARI</t>
+          <t>Declarații_DIVIDENDE, Reguli_DIVIDENDE, Jurnale_DIVIDENDE, NotaExport_DIVIDENDE</t>
         </is>
       </c>
       <c r="F10" s="66" t="inlineStr">
         <is>
-          <t>Pe mijloc fix + lunar</t>
+          <t>La AGA de repartizare și la 31.12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="66" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE</t>
+          <t>MOD_IMOBILIZARI</t>
         </is>
       </c>
       <c r="B11" s="66" t="inlineStr">
         <is>
-          <t>F-311, F-312, F-209</t>
+          <t>F-203, F-205, F-207, F-214</t>
         </is>
       </c>
       <c r="C11" s="66" t="inlineStr">
         <is>
-          <t>711/712/722: lanț complet producție / servicii / MF</t>
+          <t>B1 Intrare; B2 TVA pe regim; B3 Costuri capitalizate; B4 Amortizare lunară</t>
         </is>
       </c>
       <c r="D11" s="66" t="inlineStr">
@@ -9997,29 +9997,29 @@
       </c>
       <c r="E11" s="66" t="inlineStr">
         <is>
-          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
+          <t>Declarații_IMOBILIZARI, Reguli_IMOBILIZARI, Jurnale_IMOBILIZARI, NotaExport_IMOBILIZARI</t>
         </is>
       </c>
       <c r="F11" s="66" t="inlineStr">
         <is>
-          <t>La producție / servicii în curs</t>
+          <t>Pe mijloc fix + lunar</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="66" t="inlineStr">
         <is>
-          <t>MOD_SUBVENTIE</t>
+          <t>MOD_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="B12" s="66" t="inlineStr">
         <is>
-          <t>F-210</t>
+          <t>F-311, F-312, F-209</t>
         </is>
       </c>
       <c r="C12" s="66" t="inlineStr">
         <is>
-          <t>B1 Încasarea subvenției; B2 Achiziția activului; B3 Amortizare + eliberare</t>
+          <t>711/712/722: lanț complet producție / servicii / MF</t>
         </is>
       </c>
       <c r="D12" s="66" t="inlineStr">
@@ -10029,29 +10029,29 @@
       </c>
       <c r="E12" s="66" t="inlineStr">
         <is>
-          <t>Declarații_SUBVENTIE, Reguli_SUBVENTIE, Jurnale_SUBVENTIE, NotaExport_SUBVENTIE</t>
+          <t>Declarații_NEUTRALIZARE, Reguli_NEUTRALIZARE, Jurnale_NEUTRALIZARE, NotaExport_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="F12" s="66" t="inlineStr">
         <is>
-          <t>Lunar, pe activ subvenționat</t>
+          <t>La producție / servicii în curs</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="66" t="inlineStr">
         <is>
-          <t>MOD_IESIRE_MF</t>
+          <t>MOD_SUBVENTIE</t>
         </is>
       </c>
       <c r="B13" s="66" t="inlineStr">
         <is>
-          <t>F-211, F-212</t>
+          <t>F-210</t>
         </is>
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>B1 Descărcare amortizare; B2 Valoare rămasă; B3 Vânzare; B4 Piese recuperate</t>
+          <t>B1 Încasarea subvenției; B2 Achiziția activului; B3 Amortizare + eliberare</t>
         </is>
       </c>
       <c r="D13" s="66" t="inlineStr">
@@ -10061,29 +10061,29 @@
       </c>
       <c r="E13" s="66" t="inlineStr">
         <is>
-          <t>Declarații_IESIRE_MF, Reguli_IESIRE_MF, Jurnale_IESIRE_MF, NotaExport_IESIRE_MF</t>
+          <t>Declarații_SUBVENTIE, Reguli_SUBVENTIE, Jurnale_SUBVENTIE, NotaExport_SUBVENTIE</t>
         </is>
       </c>
       <c r="F13" s="66" t="inlineStr">
         <is>
-          <t>Pe eveniment de ieșire</t>
+          <t>Lunar, pe activ subvenționat</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="66" t="inlineStr">
         <is>
-          <t>MOD_APROV_TRANZIT</t>
+          <t>MOD_IESIRE_MF</t>
         </is>
       </c>
       <c r="B14" s="66" t="inlineStr">
         <is>
-          <t>F-302</t>
+          <t>F-211, F-212</t>
         </is>
       </c>
       <c r="C14" s="66" t="inlineStr">
         <is>
-          <t>32x: factură înainte de marfă / NIR înainte de factură</t>
+          <t>B1 Descărcare amortizare; B2 Valoare rămasă; B3 Vânzare; B4 Piese recuperate</t>
         </is>
       </c>
       <c r="D14" s="66" t="inlineStr">
@@ -10093,29 +10093,29 @@
       </c>
       <c r="E14" s="66" t="inlineStr">
         <is>
-          <t>Declarații_APROV_TRANZIT, Reguli_APROV_TRANZIT, Jurnale_APROV_TRANZIT, NotaExport_APROV_TRANZIT</t>
+          <t>Declarații_IESIRE_MF, Reguli_IESIRE_MF, Jurnale_IESIRE_MF, NotaExport_IESIRE_MF</t>
         </is>
       </c>
       <c r="F14" s="66" t="inlineStr">
         <is>
-          <t>La aprovizionări incomplete</t>
+          <t>Pe eveniment de ieșire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="66" t="inlineStr">
         <is>
-          <t>MOD_TAXARE_INVERSA</t>
+          <t>MOD_APROV_TRANZIT</t>
         </is>
       </c>
       <c r="B15" s="66" t="inlineStr">
         <is>
-          <t>F-303, F-402</t>
+          <t>F-302</t>
         </is>
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>Autolichidare 4426 = 4427, intracomunitar și intern</t>
+          <t>32x: factură înainte de marfă / NIR înainte de factură</t>
         </is>
       </c>
       <c r="D15" s="66" t="inlineStr">
@@ -10125,29 +10125,29 @@
       </c>
       <c r="E15" s="66" t="inlineStr">
         <is>
-          <t>Declarații_TAXARE_INVERSA, Reguli_TAXARE_INVERSA, Jurnale_TAXARE_INVERSA, NotaExport_TAXARE_INVERSA</t>
+          <t>Declarații_APROV_TRANZIT, Reguli_APROV_TRANZIT, Jurnale_APROV_TRANZIT, NotaExport_APROV_TRANZIT</t>
         </is>
       </c>
       <c r="F15" s="66" t="inlineStr">
         <is>
-          <t>La fiecare factură cu taxare inversă</t>
+          <t>La aprovizionări incomplete</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="66" t="inlineStr">
         <is>
-          <t>MOD_VANZ_AMANUNT</t>
+          <t>MOD_TAXARE_INVERSA</t>
         </is>
       </c>
       <c r="B16" s="66" t="inlineStr">
         <is>
-          <t>F-316, F-318, F-317</t>
+          <t>F-303, F-402</t>
         </is>
       </c>
       <c r="C16" s="66" t="inlineStr">
         <is>
-          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
+          <t>Autolichidare 4426 = 4427, intracomunitar și intern</t>
         </is>
       </c>
       <c r="D16" s="66" t="inlineStr">
@@ -10157,29 +10157,29 @@
       </c>
       <c r="E16" s="66" t="inlineStr">
         <is>
-          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
+          <t>Declarații_TAXARE_INVERSA, Reguli_TAXARE_INVERSA, Jurnale_TAXARE_INVERSA, NotaExport_TAXARE_INVERSA</t>
         </is>
       </c>
       <c r="F16" s="66" t="inlineStr">
         <is>
-          <t>La operațiuni amănunt + închidere lună amănunt</t>
+          <t>La fiecare factură cu taxare inversă</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="66" t="inlineStr">
         <is>
-          <t>MOD_IMPORT</t>
+          <t>MOD_VANZ_AMANUNT</t>
         </is>
       </c>
       <c r="B17" s="66" t="inlineStr">
         <is>
-          <t>F-319, F-320</t>
+          <t>F-316, F-318, F-317</t>
         </is>
       </c>
       <c r="C17" s="66" t="inlineStr">
         <is>
-          <t>TVA vamală prin 446.VAMA sau plătită direct; taxele în costul stocului</t>
+          <t>Gestiune amănunt: PVA, corelații, retur, vânzare parțială</t>
         </is>
       </c>
       <c r="D17" s="66" t="inlineStr">
@@ -10189,29 +10189,29 @@
       </c>
       <c r="E17" s="66" t="inlineStr">
         <is>
-          <t>Declarații_IMPORT, Reguli_IMPORT, Jurnale_IMPORT, NotaExport_IMPORT</t>
+          <t>Declarații_AMANUNT, Reguli_AMANUNT, Jurnale_AMANUNT, NotaExport_AMANUNT</t>
         </is>
       </c>
       <c r="F17" s="66" t="inlineStr">
         <is>
-          <t>La fiecare DVI</t>
+          <t>La operațiuni amănunt + închidere lună amănunt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="66" t="inlineStr">
         <is>
-          <t>MOD_TVA_INCASARE</t>
+          <t>MOD_IMPORT</t>
         </is>
       </c>
       <c r="B18" s="66" t="inlineStr">
         <is>
-          <t>F-401</t>
+          <t>F-319, F-320</t>
         </is>
       </c>
       <c r="C18" s="66" t="inlineStr">
         <is>
-          <t>4428.INC: factură → plată/încasare → 4426/4427</t>
+          <t>TVA vamală prin 446.VAMA sau plătită direct; taxele în costul stocului</t>
         </is>
       </c>
       <c r="D18" s="66" t="inlineStr">
@@ -10221,29 +10221,29 @@
       </c>
       <c r="E18" s="66" t="inlineStr">
         <is>
-          <t>Declarații_TVA_INC, Reguli_TVA_INC, Jurnale_TVA_INC, NotaExport_TVA_INC</t>
+          <t>Declarații_IMPORT, Reguli_IMPORT, Jurnale_IMPORT, NotaExport_IMPORT</t>
         </is>
       </c>
       <c r="F18" s="66" t="inlineStr">
         <is>
-          <t>Când regimul e TVA la încasare</t>
+          <t>La fiecare DVI</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="66" t="inlineStr">
         <is>
-          <t>MOD_INCHIDERE_TVA</t>
+          <t>MOD_TVA_INCASARE</t>
         </is>
       </c>
       <c r="B19" s="66" t="inlineStr">
         <is>
-          <t>F-405</t>
+          <t>F-401</t>
         </is>
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>Închidere 4426/4427 → 4423/4424</t>
+          <t>4428.INC: factură → plată/încasare → 4426/4427</t>
         </is>
       </c>
       <c r="D19" s="66" t="inlineStr">
@@ -10253,29 +10253,29 @@
       </c>
       <c r="E19" s="66" t="inlineStr">
         <is>
-          <t>Declarații_INCHIDERE_TVA, Reguli_INCHIDERE_TVA, Jurnale_INCHIDERE_TVA, NotaExport_INCHIDERE_TVA</t>
+          <t>Declarații_TVA_INC, Reguli_TVA_INC, Jurnale_TVA_INC, NotaExport_TVA_INC</t>
         </is>
       </c>
       <c r="F19" s="66" t="inlineStr">
         <is>
-          <t>La fiecare lună, după rulaje TVA</t>
+          <t>Când regimul e TVA la încasare</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="66" t="inlineStr">
         <is>
-          <t>MOD_FARA_DOCUMENT</t>
+          <t>MOD_INCHIDERE_TVA</t>
         </is>
       </c>
       <c r="B20" s="66" t="inlineStr">
         <is>
-          <t>F-406</t>
+          <t>F-405</t>
         </is>
       </c>
       <c r="C20" s="66" t="inlineStr">
         <is>
-          <t>TVA nedeductibilă în cheltuială; colectare la lipsa nejustificată</t>
+          <t>Închidere 4426/4427 → 4423/4424</t>
         </is>
       </c>
       <c r="D20" s="66" t="inlineStr">
@@ -10285,29 +10285,29 @@
       </c>
       <c r="E20" s="66" t="inlineStr">
         <is>
-          <t>Declarații_FARA_DOCUMENT, Reguli_FARA_DOCUMENT, Jurnale_FARA_DOCUMENT, NotaExport_FARA_DOCUMENT</t>
+          <t>Declarații_INCHIDERE_TVA, Reguli_INCHIDERE_TVA, Jurnale_INCHIDERE_TVA, NotaExport_INCHIDERE_TVA</t>
         </is>
       </c>
       <c r="F20" s="66" t="inlineStr">
         <is>
-          <t>Lunar la cheltuielile auto; la fiecare inventar cu minus</t>
+          <t>La fiecare lună, după rulaje TVA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="66" t="inlineStr">
         <is>
-          <t>MOD_INTERMEDIAR</t>
+          <t>MOD_FARA_DOCUMENT</t>
         </is>
       </c>
       <c r="B21" s="66" t="inlineStr">
         <is>
-          <t>F-408, F-501, F-411</t>
+          <t>F-406</t>
         </is>
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>408/418/473: deschidere + stingere + red flags</t>
+          <t>TVA nedeductibilă în cheltuială; colectare la lipsa nejustificată</t>
         </is>
       </c>
       <c r="D21" s="66" t="inlineStr">
@@ -10317,29 +10317,29 @@
       </c>
       <c r="E21" s="66" t="inlineStr">
         <is>
-          <t>Declarații_INTERMEDIAR, Reguli_INTERMEDIAR, Jurnale_INTERMEDIAR, NotaExport_INTERMEDIAR</t>
+          <t>Declarații_FARA_DOCUMENT, Reguli_FARA_DOCUMENT, Jurnale_FARA_DOCUMENT, NotaExport_FARA_DOCUMENT</t>
         </is>
       </c>
       <c r="F21" s="66" t="inlineStr">
         <is>
-          <t>La facturi nesosite / sume neclare</t>
+          <t>Lunar la cheltuielile auto; la fiecare inventar cu minus</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="66" t="inlineStr">
         <is>
-          <t>MOD_AVANSURI</t>
+          <t>MOD_INTERMEDIAR</t>
         </is>
       </c>
       <c r="B22" s="66" t="inlineStr">
         <is>
-          <t>F-410, F-415</t>
+          <t>F-408, F-501, F-411</t>
         </is>
       </c>
       <c r="C22" s="66" t="inlineStr">
         <is>
-          <t>419/409: avans cu TVA, stingere la factura finală, supraîncasare</t>
+          <t>408/418/473: deschidere + stingere + red flags</t>
         </is>
       </c>
       <c r="D22" s="66" t="inlineStr">
@@ -10349,29 +10349,29 @@
       </c>
       <c r="E22" s="66" t="inlineStr">
         <is>
-          <t>Declarații_AVANSURI, Reguli_AVANSURI, Jurnale_AVANSURI, NotaExport_AVANSURI</t>
+          <t>Declarații_INTERMEDIAR, Reguli_INTERMEDIAR, Jurnale_INTERMEDIAR, NotaExport_INTERMEDIAR</t>
         </is>
       </c>
       <c r="F22" s="66" t="inlineStr">
         <is>
-          <t>La fiecare avans și la orice sold creditor pe 4111</t>
+          <t>La facturi nesosite / sume neclare</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="66" t="inlineStr">
         <is>
-          <t>MOD_SALARII</t>
+          <t>MOD_AVANSURI</t>
         </is>
       </c>
       <c r="B23" s="66" t="inlineStr">
         <is>
-          <t>F-413</t>
+          <t>F-410, F-415</t>
         </is>
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>B1 Plata avansului; B2 Costurile lunii; B3 Plăți (net, taxe, CAM)</t>
+          <t>419/409: avans cu TVA, stingere la factura finală, supraîncasare</t>
         </is>
       </c>
       <c r="D23" s="66" t="inlineStr">
@@ -10381,29 +10381,29 @@
       </c>
       <c r="E23" s="66" t="inlineStr">
         <is>
-          <t>Declarații_SALARII, Reguli_SALARII, Jurnale_SALARII, NotaExport_SALARII</t>
+          <t>Declarații_AVANSURI, Reguli_AVANSURI, Jurnale_AVANSURI, NotaExport_AVANSURI</t>
         </is>
       </c>
       <c r="F23" s="66" t="inlineStr">
         <is>
-          <t>Lunar, pe registru de angajați</t>
+          <t>La fiecare avans și la orice sold creditor pe 4111</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="66" t="inlineStr">
         <is>
-          <t>MOD_SALARII_EVENIMENTE</t>
+          <t>MOD_SALARII</t>
         </is>
       </c>
       <c r="B24" s="66" t="inlineStr">
         <is>
-          <t>F-416, F-417, F-418, F-419</t>
+          <t>F-413</t>
         </is>
       </c>
       <c r="C24" s="66" t="inlineStr">
         <is>
-          <t>42x: medicale, popriri, drepturi neridicate, creanțe față de foști salariați</t>
+          <t>B1 Plata avansului; B2 Costurile lunii; B3 Plăți (net, taxe, CAM)</t>
         </is>
       </c>
       <c r="D24" s="66" t="inlineStr">
@@ -10413,29 +10413,29 @@
       </c>
       <c r="E24" s="66" t="inlineStr">
         <is>
-          <t>Declarații_SALARII_EVENIMENTE, Reguli_SALARII_EVENIMENTE, Jurnale_SALARII_EVENIMENTE, NotaExport_SALARII_EVENIMENTE</t>
+          <t>Declarații_SALARII, Reguli_SALARII, Jurnale_SALARII, NotaExport_SALARII</t>
         </is>
       </c>
       <c r="F24" s="66" t="inlineStr">
         <is>
-          <t>Pe eveniment, lângă statul lunar</t>
+          <t>Lunar, pe registru de angajați</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="66" t="inlineStr">
         <is>
-          <t>MOD_DECONT</t>
+          <t>MOD_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="B25" s="66" t="inlineStr">
         <is>
-          <t>F-502</t>
+          <t>F-416, F-417, F-418, F-419</t>
         </is>
       </c>
       <c r="C25" s="66" t="inlineStr">
         <is>
-          <t>B1 Avans; B2 Cheltuieli + TVA; B3 Regularizare avans; B4 Plată / restituire</t>
+          <t>42x: medicale, popriri, drepturi neridicate, creanțe față de foști salariați</t>
         </is>
       </c>
       <c r="D25" s="66" t="inlineStr">
@@ -10445,98 +10445,130 @@
       </c>
       <c r="E25" s="66" t="inlineStr">
         <is>
-          <t>Declarații_DECONT, Reguli_DECONT, Registru_DECONT, Jurnale_DECONT, NotaExport_DECONT</t>
+          <t>Declarații_SALARII_EVENIMENTE, Reguli_SALARII_EVENIMENTE, Jurnale_SALARII_EVENIMENTE, NotaExport_SALARII_EVENIMENTE</t>
         </is>
       </c>
       <c r="F25" s="66" t="inlineStr">
         <is>
-          <t>Pe decont</t>
+          <t>Pe eveniment, lângă statul lunar</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="66" t="inlineStr">
         <is>
+          <t>MOD_DECONT</t>
+        </is>
+      </c>
+      <c r="B26" s="66" t="inlineStr">
+        <is>
+          <t>F-502</t>
+        </is>
+      </c>
+      <c r="C26" s="66" t="inlineStr">
+        <is>
+          <t>B1 Avans; B2 Cheltuieli + TVA; B3 Regularizare avans; B4 Plată / restituire</t>
+        </is>
+      </c>
+      <c r="D26" s="66" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+      <c r="E26" s="66" t="inlineStr">
+        <is>
+          <t>Declarații_DECONT, Reguli_DECONT, Registru_DECONT, Jurnale_DECONT, NotaExport_DECONT</t>
+        </is>
+      </c>
+      <c r="F26" s="66" t="inlineStr">
+        <is>
+          <t>Pe decont</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="66" t="inlineStr">
+        <is>
           <t>MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="B26" s="66" t="inlineStr">
+      <c r="B27" s="66" t="inlineStr">
         <is>
           <t>F-422, F-413</t>
         </is>
       </c>
-      <c r="C26" s="66" t="inlineStr">
+      <c r="C27" s="66" t="inlineStr">
         <is>
           <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
         </is>
       </c>
-      <c r="D26" s="66" t="inlineStr">
+      <c r="D27" s="66" t="inlineStr">
         <is>
           <t>IMPLEMENTAT</t>
         </is>
       </c>
-      <c r="E26" s="66" t="inlineStr">
+      <c r="E27" s="66" t="inlineStr">
         <is>
           <t>Declarații_INCHIDERE_LUNARA, Reguli_INCHIDERE_LUNARA, Verificări_INCHIDERE_LUNARA, Abateri_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="F26" s="66" t="inlineStr">
+      <c r="F27" s="66" t="inlineStr">
         <is>
           <t>Lunar, pe balanța de verificare</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="36" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>CUM SE NAVIGHEAZĂ (cele două grafuri, acum sincronizate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="33" t="inlineStr">
-        <is>
-          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="33" t="inlineStr">
         <is>
-          <t>2. Pe corelație: Corelații de control → C-01…C-34 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
+          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="33" t="inlineStr">
         <is>
-          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
+          <t>2. Pe corelație: Corelații de control → C-01…C-34 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="33" t="inlineStr">
         <is>
-          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="33" t="inlineStr">
         <is>
+          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
           <t>5. Pe modul: CatalogModule (în Module_Declarative…) → Activ=DA → completezi Declarații → notele se generează.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="38" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="38" t="inlineStr">
         <is>
           <t>INVARIANT: orice cont Tier A din Plan de conturi duce (via Flux pas) la toate fluxurile relevante, inclusiv F-304…F-802 pe cazurile grele (371, 378, 4428, 32x, 408, 331, 711, 8035).</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="63" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="63" t="inlineStr">
         <is>
           <t>MOD_CAPITALURI nu dublează MOD_INCHIDERE_EX: acela închide clasele 6 și 7 pe 121, acesta repartizează rezultatul obținut (129/1061/1171).</t>
         </is>
@@ -10546,13 +10578,13 @@
   <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30107,7 +30139,7 @@
       </c>
       <c r="H19" s="69" t="inlineStr">
         <is>
-          <t>Impozit 16%. Termen de plată: 25.01 a anului următor repartizării, CHIAR DACĂ dividendele nu au fost ridicate. D100 + D205</t>
+          <t>Impozit 16%. Termen de plată: 25.01 a anului următor repartizării, CHIAR DACĂ dividendele nu au fost ridicate. D100 + D205 | modul: MOD_DIVIDENDE</t>
         </is>
       </c>
     </row>
@@ -30147,7 +30179,7 @@
       </c>
       <c r="H20" s="69" t="inlineStr">
         <is>
-          <t>Cer inventariere ȘI bilanț interimar; se acordă doar trimestrial. Bilanțul interimar se depune până la 31 iulie.</t>
+          <t>Cer inventariere ȘI bilanț interimar; se acordă doar trimestrial. Bilanțul interimar se depune până la 31 iulie. | modul: MOD_DIVIDENDE</t>
         </is>
       </c>
     </row>
@@ -57015,7 +57047,7 @@
       </c>
       <c r="F49" s="61" t="inlineStr">
         <is>
-          <t>F-114, F-109, F-112</t>
+          <t>F-114, F-109, F-112 | Module_Declarative_Fluxuri.xlsx → MOD_DIVIDENDE</t>
         </is>
       </c>
       <c r="G49" s="61" t="inlineStr">
@@ -57059,7 +57091,7 @@
       </c>
       <c r="F50" s="61" t="inlineStr">
         <is>
-          <t>F-110</t>
+          <t>F-110 | Module_Declarative_Fluxuri.xlsx → MOD_DIVIDENDE</t>
         </is>
       </c>
       <c r="G50" s="61" t="inlineStr">
@@ -57150,7 +57182,7 @@
       </c>
       <c r="F52" s="61" t="inlineStr">
         <is>
-          <t>F-109</t>
+          <t>F-109 | Module_Declarative_Fluxuri.xlsx → MOD_DIVIDENDE</t>
         </is>
       </c>
       <c r="G52" s="61" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -10934,7 +10934,7 @@
     <row r="31">
       <c r="A31" s="33" t="inlineStr">
         <is>
-          <t>2. Pe corelație: Corelații de control → C-01…C-34 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
+          <t>2. Pe corelație: Corelații de control → C-01…C-39 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
         </is>
       </c>
     </row>
@@ -58878,7 +58878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -60467,6 +60467,224 @@
       <c r="G52" s="61" t="inlineStr">
         <is>
           <t>Înaltă — impozitul se datorează la data DISTRIBUIRII, nu a plății</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="61" t="inlineStr">
+        <is>
+          <t>C-35</t>
+        </is>
+      </c>
+      <c r="B53" s="61" t="inlineStr">
+        <is>
+          <t>sold 5191 NICIODATĂ debitor
+ȘI sold 5191 = soldul confirmat de bancă,
+pe fiecare analitic de linie</t>
+        </is>
+      </c>
+      <c r="C53" s="61" t="inlineStr">
+        <is>
+          <t>Extrasul de LINIE DE CREDIT (separat de extrasul de cont), la sfârșit de lună</t>
+        </is>
+      </c>
+      <c r="D53" s="61" t="inlineStr">
+        <is>
+          <t>Sold zero: linia e disponibilă și netrasă — starea normală între trageri.</t>
+        </is>
+      </c>
+      <c r="E53" s="61" t="inlineStr">
+        <is>
+          <t>Sold debitor: s-a restituit mai mult decât s-a tras, deci o înregistrare
+  pe sensul greșit
+Dobânda operată prin 5191 în loc de 666, pentru că extrasul de linie
+  n-a fost cerut clientului — cheltuiala dispare, iar impozitul pe
+  profit se plătește în plus
+Două linii pe același analitic: totalul poate ieși, liniile nu</t>
+        </is>
+      </c>
+      <c r="F53" s="61" t="inlineStr">
+        <is>
+          <t>F-507</t>
+        </is>
+      </c>
+      <c r="G53" s="61" t="inlineStr">
+        <is>
+          <t>Înaltă — la linie NU există scadențar, deci soldul confirmat de bancă e singura verificare independentă disponibilă</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="61" t="inlineStr">
+        <is>
+          <t>C-36</t>
+        </is>
+      </c>
+      <c r="B54" s="61" t="inlineStr">
+        <is>
+          <t>sold 581 = 0 la sfârșit de lună
+ȘI diferența de curs valutar NU trece prin 581</t>
+        </is>
+      </c>
+      <c r="C54" s="61" t="inlineStr">
+        <is>
+          <t>Balanța la sfârșit de lună + jurnalul de bancă</t>
+        </is>
+      </c>
+      <c r="D54" s="61" t="inlineStr">
+        <is>
+          <t>Transfer inițiat la sfârșitul lunii și primit la începutul lunii
+  următoare: soldul e chiar realitatea, banii sunt pe drum.</t>
+        </is>
+      </c>
+      <c r="E54" s="61" t="inlineStr">
+        <is>
+          <t>Diferența de curs de la transferul valută → lei lăsată în 581: contul
+  nu se mai închide, iar soldul rămas devine imposibil de citit —
+  transfer în curs sau diferență necontabilizată?
+Transfer înregistrat pe o singură parte</t>
+        </is>
+      </c>
+      <c r="F54" s="61" t="inlineStr">
+        <is>
+          <t>F-501 | Module_Declarative_Fluxuri.xlsx → MOD_INTERMEDIAR</t>
+        </is>
+      </c>
+      <c r="G54" s="61" t="inlineStr">
+        <is>
+          <t>Medie — 581 e cont de tranzit PUR: trebuie să iasă cu exact cât a intrat, iar diferența de curs aparține contului în valută, unde s-a și produs</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="61" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="B55" s="61" t="inlineStr">
+        <is>
+          <t>Σ analitice = sold sintetic,
+pe FIECARE cont cu analitic obligatoriu
+(4111 · 401 · 512x · 542 · 446 · 455 · 1012)</t>
+        </is>
+      </c>
+      <c r="C55" s="61" t="inlineStr">
+        <is>
+          <t>Balanța analitică vs. balanța sintetică; la bancă, și extrasul de cont</t>
+        </is>
+      </c>
+      <c r="D55" s="61" t="inlineStr">
+        <is>
+          <t>Nimic. Nu există motiv legitim pentru care suma analiticelor să difere
+  de sintetic — e o identitate, nu o estimare.</t>
+        </is>
+      </c>
+      <c r="E55" s="61" t="inlineStr">
+        <is>
+          <t>Operațiune făcută DUPĂ închiderea de lună, fără refacerea închiderii —
+  cauza cea mai frecventă, și nu se anunță singură
+Sume nealocate lăsate pe 4111 sau 401 fără analitic de partener
+Cont pornit fără analitic și spart ulterior: istoricul rămâne pe
+  sintetic
+La bancă: jurnalul dă cu extrasul, dar nu dă cu balanța — semn că
+  diferența e între analitic și sintetic, nu în operare</t>
+        </is>
+      </c>
+      <c r="F55" s="61" t="inlineStr">
+        <is>
+          <t>F-214, F-503, F-507 | Module_Declarative_Fluxuri.xlsx → MOD_IMOBILIZARI</t>
+        </is>
+      </c>
+      <c r="G55" s="61" t="inlineStr">
+        <is>
+          <t>Înaltă — e verificarea pe care formatorul o cere la preluarea oricărei societăți, înaintea oricărei alte analize</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="61" t="inlineStr">
+        <is>
+          <t>C-38</t>
+        </is>
+      </c>
+      <c r="B56" s="61" t="inlineStr">
+        <is>
+          <t>sold 5311 ≤ 50.000 lei la sfârșitul FIECĂREI ZILE</t>
+        </is>
+      </c>
+      <c r="C56" s="61" t="inlineStr">
+        <is>
+          <t>Registrul de casă, pe fiecare casierie</t>
+        </is>
+      </c>
+      <c r="D56" s="61" t="inlineStr">
+        <is>
+          <t>Depășirea cu sumele aferente plății salariilor și altor drepturi de
+  personal, pentru perioada scurtă prevăzută de lege.</t>
+        </is>
+      </c>
+      <c r="E56" s="61" t="inlineStr">
+        <is>
+          <t>Sold peste plafon purtat de la o zi la alta: ce depășește trebuie
+  depus în cont
+Casierie deschisă special ca să se multiplice plafonul ❓
+Sold de casă mare și constant, fără numerar real în casă — cazul pe
+  care controlul îl cere arătat efectiv</t>
+        </is>
+      </c>
+      <c r="F56" s="61" t="inlineStr">
+        <is>
+          <t>F-502 | Module_Declarative_Fluxuri.xlsx → MOD_DECONT</t>
+        </is>
+      </c>
+      <c r="G56" s="61" t="inlineStr">
+        <is>
+          <t>Înaltă — plafonul a fost introdus relativ recent; cine lucrează după obiceiul vechi, când soldul era nelimitat, îl încalcă fără să știe</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="61" t="inlineStr">
+        <is>
+          <t>C-39</t>
+        </is>
+      </c>
+      <c r="B57" s="61" t="inlineStr">
+        <is>
+          <t>la preluarea unei balanțe ÎN CURSUL ANULUI
+se preiau TOTAL SUME debitoare și creditoare,
+nu soldurile</t>
+        </is>
+      </c>
+      <c r="C57" s="61" t="inlineStr">
+        <is>
+          <t>Balanța de preluare vs. balanța lunii următoare</t>
+        </is>
+      </c>
+      <c r="D57" s="61" t="inlineStr">
+        <is>
+          <t>Preluare la 1 ianuarie: acolo soldurile CHIAR sunt punctul de plecare,
+  iar rulajele anului pornesc de la zero pe bună dreptate.</t>
+        </is>
+      </c>
+      <c r="E57" s="61" t="inlineStr">
+        <is>
+          <t>Preluare la mijloc de an cu soldurile puse ca sold inițial: rulajele
+  anului pornesc de la zero din luna preluării, iar ORICE verificare
+  pe rulaj devine falsă — corelația cu fișa de rol la TVA, CAM-ul ca
+  procent din brut, rulajul creditor al obligațiilor salariale
+Total sume care nu cresc monoton de la o lună la alta</t>
+        </is>
+      </c>
+      <c r="F57" s="61" t="inlineStr">
+        <is>
+          <t>F-422, F-405 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_LUNARA / MOD_INCHIDERE_TVA</t>
+        </is>
+      </c>
+      <c r="G57" s="61" t="inlineStr">
+        <is>
+          <t>Înaltă — eroarea nu se vede în luna preluării, ci la prima verificare pe rulaj, când nu mai știe nimeni de unde vine</t>
         </is>
       </c>
     </row>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1881,7 +1881,7 @@
     <row r="116">
       <c r="A116" s="61" t="inlineStr">
         <is>
-          <t>Module_Declarative_Fluxuri.xlsx — 23 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
+          <t>Module_Declarative_Fluxuri.xlsx — 24 module declarative (Declarații → Reguli → Jurnale → NotaExport). Niciunul nu mai e „exemplu extern”: salariile, deconturile și leasingul au devenit interne, cu cifrele verificate contra fișierelor reale de la client.</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="E10" s="29" t="inlineStr">
         <is>
-          <t>F-104 | modul: MOD_INCHIDERE_EX</t>
+          <t>F-104 | modul: MOD_INCHIDERE_EX / MOD_CONTROL_BALANTA</t>
         </is>
       </c>
       <c r="F10" s="29" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="E15" s="29" t="inlineStr">
         <is>
-          <t>F-104; F-314 711 se închide pe 121 | modul: MOD_INCHIDERE_EX</t>
+          <t>F-104; F-314 711 se închide pe 121 | modul: MOD_INCHIDERE_EX / MOD_CONTROL_BALANTA</t>
         </is>
       </c>
       <c r="F15" s="29" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>F-214 oglinda 21x↔28x; F-211/F-212 descărcare la ieșire | modul: MOD_LEASING_FIN / MOD_IESIRE_MF / MOD_IMOBILIZARI</t>
+          <t>F-214 oglinda 21x↔28x; F-211/F-212 descărcare la ieșire | modul: MOD_LEASING_FIN / MOD_IESIRE_MF / MOD_IMOBILIZARI / MOD_CONTROL_BALANTA</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E51" s="29" t="inlineStr">
         <is>
-          <t>F-104 | modul: MOD_INCHIDERE_EX</t>
+          <t>F-104 | modul: MOD_INCHIDERE_EX / MOD_CONTROL_BALANTA</t>
         </is>
       </c>
       <c r="F51" s="29" t="inlineStr">
@@ -10117,7 +10117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10888,86 +10888,118 @@
     <row r="27">
       <c r="A27" s="66" t="inlineStr">
         <is>
+          <t>MOD_CONTROL_BALANTA</t>
+        </is>
+      </c>
+      <c r="B27" s="66" t="inlineStr">
+        <is>
+          <t>F-214, F-104</t>
+        </is>
+      </c>
+      <c r="C27" s="66" t="inlineStr">
+        <is>
+          <t>V1 Analitic ↔ sintetic; V2 121 cu clasele 6 și 7; V3 Solduri cu semn contrar naturii; V4 Continuitatea total-sumelor</t>
+        </is>
+      </c>
+      <c r="D27" s="66" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+      <c r="E27" s="66" t="inlineStr">
+        <is>
+          <t>Declarații_CONTROL_BALANTA, Reguli_CONTROL_BALANTA, Verificări_CONTROL_BALANTA, Abateri_CONTROL_BALANTA</t>
+        </is>
+      </c>
+      <c r="F27" s="66" t="inlineStr">
+        <is>
+          <t>Lunar, pe balanța de verificare; obligatoriu la preluarea unei societăți</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="66" t="inlineStr">
+        <is>
           <t>MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="B27" s="66" t="inlineStr">
+      <c r="B28" s="66" t="inlineStr">
         <is>
           <t>F-422, F-413</t>
         </is>
       </c>
-      <c r="C27" s="66" t="inlineStr">
+      <c r="C28" s="66" t="inlineStr">
         <is>
           <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
         </is>
       </c>
-      <c r="D27" s="66" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>IMPLEMENTAT</t>
         </is>
       </c>
-      <c r="E27" s="66" t="inlineStr">
+      <c r="E28" s="66" t="inlineStr">
         <is>
           <t>Declarații_INCHIDERE_LUNARA, Reguli_INCHIDERE_LUNARA, Verificări_INCHIDERE_LUNARA, Abateri_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="F27" s="66" t="inlineStr">
+      <c r="F28" s="66" t="inlineStr">
         <is>
           <t>Lunar, pe balanța de verificare</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="36" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>CUM SE NAVIGHEAZĂ (cele două grafuri, acum sincronizate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="33" t="inlineStr">
-        <is>
-          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="33" t="inlineStr">
         <is>
-          <t>2. Pe corelație: Corelații de control → C-01…C-39 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
+          <t>1. Pe cont: Plan de conturi → coloana „Flux (pas)" → include F-301…F-802 (inclusiv intersecții).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="33" t="inlineStr">
         <is>
-          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
+          <t>2. Pe corelație: Corelații de control → C-01…C-39 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="33" t="inlineStr">
         <is>
-          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+          <t>3. Pe rol: Doar rol în flux → conturi de serviciu → fluxuri.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="33" t="inlineStr">
         <is>
+          <t>4. Pe acoperire: Matrice acoperire → cont Tier A → toate fluxurile + gol/parțial onest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
           <t>5. Pe modul: CatalogModule (în Module_Declarative…) → Activ=DA → completezi Declarații → notele se generează.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="38" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="38" t="inlineStr">
         <is>
           <t>INVARIANT: orice cont Tier A din Plan de conturi duce (via Flux pas) la toate fluxurile relevante, inclusiv F-304…F-802 pe cazurile grele (371, 378, 4428, 32x, 408, 331, 711, 8035).</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="63" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="63" t="inlineStr">
         <is>
           <t>MOD_CAPITALURI nu dublează MOD_INCHIDERE_EX: acela închide clasele 6 și 7 pe 121, acesta repartizează rezultatul obținut (129/1061/1171).</t>
         </is>
@@ -10975,15 +11007,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31006,7 +31038,7 @@
       </c>
       <c r="H14" s="29" t="inlineStr">
         <is>
-          <t>Pas revelator: 121 colectează cls.6+7. D101, D100 | modul: MOD_INCHIDERE_EX</t>
+          <t>Pas revelator: 121 colectează cls.6+7. D101, D100 | modul: MOD_INCHIDERE_EX / MOD_CONTROL_BALANTA</t>
         </is>
       </c>
     </row>
@@ -31973,7 +32005,7 @@
       </c>
       <c r="H39" s="69" t="inlineStr">
         <is>
-          <t>Flux de CONTROL: pașii sunt verificări, nu înregistrări | modul: MOD_IMOBILIZARI | ❓ Î-14</t>
+          <t>Flux de CONTROL: pașii sunt verificări, nu înregistrări | modul: MOD_IMOBILIZARI / MOD_CONTROL_BALANTA | ❓ Î-14</t>
         </is>
       </c>
     </row>
@@ -59187,7 +59219,7 @@
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>F-104, F-314, F-311, F-312, F-209 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_EX | Module_Declarative_Fluxuri.xlsx → MOD_NEUTRALIZARE</t>
+          <t>F-104, F-314, F-311, F-312, F-209 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_EX | Module_Declarative_Fluxuri.xlsx → MOD_CONTROL_BALANTA / MOD_NEUTRALIZARE</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -59566,7 +59598,7 @@
       </c>
       <c r="F31" s="61" t="inlineStr">
         <is>
-          <t>F-211, F-212, F-214 | Module_Declarative_Fluxuri.xlsx → MOD_IESIRE_MF / MOD_IMOBILIZARI</t>
+          <t>F-211, F-212, F-214 | Module_Declarative_Fluxuri.xlsx → MOD_IESIRE_MF / MOD_IMOBILIZARI / MOD_CONTROL_BALANTA</t>
         </is>
       </c>
       <c r="G31" s="61" t="inlineStr">
@@ -59609,7 +59641,7 @@
       </c>
       <c r="F32" s="61" t="inlineStr">
         <is>
-          <t>F-202, F-203, F-214 | Module_Declarative_Fluxuri.xlsx → MOD_IMOBILIZARI</t>
+          <t>F-202, F-203, F-214 | Module_Declarative_Fluxuri.xlsx → MOD_IMOBILIZARI / MOD_CONTROL_BALANTA</t>
         </is>
       </c>
       <c r="G32" s="61" t="inlineStr">
@@ -59651,7 +59683,7 @@
       </c>
       <c r="F33" s="61" t="inlineStr">
         <is>
-          <t>F-207, F-214 | Module_Declarative_Fluxuri.xlsx → MOD_IMOBILIZARI | ❓ Î-14</t>
+          <t>F-207, F-214 | Module_Declarative_Fluxuri.xlsx → MOD_IMOBILIZARI / MOD_CONTROL_BALANTA | ❓ Î-14</t>
         </is>
       </c>
       <c r="G33" s="61" t="inlineStr">
@@ -59693,7 +59725,7 @@
       </c>
       <c r="F34" s="61" t="inlineStr">
         <is>
-          <t>F-104, F-314, F-103 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_EX / MOD_CAPITALURI</t>
+          <t>F-104, F-314, F-103 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_EX / MOD_CONTROL_BALANTA / MOD_CAPITALURI</t>
         </is>
       </c>
       <c r="G34" s="61" t="inlineStr">
@@ -60593,7 +60625,7 @@
       </c>
       <c r="F55" s="61" t="inlineStr">
         <is>
-          <t>F-214, F-503, F-507 | Module_Declarative_Fluxuri.xlsx → MOD_IMOBILIZARI</t>
+          <t>F-214, F-503, F-507 | Module_Declarative_Fluxuri.xlsx → MOD_IMOBILIZARI / MOD_CONTROL_BALANTA</t>
         </is>
       </c>
       <c r="G55" s="61" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1888,14 +1888,14 @@
     <row r="117">
       <c r="A117" s="61" t="inlineStr">
         <is>
-          <t>intrebari-formator.md / .html — cele 23 întrebări rămase deschise (din 36: 13 verificate cu temei legal, 9 decizii de cabinet), grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
+          <t>intrebari-formator.md / .html — cele 27 întrebări rămase deschise (din 40: 13 verificate cu temei legal, 9 decizii de cabinet), grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="61" t="inlineStr">
         <is>
-          <t>Cele 5 documente de studiu, în .md, .docx și .html: Capitaluri, credite, leasing și provizioane · Imobilizări · Stocuri, TVA și corelații de balanță · Salarii, contribuții și rețineri · Control, documente și numerar. Titlurile sunt pe subiect contabil, nu pe ziua de training — cauți o regulă pe clasa contului, nu pe data când s-a predat.</t>
+          <t>Cele 6 documente de studiu, în .md, .docx și .html: Capitaluri, credite, leasing și provizioane · Imobilizări · Stocuri, TVA și corelații de balanță · Salarii, contribuții și rețineri · Trezorerie: bancă, casă, efecte de încasat și avansuri · Control, documente și numerar. Titlurile sunt pe subiect contabil, nu pe ziua de training — cauți o regulă pe clasa contului, nu pe data când s-a predat.</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6086,32 +6086,33 @@
       </c>
       <c r="B40" s="61" t="inlineStr">
         <is>
-          <t>Dividende — CASS, declarații și termene</t>
+          <t>Trezorerie — diferențe de curs și plafoane</t>
         </is>
       </c>
       <c r="C40" s="61" t="inlineStr">
         <is>
-          <t>CASS pe dividende se datorează la dividendele DISTRIBUITE sau la cele efectiv RIDICATE?</t>
+          <t>Reevaluarea de sfârșit de lună a conturilor în valută se înregistrează pe 665/765 sau pe 668/768?</t>
         </is>
       </c>
       <c r="D40" s="61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-107
+MOD_CREDIT_VALUTA</t>
         </is>
       </c>
       <c r="E40" s="61" t="inlineStr">
         <is>
-          <t>Momentul în care se naște obligația de CASS și, prin el, ce arată Declarația Unică față de soldul lui 457. Un 457 cu sold creditor la 31.12 înseamnă dividende distribuite și neridicate: dacă baza CASS e distribuirea, obligația există deja; dacă e ridicarea, nu.</t>
+          <t>F-107 pasul de reevaluare, MOD_CREDIT_VALUTA în întregime, și structura analitică a lui 665/765. Nu e nuanță de stil: cele două variante pun aceeași sumă în conturi care se raportează diferit.</t>
         </is>
       </c>
       <c r="F40" s="61" t="inlineStr">
         <is>
-          <t>Am urmat notițele — baza e ridicarea — pentru că le confirmă structura declarației (două rubrici înseamnă două momente). Locul de verificat e art. 170 din Codul fiscal, care descrie ce venituri intră în baza anuală; n-am putut-o confirma pe sursă publică, deci rămâne întrebare, nu răspuns. Contrastul cu impozitul e clar și el e sigur: impozitul de 16% se datorează la DISTRIBUIRE, cu termen 25.01, indiferent de ridicare.</t>
+          <t>Am păstrat 665/765 pentru ambele situații, cu analitic .DEC și .REV. Motivul: funcțiunea contului 665 din OMFP 1802/2014 include explicit diferențele rezultate „la sfârșitul lunii/exercițiului financiar, din evaluarea disponibilităților bancare și a numerarului în valută” — deci reevaluarea e chiar în funcțiunea lui. Iar 668/768 au alt rost: creanțele și datoriile exprimate în LEI, decontabile după cursul unei valute. Scopul formatorului — reevaluarea separată de decontare — se atinge cu analiticul, fără să mute reevaluarea în afara contului de diferențe de curs. Dacă formatorul confirmă varianta lui, se schimbă; dar atunci trebuie explicat cum se raportează diferențele de curs care nu mai sunt în contul lor.</t>
         </is>
       </c>
       <c r="G40" s="61" t="inlineStr">
         <is>
-          <t>training 26.08.2026, punctul 2</t>
+          <t>training 28.08.2026, punctul 1</t>
         </is>
       </c>
     </row>
@@ -6123,189 +6124,337 @@
       </c>
       <c r="B41" s="61" t="inlineStr">
         <is>
+          <t>Trezorerie — diferențe de curs și plafoane</t>
+        </is>
+      </c>
+      <c r="C41" s="61" t="inlineStr">
+        <is>
+          <t>Plafonul de 50.000 lei la soldul de casă e per societate sau per casierie / punct de lucru?</t>
+        </is>
+      </c>
+      <c r="D41" s="61" t="inlineStr">
+        <is>
+          <t>C-38</t>
+        </is>
+      </c>
+      <c r="E41" s="61" t="inlineStr">
+        <is>
+          <t>C-38 și cadența pe 5311. Dacă limita e per societate, o a doua casierie nu rezolvă nimic și clientul e în neregulă; dacă e per casierie, orice societate poate multiplica plafonul deschizând puncte de lucru, ceea ce ar goli restricția de sens.</t>
+        </is>
+      </c>
+      <c r="F41" s="61" t="inlineStr">
+        <is>
+          <t>Am formulat C-38 pe casierie, cum spun notițele, dar cu semnalul „casierie deschisă special ca să se multiplice plafonul” trecut la SUSPECT — pentru că intenția se vede, indiferent cum e textul. De confirmat art. 4 din Legea 70/2015 în forma în vigoare.</t>
+        </is>
+      </c>
+      <c r="G41" s="61" t="inlineStr">
+        <is>
+          <t>training 28.08.2026, punctul 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="61" t="inlineStr">
+        <is>
+          <t>Î-33</t>
+        </is>
+      </c>
+      <c r="B42" s="61" t="inlineStr">
+        <is>
+          <t>Gestiuni, bonuri de consum și compensări</t>
+        </is>
+      </c>
+      <c r="C42" s="61" t="inlineStr">
+        <is>
+          <t>Care e forma obligatorie a bonului de consum, și în ce cazuri poate fi înlocuit cu alt document?</t>
+        </is>
+      </c>
+      <c r="D42" s="61" t="inlineStr">
+        <is>
+          <t>F-321</t>
+        </is>
+      </c>
+      <c r="E42" s="61" t="inlineStr">
+        <is>
+          <t>F-321 pasul 3 și regula „consumul trece prin gestiune” din documentul de stocuri. De forma documentului depinde ce i se cere clientului să aducă lunar — iar cerința se face o dată, la preluare, sau nu se mai face.</t>
+        </is>
+      </c>
+      <c r="F42" s="61" t="inlineStr">
+        <is>
+          <t>Am modelat consumul pe bon de consum, fără să afirm o formă anume. Alternativele de verificat: fișa limită de consum la consumuri repetitive, și avizul intern la transferurile între gestiuni.</t>
+        </is>
+      </c>
+      <c r="G42" s="61" t="inlineStr">
+        <is>
+          <t>training 28.08.2026, punctul 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="61" t="inlineStr">
+        <is>
+          <t>Î-34</t>
+        </is>
+      </c>
+      <c r="B43" s="61" t="inlineStr">
+        <is>
+          <t>Gestiuni, bonuri de consum și compensări</t>
+        </is>
+      </c>
+      <c r="C43" s="61" t="inlineStr">
+        <is>
+          <t>Ce document susține compensarea 4091 ↔ 419 la același partener, și de la ce prag trebuie făcută prin sistemul reglementat?</t>
+        </is>
+      </c>
+      <c r="D43" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="61" t="inlineStr">
+        <is>
+          <t>Dacă apare un flux de compensare, el are nevoie de documentul justificativ ca stare inițială. Fără el, compensarea e o decizie unilaterală asupra unor solduri care aparțin la două raporturi juridice diferite.</t>
+        </is>
+      </c>
+      <c r="F43" s="61" t="inlineStr">
+        <is>
+          <t>Analiza e în documentul de control, §9.4: compensarea e posibilă, dar cere acord scris între părți, iar TVA-ul NU se compensează odată cu avansurile — regularizarea lui se face la facturile finale, prin stornarea fiecărui avans în parte. N-am scris flux, pentru că starea inițială depinde de răspuns.</t>
+        </is>
+      </c>
+      <c r="G43" s="61" t="inlineStr">
+        <is>
+          <t>training 28.08.2026, punctul 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="61" t="inlineStr">
+        <is>
+          <t>Î-35</t>
+        </is>
+      </c>
+      <c r="B44" s="61" t="inlineStr">
+        <is>
+          <t>Dividende — CASS, declarații și termene</t>
+        </is>
+      </c>
+      <c r="C44" s="61" t="inlineStr">
+        <is>
+          <t>CASS pe dividende se datorează la dividendele DISTRIBUITE sau la cele efectiv RIDICATE?</t>
+        </is>
+      </c>
+      <c r="D44" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="61" t="inlineStr">
+        <is>
+          <t>Momentul în care se naște obligația de CASS și, prin el, ce arată Declarația Unică față de soldul lui 457. Un 457 cu sold creditor la 31.12 înseamnă dividende distribuite și neridicate: dacă baza CASS e distribuirea, obligația există deja; dacă e ridicarea, nu.</t>
+        </is>
+      </c>
+      <c r="F44" s="61" t="inlineStr">
+        <is>
+          <t>Am urmat notițele — baza e ridicarea — pentru că le confirmă structura declarației (două rubrici înseamnă două momente). Locul de verificat e art. 170 din Codul fiscal, care descrie ce venituri intră în baza anuală; n-am putut-o confirma pe sursă publică, deci rămâne întrebare, nu răspuns. Contrastul cu impozitul e clar și el e sigur: impozitul de 16% se datorează la DISTRIBUIRE, cu termen 25.01, indiferent de ridicare.</t>
+        </is>
+      </c>
+      <c r="G44" s="61" t="inlineStr">
+        <is>
+          <t>training 26.08.2026, punctul 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="61" t="inlineStr">
+        <is>
+          <t>Î-36</t>
+        </is>
+      </c>
+      <c r="B45" s="61" t="inlineStr">
+        <is>
           <t>Acte de control — 4423 sau 4481</t>
         </is>
       </c>
-      <c r="C41" s="61" t="inlineStr">
+      <c r="C45" s="61" t="inlineStr">
         <is>
           <t>Sumele stabilite prin decizie de impunere pe TVA se înregistrează în 4423 cu analitic distinct, sau în 4481?</t>
         </is>
       </c>
-      <c r="D41" s="61" t="inlineStr">
+      <c r="D45" s="61" t="inlineStr">
         <is>
           <t>F-421
 C-29
 C-33</t>
         </is>
       </c>
-      <c r="E41" s="61" t="inlineStr">
+      <c r="E45" s="61" t="inlineStr">
         <is>
           <t>F-421 în întregime, corelațiile C-29 și C-33, și structura analitică a lui 4423. Nu e o nuanță de stil: cele două variante dau solduri diferite pe contul pe care decontul de TVA îl reconciliază.</t>
         </is>
       </c>
-      <c r="F41" s="61" t="inlineStr">
+      <c r="F45" s="61" t="inlineStr">
         <is>
           <t>Am adoptat varianta din 26.08, pentru că e singura care dă un motiv verificabil: un analitic separă EVIDENȚA, dar nu separă SOLDUL, iar decontul se compară pe soldul sintetic al lui 4423. F-421 e rescris pe 4481, cu ❓ pe el. Dacă formatorul confirmă varianta din 21.08, fluxul se întoarce — dar atunci trebuie explicat cum rămâne corelația decont ↔ balanță valabilă, pentru că azi nu văd cum.</t>
         </is>
       </c>
-      <c r="G41" s="61" t="inlineStr">
+      <c r="G45" s="61" t="inlineStr">
         <is>
           <t>training 26.08.2026, punctul 3</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="61" t="inlineStr">
-        <is>
-          <t>Î-33</t>
-        </is>
-      </c>
-      <c r="B42" s="61" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="61" t="inlineStr">
+        <is>
+          <t>Î-37</t>
+        </is>
+      </c>
+      <c r="B46" s="61" t="inlineStr">
         <is>
           <t>Microîntreprindere — prag și cotă</t>
         </is>
       </c>
-      <c r="C42" s="61" t="inlineStr">
+      <c r="C46" s="61" t="inlineStr">
         <is>
           <t>Care sunt pragul de venituri și cota de impozit pentru microîntreprinderi, în vigoare la data operațiunii?</t>
         </is>
       </c>
-      <c r="D42" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="61" t="inlineStr">
+      <c r="D46" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="61" t="inlineStr">
         <is>
           <t>Fluxul de impozit micro (698 = 4418) și avertizarea clientului care se apropie de prag. Trecerea se face din trimestrul depășirii, deci un prag greșit înseamnă o declarație greșită, nu doar o estimare.</t>
         </is>
       </c>
-      <c r="F42" s="61" t="inlineStr">
+      <c r="F46" s="61" t="inlineStr">
         <is>
           <t>Am folosit 100.000 EUR și 1% ca în notițe, marcate ❓.</t>
         </is>
       </c>
-      <c r="G42" s="61" t="inlineStr">
+      <c r="G46" s="61" t="inlineStr">
         <is>
           <t>training 21.08.2026, punctul 2</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="61" t="inlineStr">
-        <is>
-          <t>Î-34</t>
-        </is>
-      </c>
-      <c r="B43" s="61" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="61" t="inlineStr">
+        <is>
+          <t>Î-38</t>
+        </is>
+      </c>
+      <c r="B47" s="61" t="inlineStr">
         <is>
           <t>Decontul de TVA și fișa de rol</t>
         </is>
       </c>
-      <c r="C43" s="61" t="inlineStr">
+      <c r="C47" s="61" t="inlineStr">
         <is>
           <t>Ce rânduri din D300 sunt preluate în fișa de rol: 36 și 37, sau 44 și 45?</t>
         </is>
       </c>
-      <c r="D43" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="61" t="inlineStr">
+      <c r="D47" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="61" t="inlineStr">
         <is>
           <t>Corelația decont ↔ fișă de rol ↔ balanță. Fără numerele corecte, corelația nu se poate scrie ca formulă, ci doar descrie.</t>
         </is>
       </c>
-      <c r="F43" s="61" t="inlineStr">
+      <c r="F47" s="61" t="inlineStr">
         <is>
           <t>Am scris corelația pe SOLD, care nu depinde de numerotarea rândurilor, și am marcat rândurile ca deschise.</t>
         </is>
       </c>
-      <c r="G43" s="61" t="inlineStr">
+      <c r="G47" s="61" t="inlineStr">
         <is>
           <t>training 21.08.2026, punctul 5</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="61" t="inlineStr">
-        <is>
-          <t>Î-35</t>
-        </is>
-      </c>
-      <c r="B44" s="61" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="61" t="inlineStr">
+        <is>
+          <t>Î-39</t>
+        </is>
+      </c>
+      <c r="B48" s="61" t="inlineStr">
         <is>
           <t>Decontul de TVA și fișa de rol</t>
         </is>
       </c>
-      <c r="C44" s="61" t="inlineStr">
+      <c r="C48" s="61" t="inlineStr">
         <is>
           <t>La declarațiile care admit rectificare, contează ordinea cronologică a înregistrării facturilor la redepunere?</t>
         </is>
       </c>
-      <c r="D44" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="61" t="inlineStr">
+      <c r="D48" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="61" t="inlineStr">
         <is>
           <t>Procedura de corecție după depunere, pe toate declarațiile care admit rectificativă. Decontul de TVA nu admite, deci acolo întrebarea nu se pune — dar la celelalte, da.</t>
         </is>
       </c>
-      <c r="F44" s="61" t="inlineStr">
+      <c r="F48" s="61" t="inlineStr">
         <is>
           <t>N-am implementat nimic pe presupunerea asta.</t>
         </is>
       </c>
-      <c r="G44" s="61" t="inlineStr">
+      <c r="G48" s="61" t="inlineStr">
         <is>
           <t>training 21.08.2026, punctul 6</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="61" t="inlineStr">
-        <is>
-          <t>Î-36</t>
-        </is>
-      </c>
-      <c r="B45" s="61" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="61" t="inlineStr">
+        <is>
+          <t>Î-40</t>
+        </is>
+      </c>
+      <c r="B49" s="61" t="inlineStr">
         <is>
           <t>Decontul de TVA și fișa de rol</t>
         </is>
       </c>
-      <c r="C45" s="61" t="inlineStr">
+      <c r="C49" s="61" t="inlineStr">
         <is>
           <t>Care sunt corelațiile complete între D300 și fișa de rol la TVA?</t>
         </is>
       </c>
-      <c r="D45" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="61" t="inlineStr">
+      <c r="D49" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="61" t="inlineStr">
         <is>
           <t>Corelațiile de control pe TVA. Ce avem acum se verifică pe sold; corelația pe rulaj, rând cu rând, are nevoie de structura exactă a fișei de rol.</t>
         </is>
       </c>
-      <c r="F45" s="61" t="inlineStr">
+      <c r="F49" s="61" t="inlineStr">
         <is>
           <t>Am scris corelația pe sold și am lăsat-o pe cea pe rulaj ca gol declarat — n-am fișă de rol de citit.</t>
         </is>
       </c>
-      <c r="G45" s="61" t="inlineStr">
+      <c r="G49" s="61" t="inlineStr">
         <is>
           <t>training 21.08.2026, punctul 7</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="63" t="inlineStr">
-        <is>
-          <t>36 de întrebări, 20 teme. Aceeași sursă cu dist/intrebari-formator.md și cu pagina publicată — nu pot diverge.</t>
+    <row r="51">
+      <c r="A51" s="63" t="inlineStr">
+        <is>
+          <t>40 de întrebări, 22 teme. Aceeași sursă cu dist/intrebari-formator.md și cu pagina publicată — nu pot diverge.</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6465,7 @@
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31158,7 +31307,7 @@
       </c>
       <c r="H17" s="69" t="inlineStr">
         <is>
-          <t>Pas revelator: reevaluarea LUNARĂ a soldului, nu doar diferența la plată | modul: MOD_CREDIT_VALUTA</t>
+          <t>Pas revelator: reevaluarea LUNARĂ a soldului, nu doar diferența la plată | modul: MOD_CREDIT_VALUTA | ❓ Î-31</t>
         </is>
       </c>
     </row>
@@ -32937,7 +33086,7 @@
       </c>
       <c r="H63" s="69" t="inlineStr">
         <is>
-          <t>⚠ Notițele scriau perechea lui 608 ca `308`. E transpoziție de cifre: 381 e contul de ambalaje, iar 308 e „Diferențe de preț la materii prime” — un cont rectificativ, nu o gestiune de consumat.</t>
+          <t>⚠ Notițele scriau perechea lui 608 ca `308`. E transpoziție de cifre: 381 e contul de ambalaje, iar 308 e „Diferențe de preț la materii prime” — un cont rectificativ, nu o gestiune de consumat. | ❓ Î-33</t>
         </is>
       </c>
     </row>
@@ -33784,7 +33933,7 @@
       </c>
       <c r="H85" s="69" t="inlineStr">
         <is>
-          <t>Sumele stabilite prin decizie de impunere NU ajung niciodată în decontul de TVA. ❓ Notițele din 21.08 spun „4423 cu analitic distinct”, cele din 26.08 spun 4481 — vezi principiul și întrebarea din listă. | ❓ Î-32</t>
+          <t>Sumele stabilite prin decizie de impunere NU ajung niciodată în decontul de TVA. ❓ Notițele din 21.08 spun „4423 cu analitic distinct”, cele din 26.08 spun 4481 — vezi principiul și întrebarea din listă. | ❓ Î-36</t>
         </is>
       </c>
     </row>
@@ -60272,7 +60421,7 @@
       </c>
       <c r="F47" s="61" t="inlineStr">
         <is>
-          <t>F-405, F-407, F-421 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_TVA | ❓ Î-32</t>
+          <t>F-405, F-407, F-421 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_TVA | ❓ Î-36</t>
         </is>
       </c>
       <c r="G47" s="61" t="inlineStr">
@@ -60447,7 +60596,7 @@
       </c>
       <c r="F51" s="61" t="inlineStr">
         <is>
-          <t>F-421, F-424 | ❓ Î-32</t>
+          <t>F-421, F-424 | ❓ Î-36</t>
         </is>
       </c>
       <c r="G51" s="61" t="inlineStr">
@@ -60667,7 +60816,7 @@
       </c>
       <c r="F56" s="61" t="inlineStr">
         <is>
-          <t>F-502 | Module_Declarative_Fluxuri.xlsx → MOD_DECONT</t>
+          <t>F-502 | Module_Declarative_Fluxuri.xlsx → MOD_DECONT | ❓ Î-32</t>
         </is>
       </c>
       <c r="G56" s="61" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1888,7 +1888,7 @@
     <row r="117">
       <c r="A117" s="61" t="inlineStr">
         <is>
-          <t>intrebari-formator.md / .html — cele 27 întrebări rămase deschise (din 40: 13 verificate cu temei legal, 9 decizii de cabinet), grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
+          <t>intrebari-formator.md / .html — cele 32 întrebări rămase deschise (din 45: 13 verificate cu temei legal, 9 decizii de cabinet), grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6091,65 +6091,65 @@
       </c>
       <c r="C40" s="61" t="inlineStr">
         <is>
+          <t>Există un plafon de sold de casă separat, de 500.000 lei, pentru magazinele de tip cash &amp; carry, supermagazine și hipermagazine?</t>
+        </is>
+      </c>
+      <c r="D40" s="61" t="inlineStr">
+        <is>
+          <t>C-38</t>
+        </is>
+      </c>
+      <c r="E40" s="61" t="inlineStr">
+        <is>
+          <t>C-38, care azi are un singur prag. Dacă se confirmă, corelația are nevoie de un al doilea prag, după tipul unității — iar la un client cu magazin mare, pragul de 50.000 ar fi semnalat greșit ca depășire în fiecare zi.</t>
+        </is>
+      </c>
+      <c r="F40" s="61" t="inlineStr">
+        <is>
+          <t>Cifra e plauzibilă: un hipermarket trece de 50.000 lei într-o oră de vârf, iar depunerea zilnică a excedentului ar fi impracticabilă. Dar plauzibil nu e verificat, iar eu n-am confirmat-o pe textul legii — deci C-38 a rămas cu un singur prag și cu întrebarea marcată.</t>
+        </is>
+      </c>
+      <c r="G40" s="61" t="inlineStr">
+        <is>
+          <t>training 28.08.2026, punctul 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="61" t="inlineStr">
+        <is>
+          <t>Î-32</t>
+        </is>
+      </c>
+      <c r="B41" s="61" t="inlineStr">
+        <is>
+          <t>Trezorerie — diferențe de curs și plafoane</t>
+        </is>
+      </c>
+      <c r="C41" s="61" t="inlineStr">
+        <is>
           <t>Reevaluarea de sfârșit de lună a conturilor în valută se înregistrează pe 665/765 sau pe 668/768?</t>
         </is>
       </c>
-      <c r="D40" s="61" t="inlineStr">
+      <c r="D41" s="61" t="inlineStr">
         <is>
           <t>F-107
 MOD_CREDIT_VALUTA</t>
         </is>
       </c>
-      <c r="E40" s="61" t="inlineStr">
+      <c r="E41" s="61" t="inlineStr">
         <is>
           <t>F-107 pasul de reevaluare, MOD_CREDIT_VALUTA în întregime, și structura analitică a lui 665/765. Nu e nuanță de stil: cele două variante pun aceeași sumă în conturi care se raportează diferit.</t>
         </is>
       </c>
-      <c r="F40" s="61" t="inlineStr">
+      <c r="F41" s="61" t="inlineStr">
         <is>
           <t>Am păstrat 665/765 pentru ambele situații, cu analitic .DEC și .REV. Motivul: funcțiunea contului 665 din OMFP 1802/2014 include explicit diferențele rezultate „la sfârșitul lunii/exercițiului financiar, din evaluarea disponibilităților bancare și a numerarului în valută” — deci reevaluarea e chiar în funcțiunea lui. Iar 668/768 au alt rost: creanțele și datoriile exprimate în LEI, decontabile după cursul unei valute. Scopul formatorului — reevaluarea separată de decontare — se atinge cu analiticul, fără să mute reevaluarea în afara contului de diferențe de curs. Dacă formatorul confirmă varianta lui, se schimbă; dar atunci trebuie explicat cum se raportează diferențele de curs care nu mai sunt în contul lor.</t>
         </is>
       </c>
-      <c r="G40" s="61" t="inlineStr">
+      <c r="G41" s="61" t="inlineStr">
         <is>
           <t>training 28.08.2026, punctul 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="61" t="inlineStr">
-        <is>
-          <t>Î-32</t>
-        </is>
-      </c>
-      <c r="B41" s="61" t="inlineStr">
-        <is>
-          <t>Trezorerie — diferențe de curs și plafoane</t>
-        </is>
-      </c>
-      <c r="C41" s="61" t="inlineStr">
-        <is>
-          <t>Plafonul de 50.000 lei la soldul de casă e per societate sau per casierie / punct de lucru?</t>
-        </is>
-      </c>
-      <c r="D41" s="61" t="inlineStr">
-        <is>
-          <t>C-38</t>
-        </is>
-      </c>
-      <c r="E41" s="61" t="inlineStr">
-        <is>
-          <t>C-38 și cadența pe 5311. Dacă limita e per societate, o a doua casierie nu rezolvă nimic și clientul e în neregulă; dacă e per casierie, orice societate poate multiplica plafonul deschizând puncte de lucru, ceea ce ar goli restricția de sens.</t>
-        </is>
-      </c>
-      <c r="F41" s="61" t="inlineStr">
-        <is>
-          <t>Am formulat C-38 pe casierie, cum spun notițele, dar cu semnalul „casierie deschisă special ca să se multiplice plafonul” trecut la SUSPECT — pentru că intenția se vede, indiferent cum e textul. De confirmat art. 4 din Legea 70/2015 în forma în vigoare.</t>
-        </is>
-      </c>
-      <c r="G41" s="61" t="inlineStr">
-        <is>
-          <t>training 28.08.2026, punctul 2</t>
         </is>
       </c>
     </row>
@@ -6161,32 +6161,32 @@
       </c>
       <c r="B42" s="61" t="inlineStr">
         <is>
-          <t>Gestiuni, bonuri de consum și compensări</t>
+          <t>Trezorerie — diferențe de curs și plafoane</t>
         </is>
       </c>
       <c r="C42" s="61" t="inlineStr">
         <is>
-          <t>Care e forma obligatorie a bonului de consum, și în ce cazuri poate fi înlocuit cu alt document?</t>
+          <t>Plafonul de 50.000 lei la soldul de casă e per societate sau per casierie / punct de lucru?</t>
         </is>
       </c>
       <c r="D42" s="61" t="inlineStr">
         <is>
-          <t>F-321</t>
+          <t>C-38</t>
         </is>
       </c>
       <c r="E42" s="61" t="inlineStr">
         <is>
-          <t>F-321 pasul 3 și regula „consumul trece prin gestiune” din documentul de stocuri. De forma documentului depinde ce i se cere clientului să aducă lunar — iar cerința se face o dată, la preluare, sau nu se mai face.</t>
+          <t>C-38 și cadența pe 5311. Dacă limita e per societate, o a doua casierie nu rezolvă nimic și clientul e în neregulă; dacă e per casierie, orice societate poate multiplica plafonul deschizând puncte de lucru, ceea ce ar goli restricția de sens.</t>
         </is>
       </c>
       <c r="F42" s="61" t="inlineStr">
         <is>
-          <t>Am modelat consumul pe bon de consum, fără să afirm o formă anume. Alternativele de verificat: fișa limită de consum la consumuri repetitive, și avizul intern la transferurile între gestiuni.</t>
+          <t>Am formulat C-38 pe casierie, cum spun notițele, dar cu semnalul „casierie deschisă special ca să se multiplice plafonul” trecut la SUSPECT — pentru că intenția se vede, indiferent cum e textul. De confirmat art. 4 din Legea 70/2015 în forma în vigoare.</t>
         </is>
       </c>
       <c r="G42" s="61" t="inlineStr">
         <is>
-          <t>training 28.08.2026, punctul 3</t>
+          <t>training 28.08.2026, punctul 2</t>
         </is>
       </c>
     </row>
@@ -6198,32 +6198,32 @@
       </c>
       <c r="B43" s="61" t="inlineStr">
         <is>
-          <t>Gestiuni, bonuri de consum și compensări</t>
+          <t>Trezorerie — convenții de înregistrare</t>
         </is>
       </c>
       <c r="C43" s="61" t="inlineStr">
         <is>
-          <t>Ce document susține compensarea 4091 ↔ 419 la același partener, și de la ce prag trebuie făcută prin sistemul reglementat?</t>
+          <t>Dobânda de plătit trece obligatoriu prin 5186, sau `666 = 5121` direct e acceptat în cabinet?</t>
         </is>
       </c>
       <c r="D43" s="61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-505</t>
         </is>
       </c>
       <c r="E43" s="61" t="inlineStr">
         <is>
-          <t>Dacă apare un flux de compensare, el are nevoie de documentul justificativ ca stare inițială. Fără el, compensarea e o decizie unilaterală asupra unor solduri care aparțin la două raporturi juridice diferite.</t>
+          <t>F-505 arată ambele căi, deci cine îl citește nu află care se folosește. Consecința practică e la verificare: cu 5186, dobânda datorată și neplătită se vede în balanță; direct pe 666, nu se vede deloc până la plată.</t>
         </is>
       </c>
       <c r="F43" s="61" t="inlineStr">
         <is>
-          <t>Analiza e în documentul de control, §9.4: compensarea e posibilă, dar cere acord scris între părți, iar TVA-ul NU se compensează odată cu avansurile — regularizarea lui se face la facturile finale, prin stornarea fiecărui avans în parte. N-am scris flux, pentru că starea inițială depinde de răspuns.</t>
+          <t>Am scris fluxul cu 5186 ca variantă principală, pentru că păstrează vizibilă datoria, și am notat varianta directă ca alternativă acceptată. Dacă cabinetul are altă convenție, F-505 se ajustează.</t>
         </is>
       </c>
       <c r="G43" s="61" t="inlineStr">
         <is>
-          <t>training 28.08.2026, punctul 4</t>
+          <t>training 28.08.2026, punctul 5</t>
         </is>
       </c>
     </row>
@@ -6235,32 +6235,32 @@
       </c>
       <c r="B44" s="61" t="inlineStr">
         <is>
-          <t>Dividende — CASS, declarații și termene</t>
+          <t>Trezorerie — convenții de înregistrare</t>
         </is>
       </c>
       <c r="C44" s="61" t="inlineStr">
         <is>
-          <t>CASS pe dividende se datorează la dividendele DISTRIBUITE sau la cele efectiv RIDICATE?</t>
+          <t>Ce documentație face diferența, la un control, între „rate contractuale” și fragmentarea unei plăți?</t>
         </is>
       </c>
       <c r="D44" s="61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C-38</t>
         </is>
       </c>
       <c r="E44" s="61" t="inlineStr">
         <is>
-          <t>Momentul în care se naște obligația de CASS și, prin el, ce arată Declarația Unică față de soldul lui 457. Un 457 cu sold creditor la 31.12 înseamnă dividende distribuite și neridicate: dacă baza CASS e distribuirea, obligația există deja; dacă e ridicarea, nu.</t>
+          <t>C-38 și secțiunea de plafoane din documentul de control. Diferența dintre legal și amendabil stă în ce poți arăta, nu în ce ai făcut.</t>
         </is>
       </c>
       <c r="F44" s="61" t="inlineStr">
         <is>
-          <t>Am urmat notițele — baza e ridicarea — pentru că le confirmă structura declarației (două rubrici înseamnă două momente). Locul de verificat e art. 170 din Codul fiscal, care descrie ce venituri intră în baza anuală; n-am putut-o confirma pe sursă publică, deci rămâne întrebare, nu răspuns. Contrastul cu impozitul e clar și el e sigur: impozitul de 16% se datorează la DISTRIBUIRE, cu termen 25.01, indiferent de ridicare.</t>
+          <t>Am scris în document că apărarea cade dacă ratele se încasează la alte date sau în alte sume decât scadențarul. Ce nu știu e dacă se cere contract cu dată certă, sau dacă e de ajuns unul sub semnătură privată.</t>
         </is>
       </c>
       <c r="G44" s="61" t="inlineStr">
         <is>
-          <t>training 26.08.2026, punctul 2</t>
+          <t>training 28.08.2026, punctul 6</t>
         </is>
       </c>
     </row>
@@ -6272,200 +6272,385 @@
       </c>
       <c r="B45" s="61" t="inlineStr">
         <is>
+          <t>Trezorerie — convenții de înregistrare</t>
+        </is>
+      </c>
+      <c r="C45" s="61" t="inlineStr">
+        <is>
+          <t>Consumabilele auto nestocate — lichid de parbriz, aditivi — merg pe 6022 împreună cu combustibilul, sau pe 604?</t>
+        </is>
+      </c>
+      <c r="D45" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="61" t="inlineStr">
+        <is>
+          <t>Convenția de înregistrare pe bonurile mixte, care apar lunar la orice firmă cu mașini. Fără o regulă fixată, același bon se înregistrează diferit de la o lună la alta, iar rulajul lui 6022 nu mai spune nimic despre consumul de combustibil.</t>
+        </is>
+      </c>
+      <c r="F45" s="61" t="inlineStr">
+        <is>
+          <t>Am scris în document criteriul general — se stochează sau nu — care duce lichidul spre 604. Dar formatorul spune explicit că e alegere de firmă, deci convenția trebuie fixată de cabinet, nu dedusă de mine.</t>
+        </is>
+      </c>
+      <c r="G45" s="61" t="inlineStr">
+        <is>
+          <t>training 28.08.2026, punctul 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="61" t="inlineStr">
+        <is>
+          <t>Î-37</t>
+        </is>
+      </c>
+      <c r="B46" s="61" t="inlineStr">
+        <is>
+          <t>Gestiuni, bonuri de consum și compensări</t>
+        </is>
+      </c>
+      <c r="C46" s="61" t="inlineStr">
+        <is>
+          <t>Care e monografia completă a răscumpărării de obligațiuni — preț de emisiune vs. preț de răscumpărare, primă sau discount, și curs valutar dacă emisiunea e în valută?</t>
+        </is>
+      </c>
+      <c r="D46" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="61" t="inlineStr">
+        <is>
+          <t>Documentul de trezorerie descrie distincția acțiuni/obligațiuni și conturile (505, 506, 161), dar nu are monografie. Fără cifre nu se poate scrie un flux care să treacă porțile 1 și 2.</t>
+        </is>
+      </c>
+      <c r="F46" s="61" t="inlineStr">
+        <is>
+          <t>Am scris distincția conceptuală și diferența 505 / 506, fără să inventez cifre. Fluxul se scrie când există un exemplu real.</t>
+        </is>
+      </c>
+      <c r="G46" s="61" t="inlineStr">
+        <is>
+          <t>training 28.08.2026, punctul 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="61" t="inlineStr">
+        <is>
+          <t>Î-38</t>
+        </is>
+      </c>
+      <c r="B47" s="61" t="inlineStr">
+        <is>
+          <t>Gestiuni, bonuri de consum și compensări</t>
+        </is>
+      </c>
+      <c r="C47" s="61" t="inlineStr">
+        <is>
+          <t>Care e forma obligatorie a bonului de consum, și în ce cazuri poate fi înlocuit cu alt document?</t>
+        </is>
+      </c>
+      <c r="D47" s="61" t="inlineStr">
+        <is>
+          <t>F-321</t>
+        </is>
+      </c>
+      <c r="E47" s="61" t="inlineStr">
+        <is>
+          <t>F-321 pasul 3 și regula „consumul trece prin gestiune” din documentul de stocuri. De forma documentului depinde ce i se cere clientului să aducă lunar — iar cerința se face o dată, la preluare, sau nu se mai face.</t>
+        </is>
+      </c>
+      <c r="F47" s="61" t="inlineStr">
+        <is>
+          <t>Am modelat consumul pe bon de consum, fără să afirm o formă anume. Alternativele de verificat: fișa limită de consum la consumuri repetitive, și avizul intern la transferurile între gestiuni.</t>
+        </is>
+      </c>
+      <c r="G47" s="61" t="inlineStr">
+        <is>
+          <t>training 28.08.2026, punctul 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="61" t="inlineStr">
+        <is>
+          <t>Î-39</t>
+        </is>
+      </c>
+      <c r="B48" s="61" t="inlineStr">
+        <is>
+          <t>Gestiuni, bonuri de consum și compensări</t>
+        </is>
+      </c>
+      <c r="C48" s="61" t="inlineStr">
+        <is>
+          <t>Ce document susține compensarea 4091 ↔ 419 la același partener, și de la ce prag trebuie făcută prin sistemul reglementat?</t>
+        </is>
+      </c>
+      <c r="D48" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="61" t="inlineStr">
+        <is>
+          <t>Dacă apare un flux de compensare, el are nevoie de documentul justificativ ca stare inițială. Fără el, compensarea e o decizie unilaterală asupra unor solduri care aparțin la două raporturi juridice diferite.</t>
+        </is>
+      </c>
+      <c r="F48" s="61" t="inlineStr">
+        <is>
+          <t>Analiza e în documentul de control, §9.4: compensarea e posibilă, dar cere acord scris între părți, iar TVA-ul NU se compensează odată cu avansurile — regularizarea lui se face la facturile finale, prin stornarea fiecărui avans în parte. N-am scris flux, pentru că starea inițială depinde de răspuns.</t>
+        </is>
+      </c>
+      <c r="G48" s="61" t="inlineStr">
+        <is>
+          <t>training 28.08.2026, punctul 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="61" t="inlineStr">
+        <is>
+          <t>Î-40</t>
+        </is>
+      </c>
+      <c r="B49" s="61" t="inlineStr">
+        <is>
+          <t>Dividende — CASS, declarații și termene</t>
+        </is>
+      </c>
+      <c r="C49" s="61" t="inlineStr">
+        <is>
+          <t>CASS pe dividende se datorează la dividendele DISTRIBUITE sau la cele efectiv RIDICATE?</t>
+        </is>
+      </c>
+      <c r="D49" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="61" t="inlineStr">
+        <is>
+          <t>Momentul în care se naște obligația de CASS și, prin el, ce arată Declarația Unică față de soldul lui 457. Un 457 cu sold creditor la 31.12 înseamnă dividende distribuite și neridicate: dacă baza CASS e distribuirea, obligația există deja; dacă e ridicarea, nu.</t>
+        </is>
+      </c>
+      <c r="F49" s="61" t="inlineStr">
+        <is>
+          <t>Am urmat notițele — baza e ridicarea — pentru că le confirmă structura declarației (două rubrici înseamnă două momente). Locul de verificat e art. 170 din Codul fiscal, care descrie ce venituri intră în baza anuală; n-am putut-o confirma pe sursă publică, deci rămâne întrebare, nu răspuns. Contrastul cu impozitul e clar și el e sigur: impozitul de 16% se datorează la DISTRIBUIRE, cu termen 25.01, indiferent de ridicare.</t>
+        </is>
+      </c>
+      <c r="G49" s="61" t="inlineStr">
+        <is>
+          <t>training 26.08.2026, punctul 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="61" t="inlineStr">
+        <is>
+          <t>Î-41</t>
+        </is>
+      </c>
+      <c r="B50" s="61" t="inlineStr">
+        <is>
           <t>Acte de control — 4423 sau 4481</t>
         </is>
       </c>
-      <c r="C45" s="61" t="inlineStr">
+      <c r="C50" s="61" t="inlineStr">
         <is>
           <t>Sumele stabilite prin decizie de impunere pe TVA se înregistrează în 4423 cu analitic distinct, sau în 4481?</t>
         </is>
       </c>
-      <c r="D45" s="61" t="inlineStr">
+      <c r="D50" s="61" t="inlineStr">
         <is>
           <t>F-421
 C-29
 C-33</t>
         </is>
       </c>
-      <c r="E45" s="61" t="inlineStr">
+      <c r="E50" s="61" t="inlineStr">
         <is>
           <t>F-421 în întregime, corelațiile C-29 și C-33, și structura analitică a lui 4423. Nu e o nuanță de stil: cele două variante dau solduri diferite pe contul pe care decontul de TVA îl reconciliază.</t>
         </is>
       </c>
-      <c r="F45" s="61" t="inlineStr">
+      <c r="F50" s="61" t="inlineStr">
         <is>
           <t>Am adoptat varianta din 26.08, pentru că e singura care dă un motiv verificabil: un analitic separă EVIDENȚA, dar nu separă SOLDUL, iar decontul se compară pe soldul sintetic al lui 4423. F-421 e rescris pe 4481, cu ❓ pe el. Dacă formatorul confirmă varianta din 21.08, fluxul se întoarce — dar atunci trebuie explicat cum rămâne corelația decont ↔ balanță valabilă, pentru că azi nu văd cum.</t>
         </is>
       </c>
-      <c r="G45" s="61" t="inlineStr">
+      <c r="G50" s="61" t="inlineStr">
         <is>
           <t>training 26.08.2026, punctul 3</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="61" t="inlineStr">
-        <is>
-          <t>Î-37</t>
-        </is>
-      </c>
-      <c r="B46" s="61" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="61" t="inlineStr">
+        <is>
+          <t>Î-42</t>
+        </is>
+      </c>
+      <c r="B51" s="61" t="inlineStr">
         <is>
           <t>Microîntreprindere — prag și cotă</t>
         </is>
       </c>
-      <c r="C46" s="61" t="inlineStr">
+      <c r="C51" s="61" t="inlineStr">
         <is>
           <t>Care sunt pragul de venituri și cota de impozit pentru microîntreprinderi, în vigoare la data operațiunii?</t>
         </is>
       </c>
-      <c r="D46" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E46" s="61" t="inlineStr">
+      <c r="D51" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="61" t="inlineStr">
         <is>
           <t>Fluxul de impozit micro (698 = 4418) și avertizarea clientului care se apropie de prag. Trecerea se face din trimestrul depășirii, deci un prag greșit înseamnă o declarație greșită, nu doar o estimare.</t>
         </is>
       </c>
-      <c r="F46" s="61" t="inlineStr">
+      <c r="F51" s="61" t="inlineStr">
         <is>
           <t>Am folosit 100.000 EUR și 1% ca în notițe, marcate ❓.</t>
         </is>
       </c>
-      <c r="G46" s="61" t="inlineStr">
+      <c r="G51" s="61" t="inlineStr">
         <is>
           <t>training 21.08.2026, punctul 2</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="61" t="inlineStr">
-        <is>
-          <t>Î-38</t>
-        </is>
-      </c>
-      <c r="B47" s="61" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="61" t="inlineStr">
+        <is>
+          <t>Î-43</t>
+        </is>
+      </c>
+      <c r="B52" s="61" t="inlineStr">
         <is>
           <t>Decontul de TVA și fișa de rol</t>
         </is>
       </c>
-      <c r="C47" s="61" t="inlineStr">
+      <c r="C52" s="61" t="inlineStr">
         <is>
           <t>Ce rânduri din D300 sunt preluate în fișa de rol: 36 și 37, sau 44 și 45?</t>
         </is>
       </c>
-      <c r="D47" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="61" t="inlineStr">
+      <c r="D52" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="61" t="inlineStr">
         <is>
           <t>Corelația decont ↔ fișă de rol ↔ balanță. Fără numerele corecte, corelația nu se poate scrie ca formulă, ci doar descrie.</t>
         </is>
       </c>
-      <c r="F47" s="61" t="inlineStr">
+      <c r="F52" s="61" t="inlineStr">
         <is>
           <t>Am scris corelația pe SOLD, care nu depinde de numerotarea rândurilor, și am marcat rândurile ca deschise.</t>
         </is>
       </c>
-      <c r="G47" s="61" t="inlineStr">
+      <c r="G52" s="61" t="inlineStr">
         <is>
           <t>training 21.08.2026, punctul 5</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="61" t="inlineStr">
-        <is>
-          <t>Î-39</t>
-        </is>
-      </c>
-      <c r="B48" s="61" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="61" t="inlineStr">
+        <is>
+          <t>Î-44</t>
+        </is>
+      </c>
+      <c r="B53" s="61" t="inlineStr">
         <is>
           <t>Decontul de TVA și fișa de rol</t>
         </is>
       </c>
-      <c r="C48" s="61" t="inlineStr">
+      <c r="C53" s="61" t="inlineStr">
         <is>
           <t>La declarațiile care admit rectificare, contează ordinea cronologică a înregistrării facturilor la redepunere?</t>
         </is>
       </c>
-      <c r="D48" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E48" s="61" t="inlineStr">
+      <c r="D53" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="61" t="inlineStr">
         <is>
           <t>Procedura de corecție după depunere, pe toate declarațiile care admit rectificativă. Decontul de TVA nu admite, deci acolo întrebarea nu se pune — dar la celelalte, da.</t>
         </is>
       </c>
-      <c r="F48" s="61" t="inlineStr">
+      <c r="F53" s="61" t="inlineStr">
         <is>
           <t>N-am implementat nimic pe presupunerea asta.</t>
         </is>
       </c>
-      <c r="G48" s="61" t="inlineStr">
+      <c r="G53" s="61" t="inlineStr">
         <is>
           <t>training 21.08.2026, punctul 6</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="61" t="inlineStr">
-        <is>
-          <t>Î-40</t>
-        </is>
-      </c>
-      <c r="B49" s="61" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="61" t="inlineStr">
+        <is>
+          <t>Î-45</t>
+        </is>
+      </c>
+      <c r="B54" s="61" t="inlineStr">
         <is>
           <t>Decontul de TVA și fișa de rol</t>
         </is>
       </c>
-      <c r="C49" s="61" t="inlineStr">
+      <c r="C54" s="61" t="inlineStr">
         <is>
           <t>Care sunt corelațiile complete între D300 și fișa de rol la TVA?</t>
         </is>
       </c>
-      <c r="D49" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="61" t="inlineStr">
+      <c r="D54" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="61" t="inlineStr">
         <is>
           <t>Corelațiile de control pe TVA. Ce avem acum se verifică pe sold; corelația pe rulaj, rând cu rând, are nevoie de structura exactă a fișei de rol.</t>
         </is>
       </c>
-      <c r="F49" s="61" t="inlineStr">
+      <c r="F54" s="61" t="inlineStr">
         <is>
           <t>Am scris corelația pe sold și am lăsat-o pe cea pe rulaj ca gol declarat — n-am fișă de rol de citit.</t>
         </is>
       </c>
-      <c r="G49" s="61" t="inlineStr">
+      <c r="G54" s="61" t="inlineStr">
         <is>
           <t>training 21.08.2026, punctul 7</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="63" t="inlineStr">
-        <is>
-          <t>40 de întrebări, 22 teme. Aceeași sursă cu dist/intrebari-formator.md și cu pagina publicată — nu pot diverge.</t>
+    <row r="56">
+      <c r="A56" s="63" t="inlineStr">
+        <is>
+          <t>45 de întrebări, 23 teme. Aceeași sursă cu dist/intrebari-formator.md și cu pagina publicată — nu pot diverge.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A56:G56"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18409,13 +18594,29 @@
           <t>Trezorerie</t>
         </is>
       </c>
-      <c r="F183" s="20" t="n"/>
-      <c r="G183" s="20" t="inlineStr"/>
-      <c r="H183" s="20" t="inlineStr"/>
-      <c r="I183" s="20" t="inlineStr"/>
+      <c r="F183" s="20" t="inlineStr">
+        <is>
+          <t>Investiție pe termen SCURT, cumpărată ca plasament. ⚠ Nu se confundă cu 261, care poartă aceeași denumire în plan: ce le deosebește nu e emitentul, e INTENȚIA de deținere. Participația durabilă merge la imobilizări financiare — 261 afiliate / 263 controlate în comun / 265 alte titluri. Intenția nu se citește din denumire, se declară la achiziție.</t>
+        </is>
+      </c>
+      <c r="G183" s="20" t="inlineStr">
+        <is>
+          <t>501 pe fiecare societate emitentă</t>
+        </is>
+      </c>
+      <c r="H183" s="20" t="inlineStr">
+        <is>
+          <t>C O</t>
+        </is>
+      </c>
+      <c r="I183" s="20" t="inlineStr">
+        <is>
+          <t>F-503</t>
+        </is>
+      </c>
       <c r="J183" s="20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B — A</t>
         </is>
       </c>
     </row>
@@ -31307,7 +31508,7 @@
       </c>
       <c r="H17" s="69" t="inlineStr">
         <is>
-          <t>Pas revelator: reevaluarea LUNARĂ a soldului, nu doar diferența la plată | modul: MOD_CREDIT_VALUTA | ❓ Î-31</t>
+          <t>Pas revelator: reevaluarea LUNARĂ a soldului, nu doar diferența la plată | modul: MOD_CREDIT_VALUTA | ❓ Î-32</t>
         </is>
       </c>
     </row>
@@ -33086,7 +33287,7 @@
       </c>
       <c r="H63" s="69" t="inlineStr">
         <is>
-          <t>⚠ Notițele scriau perechea lui 608 ca `308`. E transpoziție de cifre: 381 e contul de ambalaje, iar 308 e „Diferențe de preț la materii prime” — un cont rectificativ, nu o gestiune de consumat. | ❓ Î-33</t>
+          <t>⚠ Notițele scriau perechea lui 608 ca `308`. E transpoziție de cifre: 381 e contul de ambalaje, iar 308 e „Diferențe de preț la materii prime” — un cont rectificativ, nu o gestiune de consumat. | ❓ Î-38</t>
         </is>
       </c>
     </row>
@@ -33933,7 +34134,7 @@
       </c>
       <c r="H85" s="69" t="inlineStr">
         <is>
-          <t>Sumele stabilite prin decizie de impunere NU ajung niciodată în decontul de TVA. ❓ Notițele din 21.08 spun „4423 cu analitic distinct”, cele din 26.08 spun 4481 — vezi principiul și întrebarea din listă. | ❓ Î-36</t>
+          <t>Sumele stabilite prin decizie de impunere NU ajung niciodată în decontul de TVA. ❓ Notițele din 21.08 spun „4423 cu analitic distinct”, cele din 26.08 spun 4481 — vezi principiul și întrebarea din listă. | ❓ Î-41</t>
         </is>
       </c>
     </row>
@@ -34340,7 +34541,7 @@
       </c>
       <c r="H96" s="69" t="inlineStr">
         <is>
-          <t>Distincția nu e de stil: 471 înseamnă „știu suma ȘI știu perioada”.</t>
+          <t>Distincția nu e de stil: 471 înseamnă „știu suma ȘI știu perioada”. | ❓ Î-34</t>
         </is>
       </c>
     </row>
@@ -60421,7 +60622,7 @@
       </c>
       <c r="F47" s="61" t="inlineStr">
         <is>
-          <t>F-405, F-407, F-421 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_TVA | ❓ Î-36</t>
+          <t>F-405, F-407, F-421 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_TVA | ❓ Î-41</t>
         </is>
       </c>
       <c r="G47" s="61" t="inlineStr">
@@ -60596,7 +60797,7 @@
       </c>
       <c r="F51" s="61" t="inlineStr">
         <is>
-          <t>F-421, F-424 | ❓ Î-36</t>
+          <t>F-421, F-424 | ❓ Î-41</t>
         </is>
       </c>
       <c r="G51" s="61" t="inlineStr">
@@ -60816,7 +61017,7 @@
       </c>
       <c r="F56" s="61" t="inlineStr">
         <is>
-          <t>F-502 | Module_Declarative_Fluxuri.xlsx → MOD_DECONT | ❓ Î-32</t>
+          <t>F-502 | Module_Declarative_Fluxuri.xlsx → MOD_DECONT | ❓ Î-31, Î-33, Î-35</t>
         </is>
       </c>
       <c r="G56" s="61" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1888,7 +1888,7 @@
     <row r="117">
       <c r="A117" s="61" t="inlineStr">
         <is>
-          <t>intrebari-formator.md / .html — cele 32 întrebări rămase deschise (din 45: 13 verificate cu temei legal, 9 decizii de cabinet), grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
+          <t>intrebari-formator.md / .html — cele 33 întrebări rămase deschise (din 46: 13 verificate cu temei legal, 9 decizii de cabinet), grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="C41" s="61" t="inlineStr">
         <is>
-          <t>Reevaluarea de sfârșit de lună a conturilor în valută se înregistrează pe 665/765 sau pe 668/768?</t>
+          <t>Care e articolul din OMFP 1802/2014 care spune că elementele NEMONETARE (inclusiv avansurile în valută) nu se reevaluează la cursul de închidere?</t>
         </is>
       </c>
       <c r="D41" s="61" t="inlineStr">
@@ -6139,17 +6139,17 @@
       </c>
       <c r="E41" s="61" t="inlineStr">
         <is>
-          <t>F-107 pasul de reevaluare, MOD_CREDIT_VALUTA în întregime, și structura analitică a lui 665/765. Nu e nuanță de stil: cele două variante pun aceeași sumă în conturi care se raportează diferit.</t>
+          <t>F-107 și MOD_CREDIT_VALUTA: dacă un avans în valută ar fi reevaluat, ar produce diferențe de curs pe un cont care n-are ce diferență să genereze. Regula e scrisă în §4.1 al documentului de trezorerie ca ➕.</t>
         </is>
       </c>
       <c r="F41" s="61" t="inlineStr">
         <is>
-          <t>Am păstrat 665/765 pentru ambele situații, cu analitic .DEC și .REV. Motivul: funcțiunea contului 665 din OMFP 1802/2014 include explicit diferențele rezultate „la sfârșitul lunii/exercițiului financiar, din evaluarea disponibilităților bancare și a numerarului în valută” — deci reevaluarea e chiar în funcțiunea lui. Iar 668/768 au alt rost: creanțele și datoriile exprimate în LEI, decontabile după cursul unei valute. Scopul formatorului — reevaluarea separată de decontare — se atinge cu analiticul, fără să mute reevaluarea în afara contului de diferențe de curs. Dacă formatorul confirmă varianta lui, se schimbă; dar atunci trebuie explicat cum se raportează diferențele de curs care nu mai sunt în contul lor.</t>
+          <t>Regula e fermă și o pot motiva — un avans dă dreptul la un bun, nu la o sumă, deci e nemonetar, iar reevaluarea privește doar monetarul. Ce n-am confirmat e articolul exact (probabil pct. 319 din OMFP 1802/2014, secțiunea de conversie a elementelor în valută) — de aceea rămâne întrebare, nu răspuns cu temei.</t>
         </is>
       </c>
       <c r="G41" s="61" t="inlineStr">
         <is>
-          <t>training 28.08.2026, punctul 1</t>
+          <t>training 28.08.2026, punctul 10</t>
         </is>
       </c>
     </row>
@@ -6166,27 +6166,28 @@
       </c>
       <c r="C42" s="61" t="inlineStr">
         <is>
-          <t>Plafonul de 50.000 lei la soldul de casă e per societate sau per casierie / punct de lucru?</t>
+          <t>Reevaluarea de sfârșit de lună a conturilor în valută se înregistrează pe 665/765 sau pe 668/768?</t>
         </is>
       </c>
       <c r="D42" s="61" t="inlineStr">
         <is>
-          <t>C-38</t>
+          <t>F-107
+MOD_CREDIT_VALUTA</t>
         </is>
       </c>
       <c r="E42" s="61" t="inlineStr">
         <is>
-          <t>C-38 și cadența pe 5311. Dacă limita e per societate, o a doua casierie nu rezolvă nimic și clientul e în neregulă; dacă e per casierie, orice societate poate multiplica plafonul deschizând puncte de lucru, ceea ce ar goli restricția de sens.</t>
+          <t>F-107 pasul de reevaluare, MOD_CREDIT_VALUTA în întregime, și structura analitică a lui 665/765. Nu e nuanță de stil: cele două variante pun aceeași sumă în conturi care se raportează diferit.</t>
         </is>
       </c>
       <c r="F42" s="61" t="inlineStr">
         <is>
-          <t>Am formulat C-38 pe casierie, cum spun notițele, dar cu semnalul „casierie deschisă special ca să se multiplice plafonul” trecut la SUSPECT — pentru că intenția se vede, indiferent cum e textul. De confirmat art. 4 din Legea 70/2015 în forma în vigoare.</t>
+          <t>Am păstrat 665/765 pentru ambele situații, cu analitic .DEC și .REV. Motivul: funcțiunea contului 665 din OMFP 1802/2014 include explicit diferențele rezultate „la sfârșitul lunii/exercițiului financiar, din evaluarea disponibilităților bancare și a numerarului în valută” — deci reevaluarea e chiar în funcțiunea lui. Iar 668/768 au alt rost: creanțele și datoriile exprimate în LEI, decontabile după cursul unei valute. Scopul formatorului — reevaluarea separată de decontare — se atinge cu analiticul, fără să mute reevaluarea în afara contului de diferențe de curs. Dacă formatorul confirmă varianta lui, se schimbă; dar atunci trebuie explicat cum se raportează diferențele de curs care nu mai sunt în contul lor.</t>
         </is>
       </c>
       <c r="G42" s="61" t="inlineStr">
         <is>
-          <t>training 28.08.2026, punctul 2</t>
+          <t>training 28.08.2026, punctul 1</t>
         </is>
       </c>
     </row>
@@ -6198,32 +6199,32 @@
       </c>
       <c r="B43" s="61" t="inlineStr">
         <is>
-          <t>Trezorerie — convenții de înregistrare</t>
+          <t>Trezorerie — diferențe de curs și plafoane</t>
         </is>
       </c>
       <c r="C43" s="61" t="inlineStr">
         <is>
-          <t>Dobânda de plătit trece obligatoriu prin 5186, sau `666 = 5121` direct e acceptat în cabinet?</t>
+          <t>Plafonul de 50.000 lei la soldul de casă e per societate sau per casierie / punct de lucru?</t>
         </is>
       </c>
       <c r="D43" s="61" t="inlineStr">
         <is>
-          <t>F-505</t>
+          <t>C-38</t>
         </is>
       </c>
       <c r="E43" s="61" t="inlineStr">
         <is>
-          <t>F-505 arată ambele căi, deci cine îl citește nu află care se folosește. Consecința practică e la verificare: cu 5186, dobânda datorată și neplătită se vede în balanță; direct pe 666, nu se vede deloc până la plată.</t>
+          <t>C-38 și cadența pe 5311. Dacă limita e per societate, o a doua casierie nu rezolvă nimic și clientul e în neregulă; dacă e per casierie, orice societate poate multiplica plafonul deschizând puncte de lucru, ceea ce ar goli restricția de sens.</t>
         </is>
       </c>
       <c r="F43" s="61" t="inlineStr">
         <is>
-          <t>Am scris fluxul cu 5186 ca variantă principală, pentru că păstrează vizibilă datoria, și am notat varianta directă ca alternativă acceptată. Dacă cabinetul are altă convenție, F-505 se ajustează.</t>
+          <t>Am formulat C-38 pe casierie, cum spun notițele, dar cu semnalul „casierie deschisă special ca să se multiplice plafonul” trecut la SUSPECT — pentru că intenția se vede, indiferent cum e textul. De confirmat art. 4 din Legea 70/2015 în forma în vigoare.</t>
         </is>
       </c>
       <c r="G43" s="61" t="inlineStr">
         <is>
-          <t>training 28.08.2026, punctul 5</t>
+          <t>training 28.08.2026, punctul 2</t>
         </is>
       </c>
     </row>
@@ -6240,27 +6241,27 @@
       </c>
       <c r="C44" s="61" t="inlineStr">
         <is>
-          <t>Ce documentație face diferența, la un control, între „rate contractuale” și fragmentarea unei plăți?</t>
+          <t>Dobânda de plătit trece obligatoriu prin 5186, sau `666 = 5121` direct e acceptat în cabinet?</t>
         </is>
       </c>
       <c r="D44" s="61" t="inlineStr">
         <is>
-          <t>C-38</t>
+          <t>F-505</t>
         </is>
       </c>
       <c r="E44" s="61" t="inlineStr">
         <is>
-          <t>C-38 și secțiunea de plafoane din documentul de control. Diferența dintre legal și amendabil stă în ce poți arăta, nu în ce ai făcut.</t>
+          <t>F-505 arată ambele căi, deci cine îl citește nu află care se folosește. Consecința practică e la verificare: cu 5186, dobânda datorată și neplătită se vede în balanță; direct pe 666, nu se vede deloc până la plată.</t>
         </is>
       </c>
       <c r="F44" s="61" t="inlineStr">
         <is>
-          <t>Am scris în document că apărarea cade dacă ratele se încasează la alte date sau în alte sume decât scadențarul. Ce nu știu e dacă se cere contract cu dată certă, sau dacă e de ajuns unul sub semnătură privată.</t>
+          <t>Am scris fluxul cu 5186 ca variantă principală, pentru că păstrează vizibilă datoria, și am notat varianta directă ca alternativă acceptată. Dacă cabinetul are altă convenție, F-505 se ajustează.</t>
         </is>
       </c>
       <c r="G44" s="61" t="inlineStr">
         <is>
-          <t>training 28.08.2026, punctul 6</t>
+          <t>training 28.08.2026, punctul 5</t>
         </is>
       </c>
     </row>
@@ -6277,27 +6278,27 @@
       </c>
       <c r="C45" s="61" t="inlineStr">
         <is>
-          <t>Consumabilele auto nestocate — lichid de parbriz, aditivi — merg pe 6022 împreună cu combustibilul, sau pe 604?</t>
+          <t>Ce documentație face diferența, la un control, între „rate contractuale” și fragmentarea unei plăți?</t>
         </is>
       </c>
       <c r="D45" s="61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C-38</t>
         </is>
       </c>
       <c r="E45" s="61" t="inlineStr">
         <is>
-          <t>Convenția de înregistrare pe bonurile mixte, care apar lunar la orice firmă cu mașini. Fără o regulă fixată, același bon se înregistrează diferit de la o lună la alta, iar rulajul lui 6022 nu mai spune nimic despre consumul de combustibil.</t>
+          <t>C-38 și secțiunea de plafoane din documentul de control. Diferența dintre legal și amendabil stă în ce poți arăta, nu în ce ai făcut.</t>
         </is>
       </c>
       <c r="F45" s="61" t="inlineStr">
         <is>
-          <t>Am scris în document criteriul general — se stochează sau nu — care duce lichidul spre 604. Dar formatorul spune explicit că e alegere de firmă, deci convenția trebuie fixată de cabinet, nu dedusă de mine.</t>
+          <t>Am scris în document că apărarea cade dacă ratele se încasează la alte date sau în alte sume decât scadențarul. Ce nu știu e dacă se cere contract cu dată certă, sau dacă e de ajuns unul sub semnătură privată.</t>
         </is>
       </c>
       <c r="G45" s="61" t="inlineStr">
         <is>
-          <t>training 28.08.2026, punctul 7</t>
+          <t>training 28.08.2026, punctul 6</t>
         </is>
       </c>
     </row>
@@ -6309,12 +6310,12 @@
       </c>
       <c r="B46" s="61" t="inlineStr">
         <is>
-          <t>Gestiuni, bonuri de consum și compensări</t>
+          <t>Trezorerie — convenții de înregistrare</t>
         </is>
       </c>
       <c r="C46" s="61" t="inlineStr">
         <is>
-          <t>Care e monografia completă a răscumpărării de obligațiuni — preț de emisiune vs. preț de răscumpărare, primă sau discount, și curs valutar dacă emisiunea e în valută?</t>
+          <t>Consumabilele auto nestocate — lichid de parbriz, aditivi — merg pe 6022 împreună cu combustibilul, sau pe 604?</t>
         </is>
       </c>
       <c r="D46" s="61" t="inlineStr">
@@ -6324,17 +6325,17 @@
       </c>
       <c r="E46" s="61" t="inlineStr">
         <is>
-          <t>Documentul de trezorerie descrie distincția acțiuni/obligațiuni și conturile (505, 506, 161), dar nu are monografie. Fără cifre nu se poate scrie un flux care să treacă porțile 1 și 2.</t>
+          <t>Convenția de înregistrare pe bonurile mixte, care apar lunar la orice firmă cu mașini. Fără o regulă fixată, același bon se înregistrează diferit de la o lună la alta, iar rulajul lui 6022 nu mai spune nimic despre consumul de combustibil.</t>
         </is>
       </c>
       <c r="F46" s="61" t="inlineStr">
         <is>
-          <t>Am scris distincția conceptuală și diferența 505 / 506, fără să inventez cifre. Fluxul se scrie când există un exemplu real.</t>
+          <t>Am scris în document criteriul general — se stochează sau nu — care duce lichidul spre 604. Dar formatorul spune explicit că e alegere de firmă, deci convenția trebuie fixată de cabinet, nu dedusă de mine.</t>
         </is>
       </c>
       <c r="G46" s="61" t="inlineStr">
         <is>
-          <t>training 28.08.2026, punctul 9</t>
+          <t>training 28.08.2026, punctul 7</t>
         </is>
       </c>
     </row>
@@ -6351,27 +6352,27 @@
       </c>
       <c r="C47" s="61" t="inlineStr">
         <is>
-          <t>Care e forma obligatorie a bonului de consum, și în ce cazuri poate fi înlocuit cu alt document?</t>
+          <t>Care e monografia completă a răscumpărării de obligațiuni — preț de emisiune vs. preț de răscumpărare, primă sau discount, și curs valutar dacă emisiunea e în valută?</t>
         </is>
       </c>
       <c r="D47" s="61" t="inlineStr">
         <is>
-          <t>F-321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E47" s="61" t="inlineStr">
         <is>
-          <t>F-321 pasul 3 și regula „consumul trece prin gestiune” din documentul de stocuri. De forma documentului depinde ce i se cere clientului să aducă lunar — iar cerința se face o dată, la preluare, sau nu se mai face.</t>
+          <t>Documentul de trezorerie descrie distincția acțiuni/obligațiuni și conturile (505, 506, 161), dar nu are monografie. Fără cifre nu se poate scrie un flux care să treacă porțile 1 și 2.</t>
         </is>
       </c>
       <c r="F47" s="61" t="inlineStr">
         <is>
-          <t>Am modelat consumul pe bon de consum, fără să afirm o formă anume. Alternativele de verificat: fișa limită de consum la consumuri repetitive, și avizul intern la transferurile între gestiuni.</t>
+          <t>Am scris distincția conceptuală și diferența 505 / 506, fără să inventez cifre. Fluxul se scrie când există un exemplu real.</t>
         </is>
       </c>
       <c r="G47" s="61" t="inlineStr">
         <is>
-          <t>training 28.08.2026, punctul 3</t>
+          <t>training 28.08.2026, punctul 9</t>
         </is>
       </c>
     </row>
@@ -6388,27 +6389,27 @@
       </c>
       <c r="C48" s="61" t="inlineStr">
         <is>
-          <t>Ce document susține compensarea 4091 ↔ 419 la același partener, și de la ce prag trebuie făcută prin sistemul reglementat?</t>
+          <t>Care e forma obligatorie a bonului de consum, și în ce cazuri poate fi înlocuit cu alt document?</t>
         </is>
       </c>
       <c r="D48" s="61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-321</t>
         </is>
       </c>
       <c r="E48" s="61" t="inlineStr">
         <is>
-          <t>Dacă apare un flux de compensare, el are nevoie de documentul justificativ ca stare inițială. Fără el, compensarea e o decizie unilaterală asupra unor solduri care aparțin la două raporturi juridice diferite.</t>
+          <t>F-321 pasul 3 și regula „consumul trece prin gestiune” din documentul de stocuri. De forma documentului depinde ce i se cere clientului să aducă lunar — iar cerința se face o dată, la preluare, sau nu se mai face.</t>
         </is>
       </c>
       <c r="F48" s="61" t="inlineStr">
         <is>
-          <t>Analiza e în documentul de control, §9.4: compensarea e posibilă, dar cere acord scris între părți, iar TVA-ul NU se compensează odată cu avansurile — regularizarea lui se face la facturile finale, prin stornarea fiecărui avans în parte. N-am scris flux, pentru că starea inițială depinde de răspuns.</t>
+          <t>Am modelat consumul pe bon de consum, fără să afirm o formă anume. Alternativele de verificat: fișa limită de consum la consumuri repetitive, și avizul intern la transferurile între gestiuni.</t>
         </is>
       </c>
       <c r="G48" s="61" t="inlineStr">
         <is>
-          <t>training 28.08.2026, punctul 4</t>
+          <t>training 28.08.2026, punctul 3</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6421,12 @@
       </c>
       <c r="B49" s="61" t="inlineStr">
         <is>
-          <t>Dividende — CASS, declarații și termene</t>
+          <t>Gestiuni, bonuri de consum și compensări</t>
         </is>
       </c>
       <c r="C49" s="61" t="inlineStr">
         <is>
-          <t>CASS pe dividende se datorează la dividendele DISTRIBUITE sau la cele efectiv RIDICATE?</t>
+          <t>Ce document susține compensarea 4091 ↔ 419 la același partener, și de la ce prag trebuie făcută prin sistemul reglementat?</t>
         </is>
       </c>
       <c r="D49" s="61" t="inlineStr">
@@ -6435,17 +6436,17 @@
       </c>
       <c r="E49" s="61" t="inlineStr">
         <is>
-          <t>Momentul în care se naște obligația de CASS și, prin el, ce arată Declarația Unică față de soldul lui 457. Un 457 cu sold creditor la 31.12 înseamnă dividende distribuite și neridicate: dacă baza CASS e distribuirea, obligația există deja; dacă e ridicarea, nu.</t>
+          <t>Dacă apare un flux de compensare, el are nevoie de documentul justificativ ca stare inițială. Fără el, compensarea e o decizie unilaterală asupra unor solduri care aparțin la două raporturi juridice diferite.</t>
         </is>
       </c>
       <c r="F49" s="61" t="inlineStr">
         <is>
-          <t>Am urmat notițele — baza e ridicarea — pentru că le confirmă structura declarației (două rubrici înseamnă două momente). Locul de verificat e art. 170 din Codul fiscal, care descrie ce venituri intră în baza anuală; n-am putut-o confirma pe sursă publică, deci rămâne întrebare, nu răspuns. Contrastul cu impozitul e clar și el e sigur: impozitul de 16% se datorează la DISTRIBUIRE, cu termen 25.01, indiferent de ridicare.</t>
+          <t>Analiza e în documentul de control, §9.4: compensarea e posibilă, dar cere acord scris între părți, iar TVA-ul NU se compensează odată cu avansurile — regularizarea lui se face la facturile finale, prin stornarea fiecărui avans în parte. N-am scris flux, pentru că starea inițială depinde de răspuns.</t>
         </is>
       </c>
       <c r="G49" s="61" t="inlineStr">
         <is>
-          <t>training 26.08.2026, punctul 2</t>
+          <t>training 28.08.2026, punctul 4</t>
         </is>
       </c>
     </row>
@@ -6457,71 +6458,71 @@
       </c>
       <c r="B50" s="61" t="inlineStr">
         <is>
+          <t>Dividende — CASS, declarații și termene</t>
+        </is>
+      </c>
+      <c r="C50" s="61" t="inlineStr">
+        <is>
+          <t>CASS pe dividende se datorează la dividendele DISTRIBUITE sau la cele efectiv RIDICATE?</t>
+        </is>
+      </c>
+      <c r="D50" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="61" t="inlineStr">
+        <is>
+          <t>Momentul în care se naște obligația de CASS și, prin el, ce arată Declarația Unică față de soldul lui 457. Un 457 cu sold creditor la 31.12 înseamnă dividende distribuite și neridicate: dacă baza CASS e distribuirea, obligația există deja; dacă e ridicarea, nu.</t>
+        </is>
+      </c>
+      <c r="F50" s="61" t="inlineStr">
+        <is>
+          <t>Am urmat notițele — baza e ridicarea — pentru că le confirmă structura declarației (două rubrici înseamnă două momente). Locul de verificat e art. 170 din Codul fiscal, care descrie ce venituri intră în baza anuală; n-am putut-o confirma pe sursă publică, deci rămâne întrebare, nu răspuns. Contrastul cu impozitul e clar și el e sigur: impozitul de 16% se datorează la DISTRIBUIRE, cu termen 25.01, indiferent de ridicare.</t>
+        </is>
+      </c>
+      <c r="G50" s="61" t="inlineStr">
+        <is>
+          <t>training 26.08.2026, punctul 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="61" t="inlineStr">
+        <is>
+          <t>Î-42</t>
+        </is>
+      </c>
+      <c r="B51" s="61" t="inlineStr">
+        <is>
           <t>Acte de control — 4423 sau 4481</t>
         </is>
       </c>
-      <c r="C50" s="61" t="inlineStr">
+      <c r="C51" s="61" t="inlineStr">
         <is>
           <t>Sumele stabilite prin decizie de impunere pe TVA se înregistrează în 4423 cu analitic distinct, sau în 4481?</t>
         </is>
       </c>
-      <c r="D50" s="61" t="inlineStr">
+      <c r="D51" s="61" t="inlineStr">
         <is>
           <t>F-421
 C-29
 C-33</t>
         </is>
       </c>
-      <c r="E50" s="61" t="inlineStr">
+      <c r="E51" s="61" t="inlineStr">
         <is>
           <t>F-421 în întregime, corelațiile C-29 și C-33, și structura analitică a lui 4423. Nu e o nuanță de stil: cele două variante dau solduri diferite pe contul pe care decontul de TVA îl reconciliază.</t>
         </is>
       </c>
-      <c r="F50" s="61" t="inlineStr">
+      <c r="F51" s="61" t="inlineStr">
         <is>
           <t>Am adoptat varianta din 26.08, pentru că e singura care dă un motiv verificabil: un analitic separă EVIDENȚA, dar nu separă SOLDUL, iar decontul se compară pe soldul sintetic al lui 4423. F-421 e rescris pe 4481, cu ❓ pe el. Dacă formatorul confirmă varianta din 21.08, fluxul se întoarce — dar atunci trebuie explicat cum rămâne corelația decont ↔ balanță valabilă, pentru că azi nu văd cum.</t>
         </is>
       </c>
-      <c r="G50" s="61" t="inlineStr">
+      <c r="G51" s="61" t="inlineStr">
         <is>
           <t>training 26.08.2026, punctul 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="61" t="inlineStr">
-        <is>
-          <t>Î-42</t>
-        </is>
-      </c>
-      <c r="B51" s="61" t="inlineStr">
-        <is>
-          <t>Microîntreprindere — prag și cotă</t>
-        </is>
-      </c>
-      <c r="C51" s="61" t="inlineStr">
-        <is>
-          <t>Care sunt pragul de venituri și cota de impozit pentru microîntreprinderi, în vigoare la data operațiunii?</t>
-        </is>
-      </c>
-      <c r="D51" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E51" s="61" t="inlineStr">
-        <is>
-          <t>Fluxul de impozit micro (698 = 4418) și avertizarea clientului care se apropie de prag. Trecerea se face din trimestrul depășirii, deci un prag greșit înseamnă o declarație greșită, nu doar o estimare.</t>
-        </is>
-      </c>
-      <c r="F51" s="61" t="inlineStr">
-        <is>
-          <t>Am folosit 100.000 EUR și 1% ca în notițe, marcate ❓.</t>
-        </is>
-      </c>
-      <c r="G51" s="61" t="inlineStr">
-        <is>
-          <t>training 21.08.2026, punctul 2</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6534,12 @@
       </c>
       <c r="B52" s="61" t="inlineStr">
         <is>
-          <t>Decontul de TVA și fișa de rol</t>
+          <t>Microîntreprindere — prag și cotă</t>
         </is>
       </c>
       <c r="C52" s="61" t="inlineStr">
         <is>
-          <t>Ce rânduri din D300 sunt preluate în fișa de rol: 36 și 37, sau 44 și 45?</t>
+          <t>Care sunt pragul de venituri și cota de impozit pentru microîntreprinderi, în vigoare la data operațiunii?</t>
         </is>
       </c>
       <c r="D52" s="61" t="inlineStr">
@@ -6548,17 +6549,17 @@
       </c>
       <c r="E52" s="61" t="inlineStr">
         <is>
-          <t>Corelația decont ↔ fișă de rol ↔ balanță. Fără numerele corecte, corelația nu se poate scrie ca formulă, ci doar descrie.</t>
+          <t>Fluxul de impozit micro (698 = 4418) și avertizarea clientului care se apropie de prag. Trecerea se face din trimestrul depășirii, deci un prag greșit înseamnă o declarație greșită, nu doar o estimare.</t>
         </is>
       </c>
       <c r="F52" s="61" t="inlineStr">
         <is>
-          <t>Am scris corelația pe SOLD, care nu depinde de numerotarea rândurilor, și am marcat rândurile ca deschise.</t>
+          <t>Am folosit 100.000 EUR și 1% ca în notițe, marcate ❓.</t>
         </is>
       </c>
       <c r="G52" s="61" t="inlineStr">
         <is>
-          <t>training 21.08.2026, punctul 5</t>
+          <t>training 21.08.2026, punctul 2</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6576,7 @@
       </c>
       <c r="C53" s="61" t="inlineStr">
         <is>
-          <t>La declarațiile care admit rectificare, contează ordinea cronologică a înregistrării facturilor la redepunere?</t>
+          <t>Ce rânduri din D300 sunt preluate în fișa de rol: 36 și 37, sau 44 și 45?</t>
         </is>
       </c>
       <c r="D53" s="61" t="inlineStr">
@@ -6585,17 +6586,17 @@
       </c>
       <c r="E53" s="61" t="inlineStr">
         <is>
-          <t>Procedura de corecție după depunere, pe toate declarațiile care admit rectificativă. Decontul de TVA nu admite, deci acolo întrebarea nu se pune — dar la celelalte, da.</t>
+          <t>Corelația decont ↔ fișă de rol ↔ balanță. Fără numerele corecte, corelația nu se poate scrie ca formulă, ci doar descrie.</t>
         </is>
       </c>
       <c r="F53" s="61" t="inlineStr">
         <is>
-          <t>N-am implementat nimic pe presupunerea asta.</t>
+          <t>Am scris corelația pe SOLD, care nu depinde de numerotarea rândurilor, și am marcat rândurile ca deschise.</t>
         </is>
       </c>
       <c r="G53" s="61" t="inlineStr">
         <is>
-          <t>training 21.08.2026, punctul 6</t>
+          <t>training 21.08.2026, punctul 5</t>
         </is>
       </c>
     </row>
@@ -6612,45 +6613,82 @@
       </c>
       <c r="C54" s="61" t="inlineStr">
         <is>
+          <t>La declarațiile care admit rectificare, contează ordinea cronologică a înregistrării facturilor la redepunere?</t>
+        </is>
+      </c>
+      <c r="D54" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="61" t="inlineStr">
+        <is>
+          <t>Procedura de corecție după depunere, pe toate declarațiile care admit rectificativă. Decontul de TVA nu admite, deci acolo întrebarea nu se pune — dar la celelalte, da.</t>
+        </is>
+      </c>
+      <c r="F54" s="61" t="inlineStr">
+        <is>
+          <t>N-am implementat nimic pe presupunerea asta.</t>
+        </is>
+      </c>
+      <c r="G54" s="61" t="inlineStr">
+        <is>
+          <t>training 21.08.2026, punctul 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="61" t="inlineStr">
+        <is>
+          <t>Î-46</t>
+        </is>
+      </c>
+      <c r="B55" s="61" t="inlineStr">
+        <is>
+          <t>Decontul de TVA și fișa de rol</t>
+        </is>
+      </c>
+      <c r="C55" s="61" t="inlineStr">
+        <is>
           <t>Care sunt corelațiile complete între D300 și fișa de rol la TVA?</t>
         </is>
       </c>
-      <c r="D54" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E54" s="61" t="inlineStr">
+      <c r="D55" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="61" t="inlineStr">
         <is>
           <t>Corelațiile de control pe TVA. Ce avem acum se verifică pe sold; corelația pe rulaj, rând cu rând, are nevoie de structura exactă a fișei de rol.</t>
         </is>
       </c>
-      <c r="F54" s="61" t="inlineStr">
+      <c r="F55" s="61" t="inlineStr">
         <is>
           <t>Am scris corelația pe sold și am lăsat-o pe cea pe rulaj ca gol declarat — n-am fișă de rol de citit.</t>
         </is>
       </c>
-      <c r="G54" s="61" t="inlineStr">
+      <c r="G55" s="61" t="inlineStr">
         <is>
           <t>training 21.08.2026, punctul 7</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="63" t="inlineStr">
-        <is>
-          <t>45 de întrebări, 23 teme. Aceeași sursă cu dist/intrebari-formator.md și cu pagina publicată — nu pot diverge.</t>
+    <row r="57">
+      <c r="A57" s="63" t="inlineStr">
+        <is>
+          <t>46 de întrebări, 23 teme. Aceeași sursă cu dist/intrebari-formator.md și cu pagina publicată — nu pot diverge.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A56:G56"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A57:G57"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13200,7 +13238,7 @@
       </c>
       <c r="F47" s="22" t="inlineStr">
         <is>
-          <t>Ca 32x, dar pt. imobilizări: bun facturat, nerecepționat.</t>
+          <t>Ca 32x, dar pt. imobilizări: bun facturat, nerecepționat. — Cont de TRANZIT, nu de avans: ține mijlocul fix facturat dar nerecepționat, până intră în 213. ⚠ Nu se confundă cu avansurile pentru imobilizări — acelea sunt 232 (corporale) și 234 (necorporale), sau 4093/4094 după plan. O revizuire paralelă îl dădea drept „avans pentru necorporale”; e o confuzie de prevenit.</t>
         </is>
       </c>
       <c r="G47" s="22" t="inlineStr">
@@ -30521,7 +30559,7 @@
       </c>
       <c r="F59" s="66" t="inlineStr">
         <is>
-          <t>Două momente: la plată și la reevaluarea lunară a soldului (ultima zi bancară). | ❓ Notițele din 28.08 cer conturi DIFERITE — 668/768 pentru reevaluare. Funcțiunea lui 665 din OMFP 1802/2014 include însă explicit evaluarea de la sfârșitul lunii a disponibilităților în valută. Scopul formatorului e corect și se atinge cu analiticul de aici, fără să mute reevaluarea în afara contului de diferențe de curs.</t>
+          <t>Două momente: la plată și la reevaluarea lunară a soldului (ultima zi bancară). | ❓ Notițele din 28.08 cer conturi DIFERITE — 668/768 pentru reevaluare. Funcțiunea lui 665 din OMFP 1802/2014 include însă explicit evaluarea de la sfârșitul lunii a disponibilităților în valută. Scopul formatorului e corect și se atinge cu analiticul de aici, fără să mute reevaluarea în afara contului de diferențe de curs. Se reevaluează doar elementele MONETARE: avansurile în valută sunt nemonetare (dau dreptul la un bun, nu la bani), deci rămân la cursul plății și nu produc rulaj pe niciun analitic .REV.</t>
         </is>
       </c>
       <c r="G59" s="66" t="inlineStr">
@@ -31508,7 +31546,7 @@
       </c>
       <c r="H17" s="69" t="inlineStr">
         <is>
-          <t>Pas revelator: reevaluarea LUNARĂ a soldului, nu doar diferența la plată | modul: MOD_CREDIT_VALUTA | ❓ Î-32</t>
+          <t>Pas revelator: reevaluarea LUNARĂ a soldului, nu doar diferența la plată | modul: MOD_CREDIT_VALUTA | ❓ Î-32, Î-33</t>
         </is>
       </c>
     </row>
@@ -33287,7 +33325,7 @@
       </c>
       <c r="H63" s="69" t="inlineStr">
         <is>
-          <t>⚠ Notițele scriau perechea lui 608 ca `308`. E transpoziție de cifre: 381 e contul de ambalaje, iar 308 e „Diferențe de preț la materii prime” — un cont rectificativ, nu o gestiune de consumat. | ❓ Î-38</t>
+          <t>⚠ Notițele scriau perechea lui 608 ca `308`. E transpoziție de cifre: 381 e contul de ambalaje, iar 308 e „Diferențe de preț la materii prime” — un cont rectificativ, nu o gestiune de consumat. | ❓ Î-39</t>
         </is>
       </c>
     </row>
@@ -34134,7 +34172,7 @@
       </c>
       <c r="H85" s="69" t="inlineStr">
         <is>
-          <t>Sumele stabilite prin decizie de impunere NU ajung niciodată în decontul de TVA. ❓ Notițele din 21.08 spun „4423 cu analitic distinct”, cele din 26.08 spun 4481 — vezi principiul și întrebarea din listă. | ❓ Î-41</t>
+          <t>Sumele stabilite prin decizie de impunere NU ajung niciodată în decontul de TVA. ❓ Notițele din 21.08 spun „4423 cu analitic distinct”, cele din 26.08 spun 4481 — vezi principiul și întrebarea din listă. | ❓ Î-42</t>
         </is>
       </c>
     </row>
@@ -34541,7 +34579,7 @@
       </c>
       <c r="H96" s="69" t="inlineStr">
         <is>
-          <t>Distincția nu e de stil: 471 înseamnă „știu suma ȘI știu perioada”. | ❓ Î-34</t>
+          <t>Distincția nu e de stil: 471 înseamnă „știu suma ȘI știu perioada”. | ❓ Î-35</t>
         </is>
       </c>
     </row>
@@ -60622,7 +60660,7 @@
       </c>
       <c r="F47" s="61" t="inlineStr">
         <is>
-          <t>F-405, F-407, F-421 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_TVA | ❓ Î-41</t>
+          <t>F-405, F-407, F-421 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_TVA | ❓ Î-42</t>
         </is>
       </c>
       <c r="G47" s="61" t="inlineStr">
@@ -60797,7 +60835,7 @@
       </c>
       <c r="F51" s="61" t="inlineStr">
         <is>
-          <t>F-421, F-424 | ❓ Î-41</t>
+          <t>F-421, F-424 | ❓ Î-42</t>
         </is>
       </c>
       <c r="G51" s="61" t="inlineStr">
@@ -61017,7 +61055,7 @@
       </c>
       <c r="F56" s="61" t="inlineStr">
         <is>
-          <t>F-502 | Module_Declarative_Fluxuri.xlsx → MOD_DECONT | ❓ Î-31, Î-33, Î-35</t>
+          <t>F-502 | Module_Declarative_Fluxuri.xlsx → MOD_DECONT | ❓ Î-31, Î-34, Î-36</t>
         </is>
       </c>
       <c r="G56" s="61" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1888,7 +1888,7 @@
     <row r="117">
       <c r="A117" s="61" t="inlineStr">
         <is>
-          <t>intrebari-formator.md / .html — cele 33 întrebări rămase deschise (din 46: 13 verificate cu temei legal, 9 decizii de cabinet), grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
+          <t>intrebari-formator.md / .html — cele 20 întrebări rămase deschise (din 46: 26 verificate cu temei legal, 7 decizii de cabinet), grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
         </is>
       </c>
     </row>
@@ -56541,7 +56541,7 @@
       </c>
       <c r="D812" s="71" t="inlineStr">
         <is>
-          <t>Reținerea din drepturile salariale. ❓ Imputația nu se poate face fără ca salariatul să fie informat și de acord (Codul muncii), iar notițele menționează un plafon „la nivelul a 5 salarii medii”, cu observația formatorului „de verificat suma”.</t>
+          <t>Reținerea din drepturile salariale. Imputația nu se poate face fără ca salariatul să fie informat și de acord (Codul muncii art. 254). Plafonul recuperării de comun acord e 5 salarii MINIME brute pe economie — verificat pe Codul muncii art. 254; notița spunea „5 salarii medii”, ceea ce era greșit. Peste plafon sau fără acord, doar prin instanță; reținerea efectivă e limitată la o treime din net (art. 169).</t>
         </is>
       </c>
       <c r="E812" s="71" t="inlineStr">

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -11566,7 +11566,7 @@
     <row r="32">
       <c r="A32" s="33" t="inlineStr">
         <is>
-          <t>2. Pe corelație: Corelații de control → C-01…C-39 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
+          <t>2. Pe corelație: Corelații de control → C-01…C-42 → fluxuri + module ancorate (calea către Module_Declarative…).</t>
         </is>
       </c>
     </row>
@@ -57926,7 +57926,7 @@
       </c>
       <c r="D846" s="71" t="inlineStr">
         <is>
-          <t>Sold 462 analitic = 0 și sold 446 analitic = 0 la finalul lunii. Analiticul pe 462 e obligatoriu, nu ornament: dacă în contract sunt doi proprietari — soț și soție — fiecare are CNP-ul lui, iar D205 se depune pe CNP până în ultima zi a lui februarie. Un sold care persistă pe 462 înseamnă chirie datorată și neplătită, nu o eroare de operare.</t>
+          <t>Sold 462 = 0 și sold 446 = 0 la finalul lunii, pe fiecare analitic. Analiticul pe 462 e obligatoriu, nu ornament: dacă în contract sunt doi proprietari — soț și soție — fiecare are CNP-ul lui, iar D205 se depune pe CNP până în ultima zi a lui februarie. Un sold care persistă pe 462 înseamnă chirie datorată și neplătită, nu o eroare de operare.</t>
         </is>
       </c>
       <c r="E846" s="71" t="inlineStr">
@@ -61137,7 +61137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -62944,6 +62944,136 @@
       <c r="G57" s="61" t="inlineStr">
         <is>
           <t>Înaltă — eroarea nu se vede în luna preluării, ci la prima verificare pe rulaj, când nu mai știe nimeni de unde vine</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="61" t="inlineStr">
+        <is>
+          <t>C-40</t>
+        </is>
+      </c>
+      <c r="B58" s="61" t="inlineStr">
+        <is>
+          <t>sold 441 din balanță = impozitul pe profit din D101
+  și = caseta de impozit pe profit din FIȘA PE PLĂTITOR</t>
+        </is>
+      </c>
+      <c r="C58" s="61" t="inlineStr">
+        <is>
+          <t>Balanța la 31.12 vs. D101 depusă vs. fișa pe plătitor de la ANAF</t>
+        </is>
+      </c>
+      <c r="D58" s="61" t="inlineStr">
+        <is>
+          <t>Diferență de rotunjire între lei și lei fără subdiviziuni, dacă
+  declarația se completează rotunjit.
+Sold debitor pe 4411 în cursul anului: e plata în plus rămasă după
+  un trimestru cu pierdere, care se absoarbe la regularizare (F-429).</t>
+        </is>
+      </c>
+      <c r="E58" s="61" t="inlineStr">
+        <is>
+          <t>Impozit declarat trimestru cu trimestru, ca și cum fiecare trimestru
+  ar fi un exercițiu separat: în T3 impozitul se calculează CUMULAT,
+  iar cine adună trimestrele plătește pe un profit pe care nu l-a avut.
+Sold 441 care nu iese cu D101: declarația e greșită, nu balanța.
+Cheltuiala 691 fără rulaj creditor într-un an cu trimestru pierdut:
+  semn că diminuarea cumulată n-a fost înregistrată deloc.</t>
+        </is>
+      </c>
+      <c r="F58" s="61" t="inlineStr">
+        <is>
+          <t>F-429, F-104 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_EX / MOD_CONTROL_BALANTA</t>
+        </is>
+      </c>
+      <c r="G58" s="61" t="inlineStr">
+        <is>
+          <t>Înaltă — se descoperă la control, cu accesorii pe toată perioada, iar reconstituirea cere refacerea tuturor trimestrelor</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="61" t="inlineStr">
+        <is>
+          <t>C-41</t>
+        </is>
+      </c>
+      <c r="B59" s="61" t="inlineStr">
+        <is>
+          <t>609 și 709 au rulaj pe sensul INVERS clasei lor:
+  609 (clasa 6) rulează în CREDIT · 709 (clasa 7) rulează în DEBIT</t>
+        </is>
+      </c>
+      <c r="C59" s="61" t="inlineStr">
+        <is>
+          <t>Fișa de cont / cartea mare, nu balanța</t>
+        </is>
+      </c>
+      <c r="D59" s="61" t="inlineStr">
+        <is>
+          <t>Storno de reducere acordată din greșeală, care readuce contul pe
+  sensul propriu clasei pentru o singură operațiune.</t>
+        </is>
+      </c>
+      <c r="E59" s="61" t="inlineStr">
+        <is>
+          <t>609 cu rulaj debitor, ca o cheltuială obișnuită: reducerea primită a
+  fost operată ca achiziție, deci cheltuiala e umflată de două ori.
+709 cu rulaj creditor: reducerea acordată a fost operată ca vânzare,
+  deci cifra de afaceri e umflată.</t>
+        </is>
+      </c>
+      <c r="F59" s="61" t="inlineStr">
+        <is>
+          <t>F-409</t>
+        </is>
+      </c>
+      <c r="G59" s="61" t="inlineStr">
+        <is>
+          <t>Medie — nu rupe balanța și nu se vede în sold, pentru că soldul net poate ascunde un rulaj greșit compensat de altul corect; de aceea verificarea se face pe fișă, unde fiecare mișcare are sensul ei</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="61" t="inlineStr">
+        <is>
+          <t>C-42</t>
+        </is>
+      </c>
+      <c r="B60" s="61" t="inlineStr">
+        <is>
+          <t>ACTIV NET din F10 = CAPITALURI PROPRII din F10
+  și imobilizările din F10 = imobilizările din F40</t>
+        </is>
+      </c>
+      <c r="C60" s="61" t="inlineStr">
+        <is>
+          <t>Bilanț: F10 (solduri) · F20 (cheltuieli, venituri, 121) · F30 (salariați) · F40 (imobilizări)</t>
+        </is>
+      </c>
+      <c r="D60" s="61" t="inlineStr">
+        <is>
+          <t>Nimic. Corelația e o identitate: dacă nu iese, e eroare, nu situație particulară.</t>
+        </is>
+      </c>
+      <c r="E60" s="61" t="inlineStr">
+        <is>
+          <t>Conturi cu soldul pe invers: în cazul ăsta bilanțul nu se generează
+  deloc — se repară întâi balanța (vezi C-23).
+Balanța modificată DUPĂ depunerea bilanțului: nu există bilant
+  rectificativ, iar diferența se explică în notele bilanțului următor.
+  La bănci se vede imediat: la creditare confruntă bilanțul cu balanța.</t>
+        </is>
+      </c>
+      <c r="F60" s="61" t="inlineStr">
+        <is>
+          <t>F-104 | Module_Declarative_Fluxuri.xlsx → MOD_INCHIDERE_EX / MOD_CONTROL_BALANTA</t>
+        </is>
+      </c>
+      <c r="G60" s="61" t="inlineStr">
+        <is>
+          <t>Înaltă — bilanțul depus nu se mai poate corecta, deci eroarea rămâne în evidența publică a firmei până la exercițiul următor</t>
         </is>
       </c>
     </row>
@@ -62969,7 +63099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -63491,7 +63621,7 @@
     <row r="21">
       <c r="A21" s="61" t="inlineStr">
         <is>
-          <t>5112 / 5113 Efecte de încasat</t>
+          <t>447 Fonduri speciale — taxe și vărsăminte asimilate</t>
         </is>
       </c>
       <c r="B21" s="61" t="inlineStr">
@@ -63501,17 +63631,17 @@
       </c>
       <c r="C21" s="61" t="inlineStr">
         <is>
-          <t>sold după scadență = efect neonorat, nu creanță curentă; se tratează ca atare, cu ajustare dacă e cazul (F-503)</t>
+          <t>fondul de handicap se constituie și se plătește lunar; sold rămas = obligație declarată și neachitată, iar ea nu apare pe vector, deci nimeni nu o reclamă până la control (F-427)</t>
         </is>
       </c>
       <c r="D21" s="61" t="inlineStr">
         <is>
-          <t>F-503 · F-504</t>
+          <t>F-427</t>
         </is>
       </c>
       <c r="E21" s="61" t="inlineStr">
         <is>
-          <t>Sold 4111 = 0 după pasul 2, sold 5112 = 0 după pasul 3 · Sold 5113 = 0, sold 5114 = 0 (9.680 + 2.420 = 12.100), sold 4111 = 0 încă din F-503</t>
+          <t>Sold 447 = 0 la finalul lunii, în ambele variante</t>
         </is>
       </c>
       <c r="F21" s="61" t="inlineStr">
@@ -63523,7 +63653,7 @@
     <row r="22">
       <c r="A22" s="61" t="inlineStr">
         <is>
-          <t>5114 Efecte remise spre scontare</t>
+          <t>5112 / 5113 Efecte de încasat</t>
         </is>
       </c>
       <c r="B22" s="61" t="inlineStr">
@@ -63533,17 +63663,17 @@
       </c>
       <c r="C22" s="61" t="inlineStr">
         <is>
-          <t>se închide în bani + cost, fără rest; sold rămas = scontare nefinalizată, cel mai probabil costul neînregistrat (F-504)</t>
+          <t>sold după scadență = efect neonorat, nu creanță curentă; se tratează ca atare, cu ajustare dacă e cazul (F-503)</t>
         </is>
       </c>
       <c r="D22" s="61" t="inlineStr">
         <is>
-          <t>F-504</t>
+          <t>F-503 · F-504</t>
         </is>
       </c>
       <c r="E22" s="61" t="inlineStr">
         <is>
-          <t>Sold 5113 = 0, sold 5114 = 0 (9.680 + 2.420 = 12.100), sold 4111 = 0 încă din F-503</t>
+          <t>Sold 4111 = 0 după pasul 2, sold 5112 = 0 după pasul 3 · Sold 5113 = 0, sold 5114 = 0 (9.680 + 2.420 = 12.100), sold 4111 = 0 încă din F-503</t>
         </is>
       </c>
       <c r="F22" s="61" t="inlineStr">
@@ -63555,110 +63685,110 @@
     <row r="23">
       <c r="A23" s="61" t="inlineStr">
         <is>
+          <t>5114 Efecte remise spre scontare</t>
+        </is>
+      </c>
+      <c r="B23" s="61" t="inlineStr">
+        <is>
+          <t>Lunar — obligatoriu</t>
+        </is>
+      </c>
+      <c r="C23" s="61" t="inlineStr">
+        <is>
+          <t>se închide în bani + cost, fără rest; sold rămas = scontare nefinalizată, cel mai probabil costul neînregistrat (F-504)</t>
+        </is>
+      </c>
+      <c r="D23" s="61" t="inlineStr">
+        <is>
+          <t>F-504</t>
+        </is>
+      </c>
+      <c r="E23" s="61" t="inlineStr">
+        <is>
+          <t>Sold 5113 = 0, sold 5114 = 0 (9.680 + 2.420 = 12.100), sold 4111 = 0 încă din F-503</t>
+        </is>
+      </c>
+      <c r="F23" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="61" t="inlineStr">
+        <is>
           <t>5328 Alte valori (tichete)</t>
         </is>
       </c>
-      <c r="B23" s="61" t="inlineStr">
+      <c r="B24" s="61" t="inlineStr">
         <is>
           <t>Lunar — obligatoriu</t>
         </is>
       </c>
-      <c r="C23" s="61" t="inlineStr">
+      <c r="C24" s="61" t="inlineStr">
         <is>
           <t>sold = tichete cumpărate și neacordate; la fiecare lună trecută devine mai greu de spus cui i se cuveneau (F-508)</t>
         </is>
       </c>
-      <c r="D23" s="61" t="inlineStr">
+      <c r="D24" s="61" t="inlineStr">
         <is>
           <t>F-508</t>
         </is>
       </c>
-      <c r="E23" s="61" t="inlineStr">
+      <c r="E24" s="61" t="inlineStr">
         <is>
           <t>Sold 5328 = 400 lei — tichete cumpărate și neacordate, care se acordă luna următoare</t>
         </is>
       </c>
-      <c r="F23" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="36" t="inlineStr">
+      <c r="F24" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>Cel puțin trimestrial</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="74" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="74" t="inlineStr">
         <is>
           <t>Cont</t>
         </is>
       </c>
-      <c r="B26" s="74" t="inlineStr">
+      <c r="B27" s="74" t="inlineStr">
         <is>
           <t>Cadență</t>
         </is>
       </c>
-      <c r="C26" s="74" t="inlineStr">
+      <c r="C27" s="74" t="inlineStr">
         <is>
           <t>De ce se urmărește</t>
         </is>
       </c>
-      <c r="D26" s="74" t="inlineStr">
+      <c r="D27" s="74" t="inlineStr">
         <is>
           <t>Flux</t>
         </is>
       </c>
-      <c r="E26" s="74" t="inlineStr">
+      <c r="E27" s="74" t="inlineStr">
         <is>
           <t>Stare terminală declarată</t>
         </is>
       </c>
-      <c r="F26" s="74" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>Gol cunoscut</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="61" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="B27" s="61" t="inlineStr">
-        <is>
-          <t>Cel puțin trimestrial</t>
-        </is>
-      </c>
-      <c r="C27" s="61" t="inlineStr">
-        <is>
-          <t>drepturi neridicate; dacă nu se golesc, se caută salariatul, nu se reportează</t>
-        </is>
-      </c>
-      <c r="D27" s="61" t="inlineStr">
-        <is>
-          <t>F-418</t>
-        </is>
-      </c>
-      <c r="E27" s="61" t="inlineStr">
-        <is>
-          <t>După reclasificare, sold 421 = restul de plată de pe statul curent, iar sold 426 = exact sumele nerevendicate</t>
-        </is>
-      </c>
-      <c r="F27" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="61" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>426</t>
         </is>
       </c>
       <c r="B28" s="61" t="inlineStr">
@@ -63668,17 +63798,17 @@
       </c>
       <c r="C28" s="61" t="inlineStr">
         <is>
-          <t>creanțe față de foști salariați; sold creditor = contrar naturii (C-23)</t>
+          <t>drepturi neridicate; dacă nu se golesc, se caută salariatul, nu se reportează</t>
         </is>
       </c>
       <c r="D28" s="61" t="inlineStr">
         <is>
-          <t>F-419</t>
+          <t>F-418</t>
         </is>
       </c>
       <c r="E28" s="61" t="inlineStr">
         <is>
-          <t>Sold 4282 = 0 după încasare</t>
+          <t>După reclasificare, sold 421 = restul de plată de pe statul curent, iar sold 426 = exact sumele nerevendicate</t>
         </is>
       </c>
       <c r="F28" s="61" t="inlineStr">
@@ -63690,199 +63820,199 @@
     <row r="29">
       <c r="A29" s="61" t="inlineStr">
         <is>
+          <t>4282</t>
+        </is>
+      </c>
+      <c r="B29" s="61" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C29" s="61" t="inlineStr">
+        <is>
+          <t>creanțe față de foști salariați; sold creditor = contrar naturii (C-23)</t>
+        </is>
+      </c>
+      <c r="D29" s="61" t="inlineStr">
+        <is>
+          <t>F-419</t>
+        </is>
+      </c>
+      <c r="E29" s="61" t="inlineStr">
+        <is>
+          <t>Sold 4282 = 0 după încasare</t>
+        </is>
+      </c>
+      <c r="F29" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="61" t="inlineStr">
+        <is>
           <t>4418</t>
         </is>
       </c>
-      <c r="B29" s="61" t="inlineStr">
+      <c r="B30" s="61" t="inlineStr">
         <is>
           <t>Cel puțin trimestrial</t>
         </is>
       </c>
-      <c r="C29" s="61" t="inlineStr">
+      <c r="C30" s="61" t="inlineStr">
         <is>
           <t>impozit micro; sold creditor = obligația trimestrului curent, sold debitor = plată în plus, de investigat</t>
         </is>
       </c>
-      <c r="D29" s="61" t="inlineStr">
+      <c r="D30" s="61" t="inlineStr">
         <is>
           <t>F-420</t>
         </is>
       </c>
-      <c r="E29" s="61" t="inlineStr">
+      <c r="E30" s="61" t="inlineStr">
         <is>
           <t>Sold 4418 creditor = impozitul trimestrului curent, nedatorat încă</t>
         </is>
       </c>
-      <c r="F29" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="75" t="inlineStr">
+      <c r="F30" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="75" t="inlineStr">
         <is>
           <t>4091 – 4094</t>
         </is>
       </c>
-      <c r="B30" s="75" t="inlineStr">
+      <c r="B31" s="75" t="inlineStr">
         <is>
           <t>Cel puțin trimestrial</t>
         </is>
       </c>
-      <c r="C30" s="75" t="inlineStr">
+      <c r="C31" s="75" t="inlineStr">
         <is>
           <t>avansuri care nu s-au stornat la factura finală</t>
         </is>
       </c>
-      <c r="D30" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="75" t="inlineStr">
+      <c r="D31" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="75" t="inlineStr">
         <is>
           <t>4091: F-410 declară starea lui 409 la nivel sintetic, nu pe analiticele de destinație 4091–4094. 4094: Idem 4093.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="61" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="61" t="inlineStr">
         <is>
           <t>419</t>
         </is>
       </c>
-      <c r="B31" s="61" t="inlineStr">
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t>Cel puțin trimestrial</t>
         </is>
       </c>
-      <c r="C31" s="61" t="inlineStr">
+      <c r="C32" s="61" t="inlineStr">
         <is>
           <t>avansuri de la clienți rămase deschise</t>
         </is>
       </c>
-      <c r="D31" s="61" t="inlineStr">
+      <c r="D32" s="61" t="inlineStr">
         <is>
           <t>F-410 · F-415</t>
         </is>
       </c>
-      <c r="E31" s="61" t="inlineStr">
+      <c r="E32" s="61" t="inlineStr">
         <is>
           <t>Sold 419=0, sold 409=0 după livrare/recepție · Sold 4111 = 0 pe partenerul respectiv; sold 419 = 4.132,23; TVA colectată suplimentar 867,77</t>
         </is>
       </c>
-      <c r="F31" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="75" t="inlineStr">
-        <is>
-          <t>401 / 411</t>
-        </is>
-      </c>
-      <c r="B32" s="75" t="inlineStr">
-        <is>
-          <t>Cel puțin trimestrial</t>
-        </is>
-      </c>
-      <c r="C32" s="75" t="inlineStr">
-        <is>
-          <t>balanță analitică; solduri cu semn contrar = eroare</t>
-        </is>
-      </c>
-      <c r="D32" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="75" t="inlineStr">
-        <is>
-          <t>401: Nu există flux care să declare „401 fără sold debitor”. Regula e o corelație de sold contrar naturii, nu o stare terminală de flux. 411: Idem 401 — vezi C-23.</t>
+      <c r="F32" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="75" t="inlineStr">
         <is>
+          <t>401 / 411</t>
+        </is>
+      </c>
+      <c r="B33" s="75" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C33" s="75" t="inlineStr">
+        <is>
+          <t>balanță analitică; solduri cu semn contrar = eroare</t>
+        </is>
+      </c>
+      <c r="D33" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="75" t="inlineStr">
+        <is>
+          <t>401: Nu există flux care să declare „401 fără sold debitor”. Regula e o corelație de sold contrar naturii, nu o stare terminală de flux. 411: Idem 401 — vezi C-23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="75" t="inlineStr">
+        <is>
           <t>455</t>
         </is>
       </c>
-      <c r="B33" s="75" t="inlineStr">
+      <c r="B34" s="75" t="inlineStr">
         <is>
           <t>Cel puțin trimestrial</t>
         </is>
       </c>
-      <c r="C33" s="75" t="inlineStr">
+      <c r="C34" s="75" t="inlineStr">
         <is>
           <t>sume datorate asociaților, cu restricții legale</t>
         </is>
       </c>
-      <c r="D33" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F33" s="75" t="inlineStr">
+      <c r="D34" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="75" t="inlineStr">
         <is>
           <t>455: Nu există flux pe 455. Restricțiile de numerar sunt rămase deschise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="61" t="inlineStr">
-        <is>
-          <t>461 / 462</t>
-        </is>
-      </c>
-      <c r="B34" s="61" t="inlineStr">
-        <is>
-          <t>Cel puțin trimestrial</t>
-        </is>
-      </c>
-      <c r="C34" s="61" t="inlineStr">
-        <is>
-          <t>debitori/creditori diverși, se împotmolesc ușor</t>
-        </is>
-      </c>
-      <c r="D34" s="61" t="inlineStr">
-        <is>
-          <t>F-425 · F-428</t>
-        </is>
-      </c>
-      <c r="E34" s="61" t="inlineStr">
-        <is>
-          <t>Sold 461 = 0 pe ambele analitice · Sold 462 analitic = 0 și sold 446 analitic = 0 la finalul lunii</t>
-        </is>
-      </c>
-      <c r="F34" s="61" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="61" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>461 / 462</t>
         </is>
       </c>
       <c r="B35" s="61" t="inlineStr">
@@ -63892,17 +64022,17 @@
       </c>
       <c r="C35" s="61" t="inlineStr">
         <is>
-          <t>imobilizări în curs care trebuiau puse în funcțiune</t>
+          <t>debitori/creditori diverși, se împotmolesc ușor</t>
         </is>
       </c>
       <c r="D35" s="61" t="inlineStr">
         <is>
-          <t>F-208</t>
+          <t>F-425 · F-428</t>
         </is>
       </c>
       <c r="E35" s="61" t="inlineStr">
         <is>
-          <t>Sold 231 = 0 după PV · Sold 231 = 0 după recepție</t>
+          <t>Sold 461 = 0 pe ambele analitice · Sold 462 = 0 și sold 446 = 0 la finalul lunii, pe fiecare analitic</t>
         </is>
       </c>
       <c r="F35" s="61" t="inlineStr">
@@ -63914,7 +64044,7 @@
     <row r="36">
       <c r="A36" s="61" t="inlineStr">
         <is>
-          <t>1621 / 5187</t>
+          <t>231</t>
         </is>
       </c>
       <c r="B36" s="61" t="inlineStr">
@@ -63924,17 +64054,17 @@
       </c>
       <c r="C36" s="61" t="inlineStr">
         <is>
-          <t>credite și dobânzi de calculat</t>
+          <t>imobilizări în curs care trebuiau puse în funcțiune</t>
         </is>
       </c>
       <c r="D36" s="61" t="inlineStr">
         <is>
-          <t>F-107 · F-506</t>
+          <t>F-208</t>
         </is>
       </c>
       <c r="E36" s="61" t="inlineStr">
         <is>
-          <t>Sold 1621 = 74.550 + 600 = 75.150 lei = 15.000 EUR × 5,0100 · Sold 5187 = 0, sold 472 = 0, Σ766 = 3.000</t>
+          <t>Sold 231 = 0 după PV · Sold 231 = 0 după recepție</t>
         </is>
       </c>
       <c r="F36" s="61" t="inlineStr">
@@ -63946,7 +64076,7 @@
     <row r="37">
       <c r="A37" s="61" t="inlineStr">
         <is>
-          <t>223 Instalații tehnice și mijloace de transport în curs de aprovizionare</t>
+          <t>1621 / 5187</t>
         </is>
       </c>
       <c r="B37" s="61" t="inlineStr">
@@ -63956,17 +64086,17 @@
       </c>
       <c r="C37" s="61" t="inlineStr">
         <is>
-          <t>tranzit pe imobilizări; sold ≠ 0 înseamnă recepție neînregistrată (F-207)</t>
+          <t>credite și dobânzi de calculat</t>
         </is>
       </c>
       <c r="D37" s="61" t="inlineStr">
         <is>
-          <t>F-207</t>
+          <t>F-107 · F-506</t>
         </is>
       </c>
       <c r="E37" s="61" t="inlineStr">
         <is>
-          <t>Sold 223 = 0 pe documentele cu recepție în perioadă</t>
+          <t>Sold 1621 = 74.550 + 600 = 75.150 lei = 15.000 EUR × 5,0100 · Sold 5187 = 0, sold 472 = 0, Σ766 = 3.000</t>
         </is>
       </c>
       <c r="F37" s="61" t="inlineStr">
@@ -63978,7 +64108,7 @@
     <row r="38">
       <c r="A38" s="61" t="inlineStr">
         <is>
-          <t>4481 Alte datorii față de bugetul statului</t>
+          <t>223 Instalații tehnice și mijloace de transport în curs de aprovizionare</t>
         </is>
       </c>
       <c r="B38" s="61" t="inlineStr">
@@ -63988,17 +64118,17 @@
       </c>
       <c r="C38" s="61" t="inlineStr">
         <is>
-          <t>datorii din decizii de impunere; sold purtat de la un an la altul = decizie neachitată sau neurmărită (F-421)</t>
+          <t>tranzit pe imobilizări; sold ≠ 0 înseamnă recepție neînregistrată (F-207)</t>
         </is>
       </c>
       <c r="D38" s="61" t="inlineStr">
         <is>
-          <t>F-421</t>
+          <t>F-207</t>
         </is>
       </c>
       <c r="E38" s="61" t="inlineStr">
         <is>
-          <t>Sold 4481 = 0 după plată</t>
+          <t>Sold 223 = 0 pe documentele cu recepție în perioadă</t>
         </is>
       </c>
       <c r="F38" s="61" t="inlineStr">
@@ -64010,30 +64140,94 @@
     <row r="39">
       <c r="A39" s="61" t="inlineStr">
         <is>
+          <t>4481 Alte datorii față de bugetul statului</t>
+        </is>
+      </c>
+      <c r="B39" s="61" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C39" s="61" t="inlineStr">
+        <is>
+          <t>datorii din decizii de impunere; sold purtat de la un an la altul = decizie neachitată sau neurmărită (F-421)</t>
+        </is>
+      </c>
+      <c r="D39" s="61" t="inlineStr">
+        <is>
+          <t>F-421</t>
+        </is>
+      </c>
+      <c r="E39" s="61" t="inlineStr">
+        <is>
+          <t>Sold 4481 = 0 după plată</t>
+        </is>
+      </c>
+      <c r="F39" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="61" t="inlineStr">
+        <is>
           <t>4482 Alte creanțe privind bugetul statului</t>
         </is>
       </c>
-      <c r="B39" s="61" t="inlineStr">
+      <c r="B40" s="61" t="inlineStr">
         <is>
           <t>Cel puțin trimestrial</t>
         </is>
       </c>
-      <c r="C39" s="61" t="inlineStr">
+      <c r="C40" s="61" t="inlineStr">
         <is>
           <t>plăți eronate în așteptare; soldul se disecă până la lămurire, nu se reportează (F-424)</t>
         </is>
       </c>
-      <c r="D39" s="61" t="inlineStr">
+      <c r="D40" s="61" t="inlineStr">
         <is>
           <t>F-424</t>
         </is>
       </c>
-      <c r="E39" s="61" t="inlineStr">
+      <c r="E40" s="61" t="inlineStr">
         <is>
           <t>Sold 4482 = 0 pe ambele analitice</t>
         </is>
       </c>
-      <c r="F39" s="61" t="inlineStr">
+      <c r="F40" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="61" t="inlineStr">
+        <is>
+          <t>4411 Impozitul pe profit</t>
+        </is>
+      </c>
+      <c r="B41" s="61" t="inlineStr">
+        <is>
+          <t>Cel puțin trimestrial</t>
+        </is>
+      </c>
+      <c r="C41" s="61" t="inlineStr">
+        <is>
+          <t>se recalculează CUMULAT la fiecare trimestru; soldul debitor e plată în plus, nu eroare, dar trebuie să se absoarbă la regularizarea următoare, altfel rămâne bani ai firmei la buget (F-429, C-40)</t>
+        </is>
+      </c>
+      <c r="D41" s="61" t="inlineStr">
+        <is>
+          <t>F-429</t>
+        </is>
+      </c>
+      <c r="E41" s="61" t="inlineStr">
+        <is>
+          <t>Σ691 = 16.000 − 6.400 + 14.400 = 24.000, adică exact 16% din profitul cumulat de 150.000</t>
+        </is>
+      </c>
+      <c r="F41" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -64044,8 +64238,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
+++ b/dist/Plan_de_conturi_ROL_Analitice_Fluxuri_SAGA.xlsx
@@ -1888,14 +1888,14 @@
     <row r="117">
       <c r="A117" s="61" t="inlineStr">
         <is>
-          <t>intrebari-formator.md / .html — cele 20 întrebări rămase deschise (din 46: 26 verificate cu temei legal, 7 decizii de cabinet), grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
+          <t>intrebari-formator.md / .html — cele 22 întrebări rămase deschise (din 48: 26 verificate cu temei legal, 7 decizii de cabinet), grupate pe temă contabilă. Aceeași sursă cu foaia „Întrebări deschise” de aici.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="61" t="inlineStr">
         <is>
-          <t>Cele 6 documente de studiu, în .md, .docx și .html: Capitaluri, credite, leasing și provizioane · Imobilizări · Stocuri, TVA și corelații de balanță · Salarii, contribuții și rețineri · Trezorerie: bancă, casă, efecte de încasat și avansuri · Control, documente și numerar. Titlurile sunt pe subiect contabil, nu pe ziua de training — cauți o regulă pe clasa contului, nu pe data când s-a predat.</t>
+          <t>Cele 7 documente de studiu, în .md, .docx și .html: Capitaluri, credite, leasing și provizioane · Imobilizări · Stocuri, TVA și corelații de balanță · Salarii, contribuții și rețineri · Trezorerie: bancă, casă, efecte de încasat și avansuri · Declarații, fișa pe plătitor și bilanțul · Control, documente și numerar. Titlurile sunt pe subiect contabil, nu pe ziua de training — cauți o regulă pe clasa contului, nu pe data când s-a predat.</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6802,10 +6802,85 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="61" t="inlineStr">
+        <is>
+          <t>Î-47</t>
+        </is>
+      </c>
+      <c r="B56" s="61" t="inlineStr">
+        <is>
+          <t>Declarații informative și avantaje salariale</t>
+        </is>
+      </c>
+      <c r="C56" s="61" t="inlineStr">
+        <is>
+          <t>Ce cuprinde de fapt D207 — doar veniturile plătite nerezidenților, sau și dividendele către persoane juridice rezidente?</t>
+        </is>
+      </c>
+      <c r="D56" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="61" t="inlineStr">
+        <is>
+          <t>Lista declarațiilor cu regim de rectificare din §12 și confruntarea D205 ↔ D100. Dacă D207 e strict pentru nerezidenți, atunci dividendele către persoane juridice rezidente se urmăresc pe alt drum, iar checklistul de sfârșit de an are un rând în plus sau în minus.</t>
+        </is>
+      </c>
+      <c r="F56" s="61" t="inlineStr">
+        <is>
+          <t>Am consemnat afirmația ca atare, marcată ❓, și n-am construit niciun checklist pe ea. D207 nu apare în tabelul de rectificative decât cu bifa, care e sigură.</t>
+        </is>
+      </c>
+      <c r="G56" s="61" t="inlineStr">
+        <is>
+          <t>training 31.08.2026, punctul 1</t>
+        </is>
+      </c>
+    </row>
     <row r="57">
-      <c r="A57" s="63" t="inlineStr">
-        <is>
-          <t>46 de întrebări, 23 teme. Aceeași sursă cu dist/intrebari-formator.md și cu pagina publicată — nu pot diverge.</t>
+      <c r="A57" s="61" t="inlineStr">
+        <is>
+          <t>Î-48</t>
+        </is>
+      </c>
+      <c r="B57" s="61" t="inlineStr">
+        <is>
+          <t>Declarații informative și avantaje salariale</t>
+        </is>
+      </c>
+      <c r="C57" s="61" t="inlineStr">
+        <is>
+          <t>Dacă avantajul locuinței de serviciu e neimpozabil în limita a 20% din salariul minim, ce se brutează — tot avantajul, sau doar excedentul?</t>
+        </is>
+      </c>
+      <c r="D57" s="61" t="inlineStr">
+        <is>
+          <t>MOD_SALARII
+F-413</t>
+        </is>
+      </c>
+      <c r="E57" s="61" t="inlineStr">
+        <is>
+          <t>MOD_SALARII și F-413. Cele două afirmații nu se pot împăca: dacă avantajul e neimpozabil, brutarea lui n-are obiect. Dacă se brutează tot, atunci plafonul de 20% nu mai e o scutire, ci doar un prag de raportare.</t>
+        </is>
+      </c>
+      <c r="F57" s="61" t="inlineStr">
+        <is>
+          <t>Nu am implementat brutarea. Am consemnat plafonul de 20% pe salariat și presupunerea cea mai probabilă — că se brutează DOAR excedentul peste plafon, cum se procedează la celelalte avantaje plafonate — dar am lăsat-o marcată, pentru că e o presupunere, nu o regulă citită.</t>
+        </is>
+      </c>
+      <c r="G57" s="61" t="inlineStr">
+        <is>
+          <t>training 31.08.2026, punctul 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="63" t="inlineStr">
+        <is>
+          <t>48 de întrebări, 24 teme. Aceeași sursă cu dist/intrebari-formator.md și cu pagina publicată — nu pot diverge.</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6891,7 @@
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A59:G59"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -34224,7 +34299,7 @@
       </c>
       <c r="H78" s="23" t="inlineStr">
         <is>
-          <t>D112, D100 | modul: MOD_SALARII / MOD_INCHIDERE_LUNARA</t>
+          <t>D112, D100 | modul: MOD_SALARII / MOD_INCHIDERE_LUNARA | ❓ Î-48</t>
         </is>
       </c>
     </row>
